--- a/StockInfo/otc_analysis_result.xlsx
+++ b/StockInfo/otc_analysis_result.xlsx
@@ -26943,16 +26943,8 @@
           <t>富喬</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>115.50</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>+9.5</t>
-        </is>
-      </c>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr"/>
       <c r="G4" s="4" t="n">
         <v>43402</v>
       </c>
@@ -26976,16 +26968,8 @@
           <t>世界</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>137.50</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>+12.5</t>
-        </is>
-      </c>
+      <c r="E5" s="4" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr"/>
       <c r="G5" s="4" t="n">
         <v>11419</v>
       </c>
@@ -27009,16 +26993,8 @@
           <t>金居</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>300.50</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>+27.0</t>
-        </is>
-      </c>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr"/>
       <c r="G6" s="4" t="n">
         <v>8567</v>
       </c>
@@ -27042,16 +27018,8 @@
           <t>康和證</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>16.95</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>+0.6</t>
-        </is>
-      </c>
+      <c r="E7" s="4" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr"/>
       <c r="G7" s="4" t="n">
         <v>4237</v>
       </c>
@@ -27075,16 +27043,8 @@
           <t>穩懋</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>297.50</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>+27.0</t>
-        </is>
-      </c>
+      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr"/>
       <c r="G8" s="4" t="n">
         <v>3673</v>
       </c>
@@ -27108,16 +27068,8 @@
           <t>萬潤</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>467.50</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>+42.5</t>
-        </is>
-      </c>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr"/>
       <c r="G9" s="4" t="n">
         <v>3619</v>
       </c>
@@ -27141,16 +27093,8 @@
           <t>良維</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>210.00</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>+14.0</t>
-        </is>
-      </c>
+      <c r="E10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr"/>
       <c r="G10" s="4" t="n">
         <v>3612</v>
       </c>
@@ -27174,16 +27118,8 @@
           <t>欣銓</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>158.00</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>+9.0</t>
-        </is>
-      </c>
+      <c r="E11" s="4" t="inlineStr"/>
+      <c r="F11" s="4" t="inlineStr"/>
       <c r="G11" s="4" t="n">
         <v>3237</v>
       </c>
@@ -27207,16 +27143,8 @@
           <t>茂迪</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>30.85</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>+2.8</t>
-        </is>
-      </c>
+      <c r="E12" s="4" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr"/>
       <c r="G12" s="4" t="n">
         <v>3083</v>
       </c>
@@ -27240,16 +27168,8 @@
           <t>信昌電</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>73.20</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>+6.0</t>
-        </is>
-      </c>
+      <c r="E13" s="4" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr"/>
       <c r="G13" s="4" t="n">
         <v>2947</v>
       </c>
@@ -27273,16 +27193,8 @@
           <t>中美晶</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>117.00</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>+3.5</t>
-        </is>
-      </c>
+      <c r="E14" s="4" t="inlineStr"/>
+      <c r="F14" s="4" t="inlineStr"/>
       <c r="G14" s="4" t="n">
         <v>2808</v>
       </c>
@@ -27306,16 +27218,8 @@
           <t>九豪</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>38.70</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>+3.5</t>
-        </is>
-      </c>
+      <c r="E15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr"/>
       <c r="G15" s="4" t="n">
         <v>2705</v>
       </c>
@@ -27339,16 +27243,8 @@
           <t>台燿</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>562.00</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>+23.0</t>
-        </is>
-      </c>
+      <c r="E16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr"/>
       <c r="G16" s="4" t="n">
         <v>2680</v>
       </c>
@@ -27372,16 +27268,8 @@
           <t>晟德</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>43.65</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>+1.25</t>
-        </is>
-      </c>
+      <c r="E17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr"/>
       <c r="G17" s="4" t="n">
         <v>2430</v>
       </c>
@@ -27405,16 +27293,8 @@
           <t>致和證</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>24.20</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>+0.95</t>
-        </is>
-      </c>
+      <c r="E18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr"/>
       <c r="G18" s="4" t="n">
         <v>2006</v>
       </c>
@@ -27438,16 +27318,8 @@
           <t>中光電</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>89.00</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>+2.4</t>
-        </is>
-      </c>
+      <c r="E19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr"/>
       <c r="G19" s="4" t="n">
         <v>1942</v>
       </c>
@@ -27471,16 +27343,8 @@
           <t>宏捷科</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>123.50</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>+9.0</t>
-        </is>
-      </c>
+      <c r="E20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr"/>
       <c r="G20" s="4" t="n">
         <v>1754</v>
       </c>
@@ -27504,16 +27368,8 @@
           <t>鈺創</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>60.50</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>+3.2</t>
-        </is>
-      </c>
+      <c r="E21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr"/>
       <c r="G21" s="4" t="n">
         <v>1726</v>
       </c>
@@ -27537,16 +27393,8 @@
           <t>環球晶</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>445.00</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>+20.0</t>
-        </is>
-      </c>
+      <c r="E22" s="4" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr"/>
       <c r="G22" s="4" t="n">
         <v>1698</v>
       </c>
@@ -27570,16 +27418,8 @@
           <t>光頡</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>62.80</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>+5.4</t>
-        </is>
-      </c>
+      <c r="E23" s="4" t="inlineStr"/>
+      <c r="F23" s="4" t="inlineStr"/>
       <c r="G23" s="4" t="n">
         <v>1688</v>
       </c>
@@ -27603,16 +27443,8 @@
           <t>信音</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>39.90</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>+1.35</t>
-        </is>
-      </c>
+      <c r="E24" s="4" t="inlineStr"/>
+      <c r="F24" s="4" t="inlineStr"/>
       <c r="G24" s="4" t="n">
         <v>1663</v>
       </c>
@@ -27636,16 +27468,8 @@
           <t>合晶</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>35.70</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>+1.2</t>
-        </is>
-      </c>
+      <c r="E25" s="4" t="inlineStr"/>
+      <c r="F25" s="4" t="inlineStr"/>
       <c r="G25" s="4" t="n">
         <v>1427</v>
       </c>
@@ -27669,16 +27493,8 @@
           <t>威剛</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>313.00</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>+12.5</t>
-        </is>
-      </c>
+      <c r="E26" s="4" t="inlineStr"/>
+      <c r="F26" s="4" t="inlineStr"/>
       <c r="G26" s="4" t="n">
         <v>1403</v>
       </c>
@@ -27702,16 +27518,8 @@
           <t>華星光</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>393.00</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>+35.5</t>
-        </is>
-      </c>
+      <c r="E27" s="4" t="inlineStr"/>
+      <c r="F27" s="4" t="inlineStr"/>
       <c r="G27" s="4" t="n">
         <v>1286</v>
       </c>
@@ -27735,16 +27543,8 @@
           <t>力旺</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>2385.00</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>+205.0</t>
-        </is>
-      </c>
+      <c r="E28" s="4" t="inlineStr"/>
+      <c r="F28" s="4" t="inlineStr"/>
       <c r="G28" s="4" t="n">
         <v>1252</v>
       </c>
@@ -27768,16 +27568,8 @@
           <t>邑錡</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>143.00</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>+9.0</t>
-        </is>
-      </c>
+      <c r="E29" s="4" t="inlineStr"/>
+      <c r="F29" s="4" t="inlineStr"/>
       <c r="G29" s="4" t="n">
         <v>1073</v>
       </c>
@@ -27801,16 +27593,8 @@
           <t>頎邦</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>55.70</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>+1.0</t>
-        </is>
-      </c>
+      <c r="E30" s="4" t="inlineStr"/>
+      <c r="F30" s="4" t="inlineStr"/>
       <c r="G30" s="4" t="n">
         <v>1042</v>
       </c>
@@ -27834,16 +27618,8 @@
           <t>光環</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>86.90</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>+7.9</t>
-        </is>
-      </c>
+      <c r="E31" s="4" t="inlineStr"/>
+      <c r="F31" s="4" t="inlineStr"/>
       <c r="G31" s="4" t="n">
         <v>1004</v>
       </c>
@@ -27867,16 +27643,8 @@
           <t>勤凱</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>192.00</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>+11.5</t>
-        </is>
-      </c>
+      <c r="E32" s="4" t="inlineStr"/>
+      <c r="F32" s="4" t="inlineStr"/>
       <c r="G32" s="4" t="n">
         <v>846</v>
       </c>
@@ -27900,16 +27668,8 @@
           <t>群聯</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>2070.00</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>+145.0</t>
-        </is>
-      </c>
+      <c r="E33" s="4" t="inlineStr"/>
+      <c r="F33" s="4" t="inlineStr"/>
       <c r="G33" s="4" t="n">
         <v>802</v>
       </c>
@@ -27933,16 +27693,8 @@
           <t>能率</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>46.30</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>+1.2</t>
-        </is>
-      </c>
+      <c r="E34" s="4" t="inlineStr"/>
+      <c r="F34" s="4" t="inlineStr"/>
       <c r="G34" s="4" t="n">
         <v>758</v>
       </c>
@@ -27966,16 +27718,8 @@
           <t>臺慶科</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>163.00</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>+6.0</t>
-        </is>
-      </c>
+      <c r="E35" s="4" t="inlineStr"/>
+      <c r="F35" s="4" t="inlineStr"/>
       <c r="G35" s="4" t="n">
         <v>750</v>
       </c>
@@ -27999,16 +27743,8 @@
           <t>正德</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>19.90</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>+0.1</t>
-        </is>
-      </c>
+      <c r="E36" s="4" t="inlineStr"/>
+      <c r="F36" s="4" t="inlineStr"/>
       <c r="G36" s="4" t="n">
         <v>694</v>
       </c>
@@ -28032,16 +27768,8 @@
           <t>台半</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>62.40</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>+2.3</t>
-        </is>
-      </c>
+      <c r="E37" s="4" t="inlineStr"/>
+      <c r="F37" s="4" t="inlineStr"/>
       <c r="G37" s="4" t="n">
         <v>693</v>
       </c>
@@ -28065,16 +27793,8 @@
           <t>閎康</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>214.00</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>+5.0</t>
-        </is>
-      </c>
+      <c r="E38" s="4" t="inlineStr"/>
+      <c r="F38" s="4" t="inlineStr"/>
       <c r="G38" s="4" t="n">
         <v>685</v>
       </c>
@@ -28098,16 +27818,8 @@
           <t>千如</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>32.50</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>+2.0</t>
-        </is>
-      </c>
+      <c r="E39" s="4" t="inlineStr"/>
+      <c r="F39" s="4" t="inlineStr"/>
       <c r="G39" s="4" t="n">
         <v>644</v>
       </c>
@@ -28131,16 +27843,8 @@
           <t>宏遠證</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>13.85</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>+0.4</t>
-        </is>
-      </c>
+      <c r="E40" s="4" t="inlineStr"/>
+      <c r="F40" s="4" t="inlineStr"/>
       <c r="G40" s="4" t="n">
         <v>622</v>
       </c>
@@ -28164,16 +27868,8 @@
           <t>安可</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>27.60</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>+1.4</t>
-        </is>
-      </c>
+      <c r="E41" s="4" t="inlineStr"/>
+      <c r="F41" s="4" t="inlineStr"/>
       <c r="G41" s="4" t="n">
         <v>605</v>
       </c>
@@ -28197,16 +27893,8 @@
           <t>廣穎</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>47.55</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>+1.15</t>
-        </is>
-      </c>
+      <c r="E42" s="4" t="inlineStr"/>
+      <c r="F42" s="4" t="inlineStr"/>
       <c r="G42" s="4" t="n">
         <v>605</v>
       </c>
@@ -28230,16 +27918,8 @@
           <t>英濟</t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>39.50</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>+2.3</t>
-        </is>
-      </c>
+      <c r="E43" s="4" t="inlineStr"/>
+      <c r="F43" s="4" t="inlineStr"/>
       <c r="G43" s="4" t="n">
         <v>604</v>
       </c>
@@ -28263,16 +27943,8 @@
           <t>波若威</t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>711.00</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>+64.0</t>
-        </is>
-      </c>
+      <c r="E44" s="4" t="inlineStr"/>
+      <c r="F44" s="4" t="inlineStr"/>
       <c r="G44" s="4" t="n">
         <v>586</v>
       </c>
@@ -28296,16 +27968,8 @@
           <t>世紀*</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>95.30</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>+1.9</t>
-        </is>
-      </c>
+      <c r="E45" s="4" t="inlineStr"/>
+      <c r="F45" s="4" t="inlineStr"/>
       <c r="G45" s="4" t="n">
         <v>583</v>
       </c>
@@ -28329,16 +27993,8 @@
           <t>德微</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>177.00</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>+16.0</t>
-        </is>
-      </c>
+      <c r="E46" s="4" t="inlineStr"/>
+      <c r="F46" s="4" t="inlineStr"/>
       <c r="G46" s="4" t="n">
         <v>582</v>
       </c>
@@ -28362,16 +28018,8 @@
           <t>久元</t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>75.50</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t>+2.0</t>
-        </is>
-      </c>
+      <c r="E47" s="4" t="inlineStr"/>
+      <c r="F47" s="4" t="inlineStr"/>
       <c r="G47" s="4" t="n">
         <v>579</v>
       </c>
@@ -28395,16 +28043,8 @@
           <t>立碁</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>69.70</t>
-        </is>
-      </c>
-      <c r="F48" s="4" t="inlineStr">
-        <is>
-          <t>+1.3</t>
-        </is>
-      </c>
+      <c r="E48" s="4" t="inlineStr"/>
+      <c r="F48" s="4" t="inlineStr"/>
       <c r="G48" s="4" t="n">
         <v>578</v>
       </c>
@@ -28428,16 +28068,8 @@
           <t>原相</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>205.00</t>
-        </is>
-      </c>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>+7.0</t>
-        </is>
-      </c>
+      <c r="E49" s="4" t="inlineStr"/>
+      <c r="F49" s="4" t="inlineStr"/>
       <c r="G49" s="4" t="n">
         <v>567</v>
       </c>
@@ -28461,16 +28093,8 @@
           <t>漢磊</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>56.80</t>
-        </is>
-      </c>
-      <c r="F50" s="4" t="inlineStr">
-        <is>
-          <t>+2.8</t>
-        </is>
-      </c>
+      <c r="E50" s="4" t="inlineStr"/>
+      <c r="F50" s="4" t="inlineStr"/>
       <c r="G50" s="4" t="n">
         <v>555</v>
       </c>
@@ -28494,16 +28118,8 @@
           <t>元太</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>185.50</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="inlineStr">
-        <is>
-          <t>-5.5</t>
-        </is>
-      </c>
+      <c r="E51" s="4" t="inlineStr"/>
+      <c r="F51" s="4" t="inlineStr"/>
       <c r="G51" s="4" t="n">
         <v>555</v>
       </c>
@@ -28527,16 +28143,8 @@
           <t>中探針</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>77.50</t>
-        </is>
-      </c>
-      <c r="F52" s="4" t="inlineStr">
-        <is>
-          <t>+7.0</t>
-        </is>
-      </c>
+      <c r="E52" s="4" t="inlineStr"/>
+      <c r="F52" s="4" t="inlineStr"/>
       <c r="G52" s="4" t="n">
         <v>551</v>
       </c>
@@ -28560,16 +28168,8 @@
           <t>東浦</t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>48.60</t>
-        </is>
-      </c>
-      <c r="F53" s="4" t="inlineStr">
-        <is>
-          <t>+0.95</t>
-        </is>
-      </c>
+      <c r="E53" s="4" t="inlineStr"/>
+      <c r="F53" s="4" t="inlineStr"/>
       <c r="G53" s="4" t="n">
         <v>540</v>
       </c>
@@ -28593,16 +28193,8 @@
           <t>精材</t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>183.50</t>
-        </is>
-      </c>
-      <c r="F54" s="4" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
+      <c r="E54" s="4" t="inlineStr"/>
+      <c r="F54" s="4" t="inlineStr"/>
       <c r="G54" s="4" t="n">
         <v>447</v>
       </c>
@@ -28626,16 +28218,8 @@
           <t>佳邦</t>
         </is>
       </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>84.90</t>
-        </is>
-      </c>
-      <c r="F55" s="4" t="inlineStr">
-        <is>
-          <t>+1.2</t>
-        </is>
-      </c>
+      <c r="E55" s="4" t="inlineStr"/>
+      <c r="F55" s="4" t="inlineStr"/>
       <c r="G55" s="4" t="n">
         <v>445</v>
       </c>
@@ -28659,16 +28243,8 @@
           <t>尚立</t>
         </is>
       </c>
-      <c r="E56" s="4" t="inlineStr">
-        <is>
-          <t>17.55</t>
-        </is>
-      </c>
-      <c r="F56" s="4" t="inlineStr">
-        <is>
-          <t>+1.05</t>
-        </is>
-      </c>
+      <c r="E56" s="4" t="inlineStr"/>
+      <c r="F56" s="4" t="inlineStr"/>
       <c r="G56" s="4" t="n">
         <v>440</v>
       </c>
@@ -28692,16 +28268,8 @@
           <t>由田</t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr">
-        <is>
-          <t>113.50</t>
-        </is>
-      </c>
-      <c r="F57" s="4" t="inlineStr">
-        <is>
-          <t>+5.5</t>
-        </is>
-      </c>
+      <c r="E57" s="4" t="inlineStr"/>
+      <c r="F57" s="4" t="inlineStr"/>
       <c r="G57" s="4" t="n">
         <v>435</v>
       </c>
@@ -28725,16 +28293,8 @@
           <t>晶宏</t>
         </is>
       </c>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t>50.20</t>
-        </is>
-      </c>
-      <c r="F58" s="4" t="inlineStr">
-        <is>
-          <t>+4.5</t>
-        </is>
-      </c>
+      <c r="E58" s="4" t="inlineStr"/>
+      <c r="F58" s="4" t="inlineStr"/>
       <c r="G58" s="4" t="n">
         <v>416</v>
       </c>
@@ -28758,16 +28318,8 @@
           <t>創威</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>72.10</t>
-        </is>
-      </c>
-      <c r="F59" s="4" t="inlineStr">
-        <is>
-          <t>+4.8</t>
-        </is>
-      </c>
+      <c r="E59" s="4" t="inlineStr"/>
+      <c r="F59" s="4" t="inlineStr"/>
       <c r="G59" s="4" t="n">
         <v>415</v>
       </c>
@@ -28791,16 +28343,8 @@
           <t>晟田</t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>46.65</t>
-        </is>
-      </c>
-      <c r="F60" s="4" t="inlineStr">
-        <is>
-          <t>+0.55</t>
-        </is>
-      </c>
+      <c r="E60" s="4" t="inlineStr"/>
+      <c r="F60" s="4" t="inlineStr"/>
       <c r="G60" s="4" t="n">
         <v>403</v>
       </c>
@@ -28824,16 +28368,8 @@
           <t>宜特</t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>131.00</t>
-        </is>
-      </c>
-      <c r="F61" s="4" t="inlineStr">
-        <is>
-          <t>+3.0</t>
-        </is>
-      </c>
+      <c r="E61" s="4" t="inlineStr"/>
+      <c r="F61" s="4" t="inlineStr"/>
       <c r="G61" s="4" t="n">
         <v>396</v>
       </c>
@@ -28857,16 +28393,8 @@
           <t>環宇-KY</t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr">
-        <is>
-          <t>306.00</t>
-        </is>
-      </c>
-      <c r="F62" s="4" t="inlineStr">
-        <is>
-          <t>+27.0</t>
-        </is>
-      </c>
+      <c r="E62" s="4" t="inlineStr"/>
+      <c r="F62" s="4" t="inlineStr"/>
       <c r="G62" s="4" t="n">
         <v>396</v>
       </c>
@@ -28890,16 +28418,8 @@
           <t>光洋科</t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>62.50</t>
-        </is>
-      </c>
-      <c r="F63" s="4" t="inlineStr">
-        <is>
-          <t>+0.2</t>
-        </is>
-      </c>
+      <c r="E63" s="4" t="inlineStr"/>
+      <c r="F63" s="4" t="inlineStr"/>
       <c r="G63" s="4" t="n">
         <v>386</v>
       </c>
@@ -28923,16 +28443,8 @@
           <t>品安</t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t>53.80</t>
-        </is>
-      </c>
-      <c r="F64" s="4" t="inlineStr">
-        <is>
-          <t>+0.8</t>
-        </is>
-      </c>
+      <c r="E64" s="4" t="inlineStr"/>
+      <c r="F64" s="4" t="inlineStr"/>
       <c r="G64" s="4" t="n">
         <v>385</v>
       </c>
@@ -28956,16 +28468,8 @@
           <t>永捷</t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr">
-        <is>
-          <t>17.10</t>
-        </is>
-      </c>
-      <c r="F65" s="4" t="inlineStr">
-        <is>
-          <t>-0.2</t>
-        </is>
-      </c>
+      <c r="E65" s="4" t="inlineStr"/>
+      <c r="F65" s="4" t="inlineStr"/>
       <c r="G65" s="4" t="n">
         <v>370</v>
       </c>
@@ -28989,16 +28493,8 @@
           <t>建榮</t>
         </is>
       </c>
-      <c r="E66" s="4" t="inlineStr">
-        <is>
-          <t>109.50</t>
-        </is>
-      </c>
-      <c r="F66" s="4" t="inlineStr">
-        <is>
-          <t>+8.5</t>
-        </is>
-      </c>
+      <c r="E66" s="4" t="inlineStr"/>
+      <c r="F66" s="4" t="inlineStr"/>
       <c r="G66" s="4" t="n">
         <v>370</v>
       </c>
@@ -29022,16 +28518,8 @@
           <t>神準</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>143.00</t>
-        </is>
-      </c>
-      <c r="F67" s="4" t="inlineStr">
-        <is>
-          <t>+13.0</t>
-        </is>
-      </c>
+      <c r="E67" s="4" t="inlineStr"/>
+      <c r="F67" s="4" t="inlineStr"/>
       <c r="G67" s="4" t="n">
         <v>367</v>
       </c>
@@ -29055,16 +28543,8 @@
           <t>岳豐</t>
         </is>
       </c>
-      <c r="E68" s="4" t="inlineStr">
-        <is>
-          <t>32.30</t>
-        </is>
-      </c>
-      <c r="F68" s="4" t="inlineStr">
-        <is>
-          <t>+0.75</t>
-        </is>
-      </c>
+      <c r="E68" s="4" t="inlineStr"/>
+      <c r="F68" s="4" t="inlineStr"/>
       <c r="G68" s="4" t="n">
         <v>359</v>
       </c>
@@ -29088,16 +28568,8 @@
           <t>金益鼎</t>
         </is>
       </c>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>102.00</t>
-        </is>
-      </c>
-      <c r="F69" s="4" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
+      <c r="E69" s="4" t="inlineStr"/>
+      <c r="F69" s="4" t="inlineStr"/>
       <c r="G69" s="4" t="n">
         <v>344</v>
       </c>
@@ -29121,16 +28593,8 @@
           <t>達航科技</t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr">
-        <is>
-          <t>71.60</t>
-        </is>
-      </c>
-      <c r="F70" s="4" t="inlineStr">
-        <is>
-          <t>+6.5</t>
-        </is>
-      </c>
+      <c r="E70" s="4" t="inlineStr"/>
+      <c r="F70" s="4" t="inlineStr"/>
       <c r="G70" s="4" t="n">
         <v>321</v>
       </c>
@@ -29154,16 +28618,8 @@
           <t>創惟</t>
         </is>
       </c>
-      <c r="E71" s="4" t="inlineStr">
-        <is>
-          <t>99.50</t>
-        </is>
-      </c>
-      <c r="F71" s="4" t="inlineStr">
-        <is>
-          <t>+3.1</t>
-        </is>
-      </c>
+      <c r="E71" s="4" t="inlineStr"/>
+      <c r="F71" s="4" t="inlineStr"/>
       <c r="G71" s="4" t="n">
         <v>309</v>
       </c>
@@ -29187,16 +28643,8 @@
           <t>雙鴻</t>
         </is>
       </c>
-      <c r="E72" s="4" t="inlineStr">
-        <is>
-          <t>1050.00</t>
-        </is>
-      </c>
-      <c r="F72" s="4" t="inlineStr">
-        <is>
-          <t>+35.0</t>
-        </is>
-      </c>
+      <c r="E72" s="4" t="inlineStr"/>
+      <c r="F72" s="4" t="inlineStr"/>
       <c r="G72" s="4" t="n">
         <v>308</v>
       </c>
@@ -29220,16 +28668,8 @@
           <t>光聯</t>
         </is>
       </c>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>24.85</t>
-        </is>
-      </c>
-      <c r="F73" s="4" t="inlineStr">
-        <is>
-          <t>+0.4</t>
-        </is>
-      </c>
+      <c r="E73" s="4" t="inlineStr"/>
+      <c r="F73" s="4" t="inlineStr"/>
       <c r="G73" s="4" t="n">
         <v>303</v>
       </c>
@@ -29253,16 +28693,8 @@
           <t>訊聯</t>
         </is>
       </c>
-      <c r="E74" s="4" t="inlineStr">
-        <is>
-          <t>104.50</t>
-        </is>
-      </c>
-      <c r="F74" s="4" t="inlineStr">
-        <is>
-          <t>+4.0</t>
-        </is>
-      </c>
+      <c r="E74" s="4" t="inlineStr"/>
+      <c r="F74" s="4" t="inlineStr"/>
       <c r="G74" s="4" t="n">
         <v>292</v>
       </c>
@@ -29286,16 +28718,8 @@
           <t>橘子</t>
         </is>
       </c>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>52.50</t>
-        </is>
-      </c>
-      <c r="F75" s="4" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
+      <c r="E75" s="4" t="inlineStr"/>
+      <c r="F75" s="4" t="inlineStr"/>
       <c r="G75" s="4" t="n">
         <v>291</v>
       </c>
@@ -29319,16 +28743,8 @@
           <t>鈊象</t>
         </is>
       </c>
-      <c r="E76" s="4" t="inlineStr">
-        <is>
-          <t>695.00</t>
-        </is>
-      </c>
-      <c r="F76" s="4" t="inlineStr">
-        <is>
-          <t>+14.0</t>
-        </is>
-      </c>
+      <c r="E76" s="4" t="inlineStr"/>
+      <c r="F76" s="4" t="inlineStr"/>
       <c r="G76" s="4" t="n">
         <v>278</v>
       </c>
@@ -29352,16 +28768,8 @@
           <t>晶呈科技</t>
         </is>
       </c>
-      <c r="E77" s="4" t="inlineStr">
-        <is>
-          <t>410.00</t>
-        </is>
-      </c>
-      <c r="F77" s="4" t="inlineStr">
-        <is>
-          <t>+21.5</t>
-        </is>
-      </c>
+      <c r="E77" s="4" t="inlineStr"/>
+      <c r="F77" s="4" t="inlineStr"/>
       <c r="G77" s="4" t="n">
         <v>263</v>
       </c>
@@ -29385,16 +28793,8 @@
           <t>耀勝</t>
         </is>
       </c>
-      <c r="E78" s="4" t="inlineStr">
-        <is>
-          <t>74.30</t>
-        </is>
-      </c>
-      <c r="F78" s="4" t="inlineStr">
-        <is>
-          <t>+6.7</t>
-        </is>
-      </c>
+      <c r="E78" s="4" t="inlineStr"/>
+      <c r="F78" s="4" t="inlineStr"/>
       <c r="G78" s="4" t="n">
         <v>261</v>
       </c>
@@ -29418,16 +28818,8 @@
           <t>皇將</t>
         </is>
       </c>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t>33.60</t>
-        </is>
-      </c>
-      <c r="F79" s="4" t="inlineStr">
-        <is>
-          <t>+1.25</t>
-        </is>
-      </c>
+      <c r="E79" s="4" t="inlineStr"/>
+      <c r="F79" s="4" t="inlineStr"/>
       <c r="G79" s="4" t="n">
         <v>260</v>
       </c>
@@ -29451,16 +28843,8 @@
           <t>力麒</t>
         </is>
       </c>
-      <c r="E80" s="4" t="inlineStr">
-        <is>
-          <t>7.94</t>
-        </is>
-      </c>
-      <c r="F80" s="4" t="inlineStr">
-        <is>
-          <t>+0.06</t>
-        </is>
-      </c>
+      <c r="E80" s="4" t="inlineStr"/>
+      <c r="F80" s="4" t="inlineStr"/>
       <c r="G80" s="4" t="n">
         <v>260</v>
       </c>
@@ -29484,16 +28868,8 @@
           <t>鑫龍騰</t>
         </is>
       </c>
-      <c r="E81" s="4" t="inlineStr">
-        <is>
-          <t>31.30</t>
-        </is>
-      </c>
-      <c r="F81" s="4" t="inlineStr">
-        <is>
-          <t>+0.65</t>
-        </is>
-      </c>
+      <c r="E81" s="4" t="inlineStr"/>
+      <c r="F81" s="4" t="inlineStr"/>
       <c r="G81" s="4" t="n">
         <v>247</v>
       </c>
@@ -29517,16 +28893,8 @@
           <t>寶雅</t>
         </is>
       </c>
-      <c r="E82" s="4" t="inlineStr">
-        <is>
-          <t>480.00</t>
-        </is>
-      </c>
-      <c r="F82" s="4" t="inlineStr">
-        <is>
-          <t>+22.0</t>
-        </is>
-      </c>
+      <c r="E82" s="4" t="inlineStr"/>
+      <c r="F82" s="4" t="inlineStr"/>
       <c r="G82" s="4" t="n">
         <v>241</v>
       </c>
@@ -29550,16 +28918,8 @@
           <t>福邦證</t>
         </is>
       </c>
-      <c r="E83" s="4" t="inlineStr">
-        <is>
-          <t>14.25</t>
-        </is>
-      </c>
-      <c r="F83" s="4" t="inlineStr">
-        <is>
-          <t>+0.3</t>
-        </is>
-      </c>
+      <c r="E83" s="4" t="inlineStr"/>
+      <c r="F83" s="4" t="inlineStr"/>
       <c r="G83" s="4" t="n">
         <v>227</v>
       </c>
@@ -29583,16 +28943,8 @@
           <t>台星科</t>
         </is>
       </c>
-      <c r="E84" s="4" t="inlineStr">
-        <is>
-          <t>144.50</t>
-        </is>
-      </c>
-      <c r="F84" s="4" t="inlineStr">
-        <is>
-          <t>+1.0</t>
-        </is>
-      </c>
+      <c r="E84" s="4" t="inlineStr"/>
+      <c r="F84" s="4" t="inlineStr"/>
       <c r="G84" s="4" t="n">
         <v>224</v>
       </c>
@@ -29616,16 +28968,8 @@
           <t>正淩</t>
         </is>
       </c>
-      <c r="E85" s="4" t="inlineStr">
-        <is>
-          <t>133.00</t>
-        </is>
-      </c>
-      <c r="F85" s="4" t="inlineStr">
-        <is>
-          <t>+2.0</t>
-        </is>
-      </c>
+      <c r="E85" s="4" t="inlineStr"/>
+      <c r="F85" s="4" t="inlineStr"/>
       <c r="G85" s="4" t="n">
         <v>220</v>
       </c>
@@ -29649,16 +28993,8 @@
           <t>廣閎科</t>
         </is>
       </c>
-      <c r="E86" s="4" t="inlineStr">
-        <is>
-          <t>90.70</t>
-        </is>
-      </c>
-      <c r="F86" s="4" t="inlineStr">
-        <is>
-          <t>+4.1</t>
-        </is>
-      </c>
+      <c r="E86" s="4" t="inlineStr"/>
+      <c r="F86" s="4" t="inlineStr"/>
       <c r="G86" s="4" t="n">
         <v>214</v>
       </c>
@@ -29682,16 +29018,8 @@
           <t>宜鼎</t>
         </is>
       </c>
-      <c r="E87" s="4" t="inlineStr">
-        <is>
-          <t>815.00</t>
-        </is>
-      </c>
-      <c r="F87" s="4" t="inlineStr">
-        <is>
-          <t>+57.0</t>
-        </is>
-      </c>
+      <c r="E87" s="4" t="inlineStr"/>
+      <c r="F87" s="4" t="inlineStr"/>
       <c r="G87" s="4" t="n">
         <v>212</v>
       </c>
@@ -29715,16 +29043,8 @@
           <t>振曜</t>
         </is>
       </c>
-      <c r="E88" s="4" t="inlineStr">
-        <is>
-          <t>102.00</t>
-        </is>
-      </c>
-      <c r="F88" s="4" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
+      <c r="E88" s="4" t="inlineStr"/>
+      <c r="F88" s="4" t="inlineStr"/>
       <c r="G88" s="4" t="n">
         <v>209</v>
       </c>
@@ -29748,16 +29068,8 @@
           <t>健亞</t>
         </is>
       </c>
-      <c r="E89" s="4" t="inlineStr">
-        <is>
-          <t>31.75</t>
-        </is>
-      </c>
-      <c r="F89" s="4" t="inlineStr">
-        <is>
-          <t>+1.95</t>
-        </is>
-      </c>
+      <c r="E89" s="4" t="inlineStr"/>
+      <c r="F89" s="4" t="inlineStr"/>
       <c r="G89" s="4" t="n">
         <v>206</v>
       </c>
@@ -29781,16 +29093,8 @@
           <t>新盛力</t>
         </is>
       </c>
-      <c r="E90" s="4" t="inlineStr">
-        <is>
-          <t>148.50</t>
-        </is>
-      </c>
-      <c r="F90" s="4" t="inlineStr">
-        <is>
-          <t>+5.0</t>
-        </is>
-      </c>
+      <c r="E90" s="4" t="inlineStr"/>
+      <c r="F90" s="4" t="inlineStr"/>
       <c r="G90" s="4" t="n">
         <v>204</v>
       </c>
@@ -29814,16 +29118,8 @@
           <t>精星</t>
         </is>
       </c>
-      <c r="E91" s="4" t="inlineStr">
-        <is>
-          <t>34.20</t>
-        </is>
-      </c>
-      <c r="F91" s="4" t="inlineStr">
-        <is>
-          <t>+0.75</t>
-        </is>
-      </c>
+      <c r="E91" s="4" t="inlineStr"/>
+      <c r="F91" s="4" t="inlineStr"/>
       <c r="G91" s="4" t="n">
         <v>201</v>
       </c>
@@ -29847,16 +29143,8 @@
           <t>青雲</t>
         </is>
       </c>
-      <c r="E92" s="4" t="inlineStr">
-        <is>
-          <t>192.50</t>
-        </is>
-      </c>
-      <c r="F92" s="4" t="inlineStr">
-        <is>
-          <t>+17.5</t>
-        </is>
-      </c>
+      <c r="E92" s="4" t="inlineStr"/>
+      <c r="F92" s="4" t="inlineStr"/>
       <c r="G92" s="4" t="n">
         <v>194</v>
       </c>
@@ -29880,16 +29168,8 @@
           <t>典範</t>
         </is>
       </c>
-      <c r="E93" s="4" t="inlineStr">
-        <is>
-          <t>22.10</t>
-        </is>
-      </c>
-      <c r="F93" s="4" t="inlineStr">
-        <is>
-          <t>+0.15</t>
-        </is>
-      </c>
+      <c r="E93" s="4" t="inlineStr"/>
+      <c r="F93" s="4" t="inlineStr"/>
       <c r="G93" s="4" t="n">
         <v>193</v>
       </c>
@@ -29913,16 +29193,8 @@
           <t>雷科</t>
         </is>
       </c>
-      <c r="E94" s="4" t="inlineStr">
-        <is>
-          <t>52.50</t>
-        </is>
-      </c>
-      <c r="F94" s="4" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
+      <c r="E94" s="4" t="inlineStr"/>
+      <c r="F94" s="4" t="inlineStr"/>
       <c r="G94" s="4" t="n">
         <v>180</v>
       </c>
@@ -29946,16 +29218,8 @@
           <t>朋程</t>
         </is>
       </c>
-      <c r="E95" s="4" t="inlineStr">
-        <is>
-          <t>131.50</t>
-        </is>
-      </c>
-      <c r="F95" s="4" t="inlineStr">
-        <is>
-          <t>+4.0</t>
-        </is>
-      </c>
+      <c r="E95" s="4" t="inlineStr"/>
+      <c r="F95" s="4" t="inlineStr"/>
       <c r="G95" s="4" t="n">
         <v>179</v>
       </c>
@@ -29979,16 +29243,8 @@
           <t>東捷</t>
         </is>
       </c>
-      <c r="E96" s="4" t="inlineStr">
-        <is>
-          <t>47.40</t>
-        </is>
-      </c>
-      <c r="F96" s="4" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
+      <c r="E96" s="4" t="inlineStr"/>
+      <c r="F96" s="4" t="inlineStr"/>
       <c r="G96" s="4" t="n">
         <v>178</v>
       </c>
@@ -30012,16 +29268,8 @@
           <t>方土昶</t>
         </is>
       </c>
-      <c r="E97" s="4" t="inlineStr">
-        <is>
-          <t>41.60</t>
-        </is>
-      </c>
-      <c r="F97" s="4" t="inlineStr">
-        <is>
-          <t>+1.75</t>
-        </is>
-      </c>
+      <c r="E97" s="4" t="inlineStr"/>
+      <c r="F97" s="4" t="inlineStr"/>
       <c r="G97" s="4" t="n">
         <v>161</v>
       </c>
@@ -30045,16 +29293,8 @@
           <t>廣明</t>
         </is>
       </c>
-      <c r="E98" s="4" t="inlineStr">
-        <is>
-          <t>101.50</t>
-        </is>
-      </c>
-      <c r="F98" s="4" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
+      <c r="E98" s="4" t="inlineStr"/>
+      <c r="F98" s="4" t="inlineStr"/>
       <c r="G98" s="4" t="n">
         <v>156</v>
       </c>
@@ -30078,16 +29318,8 @@
           <t>西勝</t>
         </is>
       </c>
-      <c r="E99" s="4" t="inlineStr">
-        <is>
-          <t>19.05</t>
-        </is>
-      </c>
-      <c r="F99" s="4" t="inlineStr">
-        <is>
-          <t>+0.05</t>
-        </is>
-      </c>
+      <c r="E99" s="4" t="inlineStr"/>
+      <c r="F99" s="4" t="inlineStr"/>
       <c r="G99" s="4" t="n">
         <v>153</v>
       </c>
@@ -30111,16 +29343,8 @@
           <t>亞電</t>
         </is>
       </c>
-      <c r="E100" s="4" t="inlineStr">
-        <is>
-          <t>35.30</t>
-        </is>
-      </c>
-      <c r="F100" s="4" t="inlineStr">
-        <is>
-          <t>+0.9</t>
-        </is>
-      </c>
+      <c r="E100" s="4" t="inlineStr"/>
+      <c r="F100" s="4" t="inlineStr"/>
       <c r="G100" s="4" t="n">
         <v>151</v>
       </c>
@@ -30144,16 +29368,8 @@
           <t>太欣</t>
         </is>
       </c>
-      <c r="E101" s="4" t="inlineStr">
-        <is>
-          <t>12.45</t>
-        </is>
-      </c>
-      <c r="F101" s="4" t="inlineStr">
-        <is>
-          <t>+1.1</t>
-        </is>
-      </c>
+      <c r="E101" s="4" t="inlineStr"/>
+      <c r="F101" s="4" t="inlineStr"/>
       <c r="G101" s="4" t="n">
         <v>149</v>
       </c>
@@ -30177,16 +29393,8 @@
           <t>神盾</t>
         </is>
       </c>
-      <c r="E102" s="4" t="inlineStr">
-        <is>
-          <t>114.00</t>
-        </is>
-      </c>
-      <c r="F102" s="4" t="inlineStr">
-        <is>
-          <t>+1.5</t>
-        </is>
-      </c>
+      <c r="E102" s="4" t="inlineStr"/>
+      <c r="F102" s="4" t="inlineStr"/>
       <c r="G102" s="4" t="n">
         <v>144</v>
       </c>
@@ -30210,16 +29418,8 @@
           <t>單井</t>
         </is>
       </c>
-      <c r="E103" s="4" t="inlineStr">
-        <is>
-          <t>24.75</t>
-        </is>
-      </c>
-      <c r="F103" s="4" t="inlineStr">
-        <is>
-          <t>+0.35</t>
-        </is>
-      </c>
+      <c r="E103" s="4" t="inlineStr"/>
+      <c r="F103" s="4" t="inlineStr"/>
       <c r="G103" s="4" t="n">
         <v>133</v>
       </c>
@@ -30320,16 +29520,8 @@
           <t>協易機</t>
         </is>
       </c>
-      <c r="E109" s="4" t="inlineStr">
-        <is>
-          <t>34.75</t>
-        </is>
-      </c>
-      <c r="F109" s="4" t="inlineStr">
-        <is>
-          <t>+1.9</t>
-        </is>
-      </c>
+      <c r="E109" s="4" t="inlineStr"/>
+      <c r="F109" s="4" t="inlineStr"/>
       <c r="G109" s="4" t="n">
         <v>-3901</v>
       </c>
@@ -30353,16 +29545,8 @@
           <t>華電網</t>
         </is>
       </c>
-      <c r="E110" s="4" t="inlineStr">
-        <is>
-          <t>56.30</t>
-        </is>
-      </c>
-      <c r="F110" s="4" t="inlineStr">
-        <is>
-          <t>-0.3</t>
-        </is>
-      </c>
+      <c r="E110" s="4" t="inlineStr"/>
+      <c r="F110" s="4" t="inlineStr"/>
       <c r="G110" s="4" t="n">
         <v>-3591</v>
       </c>
@@ -30386,16 +29570,8 @@
           <t>泰茂</t>
         </is>
       </c>
-      <c r="E111" s="4" t="inlineStr">
-        <is>
-          <t>45.30</t>
-        </is>
-      </c>
-      <c r="F111" s="4" t="inlineStr">
-        <is>
-          <t>-5.0</t>
-        </is>
-      </c>
+      <c r="E111" s="4" t="inlineStr"/>
+      <c r="F111" s="4" t="inlineStr"/>
       <c r="G111" s="4" t="n">
         <v>-2230</v>
       </c>
@@ -30419,16 +29595,8 @@
           <t>南仁湖</t>
         </is>
       </c>
-      <c r="E112" s="4" t="inlineStr">
-        <is>
-          <t>8.78</t>
-        </is>
-      </c>
-      <c r="F112" s="4" t="inlineStr">
-        <is>
-          <t>-0.14</t>
-        </is>
-      </c>
+      <c r="E112" s="4" t="inlineStr"/>
+      <c r="F112" s="4" t="inlineStr"/>
       <c r="G112" s="4" t="n">
         <v>-1696</v>
       </c>
@@ -30452,16 +29620,8 @@
           <t>華容</t>
         </is>
       </c>
-      <c r="E113" s="4" t="inlineStr">
-        <is>
-          <t>29.45</t>
-        </is>
-      </c>
-      <c r="F113" s="4" t="inlineStr">
-        <is>
-          <t>+2.65</t>
-        </is>
-      </c>
+      <c r="E113" s="4" t="inlineStr"/>
+      <c r="F113" s="4" t="inlineStr"/>
       <c r="G113" s="4" t="n">
         <v>-1222</v>
       </c>
@@ -30485,16 +29645,8 @@
           <t>精確</t>
         </is>
       </c>
-      <c r="E114" s="4" t="inlineStr">
-        <is>
-          <t>57.00</t>
-        </is>
-      </c>
-      <c r="F114" s="4" t="inlineStr">
-        <is>
-          <t>-1.3</t>
-        </is>
-      </c>
+      <c r="E114" s="4" t="inlineStr"/>
+      <c r="F114" s="4" t="inlineStr"/>
       <c r="G114" s="4" t="n">
         <v>-1024</v>
       </c>
@@ -30518,16 +29670,8 @@
           <t>加百裕</t>
         </is>
       </c>
-      <c r="E115" s="4" t="inlineStr">
-        <is>
-          <t>38.15</t>
-        </is>
-      </c>
-      <c r="F115" s="4" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
+      <c r="E115" s="4" t="inlineStr"/>
+      <c r="F115" s="4" t="inlineStr"/>
       <c r="G115" s="4" t="n">
         <v>-1014</v>
       </c>
@@ -30551,16 +29695,8 @@
           <t>榮剛</t>
         </is>
       </c>
-      <c r="E116" s="4" t="inlineStr">
-        <is>
-          <t>34.90</t>
-        </is>
-      </c>
-      <c r="F116" s="4" t="inlineStr">
-        <is>
-          <t>-0.55</t>
-        </is>
-      </c>
+      <c r="E116" s="4" t="inlineStr"/>
+      <c r="F116" s="4" t="inlineStr"/>
       <c r="G116" s="4" t="n">
         <v>-945</v>
       </c>
@@ -30584,16 +29720,8 @@
           <t>凱崴</t>
         </is>
       </c>
-      <c r="E117" s="4" t="inlineStr">
-        <is>
-          <t>64.10</t>
-        </is>
-      </c>
-      <c r="F117" s="4" t="inlineStr">
-        <is>
-          <t>+5.1</t>
-        </is>
-      </c>
+      <c r="E117" s="4" t="inlineStr"/>
+      <c r="F117" s="4" t="inlineStr"/>
       <c r="G117" s="4" t="n">
         <v>-831</v>
       </c>
@@ -30617,16 +29745,8 @@
           <t>長科*</t>
         </is>
       </c>
-      <c r="E118" s="4" t="inlineStr">
-        <is>
-          <t>48.35</t>
-        </is>
-      </c>
-      <c r="F118" s="4" t="inlineStr">
-        <is>
-          <t>+0.45</t>
-        </is>
-      </c>
+      <c r="E118" s="4" t="inlineStr"/>
+      <c r="F118" s="4" t="inlineStr"/>
       <c r="G118" s="4" t="n">
         <v>-785</v>
       </c>
@@ -30650,16 +29770,8 @@
           <t>奇鈦科</t>
         </is>
       </c>
-      <c r="E119" s="4" t="inlineStr">
-        <is>
-          <t>77.90</t>
-        </is>
-      </c>
-      <c r="F119" s="4" t="inlineStr">
-        <is>
-          <t>+4.2</t>
-        </is>
-      </c>
+      <c r="E119" s="4" t="inlineStr"/>
+      <c r="F119" s="4" t="inlineStr"/>
       <c r="G119" s="4" t="n">
         <v>-762</v>
       </c>
@@ -30683,16 +29795,8 @@
           <t>蜜望實</t>
         </is>
       </c>
-      <c r="E120" s="4" t="inlineStr">
-        <is>
-          <t>76.60</t>
-        </is>
-      </c>
-      <c r="F120" s="4" t="inlineStr">
-        <is>
-          <t>+1.9</t>
-        </is>
-      </c>
+      <c r="E120" s="4" t="inlineStr"/>
+      <c r="F120" s="4" t="inlineStr"/>
       <c r="G120" s="4" t="n">
         <v>-706</v>
       </c>
@@ -30716,16 +29820,8 @@
           <t>系統電</t>
         </is>
       </c>
-      <c r="E121" s="4" t="inlineStr">
-        <is>
-          <t>68.10</t>
-        </is>
-      </c>
-      <c r="F121" s="4" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
+      <c r="E121" s="4" t="inlineStr"/>
+      <c r="F121" s="4" t="inlineStr"/>
       <c r="G121" s="4" t="n">
         <v>-701</v>
       </c>
@@ -30749,16 +29845,8 @@
           <t>亞通</t>
         </is>
       </c>
-      <c r="E122" s="4" t="inlineStr">
-        <is>
-          <t>25.30</t>
-        </is>
-      </c>
-      <c r="F122" s="4" t="inlineStr">
-        <is>
-          <t>-0.9</t>
-        </is>
-      </c>
+      <c r="E122" s="4" t="inlineStr"/>
+      <c r="F122" s="4" t="inlineStr"/>
       <c r="G122" s="4" t="n">
         <v>-691</v>
       </c>
@@ -30782,16 +29870,8 @@
           <t>旺矽</t>
         </is>
       </c>
-      <c r="E123" s="4" t="inlineStr">
-        <is>
-          <t>2650.00</t>
-        </is>
-      </c>
-      <c r="F123" s="4" t="inlineStr">
-        <is>
-          <t>-155.0</t>
-        </is>
-      </c>
+      <c r="E123" s="4" t="inlineStr"/>
+      <c r="F123" s="4" t="inlineStr"/>
       <c r="G123" s="4" t="n">
         <v>-678</v>
       </c>
@@ -30815,16 +29895,8 @@
           <t>順達</t>
         </is>
       </c>
-      <c r="E124" s="4" t="inlineStr">
-        <is>
-          <t>286.50</t>
-        </is>
-      </c>
-      <c r="F124" s="4" t="inlineStr">
-        <is>
-          <t>+6.5</t>
-        </is>
-      </c>
+      <c r="E124" s="4" t="inlineStr"/>
+      <c r="F124" s="4" t="inlineStr"/>
       <c r="G124" s="4" t="n">
         <v>-658</v>
       </c>
@@ -30848,16 +29920,8 @@
           <t>新復興</t>
         </is>
       </c>
-      <c r="E125" s="4" t="inlineStr">
-        <is>
-          <t>62.50</t>
-        </is>
-      </c>
-      <c r="F125" s="4" t="inlineStr">
-        <is>
-          <t>+5.2</t>
-        </is>
-      </c>
+      <c r="E125" s="4" t="inlineStr"/>
+      <c r="F125" s="4" t="inlineStr"/>
       <c r="G125" s="4" t="n">
         <v>-598</v>
       </c>
@@ -30881,16 +29945,8 @@
           <t>大樹</t>
         </is>
       </c>
-      <c r="E126" s="4" t="inlineStr">
-        <is>
-          <t>87.10</t>
-        </is>
-      </c>
-      <c r="F126" s="4" t="inlineStr">
-        <is>
-          <t>-1.1</t>
-        </is>
-      </c>
+      <c r="E126" s="4" t="inlineStr"/>
+      <c r="F126" s="4" t="inlineStr"/>
       <c r="G126" s="4" t="n">
         <v>-548</v>
       </c>
@@ -30914,16 +29970,8 @@
           <t>聯光通</t>
         </is>
       </c>
-      <c r="E127" s="4" t="inlineStr">
-        <is>
-          <t>42.85</t>
-        </is>
-      </c>
-      <c r="F127" s="4" t="inlineStr">
-        <is>
-          <t>+0.7</t>
-        </is>
-      </c>
+      <c r="E127" s="4" t="inlineStr"/>
+      <c r="F127" s="4" t="inlineStr"/>
       <c r="G127" s="4" t="n">
         <v>-540</v>
       </c>
@@ -30947,16 +29995,8 @@
           <t>永信建</t>
         </is>
       </c>
-      <c r="E128" s="4" t="inlineStr">
-        <is>
-          <t>56.50</t>
-        </is>
-      </c>
-      <c r="F128" s="4" t="inlineStr">
-        <is>
-          <t>-1.3</t>
-        </is>
-      </c>
+      <c r="E128" s="4" t="inlineStr"/>
+      <c r="F128" s="4" t="inlineStr"/>
       <c r="G128" s="4" t="n">
         <v>-521</v>
       </c>
@@ -30980,16 +30020,8 @@
           <t>僑威</t>
         </is>
       </c>
-      <c r="E129" s="4" t="inlineStr">
-        <is>
-          <t>61.10</t>
-        </is>
-      </c>
-      <c r="F129" s="4" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
+      <c r="E129" s="4" t="inlineStr"/>
+      <c r="F129" s="4" t="inlineStr"/>
       <c r="G129" s="4" t="n">
         <v>-514</v>
       </c>
@@ -31013,16 +30045,8 @@
           <t>北基</t>
         </is>
       </c>
-      <c r="E130" s="4" t="inlineStr">
-        <is>
-          <t>23.80</t>
-        </is>
-      </c>
-      <c r="F130" s="4" t="inlineStr">
-        <is>
-          <t>-0.2</t>
-        </is>
-      </c>
+      <c r="E130" s="4" t="inlineStr"/>
+      <c r="F130" s="4" t="inlineStr"/>
       <c r="G130" s="4" t="n">
         <v>-469</v>
       </c>
@@ -31046,16 +30070,8 @@
           <t>太景*-KY</t>
         </is>
       </c>
-      <c r="E131" s="4" t="inlineStr">
-        <is>
-          <t>12.45</t>
-        </is>
-      </c>
-      <c r="F131" s="4" t="inlineStr">
-        <is>
-          <t>+0.1</t>
-        </is>
-      </c>
+      <c r="E131" s="4" t="inlineStr"/>
+      <c r="F131" s="4" t="inlineStr"/>
       <c r="G131" s="4" t="n">
         <v>-452</v>
       </c>
@@ -31079,16 +30095,8 @@
           <t>富強鑫</t>
         </is>
       </c>
-      <c r="E132" s="4" t="inlineStr">
-        <is>
-          <t>25.40</t>
-        </is>
-      </c>
-      <c r="F132" s="4" t="inlineStr">
-        <is>
-          <t>+1.15</t>
-        </is>
-      </c>
+      <c r="E132" s="4" t="inlineStr"/>
+      <c r="F132" s="4" t="inlineStr"/>
       <c r="G132" s="4" t="n">
         <v>-437</v>
       </c>
@@ -31112,16 +30120,8 @@
           <t>鉅橡</t>
         </is>
       </c>
-      <c r="E133" s="4" t="inlineStr">
-        <is>
-          <t>68.70</t>
-        </is>
-      </c>
-      <c r="F133" s="4" t="inlineStr">
-        <is>
-          <t>+3.4</t>
-        </is>
-      </c>
+      <c r="E133" s="4" t="inlineStr"/>
+      <c r="F133" s="4" t="inlineStr"/>
       <c r="G133" s="4" t="n">
         <v>-433</v>
       </c>
@@ -31145,16 +30145,8 @@
           <t>大江</t>
         </is>
       </c>
-      <c r="E134" s="4" t="inlineStr">
-        <is>
-          <t>136.00</t>
-        </is>
-      </c>
-      <c r="F134" s="4" t="inlineStr">
-        <is>
-          <t>-4.5</t>
-        </is>
-      </c>
+      <c r="E134" s="4" t="inlineStr"/>
+      <c r="F134" s="4" t="inlineStr"/>
       <c r="G134" s="4" t="n">
         <v>-412</v>
       </c>
@@ -31178,16 +30170,8 @@
           <t>金山電</t>
         </is>
       </c>
-      <c r="E135" s="4" t="inlineStr">
-        <is>
-          <t>60.90</t>
-        </is>
-      </c>
-      <c r="F135" s="4" t="inlineStr">
-        <is>
-          <t>+1.8</t>
-        </is>
-      </c>
+      <c r="E135" s="4" t="inlineStr"/>
+      <c r="F135" s="4" t="inlineStr"/>
       <c r="G135" s="4" t="n">
         <v>-404</v>
       </c>
@@ -31211,16 +30195,8 @@
           <t>湧德</t>
         </is>
       </c>
-      <c r="E136" s="4" t="inlineStr">
-        <is>
-          <t>120.00</t>
-        </is>
-      </c>
-      <c r="F136" s="4" t="inlineStr">
-        <is>
-          <t>+1.5</t>
-        </is>
-      </c>
+      <c r="E136" s="4" t="inlineStr"/>
+      <c r="F136" s="4" t="inlineStr"/>
       <c r="G136" s="4" t="n">
         <v>-397</v>
       </c>
@@ -31244,16 +30220,8 @@
           <t>萬泰科</t>
         </is>
       </c>
-      <c r="E137" s="4" t="inlineStr">
-        <is>
-          <t>51.60</t>
-        </is>
-      </c>
-      <c r="F137" s="4" t="inlineStr">
-        <is>
-          <t>+0.7</t>
-        </is>
-      </c>
+      <c r="E137" s="4" t="inlineStr"/>
+      <c r="F137" s="4" t="inlineStr"/>
       <c r="G137" s="4" t="n">
         <v>-388</v>
       </c>
@@ -31277,16 +30245,8 @@
           <t>德宏</t>
         </is>
       </c>
-      <c r="E138" s="4" t="inlineStr">
-        <is>
-          <t>196.50</t>
-        </is>
-      </c>
-      <c r="F138" s="4" t="inlineStr">
-        <is>
-          <t>+17.5</t>
-        </is>
-      </c>
+      <c r="E138" s="4" t="inlineStr"/>
+      <c r="F138" s="4" t="inlineStr"/>
       <c r="G138" s="4" t="n">
         <v>-371</v>
       </c>
@@ -31310,16 +30270,8 @@
           <t>正基</t>
         </is>
       </c>
-      <c r="E139" s="4" t="inlineStr">
-        <is>
-          <t>65.30</t>
-        </is>
-      </c>
-      <c r="F139" s="4" t="inlineStr">
-        <is>
-          <t>+0.6</t>
-        </is>
-      </c>
+      <c r="E139" s="4" t="inlineStr"/>
+      <c r="F139" s="4" t="inlineStr"/>
       <c r="G139" s="4" t="n">
         <v>-369</v>
       </c>
@@ -31343,16 +30295,8 @@
           <t>上詮</t>
         </is>
       </c>
-      <c r="E140" s="4" t="inlineStr">
-        <is>
-          <t>551.00</t>
-        </is>
-      </c>
-      <c r="F140" s="4" t="inlineStr">
-        <is>
-          <t>+50.0</t>
-        </is>
-      </c>
+      <c r="E140" s="4" t="inlineStr"/>
+      <c r="F140" s="4" t="inlineStr"/>
       <c r="G140" s="4" t="n">
         <v>-323</v>
       </c>
@@ -31376,16 +30320,8 @@
           <t>聚和</t>
         </is>
       </c>
-      <c r="E141" s="4" t="inlineStr">
-        <is>
-          <t>39.40</t>
-        </is>
-      </c>
-      <c r="F141" s="4" t="inlineStr">
-        <is>
-          <t>-0.75</t>
-        </is>
-      </c>
+      <c r="E141" s="4" t="inlineStr"/>
+      <c r="F141" s="4" t="inlineStr"/>
       <c r="G141" s="4" t="n">
         <v>-315</v>
       </c>
@@ -31409,16 +30345,8 @@
           <t>立端</t>
         </is>
       </c>
-      <c r="E142" s="4" t="inlineStr">
-        <is>
-          <t>61.70</t>
-        </is>
-      </c>
-      <c r="F142" s="4" t="inlineStr">
-        <is>
-          <t>-0.8</t>
-        </is>
-      </c>
+      <c r="E142" s="4" t="inlineStr"/>
+      <c r="F142" s="4" t="inlineStr"/>
       <c r="G142" s="4" t="n">
         <v>-309</v>
       </c>
@@ -31442,16 +30370,8 @@
           <t>高端疫苗</t>
         </is>
       </c>
-      <c r="E143" s="4" t="inlineStr">
-        <is>
-          <t>35.95</t>
-        </is>
-      </c>
-      <c r="F143" s="4" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
+      <c r="E143" s="4" t="inlineStr"/>
+      <c r="F143" s="4" t="inlineStr"/>
       <c r="G143" s="4" t="n">
         <v>-293</v>
       </c>
@@ -31475,16 +30395,8 @@
           <t>鑫科</t>
         </is>
       </c>
-      <c r="E144" s="4" t="inlineStr">
-        <is>
-          <t>64.90</t>
-        </is>
-      </c>
-      <c r="F144" s="4" t="inlineStr">
-        <is>
-          <t>-1.4</t>
-        </is>
-      </c>
+      <c r="E144" s="4" t="inlineStr"/>
+      <c r="F144" s="4" t="inlineStr"/>
       <c r="G144" s="4" t="n">
         <v>-291</v>
       </c>
@@ -31508,16 +30420,8 @@
           <t>緯軟</t>
         </is>
       </c>
-      <c r="E145" s="4" t="inlineStr">
-        <is>
-          <t>113.50</t>
-        </is>
-      </c>
-      <c r="F145" s="4" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
+      <c r="E145" s="4" t="inlineStr"/>
+      <c r="F145" s="4" t="inlineStr"/>
       <c r="G145" s="4" t="n">
         <v>-254</v>
       </c>
@@ -31541,16 +30445,8 @@
           <t>沛亨</t>
         </is>
       </c>
-      <c r="E146" s="4" t="inlineStr">
-        <is>
-          <t>290.00</t>
-        </is>
-      </c>
-      <c r="F146" s="4" t="inlineStr">
-        <is>
-          <t>+8.0</t>
-        </is>
-      </c>
+      <c r="E146" s="4" t="inlineStr"/>
+      <c r="F146" s="4" t="inlineStr"/>
       <c r="G146" s="4" t="n">
         <v>-240</v>
       </c>
@@ -31574,16 +30470,8 @@
           <t>萬旭</t>
         </is>
       </c>
-      <c r="E147" s="4" t="inlineStr">
-        <is>
-          <t>33.15</t>
-        </is>
-      </c>
-      <c r="F147" s="4" t="inlineStr">
-        <is>
-          <t>+1.6</t>
-        </is>
-      </c>
+      <c r="E147" s="4" t="inlineStr"/>
+      <c r="F147" s="4" t="inlineStr"/>
       <c r="G147" s="4" t="n">
         <v>-235</v>
       </c>
@@ -31607,16 +30495,8 @@
           <t>大中</t>
         </is>
       </c>
-      <c r="E148" s="4" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
-      </c>
-      <c r="F148" s="4" t="inlineStr">
-        <is>
-          <t>-3.5</t>
-        </is>
-      </c>
+      <c r="E148" s="4" t="inlineStr"/>
+      <c r="F148" s="4" t="inlineStr"/>
       <c r="G148" s="4" t="n">
         <v>-227</v>
       </c>
@@ -31640,16 +30520,8 @@
           <t>世禾</t>
         </is>
       </c>
-      <c r="E149" s="4" t="inlineStr">
-        <is>
-          <t>183.00</t>
-        </is>
-      </c>
-      <c r="F149" s="4" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
+      <c r="E149" s="4" t="inlineStr"/>
+      <c r="F149" s="4" t="inlineStr"/>
       <c r="G149" s="4" t="n">
         <v>-208</v>
       </c>
@@ -31673,16 +30545,8 @@
           <t>尚凡*</t>
         </is>
       </c>
-      <c r="E150" s="4" t="inlineStr">
-        <is>
-          <t>28.75</t>
-        </is>
-      </c>
-      <c r="F150" s="4" t="inlineStr">
-        <is>
-          <t>+0.95</t>
-        </is>
-      </c>
+      <c r="E150" s="4" t="inlineStr"/>
+      <c r="F150" s="4" t="inlineStr"/>
       <c r="G150" s="4" t="n">
         <v>-205</v>
       </c>
@@ -31706,16 +30570,8 @@
           <t>穩得</t>
         </is>
       </c>
-      <c r="E151" s="4" t="inlineStr">
-        <is>
-          <t>152.50</t>
-        </is>
-      </c>
-      <c r="F151" s="4" t="inlineStr">
-        <is>
-          <t>-3.5</t>
-        </is>
-      </c>
+      <c r="E151" s="4" t="inlineStr"/>
+      <c r="F151" s="4" t="inlineStr"/>
       <c r="G151" s="4" t="n">
         <v>-204</v>
       </c>
@@ -31739,16 +30595,8 @@
           <t>浩鼎</t>
         </is>
       </c>
-      <c r="E152" s="4" t="inlineStr">
-        <is>
-          <t>41.70</t>
-        </is>
-      </c>
-      <c r="F152" s="4" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
+      <c r="E152" s="4" t="inlineStr"/>
+      <c r="F152" s="4" t="inlineStr"/>
       <c r="G152" s="4" t="n">
         <v>-202</v>
       </c>
@@ -31772,16 +30620,8 @@
           <t>元創精密</t>
         </is>
       </c>
-      <c r="E153" s="4" t="inlineStr">
-        <is>
-          <t>37.00</t>
-        </is>
-      </c>
-      <c r="F153" s="4" t="inlineStr">
-        <is>
-          <t>-0.8</t>
-        </is>
-      </c>
+      <c r="E153" s="4" t="inlineStr"/>
+      <c r="F153" s="4" t="inlineStr"/>
       <c r="G153" s="4" t="n">
         <v>-198</v>
       </c>
@@ -31805,16 +30645,8 @@
           <t>泰藝</t>
         </is>
       </c>
-      <c r="E154" s="4" t="inlineStr">
-        <is>
-          <t>31.05</t>
-        </is>
-      </c>
-      <c r="F154" s="4" t="inlineStr">
-        <is>
-          <t>+1.95</t>
-        </is>
-      </c>
+      <c r="E154" s="4" t="inlineStr"/>
+      <c r="F154" s="4" t="inlineStr"/>
       <c r="G154" s="4" t="n">
         <v>-195</v>
       </c>
@@ -31838,16 +30670,8 @@
           <t>九齊</t>
         </is>
       </c>
-      <c r="E155" s="4" t="inlineStr">
-        <is>
-          <t>48.40</t>
-        </is>
-      </c>
-      <c r="F155" s="4" t="inlineStr">
-        <is>
-          <t>+2.35</t>
-        </is>
-      </c>
+      <c r="E155" s="4" t="inlineStr"/>
+      <c r="F155" s="4" t="inlineStr"/>
       <c r="G155" s="4" t="n">
         <v>-184</v>
       </c>
@@ -31871,16 +30695,8 @@
           <t>寶德</t>
         </is>
       </c>
-      <c r="E156" s="4" t="inlineStr">
-        <is>
-          <t>29.90</t>
-        </is>
-      </c>
-      <c r="F156" s="4" t="inlineStr">
-        <is>
-          <t>-0.65</t>
-        </is>
-      </c>
+      <c r="E156" s="4" t="inlineStr"/>
+      <c r="F156" s="4" t="inlineStr"/>
       <c r="G156" s="4" t="n">
         <v>-179</v>
       </c>
@@ -31904,16 +30720,8 @@
           <t>聯亞</t>
         </is>
       </c>
-      <c r="E157" s="4" t="inlineStr">
-        <is>
-          <t>1265.00</t>
-        </is>
-      </c>
-      <c r="F157" s="4" t="inlineStr">
-        <is>
-          <t>+75.0</t>
-        </is>
-      </c>
+      <c r="E157" s="4" t="inlineStr"/>
+      <c r="F157" s="4" t="inlineStr"/>
       <c r="G157" s="4" t="n">
         <v>-171</v>
       </c>
@@ -31937,16 +30745,8 @@
           <t>南俊國際</t>
         </is>
       </c>
-      <c r="E158" s="4" t="inlineStr">
-        <is>
-          <t>434.50</t>
-        </is>
-      </c>
-      <c r="F158" s="4" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
+      <c r="E158" s="4" t="inlineStr"/>
+      <c r="F158" s="4" t="inlineStr"/>
       <c r="G158" s="4" t="n">
         <v>-168</v>
       </c>

--- a/StockInfo/otc_analysis_result.xlsx
+++ b/StockInfo/otc_analysis_result.xlsx
@@ -26614,16 +26614,8 @@
           <t>富喬</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>102.00</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>+5.4</t>
-        </is>
-      </c>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr"/>
       <c r="G4" s="4" t="n">
         <v>6770</v>
       </c>
@@ -26647,16 +26639,8 @@
           <t>世界</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>121.00</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>+11.0</t>
-        </is>
-      </c>
+      <c r="E5" s="4" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr"/>
       <c r="G5" s="4" t="n">
         <v>5026</v>
       </c>
@@ -26680,16 +26664,8 @@
           <t>穩懋</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>407.00</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>+31.0</t>
-        </is>
-      </c>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr"/>
       <c r="G6" s="4" t="n">
         <v>4172</v>
       </c>
@@ -26713,16 +26689,8 @@
           <t>金居</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>243.50</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>+13.5</t>
-        </is>
-      </c>
+      <c r="E7" s="4" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr"/>
       <c r="G7" s="4" t="n">
         <v>3378</v>
       </c>
@@ -26746,16 +26714,8 @@
           <t>萬泰科</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>55.50</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>+2.3</t>
-        </is>
-      </c>
+      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr"/>
       <c r="G8" s="4" t="n">
         <v>3275</v>
       </c>
@@ -26779,16 +26739,8 @@
           <t>宏捷科</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>138.00</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>+12.5</t>
-        </is>
-      </c>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr"/>
       <c r="G9" s="4" t="n">
         <v>3111</v>
       </c>
@@ -26812,16 +26764,8 @@
           <t>頎邦</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>89.80</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>+5.8</t>
-        </is>
-      </c>
+      <c r="E10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr"/>
       <c r="G10" s="4" t="n">
         <v>2539</v>
       </c>
@@ -26845,16 +26789,8 @@
           <t>台半</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>58.60</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>+5.3</t>
-        </is>
-      </c>
+      <c r="E11" s="4" t="inlineStr"/>
+      <c r="F11" s="4" t="inlineStr"/>
       <c r="G11" s="4" t="n">
         <v>1999</v>
       </c>
@@ -26878,16 +26814,8 @@
           <t>擎亞</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>94.00</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>+4.8</t>
-        </is>
-      </c>
+      <c r="E12" s="4" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr"/>
       <c r="G12" s="4" t="n">
         <v>1431</v>
       </c>
@@ -26911,16 +26839,8 @@
           <t>順達</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>357.00</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>+25.0</t>
-        </is>
-      </c>
+      <c r="E13" s="4" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr"/>
       <c r="G13" s="4" t="n">
         <v>1315</v>
       </c>
@@ -26944,16 +26864,8 @@
           <t>茂迪</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>25.45</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>+0.25</t>
-        </is>
-      </c>
+      <c r="E14" s="4" t="inlineStr"/>
+      <c r="F14" s="4" t="inlineStr"/>
       <c r="G14" s="4" t="n">
         <v>1092</v>
       </c>
@@ -26977,16 +26889,8 @@
           <t>台燿</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>683.00</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>+62.0</t>
-        </is>
-      </c>
+      <c r="E15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr"/>
       <c r="G15" s="4" t="n">
         <v>939</v>
       </c>
@@ -27010,16 +26914,8 @@
           <t>建榮</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>109.50</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>+8.5</t>
-        </is>
-      </c>
+      <c r="E16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr"/>
       <c r="G16" s="4" t="n">
         <v>913</v>
       </c>
@@ -27043,16 +26939,8 @@
           <t>北基</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>25.20</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>+1.5</t>
-        </is>
-      </c>
+      <c r="E17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr"/>
       <c r="G17" s="4" t="n">
         <v>908</v>
       </c>
@@ -27076,16 +26964,8 @@
           <t>精確</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>61.00</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>+2.2</t>
-        </is>
-      </c>
+      <c r="E18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr"/>
       <c r="G18" s="4" t="n">
         <v>750</v>
       </c>
@@ -27109,16 +26989,8 @@
           <t>世紀*</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>78.90</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>+3.6</t>
-        </is>
-      </c>
+      <c r="E19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr"/>
       <c r="G19" s="4" t="n">
         <v>664</v>
       </c>
@@ -27142,16 +27014,8 @@
           <t>光環</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>87.10</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>+4.0</t>
-        </is>
-      </c>
+      <c r="E20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr"/>
       <c r="G20" s="4" t="n">
         <v>582</v>
       </c>
@@ -27175,16 +27039,8 @@
           <t>立端</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>70.50</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>+1.0</t>
-        </is>
-      </c>
+      <c r="E21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr"/>
       <c r="G21" s="4" t="n">
         <v>515</v>
       </c>
@@ -27208,16 +27064,8 @@
           <t>廣明</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>86.90</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>+1.4</t>
-        </is>
-      </c>
+      <c r="E22" s="4" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr"/>
       <c r="G22" s="4" t="n">
         <v>456</v>
       </c>
@@ -27241,16 +27089,8 @@
           <t>聯光通</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>44.95</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>+1.1</t>
-        </is>
-      </c>
+      <c r="E23" s="4" t="inlineStr"/>
+      <c r="F23" s="4" t="inlineStr"/>
       <c r="G23" s="4" t="n">
         <v>437</v>
       </c>
@@ -27274,16 +27114,8 @@
           <t>鈊象</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>775.00</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>+20.0</t>
-        </is>
-      </c>
+      <c r="E24" s="4" t="inlineStr"/>
+      <c r="F24" s="4" t="inlineStr"/>
       <c r="G24" s="4" t="n">
         <v>402</v>
       </c>
@@ -27307,16 +27139,8 @@
           <t>勤凱</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>207.00</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>+18.5</t>
-        </is>
-      </c>
+      <c r="E25" s="4" t="inlineStr"/>
+      <c r="F25" s="4" t="inlineStr"/>
       <c r="G25" s="4" t="n">
         <v>385</v>
       </c>
@@ -27340,16 +27164,8 @@
           <t>康和證</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>16.65</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>+0.2</t>
-        </is>
-      </c>
+      <c r="E26" s="4" t="inlineStr"/>
+      <c r="F26" s="4" t="inlineStr"/>
       <c r="G26" s="4" t="n">
         <v>367</v>
       </c>
@@ -27373,16 +27189,8 @@
           <t>昇達科</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>1640.00</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>+145.0</t>
-        </is>
-      </c>
+      <c r="E27" s="4" t="inlineStr"/>
+      <c r="F27" s="4" t="inlineStr"/>
       <c r="G27" s="4" t="n">
         <v>366</v>
       </c>
@@ -27406,16 +27214,8 @@
           <t>鉅橡</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>55.70</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>+2.6</t>
-        </is>
-      </c>
+      <c r="E28" s="4" t="inlineStr"/>
+      <c r="F28" s="4" t="inlineStr"/>
       <c r="G28" s="4" t="n">
         <v>365</v>
       </c>
@@ -27439,16 +27239,8 @@
           <t>佶優</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>32.30</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>+0.9</t>
-        </is>
-      </c>
+      <c r="E29" s="4" t="inlineStr"/>
+      <c r="F29" s="4" t="inlineStr"/>
       <c r="G29" s="4" t="n">
         <v>355</v>
       </c>
@@ -27472,16 +27264,8 @@
           <t>久元</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>79.20</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>+7.2</t>
-        </is>
-      </c>
+      <c r="E30" s="4" t="inlineStr"/>
+      <c r="F30" s="4" t="inlineStr"/>
       <c r="G30" s="4" t="n">
         <v>321</v>
       </c>
@@ -27505,16 +27289,8 @@
           <t>合晶</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>30.90</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>-0.4</t>
-        </is>
-      </c>
+      <c r="E31" s="4" t="inlineStr"/>
+      <c r="F31" s="4" t="inlineStr"/>
       <c r="G31" s="4" t="n">
         <v>295</v>
       </c>
@@ -27538,16 +27314,8 @@
           <t>元太</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>142.50</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
+      <c r="E32" s="4" t="inlineStr"/>
+      <c r="F32" s="4" t="inlineStr"/>
       <c r="G32" s="4" t="n">
         <v>287</v>
       </c>
@@ -27571,16 +27339,8 @@
           <t>致和證</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>23.85</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>+0.35</t>
-        </is>
-      </c>
+      <c r="E33" s="4" t="inlineStr"/>
+      <c r="F33" s="4" t="inlineStr"/>
       <c r="G33" s="4" t="n">
         <v>284</v>
       </c>
@@ -27604,16 +27364,8 @@
           <t>環宇-KY</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>470.50</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>+35.5</t>
-        </is>
-      </c>
+      <c r="E34" s="4" t="inlineStr"/>
+      <c r="F34" s="4" t="inlineStr"/>
       <c r="G34" s="4" t="n">
         <v>282</v>
       </c>
@@ -27637,16 +27389,8 @@
           <t>能率</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>35.45</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
+      <c r="E35" s="4" t="inlineStr"/>
+      <c r="F35" s="4" t="inlineStr"/>
       <c r="G35" s="4" t="n">
         <v>271</v>
       </c>
@@ -27670,16 +27414,8 @@
           <t>精材</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>156.50</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>+2.0</t>
-        </is>
-      </c>
+      <c r="E36" s="4" t="inlineStr"/>
+      <c r="F36" s="4" t="inlineStr"/>
       <c r="G36" s="4" t="n">
         <v>257</v>
       </c>
@@ -27703,16 +27439,8 @@
           <t>博大</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>111.00</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>+5.5</t>
-        </is>
-      </c>
+      <c r="E37" s="4" t="inlineStr"/>
+      <c r="F37" s="4" t="inlineStr"/>
       <c r="G37" s="4" t="n">
         <v>257</v>
       </c>
@@ -27736,16 +27464,8 @@
           <t>元大期</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>99.80</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>+2.2</t>
-        </is>
-      </c>
+      <c r="E38" s="4" t="inlineStr"/>
+      <c r="F38" s="4" t="inlineStr"/>
       <c r="G38" s="4" t="n">
         <v>253</v>
       </c>
@@ -27769,16 +27489,8 @@
           <t>福邦證</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>14.80</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>+0.15</t>
-        </is>
-      </c>
+      <c r="E39" s="4" t="inlineStr"/>
+      <c r="F39" s="4" t="inlineStr"/>
       <c r="G39" s="4" t="n">
         <v>248</v>
       </c>
@@ -27802,16 +27514,8 @@
           <t>大國鋼</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>34.55</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>+0.35</t>
-        </is>
-      </c>
+      <c r="E40" s="4" t="inlineStr"/>
+      <c r="F40" s="4" t="inlineStr"/>
       <c r="G40" s="4" t="n">
         <v>248</v>
       </c>
@@ -27835,16 +27539,8 @@
           <t>久正</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>12.80</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>-0.2</t>
-        </is>
-      </c>
+      <c r="E41" s="4" t="inlineStr"/>
+      <c r="F41" s="4" t="inlineStr"/>
       <c r="G41" s="4" t="n">
         <v>232</v>
       </c>
@@ -27868,16 +27564,8 @@
           <t>宏觀</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>223.50</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>+11.0</t>
-        </is>
-      </c>
+      <c r="E42" s="4" t="inlineStr"/>
+      <c r="F42" s="4" t="inlineStr"/>
       <c r="G42" s="4" t="n">
         <v>228</v>
       </c>
@@ -27901,16 +27589,8 @@
           <t>榮剛</t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>32.00</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>+0.05</t>
-        </is>
-      </c>
+      <c r="E43" s="4" t="inlineStr"/>
+      <c r="F43" s="4" t="inlineStr"/>
       <c r="G43" s="4" t="n">
         <v>220</v>
       </c>
@@ -27934,16 +27614,8 @@
           <t>均豪</t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>101.00</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>+1.2</t>
-        </is>
-      </c>
+      <c r="E44" s="4" t="inlineStr"/>
+      <c r="F44" s="4" t="inlineStr"/>
       <c r="G44" s="4" t="n">
         <v>219</v>
       </c>
@@ -27967,16 +27639,8 @@
           <t>德晉</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>34.60</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>+0.7</t>
-        </is>
-      </c>
+      <c r="E45" s="4" t="inlineStr"/>
+      <c r="F45" s="4" t="inlineStr"/>
       <c r="G45" s="4" t="n">
         <v>218</v>
       </c>
@@ -28000,16 +27664,8 @@
           <t>鑫聯大投控</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>65.20</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>+1.8</t>
-        </is>
-      </c>
+      <c r="E46" s="4" t="inlineStr"/>
+      <c r="F46" s="4" t="inlineStr"/>
       <c r="G46" s="4" t="n">
         <v>216</v>
       </c>
@@ -28033,16 +27689,8 @@
           <t>濱川</t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>50.60</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t>+1.3</t>
-        </is>
-      </c>
+      <c r="E47" s="4" t="inlineStr"/>
+      <c r="F47" s="4" t="inlineStr"/>
       <c r="G47" s="4" t="n">
         <v>208</v>
       </c>
@@ -28066,16 +27714,8 @@
           <t>湧德</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>124.00</t>
-        </is>
-      </c>
-      <c r="F48" s="4" t="inlineStr">
-        <is>
-          <t>+11.0</t>
-        </is>
-      </c>
+      <c r="E48" s="4" t="inlineStr"/>
+      <c r="F48" s="4" t="inlineStr"/>
       <c r="G48" s="4" t="n">
         <v>192</v>
       </c>
@@ -28099,16 +27739,8 @@
           <t>廣閎科</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>118.50</t>
-        </is>
-      </c>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>+10.5</t>
-        </is>
-      </c>
+      <c r="E49" s="4" t="inlineStr"/>
+      <c r="F49" s="4" t="inlineStr"/>
       <c r="G49" s="4" t="n">
         <v>187</v>
       </c>
@@ -28132,16 +27764,8 @@
           <t>蜜望實</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>63.60</t>
-        </is>
-      </c>
-      <c r="F50" s="4" t="inlineStr">
-        <is>
-          <t>-0.6</t>
-        </is>
-      </c>
+      <c r="E50" s="4" t="inlineStr"/>
+      <c r="F50" s="4" t="inlineStr"/>
       <c r="G50" s="4" t="n">
         <v>187</v>
       </c>
@@ -28165,16 +27789,8 @@
           <t>台嘉碩</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>35.00</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="inlineStr">
-        <is>
-          <t>-0.6</t>
-        </is>
-      </c>
+      <c r="E51" s="4" t="inlineStr"/>
+      <c r="F51" s="4" t="inlineStr"/>
       <c r="G51" s="4" t="n">
         <v>180</v>
       </c>
@@ -28198,16 +27814,8 @@
           <t>安國</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>90.40</t>
-        </is>
-      </c>
-      <c r="F52" s="4" t="inlineStr">
-        <is>
-          <t>-1.6</t>
-        </is>
-      </c>
+      <c r="E52" s="4" t="inlineStr"/>
+      <c r="F52" s="4" t="inlineStr"/>
       <c r="G52" s="4" t="n">
         <v>169</v>
       </c>
@@ -28231,16 +27839,8 @@
           <t>IET-KY</t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>602.00</t>
-        </is>
-      </c>
-      <c r="F53" s="4" t="inlineStr">
-        <is>
-          <t>+38.0</t>
-        </is>
-      </c>
+      <c r="E53" s="4" t="inlineStr"/>
+      <c r="F53" s="4" t="inlineStr"/>
       <c r="G53" s="4" t="n">
         <v>163</v>
       </c>
@@ -28264,16 +27864,8 @@
           <t>金山電</t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>51.80</t>
-        </is>
-      </c>
-      <c r="F54" s="4" t="inlineStr">
-        <is>
-          <t>+0.8</t>
-        </is>
-      </c>
+      <c r="E54" s="4" t="inlineStr"/>
+      <c r="F54" s="4" t="inlineStr"/>
       <c r="G54" s="4" t="n">
         <v>160</v>
       </c>
@@ -28297,16 +27889,8 @@
           <t>信昌電</t>
         </is>
       </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>57.60</t>
-        </is>
-      </c>
-      <c r="F55" s="4" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
+      <c r="E55" s="4" t="inlineStr"/>
+      <c r="F55" s="4" t="inlineStr"/>
       <c r="G55" s="4" t="n">
         <v>156</v>
       </c>
@@ -28330,16 +27914,8 @@
           <t>竣邦-KY</t>
         </is>
       </c>
-      <c r="E56" s="4" t="inlineStr">
-        <is>
-          <t>62.50</t>
-        </is>
-      </c>
-      <c r="F56" s="4" t="inlineStr">
-        <is>
-          <t>+0.8</t>
-        </is>
-      </c>
+      <c r="E56" s="4" t="inlineStr"/>
+      <c r="F56" s="4" t="inlineStr"/>
       <c r="G56" s="4" t="n">
         <v>155</v>
       </c>
@@ -28363,16 +27939,8 @@
           <t>由田</t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr">
-        <is>
-          <t>152.50</t>
-        </is>
-      </c>
-      <c r="F57" s="4" t="inlineStr">
-        <is>
-          <t>+13.5</t>
-        </is>
-      </c>
+      <c r="E57" s="4" t="inlineStr"/>
+      <c r="F57" s="4" t="inlineStr"/>
       <c r="G57" s="4" t="n">
         <v>148</v>
       </c>
@@ -28396,16 +27964,8 @@
           <t>南仁湖</t>
         </is>
       </c>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t>7.83</t>
-        </is>
-      </c>
-      <c r="F58" s="4" t="inlineStr">
-        <is>
-          <t>+0.03</t>
-        </is>
-      </c>
+      <c r="E58" s="4" t="inlineStr"/>
+      <c r="F58" s="4" t="inlineStr"/>
       <c r="G58" s="4" t="n">
         <v>147</v>
       </c>
@@ -28429,16 +27989,8 @@
           <t>新鉅科</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>27.05</t>
-        </is>
-      </c>
-      <c r="F59" s="4" t="inlineStr">
-        <is>
-          <t>-0.55</t>
-        </is>
-      </c>
+      <c r="E59" s="4" t="inlineStr"/>
+      <c r="F59" s="4" t="inlineStr"/>
       <c r="G59" s="4" t="n">
         <v>144</v>
       </c>
@@ -28462,16 +28014,8 @@
           <t>健喬</t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>31.10</t>
-        </is>
-      </c>
-      <c r="F60" s="4" t="inlineStr">
-        <is>
-          <t>+0.1</t>
-        </is>
-      </c>
+      <c r="E60" s="4" t="inlineStr"/>
+      <c r="F60" s="4" t="inlineStr"/>
       <c r="G60" s="4" t="n">
         <v>143</v>
       </c>
@@ -28495,16 +28039,8 @@
           <t>信立</t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>54.60</t>
-        </is>
-      </c>
-      <c r="F61" s="4" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
+      <c r="E61" s="4" t="inlineStr"/>
+      <c r="F61" s="4" t="inlineStr"/>
       <c r="G61" s="4" t="n">
         <v>141</v>
       </c>
@@ -28528,16 +28064,8 @@
           <t>邦泰</t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr">
-        <is>
-          <t>17.90</t>
-        </is>
-      </c>
-      <c r="F62" s="4" t="inlineStr">
-        <is>
-          <t>-0.6</t>
-        </is>
-      </c>
+      <c r="E62" s="4" t="inlineStr"/>
+      <c r="F62" s="4" t="inlineStr"/>
       <c r="G62" s="4" t="n">
         <v>140</v>
       </c>
@@ -28561,16 +28089,8 @@
           <t>前鼎</t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>103.50</t>
-        </is>
-      </c>
-      <c r="F63" s="4" t="inlineStr">
-        <is>
-          <t>+2.5</t>
-        </is>
-      </c>
+      <c r="E63" s="4" t="inlineStr"/>
+      <c r="F63" s="4" t="inlineStr"/>
       <c r="G63" s="4" t="n">
         <v>139</v>
       </c>
@@ -28594,16 +28114,8 @@
           <t>華星光</t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t>404.50</t>
-        </is>
-      </c>
-      <c r="F64" s="4" t="inlineStr">
-        <is>
-          <t>+20.5</t>
-        </is>
-      </c>
+      <c r="E64" s="4" t="inlineStr"/>
+      <c r="F64" s="4" t="inlineStr"/>
       <c r="G64" s="4" t="n">
         <v>131</v>
       </c>
@@ -28627,16 +28139,8 @@
           <t>加百裕</t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr">
-        <is>
-          <t>32.25</t>
-        </is>
-      </c>
-      <c r="F65" s="4" t="inlineStr">
-        <is>
-          <t>+0.45</t>
-        </is>
-      </c>
+      <c r="E65" s="4" t="inlineStr"/>
+      <c r="F65" s="4" t="inlineStr"/>
       <c r="G65" s="4" t="n">
         <v>124</v>
       </c>
@@ -28660,16 +28164,8 @@
           <t>尼克森</t>
         </is>
       </c>
-      <c r="E66" s="4" t="inlineStr">
-        <is>
-          <t>50.10</t>
-        </is>
-      </c>
-      <c r="F66" s="4" t="inlineStr">
-        <is>
-          <t>-0.2</t>
-        </is>
-      </c>
+      <c r="E66" s="4" t="inlineStr"/>
+      <c r="F66" s="4" t="inlineStr"/>
       <c r="G66" s="4" t="n">
         <v>123</v>
       </c>
@@ -28693,16 +28189,8 @@
           <t>新華</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>22.35</t>
-        </is>
-      </c>
-      <c r="F67" s="4" t="inlineStr">
-        <is>
-          <t>+0.35</t>
-        </is>
-      </c>
+      <c r="E67" s="4" t="inlineStr"/>
+      <c r="F67" s="4" t="inlineStr"/>
       <c r="G67" s="4" t="n">
         <v>121</v>
       </c>
@@ -28726,16 +28214,8 @@
           <t>群翊</t>
         </is>
       </c>
-      <c r="E68" s="4" t="inlineStr">
-        <is>
-          <t>359.50</t>
-        </is>
-      </c>
-      <c r="F68" s="4" t="inlineStr">
-        <is>
-          <t>+5.0</t>
-        </is>
-      </c>
+      <c r="E68" s="4" t="inlineStr"/>
+      <c r="F68" s="4" t="inlineStr"/>
       <c r="G68" s="4" t="n">
         <v>116</v>
       </c>
@@ -28759,16 +28239,8 @@
           <t>原相</t>
         </is>
       </c>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>182.50</t>
-        </is>
-      </c>
-      <c r="F69" s="4" t="inlineStr">
-        <is>
-          <t>+2.5</t>
-        </is>
-      </c>
+      <c r="E69" s="4" t="inlineStr"/>
+      <c r="F69" s="4" t="inlineStr"/>
       <c r="G69" s="4" t="n">
         <v>114</v>
       </c>
@@ -28792,16 +28264,8 @@
           <t>環球晶</t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr">
-        <is>
-          <t>412.00</t>
-        </is>
-      </c>
-      <c r="F70" s="4" t="inlineStr">
-        <is>
-          <t>+2.5</t>
-        </is>
-      </c>
+      <c r="E70" s="4" t="inlineStr"/>
+      <c r="F70" s="4" t="inlineStr"/>
       <c r="G70" s="4" t="n">
         <v>113</v>
       </c>
@@ -28825,16 +28289,8 @@
           <t>榮群</t>
         </is>
       </c>
-      <c r="E71" s="4" t="inlineStr">
-        <is>
-          <t>25.60</t>
-        </is>
-      </c>
-      <c r="F71" s="4" t="inlineStr">
-        <is>
-          <t>+2.3</t>
-        </is>
-      </c>
+      <c r="E71" s="4" t="inlineStr"/>
+      <c r="F71" s="4" t="inlineStr"/>
       <c r="G71" s="4" t="n">
         <v>112</v>
       </c>
@@ -28858,16 +28314,8 @@
           <t>光頡</t>
         </is>
       </c>
-      <c r="E72" s="4" t="inlineStr">
-        <is>
-          <t>45.50</t>
-        </is>
-      </c>
-      <c r="F72" s="4" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
+      <c r="E72" s="4" t="inlineStr"/>
+      <c r="F72" s="4" t="inlineStr"/>
       <c r="G72" s="4" t="n">
         <v>108</v>
       </c>
@@ -28891,16 +28339,8 @@
           <t>龍巖</t>
         </is>
       </c>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>46.90</t>
-        </is>
-      </c>
-      <c r="F73" s="4" t="inlineStr">
-        <is>
-          <t>+0.45</t>
-        </is>
-      </c>
+      <c r="E73" s="4" t="inlineStr"/>
+      <c r="F73" s="4" t="inlineStr"/>
       <c r="G73" s="4" t="n">
         <v>106</v>
       </c>
@@ -28924,16 +28364,8 @@
           <t>碩禾</t>
         </is>
       </c>
-      <c r="E74" s="4" t="inlineStr">
-        <is>
-          <t>105.50</t>
-        </is>
-      </c>
-      <c r="F74" s="4" t="inlineStr">
-        <is>
-          <t>+3.5</t>
-        </is>
-      </c>
+      <c r="E74" s="4" t="inlineStr"/>
+      <c r="F74" s="4" t="inlineStr"/>
       <c r="G74" s="4" t="n">
         <v>104</v>
       </c>
@@ -28957,16 +28389,8 @@
           <t>世禾</t>
         </is>
       </c>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>171.50</t>
-        </is>
-      </c>
-      <c r="F75" s="4" t="inlineStr">
-        <is>
-          <t>+6.0</t>
-        </is>
-      </c>
+      <c r="E75" s="4" t="inlineStr"/>
+      <c r="F75" s="4" t="inlineStr"/>
       <c r="G75" s="4" t="n">
         <v>103</v>
       </c>
@@ -28990,16 +28414,8 @@
           <t>上詮</t>
         </is>
       </c>
-      <c r="E76" s="4" t="inlineStr">
-        <is>
-          <t>660.00</t>
-        </is>
-      </c>
-      <c r="F76" s="4" t="inlineStr">
-        <is>
-          <t>+60.0</t>
-        </is>
-      </c>
+      <c r="E76" s="4" t="inlineStr"/>
+      <c r="F76" s="4" t="inlineStr"/>
       <c r="G76" s="4" t="n">
         <v>102</v>
       </c>
@@ -29023,16 +28439,8 @@
           <t>網家</t>
         </is>
       </c>
-      <c r="E77" s="4" t="inlineStr">
-        <is>
-          <t>22.15</t>
-        </is>
-      </c>
-      <c r="F77" s="4" t="inlineStr">
-        <is>
-          <t>-0.3</t>
-        </is>
-      </c>
+      <c r="E77" s="4" t="inlineStr"/>
+      <c r="F77" s="4" t="inlineStr"/>
       <c r="G77" s="4" t="n">
         <v>100</v>
       </c>
@@ -29056,16 +28464,8 @@
           <t>禾瑞亞</t>
         </is>
       </c>
-      <c r="E78" s="4" t="inlineStr">
-        <is>
-          <t>45.70</t>
-        </is>
-      </c>
-      <c r="F78" s="4" t="inlineStr">
-        <is>
-          <t>+1.85</t>
-        </is>
-      </c>
+      <c r="E78" s="4" t="inlineStr"/>
+      <c r="F78" s="4" t="inlineStr"/>
       <c r="G78" s="4" t="n">
         <v>98</v>
       </c>
@@ -29089,16 +28489,8 @@
           <t>旺矽</t>
         </is>
       </c>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t>3920.00</t>
-        </is>
-      </c>
-      <c r="F79" s="4" t="inlineStr">
-        <is>
-          <t>+155.0</t>
-        </is>
-      </c>
+      <c r="E79" s="4" t="inlineStr"/>
+      <c r="F79" s="4" t="inlineStr"/>
       <c r="G79" s="4" t="n">
         <v>96</v>
       </c>
@@ -29122,16 +28514,8 @@
           <t>先進光</t>
         </is>
       </c>
-      <c r="E80" s="4" t="inlineStr">
-        <is>
-          <t>94.20</t>
-        </is>
-      </c>
-      <c r="F80" s="4" t="inlineStr">
-        <is>
-          <t>+1.1</t>
-        </is>
-      </c>
+      <c r="E80" s="4" t="inlineStr"/>
+      <c r="F80" s="4" t="inlineStr"/>
       <c r="G80" s="4" t="n">
         <v>95</v>
       </c>
@@ -29155,16 +28539,8 @@
           <t>漢磊</t>
         </is>
       </c>
-      <c r="E81" s="4" t="inlineStr">
-        <is>
-          <t>48.95</t>
-        </is>
-      </c>
-      <c r="F81" s="4" t="inlineStr">
-        <is>
-          <t>+0.65</t>
-        </is>
-      </c>
+      <c r="E81" s="4" t="inlineStr"/>
+      <c r="F81" s="4" t="inlineStr"/>
       <c r="G81" s="4" t="n">
         <v>93</v>
       </c>
@@ -29188,16 +28564,8 @@
           <t>振發</t>
         </is>
       </c>
-      <c r="E82" s="4" t="inlineStr">
-        <is>
-          <t>19.25</t>
-        </is>
-      </c>
-      <c r="F82" s="4" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
+      <c r="E82" s="4" t="inlineStr"/>
+      <c r="F82" s="4" t="inlineStr"/>
       <c r="G82" s="4" t="n">
         <v>90</v>
       </c>
@@ -29221,16 +28589,8 @@
           <t>晶呈科技</t>
         </is>
       </c>
-      <c r="E83" s="4" t="inlineStr">
-        <is>
-          <t>435.00</t>
-        </is>
-      </c>
-      <c r="F83" s="4" t="inlineStr">
-        <is>
-          <t>+4.0</t>
-        </is>
-      </c>
+      <c r="E83" s="4" t="inlineStr"/>
+      <c r="F83" s="4" t="inlineStr"/>
       <c r="G83" s="4" t="n">
         <v>88</v>
       </c>
@@ -29254,16 +28614,8 @@
           <t>松上</t>
         </is>
       </c>
-      <c r="E84" s="4" t="inlineStr">
-        <is>
-          <t>19.20</t>
-        </is>
-      </c>
-      <c r="F84" s="4" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
+      <c r="E84" s="4" t="inlineStr"/>
+      <c r="F84" s="4" t="inlineStr"/>
       <c r="G84" s="4" t="n">
         <v>86</v>
       </c>
@@ -29287,16 +28639,8 @@
           <t>波若威</t>
         </is>
       </c>
-      <c r="E85" s="4" t="inlineStr">
-        <is>
-          <t>1045.00</t>
-        </is>
-      </c>
-      <c r="F85" s="4" t="inlineStr">
-        <is>
-          <t>+93.0</t>
-        </is>
-      </c>
+      <c r="E85" s="4" t="inlineStr"/>
+      <c r="F85" s="4" t="inlineStr"/>
       <c r="G85" s="4" t="n">
         <v>84</v>
       </c>
@@ -29320,16 +28664,8 @@
           <t>南俊國際</t>
         </is>
       </c>
-      <c r="E86" s="4" t="inlineStr">
-        <is>
-          <t>596.00</t>
-        </is>
-      </c>
-      <c r="F86" s="4" t="inlineStr">
-        <is>
-          <t>+26.0</t>
-        </is>
-      </c>
+      <c r="E86" s="4" t="inlineStr"/>
+      <c r="F86" s="4" t="inlineStr"/>
       <c r="G86" s="4" t="n">
         <v>82</v>
       </c>
@@ -29353,16 +28689,8 @@
           <t>凱崴</t>
         </is>
       </c>
-      <c r="E87" s="4" t="inlineStr">
-        <is>
-          <t>54.50</t>
-        </is>
-      </c>
-      <c r="F87" s="4" t="inlineStr">
-        <is>
-          <t>+1.0</t>
-        </is>
-      </c>
+      <c r="E87" s="4" t="inlineStr"/>
+      <c r="F87" s="4" t="inlineStr"/>
       <c r="G87" s="4" t="n">
         <v>80</v>
       </c>
@@ -29386,16 +28714,8 @@
           <t>大江</t>
         </is>
       </c>
-      <c r="E88" s="4" t="inlineStr">
-        <is>
-          <t>124.50</t>
-        </is>
-      </c>
-      <c r="F88" s="4" t="inlineStr">
-        <is>
-          <t>-2.5</t>
-        </is>
-      </c>
+      <c r="E88" s="4" t="inlineStr"/>
+      <c r="F88" s="4" t="inlineStr"/>
       <c r="G88" s="4" t="n">
         <v>80</v>
       </c>
@@ -29419,16 +28739,8 @@
           <t>科嶠</t>
         </is>
       </c>
-      <c r="E89" s="4" t="inlineStr">
-        <is>
-          <t>156.50</t>
-        </is>
-      </c>
-      <c r="F89" s="4" t="inlineStr">
-        <is>
-          <t>+2.5</t>
-        </is>
-      </c>
+      <c r="E89" s="4" t="inlineStr"/>
+      <c r="F89" s="4" t="inlineStr"/>
       <c r="G89" s="4" t="n">
         <v>79</v>
       </c>
@@ -29452,16 +28764,8 @@
           <t>聯寶</t>
         </is>
       </c>
-      <c r="E90" s="4" t="inlineStr">
-        <is>
-          <t>52.00</t>
-        </is>
-      </c>
-      <c r="F90" s="4" t="inlineStr">
-        <is>
-          <t>-4.5</t>
-        </is>
-      </c>
+      <c r="E90" s="4" t="inlineStr"/>
+      <c r="F90" s="4" t="inlineStr"/>
       <c r="G90" s="4" t="n">
         <v>77</v>
       </c>
@@ -29485,16 +28789,8 @@
           <t>英濟</t>
         </is>
       </c>
-      <c r="E91" s="4" t="inlineStr">
-        <is>
-          <t>31.05</t>
-        </is>
-      </c>
-      <c r="F91" s="4" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
+      <c r="E91" s="4" t="inlineStr"/>
+      <c r="F91" s="4" t="inlineStr"/>
       <c r="G91" s="4" t="n">
         <v>76</v>
       </c>
@@ -29518,16 +28814,8 @@
           <t>新潤</t>
         </is>
       </c>
-      <c r="E92" s="4" t="inlineStr">
-        <is>
-          <t>39.70</t>
-        </is>
-      </c>
-      <c r="F92" s="4" t="inlineStr">
-        <is>
-          <t>+0.85</t>
-        </is>
-      </c>
+      <c r="E92" s="4" t="inlineStr"/>
+      <c r="F92" s="4" t="inlineStr"/>
       <c r="G92" s="4" t="n">
         <v>76</v>
       </c>
@@ -29551,16 +28839,8 @@
           <t>閎康</t>
         </is>
       </c>
-      <c r="E93" s="4" t="inlineStr">
-        <is>
-          <t>236.50</t>
-        </is>
-      </c>
-      <c r="F93" s="4" t="inlineStr">
-        <is>
-          <t>+9.5</t>
-        </is>
-      </c>
+      <c r="E93" s="4" t="inlineStr"/>
+      <c r="F93" s="4" t="inlineStr"/>
       <c r="G93" s="4" t="n">
         <v>73</v>
       </c>
@@ -29584,16 +28864,8 @@
           <t>浩鼎</t>
         </is>
       </c>
-      <c r="E94" s="4" t="inlineStr">
-        <is>
-          <t>39.00</t>
-        </is>
-      </c>
-      <c r="F94" s="4" t="inlineStr">
-        <is>
-          <t>+1.05</t>
-        </is>
-      </c>
+      <c r="E94" s="4" t="inlineStr"/>
+      <c r="F94" s="4" t="inlineStr"/>
       <c r="G94" s="4" t="n">
         <v>73</v>
       </c>
@@ -29617,16 +28889,8 @@
           <t>福華</t>
         </is>
       </c>
-      <c r="E95" s="4" t="inlineStr">
-        <is>
-          <t>15.60</t>
-        </is>
-      </c>
-      <c r="F95" s="4" t="inlineStr">
-        <is>
-          <t>+0.55</t>
-        </is>
-      </c>
+      <c r="E95" s="4" t="inlineStr"/>
+      <c r="F95" s="4" t="inlineStr"/>
       <c r="G95" s="4" t="n">
         <v>72</v>
       </c>
@@ -29650,16 +28914,8 @@
           <t>臺慶科</t>
         </is>
       </c>
-      <c r="E96" s="4" t="inlineStr">
-        <is>
-          <t>143.00</t>
-        </is>
-      </c>
-      <c r="F96" s="4" t="inlineStr">
-        <is>
-          <t>+2.0</t>
-        </is>
-      </c>
+      <c r="E96" s="4" t="inlineStr"/>
+      <c r="F96" s="4" t="inlineStr"/>
       <c r="G96" s="4" t="n">
         <v>71</v>
       </c>
@@ -29683,16 +28939,8 @@
           <t>康全電訊</t>
         </is>
       </c>
-      <c r="E97" s="4" t="inlineStr">
-        <is>
-          <t>22.00</t>
-        </is>
-      </c>
-      <c r="F97" s="4" t="inlineStr">
-        <is>
-          <t>-0.6</t>
-        </is>
-      </c>
+      <c r="E97" s="4" t="inlineStr"/>
+      <c r="F97" s="4" t="inlineStr"/>
       <c r="G97" s="4" t="n">
         <v>71</v>
       </c>
@@ -29716,16 +28964,8 @@
           <t>青雲</t>
         </is>
       </c>
-      <c r="E98" s="4" t="inlineStr">
-        <is>
-          <t>303.50</t>
-        </is>
-      </c>
-      <c r="F98" s="4" t="inlineStr">
-        <is>
-          <t>+27.5</t>
-        </is>
-      </c>
+      <c r="E98" s="4" t="inlineStr"/>
+      <c r="F98" s="4" t="inlineStr"/>
       <c r="G98" s="4" t="n">
         <v>67</v>
       </c>
@@ -29749,16 +28989,8 @@
           <t>佰研</t>
         </is>
       </c>
-      <c r="E99" s="4" t="inlineStr">
-        <is>
-          <t>59.30</t>
-        </is>
-      </c>
-      <c r="F99" s="4" t="inlineStr">
-        <is>
-          <t>-1.6</t>
-        </is>
-      </c>
+      <c r="E99" s="4" t="inlineStr"/>
+      <c r="F99" s="4" t="inlineStr"/>
       <c r="G99" s="4" t="n">
         <v>65</v>
       </c>
@@ -29782,16 +29014,8 @@
           <t>精測</t>
         </is>
       </c>
-      <c r="E100" s="4" t="inlineStr">
-        <is>
-          <t>3325.00</t>
-        </is>
-      </c>
-      <c r="F100" s="4" t="inlineStr">
-        <is>
-          <t>+160.0</t>
-        </is>
-      </c>
+      <c r="E100" s="4" t="inlineStr"/>
+      <c r="F100" s="4" t="inlineStr"/>
       <c r="G100" s="4" t="n">
         <v>65</v>
       </c>
@@ -29815,16 +29039,8 @@
           <t>軒郁</t>
         </is>
       </c>
-      <c r="E101" s="4" t="inlineStr">
-        <is>
-          <t>118.00</t>
-        </is>
-      </c>
-      <c r="F101" s="4" t="inlineStr">
-        <is>
-          <t>+1.5</t>
-        </is>
-      </c>
+      <c r="E101" s="4" t="inlineStr"/>
+      <c r="F101" s="4" t="inlineStr"/>
       <c r="G101" s="4" t="n">
         <v>61</v>
       </c>
@@ -29848,16 +29064,8 @@
           <t>新復興</t>
         </is>
       </c>
-      <c r="E102" s="4" t="inlineStr">
-        <is>
-          <t>57.30</t>
-        </is>
-      </c>
-      <c r="F102" s="4" t="inlineStr">
-        <is>
-          <t>+1.9</t>
-        </is>
-      </c>
+      <c r="E102" s="4" t="inlineStr"/>
+      <c r="F102" s="4" t="inlineStr"/>
       <c r="G102" s="4" t="n">
         <v>60</v>
       </c>
@@ -29881,16 +29089,8 @@
           <t>力旺</t>
         </is>
       </c>
-      <c r="E103" s="4" t="inlineStr">
-        <is>
-          <t>2795.00</t>
-        </is>
-      </c>
-      <c r="F103" s="4" t="inlineStr">
-        <is>
-          <t>+165.0</t>
-        </is>
-      </c>
+      <c r="E103" s="4" t="inlineStr"/>
+      <c r="F103" s="4" t="inlineStr"/>
       <c r="G103" s="4" t="n">
         <v>57</v>
       </c>
@@ -29991,16 +29191,8 @@
           <t>威剛</t>
         </is>
       </c>
-      <c r="E109" s="4" t="inlineStr">
-        <is>
-          <t>363.00</t>
-        </is>
-      </c>
-      <c r="F109" s="4" t="inlineStr">
-        <is>
-          <t>+1.5</t>
-        </is>
-      </c>
+      <c r="E109" s="4" t="inlineStr"/>
+      <c r="F109" s="4" t="inlineStr"/>
       <c r="G109" s="4" t="n">
         <v>-5377</v>
       </c>
@@ -30024,16 +29216,8 @@
           <t>中探針</t>
         </is>
       </c>
-      <c r="E110" s="4" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
-      </c>
-      <c r="F110" s="4" t="inlineStr">
-        <is>
-          <t>+7.5</t>
-        </is>
-      </c>
+      <c r="E110" s="4" t="inlineStr"/>
+      <c r="F110" s="4" t="inlineStr"/>
       <c r="G110" s="4" t="n">
         <v>-4082</v>
       </c>
@@ -30057,16 +29241,8 @@
           <t>鈺創</t>
         </is>
       </c>
-      <c r="E111" s="4" t="inlineStr">
-        <is>
-          <t>64.60</t>
-        </is>
-      </c>
-      <c r="F111" s="4" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
+      <c r="E111" s="4" t="inlineStr"/>
+      <c r="F111" s="4" t="inlineStr"/>
       <c r="G111" s="4" t="n">
         <v>-2882</v>
       </c>
@@ -30090,16 +29266,8 @@
           <t>宜鼎</t>
         </is>
       </c>
-      <c r="E112" s="4" t="inlineStr">
-        <is>
-          <t>978.00</t>
-        </is>
-      </c>
-      <c r="F112" s="4" t="inlineStr">
-        <is>
-          <t>+21.0</t>
-        </is>
-      </c>
+      <c r="E112" s="4" t="inlineStr"/>
+      <c r="F112" s="4" t="inlineStr"/>
       <c r="G112" s="4" t="n">
         <v>-2566</v>
       </c>
@@ -30123,16 +29291,8 @@
           <t>廣穎</t>
         </is>
       </c>
-      <c r="E113" s="4" t="inlineStr">
-        <is>
-          <t>69.30</t>
-        </is>
-      </c>
-      <c r="F113" s="4" t="inlineStr">
-        <is>
-          <t>+1.3</t>
-        </is>
-      </c>
+      <c r="E113" s="4" t="inlineStr"/>
+      <c r="F113" s="4" t="inlineStr"/>
       <c r="G113" s="4" t="n">
         <v>-2267</v>
       </c>
@@ -30156,16 +29316,8 @@
           <t>欣銓</t>
         </is>
       </c>
-      <c r="E114" s="4" t="inlineStr">
-        <is>
-          <t>156.00</t>
-        </is>
-      </c>
-      <c r="F114" s="4" t="inlineStr">
-        <is>
-          <t>-5.0</t>
-        </is>
-      </c>
+      <c r="E114" s="4" t="inlineStr"/>
+      <c r="F114" s="4" t="inlineStr"/>
       <c r="G114" s="4" t="n">
         <v>-1989</v>
       </c>
@@ -30189,16 +29341,8 @@
           <t>東捷</t>
         </is>
       </c>
-      <c r="E115" s="4" t="inlineStr">
-        <is>
-          <t>64.80</t>
-        </is>
-      </c>
-      <c r="F115" s="4" t="inlineStr">
-        <is>
-          <t>-1.2</t>
-        </is>
-      </c>
+      <c r="E115" s="4" t="inlineStr"/>
+      <c r="F115" s="4" t="inlineStr"/>
       <c r="G115" s="4" t="n">
         <v>-1490</v>
       </c>
@@ -30222,16 +29366,8 @@
           <t>中美晶</t>
         </is>
       </c>
-      <c r="E116" s="4" t="inlineStr">
-        <is>
-          <t>106.00</t>
-        </is>
-      </c>
-      <c r="F116" s="4" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
+      <c r="E116" s="4" t="inlineStr"/>
+      <c r="F116" s="4" t="inlineStr"/>
       <c r="G116" s="4" t="n">
         <v>-1223</v>
       </c>
@@ -30255,16 +29391,8 @@
           <t>達航科技</t>
         </is>
       </c>
-      <c r="E117" s="4" t="inlineStr">
-        <is>
-          <t>106.00</t>
-        </is>
-      </c>
-      <c r="F117" s="4" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
+      <c r="E117" s="4" t="inlineStr"/>
+      <c r="F117" s="4" t="inlineStr"/>
       <c r="G117" s="4" t="n">
         <v>-956</v>
       </c>
@@ -30288,16 +29416,8 @@
           <t>晟德</t>
         </is>
       </c>
-      <c r="E118" s="4" t="inlineStr">
-        <is>
-          <t>40.95</t>
-        </is>
-      </c>
-      <c r="F118" s="4" t="inlineStr">
-        <is>
-          <t>-0.75</t>
-        </is>
-      </c>
+      <c r="E118" s="4" t="inlineStr"/>
+      <c r="F118" s="4" t="inlineStr"/>
       <c r="G118" s="4" t="n">
         <v>-825</v>
       </c>
@@ -30321,16 +29441,8 @@
           <t>鈦昇</t>
         </is>
       </c>
-      <c r="E119" s="4" t="inlineStr">
-        <is>
-          <t>151.50</t>
-        </is>
-      </c>
-      <c r="F119" s="4" t="inlineStr">
-        <is>
-          <t>-3.0</t>
-        </is>
-      </c>
+      <c r="E119" s="4" t="inlineStr"/>
+      <c r="F119" s="4" t="inlineStr"/>
       <c r="G119" s="4" t="n">
         <v>-814</v>
       </c>
@@ -30354,16 +29466,8 @@
           <t>華電網</t>
         </is>
       </c>
-      <c r="E120" s="4" t="inlineStr">
-        <is>
-          <t>61.40</t>
-        </is>
-      </c>
-      <c r="F120" s="4" t="inlineStr">
-        <is>
-          <t>+1.9</t>
-        </is>
-      </c>
+      <c r="E120" s="4" t="inlineStr"/>
+      <c r="F120" s="4" t="inlineStr"/>
       <c r="G120" s="4" t="n">
         <v>-671</v>
       </c>
@@ -30387,16 +29491,8 @@
           <t>高技</t>
         </is>
       </c>
-      <c r="E121" s="4" t="inlineStr">
-        <is>
-          <t>278.50</t>
-        </is>
-      </c>
-      <c r="F121" s="4" t="inlineStr">
-        <is>
-          <t>+2.0</t>
-        </is>
-      </c>
+      <c r="E121" s="4" t="inlineStr"/>
+      <c r="F121" s="4" t="inlineStr"/>
       <c r="G121" s="4" t="n">
         <v>-667</v>
       </c>
@@ -30420,16 +29516,8 @@
           <t>九豪</t>
         </is>
       </c>
-      <c r="E122" s="4" t="inlineStr">
-        <is>
-          <t>39.00</t>
-        </is>
-      </c>
-      <c r="F122" s="4" t="inlineStr">
-        <is>
-          <t>-1.35</t>
-        </is>
-      </c>
+      <c r="E122" s="4" t="inlineStr"/>
+      <c r="F122" s="4" t="inlineStr"/>
       <c r="G122" s="4" t="n">
         <v>-536</v>
       </c>
@@ -30453,16 +29541,8 @@
           <t>翔名</t>
         </is>
       </c>
-      <c r="E123" s="4" t="inlineStr">
-        <is>
-          <t>166.50</t>
-        </is>
-      </c>
-      <c r="F123" s="4" t="inlineStr">
-        <is>
-          <t>+6.0</t>
-        </is>
-      </c>
+      <c r="E123" s="4" t="inlineStr"/>
+      <c r="F123" s="4" t="inlineStr"/>
       <c r="G123" s="4" t="n">
         <v>-513</v>
       </c>
@@ -30486,16 +29566,8 @@
           <t>雙鴻</t>
         </is>
       </c>
-      <c r="E124" s="4" t="inlineStr">
-        <is>
-          <t>918.00</t>
-        </is>
-      </c>
-      <c r="F124" s="4" t="inlineStr">
-        <is>
-          <t>+8.0</t>
-        </is>
-      </c>
+      <c r="E124" s="4" t="inlineStr"/>
+      <c r="F124" s="4" t="inlineStr"/>
       <c r="G124" s="4" t="n">
         <v>-505</v>
       </c>
@@ -30519,16 +29591,8 @@
           <t>創威</t>
         </is>
       </c>
-      <c r="E125" s="4" t="inlineStr">
-        <is>
-          <t>95.50</t>
-        </is>
-      </c>
-      <c r="F125" s="4" t="inlineStr">
-        <is>
-          <t>+6.3</t>
-        </is>
-      </c>
+      <c r="E125" s="4" t="inlineStr"/>
+      <c r="F125" s="4" t="inlineStr"/>
       <c r="G125" s="4" t="n">
         <v>-484</v>
       </c>
@@ -30552,16 +29616,8 @@
           <t>松瑞藥</t>
         </is>
       </c>
-      <c r="E126" s="4" t="inlineStr">
-        <is>
-          <t>20.70</t>
-        </is>
-      </c>
-      <c r="F126" s="4" t="inlineStr">
-        <is>
-          <t>-0.45</t>
-        </is>
-      </c>
+      <c r="E126" s="4" t="inlineStr"/>
+      <c r="F126" s="4" t="inlineStr"/>
       <c r="G126" s="4" t="n">
         <v>-453</v>
       </c>
@@ -30585,16 +29641,8 @@
           <t>國統</t>
         </is>
       </c>
-      <c r="E127" s="4" t="inlineStr">
-        <is>
-          <t>50.20</t>
-        </is>
-      </c>
-      <c r="F127" s="4" t="inlineStr">
-        <is>
-          <t>-0.9</t>
-        </is>
-      </c>
+      <c r="E127" s="4" t="inlineStr"/>
+      <c r="F127" s="4" t="inlineStr"/>
       <c r="G127" s="4" t="n">
         <v>-445</v>
       </c>
@@ -30618,16 +29666,8 @@
           <t>聚和</t>
         </is>
       </c>
-      <c r="E128" s="4" t="inlineStr">
-        <is>
-          <t>43.00</t>
-        </is>
-      </c>
-      <c r="F128" s="4" t="inlineStr">
-        <is>
-          <t>-1.65</t>
-        </is>
-      </c>
+      <c r="E128" s="4" t="inlineStr"/>
+      <c r="F128" s="4" t="inlineStr"/>
       <c r="G128" s="4" t="n">
         <v>-410</v>
       </c>
@@ -30651,16 +29691,8 @@
           <t>力麒</t>
         </is>
       </c>
-      <c r="E129" s="4" t="inlineStr">
-        <is>
-          <t>7.83</t>
-        </is>
-      </c>
-      <c r="F129" s="4" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
+      <c r="E129" s="4" t="inlineStr"/>
+      <c r="F129" s="4" t="inlineStr"/>
       <c r="G129" s="4" t="n">
         <v>-404</v>
       </c>
@@ -30684,16 +29716,8 @@
           <t>品安</t>
         </is>
       </c>
-      <c r="E130" s="4" t="inlineStr">
-        <is>
-          <t>48.70</t>
-        </is>
-      </c>
-      <c r="F130" s="4" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
+      <c r="E130" s="4" t="inlineStr"/>
+      <c r="F130" s="4" t="inlineStr"/>
       <c r="G130" s="4" t="n">
         <v>-403</v>
       </c>
@@ -30717,16 +29741,8 @@
           <t>皇將</t>
         </is>
       </c>
-      <c r="E131" s="4" t="inlineStr">
-        <is>
-          <t>36.50</t>
-        </is>
-      </c>
-      <c r="F131" s="4" t="inlineStr">
-        <is>
-          <t>-2.4</t>
-        </is>
-      </c>
+      <c r="E131" s="4" t="inlineStr"/>
+      <c r="F131" s="4" t="inlineStr"/>
       <c r="G131" s="4" t="n">
         <v>-386</v>
       </c>
@@ -30750,16 +29766,8 @@
           <t>聯亞</t>
         </is>
       </c>
-      <c r="E132" s="4" t="inlineStr">
-        <is>
-          <t>2005.00</t>
-        </is>
-      </c>
-      <c r="F132" s="4" t="inlineStr">
-        <is>
-          <t>+180.0</t>
-        </is>
-      </c>
+      <c r="E132" s="4" t="inlineStr"/>
+      <c r="F132" s="4" t="inlineStr"/>
       <c r="G132" s="4" t="n">
         <v>-366</v>
       </c>
@@ -30783,16 +29791,8 @@
           <t>博智</t>
         </is>
       </c>
-      <c r="E133" s="4" t="inlineStr">
-        <is>
-          <t>278.00</t>
-        </is>
-      </c>
-      <c r="F133" s="4" t="inlineStr">
-        <is>
-          <t>+25.0</t>
-        </is>
-      </c>
+      <c r="E133" s="4" t="inlineStr"/>
+      <c r="F133" s="4" t="inlineStr"/>
       <c r="G133" s="4" t="n">
         <v>-342</v>
       </c>
@@ -30816,16 +29816,8 @@
           <t>群聯</t>
         </is>
       </c>
-      <c r="E134" s="4" t="inlineStr">
-        <is>
-          <t>1570.00</t>
-        </is>
-      </c>
-      <c r="F134" s="4" t="inlineStr">
-        <is>
-          <t>+15.0</t>
-        </is>
-      </c>
+      <c r="E134" s="4" t="inlineStr"/>
+      <c r="F134" s="4" t="inlineStr"/>
       <c r="G134" s="4" t="n">
         <v>-329</v>
       </c>
@@ -30849,16 +29841,8 @@
           <t>同亨</t>
         </is>
       </c>
-      <c r="E135" s="4" t="inlineStr">
-        <is>
-          <t>26.45</t>
-        </is>
-      </c>
-      <c r="F135" s="4" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
+      <c r="E135" s="4" t="inlineStr"/>
+      <c r="F135" s="4" t="inlineStr"/>
       <c r="G135" s="4" t="n">
         <v>-327</v>
       </c>
@@ -30882,16 +29866,8 @@
           <t>建舜電</t>
         </is>
       </c>
-      <c r="E136" s="4" t="inlineStr">
-        <is>
-          <t>13.55</t>
-        </is>
-      </c>
-      <c r="F136" s="4" t="inlineStr">
-        <is>
-          <t>+0.3</t>
-        </is>
-      </c>
+      <c r="E136" s="4" t="inlineStr"/>
+      <c r="F136" s="4" t="inlineStr"/>
       <c r="G136" s="4" t="n">
         <v>-292</v>
       </c>
@@ -30915,16 +29891,8 @@
           <t>亞泰金屬</t>
         </is>
       </c>
-      <c r="E137" s="4" t="inlineStr">
-        <is>
-          <t>354.50</t>
-        </is>
-      </c>
-      <c r="F137" s="4" t="inlineStr">
-        <is>
-          <t>-3.5</t>
-        </is>
-      </c>
+      <c r="E137" s="4" t="inlineStr"/>
+      <c r="F137" s="4" t="inlineStr"/>
       <c r="G137" s="4" t="n">
         <v>-280</v>
       </c>
@@ -30948,16 +29916,8 @@
           <t>東浦</t>
         </is>
       </c>
-      <c r="E138" s="4" t="inlineStr">
-        <is>
-          <t>44.80</t>
-        </is>
-      </c>
-      <c r="F138" s="4" t="inlineStr">
-        <is>
-          <t>+2.2</t>
-        </is>
-      </c>
+      <c r="E138" s="4" t="inlineStr"/>
+      <c r="F138" s="4" t="inlineStr"/>
       <c r="G138" s="4" t="n">
         <v>-275</v>
       </c>
@@ -30981,16 +29941,8 @@
           <t>陽程</t>
         </is>
       </c>
-      <c r="E139" s="4" t="inlineStr">
-        <is>
-          <t>72.10</t>
-        </is>
-      </c>
-      <c r="F139" s="4" t="inlineStr">
-        <is>
-          <t>-0.7</t>
-        </is>
-      </c>
+      <c r="E139" s="4" t="inlineStr"/>
+      <c r="F139" s="4" t="inlineStr"/>
       <c r="G139" s="4" t="n">
         <v>-275</v>
       </c>
@@ -31014,16 +29966,8 @@
           <t>伍豐</t>
         </is>
       </c>
-      <c r="E140" s="4" t="inlineStr">
-        <is>
-          <t>22.90</t>
-        </is>
-      </c>
-      <c r="F140" s="4" t="inlineStr">
-        <is>
-          <t>-0.55</t>
-        </is>
-      </c>
+      <c r="E140" s="4" t="inlineStr"/>
+      <c r="F140" s="4" t="inlineStr"/>
       <c r="G140" s="4" t="n">
         <v>-270</v>
       </c>
@@ -31047,16 +29991,8 @@
           <t>德宏</t>
         </is>
       </c>
-      <c r="E141" s="4" t="inlineStr">
-        <is>
-          <t>271.00</t>
-        </is>
-      </c>
-      <c r="F141" s="4" t="inlineStr">
-        <is>
-          <t>+24.5</t>
-        </is>
-      </c>
+      <c r="E141" s="4" t="inlineStr"/>
+      <c r="F141" s="4" t="inlineStr"/>
       <c r="G141" s="4" t="n">
         <v>-248</v>
       </c>
@@ -31080,16 +30016,8 @@
           <t>華景電</t>
         </is>
       </c>
-      <c r="E142" s="4" t="inlineStr">
-        <is>
-          <t>376.50</t>
-        </is>
-      </c>
-      <c r="F142" s="4" t="inlineStr">
-        <is>
-          <t>+3.0</t>
-        </is>
-      </c>
+      <c r="E142" s="4" t="inlineStr"/>
+      <c r="F142" s="4" t="inlineStr"/>
       <c r="G142" s="4" t="n">
         <v>-247</v>
       </c>
@@ -31113,16 +30041,8 @@
           <t>聖暉*</t>
         </is>
       </c>
-      <c r="E143" s="4" t="inlineStr">
-        <is>
-          <t>688.00</t>
-        </is>
-      </c>
-      <c r="F143" s="4" t="inlineStr">
-        <is>
-          <t>-11.0</t>
-        </is>
-      </c>
+      <c r="E143" s="4" t="inlineStr"/>
+      <c r="F143" s="4" t="inlineStr"/>
       <c r="G143" s="4" t="n">
         <v>-238</v>
       </c>
@@ -31146,16 +30066,8 @@
           <t>振曜</t>
         </is>
       </c>
-      <c r="E144" s="4" t="inlineStr">
-        <is>
-          <t>95.70</t>
-        </is>
-      </c>
-      <c r="F144" s="4" t="inlineStr">
-        <is>
-          <t>+0.6</t>
-        </is>
-      </c>
+      <c r="E144" s="4" t="inlineStr"/>
+      <c r="F144" s="4" t="inlineStr"/>
       <c r="G144" s="4" t="n">
         <v>-234</v>
       </c>
@@ -31179,16 +30091,8 @@
           <t>胡連</t>
         </is>
       </c>
-      <c r="E145" s="4" t="inlineStr">
-        <is>
-          <t>106.50</t>
-        </is>
-      </c>
-      <c r="F145" s="4" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
+      <c r="E145" s="4" t="inlineStr"/>
+      <c r="F145" s="4" t="inlineStr"/>
       <c r="G145" s="4" t="n">
         <v>-224</v>
       </c>
@@ -31212,16 +30116,8 @@
           <t>合一</t>
         </is>
       </c>
-      <c r="E146" s="4" t="inlineStr">
-        <is>
-          <t>54.50</t>
-        </is>
-      </c>
-      <c r="F146" s="4" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
+      <c r="E146" s="4" t="inlineStr"/>
+      <c r="F146" s="4" t="inlineStr"/>
       <c r="G146" s="4" t="n">
         <v>-215</v>
       </c>
@@ -31245,16 +30141,8 @@
           <t>台星科</t>
         </is>
       </c>
-      <c r="E147" s="4" t="inlineStr">
-        <is>
-          <t>144.00</t>
-        </is>
-      </c>
-      <c r="F147" s="4" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
+      <c r="E147" s="4" t="inlineStr"/>
+      <c r="F147" s="4" t="inlineStr"/>
       <c r="G147" s="4" t="n">
         <v>-197</v>
       </c>
@@ -31278,16 +30166,8 @@
           <t>M31</t>
         </is>
       </c>
-      <c r="E148" s="4" t="inlineStr">
-        <is>
-          <t>463.00</t>
-        </is>
-      </c>
-      <c r="F148" s="4" t="inlineStr">
-        <is>
-          <t>-8.0</t>
-        </is>
-      </c>
+      <c r="E148" s="4" t="inlineStr"/>
+      <c r="F148" s="4" t="inlineStr"/>
       <c r="G148" s="4" t="n">
         <v>-190</v>
       </c>
@@ -31311,16 +30191,8 @@
           <t>益安</t>
         </is>
       </c>
-      <c r="E149" s="4" t="inlineStr">
-        <is>
-          <t>88.50</t>
-        </is>
-      </c>
-      <c r="F149" s="4" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
+      <c r="E149" s="4" t="inlineStr"/>
+      <c r="F149" s="4" t="inlineStr"/>
       <c r="G149" s="4" t="n">
         <v>-180</v>
       </c>
@@ -31344,16 +30216,8 @@
           <t>博磊</t>
         </is>
       </c>
-      <c r="E150" s="4" t="inlineStr">
-        <is>
-          <t>64.60</t>
-        </is>
-      </c>
-      <c r="F150" s="4" t="inlineStr">
-        <is>
-          <t>-1.2</t>
-        </is>
-      </c>
+      <c r="E150" s="4" t="inlineStr"/>
+      <c r="F150" s="4" t="inlineStr"/>
       <c r="G150" s="4" t="n">
         <v>-178</v>
       </c>
@@ -31377,16 +30241,8 @@
           <t>系微</t>
         </is>
       </c>
-      <c r="E151" s="4" t="inlineStr">
-        <is>
-          <t>268.00</t>
-        </is>
-      </c>
-      <c r="F151" s="4" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
+      <c r="E151" s="4" t="inlineStr"/>
+      <c r="F151" s="4" t="inlineStr"/>
       <c r="G151" s="4" t="n">
         <v>-156</v>
       </c>
@@ -31410,16 +30266,8 @@
           <t>中裕</t>
         </is>
       </c>
-      <c r="E152" s="4" t="inlineStr">
-        <is>
-          <t>55.10</t>
-        </is>
-      </c>
-      <c r="F152" s="4" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
+      <c r="E152" s="4" t="inlineStr"/>
+      <c r="F152" s="4" t="inlineStr"/>
       <c r="G152" s="4" t="n">
         <v>-154</v>
       </c>
@@ -31443,16 +30291,8 @@
           <t>日揚</t>
         </is>
       </c>
-      <c r="E153" s="4" t="inlineStr">
-        <is>
-          <t>57.60</t>
-        </is>
-      </c>
-      <c r="F153" s="4" t="inlineStr">
-        <is>
-          <t>+5.2</t>
-        </is>
-      </c>
+      <c r="E153" s="4" t="inlineStr"/>
+      <c r="F153" s="4" t="inlineStr"/>
       <c r="G153" s="4" t="n">
         <v>-149</v>
       </c>
@@ -31476,16 +30316,8 @@
           <t>神盾</t>
         </is>
       </c>
-      <c r="E154" s="4" t="inlineStr">
-        <is>
-          <t>101.00</t>
-        </is>
-      </c>
-      <c r="F154" s="4" t="inlineStr">
-        <is>
-          <t>-8.0</t>
-        </is>
-      </c>
+      <c r="E154" s="4" t="inlineStr"/>
+      <c r="F154" s="4" t="inlineStr"/>
       <c r="G154" s="4" t="n">
         <v>-147</v>
       </c>
@@ -31509,16 +30341,8 @@
           <t>磐亞</t>
         </is>
       </c>
-      <c r="E155" s="4" t="inlineStr">
-        <is>
-          <t>11.35</t>
-        </is>
-      </c>
-      <c r="F155" s="4" t="inlineStr">
-        <is>
-          <t>+0.15</t>
-        </is>
-      </c>
+      <c r="E155" s="4" t="inlineStr"/>
+      <c r="F155" s="4" t="inlineStr"/>
       <c r="G155" s="4" t="n">
         <v>-146</v>
       </c>
@@ -31542,16 +30366,8 @@
           <t>永信建</t>
         </is>
       </c>
-      <c r="E156" s="4" t="inlineStr">
-        <is>
-          <t>50.60</t>
-        </is>
-      </c>
-      <c r="F156" s="4" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
+      <c r="E156" s="4" t="inlineStr"/>
+      <c r="F156" s="4" t="inlineStr"/>
       <c r="G156" s="4" t="n">
         <v>-145</v>
       </c>
@@ -31575,16 +30391,8 @@
           <t>太景*-KY</t>
         </is>
       </c>
-      <c r="E157" s="4" t="inlineStr">
-        <is>
-          <t>11.20</t>
-        </is>
-      </c>
-      <c r="F157" s="4" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
+      <c r="E157" s="4" t="inlineStr"/>
+      <c r="F157" s="4" t="inlineStr"/>
       <c r="G157" s="4" t="n">
         <v>-144</v>
       </c>
@@ -31608,16 +30416,8 @@
           <t>健亞</t>
         </is>
       </c>
-      <c r="E158" s="4" t="inlineStr">
-        <is>
-          <t>34.70</t>
-        </is>
-      </c>
-      <c r="F158" s="4" t="inlineStr">
-        <is>
-          <t>+0.65</t>
-        </is>
-      </c>
+      <c r="E158" s="4" t="inlineStr"/>
+      <c r="F158" s="4" t="inlineStr"/>
       <c r="G158" s="4" t="n">
         <v>-141</v>
       </c>

--- a/StockInfo/otc_analysis_result.xlsx
+++ b/StockInfo/otc_analysis_result.xlsx
@@ -5333,8 +5333,16 @@
           <t>威剛</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>440.00</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>+40.0</t>
+        </is>
+      </c>
       <c r="G4" s="4" t="n">
         <v>6810</v>
       </c>
@@ -5361,8 +5369,16 @@
           <t>中美晶</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr"/>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>143.00</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>+13.0</t>
+        </is>
+      </c>
       <c r="G5" s="4" t="n">
         <v>5275</v>
       </c>
@@ -5393,8 +5409,16 @@
           <t>精材</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr"/>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>218.00</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>+19.5</t>
+        </is>
+      </c>
       <c r="G6" s="4" t="n">
         <v>1876</v>
       </c>
@@ -5425,8 +5449,16 @@
           <t>群聯</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr"/>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>1835.00</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>+155.0</t>
+        </is>
+      </c>
       <c r="G7" s="4" t="n">
         <v>1856</v>
       </c>
@@ -5457,8 +5489,16 @@
           <t>鈺創</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr"/>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>64.20</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>+3.1</t>
+        </is>
+      </c>
       <c r="G8" s="4" t="n">
         <v>1561</v>
       </c>
@@ -5485,8 +5525,16 @@
           <t>華宏</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr"/>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>74.80</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>+6.8</t>
+        </is>
+      </c>
       <c r="G9" s="4" t="n">
         <v>1402</v>
       </c>
@@ -5521,8 +5569,16 @@
           <t>康和證</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr"/>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>19.00</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>+0.1</t>
+        </is>
+      </c>
       <c r="G10" s="4" t="n">
         <v>1350</v>
       </c>
@@ -5553,8 +5609,16 @@
           <t>擎亞</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr"/>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>91.70</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>+3.1</t>
+        </is>
+      </c>
       <c r="G11" s="4" t="n">
         <v>1323</v>
       </c>
@@ -5581,8 +5645,16 @@
           <t>系統電</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr"/>
-      <c r="F12" s="4" t="inlineStr"/>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>62.30</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>+2.3</t>
+        </is>
+      </c>
       <c r="G12" s="4" t="n">
         <v>1252</v>
       </c>
@@ -5617,8 +5689,16 @@
           <t>廣穎</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr"/>
-      <c r="F13" s="4" t="inlineStr"/>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>88.10</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>+8.0</t>
+        </is>
+      </c>
       <c r="G13" s="4" t="n">
         <v>1224</v>
       </c>
@@ -5645,8 +5725,16 @@
           <t>致和證</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr"/>
-      <c r="F14" s="4" t="inlineStr"/>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>27.10</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>+0.6</t>
+        </is>
+      </c>
       <c r="G14" s="4" t="n">
         <v>1152</v>
       </c>
@@ -5677,8 +5765,16 @@
           <t>環球晶</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr"/>
-      <c r="F15" s="4" t="inlineStr"/>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>620.00</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>+38.0</t>
+        </is>
+      </c>
       <c r="G15" s="4" t="n">
         <v>1137</v>
       </c>
@@ -5709,8 +5805,16 @@
           <t>宏遠證</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr"/>
-      <c r="F16" s="4" t="inlineStr"/>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>14.00</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>+0.35</t>
+        </is>
+      </c>
       <c r="G16" s="4" t="n">
         <v>950</v>
       </c>
@@ -5741,8 +5845,16 @@
           <t>方土昶</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="4" t="inlineStr"/>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>39.40</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>+3.55</t>
+        </is>
+      </c>
       <c r="G17" s="4" t="n">
         <v>949</v>
       </c>
@@ -5773,8 +5885,16 @@
           <t>凱崴</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr"/>
-      <c r="F18" s="4" t="inlineStr"/>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>66.10</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>-5.4</t>
+        </is>
+      </c>
       <c r="G18" s="4" t="n">
         <v>906</v>
       </c>
@@ -5805,8 +5925,16 @@
           <t>華電網</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr"/>
-      <c r="F19" s="4" t="inlineStr"/>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>57.90</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>-3.1</t>
+        </is>
+      </c>
       <c r="G19" s="4" t="n">
         <v>848</v>
       </c>
@@ -5837,8 +5965,16 @@
           <t>港建*</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr"/>
-      <c r="F20" s="4" t="inlineStr"/>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>55.70</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>-5.9</t>
+        </is>
+      </c>
       <c r="G20" s="4" t="n">
         <v>764</v>
       </c>
@@ -5877,8 +6013,16 @@
           <t>宜鼎</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr"/>
-      <c r="F21" s="4" t="inlineStr"/>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>1190.00</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>+105.0</t>
+        </is>
+      </c>
       <c r="G21" s="4" t="n">
         <v>726</v>
       </c>
@@ -5909,8 +6053,16 @@
           <t>磐亞</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr"/>
-      <c r="F22" s="4" t="inlineStr"/>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>14.70</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>-0.45</t>
+        </is>
+      </c>
       <c r="G22" s="4" t="n">
         <v>714</v>
       </c>
@@ -5937,8 +6089,16 @@
           <t>富強鑫</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr"/>
-      <c r="F23" s="4" t="inlineStr"/>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>26.80</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>-0.35</t>
+        </is>
+      </c>
       <c r="G23" s="4" t="n">
         <v>655</v>
       </c>
@@ -5969,8 +6129,16 @@
           <t>廣明</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr"/>
-      <c r="F24" s="4" t="inlineStr"/>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>81.00</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>-1.8</t>
+        </is>
+      </c>
       <c r="G24" s="4" t="n">
         <v>576</v>
       </c>
@@ -5997,8 +6165,16 @@
           <t>高鋒</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr"/>
-      <c r="F25" s="4" t="inlineStr"/>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>46.00</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>+2.8</t>
+        </is>
+      </c>
       <c r="G25" s="4" t="n">
         <v>547</v>
       </c>
@@ -6025,8 +6201,16 @@
           <t>前鼎</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr"/>
-      <c r="F26" s="4" t="inlineStr"/>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>164.00</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>-11.5</t>
+        </is>
+      </c>
       <c r="G26" s="4" t="n">
         <v>522</v>
       </c>
@@ -6057,8 +6241,16 @@
           <t>萬潤</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr"/>
-      <c r="F27" s="4" t="inlineStr"/>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>1080.00</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
       <c r="G27" s="4" t="n">
         <v>517</v>
       </c>
@@ -6085,8 +6277,16 @@
           <t>創威</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr"/>
-      <c r="F28" s="4" t="inlineStr"/>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>103.00</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>-7.0</t>
+        </is>
+      </c>
       <c r="G28" s="4" t="n">
         <v>517</v>
       </c>
@@ -6113,8 +6313,16 @@
           <t>亞泰金屬</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr"/>
-      <c r="F29" s="4" t="inlineStr"/>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>409.00</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>+24.0</t>
+        </is>
+      </c>
       <c r="G29" s="4" t="n">
         <v>472</v>
       </c>
@@ -6141,8 +6349,16 @@
           <t>立端</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr"/>
-      <c r="F30" s="4" t="inlineStr"/>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>79.90</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>-1.2</t>
+        </is>
+      </c>
       <c r="G30" s="4" t="n">
         <v>451</v>
       </c>
@@ -6173,8 +6389,16 @@
           <t>加百裕</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr"/>
-      <c r="F31" s="4" t="inlineStr"/>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>35.30</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>+1.3</t>
+        </is>
+      </c>
       <c r="G31" s="4" t="n">
         <v>437</v>
       </c>
@@ -6201,8 +6425,16 @@
           <t>大中</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr"/>
-      <c r="F32" s="4" t="inlineStr"/>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>200.50</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>+18.0</t>
+        </is>
+      </c>
       <c r="G32" s="4" t="n">
         <v>429</v>
       </c>
@@ -6237,8 +6469,16 @@
           <t>聯亞</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr"/>
-      <c r="F33" s="4" t="inlineStr"/>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>2540.00</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>-280.0</t>
+        </is>
+      </c>
       <c r="G33" s="4" t="n">
         <v>406</v>
       </c>
@@ -6265,8 +6505,16 @@
           <t>智擎</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr"/>
-      <c r="F34" s="4" t="inlineStr"/>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>53.80</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>-0.6</t>
+        </is>
+      </c>
       <c r="G34" s="4" t="n">
         <v>405</v>
       </c>
@@ -6301,8 +6549,16 @@
           <t>協易機</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr"/>
-      <c r="F35" s="4" t="inlineStr"/>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>29.30</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
       <c r="G35" s="4" t="n">
         <v>396</v>
       </c>
@@ -6329,8 +6585,16 @@
           <t>基亞</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr"/>
-      <c r="F36" s="4" t="inlineStr"/>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>35.05</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>+3.15</t>
+        </is>
+      </c>
       <c r="G36" s="4" t="n">
         <v>395</v>
       </c>
@@ -6365,8 +6629,16 @@
           <t>聖暉*</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr"/>
-      <c r="F37" s="4" t="inlineStr"/>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>928.00</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>-44.0</t>
+        </is>
+      </c>
       <c r="G37" s="4" t="n">
         <v>385</v>
       </c>
@@ -6397,8 +6669,16 @@
           <t>博智</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr"/>
-      <c r="F38" s="4" t="inlineStr"/>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>416.50</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>+37.5</t>
+        </is>
+      </c>
       <c r="G38" s="4" t="n">
         <v>377</v>
       </c>
@@ -6425,8 +6705,16 @@
           <t>鑫聯大投控</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr"/>
-      <c r="F39" s="4" t="inlineStr"/>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>81.70</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>+1.0</t>
+        </is>
+      </c>
       <c r="G39" s="4" t="n">
         <v>374</v>
       </c>
@@ -6457,8 +6745,16 @@
           <t>凱碩</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr"/>
-      <c r="F40" s="4" t="inlineStr"/>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>20.60</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>-0.95</t>
+        </is>
+      </c>
       <c r="G40" s="4" t="n">
         <v>332</v>
       </c>
@@ -6493,8 +6789,16 @@
           <t>亞電</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr"/>
-      <c r="F41" s="4" t="inlineStr"/>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>40.05</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>-1.4</t>
+        </is>
+      </c>
       <c r="G41" s="4" t="n">
         <v>321</v>
       </c>
@@ -6521,8 +6825,16 @@
           <t>東典光電</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr"/>
-      <c r="F42" s="4" t="inlineStr"/>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>121.50</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
       <c r="G42" s="4" t="n">
         <v>313</v>
       </c>
@@ -6553,8 +6865,16 @@
           <t>凡甲</t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr"/>
-      <c r="F43" s="4" t="inlineStr"/>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>295.00</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>+25.5</t>
+        </is>
+      </c>
       <c r="G43" s="4" t="n">
         <v>309</v>
       </c>
@@ -6585,8 +6905,16 @@
           <t>弘塑</t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr"/>
-      <c r="F44" s="4" t="inlineStr"/>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>2875.00</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>-255.0</t>
+        </is>
+      </c>
       <c r="G44" s="4" t="n">
         <v>296</v>
       </c>
@@ -6617,8 +6945,16 @@
           <t>環宇-KY</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr"/>
-      <c r="F45" s="4" t="inlineStr"/>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>570.00</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>-26.0</t>
+        </is>
+      </c>
       <c r="G45" s="4" t="n">
         <v>249</v>
       </c>
@@ -6649,8 +6985,16 @@
           <t>宜特</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr"/>
-      <c r="F46" s="4" t="inlineStr"/>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>176.00</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>-6.5</t>
+        </is>
+      </c>
       <c r="G46" s="4" t="n">
         <v>219</v>
       </c>
@@ -6681,8 +7025,16 @@
           <t>太景*-KY</t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr"/>
-      <c r="F47" s="4" t="inlineStr"/>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>10.10</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>-0.0</t>
+        </is>
+      </c>
       <c r="G47" s="4" t="n">
         <v>212</v>
       </c>
@@ -6713,8 +7065,16 @@
           <t>旺矽</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr"/>
-      <c r="F48" s="4" t="inlineStr"/>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>4880.00</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>+230.0</t>
+        </is>
+      </c>
       <c r="G48" s="4" t="n">
         <v>209</v>
       </c>
@@ -6741,8 +7101,16 @@
           <t>德勝</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr"/>
-      <c r="F49" s="4" t="inlineStr"/>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>61.80</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>-2.5</t>
+        </is>
+      </c>
       <c r="G49" s="4" t="n">
         <v>190</v>
       </c>
@@ -6769,8 +7137,16 @@
           <t>華容</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr"/>
-      <c r="F50" s="4" t="inlineStr"/>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>23.60</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>-0.15</t>
+        </is>
+      </c>
       <c r="G50" s="4" t="n">
         <v>189</v>
       </c>
@@ -6797,8 +7173,16 @@
           <t>橘子</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr"/>
-      <c r="F51" s="4" t="inlineStr"/>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>39.15</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>-1.05</t>
+        </is>
+      </c>
       <c r="G51" s="4" t="n">
         <v>189</v>
       </c>
@@ -6825,8 +7209,16 @@
           <t>金山電</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr"/>
-      <c r="F52" s="4" t="inlineStr"/>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>56.30</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>-0.2</t>
+        </is>
+      </c>
       <c r="G52" s="4" t="n">
         <v>186</v>
       </c>
@@ -6853,8 +7245,16 @@
           <t>聯寶</t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr"/>
-      <c r="F53" s="4" t="inlineStr"/>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>53.20</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>-4.2</t>
+        </is>
+      </c>
       <c r="G53" s="4" t="n">
         <v>178</v>
       </c>
@@ -6889,8 +7289,16 @@
           <t>金益鼎</t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr"/>
-      <c r="F54" s="4" t="inlineStr"/>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>85.30</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>+1.3</t>
+        </is>
+      </c>
       <c r="G54" s="4" t="n">
         <v>175</v>
       </c>
@@ -6917,8 +7325,16 @@
           <t>德宏</t>
         </is>
       </c>
-      <c r="E55" s="4" t="inlineStr"/>
-      <c r="F55" s="4" t="inlineStr"/>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>308.50</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>-27.0</t>
+        </is>
+      </c>
       <c r="G55" s="4" t="n">
         <v>168</v>
       </c>
@@ -6949,8 +7365,16 @@
           <t>福華</t>
         </is>
       </c>
-      <c r="E56" s="4" t="inlineStr"/>
-      <c r="F56" s="4" t="inlineStr"/>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>13.00</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>-0.6</t>
+        </is>
+      </c>
       <c r="G56" s="4" t="n">
         <v>165</v>
       </c>
@@ -6981,8 +7405,16 @@
           <t>信昌電</t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr"/>
-      <c r="F57" s="4" t="inlineStr"/>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>77.40</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>+1.2</t>
+        </is>
+      </c>
       <c r="G57" s="4" t="n">
         <v>162</v>
       </c>
@@ -7009,8 +7441,16 @@
           <t>IET-KY</t>
         </is>
       </c>
-      <c r="E58" s="4" t="inlineStr"/>
-      <c r="F58" s="4" t="inlineStr"/>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>687.00</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>-76.0</t>
+        </is>
+      </c>
       <c r="G58" s="4" t="n">
         <v>160</v>
       </c>
@@ -7037,8 +7477,16 @@
           <t>龍巖</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr"/>
-      <c r="F59" s="4" t="inlineStr"/>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>45.80</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>+1.75</t>
+        </is>
+      </c>
       <c r="G59" s="4" t="n">
         <v>159</v>
       </c>
@@ -7065,8 +7513,16 @@
           <t>博磊</t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr"/>
-      <c r="F60" s="4" t="inlineStr"/>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>153.00</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>-10.5</t>
+        </is>
+      </c>
       <c r="G60" s="4" t="n">
         <v>150</v>
       </c>
@@ -7093,8 +7549,16 @@
           <t>振曜</t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr"/>
-      <c r="F61" s="4" t="inlineStr"/>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>87.50</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>-1.8</t>
+        </is>
+      </c>
       <c r="G61" s="4" t="n">
         <v>149</v>
       </c>
@@ -7121,8 +7585,16 @@
           <t>力旺</t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr"/>
-      <c r="F62" s="4" t="inlineStr"/>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>4045.00</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>+145.0</t>
+        </is>
+      </c>
       <c r="G62" s="4" t="n">
         <v>148</v>
       </c>
@@ -7153,8 +7625,16 @@
           <t>大樹</t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr"/>
-      <c r="F63" s="4" t="inlineStr"/>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>78.00</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>-0.6</t>
+        </is>
+      </c>
       <c r="G63" s="4" t="n">
         <v>146</v>
       </c>
@@ -7181,8 +7661,16 @@
           <t>德微</t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr"/>
-      <c r="F64" s="4" t="inlineStr"/>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>227.00</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>+3.0</t>
+        </is>
+      </c>
       <c r="G64" s="4" t="n">
         <v>142</v>
       </c>
@@ -7213,8 +7701,16 @@
           <t>光譜</t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr"/>
-      <c r="F65" s="4" t="inlineStr"/>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>22.70</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>-0.05</t>
+        </is>
+      </c>
       <c r="G65" s="4" t="n">
         <v>142</v>
       </c>
@@ -7245,8 +7741,16 @@
           <t>泰茂</t>
         </is>
       </c>
-      <c r="E66" s="4" t="inlineStr"/>
-      <c r="F66" s="4" t="inlineStr"/>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>27.65</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>-1.35</t>
+        </is>
+      </c>
       <c r="G66" s="4" t="n">
         <v>141</v>
       </c>
@@ -7277,8 +7781,16 @@
           <t>九豪</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr"/>
-      <c r="F67" s="4" t="inlineStr"/>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>45.50</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>+0.85</t>
+        </is>
+      </c>
       <c r="G67" s="4" t="n">
         <v>141</v>
       </c>
@@ -7305,8 +7817,16 @@
           <t>三圓</t>
         </is>
       </c>
-      <c r="E68" s="4" t="inlineStr"/>
-      <c r="F68" s="4" t="inlineStr"/>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>12.90</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>-0.95</t>
+        </is>
+      </c>
       <c r="G68" s="4" t="n">
         <v>140</v>
       </c>
@@ -7333,8 +7853,16 @@
           <t>南仁湖</t>
         </is>
       </c>
-      <c r="E69" s="4" t="inlineStr"/>
-      <c r="F69" s="4" t="inlineStr"/>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>7.80</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>-0.09</t>
+        </is>
+      </c>
       <c r="G69" s="4" t="n">
         <v>137</v>
       </c>
@@ -7365,8 +7893,16 @@
           <t>精剛</t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr"/>
-      <c r="F70" s="4" t="inlineStr"/>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>19.45</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
       <c r="G70" s="4" t="n">
         <v>132</v>
       </c>
@@ -7393,8 +7929,16 @@
           <t>沛亨</t>
         </is>
       </c>
-      <c r="E71" s="4" t="inlineStr"/>
-      <c r="F71" s="4" t="inlineStr"/>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>429.00</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>-7.0</t>
+        </is>
+      </c>
       <c r="G71" s="4" t="n">
         <v>127</v>
       </c>
@@ -7421,8 +7965,16 @@
           <t>統振</t>
         </is>
       </c>
-      <c r="E72" s="4" t="inlineStr"/>
-      <c r="F72" s="4" t="inlineStr"/>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>51.80</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>+0.4</t>
+        </is>
+      </c>
       <c r="G72" s="4" t="n">
         <v>125</v>
       </c>
@@ -7453,8 +8005,16 @@
           <t>西勝</t>
         </is>
       </c>
-      <c r="E73" s="4" t="inlineStr"/>
-      <c r="F73" s="4" t="inlineStr"/>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>17.35</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>-0.55</t>
+        </is>
+      </c>
       <c r="G73" s="4" t="n">
         <v>116</v>
       </c>
@@ -7481,8 +8041,16 @@
           <t>信音</t>
         </is>
       </c>
-      <c r="E74" s="4" t="inlineStr"/>
-      <c r="F74" s="4" t="inlineStr"/>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>31.10</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>-0.45</t>
+        </is>
+      </c>
       <c r="G74" s="4" t="n">
         <v>114</v>
       </c>
@@ -7513,8 +8081,16 @@
           <t>岳豐</t>
         </is>
       </c>
-      <c r="E75" s="4" t="inlineStr"/>
-      <c r="F75" s="4" t="inlineStr"/>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>29.70</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>+0.05</t>
+        </is>
+      </c>
       <c r="G75" s="4" t="n">
         <v>112</v>
       </c>
@@ -7541,8 +8117,16 @@
           <t>能率</t>
         </is>
       </c>
-      <c r="E76" s="4" t="inlineStr"/>
-      <c r="F76" s="4" t="inlineStr"/>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>35.80</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>-0.35</t>
+        </is>
+      </c>
       <c r="G76" s="4" t="n">
         <v>111</v>
       </c>
@@ -7569,8 +8153,16 @@
           <t>鏵友益</t>
         </is>
       </c>
-      <c r="E77" s="4" t="inlineStr"/>
-      <c r="F77" s="4" t="inlineStr"/>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>173.50</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>-12.5</t>
+        </is>
+      </c>
       <c r="G77" s="4" t="n">
         <v>111</v>
       </c>
@@ -7597,8 +8189,16 @@
           <t>光耀</t>
         </is>
       </c>
-      <c r="E78" s="4" t="inlineStr"/>
-      <c r="F78" s="4" t="inlineStr"/>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>26.20</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>+1.45</t>
+        </is>
+      </c>
       <c r="G78" s="4" t="n">
         <v>108</v>
       </c>
@@ -7629,8 +8229,16 @@
           <t>全宇昕</t>
         </is>
       </c>
-      <c r="E79" s="4" t="inlineStr"/>
-      <c r="F79" s="4" t="inlineStr"/>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>103.00</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>+7.8</t>
+        </is>
+      </c>
       <c r="G79" s="4" t="n">
         <v>105</v>
       </c>
@@ -7657,8 +8265,16 @@
           <t>利機</t>
         </is>
       </c>
-      <c r="E80" s="4" t="inlineStr"/>
-      <c r="F80" s="4" t="inlineStr"/>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>85.30</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>-5.7</t>
+        </is>
+      </c>
       <c r="G80" s="4" t="n">
         <v>104</v>
       </c>
@@ -7685,8 +8301,16 @@
           <t>易發</t>
         </is>
       </c>
-      <c r="E81" s="4" t="inlineStr"/>
-      <c r="F81" s="4" t="inlineStr"/>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>84.70</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>-5.5</t>
+        </is>
+      </c>
       <c r="G81" s="4" t="n">
         <v>101</v>
       </c>
@@ -7713,8 +8337,16 @@
           <t>台嘉碩</t>
         </is>
       </c>
-      <c r="E82" s="4" t="inlineStr"/>
-      <c r="F82" s="4" t="inlineStr"/>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>40.55</t>
+        </is>
+      </c>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>-2.95</t>
+        </is>
+      </c>
       <c r="G82" s="4" t="n">
         <v>100</v>
       </c>
@@ -7741,8 +8373,16 @@
           <t>永捷</t>
         </is>
       </c>
-      <c r="E83" s="4" t="inlineStr"/>
-      <c r="F83" s="4" t="inlineStr"/>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>14.70</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
       <c r="G83" s="4" t="n">
         <v>97</v>
       </c>
@@ -7769,8 +8409,16 @@
           <t>品安</t>
         </is>
       </c>
-      <c r="E84" s="4" t="inlineStr"/>
-      <c r="F84" s="4" t="inlineStr"/>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>52.00</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>+1.5</t>
+        </is>
+      </c>
       <c r="G84" s="4" t="n">
         <v>97</v>
       </c>
@@ -7797,8 +8445,16 @@
           <t>寶德</t>
         </is>
       </c>
-      <c r="E85" s="4" t="inlineStr"/>
-      <c r="F85" s="4" t="inlineStr"/>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>27.40</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>+0.05</t>
+        </is>
+      </c>
       <c r="G85" s="4" t="n">
         <v>95</v>
       </c>
@@ -7825,8 +8481,16 @@
           <t>安可</t>
         </is>
       </c>
-      <c r="E86" s="4" t="inlineStr"/>
-      <c r="F86" s="4" t="inlineStr"/>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>29.95</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>-0.2</t>
+        </is>
+      </c>
       <c r="G86" s="4" t="n">
         <v>93</v>
       </c>
@@ -7853,8 +8517,16 @@
           <t>五福</t>
         </is>
       </c>
-      <c r="E87" s="4" t="inlineStr"/>
-      <c r="F87" s="4" t="inlineStr"/>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>102.00</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>+0.5</t>
+        </is>
+      </c>
       <c r="G87" s="4" t="n">
         <v>91</v>
       </c>
@@ -7881,8 +8553,16 @@
           <t>崇越電</t>
         </is>
       </c>
-      <c r="E88" s="4" t="inlineStr"/>
-      <c r="F88" s="4" t="inlineStr"/>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>103.00</t>
+        </is>
+      </c>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t>-9.0</t>
+        </is>
+      </c>
       <c r="G88" s="4" t="n">
         <v>90</v>
       </c>
@@ -7909,8 +8589,16 @@
           <t>益安</t>
         </is>
       </c>
-      <c r="E89" s="4" t="inlineStr"/>
-      <c r="F89" s="4" t="inlineStr"/>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>82.70</t>
+        </is>
+      </c>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t>+0.5</t>
+        </is>
+      </c>
       <c r="G89" s="4" t="n">
         <v>88</v>
       </c>
@@ -7937,8 +8625,16 @@
           <t>僑威</t>
         </is>
       </c>
-      <c r="E90" s="4" t="inlineStr"/>
-      <c r="F90" s="4" t="inlineStr"/>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>56.20</t>
+        </is>
+      </c>
+      <c r="F90" s="4" t="inlineStr">
+        <is>
+          <t>-0.1</t>
+        </is>
+      </c>
       <c r="G90" s="4" t="n">
         <v>86</v>
       </c>
@@ -7965,8 +8661,16 @@
           <t>彬台</t>
         </is>
       </c>
-      <c r="E91" s="4" t="inlineStr"/>
-      <c r="F91" s="4" t="inlineStr"/>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>32.90</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>-1.6</t>
+        </is>
+      </c>
       <c r="G91" s="4" t="n">
         <v>86</v>
       </c>
@@ -7993,8 +8697,16 @@
           <t>順藥</t>
         </is>
       </c>
-      <c r="E92" s="4" t="inlineStr"/>
-      <c r="F92" s="4" t="inlineStr"/>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>126.00</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t>+1.0</t>
+        </is>
+      </c>
       <c r="G92" s="4" t="n">
         <v>82</v>
       </c>
@@ -8025,8 +8737,16 @@
           <t>泰谷</t>
         </is>
       </c>
-      <c r="E93" s="4" t="inlineStr"/>
-      <c r="F93" s="4" t="inlineStr"/>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>50.40</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>-5.6</t>
+        </is>
+      </c>
       <c r="G93" s="4" t="n">
         <v>80</v>
       </c>
@@ -8057,8 +8777,16 @@
           <t>安碁</t>
         </is>
       </c>
-      <c r="E94" s="4" t="inlineStr"/>
-      <c r="F94" s="4" t="inlineStr"/>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>27.25</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t>-1.3</t>
+        </is>
+      </c>
       <c r="G94" s="4" t="n">
         <v>80</v>
       </c>
@@ -8089,8 +8817,16 @@
           <t>愛地雅</t>
         </is>
       </c>
-      <c r="E95" s="4" t="inlineStr"/>
-      <c r="F95" s="4" t="inlineStr"/>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>6.10</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
       <c r="G95" s="4" t="n">
         <v>73</v>
       </c>
@@ -8121,8 +8857,16 @@
           <t>精湛</t>
         </is>
       </c>
-      <c r="E96" s="4" t="inlineStr"/>
-      <c r="F96" s="4" t="inlineStr"/>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>53.60</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
       <c r="G96" s="4" t="n">
         <v>72</v>
       </c>
@@ -8149,8 +8893,16 @@
           <t>逸達</t>
         </is>
       </c>
-      <c r="E97" s="4" t="inlineStr"/>
-      <c r="F97" s="4" t="inlineStr"/>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>81.50</t>
+        </is>
+      </c>
+      <c r="F97" s="4" t="inlineStr">
+        <is>
+          <t>+0.8</t>
+        </is>
+      </c>
       <c r="G97" s="4" t="n">
         <v>72</v>
       </c>
@@ -8177,8 +8929,16 @@
           <t>91APP*-KY</t>
         </is>
       </c>
-      <c r="E98" s="4" t="inlineStr"/>
-      <c r="F98" s="4" t="inlineStr"/>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>61.80</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>+0.4</t>
+        </is>
+      </c>
       <c r="G98" s="4" t="n">
         <v>72</v>
       </c>
@@ -8205,8 +8965,16 @@
           <t>力肯</t>
         </is>
       </c>
-      <c r="E99" s="4" t="inlineStr"/>
-      <c r="F99" s="4" t="inlineStr"/>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>37.85</t>
+        </is>
+      </c>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t>+0.55</t>
+        </is>
+      </c>
       <c r="G99" s="4" t="n">
         <v>68</v>
       </c>
@@ -8241,8 +9009,16 @@
           <t>易飛網</t>
         </is>
       </c>
-      <c r="E100" s="4" t="inlineStr"/>
-      <c r="F100" s="4" t="inlineStr"/>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t>16.55</t>
+        </is>
+      </c>
+      <c r="F100" s="4" t="inlineStr">
+        <is>
+          <t>-0.4</t>
+        </is>
+      </c>
       <c r="G100" s="4" t="n">
         <v>68</v>
       </c>
@@ -8269,8 +9045,16 @@
           <t>尚立</t>
         </is>
       </c>
-      <c r="E101" s="4" t="inlineStr"/>
-      <c r="F101" s="4" t="inlineStr"/>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t>13.40</t>
+        </is>
+      </c>
+      <c r="F101" s="4" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
       <c r="G101" s="4" t="n">
         <v>67</v>
       </c>
@@ -8297,8 +9081,16 @@
           <t>光環</t>
         </is>
       </c>
-      <c r="E102" s="4" t="inlineStr"/>
-      <c r="F102" s="4" t="inlineStr"/>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t>101.50</t>
+        </is>
+      </c>
+      <c r="F102" s="4" t="inlineStr">
+        <is>
+          <t>-4.5</t>
+        </is>
+      </c>
       <c r="G102" s="4" t="n">
         <v>66</v>
       </c>
@@ -8325,8 +9117,16 @@
           <t>泰藝</t>
         </is>
       </c>
-      <c r="E103" s="4" t="inlineStr"/>
-      <c r="F103" s="4" t="inlineStr"/>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t>42.10</t>
+        </is>
+      </c>
+      <c r="F103" s="4" t="inlineStr">
+        <is>
+          <t>-2.85</t>
+        </is>
+      </c>
       <c r="G103" s="4" t="n">
         <v>65</v>
       </c>
@@ -8457,8 +9257,16 @@
           <t>合晶</t>
         </is>
       </c>
-      <c r="E109" s="4" t="inlineStr"/>
-      <c r="F109" s="4" t="inlineStr"/>
+      <c r="E109" s="4" t="inlineStr">
+        <is>
+          <t>40.30</t>
+        </is>
+      </c>
+      <c r="F109" s="4" t="inlineStr">
+        <is>
+          <t>-0.4</t>
+        </is>
+      </c>
       <c r="G109" s="4" t="n">
         <v>-6506</v>
       </c>
@@ -8497,8 +9305,16 @@
           <t>世界</t>
         </is>
       </c>
-      <c r="E110" s="4" t="inlineStr"/>
-      <c r="F110" s="4" t="inlineStr"/>
+      <c r="E110" s="4" t="inlineStr">
+        <is>
+          <t>138.50</t>
+        </is>
+      </c>
+      <c r="F110" s="4" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
       <c r="G110" s="4" t="n">
         <v>-6346</v>
       </c>
@@ -8529,8 +9345,16 @@
           <t>東捷</t>
         </is>
       </c>
-      <c r="E111" s="4" t="inlineStr"/>
-      <c r="F111" s="4" t="inlineStr"/>
+      <c r="E111" s="4" t="inlineStr">
+        <is>
+          <t>78.50</t>
+        </is>
+      </c>
+      <c r="F111" s="4" t="inlineStr">
+        <is>
+          <t>-5.7</t>
+        </is>
+      </c>
       <c r="G111" s="4" t="n">
         <v>-5757</v>
       </c>
@@ -8565,8 +9389,16 @@
           <t>均豪</t>
         </is>
       </c>
-      <c r="E112" s="4" t="inlineStr"/>
-      <c r="F112" s="4" t="inlineStr"/>
+      <c r="E112" s="4" t="inlineStr">
+        <is>
+          <t>106.50</t>
+        </is>
+      </c>
+      <c r="F112" s="4" t="inlineStr">
+        <is>
+          <t>-10.5</t>
+        </is>
+      </c>
       <c r="G112" s="4" t="n">
         <v>-4490</v>
       </c>
@@ -8601,8 +9433,16 @@
           <t>良維</t>
         </is>
       </c>
-      <c r="E113" s="4" t="inlineStr"/>
-      <c r="F113" s="4" t="inlineStr"/>
+      <c r="E113" s="4" t="inlineStr">
+        <is>
+          <t>285.50</t>
+        </is>
+      </c>
+      <c r="F113" s="4" t="inlineStr">
+        <is>
+          <t>-31.5</t>
+        </is>
+      </c>
       <c r="G113" s="4" t="n">
         <v>-3511</v>
       </c>
@@ -8637,8 +9477,16 @@
           <t>富喬</t>
         </is>
       </c>
-      <c r="E114" s="4" t="inlineStr"/>
-      <c r="F114" s="4" t="inlineStr"/>
+      <c r="E114" s="4" t="inlineStr">
+        <is>
+          <t>108.00</t>
+        </is>
+      </c>
+      <c r="F114" s="4" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
       <c r="G114" s="4" t="n">
         <v>-2924</v>
       </c>
@@ -8669,8 +9517,16 @@
           <t>台半</t>
         </is>
       </c>
-      <c r="E115" s="4" t="inlineStr"/>
-      <c r="F115" s="4" t="inlineStr"/>
+      <c r="E115" s="4" t="inlineStr">
+        <is>
+          <t>59.60</t>
+        </is>
+      </c>
+      <c r="F115" s="4" t="inlineStr">
+        <is>
+          <t>+1.4</t>
+        </is>
+      </c>
       <c r="G115" s="4" t="n">
         <v>-2734</v>
       </c>
@@ -8697,8 +9553,16 @@
           <t>穩懋</t>
         </is>
       </c>
-      <c r="E116" s="4" t="inlineStr"/>
-      <c r="F116" s="4" t="inlineStr"/>
+      <c r="E116" s="4" t="inlineStr">
+        <is>
+          <t>492.50</t>
+        </is>
+      </c>
+      <c r="F116" s="4" t="inlineStr">
+        <is>
+          <t>-54.5</t>
+        </is>
+      </c>
       <c r="G116" s="4" t="n">
         <v>-2283</v>
       </c>
@@ -8729,8 +9593,16 @@
           <t>頎邦</t>
         </is>
       </c>
-      <c r="E117" s="4" t="inlineStr"/>
-      <c r="F117" s="4" t="inlineStr"/>
+      <c r="E117" s="4" t="inlineStr">
+        <is>
+          <t>131.00</t>
+        </is>
+      </c>
+      <c r="F117" s="4" t="inlineStr">
+        <is>
+          <t>-14.0</t>
+        </is>
+      </c>
       <c r="G117" s="4" t="n">
         <v>-1986</v>
       </c>
@@ -8761,8 +9633,16 @@
           <t>世紀*</t>
         </is>
       </c>
-      <c r="E118" s="4" t="inlineStr"/>
-      <c r="F118" s="4" t="inlineStr"/>
+      <c r="E118" s="4" t="inlineStr">
+        <is>
+          <t>74.30</t>
+        </is>
+      </c>
+      <c r="F118" s="4" t="inlineStr">
+        <is>
+          <t>-3.0</t>
+        </is>
+      </c>
       <c r="G118" s="4" t="n">
         <v>-1833</v>
       </c>
@@ -8793,8 +9673,16 @@
           <t>尼克森</t>
         </is>
       </c>
-      <c r="E119" s="4" t="inlineStr"/>
-      <c r="F119" s="4" t="inlineStr"/>
+      <c r="E119" s="4" t="inlineStr">
+        <is>
+          <t>57.30</t>
+        </is>
+      </c>
+      <c r="F119" s="4" t="inlineStr">
+        <is>
+          <t>+2.1</t>
+        </is>
+      </c>
       <c r="G119" s="4" t="n">
         <v>-1744</v>
       </c>
@@ -8833,8 +9721,16 @@
           <t>順達</t>
         </is>
       </c>
-      <c r="E120" s="4" t="inlineStr"/>
-      <c r="F120" s="4" t="inlineStr"/>
+      <c r="E120" s="4" t="inlineStr">
+        <is>
+          <t>385.50</t>
+        </is>
+      </c>
+      <c r="F120" s="4" t="inlineStr">
+        <is>
+          <t>+4.0</t>
+        </is>
+      </c>
       <c r="G120" s="4" t="n">
         <v>-1675</v>
       </c>
@@ -8861,8 +9757,16 @@
           <t>久元</t>
         </is>
       </c>
-      <c r="E121" s="4" t="inlineStr"/>
-      <c r="F121" s="4" t="inlineStr"/>
+      <c r="E121" s="4" t="inlineStr">
+        <is>
+          <t>90.60</t>
+        </is>
+      </c>
+      <c r="F121" s="4" t="inlineStr">
+        <is>
+          <t>-4.5</t>
+        </is>
+      </c>
       <c r="G121" s="4" t="n">
         <v>-1455</v>
       </c>
@@ -8897,8 +9801,16 @@
           <t>鈦昇</t>
         </is>
       </c>
-      <c r="E122" s="4" t="inlineStr"/>
-      <c r="F122" s="4" t="inlineStr"/>
+      <c r="E122" s="4" t="inlineStr">
+        <is>
+          <t>159.00</t>
+        </is>
+      </c>
+      <c r="F122" s="4" t="inlineStr">
+        <is>
+          <t>+2.5</t>
+        </is>
+      </c>
       <c r="G122" s="4" t="n">
         <v>-1442</v>
       </c>
@@ -8929,8 +9841,16 @@
           <t>萬泰科</t>
         </is>
       </c>
-      <c r="E123" s="4" t="inlineStr"/>
-      <c r="F123" s="4" t="inlineStr"/>
+      <c r="E123" s="4" t="inlineStr">
+        <is>
+          <t>72.50</t>
+        </is>
+      </c>
+      <c r="F123" s="4" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
       <c r="G123" s="4" t="n">
         <v>-1420</v>
       </c>
@@ -8957,8 +9877,16 @@
           <t>元太</t>
         </is>
       </c>
-      <c r="E124" s="4" t="inlineStr"/>
-      <c r="F124" s="4" t="inlineStr"/>
+      <c r="E124" s="4" t="inlineStr">
+        <is>
+          <t>141.00</t>
+        </is>
+      </c>
+      <c r="F124" s="4" t="inlineStr">
+        <is>
+          <t>-3.0</t>
+        </is>
+      </c>
       <c r="G124" s="4" t="n">
         <v>-1364</v>
       </c>
@@ -8989,8 +9917,16 @@
           <t>榮剛</t>
         </is>
       </c>
-      <c r="E125" s="4" t="inlineStr"/>
-      <c r="F125" s="4" t="inlineStr"/>
+      <c r="E125" s="4" t="inlineStr">
+        <is>
+          <t>30.80</t>
+        </is>
+      </c>
+      <c r="F125" s="4" t="inlineStr">
+        <is>
+          <t>-0.55</t>
+        </is>
+      </c>
       <c r="G125" s="4" t="n">
         <v>-1263</v>
       </c>
@@ -9021,8 +9957,16 @@
           <t>國統</t>
         </is>
       </c>
-      <c r="E126" s="4" t="inlineStr"/>
-      <c r="F126" s="4" t="inlineStr"/>
+      <c r="E126" s="4" t="inlineStr">
+        <is>
+          <t>49.60</t>
+        </is>
+      </c>
+      <c r="F126" s="4" t="inlineStr">
+        <is>
+          <t>-0.35</t>
+        </is>
+      </c>
       <c r="G126" s="4" t="n">
         <v>-1009</v>
       </c>
@@ -9053,8 +9997,16 @@
           <t>台星科</t>
         </is>
       </c>
-      <c r="E127" s="4" t="inlineStr"/>
-      <c r="F127" s="4" t="inlineStr"/>
+      <c r="E127" s="4" t="inlineStr">
+        <is>
+          <t>164.50</t>
+        </is>
+      </c>
+      <c r="F127" s="4" t="inlineStr">
+        <is>
+          <t>-9.0</t>
+        </is>
+      </c>
       <c r="G127" s="4" t="n">
         <v>-975</v>
       </c>
@@ -9085,8 +10037,16 @@
           <t>欣銓</t>
         </is>
       </c>
-      <c r="E128" s="4" t="inlineStr"/>
-      <c r="F128" s="4" t="inlineStr"/>
+      <c r="E128" s="4" t="inlineStr">
+        <is>
+          <t>194.00</t>
+        </is>
+      </c>
+      <c r="F128" s="4" t="inlineStr">
+        <is>
+          <t>-16.0</t>
+        </is>
+      </c>
       <c r="G128" s="4" t="n">
         <v>-866</v>
       </c>
@@ -9117,8 +10077,16 @@
           <t>雙鴻</t>
         </is>
       </c>
-      <c r="E129" s="4" t="inlineStr"/>
-      <c r="F129" s="4" t="inlineStr"/>
+      <c r="E129" s="4" t="inlineStr">
+        <is>
+          <t>1180.00</t>
+        </is>
+      </c>
+      <c r="F129" s="4" t="inlineStr">
+        <is>
+          <t>-35.0</t>
+        </is>
+      </c>
       <c r="G129" s="4" t="n">
         <v>-814</v>
       </c>
@@ -9145,8 +10113,16 @@
           <t>譜瑞-KY</t>
         </is>
       </c>
-      <c r="E130" s="4" t="inlineStr"/>
-      <c r="F130" s="4" t="inlineStr"/>
+      <c r="E130" s="4" t="inlineStr">
+        <is>
+          <t>615.00</t>
+        </is>
+      </c>
+      <c r="F130" s="4" t="inlineStr">
+        <is>
+          <t>-34.0</t>
+        </is>
+      </c>
       <c r="G130" s="4" t="n">
         <v>-813</v>
       </c>
@@ -9181,8 +10157,16 @@
           <t>力麒</t>
         </is>
       </c>
-      <c r="E131" s="4" t="inlineStr"/>
-      <c r="F131" s="4" t="inlineStr"/>
+      <c r="E131" s="4" t="inlineStr">
+        <is>
+          <t>7.51</t>
+        </is>
+      </c>
+      <c r="F131" s="4" t="inlineStr">
+        <is>
+          <t>-0.19</t>
+        </is>
+      </c>
       <c r="G131" s="4" t="n">
         <v>-784</v>
       </c>
@@ -9209,8 +10193,16 @@
           <t>湧德</t>
         </is>
       </c>
-      <c r="E132" s="4" t="inlineStr"/>
-      <c r="F132" s="4" t="inlineStr"/>
+      <c r="E132" s="4" t="inlineStr">
+        <is>
+          <t>131.50</t>
+        </is>
+      </c>
+      <c r="F132" s="4" t="inlineStr">
+        <is>
+          <t>-1.5</t>
+        </is>
+      </c>
       <c r="G132" s="4" t="n">
         <v>-770</v>
       </c>
@@ -9237,8 +10229,16 @@
           <t>閎康</t>
         </is>
       </c>
-      <c r="E133" s="4" t="inlineStr"/>
-      <c r="F133" s="4" t="inlineStr"/>
+      <c r="E133" s="4" t="inlineStr">
+        <is>
+          <t>313.00</t>
+        </is>
+      </c>
+      <c r="F133" s="4" t="inlineStr">
+        <is>
+          <t>-34.5</t>
+        </is>
+      </c>
       <c r="G133" s="4" t="n">
         <v>-721</v>
       </c>
@@ -9269,8 +10269,16 @@
           <t>漢磊</t>
         </is>
       </c>
-      <c r="E134" s="4" t="inlineStr"/>
-      <c r="F134" s="4" t="inlineStr"/>
+      <c r="E134" s="4" t="inlineStr">
+        <is>
+          <t>56.50</t>
+        </is>
+      </c>
+      <c r="F134" s="4" t="inlineStr">
+        <is>
+          <t>+0.8</t>
+        </is>
+      </c>
       <c r="G134" s="4" t="n">
         <v>-596</v>
       </c>
@@ -9297,8 +10305,16 @@
           <t>原相</t>
         </is>
       </c>
-      <c r="E135" s="4" t="inlineStr"/>
-      <c r="F135" s="4" t="inlineStr"/>
+      <c r="E135" s="4" t="inlineStr">
+        <is>
+          <t>205.50</t>
+        </is>
+      </c>
+      <c r="F135" s="4" t="inlineStr">
+        <is>
+          <t>-6.5</t>
+        </is>
+      </c>
       <c r="G135" s="4" t="n">
         <v>-595</v>
       </c>
@@ -9325,8 +10341,16 @@
           <t>旭軟</t>
         </is>
       </c>
-      <c r="E136" s="4" t="inlineStr"/>
-      <c r="F136" s="4" t="inlineStr"/>
+      <c r="E136" s="4" t="inlineStr">
+        <is>
+          <t>27.80</t>
+        </is>
+      </c>
+      <c r="F136" s="4" t="inlineStr">
+        <is>
+          <t>-0.95</t>
+        </is>
+      </c>
       <c r="G136" s="4" t="n">
         <v>-546</v>
       </c>
@@ -9361,8 +10385,16 @@
           <t>太欣</t>
         </is>
       </c>
-      <c r="E137" s="4" t="inlineStr"/>
-      <c r="F137" s="4" t="inlineStr"/>
+      <c r="E137" s="4" t="inlineStr">
+        <is>
+          <t>11.65</t>
+        </is>
+      </c>
+      <c r="F137" s="4" t="inlineStr">
+        <is>
+          <t>-0.3</t>
+        </is>
+      </c>
       <c r="G137" s="4" t="n">
         <v>-525</v>
       </c>
@@ -9397,8 +10429,16 @@
           <t>波若威</t>
         </is>
       </c>
-      <c r="E138" s="4" t="inlineStr"/>
-      <c r="F138" s="4" t="inlineStr"/>
+      <c r="E138" s="4" t="inlineStr">
+        <is>
+          <t>1040.00</t>
+        </is>
+      </c>
+      <c r="F138" s="4" t="inlineStr">
+        <is>
+          <t>-115.0</t>
+        </is>
+      </c>
       <c r="G138" s="4" t="n">
         <v>-509</v>
       </c>
@@ -9429,8 +10469,16 @@
           <t>瑞耘</t>
         </is>
       </c>
-      <c r="E139" s="4" t="inlineStr"/>
-      <c r="F139" s="4" t="inlineStr"/>
+      <c r="E139" s="4" t="inlineStr">
+        <is>
+          <t>99.50</t>
+        </is>
+      </c>
+      <c r="F139" s="4" t="inlineStr">
+        <is>
+          <t>-6.5</t>
+        </is>
+      </c>
       <c r="G139" s="4" t="n">
         <v>-483</v>
       </c>
@@ -9465,8 +10513,16 @@
           <t>互動</t>
         </is>
       </c>
-      <c r="E140" s="4" t="inlineStr"/>
-      <c r="F140" s="4" t="inlineStr"/>
+      <c r="E140" s="4" t="inlineStr">
+        <is>
+          <t>86.20</t>
+        </is>
+      </c>
+      <c r="F140" s="4" t="inlineStr">
+        <is>
+          <t>-4.2</t>
+        </is>
+      </c>
       <c r="G140" s="4" t="n">
         <v>-457</v>
       </c>
@@ -9501,8 +10557,16 @@
           <t>立敦</t>
         </is>
       </c>
-      <c r="E141" s="4" t="inlineStr"/>
-      <c r="F141" s="4" t="inlineStr"/>
+      <c r="E141" s="4" t="inlineStr">
+        <is>
+          <t>60.70</t>
+        </is>
+      </c>
+      <c r="F141" s="4" t="inlineStr">
+        <is>
+          <t>-2.8</t>
+        </is>
+      </c>
       <c r="G141" s="4" t="n">
         <v>-450</v>
       </c>
@@ -9529,8 +10593,16 @@
           <t>健喬</t>
         </is>
       </c>
-      <c r="E142" s="4" t="inlineStr"/>
-      <c r="F142" s="4" t="inlineStr"/>
+      <c r="E142" s="4" t="inlineStr">
+        <is>
+          <t>30.95</t>
+        </is>
+      </c>
+      <c r="F142" s="4" t="inlineStr">
+        <is>
+          <t>-0.05</t>
+        </is>
+      </c>
       <c r="G142" s="4" t="n">
         <v>-445</v>
       </c>
@@ -9561,8 +10633,16 @@
           <t>福邦證</t>
         </is>
       </c>
-      <c r="E143" s="4" t="inlineStr"/>
-      <c r="F143" s="4" t="inlineStr"/>
+      <c r="E143" s="4" t="inlineStr">
+        <is>
+          <t>14.95</t>
+        </is>
+      </c>
+      <c r="F143" s="4" t="inlineStr">
+        <is>
+          <t>+0.05</t>
+        </is>
+      </c>
       <c r="G143" s="4" t="n">
         <v>-409</v>
       </c>
@@ -9589,8 +10669,16 @@
           <t>建舜電</t>
         </is>
       </c>
-      <c r="E144" s="4" t="inlineStr"/>
-      <c r="F144" s="4" t="inlineStr"/>
+      <c r="E144" s="4" t="inlineStr">
+        <is>
+          <t>13.80</t>
+        </is>
+      </c>
+      <c r="F144" s="4" t="inlineStr">
+        <is>
+          <t>-0.7</t>
+        </is>
+      </c>
       <c r="G144" s="4" t="n">
         <v>-393</v>
       </c>
@@ -9617,8 +10705,16 @@
           <t>力致</t>
         </is>
       </c>
-      <c r="E145" s="4" t="inlineStr"/>
-      <c r="F145" s="4" t="inlineStr"/>
+      <c r="E145" s="4" t="inlineStr">
+        <is>
+          <t>97.00</t>
+        </is>
+      </c>
+      <c r="F145" s="4" t="inlineStr">
+        <is>
+          <t>-2.1</t>
+        </is>
+      </c>
       <c r="G145" s="4" t="n">
         <v>-391</v>
       </c>
@@ -9649,8 +10745,16 @@
           <t>川寶</t>
         </is>
       </c>
-      <c r="E146" s="4" t="inlineStr"/>
-      <c r="F146" s="4" t="inlineStr"/>
+      <c r="E146" s="4" t="inlineStr">
+        <is>
+          <t>65.90</t>
+        </is>
+      </c>
+      <c r="F146" s="4" t="inlineStr">
+        <is>
+          <t>-0.7</t>
+        </is>
+      </c>
       <c r="G146" s="4" t="n">
         <v>-386</v>
       </c>
@@ -9685,8 +10789,16 @@
           <t>永信建</t>
         </is>
       </c>
-      <c r="E147" s="4" t="inlineStr"/>
-      <c r="F147" s="4" t="inlineStr"/>
+      <c r="E147" s="4" t="inlineStr">
+        <is>
+          <t>49.85</t>
+        </is>
+      </c>
+      <c r="F147" s="4" t="inlineStr">
+        <is>
+          <t>-0.55</t>
+        </is>
+      </c>
       <c r="G147" s="4" t="n">
         <v>-368</v>
       </c>
@@ -9713,8 +10825,16 @@
           <t>家登</t>
         </is>
       </c>
-      <c r="E148" s="4" t="inlineStr"/>
-      <c r="F148" s="4" t="inlineStr"/>
+      <c r="E148" s="4" t="inlineStr">
+        <is>
+          <t>449.00</t>
+        </is>
+      </c>
+      <c r="F148" s="4" t="inlineStr">
+        <is>
+          <t>-10.0</t>
+        </is>
+      </c>
       <c r="G148" s="4" t="n">
         <v>-364</v>
       </c>
@@ -9745,8 +10865,16 @@
           <t>千附</t>
         </is>
       </c>
-      <c r="E149" s="4" t="inlineStr"/>
-      <c r="F149" s="4" t="inlineStr"/>
+      <c r="E149" s="4" t="inlineStr">
+        <is>
+          <t>64.30</t>
+        </is>
+      </c>
+      <c r="F149" s="4" t="inlineStr">
+        <is>
+          <t>-0.0</t>
+        </is>
+      </c>
       <c r="G149" s="4" t="n">
         <v>-362</v>
       </c>
@@ -9773,8 +10901,16 @@
           <t>晟德</t>
         </is>
       </c>
-      <c r="E150" s="4" t="inlineStr"/>
-      <c r="F150" s="4" t="inlineStr"/>
+      <c r="E150" s="4" t="inlineStr">
+        <is>
+          <t>38.85</t>
+        </is>
+      </c>
+      <c r="F150" s="4" t="inlineStr">
+        <is>
+          <t>-0.45</t>
+        </is>
+      </c>
       <c r="G150" s="4" t="n">
         <v>-358</v>
       </c>
@@ -9805,8 +10941,16 @@
           <t>華景電</t>
         </is>
       </c>
-      <c r="E151" s="4" t="inlineStr"/>
-      <c r="F151" s="4" t="inlineStr"/>
+      <c r="E151" s="4" t="inlineStr">
+        <is>
+          <t>435.00</t>
+        </is>
+      </c>
+      <c r="F151" s="4" t="inlineStr">
+        <is>
+          <t>-24.0</t>
+        </is>
+      </c>
       <c r="G151" s="4" t="n">
         <v>-343</v>
       </c>
@@ -9833,8 +10977,16 @@
           <t>長科*</t>
         </is>
       </c>
-      <c r="E152" s="4" t="inlineStr"/>
-      <c r="F152" s="4" t="inlineStr"/>
+      <c r="E152" s="4" t="inlineStr">
+        <is>
+          <t>52.30</t>
+        </is>
+      </c>
+      <c r="F152" s="4" t="inlineStr">
+        <is>
+          <t>-2.2</t>
+        </is>
+      </c>
       <c r="G152" s="4" t="n">
         <v>-334</v>
       </c>
@@ -9861,8 +11013,16 @@
           <t>友輝</t>
         </is>
       </c>
-      <c r="E153" s="4" t="inlineStr"/>
-      <c r="F153" s="4" t="inlineStr"/>
+      <c r="E153" s="4" t="inlineStr">
+        <is>
+          <t>70.60</t>
+        </is>
+      </c>
+      <c r="F153" s="4" t="inlineStr">
+        <is>
+          <t>+3.1</t>
+        </is>
+      </c>
       <c r="G153" s="4" t="n">
         <v>-317</v>
       </c>
@@ -9897,8 +11057,16 @@
           <t>系微</t>
         </is>
       </c>
-      <c r="E154" s="4" t="inlineStr"/>
-      <c r="F154" s="4" t="inlineStr"/>
+      <c r="E154" s="4" t="inlineStr">
+        <is>
+          <t>319.00</t>
+        </is>
+      </c>
+      <c r="F154" s="4" t="inlineStr">
+        <is>
+          <t>-5.5</t>
+        </is>
+      </c>
       <c r="G154" s="4" t="n">
         <v>-310</v>
       </c>
@@ -9925,8 +11093,16 @@
           <t>金居</t>
         </is>
       </c>
-      <c r="E155" s="4" t="inlineStr"/>
-      <c r="F155" s="4" t="inlineStr"/>
+      <c r="E155" s="4" t="inlineStr">
+        <is>
+          <t>335.50</t>
+        </is>
+      </c>
+      <c r="F155" s="4" t="inlineStr">
+        <is>
+          <t>-24.0</t>
+        </is>
+      </c>
       <c r="G155" s="4" t="n">
         <v>-310</v>
       </c>
@@ -9953,8 +11129,16 @@
           <t>陽程</t>
         </is>
       </c>
-      <c r="E156" s="4" t="inlineStr"/>
-      <c r="F156" s="4" t="inlineStr"/>
+      <c r="E156" s="4" t="inlineStr">
+        <is>
+          <t>77.00</t>
+        </is>
+      </c>
+      <c r="F156" s="4" t="inlineStr">
+        <is>
+          <t>-1.3</t>
+        </is>
+      </c>
       <c r="G156" s="4" t="n">
         <v>-307</v>
       </c>
@@ -9981,8 +11165,16 @@
           <t>世禾</t>
         </is>
       </c>
-      <c r="E157" s="4" t="inlineStr"/>
-      <c r="F157" s="4" t="inlineStr"/>
+      <c r="E157" s="4" t="inlineStr">
+        <is>
+          <t>201.50</t>
+        </is>
+      </c>
+      <c r="F157" s="4" t="inlineStr">
+        <is>
+          <t>-8.0</t>
+        </is>
+      </c>
       <c r="G157" s="4" t="n">
         <v>-307</v>
       </c>
@@ -10009,8 +11201,16 @@
           <t>精確</t>
         </is>
       </c>
-      <c r="E158" s="4" t="inlineStr"/>
-      <c r="F158" s="4" t="inlineStr"/>
+      <c r="E158" s="4" t="inlineStr">
+        <is>
+          <t>81.60</t>
+        </is>
+      </c>
+      <c r="F158" s="4" t="inlineStr">
+        <is>
+          <t>-0.2</t>
+        </is>
+      </c>
       <c r="G158" s="4" t="n">
         <v>-306</v>
       </c>
@@ -25474,16 +26674,8 @@
           <t>威剛</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>393.50</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>+35.5</t>
-        </is>
-      </c>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr"/>
       <c r="G4" s="4" t="n">
         <v>10280</v>
       </c>
@@ -25507,16 +26699,8 @@
           <t>凱崴</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>83.10</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>+7.5</t>
-        </is>
-      </c>
+      <c r="E5" s="4" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr"/>
       <c r="G5" s="4" t="n">
         <v>6305</v>
       </c>
@@ -25540,16 +26724,8 @@
           <t>環球晶</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>597.00</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>+46.0</t>
-        </is>
-      </c>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr"/>
       <c r="G6" s="4" t="n">
         <v>3900</v>
       </c>
@@ -25573,16 +26749,8 @@
           <t>頎邦</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>135.50</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>+9.0</t>
-        </is>
-      </c>
+      <c r="E7" s="4" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr"/>
       <c r="G7" s="4" t="n">
         <v>3386</v>
       </c>
@@ -25606,16 +26774,8 @@
           <t>鑫聯大投控</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>77.30</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>+7.0</t>
-        </is>
-      </c>
+      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr"/>
       <c r="G8" s="4" t="n">
         <v>3353</v>
       </c>
@@ -25639,16 +26799,8 @@
           <t>欣銓</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>206.00</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>+18.5</t>
-        </is>
-      </c>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr"/>
       <c r="G9" s="4" t="n">
         <v>2736</v>
       </c>
@@ -25672,16 +26824,8 @@
           <t>中美晶</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>134.50</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>+3.0</t>
-        </is>
-      </c>
+      <c r="E10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr"/>
       <c r="G10" s="4" t="n">
         <v>2552</v>
       </c>
@@ -25705,16 +26849,8 @@
           <t>順達</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>379.50</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>+10.5</t>
-        </is>
-      </c>
+      <c r="E11" s="4" t="inlineStr"/>
+      <c r="F11" s="4" t="inlineStr"/>
       <c r="G11" s="4" t="n">
         <v>1572</v>
       </c>
@@ -25738,16 +26874,8 @@
           <t>立碁</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>80.90</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>+3.3</t>
-        </is>
-      </c>
+      <c r="E12" s="4" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr"/>
       <c r="G12" s="4" t="n">
         <v>1527</v>
       </c>
@@ -25771,16 +26899,8 @@
           <t>廣穎</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>87.30</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>+7.9</t>
-        </is>
-      </c>
+      <c r="E13" s="4" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr"/>
       <c r="G13" s="4" t="n">
         <v>1481</v>
       </c>
@@ -25804,16 +26924,8 @@
           <t>神盾</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>130.50</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>+11.5</t>
-        </is>
-      </c>
+      <c r="E14" s="4" t="inlineStr"/>
+      <c r="F14" s="4" t="inlineStr"/>
       <c r="G14" s="4" t="n">
         <v>1314</v>
       </c>
@@ -25837,16 +26949,8 @@
           <t>漢磊</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>59.10</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>+1.2</t>
-        </is>
-      </c>
+      <c r="E15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr"/>
       <c r="G15" s="4" t="n">
         <v>1155</v>
       </c>
@@ -25870,16 +26974,8 @@
           <t>聖暉*</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>890.00</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>+27.0</t>
-        </is>
-      </c>
+      <c r="E16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr"/>
       <c r="G16" s="4" t="n">
         <v>1088</v>
       </c>
@@ -25903,16 +26999,8 @@
           <t>品安</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>55.10</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>+5.0</t>
-        </is>
-      </c>
+      <c r="E17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr"/>
       <c r="G17" s="4" t="n">
         <v>1048</v>
       </c>
@@ -25936,16 +27024,8 @@
           <t>九豪</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>50.10</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>+2.1</t>
-        </is>
-      </c>
+      <c r="E18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr"/>
       <c r="G18" s="4" t="n">
         <v>1045</v>
       </c>
@@ -25969,16 +27049,8 @@
           <t>合晶</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>43.25</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>+3.9</t>
-        </is>
-      </c>
+      <c r="E19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr"/>
       <c r="G19" s="4" t="n">
         <v>1027</v>
       </c>
@@ -26002,16 +27074,8 @@
           <t>光洋科</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>155.00</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>+1.5</t>
-        </is>
-      </c>
+      <c r="E20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr"/>
       <c r="G20" s="4" t="n">
         <v>1006</v>
       </c>
@@ -26035,16 +27099,8 @@
           <t>康和證</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>17.90</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>+0.15</t>
-        </is>
-      </c>
+      <c r="E21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr"/>
       <c r="G21" s="4" t="n">
         <v>955</v>
       </c>
@@ -26068,16 +27124,8 @@
           <t>中探針</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>283.00</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>+15.0</t>
-        </is>
-      </c>
+      <c r="E22" s="4" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr"/>
       <c r="G22" s="4" t="n">
         <v>814</v>
       </c>
@@ -26101,16 +27149,8 @@
           <t>陽程</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>87.60</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>+1.7</t>
-        </is>
-      </c>
+      <c r="E23" s="4" t="inlineStr"/>
+      <c r="F23" s="4" t="inlineStr"/>
       <c r="G23" s="4" t="n">
         <v>807</v>
       </c>
@@ -26134,16 +27174,8 @@
           <t>臺慶科</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>188.00</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>+5.5</t>
-        </is>
-      </c>
+      <c r="E24" s="4" t="inlineStr"/>
+      <c r="F24" s="4" t="inlineStr"/>
       <c r="G24" s="4" t="n">
         <v>773</v>
       </c>
@@ -26167,16 +27199,8 @@
           <t>金山電</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>65.50</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>+0.8</t>
-        </is>
-      </c>
+      <c r="E25" s="4" t="inlineStr"/>
+      <c r="F25" s="4" t="inlineStr"/>
       <c r="G25" s="4" t="n">
         <v>761</v>
       </c>
@@ -26200,16 +27224,8 @@
           <t>匯鑽科</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>70.40</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>+3.7</t>
-        </is>
-      </c>
+      <c r="E26" s="4" t="inlineStr"/>
+      <c r="F26" s="4" t="inlineStr"/>
       <c r="G26" s="4" t="n">
         <v>729</v>
       </c>
@@ -26233,16 +27249,8 @@
           <t>新盛力</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>145.00</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>+2.5</t>
-        </is>
-      </c>
+      <c r="E27" s="4" t="inlineStr"/>
+      <c r="F27" s="4" t="inlineStr"/>
       <c r="G27" s="4" t="n">
         <v>718</v>
       </c>
@@ -26266,16 +27274,8 @@
           <t>國統</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>50.90</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>+1.0</t>
-        </is>
-      </c>
+      <c r="E28" s="4" t="inlineStr"/>
+      <c r="F28" s="4" t="inlineStr"/>
       <c r="G28" s="4" t="n">
         <v>710</v>
       </c>
@@ -26299,16 +27299,8 @@
           <t>雙鴻</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>1050.00</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>+10.0</t>
-        </is>
-      </c>
+      <c r="E29" s="4" t="inlineStr"/>
+      <c r="F29" s="4" t="inlineStr"/>
       <c r="G29" s="4" t="n">
         <v>693</v>
       </c>
@@ -26332,16 +27324,8 @@
           <t>華景電</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>508.00</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>+34.0</t>
-        </is>
-      </c>
+      <c r="E30" s="4" t="inlineStr"/>
+      <c r="F30" s="4" t="inlineStr"/>
       <c r="G30" s="4" t="n">
         <v>667</v>
       </c>
@@ -26365,16 +27349,8 @@
           <t>光頡</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>56.60</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>-0.7</t>
-        </is>
-      </c>
+      <c r="E31" s="4" t="inlineStr"/>
+      <c r="F31" s="4" t="inlineStr"/>
       <c r="G31" s="4" t="n">
         <v>666</v>
       </c>
@@ -26398,16 +27374,8 @@
           <t>沛亨</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>460.00</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>+41.5</t>
-        </is>
-      </c>
+      <c r="E32" s="4" t="inlineStr"/>
+      <c r="F32" s="4" t="inlineStr"/>
       <c r="G32" s="4" t="n">
         <v>656</v>
       </c>
@@ -26431,16 +27399,8 @@
           <t>華容</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>26.25</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>+0.4</t>
-        </is>
-      </c>
+      <c r="E33" s="4" t="inlineStr"/>
+      <c r="F33" s="4" t="inlineStr"/>
       <c r="G33" s="4" t="n">
         <v>652</v>
       </c>
@@ -26464,16 +27424,8 @@
           <t>美琪瑪</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>93.00</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>+1.6</t>
-        </is>
-      </c>
+      <c r="E34" s="4" t="inlineStr"/>
+      <c r="F34" s="4" t="inlineStr"/>
       <c r="G34" s="4" t="n">
         <v>647</v>
       </c>
@@ -26497,16 +27449,8 @@
           <t>立端</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>85.50</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>+1.6</t>
-        </is>
-      </c>
+      <c r="E35" s="4" t="inlineStr"/>
+      <c r="F35" s="4" t="inlineStr"/>
       <c r="G35" s="4" t="n">
         <v>621</v>
       </c>
@@ -26530,16 +27474,8 @@
           <t>立敦</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>66.20</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>+0.6</t>
-        </is>
-      </c>
+      <c r="E36" s="4" t="inlineStr"/>
+      <c r="F36" s="4" t="inlineStr"/>
       <c r="G36" s="4" t="n">
         <v>588</v>
       </c>
@@ -26563,16 +27499,8 @@
           <t>福華</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>14.55</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>+0.3</t>
-        </is>
-      </c>
+      <c r="E37" s="4" t="inlineStr"/>
+      <c r="F37" s="4" t="inlineStr"/>
       <c r="G37" s="4" t="n">
         <v>565</v>
       </c>
@@ -26596,16 +27524,8 @@
           <t>富強鑫</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>26.20</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>+1.0</t>
-        </is>
-      </c>
+      <c r="E38" s="4" t="inlineStr"/>
+      <c r="F38" s="4" t="inlineStr"/>
       <c r="G38" s="4" t="n">
         <v>558</v>
       </c>
@@ -26629,16 +27549,8 @@
           <t>萬潤</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>1330.00</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>+105.0</t>
-        </is>
-      </c>
+      <c r="E39" s="4" t="inlineStr"/>
+      <c r="F39" s="4" t="inlineStr"/>
       <c r="G39" s="4" t="n">
         <v>554</v>
       </c>
@@ -26662,16 +27574,8 @@
           <t>信昌電</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>89.40</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>-1.3</t>
-        </is>
-      </c>
+      <c r="E40" s="4" t="inlineStr"/>
+      <c r="F40" s="4" t="inlineStr"/>
       <c r="G40" s="4" t="n">
         <v>552</v>
       </c>
@@ -26695,16 +27599,8 @@
           <t>致和證</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>25.25</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>+0.25</t>
-        </is>
-      </c>
+      <c r="E41" s="4" t="inlineStr"/>
+      <c r="F41" s="4" t="inlineStr"/>
       <c r="G41" s="4" t="n">
         <v>549</v>
       </c>
@@ -26728,16 +27624,8 @@
           <t>耕興</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>219.50</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>-4.0</t>
-        </is>
-      </c>
+      <c r="E42" s="4" t="inlineStr"/>
+      <c r="F42" s="4" t="inlineStr"/>
       <c r="G42" s="4" t="n">
         <v>519</v>
       </c>
@@ -26761,16 +27649,8 @@
           <t>典範</t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>20.30</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>+0.3</t>
-        </is>
-      </c>
+      <c r="E43" s="4" t="inlineStr"/>
+      <c r="F43" s="4" t="inlineStr"/>
       <c r="G43" s="4" t="n">
         <v>442</v>
       </c>
@@ -26794,16 +27674,8 @@
           <t>港建*</t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>69.30</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>-4.2</t>
-        </is>
-      </c>
+      <c r="E44" s="4" t="inlineStr"/>
+      <c r="F44" s="4" t="inlineStr"/>
       <c r="G44" s="4" t="n">
         <v>435</v>
       </c>
@@ -26827,16 +27699,8 @@
           <t>世禾</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>213.50</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>+4.0</t>
-        </is>
-      </c>
+      <c r="E45" s="4" t="inlineStr"/>
+      <c r="F45" s="4" t="inlineStr"/>
       <c r="G45" s="4" t="n">
         <v>426</v>
       </c>
@@ -26860,16 +27724,8 @@
           <t>系統電</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>61.60</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>+1.4</t>
-        </is>
-      </c>
+      <c r="E46" s="4" t="inlineStr"/>
+      <c r="F46" s="4" t="inlineStr"/>
       <c r="G46" s="4" t="n">
         <v>419</v>
       </c>
@@ -26893,16 +27749,8 @@
           <t>高僑</t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>34.80</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t>+0.7</t>
-        </is>
-      </c>
+      <c r="E47" s="4" t="inlineStr"/>
+      <c r="F47" s="4" t="inlineStr"/>
       <c r="G47" s="4" t="n">
         <v>407</v>
       </c>
@@ -26926,16 +27774,8 @@
           <t>茂迪</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>28.85</t>
-        </is>
-      </c>
-      <c r="F48" s="4" t="inlineStr">
-        <is>
-          <t>+0.05</t>
-        </is>
-      </c>
+      <c r="E48" s="4" t="inlineStr"/>
+      <c r="F48" s="4" t="inlineStr"/>
       <c r="G48" s="4" t="n">
         <v>398</v>
       </c>
@@ -26959,16 +27799,8 @@
           <t>鈺創</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>68.60</t>
-        </is>
-      </c>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>+2.6</t>
-        </is>
-      </c>
+      <c r="E49" s="4" t="inlineStr"/>
+      <c r="F49" s="4" t="inlineStr"/>
       <c r="G49" s="4" t="n">
         <v>370</v>
       </c>
@@ -26992,16 +27824,8 @@
           <t>耀勝</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>68.90</t>
-        </is>
-      </c>
-      <c r="F50" s="4" t="inlineStr">
-        <is>
-          <t>+3.8</t>
-        </is>
-      </c>
+      <c r="E50" s="4" t="inlineStr"/>
+      <c r="F50" s="4" t="inlineStr"/>
       <c r="G50" s="4" t="n">
         <v>352</v>
       </c>
@@ -27025,16 +27849,8 @@
           <t>榮剛</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>33.75</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="inlineStr">
-        <is>
-          <t>+0.05</t>
-        </is>
-      </c>
+      <c r="E51" s="4" t="inlineStr"/>
+      <c r="F51" s="4" t="inlineStr"/>
       <c r="G51" s="4" t="n">
         <v>346</v>
       </c>
@@ -27058,16 +27874,8 @@
           <t>寶雅</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>543.00</t>
-        </is>
-      </c>
-      <c r="F52" s="4" t="inlineStr">
-        <is>
-          <t>+24.0</t>
-        </is>
-      </c>
+      <c r="E52" s="4" t="inlineStr"/>
+      <c r="F52" s="4" t="inlineStr"/>
       <c r="G52" s="4" t="n">
         <v>342</v>
       </c>
@@ -27091,16 +27899,8 @@
           <t>鈦昇</t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>149.50</t>
-        </is>
-      </c>
-      <c r="F53" s="4" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
+      <c r="E53" s="4" t="inlineStr"/>
+      <c r="F53" s="4" t="inlineStr"/>
       <c r="G53" s="4" t="n">
         <v>341</v>
       </c>
@@ -27124,16 +27924,8 @@
           <t>森鉅</t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>43.60</t>
-        </is>
-      </c>
-      <c r="F54" s="4" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
+      <c r="E54" s="4" t="inlineStr"/>
+      <c r="F54" s="4" t="inlineStr"/>
       <c r="G54" s="4" t="n">
         <v>320</v>
       </c>
@@ -27157,16 +27949,8 @@
           <t>奇鈦科</t>
         </is>
       </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>103.50</t>
-        </is>
-      </c>
-      <c r="F55" s="4" t="inlineStr">
-        <is>
-          <t>+9.4</t>
-        </is>
-      </c>
+      <c r="E55" s="4" t="inlineStr"/>
+      <c r="F55" s="4" t="inlineStr"/>
       <c r="G55" s="4" t="n">
         <v>319</v>
       </c>
@@ -27190,16 +27974,8 @@
           <t>光譜</t>
         </is>
       </c>
-      <c r="E56" s="4" t="inlineStr">
-        <is>
-          <t>24.50</t>
-        </is>
-      </c>
-      <c r="F56" s="4" t="inlineStr">
-        <is>
-          <t>-0.6</t>
-        </is>
-      </c>
+      <c r="E56" s="4" t="inlineStr"/>
+      <c r="F56" s="4" t="inlineStr"/>
       <c r="G56" s="4" t="n">
         <v>309</v>
       </c>
@@ -27223,16 +27999,8 @@
           <t>九暘</t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr">
-        <is>
-          <t>65.40</t>
-        </is>
-      </c>
-      <c r="F57" s="4" t="inlineStr">
-        <is>
-          <t>+5.9</t>
-        </is>
-      </c>
+      <c r="E57" s="4" t="inlineStr"/>
+      <c r="F57" s="4" t="inlineStr"/>
       <c r="G57" s="4" t="n">
         <v>299</v>
       </c>
@@ -27256,16 +28024,8 @@
           <t>艾訊</t>
         </is>
       </c>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t>103.00</t>
-        </is>
-      </c>
-      <c r="F58" s="4" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
+      <c r="E58" s="4" t="inlineStr"/>
+      <c r="F58" s="4" t="inlineStr"/>
       <c r="G58" s="4" t="n">
         <v>291</v>
       </c>
@@ -27289,16 +28049,8 @@
           <t>晟田</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>48.60</t>
-        </is>
-      </c>
-      <c r="F59" s="4" t="inlineStr">
-        <is>
-          <t>-0.75</t>
-        </is>
-      </c>
+      <c r="E59" s="4" t="inlineStr"/>
+      <c r="F59" s="4" t="inlineStr"/>
       <c r="G59" s="4" t="n">
         <v>287</v>
       </c>
@@ -27322,16 +28074,8 @@
           <t>倍微</t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>29.00</t>
-        </is>
-      </c>
-      <c r="F60" s="4" t="inlineStr">
-        <is>
-          <t>+2.6</t>
-        </is>
-      </c>
+      <c r="E60" s="4" t="inlineStr"/>
+      <c r="F60" s="4" t="inlineStr"/>
       <c r="G60" s="4" t="n">
         <v>285</v>
       </c>
@@ -27355,16 +28099,8 @@
           <t>碩禾</t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>119.00</t>
-        </is>
-      </c>
-      <c r="F61" s="4" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
+      <c r="E61" s="4" t="inlineStr"/>
+      <c r="F61" s="4" t="inlineStr"/>
       <c r="G61" s="4" t="n">
         <v>284</v>
       </c>
@@ -27388,16 +28124,8 @@
           <t>正德</t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr">
-        <is>
-          <t>18.00</t>
-        </is>
-      </c>
-      <c r="F62" s="4" t="inlineStr">
-        <is>
-          <t>+0.15</t>
-        </is>
-      </c>
+      <c r="E62" s="4" t="inlineStr"/>
+      <c r="F62" s="4" t="inlineStr"/>
       <c r="G62" s="4" t="n">
         <v>281</v>
       </c>
@@ -27421,16 +28149,8 @@
           <t>建榮</t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>117.00</t>
-        </is>
-      </c>
-      <c r="F63" s="4" t="inlineStr">
-        <is>
-          <t>-8.5</t>
-        </is>
-      </c>
+      <c r="E63" s="4" t="inlineStr"/>
+      <c r="F63" s="4" t="inlineStr"/>
       <c r="G63" s="4" t="n">
         <v>278</v>
       </c>
@@ -27454,16 +28174,8 @@
           <t>太景*-KY</t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t>10.30</t>
-        </is>
-      </c>
-      <c r="F64" s="4" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
+      <c r="E64" s="4" t="inlineStr"/>
+      <c r="F64" s="4" t="inlineStr"/>
       <c r="G64" s="4" t="n">
         <v>276</v>
       </c>
@@ -27487,16 +28199,8 @@
           <t>群翊</t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr">
-        <is>
-          <t>426.00</t>
-        </is>
-      </c>
-      <c r="F65" s="4" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
+      <c r="E65" s="4" t="inlineStr"/>
+      <c r="F65" s="4" t="inlineStr"/>
       <c r="G65" s="4" t="n">
         <v>271</v>
       </c>
@@ -27520,16 +28224,8 @@
           <t>佳邦</t>
         </is>
       </c>
-      <c r="E66" s="4" t="inlineStr">
-        <is>
-          <t>87.60</t>
-        </is>
-      </c>
-      <c r="F66" s="4" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
+      <c r="E66" s="4" t="inlineStr"/>
+      <c r="F66" s="4" t="inlineStr"/>
       <c r="G66" s="4" t="n">
         <v>269</v>
       </c>
@@ -27553,16 +28249,8 @@
           <t>亞信</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>105.50</t>
-        </is>
-      </c>
-      <c r="F67" s="4" t="inlineStr">
-        <is>
-          <t>+9.3</t>
-        </is>
-      </c>
+      <c r="E67" s="4" t="inlineStr"/>
+      <c r="F67" s="4" t="inlineStr"/>
       <c r="G67" s="4" t="n">
         <v>262</v>
       </c>
@@ -27586,16 +28274,8 @@
           <t>協禧</t>
         </is>
       </c>
-      <c r="E68" s="4" t="inlineStr">
-        <is>
-          <t>30.40</t>
-        </is>
-      </c>
-      <c r="F68" s="4" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
+      <c r="E68" s="4" t="inlineStr"/>
+      <c r="F68" s="4" t="inlineStr"/>
       <c r="G68" s="4" t="n">
         <v>260</v>
       </c>
@@ -27619,16 +28299,8 @@
           <t>青雲</t>
         </is>
       </c>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>365.50</t>
-        </is>
-      </c>
-      <c r="F69" s="4" t="inlineStr">
-        <is>
-          <t>+33.0</t>
-        </is>
-      </c>
+      <c r="E69" s="4" t="inlineStr"/>
+      <c r="F69" s="4" t="inlineStr"/>
       <c r="G69" s="4" t="n">
         <v>260</v>
       </c>
@@ -27652,16 +28324,8 @@
           <t>宜鼎</t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr">
-        <is>
-          <t>1120.00</t>
-        </is>
-      </c>
-      <c r="F70" s="4" t="inlineStr">
-        <is>
-          <t>+100.0</t>
-        </is>
-      </c>
+      <c r="E70" s="4" t="inlineStr"/>
+      <c r="F70" s="4" t="inlineStr"/>
       <c r="G70" s="4" t="n">
         <v>258</v>
       </c>
@@ -27685,16 +28349,8 @@
           <t>台星科</t>
         </is>
       </c>
-      <c r="E71" s="4" t="inlineStr">
-        <is>
-          <t>176.00</t>
-        </is>
-      </c>
-      <c r="F71" s="4" t="inlineStr">
-        <is>
-          <t>+4.5</t>
-        </is>
-      </c>
+      <c r="E71" s="4" t="inlineStr"/>
+      <c r="F71" s="4" t="inlineStr"/>
       <c r="G71" s="4" t="n">
         <v>257</v>
       </c>
@@ -27718,16 +28374,8 @@
           <t>朋程</t>
         </is>
       </c>
-      <c r="E72" s="4" t="inlineStr">
-        <is>
-          <t>134.00</t>
-        </is>
-      </c>
-      <c r="F72" s="4" t="inlineStr">
-        <is>
-          <t>+1.5</t>
-        </is>
-      </c>
+      <c r="E72" s="4" t="inlineStr"/>
+      <c r="F72" s="4" t="inlineStr"/>
       <c r="G72" s="4" t="n">
         <v>256</v>
       </c>
@@ -27751,16 +28399,8 @@
           <t>聯一光</t>
         </is>
       </c>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>35.70</t>
-        </is>
-      </c>
-      <c r="F73" s="4" t="inlineStr">
-        <is>
-          <t>+2.1</t>
-        </is>
-      </c>
+      <c r="E73" s="4" t="inlineStr"/>
+      <c r="F73" s="4" t="inlineStr"/>
       <c r="G73" s="4" t="n">
         <v>245</v>
       </c>
@@ -27784,16 +28424,8 @@
           <t>群聯</t>
         </is>
       </c>
-      <c r="E74" s="4" t="inlineStr">
-        <is>
-          <t>1765.00</t>
-        </is>
-      </c>
-      <c r="F74" s="4" t="inlineStr">
-        <is>
-          <t>+130.0</t>
-        </is>
-      </c>
+      <c r="E74" s="4" t="inlineStr"/>
+      <c r="F74" s="4" t="inlineStr"/>
       <c r="G74" s="4" t="n">
         <v>243</v>
       </c>
@@ -27817,16 +28449,8 @@
           <t>蜜望實</t>
         </is>
       </c>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>87.70</t>
-        </is>
-      </c>
-      <c r="F75" s="4" t="inlineStr">
-        <is>
-          <t>-3.6</t>
-        </is>
-      </c>
+      <c r="E75" s="4" t="inlineStr"/>
+      <c r="F75" s="4" t="inlineStr"/>
       <c r="G75" s="4" t="n">
         <v>239</v>
       </c>
@@ -27850,16 +28474,8 @@
           <t>鏵友益</t>
         </is>
       </c>
-      <c r="E76" s="4" t="inlineStr">
-        <is>
-          <t>164.00</t>
-        </is>
-      </c>
-      <c r="F76" s="4" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
+      <c r="E76" s="4" t="inlineStr"/>
+      <c r="F76" s="4" t="inlineStr"/>
       <c r="G76" s="4" t="n">
         <v>236</v>
       </c>
@@ -27883,16 +28499,8 @@
           <t>華宏</t>
         </is>
       </c>
-      <c r="E77" s="4" t="inlineStr">
-        <is>
-          <t>63.00</t>
-        </is>
-      </c>
-      <c r="F77" s="4" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
+      <c r="E77" s="4" t="inlineStr"/>
+      <c r="F77" s="4" t="inlineStr"/>
       <c r="G77" s="4" t="n">
         <v>236</v>
       </c>
@@ -27916,16 +28524,8 @@
           <t>越峰</t>
         </is>
       </c>
-      <c r="E78" s="4" t="inlineStr">
-        <is>
-          <t>28.15</t>
-        </is>
-      </c>
-      <c r="F78" s="4" t="inlineStr">
-        <is>
-          <t>-0.35</t>
-        </is>
-      </c>
+      <c r="E78" s="4" t="inlineStr"/>
+      <c r="F78" s="4" t="inlineStr"/>
       <c r="G78" s="4" t="n">
         <v>233</v>
       </c>
@@ -27949,16 +28549,8 @@
           <t>晶呈科技</t>
         </is>
       </c>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t>532.00</t>
-        </is>
-      </c>
-      <c r="F79" s="4" t="inlineStr">
-        <is>
-          <t>+24.0</t>
-        </is>
-      </c>
+      <c r="E79" s="4" t="inlineStr"/>
+      <c r="F79" s="4" t="inlineStr"/>
       <c r="G79" s="4" t="n">
         <v>221</v>
       </c>
@@ -27982,16 +28574,8 @@
           <t>瑞耘</t>
         </is>
       </c>
-      <c r="E80" s="4" t="inlineStr">
-        <is>
-          <t>93.20</t>
-        </is>
-      </c>
-      <c r="F80" s="4" t="inlineStr">
-        <is>
-          <t>+8.4</t>
-        </is>
-      </c>
+      <c r="E80" s="4" t="inlineStr"/>
+      <c r="F80" s="4" t="inlineStr"/>
       <c r="G80" s="4" t="n">
         <v>217</v>
       </c>
@@ -28015,16 +28599,8 @@
           <t>信音</t>
         </is>
       </c>
-      <c r="E81" s="4" t="inlineStr">
-        <is>
-          <t>32.80</t>
-        </is>
-      </c>
-      <c r="F81" s="4" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
+      <c r="E81" s="4" t="inlineStr"/>
+      <c r="F81" s="4" t="inlineStr"/>
       <c r="G81" s="4" t="n">
         <v>216</v>
       </c>
@@ -28048,16 +28624,8 @@
           <t>安碁</t>
         </is>
       </c>
-      <c r="E82" s="4" t="inlineStr">
-        <is>
-          <t>33.20</t>
-        </is>
-      </c>
-      <c r="F82" s="4" t="inlineStr">
-        <is>
-          <t>+3.0</t>
-        </is>
-      </c>
+      <c r="E82" s="4" t="inlineStr"/>
+      <c r="F82" s="4" t="inlineStr"/>
       <c r="G82" s="4" t="n">
         <v>213</v>
       </c>
@@ -28081,16 +28649,8 @@
           <t>友威科</t>
         </is>
       </c>
-      <c r="E83" s="4" t="inlineStr">
-        <is>
-          <t>82.30</t>
-        </is>
-      </c>
-      <c r="F83" s="4" t="inlineStr">
-        <is>
-          <t>-1.3</t>
-        </is>
-      </c>
+      <c r="E83" s="4" t="inlineStr"/>
+      <c r="F83" s="4" t="inlineStr"/>
       <c r="G83" s="4" t="n">
         <v>211</v>
       </c>
@@ -28114,16 +28674,8 @@
           <t>聚和</t>
         </is>
       </c>
-      <c r="E84" s="4" t="inlineStr">
-        <is>
-          <t>43.65</t>
-        </is>
-      </c>
-      <c r="F84" s="4" t="inlineStr">
-        <is>
-          <t>-0.3</t>
-        </is>
-      </c>
+      <c r="E84" s="4" t="inlineStr"/>
+      <c r="F84" s="4" t="inlineStr"/>
       <c r="G84" s="4" t="n">
         <v>208</v>
       </c>
@@ -28147,16 +28699,8 @@
           <t>久正</t>
         </is>
       </c>
-      <c r="E85" s="4" t="inlineStr">
-        <is>
-          <t>13.70</t>
-        </is>
-      </c>
-      <c r="F85" s="4" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
+      <c r="E85" s="4" t="inlineStr"/>
+      <c r="F85" s="4" t="inlineStr"/>
       <c r="G85" s="4" t="n">
         <v>197</v>
       </c>
@@ -28180,16 +28724,8 @@
           <t>朋億*</t>
         </is>
       </c>
-      <c r="E86" s="4" t="inlineStr">
-        <is>
-          <t>249.50</t>
-        </is>
-      </c>
-      <c r="F86" s="4" t="inlineStr">
-        <is>
-          <t>+7.5</t>
-        </is>
-      </c>
+      <c r="E86" s="4" t="inlineStr"/>
+      <c r="F86" s="4" t="inlineStr"/>
       <c r="G86" s="4" t="n">
         <v>197</v>
       </c>
@@ -28213,16 +28749,8 @@
           <t>前鼎</t>
         </is>
       </c>
-      <c r="E87" s="4" t="inlineStr">
-        <is>
-          <t>205.00</t>
-        </is>
-      </c>
-      <c r="F87" s="4" t="inlineStr">
-        <is>
-          <t>+17.5</t>
-        </is>
-      </c>
+      <c r="E87" s="4" t="inlineStr"/>
+      <c r="F87" s="4" t="inlineStr"/>
       <c r="G87" s="4" t="n">
         <v>189</v>
       </c>
@@ -28246,16 +28774,8 @@
           <t>千附</t>
         </is>
       </c>
-      <c r="E88" s="4" t="inlineStr">
-        <is>
-          <t>72.00</t>
-        </is>
-      </c>
-      <c r="F88" s="4" t="inlineStr">
-        <is>
-          <t>+3.4</t>
-        </is>
-      </c>
+      <c r="E88" s="4" t="inlineStr"/>
+      <c r="F88" s="4" t="inlineStr"/>
       <c r="G88" s="4" t="n">
         <v>187</v>
       </c>
@@ -28279,16 +28799,8 @@
           <t>南俊國際</t>
         </is>
       </c>
-      <c r="E89" s="4" t="inlineStr">
-        <is>
-          <t>787.00</t>
-        </is>
-      </c>
-      <c r="F89" s="4" t="inlineStr">
-        <is>
-          <t>+54.0</t>
-        </is>
-      </c>
+      <c r="E89" s="4" t="inlineStr"/>
+      <c r="F89" s="4" t="inlineStr"/>
       <c r="G89" s="4" t="n">
         <v>186</v>
       </c>
@@ -28312,16 +28824,8 @@
           <t>萬泰科</t>
         </is>
       </c>
-      <c r="E90" s="4" t="inlineStr">
-        <is>
-          <t>64.30</t>
-        </is>
-      </c>
-      <c r="F90" s="4" t="inlineStr">
-        <is>
-          <t>+0.4</t>
-        </is>
-      </c>
+      <c r="E90" s="4" t="inlineStr"/>
+      <c r="F90" s="4" t="inlineStr"/>
       <c r="G90" s="4" t="n">
         <v>170</v>
       </c>
@@ -28345,16 +28849,8 @@
           <t>東研信超</t>
         </is>
       </c>
-      <c r="E91" s="4" t="inlineStr">
-        <is>
-          <t>73.00</t>
-        </is>
-      </c>
-      <c r="F91" s="4" t="inlineStr">
-        <is>
-          <t>+2.1</t>
-        </is>
-      </c>
+      <c r="E91" s="4" t="inlineStr"/>
+      <c r="F91" s="4" t="inlineStr"/>
       <c r="G91" s="4" t="n">
         <v>170</v>
       </c>
@@ -28378,16 +28874,8 @@
           <t>生華科</t>
         </is>
       </c>
-      <c r="E92" s="4" t="inlineStr">
-        <is>
-          <t>55.50</t>
-        </is>
-      </c>
-      <c r="F92" s="4" t="inlineStr">
-        <is>
-          <t>+1.3</t>
-        </is>
-      </c>
+      <c r="E92" s="4" t="inlineStr"/>
+      <c r="F92" s="4" t="inlineStr"/>
       <c r="G92" s="4" t="n">
         <v>169</v>
       </c>
@@ -28411,16 +28899,8 @@
           <t>均華</t>
         </is>
       </c>
-      <c r="E93" s="4" t="inlineStr">
-        <is>
-          <t>1525.00</t>
-        </is>
-      </c>
-      <c r="F93" s="4" t="inlineStr">
-        <is>
-          <t>-50.0</t>
-        </is>
-      </c>
+      <c r="E93" s="4" t="inlineStr"/>
+      <c r="F93" s="4" t="inlineStr"/>
       <c r="G93" s="4" t="n">
         <v>168</v>
       </c>
@@ -28444,16 +28924,8 @@
           <t>中裕</t>
         </is>
       </c>
-      <c r="E94" s="4" t="inlineStr">
-        <is>
-          <t>50.90</t>
-        </is>
-      </c>
-      <c r="F94" s="4" t="inlineStr">
-        <is>
-          <t>+0.3</t>
-        </is>
-      </c>
+      <c r="E94" s="4" t="inlineStr"/>
+      <c r="F94" s="4" t="inlineStr"/>
       <c r="G94" s="4" t="n">
         <v>163</v>
       </c>
@@ -28477,16 +28949,8 @@
           <t>利機</t>
         </is>
       </c>
-      <c r="E95" s="4" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
-      </c>
-      <c r="F95" s="4" t="inlineStr">
-        <is>
-          <t>+8.7</t>
-        </is>
-      </c>
+      <c r="E95" s="4" t="inlineStr"/>
+      <c r="F95" s="4" t="inlineStr"/>
       <c r="G95" s="4" t="n">
         <v>162</v>
       </c>
@@ -28510,16 +28974,8 @@
           <t>精測</t>
         </is>
       </c>
-      <c r="E96" s="4" t="inlineStr">
-        <is>
-          <t>4105.00</t>
-        </is>
-      </c>
-      <c r="F96" s="4" t="inlineStr">
-        <is>
-          <t>+295.0</t>
-        </is>
-      </c>
+      <c r="E96" s="4" t="inlineStr"/>
+      <c r="F96" s="4" t="inlineStr"/>
       <c r="G96" s="4" t="n">
         <v>162</v>
       </c>
@@ -28543,16 +28999,8 @@
           <t>尼克森</t>
         </is>
       </c>
-      <c r="E97" s="4" t="inlineStr">
-        <is>
-          <t>53.60</t>
-        </is>
-      </c>
-      <c r="F97" s="4" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
+      <c r="E97" s="4" t="inlineStr"/>
+      <c r="F97" s="4" t="inlineStr"/>
       <c r="G97" s="4" t="n">
         <v>161</v>
       </c>
@@ -28576,16 +29024,8 @@
           <t>千如</t>
         </is>
       </c>
-      <c r="E98" s="4" t="inlineStr">
-        <is>
-          <t>33.90</t>
-        </is>
-      </c>
-      <c r="F98" s="4" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
+      <c r="E98" s="4" t="inlineStr"/>
+      <c r="F98" s="4" t="inlineStr"/>
       <c r="G98" s="4" t="n">
         <v>160</v>
       </c>
@@ -28609,16 +29049,8 @@
           <t>東碩</t>
         </is>
       </c>
-      <c r="E99" s="4" t="inlineStr">
-        <is>
-          <t>21.15</t>
-        </is>
-      </c>
-      <c r="F99" s="4" t="inlineStr">
-        <is>
-          <t>+1.9</t>
-        </is>
-      </c>
+      <c r="E99" s="4" t="inlineStr"/>
+      <c r="F99" s="4" t="inlineStr"/>
       <c r="G99" s="4" t="n">
         <v>159</v>
       </c>
@@ -28642,16 +29074,8 @@
           <t>創惟</t>
         </is>
       </c>
-      <c r="E100" s="4" t="inlineStr">
-        <is>
-          <t>94.80</t>
-        </is>
-      </c>
-      <c r="F100" s="4" t="inlineStr">
-        <is>
-          <t>+1.4</t>
-        </is>
-      </c>
+      <c r="E100" s="4" t="inlineStr"/>
+      <c r="F100" s="4" t="inlineStr"/>
       <c r="G100" s="4" t="n">
         <v>158</v>
       </c>
@@ -28675,16 +29099,8 @@
           <t>濱川</t>
         </is>
       </c>
-      <c r="E101" s="4" t="inlineStr">
-        <is>
-          <t>54.40</t>
-        </is>
-      </c>
-      <c r="F101" s="4" t="inlineStr">
-        <is>
-          <t>+2.1</t>
-        </is>
-      </c>
+      <c r="E101" s="4" t="inlineStr"/>
+      <c r="F101" s="4" t="inlineStr"/>
       <c r="G101" s="4" t="n">
         <v>156</v>
       </c>
@@ -28708,16 +29124,8 @@
           <t>鈺太</t>
         </is>
       </c>
-      <c r="E102" s="4" t="inlineStr">
-        <is>
-          <t>288.00</t>
-        </is>
-      </c>
-      <c r="F102" s="4" t="inlineStr">
-        <is>
-          <t>+17.0</t>
-        </is>
-      </c>
+      <c r="E102" s="4" t="inlineStr"/>
+      <c r="F102" s="4" t="inlineStr"/>
       <c r="G102" s="4" t="n">
         <v>151</v>
       </c>
@@ -28741,16 +29149,8 @@
           <t>康全電訊</t>
         </is>
       </c>
-      <c r="E103" s="4" t="inlineStr">
-        <is>
-          <t>22.20</t>
-        </is>
-      </c>
-      <c r="F103" s="4" t="inlineStr">
-        <is>
-          <t>+0.6</t>
-        </is>
-      </c>
+      <c r="E103" s="4" t="inlineStr"/>
+      <c r="F103" s="4" t="inlineStr"/>
       <c r="G103" s="4" t="n">
         <v>151</v>
       </c>
@@ -28851,16 +29251,8 @@
           <t>世界</t>
         </is>
       </c>
-      <c r="E109" s="4" t="inlineStr">
-        <is>
-          <t>138.50</t>
-        </is>
-      </c>
-      <c r="F109" s="4" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
+      <c r="E109" s="4" t="inlineStr"/>
+      <c r="F109" s="4" t="inlineStr"/>
       <c r="G109" s="4" t="n">
         <v>-12693</v>
       </c>
@@ -28884,16 +29276,8 @@
           <t>精材</t>
         </is>
       </c>
-      <c r="E110" s="4" t="inlineStr">
-        <is>
-          <t>193.00</t>
-        </is>
-      </c>
-      <c r="F110" s="4" t="inlineStr">
-        <is>
-          <t>-9.5</t>
-        </is>
-      </c>
+      <c r="E110" s="4" t="inlineStr"/>
+      <c r="F110" s="4" t="inlineStr"/>
       <c r="G110" s="4" t="n">
         <v>-5392</v>
       </c>
@@ -28917,16 +29301,8 @@
           <t>金居</t>
         </is>
       </c>
-      <c r="E111" s="4" t="inlineStr">
-        <is>
-          <t>393.50</t>
-        </is>
-      </c>
-      <c r="F111" s="4" t="inlineStr">
-        <is>
-          <t>-10.5</t>
-        </is>
-      </c>
+      <c r="E111" s="4" t="inlineStr"/>
+      <c r="F111" s="4" t="inlineStr"/>
       <c r="G111" s="4" t="n">
         <v>-5257</v>
       </c>
@@ -28950,16 +29326,8 @@
           <t>華電網</t>
         </is>
       </c>
-      <c r="E112" s="4" t="inlineStr">
-        <is>
-          <t>70.30</t>
-        </is>
-      </c>
-      <c r="F112" s="4" t="inlineStr">
-        <is>
-          <t>-3.8</t>
-        </is>
-      </c>
+      <c r="E112" s="4" t="inlineStr"/>
+      <c r="F112" s="4" t="inlineStr"/>
       <c r="G112" s="4" t="n">
         <v>-3976</v>
       </c>
@@ -28983,16 +29351,8 @@
           <t>元太</t>
         </is>
       </c>
-      <c r="E113" s="4" t="inlineStr">
-        <is>
-          <t>154.00</t>
-        </is>
-      </c>
-      <c r="F113" s="4" t="inlineStr">
-        <is>
-          <t>-4.0</t>
-        </is>
-      </c>
+      <c r="E113" s="4" t="inlineStr"/>
+      <c r="F113" s="4" t="inlineStr"/>
       <c r="G113" s="4" t="n">
         <v>-2912</v>
       </c>
@@ -29016,16 +29376,8 @@
           <t>聯光通</t>
         </is>
       </c>
-      <c r="E114" s="4" t="inlineStr">
-        <is>
-          <t>53.20</t>
-        </is>
-      </c>
-      <c r="F114" s="4" t="inlineStr">
-        <is>
-          <t>+1.6</t>
-        </is>
-      </c>
+      <c r="E114" s="4" t="inlineStr"/>
+      <c r="F114" s="4" t="inlineStr"/>
       <c r="G114" s="4" t="n">
         <v>-2547</v>
       </c>
@@ -29049,16 +29401,8 @@
           <t>亞電</t>
         </is>
       </c>
-      <c r="E115" s="4" t="inlineStr">
-        <is>
-          <t>46.05</t>
-        </is>
-      </c>
-      <c r="F115" s="4" t="inlineStr">
-        <is>
-          <t>+0.8</t>
-        </is>
-      </c>
+      <c r="E115" s="4" t="inlineStr"/>
+      <c r="F115" s="4" t="inlineStr"/>
       <c r="G115" s="4" t="n">
         <v>-2409</v>
       </c>
@@ -29082,16 +29426,8 @@
           <t>東捷</t>
         </is>
       </c>
-      <c r="E116" s="4" t="inlineStr">
-        <is>
-          <t>83.30</t>
-        </is>
-      </c>
-      <c r="F116" s="4" t="inlineStr">
-        <is>
-          <t>-0.2</t>
-        </is>
-      </c>
+      <c r="E116" s="4" t="inlineStr"/>
+      <c r="F116" s="4" t="inlineStr"/>
       <c r="G116" s="4" t="n">
         <v>-2334</v>
       </c>
@@ -29115,16 +29451,8 @@
           <t>均豪</t>
         </is>
       </c>
-      <c r="E117" s="4" t="inlineStr">
-        <is>
-          <t>118.50</t>
-        </is>
-      </c>
-      <c r="F117" s="4" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
+      <c r="E117" s="4" t="inlineStr"/>
+      <c r="F117" s="4" t="inlineStr"/>
       <c r="G117" s="4" t="n">
         <v>-2090</v>
       </c>
@@ -29148,16 +29476,8 @@
           <t>富喬</t>
         </is>
       </c>
-      <c r="E118" s="4" t="inlineStr">
-        <is>
-          <t>119.00</t>
-        </is>
-      </c>
-      <c r="F118" s="4" t="inlineStr">
-        <is>
-          <t>+1.0</t>
-        </is>
-      </c>
+      <c r="E118" s="4" t="inlineStr"/>
+      <c r="F118" s="4" t="inlineStr"/>
       <c r="G118" s="4" t="n">
         <v>-1676</v>
       </c>
@@ -29181,16 +29501,8 @@
           <t>高技</t>
         </is>
       </c>
-      <c r="E119" s="4" t="inlineStr">
-        <is>
-          <t>438.50</t>
-        </is>
-      </c>
-      <c r="F119" s="4" t="inlineStr">
-        <is>
-          <t>-3.0</t>
-        </is>
-      </c>
+      <c r="E119" s="4" t="inlineStr"/>
+      <c r="F119" s="4" t="inlineStr"/>
       <c r="G119" s="4" t="n">
         <v>-1643</v>
       </c>
@@ -29214,16 +29526,8 @@
           <t>中光電</t>
         </is>
       </c>
-      <c r="E120" s="4" t="inlineStr">
-        <is>
-          <t>78.30</t>
-        </is>
-      </c>
-      <c r="F120" s="4" t="inlineStr">
-        <is>
-          <t>-0.7</t>
-        </is>
-      </c>
+      <c r="E120" s="4" t="inlineStr"/>
+      <c r="F120" s="4" t="inlineStr"/>
       <c r="G120" s="4" t="n">
         <v>-1621</v>
       </c>
@@ -29247,16 +29551,8 @@
           <t>磐亞</t>
         </is>
       </c>
-      <c r="E121" s="4" t="inlineStr">
-        <is>
-          <t>15.90</t>
-        </is>
-      </c>
-      <c r="F121" s="4" t="inlineStr">
-        <is>
-          <t>+0.05</t>
-        </is>
-      </c>
+      <c r="E121" s="4" t="inlineStr"/>
+      <c r="F121" s="4" t="inlineStr"/>
       <c r="G121" s="4" t="n">
         <v>-1596</v>
       </c>
@@ -29280,16 +29576,8 @@
           <t>中天</t>
         </is>
       </c>
-      <c r="E122" s="4" t="inlineStr">
-        <is>
-          <t>16.35</t>
-        </is>
-      </c>
-      <c r="F122" s="4" t="inlineStr">
-        <is>
-          <t>-0.4</t>
-        </is>
-      </c>
+      <c r="E122" s="4" t="inlineStr"/>
+      <c r="F122" s="4" t="inlineStr"/>
       <c r="G122" s="4" t="n">
         <v>-1524</v>
       </c>
@@ -29313,16 +29601,8 @@
           <t>台嘉碩</t>
         </is>
       </c>
-      <c r="E123" s="4" t="inlineStr">
-        <is>
-          <t>53.60</t>
-        </is>
-      </c>
-      <c r="F123" s="4" t="inlineStr">
-        <is>
-          <t>+4.8</t>
-        </is>
-      </c>
+      <c r="E123" s="4" t="inlineStr"/>
+      <c r="F123" s="4" t="inlineStr"/>
       <c r="G123" s="4" t="n">
         <v>-1505</v>
       </c>
@@ -29346,16 +29626,8 @@
           <t>智通*</t>
         </is>
       </c>
-      <c r="E124" s="4" t="inlineStr">
-        <is>
-          <t>101.00</t>
-        </is>
-      </c>
-      <c r="F124" s="4" t="inlineStr">
-        <is>
-          <t>+2.2</t>
-        </is>
-      </c>
+      <c r="E124" s="4" t="inlineStr"/>
+      <c r="F124" s="4" t="inlineStr"/>
       <c r="G124" s="4" t="n">
         <v>-1450</v>
       </c>
@@ -29379,16 +29651,8 @@
           <t>創威</t>
         </is>
       </c>
-      <c r="E125" s="4" t="inlineStr">
-        <is>
-          <t>133.50</t>
-        </is>
-      </c>
-      <c r="F125" s="4" t="inlineStr">
-        <is>
-          <t>+6.5</t>
-        </is>
-      </c>
+      <c r="E125" s="4" t="inlineStr"/>
+      <c r="F125" s="4" t="inlineStr"/>
       <c r="G125" s="4" t="n">
         <v>-1409</v>
       </c>
@@ -29412,16 +29676,8 @@
           <t>良維</t>
         </is>
       </c>
-      <c r="E126" s="4" t="inlineStr">
-        <is>
-          <t>266.50</t>
-        </is>
-      </c>
-      <c r="F126" s="4" t="inlineStr">
-        <is>
-          <t>+8.0</t>
-        </is>
-      </c>
+      <c r="E126" s="4" t="inlineStr"/>
+      <c r="F126" s="4" t="inlineStr"/>
       <c r="G126" s="4" t="n">
         <v>-1393</v>
       </c>
@@ -29445,16 +29701,8 @@
           <t>鉅橡</t>
         </is>
       </c>
-      <c r="E127" s="4" t="inlineStr">
-        <is>
-          <t>77.20</t>
-        </is>
-      </c>
-      <c r="F127" s="4" t="inlineStr">
-        <is>
-          <t>-1.1</t>
-        </is>
-      </c>
+      <c r="E127" s="4" t="inlineStr"/>
+      <c r="F127" s="4" t="inlineStr"/>
       <c r="G127" s="4" t="n">
         <v>-1365</v>
       </c>
@@ -29478,16 +29726,8 @@
           <t>泰藝</t>
         </is>
       </c>
-      <c r="E128" s="4" t="inlineStr">
-        <is>
-          <t>56.60</t>
-        </is>
-      </c>
-      <c r="F128" s="4" t="inlineStr">
-        <is>
-          <t>+2.0</t>
-        </is>
-      </c>
+      <c r="E128" s="4" t="inlineStr"/>
+      <c r="F128" s="4" t="inlineStr"/>
       <c r="G128" s="4" t="n">
         <v>-1170</v>
       </c>
@@ -29511,16 +29751,8 @@
           <t>元山</t>
         </is>
       </c>
-      <c r="E129" s="4" t="inlineStr">
-        <is>
-          <t>55.20</t>
-        </is>
-      </c>
-      <c r="F129" s="4" t="inlineStr">
-        <is>
-          <t>+0.1</t>
-        </is>
-      </c>
+      <c r="E129" s="4" t="inlineStr"/>
+      <c r="F129" s="4" t="inlineStr"/>
       <c r="G129" s="4" t="n">
         <v>-1129</v>
       </c>
@@ -29544,16 +29776,8 @@
           <t>擎亞</t>
         </is>
       </c>
-      <c r="E130" s="4" t="inlineStr">
-        <is>
-          <t>93.50</t>
-        </is>
-      </c>
-      <c r="F130" s="4" t="inlineStr">
-        <is>
-          <t>-0.2</t>
-        </is>
-      </c>
+      <c r="E130" s="4" t="inlineStr"/>
+      <c r="F130" s="4" t="inlineStr"/>
       <c r="G130" s="4" t="n">
         <v>-918</v>
       </c>
@@ -29577,16 +29801,8 @@
           <t>晟德</t>
         </is>
       </c>
-      <c r="E131" s="4" t="inlineStr">
-        <is>
-          <t>39.55</t>
-        </is>
-      </c>
-      <c r="F131" s="4" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
+      <c r="E131" s="4" t="inlineStr"/>
+      <c r="F131" s="4" t="inlineStr"/>
       <c r="G131" s="4" t="n">
         <v>-847</v>
       </c>
@@ -29610,16 +29826,8 @@
           <t>旭品</t>
         </is>
       </c>
-      <c r="E132" s="4" t="inlineStr">
-        <is>
-          <t>14.40</t>
-        </is>
-      </c>
-      <c r="F132" s="4" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
+      <c r="E132" s="4" t="inlineStr"/>
+      <c r="F132" s="4" t="inlineStr"/>
       <c r="G132" s="4" t="n">
         <v>-772</v>
       </c>
@@ -29643,16 +29851,8 @@
           <t>磐儀</t>
         </is>
       </c>
-      <c r="E133" s="4" t="inlineStr">
-        <is>
-          <t>56.40</t>
-        </is>
-      </c>
-      <c r="F133" s="4" t="inlineStr">
-        <is>
-          <t>+4.7</t>
-        </is>
-      </c>
+      <c r="E133" s="4" t="inlineStr"/>
+      <c r="F133" s="4" t="inlineStr"/>
       <c r="G133" s="4" t="n">
         <v>-772</v>
       </c>
@@ -29676,16 +29876,8 @@
           <t>廣明</t>
         </is>
       </c>
-      <c r="E134" s="4" t="inlineStr">
-        <is>
-          <t>85.50</t>
-        </is>
-      </c>
-      <c r="F134" s="4" t="inlineStr">
-        <is>
-          <t>-0.3</t>
-        </is>
-      </c>
+      <c r="E134" s="4" t="inlineStr"/>
+      <c r="F134" s="4" t="inlineStr"/>
       <c r="G134" s="4" t="n">
         <v>-721</v>
       </c>
@@ -29709,16 +29901,8 @@
           <t>湧德</t>
         </is>
       </c>
-      <c r="E135" s="4" t="inlineStr">
-        <is>
-          <t>134.00</t>
-        </is>
-      </c>
-      <c r="F135" s="4" t="inlineStr">
-        <is>
-          <t>-2.5</t>
-        </is>
-      </c>
+      <c r="E135" s="4" t="inlineStr"/>
+      <c r="F135" s="4" t="inlineStr"/>
       <c r="G135" s="4" t="n">
         <v>-719</v>
       </c>
@@ -29742,16 +29926,8 @@
           <t>穩懋</t>
         </is>
       </c>
-      <c r="E136" s="4" t="inlineStr">
-        <is>
-          <t>617.00</t>
-        </is>
-      </c>
-      <c r="F136" s="4" t="inlineStr">
-        <is>
-          <t>+25.0</t>
-        </is>
-      </c>
+      <c r="E136" s="4" t="inlineStr"/>
+      <c r="F136" s="4" t="inlineStr"/>
       <c r="G136" s="4" t="n">
         <v>-692</v>
       </c>
@@ -29775,16 +29951,8 @@
           <t>廣閎科</t>
         </is>
       </c>
-      <c r="E137" s="4" t="inlineStr">
-        <is>
-          <t>155.00</t>
-        </is>
-      </c>
-      <c r="F137" s="4" t="inlineStr">
-        <is>
-          <t>-2.5</t>
-        </is>
-      </c>
+      <c r="E137" s="4" t="inlineStr"/>
+      <c r="F137" s="4" t="inlineStr"/>
       <c r="G137" s="4" t="n">
         <v>-613</v>
       </c>
@@ -29808,16 +29976,8 @@
           <t>新復興</t>
         </is>
       </c>
-      <c r="E138" s="4" t="inlineStr">
-        <is>
-          <t>64.60</t>
-        </is>
-      </c>
-      <c r="F138" s="4" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
+      <c r="E138" s="4" t="inlineStr"/>
+      <c r="F138" s="4" t="inlineStr"/>
       <c r="G138" s="4" t="n">
         <v>-594</v>
       </c>
@@ -29841,16 +30001,8 @@
           <t>永捷</t>
         </is>
       </c>
-      <c r="E139" s="4" t="inlineStr">
-        <is>
-          <t>16.70</t>
-        </is>
-      </c>
-      <c r="F139" s="4" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
+      <c r="E139" s="4" t="inlineStr"/>
+      <c r="F139" s="4" t="inlineStr"/>
       <c r="G139" s="4" t="n">
         <v>-591</v>
       </c>
@@ -29874,16 +30026,8 @@
           <t>德晉</t>
         </is>
       </c>
-      <c r="E140" s="4" t="inlineStr">
-        <is>
-          <t>43.70</t>
-        </is>
-      </c>
-      <c r="F140" s="4" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
+      <c r="E140" s="4" t="inlineStr"/>
+      <c r="F140" s="4" t="inlineStr"/>
       <c r="G140" s="4" t="n">
         <v>-577</v>
       </c>
@@ -29907,16 +30051,8 @@
           <t>IET-KY</t>
         </is>
       </c>
-      <c r="E141" s="4" t="inlineStr">
-        <is>
-          <t>872.00</t>
-        </is>
-      </c>
-      <c r="F141" s="4" t="inlineStr">
-        <is>
-          <t>+29.0</t>
-        </is>
-      </c>
+      <c r="E141" s="4" t="inlineStr"/>
+      <c r="F141" s="4" t="inlineStr"/>
       <c r="G141" s="4" t="n">
         <v>-565</v>
       </c>
@@ -29940,16 +30076,8 @@
           <t>德勝</t>
         </is>
       </c>
-      <c r="E142" s="4" t="inlineStr">
-        <is>
-          <t>73.50</t>
-        </is>
-      </c>
-      <c r="F142" s="4" t="inlineStr">
-        <is>
-          <t>+2.5</t>
-        </is>
-      </c>
+      <c r="E142" s="4" t="inlineStr"/>
+      <c r="F142" s="4" t="inlineStr"/>
       <c r="G142" s="4" t="n">
         <v>-537</v>
       </c>
@@ -29973,16 +30101,8 @@
           <t>易發</t>
         </is>
       </c>
-      <c r="E143" s="4" t="inlineStr">
-        <is>
-          <t>93.10</t>
-        </is>
-      </c>
-      <c r="F143" s="4" t="inlineStr">
-        <is>
-          <t>+2.1</t>
-        </is>
-      </c>
+      <c r="E143" s="4" t="inlineStr"/>
+      <c r="F143" s="4" t="inlineStr"/>
       <c r="G143" s="4" t="n">
         <v>-535</v>
       </c>
@@ -30006,16 +30126,8 @@
           <t>旺矽</t>
         </is>
       </c>
-      <c r="E144" s="4" t="inlineStr">
-        <is>
-          <t>4940.00</t>
-        </is>
-      </c>
-      <c r="F144" s="4" t="inlineStr">
-        <is>
-          <t>-195.0</t>
-        </is>
-      </c>
+      <c r="E144" s="4" t="inlineStr"/>
+      <c r="F144" s="4" t="inlineStr"/>
       <c r="G144" s="4" t="n">
         <v>-532</v>
       </c>
@@ -30039,16 +30151,8 @@
           <t>上詮</t>
         </is>
       </c>
-      <c r="E145" s="4" t="inlineStr">
-        <is>
-          <t>990.00</t>
-        </is>
-      </c>
-      <c r="F145" s="4" t="inlineStr">
-        <is>
-          <t>+2.0</t>
-        </is>
-      </c>
+      <c r="E145" s="4" t="inlineStr"/>
+      <c r="F145" s="4" t="inlineStr"/>
       <c r="G145" s="4" t="n">
         <v>-493</v>
       </c>
@@ -30072,16 +30176,8 @@
           <t>笙科</t>
         </is>
       </c>
-      <c r="E146" s="4" t="inlineStr">
-        <is>
-          <t>27.05</t>
-        </is>
-      </c>
-      <c r="F146" s="4" t="inlineStr">
-        <is>
-          <t>+1.45</t>
-        </is>
-      </c>
+      <c r="E146" s="4" t="inlineStr"/>
+      <c r="F146" s="4" t="inlineStr"/>
       <c r="G146" s="4" t="n">
         <v>-482</v>
       </c>
@@ -30105,16 +30201,8 @@
           <t>今展科</t>
         </is>
       </c>
-      <c r="E147" s="4" t="inlineStr">
-        <is>
-          <t>43.30</t>
-        </is>
-      </c>
-      <c r="F147" s="4" t="inlineStr">
-        <is>
-          <t>-1.45</t>
-        </is>
-      </c>
+      <c r="E147" s="4" t="inlineStr"/>
+      <c r="F147" s="4" t="inlineStr"/>
       <c r="G147" s="4" t="n">
         <v>-482</v>
       </c>
@@ -30138,16 +30226,8 @@
           <t>久元</t>
         </is>
       </c>
-      <c r="E148" s="4" t="inlineStr">
-        <is>
-          <t>92.20</t>
-        </is>
-      </c>
-      <c r="F148" s="4" t="inlineStr">
-        <is>
-          <t>+6.1</t>
-        </is>
-      </c>
+      <c r="E148" s="4" t="inlineStr"/>
+      <c r="F148" s="4" t="inlineStr"/>
       <c r="G148" s="4" t="n">
         <v>-475</v>
       </c>
@@ -30171,16 +30251,8 @@
           <t>M31</t>
         </is>
       </c>
-      <c r="E149" s="4" t="inlineStr">
-        <is>
-          <t>578.00</t>
-        </is>
-      </c>
-      <c r="F149" s="4" t="inlineStr">
-        <is>
-          <t>+22.0</t>
-        </is>
-      </c>
+      <c r="E149" s="4" t="inlineStr"/>
+      <c r="F149" s="4" t="inlineStr"/>
       <c r="G149" s="4" t="n">
         <v>-458</v>
       </c>
@@ -30204,16 +30276,8 @@
           <t>東洋</t>
         </is>
       </c>
-      <c r="E150" s="4" t="inlineStr">
-        <is>
-          <t>73.70</t>
-        </is>
-      </c>
-      <c r="F150" s="4" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
+      <c r="E150" s="4" t="inlineStr"/>
+      <c r="F150" s="4" t="inlineStr"/>
       <c r="G150" s="4" t="n">
         <v>-457</v>
       </c>
@@ -30237,16 +30301,8 @@
           <t>點序</t>
         </is>
       </c>
-      <c r="E151" s="4" t="inlineStr">
-        <is>
-          <t>83.90</t>
-        </is>
-      </c>
-      <c r="F151" s="4" t="inlineStr">
-        <is>
-          <t>+4.6</t>
-        </is>
-      </c>
+      <c r="E151" s="4" t="inlineStr"/>
+      <c r="F151" s="4" t="inlineStr"/>
       <c r="G151" s="4" t="n">
         <v>-439</v>
       </c>
@@ -30270,16 +30326,8 @@
           <t>璟德</t>
         </is>
       </c>
-      <c r="E152" s="4" t="inlineStr">
-        <is>
-          <t>168.50</t>
-        </is>
-      </c>
-      <c r="F152" s="4" t="inlineStr">
-        <is>
-          <t>-9.0</t>
-        </is>
-      </c>
+      <c r="E152" s="4" t="inlineStr"/>
+      <c r="F152" s="4" t="inlineStr"/>
       <c r="G152" s="4" t="n">
         <v>-433</v>
       </c>
@@ -30303,16 +30351,8 @@
           <t>德宏</t>
         </is>
       </c>
-      <c r="E153" s="4" t="inlineStr">
-        <is>
-          <t>385.00</t>
-        </is>
-      </c>
-      <c r="F153" s="4" t="inlineStr">
-        <is>
-          <t>-15.0</t>
-        </is>
-      </c>
+      <c r="E153" s="4" t="inlineStr"/>
+      <c r="F153" s="4" t="inlineStr"/>
       <c r="G153" s="4" t="n">
         <v>-414</v>
       </c>
@@ -30336,16 +30376,8 @@
           <t>禾瑞亞</t>
         </is>
       </c>
-      <c r="E154" s="4" t="inlineStr">
-        <is>
-          <t>58.10</t>
-        </is>
-      </c>
-      <c r="F154" s="4" t="inlineStr">
-        <is>
-          <t>+5.2</t>
-        </is>
-      </c>
+      <c r="E154" s="4" t="inlineStr"/>
+      <c r="F154" s="4" t="inlineStr"/>
       <c r="G154" s="4" t="n">
         <v>-369</v>
       </c>
@@ -30369,16 +30401,8 @@
           <t>家登</t>
         </is>
       </c>
-      <c r="E155" s="4" t="inlineStr">
-        <is>
-          <t>503.00</t>
-        </is>
-      </c>
-      <c r="F155" s="4" t="inlineStr">
-        <is>
-          <t>+30.0</t>
-        </is>
-      </c>
+      <c r="E155" s="4" t="inlineStr"/>
+      <c r="F155" s="4" t="inlineStr"/>
       <c r="G155" s="4" t="n">
         <v>-362</v>
       </c>
@@ -30402,16 +30426,8 @@
           <t>閎康</t>
         </is>
       </c>
-      <c r="E156" s="4" t="inlineStr">
-        <is>
-          <t>369.00</t>
-        </is>
-      </c>
-      <c r="F156" s="4" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
+      <c r="E156" s="4" t="inlineStr"/>
+      <c r="F156" s="4" t="inlineStr"/>
       <c r="G156" s="4" t="n">
         <v>-345</v>
       </c>
@@ -30435,16 +30451,8 @@
           <t>方土昶</t>
         </is>
       </c>
-      <c r="E157" s="4" t="inlineStr">
-        <is>
-          <t>40.15</t>
-        </is>
-      </c>
-      <c r="F157" s="4" t="inlineStr">
-        <is>
-          <t>+2.0</t>
-        </is>
-      </c>
+      <c r="E157" s="4" t="inlineStr"/>
+      <c r="F157" s="4" t="inlineStr"/>
       <c r="G157" s="4" t="n">
         <v>-343</v>
       </c>
@@ -30468,16 +30476,8 @@
           <t>精確</t>
         </is>
       </c>
-      <c r="E158" s="4" t="inlineStr">
-        <is>
-          <t>69.40</t>
-        </is>
-      </c>
-      <c r="F158" s="4" t="inlineStr">
-        <is>
-          <t>+0.4</t>
-        </is>
-      </c>
+      <c r="E158" s="4" t="inlineStr"/>
+      <c r="F158" s="4" t="inlineStr"/>
       <c r="G158" s="4" t="n">
         <v>-339</v>
       </c>

--- a/StockInfo/otc_analysis_result.xlsx
+++ b/StockInfo/otc_analysis_result.xlsx
@@ -26573,16 +26573,8 @@
           <t>世界</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>169.00</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>+15.0</t>
-        </is>
-      </c>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr"/>
       <c r="G4" s="4" t="n">
         <v>17337</v>
       </c>
@@ -26606,16 +26598,8 @@
           <t>合晶</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>50.60</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>+2.1</t>
-        </is>
-      </c>
+      <c r="E5" s="4" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr"/>
       <c r="G5" s="4" t="n">
         <v>8841</v>
       </c>
@@ -26639,16 +26623,8 @@
           <t>鈺創</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>78.50</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>+4.4</t>
-        </is>
-      </c>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr"/>
       <c r="G6" s="4" t="n">
         <v>7778</v>
       </c>
@@ -26672,16 +26648,8 @@
           <t>光洋科</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>168.50</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>+8.5</t>
-        </is>
-      </c>
+      <c r="E7" s="4" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr"/>
       <c r="G7" s="4" t="n">
         <v>6614</v>
       </c>
@@ -26705,16 +26673,8 @@
           <t>頎邦</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>-2.5</t>
-        </is>
-      </c>
+      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr"/>
       <c r="G8" s="4" t="n">
         <v>5217</v>
       </c>
@@ -26738,16 +26698,8 @@
           <t>富喬</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>113.50</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>-2.5</t>
-        </is>
-      </c>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr"/>
       <c r="G9" s="4" t="n">
         <v>5193</v>
       </c>
@@ -26771,16 +26723,8 @@
           <t>台半</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>68.50</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>+3.9</t>
-        </is>
-      </c>
+      <c r="E10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr"/>
       <c r="G10" s="4" t="n">
         <v>5032</v>
       </c>
@@ -26804,16 +26748,8 @@
           <t>金山電</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>77.30</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>+6.5</t>
-        </is>
-      </c>
+      <c r="E11" s="4" t="inlineStr"/>
+      <c r="F11" s="4" t="inlineStr"/>
       <c r="G11" s="4" t="n">
         <v>4780</v>
       </c>
@@ -26837,16 +26773,8 @@
           <t>擎亞</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>96.80</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>+0.6</t>
-        </is>
-      </c>
+      <c r="E12" s="4" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr"/>
       <c r="G12" s="4" t="n">
         <v>4261</v>
       </c>
@@ -26870,16 +26798,8 @@
           <t>群聯</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>2325.00</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>+210.0</t>
-        </is>
-      </c>
+      <c r="E13" s="4" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr"/>
       <c r="G13" s="4" t="n">
         <v>3678</v>
       </c>
@@ -26903,16 +26823,8 @@
           <t>信昌電</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>101.00</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>+8.8</t>
-        </is>
-      </c>
+      <c r="E14" s="4" t="inlineStr"/>
+      <c r="F14" s="4" t="inlineStr"/>
       <c r="G14" s="4" t="n">
         <v>3429</v>
       </c>
@@ -26936,16 +26848,8 @@
           <t>環球晶</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>721.00</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>+55.0</t>
-        </is>
-      </c>
+      <c r="E15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr"/>
       <c r="G15" s="4" t="n">
         <v>2828</v>
       </c>
@@ -26969,16 +26873,8 @@
           <t>康和證</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>20.40</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>+0.4</t>
-        </is>
-      </c>
+      <c r="E16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr"/>
       <c r="G16" s="4" t="n">
         <v>2487</v>
       </c>
@@ -27002,16 +26898,8 @@
           <t>金居</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>458.50</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>+25.5</t>
-        </is>
-      </c>
+      <c r="E17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr"/>
       <c r="G17" s="4" t="n">
         <v>2188</v>
       </c>
@@ -27035,16 +26923,8 @@
           <t>榮剛</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>35.10</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>+0.3</t>
-        </is>
-      </c>
+      <c r="E18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr"/>
       <c r="G18" s="4" t="n">
         <v>2052</v>
       </c>
@@ -27068,16 +26948,8 @@
           <t>廣穎</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>91.70</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>+4.0</t>
-        </is>
-      </c>
+      <c r="E19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr"/>
       <c r="G19" s="4" t="n">
         <v>1606</v>
       </c>
@@ -27101,16 +26973,8 @@
           <t>中美晶</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>145.50</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>+1.0</t>
-        </is>
-      </c>
+      <c r="E20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr"/>
       <c r="G20" s="4" t="n">
         <v>1511</v>
       </c>
@@ -27134,16 +26998,8 @@
           <t>福邦證</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>15.90</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>+0.2</t>
-        </is>
-      </c>
+      <c r="E21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr"/>
       <c r="G21" s="4" t="n">
         <v>1341</v>
       </c>
@@ -27167,16 +27023,8 @@
           <t>宏遠證</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>15.05</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>+0.3</t>
-        </is>
-      </c>
+      <c r="E22" s="4" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr"/>
       <c r="G22" s="4" t="n">
         <v>1140</v>
       </c>
@@ -27200,16 +27048,8 @@
           <t>鈺太</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>302.00</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>+15.0</t>
-        </is>
-      </c>
+      <c r="E23" s="4" t="inlineStr"/>
+      <c r="F23" s="4" t="inlineStr"/>
       <c r="G23" s="4" t="n">
         <v>986</v>
       </c>
@@ -27233,16 +27073,8 @@
           <t>致和證</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>31.20</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>+0.8</t>
-        </is>
-      </c>
+      <c r="E24" s="4" t="inlineStr"/>
+      <c r="F24" s="4" t="inlineStr"/>
       <c r="G24" s="4" t="n">
         <v>959</v>
       </c>
@@ -27266,16 +27098,8 @@
           <t>波若威</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>1135.00</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>-85.0</t>
-        </is>
-      </c>
+      <c r="E25" s="4" t="inlineStr"/>
+      <c r="F25" s="4" t="inlineStr"/>
       <c r="G25" s="4" t="n">
         <v>738</v>
       </c>
@@ -27299,16 +27123,8 @@
           <t>鈦昇</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>195.50</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>-6.5</t>
-        </is>
-      </c>
+      <c r="E26" s="4" t="inlineStr"/>
+      <c r="F26" s="4" t="inlineStr"/>
       <c r="G26" s="4" t="n">
         <v>647</v>
       </c>
@@ -27332,16 +27148,8 @@
           <t>精確</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>89.80</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>+6.8</t>
-        </is>
-      </c>
+      <c r="E27" s="4" t="inlineStr"/>
+      <c r="F27" s="4" t="inlineStr"/>
       <c r="G27" s="4" t="n">
         <v>639</v>
       </c>
@@ -27365,16 +27173,8 @@
           <t>國統</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>52.50</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>+0.4</t>
-        </is>
-      </c>
+      <c r="E28" s="4" t="inlineStr"/>
+      <c r="F28" s="4" t="inlineStr"/>
       <c r="G28" s="4" t="n">
         <v>609</v>
       </c>
@@ -27398,16 +27198,8 @@
           <t>磐亞</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>15.15</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>+0.2</t>
-        </is>
-      </c>
+      <c r="E29" s="4" t="inlineStr"/>
+      <c r="F29" s="4" t="inlineStr"/>
       <c r="G29" s="4" t="n">
         <v>503</v>
       </c>
@@ -27431,16 +27223,8 @@
           <t>艾訊</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>120.50</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>+4.5</t>
-        </is>
-      </c>
+      <c r="E30" s="4" t="inlineStr"/>
+      <c r="F30" s="4" t="inlineStr"/>
       <c r="G30" s="4" t="n">
         <v>481</v>
       </c>
@@ -27464,16 +27248,8 @@
           <t>律勝</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>31.10</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>+2.25</t>
-        </is>
-      </c>
+      <c r="E31" s="4" t="inlineStr"/>
+      <c r="F31" s="4" t="inlineStr"/>
       <c r="G31" s="4" t="n">
         <v>415</v>
       </c>
@@ -27497,16 +27273,8 @@
           <t>湧德</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>142.00</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>+3.0</t>
-        </is>
-      </c>
+      <c r="E32" s="4" t="inlineStr"/>
+      <c r="F32" s="4" t="inlineStr"/>
       <c r="G32" s="4" t="n">
         <v>393</v>
       </c>
@@ -27530,16 +27298,8 @@
           <t>閎康</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>327.00</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>-4.0</t>
-        </is>
-      </c>
+      <c r="E33" s="4" t="inlineStr"/>
+      <c r="F33" s="4" t="inlineStr"/>
       <c r="G33" s="4" t="n">
         <v>372</v>
       </c>
@@ -27563,16 +27323,8 @@
           <t>新盛力</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>166.50</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>+10.5</t>
-        </is>
-      </c>
+      <c r="E34" s="4" t="inlineStr"/>
+      <c r="F34" s="4" t="inlineStr"/>
       <c r="G34" s="4" t="n">
         <v>364</v>
       </c>
@@ -27596,16 +27348,8 @@
           <t>群翊</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>461.00</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
+      <c r="E35" s="4" t="inlineStr"/>
+      <c r="F35" s="4" t="inlineStr"/>
       <c r="G35" s="4" t="n">
         <v>361</v>
       </c>
@@ -27629,16 +27373,8 @@
           <t>豪勉</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>38.25</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>-0.2</t>
-        </is>
-      </c>
+      <c r="E36" s="4" t="inlineStr"/>
+      <c r="F36" s="4" t="inlineStr"/>
       <c r="G36" s="4" t="n">
         <v>316</v>
       </c>
@@ -27662,16 +27398,8 @@
           <t>弘塑</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>3200.00</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>+290.0</t>
-        </is>
-      </c>
+      <c r="E37" s="4" t="inlineStr"/>
+      <c r="F37" s="4" t="inlineStr"/>
       <c r="G37" s="4" t="n">
         <v>279</v>
       </c>
@@ -27695,16 +27423,8 @@
           <t>千附</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>63.50</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>-0.6</t>
-        </is>
-      </c>
+      <c r="E38" s="4" t="inlineStr"/>
+      <c r="F38" s="4" t="inlineStr"/>
       <c r="G38" s="4" t="n">
         <v>259</v>
       </c>
@@ -27728,16 +27448,8 @@
           <t>碩禾</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>136.00</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>+1.0</t>
-        </is>
-      </c>
+      <c r="E39" s="4" t="inlineStr"/>
+      <c r="F39" s="4" t="inlineStr"/>
       <c r="G39" s="4" t="n">
         <v>255</v>
       </c>
@@ -27761,16 +27473,8 @@
           <t>陽程</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>98.90</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>-2.1</t>
-        </is>
-      </c>
+      <c r="E40" s="4" t="inlineStr"/>
+      <c r="F40" s="4" t="inlineStr"/>
       <c r="G40" s="4" t="n">
         <v>238</v>
       </c>
@@ -27794,16 +27498,8 @@
           <t>訊達</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>20.50</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>+1.85</t>
-        </is>
-      </c>
+      <c r="E41" s="4" t="inlineStr"/>
+      <c r="F41" s="4" t="inlineStr"/>
       <c r="G41" s="4" t="n">
         <v>221</v>
       </c>
@@ -27827,16 +27523,8 @@
           <t>久元</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>121.50</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>+11.0</t>
-        </is>
-      </c>
+      <c r="E42" s="4" t="inlineStr"/>
+      <c r="F42" s="4" t="inlineStr"/>
       <c r="G42" s="4" t="n">
         <v>221</v>
       </c>
@@ -27860,16 +27548,8 @@
           <t>聖暉*</t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>877.00</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>+17.0</t>
-        </is>
-      </c>
+      <c r="E43" s="4" t="inlineStr"/>
+      <c r="F43" s="4" t="inlineStr"/>
       <c r="G43" s="4" t="n">
         <v>213</v>
       </c>
@@ -27893,16 +27573,8 @@
           <t>旺矽</t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>4950.00</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>-50.0</t>
-        </is>
-      </c>
+      <c r="E44" s="4" t="inlineStr"/>
+      <c r="F44" s="4" t="inlineStr"/>
       <c r="G44" s="4" t="n">
         <v>204</v>
       </c>
@@ -27926,16 +27598,8 @@
           <t>寶雅</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>598.00</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>+28.0</t>
-        </is>
-      </c>
+      <c r="E45" s="4" t="inlineStr"/>
+      <c r="F45" s="4" t="inlineStr"/>
       <c r="G45" s="4" t="n">
         <v>185</v>
       </c>
@@ -27959,16 +27623,8 @@
           <t>建舜電</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>13.05</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>-0.2</t>
-        </is>
-      </c>
+      <c r="E46" s="4" t="inlineStr"/>
+      <c r="F46" s="4" t="inlineStr"/>
       <c r="G46" s="4" t="n">
         <v>184</v>
       </c>
@@ -27992,16 +27648,8 @@
           <t>精測</t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>3800.00</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t>+140.0</t>
-        </is>
-      </c>
+      <c r="E47" s="4" t="inlineStr"/>
+      <c r="F47" s="4" t="inlineStr"/>
       <c r="G47" s="4" t="n">
         <v>181</v>
       </c>
@@ -28025,16 +27673,8 @@
           <t>瀧澤科</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>44.00</t>
-        </is>
-      </c>
-      <c r="F48" s="4" t="inlineStr">
-        <is>
-          <t>+2.45</t>
-        </is>
-      </c>
+      <c r="E48" s="4" t="inlineStr"/>
+      <c r="F48" s="4" t="inlineStr"/>
       <c r="G48" s="4" t="n">
         <v>181</v>
       </c>
@@ -28058,16 +27698,8 @@
           <t>東典光電</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>151.50</t>
-        </is>
-      </c>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>-8.0</t>
-        </is>
-      </c>
+      <c r="E49" s="4" t="inlineStr"/>
+      <c r="F49" s="4" t="inlineStr"/>
       <c r="G49" s="4" t="n">
         <v>179</v>
       </c>
@@ -28091,16 +27723,8 @@
           <t>正德</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>17.60</t>
-        </is>
-      </c>
-      <c r="F50" s="4" t="inlineStr">
-        <is>
-          <t>+0.2</t>
-        </is>
-      </c>
+      <c r="E50" s="4" t="inlineStr"/>
+      <c r="F50" s="4" t="inlineStr"/>
       <c r="G50" s="4" t="n">
         <v>173</v>
       </c>
@@ -28124,16 +27748,8 @@
           <t>撼訊</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>66.00</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="inlineStr">
-        <is>
-          <t>+6.0</t>
-        </is>
-      </c>
+      <c r="E51" s="4" t="inlineStr"/>
+      <c r="F51" s="4" t="inlineStr"/>
       <c r="G51" s="4" t="n">
         <v>173</v>
       </c>
@@ -28157,16 +27773,8 @@
           <t>金益鼎</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>91.60</t>
-        </is>
-      </c>
-      <c r="F52" s="4" t="inlineStr">
-        <is>
-          <t>+2.5</t>
-        </is>
-      </c>
+      <c r="E52" s="4" t="inlineStr"/>
+      <c r="F52" s="4" t="inlineStr"/>
       <c r="G52" s="4" t="n">
         <v>172</v>
       </c>
@@ -28190,16 +27798,8 @@
           <t>晶宏</t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>51.00</t>
-        </is>
-      </c>
-      <c r="F53" s="4" t="inlineStr">
-        <is>
-          <t>-0.9</t>
-        </is>
-      </c>
+      <c r="E53" s="4" t="inlineStr"/>
+      <c r="F53" s="4" t="inlineStr"/>
       <c r="G53" s="4" t="n">
         <v>168</v>
       </c>
@@ -28223,16 +27823,8 @@
           <t>宏捷科</t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>156.00</t>
-        </is>
-      </c>
-      <c r="F54" s="4" t="inlineStr">
-        <is>
-          <t>+2.0</t>
-        </is>
-      </c>
+      <c r="E54" s="4" t="inlineStr"/>
+      <c r="F54" s="4" t="inlineStr"/>
       <c r="G54" s="4" t="n">
         <v>168</v>
       </c>
@@ -28256,16 +27848,8 @@
           <t>創惟</t>
         </is>
       </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>99.00</t>
-        </is>
-      </c>
-      <c r="F55" s="4" t="inlineStr">
-        <is>
-          <t>+0.6</t>
-        </is>
-      </c>
+      <c r="E55" s="4" t="inlineStr"/>
+      <c r="F55" s="4" t="inlineStr"/>
       <c r="G55" s="4" t="n">
         <v>163</v>
       </c>
@@ -28289,16 +27873,8 @@
           <t>福華</t>
         </is>
       </c>
-      <c r="E56" s="4" t="inlineStr">
-        <is>
-          <t>12.30</t>
-        </is>
-      </c>
-      <c r="F56" s="4" t="inlineStr">
-        <is>
-          <t>-0.3</t>
-        </is>
-      </c>
+      <c r="E56" s="4" t="inlineStr"/>
+      <c r="F56" s="4" t="inlineStr"/>
       <c r="G56" s="4" t="n">
         <v>153</v>
       </c>
@@ -28322,16 +27898,8 @@
           <t>單井</t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr">
-        <is>
-          <t>29.30</t>
-        </is>
-      </c>
-      <c r="F57" s="4" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
+      <c r="E57" s="4" t="inlineStr"/>
+      <c r="F57" s="4" t="inlineStr"/>
       <c r="G57" s="4" t="n">
         <v>148</v>
       </c>
@@ -28355,16 +27923,8 @@
           <t>旭軟</t>
         </is>
       </c>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t>28.05</t>
-        </is>
-      </c>
-      <c r="F58" s="4" t="inlineStr">
-        <is>
-          <t>+2.55</t>
-        </is>
-      </c>
+      <c r="E58" s="4" t="inlineStr"/>
+      <c r="F58" s="4" t="inlineStr"/>
       <c r="G58" s="4" t="n">
         <v>147</v>
       </c>
@@ -28388,16 +27948,8 @@
           <t>家登</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>581.00</t>
-        </is>
-      </c>
-      <c r="F59" s="4" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
+      <c r="E59" s="4" t="inlineStr"/>
+      <c r="F59" s="4" t="inlineStr"/>
       <c r="G59" s="4" t="n">
         <v>146</v>
       </c>
@@ -28421,16 +27973,8 @@
           <t>朋億*</t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>247.50</t>
-        </is>
-      </c>
-      <c r="F60" s="4" t="inlineStr">
-        <is>
-          <t>+8.5</t>
-        </is>
-      </c>
+      <c r="E60" s="4" t="inlineStr"/>
+      <c r="F60" s="4" t="inlineStr"/>
       <c r="G60" s="4" t="n">
         <v>146</v>
       </c>
@@ -28454,16 +27998,8 @@
           <t>西勝</t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>15.60</t>
-        </is>
-      </c>
-      <c r="F61" s="4" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
+      <c r="E61" s="4" t="inlineStr"/>
+      <c r="F61" s="4" t="inlineStr"/>
       <c r="G61" s="4" t="n">
         <v>140</v>
       </c>
@@ -28487,16 +28023,8 @@
           <t>茂綸</t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr">
-        <is>
-          <t>96.90</t>
-        </is>
-      </c>
-      <c r="F62" s="4" t="inlineStr">
-        <is>
-          <t>+1.0</t>
-        </is>
-      </c>
+      <c r="E62" s="4" t="inlineStr"/>
+      <c r="F62" s="4" t="inlineStr"/>
       <c r="G62" s="4" t="n">
         <v>139</v>
       </c>
@@ -28520,16 +28048,8 @@
           <t>華盈</t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>15.70</t>
-        </is>
-      </c>
-      <c r="F63" s="4" t="inlineStr">
-        <is>
-          <t>+1.05</t>
-        </is>
-      </c>
+      <c r="E63" s="4" t="inlineStr"/>
+      <c r="F63" s="4" t="inlineStr"/>
       <c r="G63" s="4" t="n">
         <v>124</v>
       </c>
@@ -28553,16 +28073,8 @@
           <t>港建*</t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t>64.70</t>
-        </is>
-      </c>
-      <c r="F64" s="4" t="inlineStr">
-        <is>
-          <t>+0.8</t>
-        </is>
-      </c>
+      <c r="E64" s="4" t="inlineStr"/>
+      <c r="F64" s="4" t="inlineStr"/>
       <c r="G64" s="4" t="n">
         <v>122</v>
       </c>
@@ -28586,16 +28098,8 @@
           <t>科嶠</t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr">
-        <is>
-          <t>232.00</t>
-        </is>
-      </c>
-      <c r="F65" s="4" t="inlineStr">
-        <is>
-          <t>-8.0</t>
-        </is>
-      </c>
+      <c r="E65" s="4" t="inlineStr"/>
+      <c r="F65" s="4" t="inlineStr"/>
       <c r="G65" s="4" t="n">
         <v>119</v>
       </c>
@@ -28619,16 +28123,8 @@
           <t>同亨</t>
         </is>
       </c>
-      <c r="E66" s="4" t="inlineStr">
-        <is>
-          <t>28.05</t>
-        </is>
-      </c>
-      <c r="F66" s="4" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
+      <c r="E66" s="4" t="inlineStr"/>
+      <c r="F66" s="4" t="inlineStr"/>
       <c r="G66" s="4" t="n">
         <v>118</v>
       </c>
@@ -28652,16 +28148,8 @@
           <t>巨有科技</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>185.50</t>
-        </is>
-      </c>
-      <c r="F67" s="4" t="inlineStr">
-        <is>
-          <t>+12.0</t>
-        </is>
-      </c>
+      <c r="E67" s="4" t="inlineStr"/>
+      <c r="F67" s="4" t="inlineStr"/>
       <c r="G67" s="4" t="n">
         <v>116</v>
       </c>
@@ -28685,16 +28173,8 @@
           <t>翔名</t>
         </is>
       </c>
-      <c r="E68" s="4" t="inlineStr">
-        <is>
-          <t>190.00</t>
-        </is>
-      </c>
-      <c r="F68" s="4" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
+      <c r="E68" s="4" t="inlineStr"/>
+      <c r="F68" s="4" t="inlineStr"/>
       <c r="G68" s="4" t="n">
         <v>107</v>
       </c>
@@ -28718,16 +28198,8 @@
           <t>天品</t>
         </is>
       </c>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>98.30</t>
-        </is>
-      </c>
-      <c r="F69" s="4" t="inlineStr">
-        <is>
-          <t>+6.2</t>
-        </is>
-      </c>
+      <c r="E69" s="4" t="inlineStr"/>
+      <c r="F69" s="4" t="inlineStr"/>
       <c r="G69" s="4" t="n">
         <v>106</v>
       </c>
@@ -28751,16 +28223,8 @@
           <t>健椿</t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr">
-        <is>
-          <t>44.20</t>
-        </is>
-      </c>
-      <c r="F70" s="4" t="inlineStr">
-        <is>
-          <t>-0.3</t>
-        </is>
-      </c>
+      <c r="E70" s="4" t="inlineStr"/>
+      <c r="F70" s="4" t="inlineStr"/>
       <c r="G70" s="4" t="n">
         <v>105</v>
       </c>
@@ -28784,16 +28248,8 @@
           <t>雍智科技</t>
         </is>
       </c>
-      <c r="E71" s="4" t="inlineStr">
-        <is>
-          <t>2395.00</t>
-        </is>
-      </c>
-      <c r="F71" s="4" t="inlineStr">
-        <is>
-          <t>-170.0</t>
-        </is>
-      </c>
+      <c r="E71" s="4" t="inlineStr"/>
+      <c r="F71" s="4" t="inlineStr"/>
       <c r="G71" s="4" t="n">
         <v>105</v>
       </c>
@@ -28817,16 +28273,8 @@
           <t>笙泉</t>
         </is>
       </c>
-      <c r="E72" s="4" t="inlineStr">
-        <is>
-          <t>36.30</t>
-        </is>
-      </c>
-      <c r="F72" s="4" t="inlineStr">
-        <is>
-          <t>+3.3</t>
-        </is>
-      </c>
+      <c r="E72" s="4" t="inlineStr"/>
+      <c r="F72" s="4" t="inlineStr"/>
       <c r="G72" s="4" t="n">
         <v>102</v>
       </c>
@@ -28850,16 +28298,8 @@
           <t>亞昕</t>
         </is>
       </c>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>25.65</t>
-        </is>
-      </c>
-      <c r="F73" s="4" t="inlineStr">
-        <is>
-          <t>+0.1</t>
-        </is>
-      </c>
+      <c r="E73" s="4" t="inlineStr"/>
+      <c r="F73" s="4" t="inlineStr"/>
       <c r="G73" s="4" t="n">
         <v>102</v>
       </c>
@@ -28883,16 +28323,8 @@
           <t>旭然</t>
         </is>
       </c>
-      <c r="E74" s="4" t="inlineStr">
-        <is>
-          <t>43.25</t>
-        </is>
-      </c>
-      <c r="F74" s="4" t="inlineStr">
-        <is>
-          <t>+3.9</t>
-        </is>
-      </c>
+      <c r="E74" s="4" t="inlineStr"/>
+      <c r="F74" s="4" t="inlineStr"/>
       <c r="G74" s="4" t="n">
         <v>100</v>
       </c>
@@ -28916,16 +28348,8 @@
           <t>茂訊</t>
         </is>
       </c>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>111.00</t>
-        </is>
-      </c>
-      <c r="F75" s="4" t="inlineStr">
-        <is>
-          <t>+2.5</t>
-        </is>
-      </c>
+      <c r="E75" s="4" t="inlineStr"/>
+      <c r="F75" s="4" t="inlineStr"/>
       <c r="G75" s="4" t="n">
         <v>91</v>
       </c>
@@ -28949,16 +28373,8 @@
           <t>金麗科</t>
         </is>
       </c>
-      <c r="E76" s="4" t="inlineStr">
-        <is>
-          <t>242.00</t>
-        </is>
-      </c>
-      <c r="F76" s="4" t="inlineStr">
-        <is>
-          <t>+22.0</t>
-        </is>
-      </c>
+      <c r="E76" s="4" t="inlineStr"/>
+      <c r="F76" s="4" t="inlineStr"/>
       <c r="G76" s="4" t="n">
         <v>84</v>
       </c>
@@ -28982,16 +28398,8 @@
           <t>健喬</t>
         </is>
       </c>
-      <c r="E77" s="4" t="inlineStr">
-        <is>
-          <t>30.95</t>
-        </is>
-      </c>
-      <c r="F77" s="4" t="inlineStr">
-        <is>
-          <t>+0.15</t>
-        </is>
-      </c>
+      <c r="E77" s="4" t="inlineStr"/>
+      <c r="F77" s="4" t="inlineStr"/>
       <c r="G77" s="4" t="n">
         <v>83</v>
       </c>
@@ -29015,16 +28423,8 @@
           <t>高技</t>
         </is>
       </c>
-      <c r="E78" s="4" t="inlineStr">
-        <is>
-          <t>406.00</t>
-        </is>
-      </c>
-      <c r="F78" s="4" t="inlineStr">
-        <is>
-          <t>+3.0</t>
-        </is>
-      </c>
+      <c r="E78" s="4" t="inlineStr"/>
+      <c r="F78" s="4" t="inlineStr"/>
       <c r="G78" s="4" t="n">
         <v>83</v>
       </c>
@@ -29048,16 +28448,8 @@
           <t>順達</t>
         </is>
       </c>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t>374.50</t>
-        </is>
-      </c>
-      <c r="F79" s="4" t="inlineStr">
-        <is>
-          <t>+12.0</t>
-        </is>
-      </c>
+      <c r="E79" s="4" t="inlineStr"/>
+      <c r="F79" s="4" t="inlineStr"/>
       <c r="G79" s="4" t="n">
         <v>78</v>
       </c>
@@ -29081,16 +28473,8 @@
           <t>博磊</t>
         </is>
       </c>
-      <c r="E80" s="4" t="inlineStr">
-        <is>
-          <t>234.00</t>
-        </is>
-      </c>
-      <c r="F80" s="4" t="inlineStr">
-        <is>
-          <t>+17.5</t>
-        </is>
-      </c>
+      <c r="E80" s="4" t="inlineStr"/>
+      <c r="F80" s="4" t="inlineStr"/>
       <c r="G80" s="4" t="n">
         <v>78</v>
       </c>
@@ -29114,16 +28498,8 @@
           <t>凡甲</t>
         </is>
       </c>
-      <c r="E81" s="4" t="inlineStr">
-        <is>
-          <t>343.50</t>
-        </is>
-      </c>
-      <c r="F81" s="4" t="inlineStr">
-        <is>
-          <t>-9.5</t>
-        </is>
-      </c>
+      <c r="E81" s="4" t="inlineStr"/>
+      <c r="F81" s="4" t="inlineStr"/>
       <c r="G81" s="4" t="n">
         <v>77</v>
       </c>
@@ -29147,16 +28523,8 @@
           <t>信驊</t>
         </is>
       </c>
-      <c r="E82" s="4" t="inlineStr">
-        <is>
-          <t>18700.00</t>
-        </is>
-      </c>
-      <c r="F82" s="4" t="inlineStr">
-        <is>
-          <t>+910.0</t>
-        </is>
-      </c>
+      <c r="E82" s="4" t="inlineStr"/>
+      <c r="F82" s="4" t="inlineStr"/>
       <c r="G82" s="4" t="n">
         <v>77</v>
       </c>
@@ -29180,16 +28548,8 @@
           <t>晉倫</t>
         </is>
       </c>
-      <c r="E83" s="4" t="inlineStr">
-        <is>
-          <t>35.65</t>
-        </is>
-      </c>
-      <c r="F83" s="4" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
+      <c r="E83" s="4" t="inlineStr"/>
+      <c r="F83" s="4" t="inlineStr"/>
       <c r="G83" s="4" t="n">
         <v>75</v>
       </c>
@@ -29213,16 +28573,8 @@
           <t>富旺</t>
         </is>
       </c>
-      <c r="E84" s="4" t="inlineStr">
-        <is>
-          <t>12.75</t>
-        </is>
-      </c>
-      <c r="F84" s="4" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
+      <c r="E84" s="4" t="inlineStr"/>
+      <c r="F84" s="4" t="inlineStr"/>
       <c r="G84" s="4" t="n">
         <v>69</v>
       </c>
@@ -29246,16 +28598,8 @@
           <t>瑞耘</t>
         </is>
       </c>
-      <c r="E85" s="4" t="inlineStr">
-        <is>
-          <t>94.80</t>
-        </is>
-      </c>
-      <c r="F85" s="4" t="inlineStr">
-        <is>
-          <t>-3.9</t>
-        </is>
-      </c>
+      <c r="E85" s="4" t="inlineStr"/>
+      <c r="F85" s="4" t="inlineStr"/>
       <c r="G85" s="4" t="n">
         <v>67</v>
       </c>
@@ -29279,16 +28623,8 @@
           <t>泰茂</t>
         </is>
       </c>
-      <c r="E86" s="4" t="inlineStr">
-        <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="F86" s="4" t="inlineStr">
-        <is>
-          <t>+2.9</t>
-        </is>
-      </c>
+      <c r="E86" s="4" t="inlineStr"/>
+      <c r="F86" s="4" t="inlineStr"/>
       <c r="G86" s="4" t="n">
         <v>66</v>
       </c>
@@ -29312,16 +28648,8 @@
           <t>位速</t>
         </is>
       </c>
-      <c r="E87" s="4" t="inlineStr">
-        <is>
-          <t>20.70</t>
-        </is>
-      </c>
-      <c r="F87" s="4" t="inlineStr">
-        <is>
-          <t>-1.2</t>
-        </is>
-      </c>
+      <c r="E87" s="4" t="inlineStr"/>
+      <c r="F87" s="4" t="inlineStr"/>
       <c r="G87" s="4" t="n">
         <v>65</v>
       </c>
@@ -29345,16 +28673,8 @@
           <t>長佳智能</t>
         </is>
       </c>
-      <c r="E88" s="4" t="inlineStr">
-        <is>
-          <t>60.90</t>
-        </is>
-      </c>
-      <c r="F88" s="4" t="inlineStr">
-        <is>
-          <t>-0.2</t>
-        </is>
-      </c>
+      <c r="E88" s="4" t="inlineStr"/>
+      <c r="F88" s="4" t="inlineStr"/>
       <c r="G88" s="4" t="n">
         <v>63</v>
       </c>
@@ -29378,16 +28698,8 @@
           <t>茂迪</t>
         </is>
       </c>
-      <c r="E89" s="4" t="inlineStr">
-        <is>
-          <t>27.55</t>
-        </is>
-      </c>
-      <c r="F89" s="4" t="inlineStr">
-        <is>
-          <t>-0.35</t>
-        </is>
-      </c>
+      <c r="E89" s="4" t="inlineStr"/>
+      <c r="F89" s="4" t="inlineStr"/>
       <c r="G89" s="4" t="n">
         <v>62</v>
       </c>
@@ -29411,16 +28723,8 @@
           <t>凌陽創新</t>
         </is>
       </c>
-      <c r="E90" s="4" t="inlineStr">
-        <is>
-          <t>164.50</t>
-        </is>
-      </c>
-      <c r="F90" s="4" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
+      <c r="E90" s="4" t="inlineStr"/>
+      <c r="F90" s="4" t="inlineStr"/>
       <c r="G90" s="4" t="n">
         <v>60</v>
       </c>
@@ -29444,16 +28748,8 @@
           <t>亞元</t>
         </is>
       </c>
-      <c r="E91" s="4" t="inlineStr">
-        <is>
-          <t>12.40</t>
-        </is>
-      </c>
-      <c r="F91" s="4" t="inlineStr">
-        <is>
-          <t>+0.3</t>
-        </is>
-      </c>
+      <c r="E91" s="4" t="inlineStr"/>
+      <c r="F91" s="4" t="inlineStr"/>
       <c r="G91" s="4" t="n">
         <v>59</v>
       </c>
@@ -29477,16 +28773,8 @@
           <t>永信建</t>
         </is>
       </c>
-      <c r="E92" s="4" t="inlineStr">
-        <is>
-          <t>49.30</t>
-        </is>
-      </c>
-      <c r="F92" s="4" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
+      <c r="E92" s="4" t="inlineStr"/>
+      <c r="F92" s="4" t="inlineStr"/>
       <c r="G92" s="4" t="n">
         <v>55</v>
       </c>
@@ -29510,16 +28798,8 @@
           <t>太普高</t>
         </is>
       </c>
-      <c r="E93" s="4" t="inlineStr">
-        <is>
-          <t>16.20</t>
-        </is>
-      </c>
-      <c r="F93" s="4" t="inlineStr">
-        <is>
-          <t>+0.35</t>
-        </is>
-      </c>
+      <c r="E93" s="4" t="inlineStr"/>
+      <c r="F93" s="4" t="inlineStr"/>
       <c r="G93" s="4" t="n">
         <v>52</v>
       </c>
@@ -29543,16 +28823,8 @@
           <t>精剛</t>
         </is>
       </c>
-      <c r="E94" s="4" t="inlineStr">
-        <is>
-          <t>20.00</t>
-        </is>
-      </c>
-      <c r="F94" s="4" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
+      <c r="E94" s="4" t="inlineStr"/>
+      <c r="F94" s="4" t="inlineStr"/>
       <c r="G94" s="4" t="n">
         <v>51</v>
       </c>
@@ -29576,16 +28848,8 @@
           <t>逸達</t>
         </is>
       </c>
-      <c r="E95" s="4" t="inlineStr">
-        <is>
-          <t>79.50</t>
-        </is>
-      </c>
-      <c r="F95" s="4" t="inlineStr">
-        <is>
-          <t>+0.1</t>
-        </is>
-      </c>
+      <c r="E95" s="4" t="inlineStr"/>
+      <c r="F95" s="4" t="inlineStr"/>
       <c r="G95" s="4" t="n">
         <v>49</v>
       </c>
@@ -29609,16 +28873,8 @@
           <t>研通</t>
         </is>
       </c>
-      <c r="E96" s="4" t="inlineStr">
-        <is>
-          <t>28.45</t>
-        </is>
-      </c>
-      <c r="F96" s="4" t="inlineStr">
-        <is>
-          <t>+2.55</t>
-        </is>
-      </c>
+      <c r="E96" s="4" t="inlineStr"/>
+      <c r="F96" s="4" t="inlineStr"/>
       <c r="G96" s="4" t="n">
         <v>45</v>
       </c>
@@ -29642,16 +28898,8 @@
           <t>力士</t>
         </is>
       </c>
-      <c r="E97" s="4" t="inlineStr">
-        <is>
-          <t>37.40</t>
-        </is>
-      </c>
-      <c r="F97" s="4" t="inlineStr">
-        <is>
-          <t>+0.1</t>
-        </is>
-      </c>
+      <c r="E97" s="4" t="inlineStr"/>
+      <c r="F97" s="4" t="inlineStr"/>
       <c r="G97" s="4" t="n">
         <v>44</v>
       </c>
@@ -29675,16 +28923,8 @@
           <t>全宇昕</t>
         </is>
       </c>
-      <c r="E98" s="4" t="inlineStr">
-        <is>
-          <t>105.00</t>
-        </is>
-      </c>
-      <c r="F98" s="4" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
+      <c r="E98" s="4" t="inlineStr"/>
+      <c r="F98" s="4" t="inlineStr"/>
       <c r="G98" s="4" t="n">
         <v>43</v>
       </c>
@@ -29708,16 +28948,8 @@
           <t>尚凡*</t>
         </is>
       </c>
-      <c r="E99" s="4" t="inlineStr">
-        <is>
-          <t>23.35</t>
-        </is>
-      </c>
-      <c r="F99" s="4" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
+      <c r="E99" s="4" t="inlineStr"/>
+      <c r="F99" s="4" t="inlineStr"/>
       <c r="G99" s="4" t="n">
         <v>42</v>
       </c>
@@ -29741,16 +28973,8 @@
           <t>中菲行</t>
         </is>
       </c>
-      <c r="E100" s="4" t="inlineStr">
-        <is>
-          <t>78.70</t>
-        </is>
-      </c>
-      <c r="F100" s="4" t="inlineStr">
-        <is>
-          <t>+0.7</t>
-        </is>
-      </c>
+      <c r="E100" s="4" t="inlineStr"/>
+      <c r="F100" s="4" t="inlineStr"/>
       <c r="G100" s="4" t="n">
         <v>41</v>
       </c>
@@ -29774,16 +28998,8 @@
           <t>邁達康</t>
         </is>
       </c>
-      <c r="E101" s="4" t="inlineStr">
-        <is>
-          <t>34.80</t>
-        </is>
-      </c>
-      <c r="F101" s="4" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
+      <c r="E101" s="4" t="inlineStr"/>
+      <c r="F101" s="4" t="inlineStr"/>
       <c r="G101" s="4" t="n">
         <v>40</v>
       </c>
@@ -29807,16 +29023,8 @@
           <t>美好證</t>
         </is>
       </c>
-      <c r="E102" s="4" t="inlineStr">
-        <is>
-          <t>34.05</t>
-        </is>
-      </c>
-      <c r="F102" s="4" t="inlineStr">
-        <is>
-          <t>+0.25</t>
-        </is>
-      </c>
+      <c r="E102" s="4" t="inlineStr"/>
+      <c r="F102" s="4" t="inlineStr"/>
       <c r="G102" s="4" t="n">
         <v>39</v>
       </c>
@@ -29840,16 +29048,8 @@
           <t>業強</t>
         </is>
       </c>
-      <c r="E103" s="4" t="inlineStr">
-        <is>
-          <t>30.95</t>
-        </is>
-      </c>
-      <c r="F103" s="4" t="inlineStr">
-        <is>
-          <t>+0.15</t>
-        </is>
-      </c>
+      <c r="E103" s="4" t="inlineStr"/>
+      <c r="F103" s="4" t="inlineStr"/>
       <c r="G103" s="4" t="n">
         <v>38</v>
       </c>
@@ -29950,16 +29150,8 @@
           <t>穩懋</t>
         </is>
       </c>
-      <c r="E109" s="4" t="inlineStr">
-        <is>
-          <t>500.00</t>
-        </is>
-      </c>
-      <c r="F109" s="4" t="inlineStr">
-        <is>
-          <t>-55.0</t>
-        </is>
-      </c>
+      <c r="E109" s="4" t="inlineStr"/>
+      <c r="F109" s="4" t="inlineStr"/>
       <c r="G109" s="4" t="n">
         <v>-11779</v>
       </c>
@@ -29983,16 +29175,8 @@
           <t>漢磊</t>
         </is>
       </c>
-      <c r="E110" s="4" t="inlineStr">
-        <is>
-          <t>73.10</t>
-        </is>
-      </c>
-      <c r="F110" s="4" t="inlineStr">
-        <is>
-          <t>-2.4</t>
-        </is>
-      </c>
+      <c r="E110" s="4" t="inlineStr"/>
+      <c r="F110" s="4" t="inlineStr"/>
       <c r="G110" s="4" t="n">
         <v>-8577</v>
       </c>
@@ -30016,16 +29200,8 @@
           <t>東捷</t>
         </is>
       </c>
-      <c r="E111" s="4" t="inlineStr">
-        <is>
-          <t>112.50</t>
-        </is>
-      </c>
-      <c r="F111" s="4" t="inlineStr">
-        <is>
-          <t>-12.5</t>
-        </is>
-      </c>
+      <c r="E111" s="4" t="inlineStr"/>
+      <c r="F111" s="4" t="inlineStr"/>
       <c r="G111" s="4" t="n">
         <v>-4267</v>
       </c>
@@ -30049,16 +29225,8 @@
           <t>建榮</t>
         </is>
       </c>
-      <c r="E112" s="4" t="inlineStr">
-        <is>
-          <t>118.50</t>
-        </is>
-      </c>
-      <c r="F112" s="4" t="inlineStr">
-        <is>
-          <t>-8.0</t>
-        </is>
-      </c>
+      <c r="E112" s="4" t="inlineStr"/>
+      <c r="F112" s="4" t="inlineStr"/>
       <c r="G112" s="4" t="n">
         <v>-3236</v>
       </c>
@@ -30082,16 +29250,8 @@
           <t>長科*</t>
         </is>
       </c>
-      <c r="E113" s="4" t="inlineStr">
-        <is>
-          <t>51.80</t>
-        </is>
-      </c>
-      <c r="F113" s="4" t="inlineStr">
-        <is>
-          <t>-1.1</t>
-        </is>
-      </c>
+      <c r="E113" s="4" t="inlineStr"/>
+      <c r="F113" s="4" t="inlineStr"/>
       <c r="G113" s="4" t="n">
         <v>-3050</v>
       </c>
@@ -30115,16 +29275,8 @@
           <t>九豪</t>
         </is>
       </c>
-      <c r="E114" s="4" t="inlineStr">
-        <is>
-          <t>46.60</t>
-        </is>
-      </c>
-      <c r="F114" s="4" t="inlineStr">
-        <is>
-          <t>-0.9</t>
-        </is>
-      </c>
+      <c r="E114" s="4" t="inlineStr"/>
+      <c r="F114" s="4" t="inlineStr"/>
       <c r="G114" s="4" t="n">
         <v>-1904</v>
       </c>
@@ -30148,16 +29300,8 @@
           <t>方土昶</t>
         </is>
       </c>
-      <c r="E115" s="4" t="inlineStr">
-        <is>
-          <t>44.10</t>
-        </is>
-      </c>
-      <c r="F115" s="4" t="inlineStr">
-        <is>
-          <t>+0.65</t>
-        </is>
-      </c>
+      <c r="E115" s="4" t="inlineStr"/>
+      <c r="F115" s="4" t="inlineStr"/>
       <c r="G115" s="4" t="n">
         <v>-1872</v>
       </c>
@@ -30181,16 +29325,8 @@
           <t>良維</t>
         </is>
       </c>
-      <c r="E116" s="4" t="inlineStr">
-        <is>
-          <t>280.50</t>
-        </is>
-      </c>
-      <c r="F116" s="4" t="inlineStr">
-        <is>
-          <t>-10.5</t>
-        </is>
-      </c>
+      <c r="E116" s="4" t="inlineStr"/>
+      <c r="F116" s="4" t="inlineStr"/>
       <c r="G116" s="4" t="n">
         <v>-1808</v>
       </c>
@@ -30214,16 +29350,8 @@
           <t>精材</t>
         </is>
       </c>
-      <c r="E117" s="4" t="inlineStr">
-        <is>
-          <t>199.00</t>
-        </is>
-      </c>
-      <c r="F117" s="4" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
+      <c r="E117" s="4" t="inlineStr"/>
+      <c r="F117" s="4" t="inlineStr"/>
       <c r="G117" s="4" t="n">
         <v>-1558</v>
       </c>
@@ -30247,16 +29375,8 @@
           <t>合一</t>
         </is>
       </c>
-      <c r="E118" s="4" t="inlineStr">
-        <is>
-          <t>54.10</t>
-        </is>
-      </c>
-      <c r="F118" s="4" t="inlineStr">
-        <is>
-          <t>-2.6</t>
-        </is>
-      </c>
+      <c r="E118" s="4" t="inlineStr"/>
+      <c r="F118" s="4" t="inlineStr"/>
       <c r="G118" s="4" t="n">
         <v>-1526</v>
       </c>
@@ -30280,16 +29400,8 @@
           <t>雷科</t>
         </is>
       </c>
-      <c r="E119" s="4" t="inlineStr">
-        <is>
-          <t>68.70</t>
-        </is>
-      </c>
-      <c r="F119" s="4" t="inlineStr">
-        <is>
-          <t>+0.6</t>
-        </is>
-      </c>
+      <c r="E119" s="4" t="inlineStr"/>
+      <c r="F119" s="4" t="inlineStr"/>
       <c r="G119" s="4" t="n">
         <v>-1415</v>
       </c>
@@ -30313,16 +29425,8 @@
           <t>新漢</t>
         </is>
       </c>
-      <c r="E120" s="4" t="inlineStr">
-        <is>
-          <t>74.00</t>
-        </is>
-      </c>
-      <c r="F120" s="4" t="inlineStr">
-        <is>
-          <t>-1.4</t>
-        </is>
-      </c>
+      <c r="E120" s="4" t="inlineStr"/>
+      <c r="F120" s="4" t="inlineStr"/>
       <c r="G120" s="4" t="n">
         <v>-1336</v>
       </c>
@@ -30346,16 +29450,8 @@
           <t>欣銓</t>
         </is>
       </c>
-      <c r="E121" s="4" t="inlineStr">
-        <is>
-          <t>226.00</t>
-        </is>
-      </c>
-      <c r="F121" s="4" t="inlineStr">
-        <is>
-          <t>-9.5</t>
-        </is>
-      </c>
+      <c r="E121" s="4" t="inlineStr"/>
+      <c r="F121" s="4" t="inlineStr"/>
       <c r="G121" s="4" t="n">
         <v>-1268</v>
       </c>
@@ -30379,16 +29475,8 @@
           <t>尼克森</t>
         </is>
       </c>
-      <c r="E122" s="4" t="inlineStr">
-        <is>
-          <t>64.90</t>
-        </is>
-      </c>
-      <c r="F122" s="4" t="inlineStr">
-        <is>
-          <t>+2.7</t>
-        </is>
-      </c>
+      <c r="E122" s="4" t="inlineStr"/>
+      <c r="F122" s="4" t="inlineStr"/>
       <c r="G122" s="4" t="n">
         <v>-1171</v>
       </c>
@@ -30412,16 +29500,8 @@
           <t>宜特</t>
         </is>
       </c>
-      <c r="E123" s="4" t="inlineStr">
-        <is>
-          <t>180.00</t>
-        </is>
-      </c>
-      <c r="F123" s="4" t="inlineStr">
-        <is>
-          <t>-12.0</t>
-        </is>
-      </c>
+      <c r="E123" s="4" t="inlineStr"/>
+      <c r="F123" s="4" t="inlineStr"/>
       <c r="G123" s="4" t="n">
         <v>-1166</v>
       </c>
@@ -30445,16 +29525,8 @@
           <t>威剛</t>
         </is>
       </c>
-      <c r="E124" s="4" t="inlineStr">
-        <is>
-          <t>461.50</t>
-        </is>
-      </c>
-      <c r="F124" s="4" t="inlineStr">
-        <is>
-          <t>+13.5</t>
-        </is>
-      </c>
+      <c r="E124" s="4" t="inlineStr"/>
+      <c r="F124" s="4" t="inlineStr"/>
       <c r="G124" s="4" t="n">
         <v>-1162</v>
       </c>
@@ -30478,16 +29550,8 @@
           <t>華星光</t>
         </is>
       </c>
-      <c r="E125" s="4" t="inlineStr">
-        <is>
-          <t>703.00</t>
-        </is>
-      </c>
-      <c r="F125" s="4" t="inlineStr">
-        <is>
-          <t>-15.0</t>
-        </is>
-      </c>
+      <c r="E125" s="4" t="inlineStr"/>
+      <c r="F125" s="4" t="inlineStr"/>
       <c r="G125" s="4" t="n">
         <v>-1154</v>
       </c>
@@ -30511,16 +29575,8 @@
           <t>元太</t>
         </is>
       </c>
-      <c r="E126" s="4" t="inlineStr">
-        <is>
-          <t>145.50</t>
-        </is>
-      </c>
-      <c r="F126" s="4" t="inlineStr">
-        <is>
-          <t>+6.0</t>
-        </is>
-      </c>
+      <c r="E126" s="4" t="inlineStr"/>
+      <c r="F126" s="4" t="inlineStr"/>
       <c r="G126" s="4" t="n">
         <v>-1126</v>
       </c>
@@ -30544,16 +29600,8 @@
           <t>立端</t>
         </is>
       </c>
-      <c r="E127" s="4" t="inlineStr">
-        <is>
-          <t>82.10</t>
-        </is>
-      </c>
-      <c r="F127" s="4" t="inlineStr">
-        <is>
-          <t>-0.2</t>
-        </is>
-      </c>
+      <c r="E127" s="4" t="inlineStr"/>
+      <c r="F127" s="4" t="inlineStr"/>
       <c r="G127" s="4" t="n">
         <v>-1119</v>
       </c>
@@ -30577,16 +29625,8 @@
           <t>鑫科</t>
         </is>
       </c>
-      <c r="E128" s="4" t="inlineStr">
-        <is>
-          <t>70.30</t>
-        </is>
-      </c>
-      <c r="F128" s="4" t="inlineStr">
-        <is>
-          <t>-4.6</t>
-        </is>
-      </c>
+      <c r="E128" s="4" t="inlineStr"/>
+      <c r="F128" s="4" t="inlineStr"/>
       <c r="G128" s="4" t="n">
         <v>-1047</v>
       </c>
@@ -30610,16 +29650,8 @@
           <t>立碁</t>
         </is>
       </c>
-      <c r="E129" s="4" t="inlineStr">
-        <is>
-          <t>68.60</t>
-        </is>
-      </c>
-      <c r="F129" s="4" t="inlineStr">
-        <is>
-          <t>-2.2</t>
-        </is>
-      </c>
+      <c r="E129" s="4" t="inlineStr"/>
+      <c r="F129" s="4" t="inlineStr"/>
       <c r="G129" s="4" t="n">
         <v>-1030</v>
       </c>
@@ -30643,16 +29675,8 @@
           <t>廣明</t>
         </is>
       </c>
-      <c r="E130" s="4" t="inlineStr">
-        <is>
-          <t>86.80</t>
-        </is>
-      </c>
-      <c r="F130" s="4" t="inlineStr">
-        <is>
-          <t>-1.7</t>
-        </is>
-      </c>
+      <c r="E130" s="4" t="inlineStr"/>
+      <c r="F130" s="4" t="inlineStr"/>
       <c r="G130" s="4" t="n">
         <v>-1027</v>
       </c>
@@ -30676,16 +29700,8 @@
           <t>晟田</t>
         </is>
       </c>
-      <c r="E131" s="4" t="inlineStr">
-        <is>
-          <t>48.70</t>
-        </is>
-      </c>
-      <c r="F131" s="4" t="inlineStr">
-        <is>
-          <t>-3.0</t>
-        </is>
-      </c>
+      <c r="E131" s="4" t="inlineStr"/>
+      <c r="F131" s="4" t="inlineStr"/>
       <c r="G131" s="4" t="n">
         <v>-1018</v>
       </c>
@@ -30709,16 +29725,8 @@
           <t>中光電</t>
         </is>
       </c>
-      <c r="E132" s="4" t="inlineStr">
-        <is>
-          <t>73.20</t>
-        </is>
-      </c>
-      <c r="F132" s="4" t="inlineStr">
-        <is>
-          <t>-1.1</t>
-        </is>
-      </c>
+      <c r="E132" s="4" t="inlineStr"/>
+      <c r="F132" s="4" t="inlineStr"/>
       <c r="G132" s="4" t="n">
         <v>-1008</v>
       </c>
@@ -30742,16 +29750,8 @@
           <t>世紀*</t>
         </is>
       </c>
-      <c r="E133" s="4" t="inlineStr">
-        <is>
-          <t>72.10</t>
-        </is>
-      </c>
-      <c r="F133" s="4" t="inlineStr">
-        <is>
-          <t>-1.8</t>
-        </is>
-      </c>
+      <c r="E133" s="4" t="inlineStr"/>
+      <c r="F133" s="4" t="inlineStr"/>
       <c r="G133" s="4" t="n">
         <v>-893</v>
       </c>
@@ -30775,16 +29775,8 @@
           <t>九暘</t>
         </is>
       </c>
-      <c r="E134" s="4" t="inlineStr">
-        <is>
-          <t>80.60</t>
-        </is>
-      </c>
-      <c r="F134" s="4" t="inlineStr">
-        <is>
-          <t>-1.2</t>
-        </is>
-      </c>
+      <c r="E134" s="4" t="inlineStr"/>
+      <c r="F134" s="4" t="inlineStr"/>
       <c r="G134" s="4" t="n">
         <v>-851</v>
       </c>
@@ -30808,16 +29800,8 @@
           <t>雙鴻</t>
         </is>
       </c>
-      <c r="E135" s="4" t="inlineStr">
-        <is>
-          <t>1105.00</t>
-        </is>
-      </c>
-      <c r="F135" s="4" t="inlineStr">
-        <is>
-          <t>-65.0</t>
-        </is>
-      </c>
+      <c r="E135" s="4" t="inlineStr"/>
+      <c r="F135" s="4" t="inlineStr"/>
       <c r="G135" s="4" t="n">
         <v>-802</v>
       </c>
@@ -30841,16 +29825,8 @@
           <t>宏觀</t>
         </is>
       </c>
-      <c r="E136" s="4" t="inlineStr">
-        <is>
-          <t>244.50</t>
-        </is>
-      </c>
-      <c r="F136" s="4" t="inlineStr">
-        <is>
-          <t>-25.5</t>
-        </is>
-      </c>
+      <c r="E136" s="4" t="inlineStr"/>
+      <c r="F136" s="4" t="inlineStr"/>
       <c r="G136" s="4" t="n">
         <v>-798</v>
       </c>
@@ -30874,16 +29850,8 @@
           <t>華電網</t>
         </is>
       </c>
-      <c r="E137" s="4" t="inlineStr">
-        <is>
-          <t>57.30</t>
-        </is>
-      </c>
-      <c r="F137" s="4" t="inlineStr">
-        <is>
-          <t>-1.4</t>
-        </is>
-      </c>
+      <c r="E137" s="4" t="inlineStr"/>
+      <c r="F137" s="4" t="inlineStr"/>
       <c r="G137" s="4" t="n">
         <v>-791</v>
       </c>
@@ -30907,16 +29875,8 @@
           <t>台燿</t>
         </is>
       </c>
-      <c r="E138" s="4" t="inlineStr">
-        <is>
-          <t>1315.00</t>
-        </is>
-      </c>
-      <c r="F138" s="4" t="inlineStr">
-        <is>
-          <t>+95.0</t>
-        </is>
-      </c>
+      <c r="E138" s="4" t="inlineStr"/>
+      <c r="F138" s="4" t="inlineStr"/>
       <c r="G138" s="4" t="n">
         <v>-785</v>
       </c>
@@ -30940,16 +29900,8 @@
           <t>鉅橡</t>
         </is>
       </c>
-      <c r="E139" s="4" t="inlineStr">
-        <is>
-          <t>84.50</t>
-        </is>
-      </c>
-      <c r="F139" s="4" t="inlineStr">
-        <is>
-          <t>nannan</t>
-        </is>
-      </c>
+      <c r="E139" s="4" t="inlineStr"/>
+      <c r="F139" s="4" t="inlineStr"/>
       <c r="G139" s="4" t="n">
         <v>-783</v>
       </c>
@@ -30973,16 +29925,8 @@
           <t>智通*</t>
         </is>
       </c>
-      <c r="E140" s="4" t="inlineStr">
-        <is>
-          <t>92.00</t>
-        </is>
-      </c>
-      <c r="F140" s="4" t="inlineStr">
-        <is>
-          <t>-0.8</t>
-        </is>
-      </c>
+      <c r="E140" s="4" t="inlineStr"/>
+      <c r="F140" s="4" t="inlineStr"/>
       <c r="G140" s="4" t="n">
         <v>-778</v>
       </c>
@@ -31006,16 +29950,8 @@
           <t>協易機</t>
         </is>
       </c>
-      <c r="E141" s="4" t="inlineStr">
-        <is>
-          <t>31.70</t>
-        </is>
-      </c>
-      <c r="F141" s="4" t="inlineStr">
-        <is>
-          <t>-1.05</t>
-        </is>
-      </c>
+      <c r="E141" s="4" t="inlineStr"/>
+      <c r="F141" s="4" t="inlineStr"/>
       <c r="G141" s="4" t="n">
         <v>-773</v>
       </c>
@@ -31039,16 +29975,8 @@
           <t>太景*-KY</t>
         </is>
       </c>
-      <c r="E142" s="4" t="inlineStr">
-        <is>
-          <t>9.68</t>
-        </is>
-      </c>
-      <c r="F142" s="4" t="inlineStr">
-        <is>
-          <t>-0.32</t>
-        </is>
-      </c>
+      <c r="E142" s="4" t="inlineStr"/>
+      <c r="F142" s="4" t="inlineStr"/>
       <c r="G142" s="4" t="n">
         <v>-770</v>
       </c>
@@ -31072,16 +30000,8 @@
           <t>臺慶科</t>
         </is>
       </c>
-      <c r="E143" s="4" t="inlineStr">
-        <is>
-          <t>170.00</t>
-        </is>
-      </c>
-      <c r="F143" s="4" t="inlineStr">
-        <is>
-          <t>-4.0</t>
-        </is>
-      </c>
+      <c r="E143" s="4" t="inlineStr"/>
+      <c r="F143" s="4" t="inlineStr"/>
       <c r="G143" s="4" t="n">
         <v>-727</v>
       </c>
@@ -31105,16 +30025,8 @@
           <t>均豪</t>
         </is>
       </c>
-      <c r="E144" s="4" t="inlineStr">
-        <is>
-          <t>129.00</t>
-        </is>
-      </c>
-      <c r="F144" s="4" t="inlineStr">
-        <is>
-          <t>-6.0</t>
-        </is>
-      </c>
+      <c r="E144" s="4" t="inlineStr"/>
+      <c r="F144" s="4" t="inlineStr"/>
       <c r="G144" s="4" t="n">
         <v>-682</v>
       </c>
@@ -31138,16 +30050,8 @@
           <t>華容</t>
         </is>
       </c>
-      <c r="E145" s="4" t="inlineStr">
-        <is>
-          <t>26.00</t>
-        </is>
-      </c>
-      <c r="F145" s="4" t="inlineStr">
-        <is>
-          <t>-0.75</t>
-        </is>
-      </c>
+      <c r="E145" s="4" t="inlineStr"/>
+      <c r="F145" s="4" t="inlineStr"/>
       <c r="G145" s="4" t="n">
         <v>-677</v>
       </c>
@@ -31171,16 +30075,8 @@
           <t>亞泰金屬</t>
         </is>
       </c>
-      <c r="E146" s="4" t="inlineStr">
-        <is>
-          <t>417.00</t>
-        </is>
-      </c>
-      <c r="F146" s="4" t="inlineStr">
-        <is>
-          <t>+10.0</t>
-        </is>
-      </c>
+      <c r="E146" s="4" t="inlineStr"/>
+      <c r="F146" s="4" t="inlineStr"/>
       <c r="G146" s="4" t="n">
         <v>-668</v>
       </c>
@@ -31204,16 +30100,8 @@
           <t>萬潤</t>
         </is>
       </c>
-      <c r="E147" s="4" t="inlineStr">
-        <is>
-          <t>1215.00</t>
-        </is>
-      </c>
-      <c r="F147" s="4" t="inlineStr">
-        <is>
-          <t>-130.0</t>
-        </is>
-      </c>
+      <c r="E147" s="4" t="inlineStr"/>
+      <c r="F147" s="4" t="inlineStr"/>
       <c r="G147" s="4" t="n">
         <v>-658</v>
       </c>
@@ -31237,16 +30125,8 @@
           <t>浩鼎</t>
         </is>
       </c>
-      <c r="E148" s="4" t="inlineStr">
-        <is>
-          <t>35.25</t>
-        </is>
-      </c>
-      <c r="F148" s="4" t="inlineStr">
-        <is>
-          <t>+0.4</t>
-        </is>
-      </c>
+      <c r="E148" s="4" t="inlineStr"/>
+      <c r="F148" s="4" t="inlineStr"/>
       <c r="G148" s="4" t="n">
         <v>-645</v>
       </c>
@@ -31270,16 +30150,8 @@
           <t>環宇-KY</t>
         </is>
       </c>
-      <c r="E149" s="4" t="inlineStr">
-        <is>
-          <t>725.00</t>
-        </is>
-      </c>
-      <c r="F149" s="4" t="inlineStr">
-        <is>
-          <t>-19.0</t>
-        </is>
-      </c>
+      <c r="E149" s="4" t="inlineStr"/>
+      <c r="F149" s="4" t="inlineStr"/>
       <c r="G149" s="4" t="n">
         <v>-629</v>
       </c>
@@ -31303,16 +30175,8 @@
           <t>中天</t>
         </is>
       </c>
-      <c r="E150" s="4" t="inlineStr">
-        <is>
-          <t>15.40</t>
-        </is>
-      </c>
-      <c r="F150" s="4" t="inlineStr">
-        <is>
-          <t>-0.55</t>
-        </is>
-      </c>
+      <c r="E150" s="4" t="inlineStr"/>
+      <c r="F150" s="4" t="inlineStr"/>
       <c r="G150" s="4" t="n">
         <v>-590</v>
       </c>
@@ -31336,16 +30200,8 @@
           <t>聯上</t>
         </is>
       </c>
-      <c r="E151" s="4" t="inlineStr">
-        <is>
-          <t>16.30</t>
-        </is>
-      </c>
-      <c r="F151" s="4" t="inlineStr">
-        <is>
-          <t>+0.05</t>
-        </is>
-      </c>
+      <c r="E151" s="4" t="inlineStr"/>
+      <c r="F151" s="4" t="inlineStr"/>
       <c r="G151" s="4" t="n">
         <v>-576</v>
       </c>
@@ -31369,16 +30225,8 @@
           <t>前鼎</t>
         </is>
       </c>
-      <c r="E152" s="4" t="inlineStr">
-        <is>
-          <t>246.50</t>
-        </is>
-      </c>
-      <c r="F152" s="4" t="inlineStr">
-        <is>
-          <t>-3.5</t>
-        </is>
-      </c>
+      <c r="E152" s="4" t="inlineStr"/>
+      <c r="F152" s="4" t="inlineStr"/>
       <c r="G152" s="4" t="n">
         <v>-566</v>
       </c>
@@ -31402,16 +30250,8 @@
           <t>華宏</t>
         </is>
       </c>
-      <c r="E153" s="4" t="inlineStr">
-        <is>
-          <t>69.90</t>
-        </is>
-      </c>
-      <c r="F153" s="4" t="inlineStr">
-        <is>
-          <t>+0.8</t>
-        </is>
-      </c>
+      <c r="E153" s="4" t="inlineStr"/>
+      <c r="F153" s="4" t="inlineStr"/>
       <c r="G153" s="4" t="n">
         <v>-562</v>
       </c>
@@ -31435,16 +30275,8 @@
           <t>聯亞</t>
         </is>
       </c>
-      <c r="E154" s="4" t="inlineStr">
-        <is>
-          <t>2655.00</t>
-        </is>
-      </c>
-      <c r="F154" s="4" t="inlineStr">
-        <is>
-          <t>-160.0</t>
-        </is>
-      </c>
+      <c r="E154" s="4" t="inlineStr"/>
+      <c r="F154" s="4" t="inlineStr"/>
       <c r="G154" s="4" t="n">
         <v>-559</v>
       </c>
@@ -31468,16 +30300,8 @@
           <t>岱稜</t>
         </is>
       </c>
-      <c r="E155" s="4" t="inlineStr">
-        <is>
-          <t>51.30</t>
-        </is>
-      </c>
-      <c r="F155" s="4" t="inlineStr">
-        <is>
-          <t>-2.4</t>
-        </is>
-      </c>
+      <c r="E155" s="4" t="inlineStr"/>
+      <c r="F155" s="4" t="inlineStr"/>
       <c r="G155" s="4" t="n">
         <v>-532</v>
       </c>
@@ -31501,16 +30325,8 @@
           <t>北基</t>
         </is>
       </c>
-      <c r="E156" s="4" t="inlineStr">
-        <is>
-          <t>21.15</t>
-        </is>
-      </c>
-      <c r="F156" s="4" t="inlineStr">
-        <is>
-          <t>-1.65</t>
-        </is>
-      </c>
+      <c r="E156" s="4" t="inlineStr"/>
+      <c r="F156" s="4" t="inlineStr"/>
       <c r="G156" s="4" t="n">
         <v>-511</v>
       </c>
@@ -31534,16 +30350,8 @@
           <t>友威科</t>
         </is>
       </c>
-      <c r="E157" s="4" t="inlineStr">
-        <is>
-          <t>92.00</t>
-        </is>
-      </c>
-      <c r="F157" s="4" t="inlineStr">
-        <is>
-          <t>-7.0</t>
-        </is>
-      </c>
+      <c r="E157" s="4" t="inlineStr"/>
+      <c r="F157" s="4" t="inlineStr"/>
       <c r="G157" s="4" t="n">
         <v>-501</v>
       </c>
@@ -31567,16 +30375,8 @@
           <t>東洋</t>
         </is>
       </c>
-      <c r="E158" s="4" t="inlineStr">
-        <is>
-          <t>73.50</t>
-        </is>
-      </c>
-      <c r="F158" s="4" t="inlineStr">
-        <is>
-          <t>-0.7</t>
-        </is>
-      </c>
+      <c r="E158" s="4" t="inlineStr"/>
+      <c r="F158" s="4" t="inlineStr"/>
       <c r="G158" s="4" t="n">
         <v>-492</v>
       </c>

--- a/StockInfo/otc_analysis_result.xlsx
+++ b/StockInfo/otc_analysis_result.xlsx
@@ -21457,16 +21457,8 @@
           <t>頎邦</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>192.50</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>+17.5</t>
-        </is>
-      </c>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr"/>
       <c r="G4" s="4" t="n">
         <v>7918</v>
       </c>
@@ -21490,16 +21482,8 @@
           <t>合晶</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>55.60</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>+5.0</t>
-        </is>
-      </c>
+      <c r="E5" s="4" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr"/>
       <c r="G5" s="4" t="n">
         <v>4759</v>
       </c>
@@ -21523,16 +21507,8 @@
           <t>茂迪</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>30.30</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>+2.75</t>
-        </is>
-      </c>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr"/>
       <c r="G6" s="4" t="n">
         <v>4739</v>
       </c>
@@ -21556,16 +21532,8 @@
           <t>環球晶</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>793.00</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>+72.0</t>
-        </is>
-      </c>
+      <c r="E7" s="4" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr"/>
       <c r="G7" s="4" t="n">
         <v>3960</v>
       </c>
@@ -21589,16 +21557,8 @@
           <t>華容</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>28.60</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>+2.6</t>
-        </is>
-      </c>
+      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr"/>
       <c r="G8" s="4" t="n">
         <v>3888</v>
       </c>
@@ -21622,16 +21582,8 @@
           <t>穩懋</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>500.00</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr"/>
       <c r="G9" s="4" t="n">
         <v>2784</v>
       </c>
@@ -21655,16 +21607,8 @@
           <t>元太</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>153.00</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>+7.5</t>
-        </is>
-      </c>
+      <c r="E10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr"/>
       <c r="G10" s="4" t="n">
         <v>2762</v>
       </c>
@@ -21688,16 +21632,8 @@
           <t>康和證</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>21.90</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>+1.5</t>
-        </is>
-      </c>
+      <c r="E11" s="4" t="inlineStr"/>
+      <c r="F11" s="4" t="inlineStr"/>
       <c r="G11" s="4" t="n">
         <v>2653</v>
       </c>
@@ -21721,16 +21657,8 @@
           <t>榮剛</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>36.10</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>+1.0</t>
-        </is>
-      </c>
+      <c r="E12" s="4" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr"/>
       <c r="G12" s="4" t="n">
         <v>2559</v>
       </c>
@@ -21754,16 +21682,8 @@
           <t>致和證</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>34.30</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>+3.1</t>
-        </is>
-      </c>
+      <c r="E13" s="4" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr"/>
       <c r="G13" s="4" t="n">
         <v>2549</v>
       </c>
@@ -21787,16 +21707,8 @@
           <t>福邦證</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>16.70</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>+0.8</t>
-        </is>
-      </c>
+      <c r="E14" s="4" t="inlineStr"/>
+      <c r="F14" s="4" t="inlineStr"/>
       <c r="G14" s="4" t="n">
         <v>2273</v>
       </c>
@@ -21820,16 +21732,8 @@
           <t>國統</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>52.80</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>+0.3</t>
-        </is>
-      </c>
+      <c r="E15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr"/>
       <c r="G15" s="4" t="n">
         <v>1200</v>
       </c>
@@ -21853,16 +21757,8 @@
           <t>創惟</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>102.00</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>+3.0</t>
-        </is>
-      </c>
+      <c r="E16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr"/>
       <c r="G16" s="4" t="n">
         <v>1152</v>
       </c>
@@ -21886,16 +21782,8 @@
           <t>宏遠證</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>16.05</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>+1.0</t>
-        </is>
-      </c>
+      <c r="E17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr"/>
       <c r="G17" s="4" t="n">
         <v>1134</v>
       </c>
@@ -21919,16 +21807,8 @@
           <t>千如</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>32.60</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>+1.65</t>
-        </is>
-      </c>
+      <c r="E18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr"/>
       <c r="G18" s="4" t="n">
         <v>1097</v>
       </c>
@@ -21952,16 +21832,8 @@
           <t>鑫聯大投控</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>84.50</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>+2.0</t>
-        </is>
-      </c>
+      <c r="E19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr"/>
       <c r="G19" s="4" t="n">
         <v>1082</v>
       </c>
@@ -21985,16 +21857,8 @@
           <t>九豪</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>48.00</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>+1.4</t>
-        </is>
-      </c>
+      <c r="E20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr"/>
       <c r="G20" s="4" t="n">
         <v>963</v>
       </c>
@@ -22018,16 +21882,8 @@
           <t>正德</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>18.50</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>+0.9</t>
-        </is>
-      </c>
+      <c r="E21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr"/>
       <c r="G21" s="4" t="n">
         <v>874</v>
       </c>
@@ -22051,16 +21907,8 @@
           <t>鑫科</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>74.40</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>+4.1</t>
-        </is>
-      </c>
+      <c r="E22" s="4" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr"/>
       <c r="G22" s="4" t="n">
         <v>873</v>
       </c>
@@ -22084,16 +21932,8 @@
           <t>世紀*</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>74.40</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>+2.3</t>
-        </is>
-      </c>
+      <c r="E23" s="4" t="inlineStr"/>
+      <c r="F23" s="4" t="inlineStr"/>
       <c r="G23" s="4" t="n">
         <v>798</v>
       </c>
@@ -22117,16 +21957,8 @@
           <t>凡甲</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>377.50</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>+34.0</t>
-        </is>
-      </c>
+      <c r="E24" s="4" t="inlineStr"/>
+      <c r="F24" s="4" t="inlineStr"/>
       <c r="G24" s="4" t="n">
         <v>748</v>
       </c>
@@ -22150,16 +21982,8 @@
           <t>精確</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>95.90</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>+6.1</t>
-        </is>
-      </c>
+      <c r="E25" s="4" t="inlineStr"/>
+      <c r="F25" s="4" t="inlineStr"/>
       <c r="G25" s="4" t="n">
         <v>747</v>
       </c>
@@ -22183,16 +22007,8 @@
           <t>長科*</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>52.00</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>+0.2</t>
-        </is>
-      </c>
+      <c r="E26" s="4" t="inlineStr"/>
+      <c r="F26" s="4" t="inlineStr"/>
       <c r="G26" s="4" t="n">
         <v>741</v>
       </c>
@@ -22216,16 +22032,8 @@
           <t>鈦昇</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>204.00</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>+8.5</t>
-        </is>
-      </c>
+      <c r="E27" s="4" t="inlineStr"/>
+      <c r="F27" s="4" t="inlineStr"/>
       <c r="G27" s="4" t="n">
         <v>721</v>
       </c>
@@ -22249,16 +22057,8 @@
           <t>尼克森</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>66.90</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>+2.0</t>
-        </is>
-      </c>
+      <c r="E28" s="4" t="inlineStr"/>
+      <c r="F28" s="4" t="inlineStr"/>
       <c r="G28" s="4" t="n">
         <v>715</v>
       </c>
@@ -22282,16 +22082,8 @@
           <t>金居</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>469.00</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>+10.5</t>
-        </is>
-      </c>
+      <c r="E29" s="4" t="inlineStr"/>
+      <c r="F29" s="4" t="inlineStr"/>
       <c r="G29" s="4" t="n">
         <v>688</v>
       </c>
@@ -22315,16 +22107,8 @@
           <t>巨有科技</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>204.00</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>+18.5</t>
-        </is>
-      </c>
+      <c r="E30" s="4" t="inlineStr"/>
+      <c r="F30" s="4" t="inlineStr"/>
       <c r="G30" s="4" t="n">
         <v>672</v>
       </c>
@@ -22348,16 +22132,8 @@
           <t>茂達</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>262.00</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>+11.5</t>
-        </is>
-      </c>
+      <c r="E31" s="4" t="inlineStr"/>
+      <c r="F31" s="4" t="inlineStr"/>
       <c r="G31" s="4" t="n">
         <v>581</v>
       </c>
@@ -22381,16 +22157,8 @@
           <t>佳邦</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>81.00</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>+3.2</t>
-        </is>
-      </c>
+      <c r="E32" s="4" t="inlineStr"/>
+      <c r="F32" s="4" t="inlineStr"/>
       <c r="G32" s="4" t="n">
         <v>563</v>
       </c>
@@ -22414,16 +22182,8 @@
           <t>系微</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>332.00</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>+30.0</t>
-        </is>
-      </c>
+      <c r="E33" s="4" t="inlineStr"/>
+      <c r="F33" s="4" t="inlineStr"/>
       <c r="G33" s="4" t="n">
         <v>520</v>
       </c>
@@ -22447,16 +22207,8 @@
           <t>亞昕</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>26.10</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>+0.45</t>
-        </is>
-      </c>
+      <c r="E34" s="4" t="inlineStr"/>
+      <c r="F34" s="4" t="inlineStr"/>
       <c r="G34" s="4" t="n">
         <v>519</v>
       </c>
@@ -22480,16 +22232,8 @@
           <t>沛亨</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>482.00</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>+43.5</t>
-        </is>
-      </c>
+      <c r="E35" s="4" t="inlineStr"/>
+      <c r="F35" s="4" t="inlineStr"/>
       <c r="G35" s="4" t="n">
         <v>513</v>
       </c>
@@ -22513,16 +22257,8 @@
           <t>蜜望實</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>95.40</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>+3.6</t>
-        </is>
-      </c>
+      <c r="E36" s="4" t="inlineStr"/>
+      <c r="F36" s="4" t="inlineStr"/>
       <c r="G36" s="4" t="n">
         <v>511</v>
       </c>
@@ -22546,16 +22282,8 @@
           <t>德微</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>242.00</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>+22.0</t>
-        </is>
-      </c>
+      <c r="E37" s="4" t="inlineStr"/>
+      <c r="F37" s="4" t="inlineStr"/>
       <c r="G37" s="4" t="n">
         <v>507</v>
       </c>
@@ -22579,16 +22307,8 @@
           <t>台半</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>71.50</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>+3.0</t>
-        </is>
-      </c>
+      <c r="E38" s="4" t="inlineStr"/>
+      <c r="F38" s="4" t="inlineStr"/>
       <c r="G38" s="4" t="n">
         <v>491</v>
       </c>
@@ -22612,16 +22332,8 @@
           <t>晟田</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>50.20</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>+1.5</t>
-        </is>
-      </c>
+      <c r="E39" s="4" t="inlineStr"/>
+      <c r="F39" s="4" t="inlineStr"/>
       <c r="G39" s="4" t="n">
         <v>490</v>
       </c>
@@ -22645,16 +22357,8 @@
           <t>單井</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>31.60</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>+2.3</t>
-        </is>
-      </c>
+      <c r="E40" s="4" t="inlineStr"/>
+      <c r="F40" s="4" t="inlineStr"/>
       <c r="G40" s="4" t="n">
         <v>485</v>
       </c>
@@ -22678,16 +22382,8 @@
           <t>中光電</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>73.20</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
+      <c r="E41" s="4" t="inlineStr"/>
+      <c r="F41" s="4" t="inlineStr"/>
       <c r="G41" s="4" t="n">
         <v>467</v>
       </c>
@@ -22711,16 +22407,8 @@
           <t>精剛</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>20.35</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>+0.35</t>
-        </is>
-      </c>
+      <c r="E42" s="4" t="inlineStr"/>
+      <c r="F42" s="4" t="inlineStr"/>
       <c r="G42" s="4" t="n">
         <v>463</v>
       </c>
@@ -22744,16 +22432,8 @@
           <t>瑞耘</t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>104.00</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>+9.2</t>
-        </is>
-      </c>
+      <c r="E43" s="4" t="inlineStr"/>
+      <c r="F43" s="4" t="inlineStr"/>
       <c r="G43" s="4" t="n">
         <v>459</v>
       </c>
@@ -22777,16 +22457,8 @@
           <t>立端</t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>82.50</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>+0.4</t>
-        </is>
-      </c>
+      <c r="E44" s="4" t="inlineStr"/>
+      <c r="F44" s="4" t="inlineStr"/>
       <c r="G44" s="4" t="n">
         <v>444</v>
       </c>
@@ -22810,16 +22482,8 @@
           <t>中美晶</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>152.00</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>+6.5</t>
-        </is>
-      </c>
+      <c r="E45" s="4" t="inlineStr"/>
+      <c r="F45" s="4" t="inlineStr"/>
       <c r="G45" s="4" t="n">
         <v>429</v>
       </c>
@@ -22843,16 +22507,8 @@
           <t>宜鼎</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>1575.00</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>+100.0</t>
-        </is>
-      </c>
+      <c r="E46" s="4" t="inlineStr"/>
+      <c r="F46" s="4" t="inlineStr"/>
       <c r="G46" s="4" t="n">
         <v>425</v>
       </c>
@@ -22876,16 +22532,8 @@
           <t>原相</t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>217.00</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t>+1.0</t>
-        </is>
-      </c>
+      <c r="E47" s="4" t="inlineStr"/>
+      <c r="F47" s="4" t="inlineStr"/>
       <c r="G47" s="4" t="n">
         <v>421</v>
       </c>
@@ -22909,16 +22557,8 @@
           <t>朋程</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>146.00</t>
-        </is>
-      </c>
-      <c r="F48" s="4" t="inlineStr">
-        <is>
-          <t>+3.0</t>
-        </is>
-      </c>
+      <c r="E48" s="4" t="inlineStr"/>
+      <c r="F48" s="4" t="inlineStr"/>
       <c r="G48" s="4" t="n">
         <v>414</v>
       </c>
@@ -22942,16 +22582,8 @@
           <t>太欣</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>12.00</t>
-        </is>
-      </c>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
+      <c r="E49" s="4" t="inlineStr"/>
+      <c r="F49" s="4" t="inlineStr"/>
       <c r="G49" s="4" t="n">
         <v>407</v>
       </c>
@@ -22975,16 +22607,8 @@
           <t>亞泰金屬</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>458.50</t>
-        </is>
-      </c>
-      <c r="F50" s="4" t="inlineStr">
-        <is>
-          <t>+41.5</t>
-        </is>
-      </c>
+      <c r="E50" s="4" t="inlineStr"/>
+      <c r="F50" s="4" t="inlineStr"/>
       <c r="G50" s="4" t="n">
         <v>381</v>
       </c>
@@ -23008,16 +22632,8 @@
           <t>東洋</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>74.50</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="inlineStr">
-        <is>
-          <t>+1.0</t>
-        </is>
-      </c>
+      <c r="E51" s="4" t="inlineStr"/>
+      <c r="F51" s="4" t="inlineStr"/>
       <c r="G51" s="4" t="n">
         <v>376</v>
       </c>
@@ -23041,16 +22657,8 @@
           <t>晶宏</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>56.10</t>
-        </is>
-      </c>
-      <c r="F52" s="4" t="inlineStr">
-        <is>
-          <t>+5.1</t>
-        </is>
-      </c>
+      <c r="E52" s="4" t="inlineStr"/>
+      <c r="F52" s="4" t="inlineStr"/>
       <c r="G52" s="4" t="n">
         <v>328</v>
       </c>
@@ -23074,16 +22682,8 @@
           <t>系統電</t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>63.80</t>
-        </is>
-      </c>
-      <c r="F53" s="4" t="inlineStr">
-        <is>
-          <t>+0.6</t>
-        </is>
-      </c>
+      <c r="E53" s="4" t="inlineStr"/>
+      <c r="F53" s="4" t="inlineStr"/>
       <c r="G53" s="4" t="n">
         <v>321</v>
       </c>
@@ -23107,16 +22707,8 @@
           <t>廣明</t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>86.40</t>
-        </is>
-      </c>
-      <c r="F54" s="4" t="inlineStr">
-        <is>
-          <t>-0.4</t>
-        </is>
-      </c>
+      <c r="E54" s="4" t="inlineStr"/>
+      <c r="F54" s="4" t="inlineStr"/>
       <c r="G54" s="4" t="n">
         <v>307</v>
       </c>
@@ -23140,16 +22732,8 @@
           <t>振曜</t>
         </is>
       </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>93.30</t>
-        </is>
-      </c>
-      <c r="F55" s="4" t="inlineStr">
-        <is>
-          <t>+2.7</t>
-        </is>
-      </c>
+      <c r="E55" s="4" t="inlineStr"/>
+      <c r="F55" s="4" t="inlineStr"/>
       <c r="G55" s="4" t="n">
         <v>288</v>
       </c>
@@ -23173,16 +22757,8 @@
           <t>台燿</t>
         </is>
       </c>
-      <c r="E56" s="4" t="inlineStr">
-        <is>
-          <t>1445.00</t>
-        </is>
-      </c>
-      <c r="F56" s="4" t="inlineStr">
-        <is>
-          <t>+130.0</t>
-        </is>
-      </c>
+      <c r="E56" s="4" t="inlineStr"/>
+      <c r="F56" s="4" t="inlineStr"/>
       <c r="G56" s="4" t="n">
         <v>287</v>
       </c>
@@ -23206,16 +22782,8 @@
           <t>霖宏</t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr">
-        <is>
-          <t>47.65</t>
-        </is>
-      </c>
-      <c r="F57" s="4" t="inlineStr">
-        <is>
-          <t>+4.3</t>
-        </is>
-      </c>
+      <c r="E57" s="4" t="inlineStr"/>
+      <c r="F57" s="4" t="inlineStr"/>
       <c r="G57" s="4" t="n">
         <v>285</v>
       </c>
@@ -23239,16 +22807,8 @@
           <t>亞通</t>
         </is>
       </c>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t>24.05</t>
-        </is>
-      </c>
-      <c r="F58" s="4" t="inlineStr">
-        <is>
-          <t>+0.35</t>
-        </is>
-      </c>
+      <c r="E58" s="4" t="inlineStr"/>
+      <c r="F58" s="4" t="inlineStr"/>
       <c r="G58" s="4" t="n">
         <v>283</v>
       </c>
@@ -23272,16 +22832,8 @@
           <t>美好證</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>34.90</t>
-        </is>
-      </c>
-      <c r="F59" s="4" t="inlineStr">
-        <is>
-          <t>+0.85</t>
-        </is>
-      </c>
+      <c r="E59" s="4" t="inlineStr"/>
+      <c r="F59" s="4" t="inlineStr"/>
       <c r="G59" s="4" t="n">
         <v>280</v>
       </c>
@@ -23305,16 +22857,8 @@
           <t>新潤</t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>40.50</t>
-        </is>
-      </c>
-      <c r="F60" s="4" t="inlineStr">
-        <is>
-          <t>+0.55</t>
-        </is>
-      </c>
+      <c r="E60" s="4" t="inlineStr"/>
+      <c r="F60" s="4" t="inlineStr"/>
       <c r="G60" s="4" t="n">
         <v>276</v>
       </c>
@@ -23338,16 +22882,8 @@
           <t>金益鼎</t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>94.40</t>
-        </is>
-      </c>
-      <c r="F61" s="4" t="inlineStr">
-        <is>
-          <t>+2.8</t>
-        </is>
-      </c>
+      <c r="E61" s="4" t="inlineStr"/>
+      <c r="F61" s="4" t="inlineStr"/>
       <c r="G61" s="4" t="n">
         <v>268</v>
       </c>
@@ -23371,16 +22907,8 @@
           <t>大立</t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr">
-        <is>
-          <t>15.35</t>
-        </is>
-      </c>
-      <c r="F62" s="4" t="inlineStr">
-        <is>
-          <t>+0.9</t>
-        </is>
-      </c>
+      <c r="E62" s="4" t="inlineStr"/>
+      <c r="F62" s="4" t="inlineStr"/>
       <c r="G62" s="4" t="n">
         <v>263</v>
       </c>
@@ -23404,16 +22932,8 @@
           <t>鈺太</t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>312.00</t>
-        </is>
-      </c>
-      <c r="F63" s="4" t="inlineStr">
-        <is>
-          <t>+10.0</t>
-        </is>
-      </c>
+      <c r="E63" s="4" t="inlineStr"/>
+      <c r="F63" s="4" t="inlineStr"/>
       <c r="G63" s="4" t="n">
         <v>258</v>
       </c>
@@ -23437,16 +22957,8 @@
           <t>太景*-KY</t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t>9.72</t>
-        </is>
-      </c>
-      <c r="F64" s="4" t="inlineStr">
-        <is>
-          <t>+0.04</t>
-        </is>
-      </c>
+      <c r="E64" s="4" t="inlineStr"/>
+      <c r="F64" s="4" t="inlineStr"/>
       <c r="G64" s="4" t="n">
         <v>249</v>
       </c>
@@ -23470,16 +22982,8 @@
           <t>旺矽</t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr">
-        <is>
-          <t>5030.00</t>
-        </is>
-      </c>
-      <c r="F65" s="4" t="inlineStr">
-        <is>
-          <t>+80.0</t>
-        </is>
-      </c>
+      <c r="E65" s="4" t="inlineStr"/>
+      <c r="F65" s="4" t="inlineStr"/>
       <c r="G65" s="4" t="n">
         <v>238</v>
       </c>
@@ -23503,16 +23007,8 @@
           <t>建舜電</t>
         </is>
       </c>
-      <c r="E66" s="4" t="inlineStr">
-        <is>
-          <t>13.45</t>
-        </is>
-      </c>
-      <c r="F66" s="4" t="inlineStr">
-        <is>
-          <t>+0.4</t>
-        </is>
-      </c>
+      <c r="E66" s="4" t="inlineStr"/>
+      <c r="F66" s="4" t="inlineStr"/>
       <c r="G66" s="4" t="n">
         <v>232</v>
       </c>
@@ -23536,16 +23032,8 @@
           <t>臺慶科</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>177.50</t>
-        </is>
-      </c>
-      <c r="F67" s="4" t="inlineStr">
-        <is>
-          <t>+7.5</t>
-        </is>
-      </c>
+      <c r="E67" s="4" t="inlineStr"/>
+      <c r="F67" s="4" t="inlineStr"/>
       <c r="G67" s="4" t="n">
         <v>223</v>
       </c>
@@ -23569,16 +23057,8 @@
           <t>智擎</t>
         </is>
       </c>
-      <c r="E68" s="4" t="inlineStr">
-        <is>
-          <t>57.80</t>
-        </is>
-      </c>
-      <c r="F68" s="4" t="inlineStr">
-        <is>
-          <t>+0.9</t>
-        </is>
-      </c>
+      <c r="E68" s="4" t="inlineStr"/>
+      <c r="F68" s="4" t="inlineStr"/>
       <c r="G68" s="4" t="n">
         <v>219</v>
       </c>
@@ -23602,16 +23082,8 @@
           <t>碩禾</t>
         </is>
       </c>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>131.50</t>
-        </is>
-      </c>
-      <c r="F69" s="4" t="inlineStr">
-        <is>
-          <t>-4.5</t>
-        </is>
-      </c>
+      <c r="E69" s="4" t="inlineStr"/>
+      <c r="F69" s="4" t="inlineStr"/>
       <c r="G69" s="4" t="n">
         <v>217</v>
       </c>
@@ -23635,16 +23107,8 @@
           <t>聯光通</t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr">
-        <is>
-          <t>45.40</t>
-        </is>
-      </c>
-      <c r="F70" s="4" t="inlineStr">
-        <is>
-          <t>+0.8</t>
-        </is>
-      </c>
+      <c r="E70" s="4" t="inlineStr"/>
+      <c r="F70" s="4" t="inlineStr"/>
       <c r="G70" s="4" t="n">
         <v>216</v>
       </c>
@@ -23668,16 +23132,8 @@
           <t>良維</t>
         </is>
       </c>
-      <c r="E71" s="4" t="inlineStr">
-        <is>
-          <t>281.50</t>
-        </is>
-      </c>
-      <c r="F71" s="4" t="inlineStr">
-        <is>
-          <t>+1.0</t>
-        </is>
-      </c>
+      <c r="E71" s="4" t="inlineStr"/>
+      <c r="F71" s="4" t="inlineStr"/>
       <c r="G71" s="4" t="n">
         <v>211</v>
       </c>
@@ -23701,16 +23157,8 @@
           <t>典範</t>
         </is>
       </c>
-      <c r="E72" s="4" t="inlineStr">
-        <is>
-          <t>19.75</t>
-        </is>
-      </c>
-      <c r="F72" s="4" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
+      <c r="E72" s="4" t="inlineStr"/>
+      <c r="F72" s="4" t="inlineStr"/>
       <c r="G72" s="4" t="n">
         <v>204</v>
       </c>
@@ -23734,16 +23182,8 @@
           <t>英濟</t>
         </is>
       </c>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>31.35</t>
-        </is>
-      </c>
-      <c r="F73" s="4" t="inlineStr">
-        <is>
-          <t>+0.9</t>
-        </is>
-      </c>
+      <c r="E73" s="4" t="inlineStr"/>
+      <c r="F73" s="4" t="inlineStr"/>
       <c r="G73" s="4" t="n">
         <v>202</v>
       </c>
@@ -23767,16 +23207,8 @@
           <t>光譜</t>
         </is>
       </c>
-      <c r="E74" s="4" t="inlineStr">
-        <is>
-          <t>24.20</t>
-        </is>
-      </c>
-      <c r="F74" s="4" t="inlineStr">
-        <is>
-          <t>+0.55</t>
-        </is>
-      </c>
+      <c r="E74" s="4" t="inlineStr"/>
+      <c r="F74" s="4" t="inlineStr"/>
       <c r="G74" s="4" t="n">
         <v>193</v>
       </c>
@@ -23800,16 +23232,8 @@
           <t>茂訊</t>
         </is>
       </c>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>114.50</t>
-        </is>
-      </c>
-      <c r="F75" s="4" t="inlineStr">
-        <is>
-          <t>+3.5</t>
-        </is>
-      </c>
+      <c r="E75" s="4" t="inlineStr"/>
+      <c r="F75" s="4" t="inlineStr"/>
       <c r="G75" s="4" t="n">
         <v>186</v>
       </c>
@@ -23833,16 +23257,8 @@
           <t>中天</t>
         </is>
       </c>
-      <c r="E76" s="4" t="inlineStr">
-        <is>
-          <t>15.20</t>
-        </is>
-      </c>
-      <c r="F76" s="4" t="inlineStr">
-        <is>
-          <t>-0.2</t>
-        </is>
-      </c>
+      <c r="E76" s="4" t="inlineStr"/>
+      <c r="F76" s="4" t="inlineStr"/>
       <c r="G76" s="4" t="n">
         <v>181</v>
       </c>
@@ -23866,16 +23282,8 @@
           <t>宏捷科</t>
         </is>
       </c>
-      <c r="E77" s="4" t="inlineStr">
-        <is>
-          <t>155.00</t>
-        </is>
-      </c>
-      <c r="F77" s="4" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
+      <c r="E77" s="4" t="inlineStr"/>
+      <c r="F77" s="4" t="inlineStr"/>
       <c r="G77" s="4" t="n">
         <v>181</v>
       </c>
@@ -23899,16 +23307,8 @@
           <t>富強鑫</t>
         </is>
       </c>
-      <c r="E78" s="4" t="inlineStr">
-        <is>
-          <t>24.80</t>
-        </is>
-      </c>
-      <c r="F78" s="4" t="inlineStr">
-        <is>
-          <t>-0.3</t>
-        </is>
-      </c>
+      <c r="E78" s="4" t="inlineStr"/>
+      <c r="F78" s="4" t="inlineStr"/>
       <c r="G78" s="4" t="n">
         <v>180</v>
       </c>
@@ -23932,16 +23332,8 @@
           <t>同亨</t>
         </is>
       </c>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t>28.50</t>
-        </is>
-      </c>
-      <c r="F79" s="4" t="inlineStr">
-        <is>
-          <t>+0.45</t>
-        </is>
-      </c>
+      <c r="E79" s="4" t="inlineStr"/>
+      <c r="F79" s="4" t="inlineStr"/>
       <c r="G79" s="4" t="n">
         <v>177</v>
       </c>
@@ -23965,16 +23357,8 @@
           <t>正基</t>
         </is>
       </c>
-      <c r="E80" s="4" t="inlineStr">
-        <is>
-          <t>65.70</t>
-        </is>
-      </c>
-      <c r="F80" s="4" t="inlineStr">
-        <is>
-          <t>+2.2</t>
-        </is>
-      </c>
+      <c r="E80" s="4" t="inlineStr"/>
+      <c r="F80" s="4" t="inlineStr"/>
       <c r="G80" s="4" t="n">
         <v>176</v>
       </c>
@@ -23998,16 +23382,8 @@
           <t>聚和</t>
         </is>
       </c>
-      <c r="E81" s="4" t="inlineStr">
-        <is>
-          <t>40.60</t>
-        </is>
-      </c>
-      <c r="F81" s="4" t="inlineStr">
-        <is>
-          <t>+0.4</t>
-        </is>
-      </c>
+      <c r="E81" s="4" t="inlineStr"/>
+      <c r="F81" s="4" t="inlineStr"/>
       <c r="G81" s="4" t="n">
         <v>172</v>
       </c>
@@ -24031,16 +23407,8 @@
           <t>鈺鎧</t>
         </is>
       </c>
-      <c r="E82" s="4" t="inlineStr">
-        <is>
-          <t>36.35</t>
-        </is>
-      </c>
-      <c r="F82" s="4" t="inlineStr">
-        <is>
-          <t>+3.3</t>
-        </is>
-      </c>
+      <c r="E82" s="4" t="inlineStr"/>
+      <c r="F82" s="4" t="inlineStr"/>
       <c r="G82" s="4" t="n">
         <v>171</v>
       </c>
@@ -24064,16 +23432,8 @@
           <t>力致</t>
         </is>
       </c>
-      <c r="E83" s="4" t="inlineStr">
-        <is>
-          <t>93.20</t>
-        </is>
-      </c>
-      <c r="F83" s="4" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
+      <c r="E83" s="4" t="inlineStr"/>
+      <c r="F83" s="4" t="inlineStr"/>
       <c r="G83" s="4" t="n">
         <v>169</v>
       </c>
@@ -24097,16 +23457,8 @@
           <t>僑威</t>
         </is>
       </c>
-      <c r="E84" s="4" t="inlineStr">
-        <is>
-          <t>57.30</t>
-        </is>
-      </c>
-      <c r="F84" s="4" t="inlineStr">
-        <is>
-          <t>+0.7</t>
-        </is>
-      </c>
+      <c r="E84" s="4" t="inlineStr"/>
+      <c r="F84" s="4" t="inlineStr"/>
       <c r="G84" s="4" t="n">
         <v>168</v>
       </c>
@@ -24130,16 +23482,8 @@
           <t>德晉</t>
         </is>
       </c>
-      <c r="E85" s="4" t="inlineStr">
-        <is>
-          <t>40.85</t>
-        </is>
-      </c>
-      <c r="F85" s="4" t="inlineStr">
-        <is>
-          <t>+1.5</t>
-        </is>
-      </c>
+      <c r="E85" s="4" t="inlineStr"/>
+      <c r="F85" s="4" t="inlineStr"/>
       <c r="G85" s="4" t="n">
         <v>161</v>
       </c>
@@ -24163,16 +23507,8 @@
           <t>類比科</t>
         </is>
       </c>
-      <c r="E86" s="4" t="inlineStr">
-        <is>
-          <t>68.00</t>
-        </is>
-      </c>
-      <c r="F86" s="4" t="inlineStr">
-        <is>
-          <t>+4.8</t>
-        </is>
-      </c>
+      <c r="E86" s="4" t="inlineStr"/>
+      <c r="F86" s="4" t="inlineStr"/>
       <c r="G86" s="4" t="n">
         <v>159</v>
       </c>
@@ -24196,16 +23532,8 @@
           <t>位速</t>
         </is>
       </c>
-      <c r="E87" s="4" t="inlineStr">
-        <is>
-          <t>22.75</t>
-        </is>
-      </c>
-      <c r="F87" s="4" t="inlineStr">
-        <is>
-          <t>+2.05</t>
-        </is>
-      </c>
+      <c r="E87" s="4" t="inlineStr"/>
+      <c r="F87" s="4" t="inlineStr"/>
       <c r="G87" s="4" t="n">
         <v>157</v>
       </c>
@@ -24229,16 +23557,8 @@
           <t>永信建</t>
         </is>
       </c>
-      <c r="E88" s="4" t="inlineStr">
-        <is>
-          <t>50.10</t>
-        </is>
-      </c>
-      <c r="F88" s="4" t="inlineStr">
-        <is>
-          <t>+0.8</t>
-        </is>
-      </c>
+      <c r="E88" s="4" t="inlineStr"/>
+      <c r="F88" s="4" t="inlineStr"/>
       <c r="G88" s="4" t="n">
         <v>156</v>
       </c>
@@ -24262,16 +23582,8 @@
           <t>新復興</t>
         </is>
       </c>
-      <c r="E89" s="4" t="inlineStr">
-        <is>
-          <t>56.90</t>
-        </is>
-      </c>
-      <c r="F89" s="4" t="inlineStr">
-        <is>
-          <t>+1.9</t>
-        </is>
-      </c>
+      <c r="E89" s="4" t="inlineStr"/>
+      <c r="F89" s="4" t="inlineStr"/>
       <c r="G89" s="4" t="n">
         <v>153</v>
       </c>
@@ -24295,16 +23607,8 @@
           <t>譜瑞-KY</t>
         </is>
       </c>
-      <c r="E90" s="4" t="inlineStr">
-        <is>
-          <t>609.00</t>
-        </is>
-      </c>
-      <c r="F90" s="4" t="inlineStr">
-        <is>
-          <t>+35.0</t>
-        </is>
-      </c>
+      <c r="E90" s="4" t="inlineStr"/>
+      <c r="F90" s="4" t="inlineStr"/>
       <c r="G90" s="4" t="n">
         <v>147</v>
       </c>
@@ -24328,16 +23632,8 @@
           <t>高僑</t>
         </is>
       </c>
-      <c r="E91" s="4" t="inlineStr">
-        <is>
-          <t>62.00</t>
-        </is>
-      </c>
-      <c r="F91" s="4" t="inlineStr">
-        <is>
-          <t>+4.0</t>
-        </is>
-      </c>
+      <c r="E91" s="4" t="inlineStr"/>
+      <c r="F91" s="4" t="inlineStr"/>
       <c r="G91" s="4" t="n">
         <v>147</v>
       </c>
@@ -24361,16 +23657,8 @@
           <t>慶騰</t>
         </is>
       </c>
-      <c r="E92" s="4" t="inlineStr">
-        <is>
-          <t>24.05</t>
-        </is>
-      </c>
-      <c r="F92" s="4" t="inlineStr">
-        <is>
-          <t>+0.15</t>
-        </is>
-      </c>
+      <c r="E92" s="4" t="inlineStr"/>
+      <c r="F92" s="4" t="inlineStr"/>
       <c r="G92" s="4" t="n">
         <v>145</v>
       </c>
@@ -24394,16 +23682,8 @@
           <t>森鉅</t>
         </is>
       </c>
-      <c r="E93" s="4" t="inlineStr">
-        <is>
-          <t>45.40</t>
-        </is>
-      </c>
-      <c r="F93" s="4" t="inlineStr">
-        <is>
-          <t>+2.5</t>
-        </is>
-      </c>
+      <c r="E93" s="4" t="inlineStr"/>
+      <c r="F93" s="4" t="inlineStr"/>
       <c r="G93" s="4" t="n">
         <v>144</v>
       </c>
@@ -24427,16 +23707,8 @@
           <t>李洲</t>
         </is>
       </c>
-      <c r="E94" s="4" t="inlineStr">
-        <is>
-          <t>18.65</t>
-        </is>
-      </c>
-      <c r="F94" s="4" t="inlineStr">
-        <is>
-          <t>+0.45</t>
-        </is>
-      </c>
+      <c r="E94" s="4" t="inlineStr"/>
+      <c r="F94" s="4" t="inlineStr"/>
       <c r="G94" s="4" t="n">
         <v>141</v>
       </c>
@@ -24460,16 +23732,8 @@
           <t>伍豐</t>
         </is>
       </c>
-      <c r="E95" s="4" t="inlineStr">
-        <is>
-          <t>23.70</t>
-        </is>
-      </c>
-      <c r="F95" s="4" t="inlineStr">
-        <is>
-          <t>+1.25</t>
-        </is>
-      </c>
+      <c r="E95" s="4" t="inlineStr"/>
+      <c r="F95" s="4" t="inlineStr"/>
       <c r="G95" s="4" t="n">
         <v>141</v>
       </c>
@@ -24493,16 +23757,8 @@
           <t>先進光</t>
         </is>
       </c>
-      <c r="E96" s="4" t="inlineStr">
-        <is>
-          <t>108.00</t>
-        </is>
-      </c>
-      <c r="F96" s="4" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
+      <c r="E96" s="4" t="inlineStr"/>
+      <c r="F96" s="4" t="inlineStr"/>
       <c r="G96" s="4" t="n">
         <v>139</v>
       </c>
@@ -24526,16 +23782,8 @@
           <t>律勝</t>
         </is>
       </c>
-      <c r="E97" s="4" t="inlineStr">
-        <is>
-          <t>34.20</t>
-        </is>
-      </c>
-      <c r="F97" s="4" t="inlineStr">
-        <is>
-          <t>+3.1</t>
-        </is>
-      </c>
+      <c r="E97" s="4" t="inlineStr"/>
+      <c r="F97" s="4" t="inlineStr"/>
       <c r="G97" s="4" t="n">
         <v>138</v>
       </c>
@@ -24559,16 +23807,8 @@
           <t>茂綸</t>
         </is>
       </c>
-      <c r="E98" s="4" t="inlineStr">
-        <is>
-          <t>101.00</t>
-        </is>
-      </c>
-      <c r="F98" s="4" t="inlineStr">
-        <is>
-          <t>+4.1</t>
-        </is>
-      </c>
+      <c r="E98" s="4" t="inlineStr"/>
+      <c r="F98" s="4" t="inlineStr"/>
       <c r="G98" s="4" t="n">
         <v>137</v>
       </c>
@@ -24592,16 +23832,8 @@
           <t>凌陽創新</t>
         </is>
       </c>
-      <c r="E99" s="4" t="inlineStr">
-        <is>
-          <t>160.00</t>
-        </is>
-      </c>
-      <c r="F99" s="4" t="inlineStr">
-        <is>
-          <t>-4.5</t>
-        </is>
-      </c>
+      <c r="E99" s="4" t="inlineStr"/>
+      <c r="F99" s="4" t="inlineStr"/>
       <c r="G99" s="4" t="n">
         <v>136</v>
       </c>
@@ -24625,16 +23857,8 @@
           <t>生華科</t>
         </is>
       </c>
-      <c r="E100" s="4" t="inlineStr">
-        <is>
-          <t>52.00</t>
-        </is>
-      </c>
-      <c r="F100" s="4" t="inlineStr">
-        <is>
-          <t>+2.4</t>
-        </is>
-      </c>
+      <c r="E100" s="4" t="inlineStr"/>
+      <c r="F100" s="4" t="inlineStr"/>
       <c r="G100" s="4" t="n">
         <v>135</v>
       </c>
@@ -24658,16 +23882,8 @@
           <t>泰藝</t>
         </is>
       </c>
-      <c r="E101" s="4" t="inlineStr">
-        <is>
-          <t>52.50</t>
-        </is>
-      </c>
-      <c r="F101" s="4" t="inlineStr">
-        <is>
-          <t>+4.7</t>
-        </is>
-      </c>
+      <c r="E101" s="4" t="inlineStr"/>
+      <c r="F101" s="4" t="inlineStr"/>
       <c r="G101" s="4" t="n">
         <v>135</v>
       </c>
@@ -24691,16 +23907,8 @@
           <t>邦泰</t>
         </is>
       </c>
-      <c r="E102" s="4" t="inlineStr">
-        <is>
-          <t>18.80</t>
-        </is>
-      </c>
-      <c r="F102" s="4" t="inlineStr">
-        <is>
-          <t>+0.25</t>
-        </is>
-      </c>
+      <c r="E102" s="4" t="inlineStr"/>
+      <c r="F102" s="4" t="inlineStr"/>
       <c r="G102" s="4" t="n">
         <v>135</v>
       </c>
@@ -24724,16 +23932,8 @@
           <t>晶焱</t>
         </is>
       </c>
-      <c r="E103" s="4" t="inlineStr">
-        <is>
-          <t>81.80</t>
-        </is>
-      </c>
-      <c r="F103" s="4" t="inlineStr">
-        <is>
-          <t>+0.9</t>
-        </is>
-      </c>
+      <c r="E103" s="4" t="inlineStr"/>
+      <c r="F103" s="4" t="inlineStr"/>
       <c r="G103" s="4" t="n">
         <v>133</v>
       </c>
@@ -24834,16 +24034,8 @@
           <t>富喬</t>
         </is>
       </c>
-      <c r="E109" s="4" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
-      </c>
-      <c r="F109" s="4" t="inlineStr">
-        <is>
-          <t>-3.5</t>
-        </is>
-      </c>
+      <c r="E109" s="4" t="inlineStr"/>
+      <c r="F109" s="4" t="inlineStr"/>
       <c r="G109" s="4" t="n">
         <v>-18009</v>
       </c>
@@ -24867,16 +24059,8 @@
           <t>湧德</t>
         </is>
       </c>
-      <c r="E110" s="4" t="inlineStr">
-        <is>
-          <t>128.00</t>
-        </is>
-      </c>
-      <c r="F110" s="4" t="inlineStr">
-        <is>
-          <t>-14.0</t>
-        </is>
-      </c>
+      <c r="E110" s="4" t="inlineStr"/>
+      <c r="F110" s="4" t="inlineStr"/>
       <c r="G110" s="4" t="n">
         <v>-6303</v>
       </c>
@@ -24900,16 +24084,8 @@
           <t>擎亞</t>
         </is>
       </c>
-      <c r="E111" s="4" t="inlineStr">
-        <is>
-          <t>95.80</t>
-        </is>
-      </c>
-      <c r="F111" s="4" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
+      <c r="E111" s="4" t="inlineStr"/>
+      <c r="F111" s="4" t="inlineStr"/>
       <c r="G111" s="4" t="n">
         <v>-3692</v>
       </c>
@@ -24933,16 +24109,8 @@
           <t>鈺創</t>
         </is>
       </c>
-      <c r="E112" s="4" t="inlineStr">
-        <is>
-          <t>77.30</t>
-        </is>
-      </c>
-      <c r="F112" s="4" t="inlineStr">
-        <is>
-          <t>-1.2</t>
-        </is>
-      </c>
+      <c r="E112" s="4" t="inlineStr"/>
+      <c r="F112" s="4" t="inlineStr"/>
       <c r="G112" s="4" t="n">
         <v>-3647</v>
       </c>
@@ -24966,16 +24134,8 @@
           <t>均豪</t>
         </is>
       </c>
-      <c r="E113" s="4" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
-      </c>
-      <c r="F113" s="4" t="inlineStr">
-        <is>
-          <t>-4.0</t>
-        </is>
-      </c>
+      <c r="E113" s="4" t="inlineStr"/>
+      <c r="F113" s="4" t="inlineStr"/>
       <c r="G113" s="4" t="n">
         <v>-1530</v>
       </c>
@@ -24999,16 +24159,8 @@
           <t>精材</t>
         </is>
       </c>
-      <c r="E114" s="4" t="inlineStr">
-        <is>
-          <t>206.00</t>
-        </is>
-      </c>
-      <c r="F114" s="4" t="inlineStr">
-        <is>
-          <t>+7.0</t>
-        </is>
-      </c>
+      <c r="E114" s="4" t="inlineStr"/>
+      <c r="F114" s="4" t="inlineStr"/>
       <c r="G114" s="4" t="n">
         <v>-1462</v>
       </c>
@@ -25032,16 +24184,8 @@
           <t>威剛</t>
         </is>
       </c>
-      <c r="E115" s="4" t="inlineStr">
-        <is>
-          <t>461.50</t>
-        </is>
-      </c>
-      <c r="F115" s="4" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
+      <c r="E115" s="4" t="inlineStr"/>
+      <c r="F115" s="4" t="inlineStr"/>
       <c r="G115" s="4" t="n">
         <v>-1450</v>
       </c>
@@ -25065,16 +24209,8 @@
           <t>陽程</t>
         </is>
       </c>
-      <c r="E116" s="4" t="inlineStr">
-        <is>
-          <t>97.30</t>
-        </is>
-      </c>
-      <c r="F116" s="4" t="inlineStr">
-        <is>
-          <t>-1.6</t>
-        </is>
-      </c>
+      <c r="E116" s="4" t="inlineStr"/>
+      <c r="F116" s="4" t="inlineStr"/>
       <c r="G116" s="4" t="n">
         <v>-1425</v>
       </c>
@@ -25098,16 +24234,8 @@
           <t>漢磊</t>
         </is>
       </c>
-      <c r="E117" s="4" t="inlineStr">
-        <is>
-          <t>74.70</t>
-        </is>
-      </c>
-      <c r="F117" s="4" t="inlineStr">
-        <is>
-          <t>+1.6</t>
-        </is>
-      </c>
+      <c r="E117" s="4" t="inlineStr"/>
+      <c r="F117" s="4" t="inlineStr"/>
       <c r="G117" s="4" t="n">
         <v>-1371</v>
       </c>
@@ -25131,16 +24259,8 @@
           <t>建榮</t>
         </is>
       </c>
-      <c r="E118" s="4" t="inlineStr">
-        <is>
-          <t>116.50</t>
-        </is>
-      </c>
-      <c r="F118" s="4" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
+      <c r="E118" s="4" t="inlineStr"/>
+      <c r="F118" s="4" t="inlineStr"/>
       <c r="G118" s="4" t="n">
         <v>-1330</v>
       </c>
@@ -25164,16 +24284,8 @@
           <t>雷科</t>
         </is>
       </c>
-      <c r="E119" s="4" t="inlineStr">
-        <is>
-          <t>69.00</t>
-        </is>
-      </c>
-      <c r="F119" s="4" t="inlineStr">
-        <is>
-          <t>+0.3</t>
-        </is>
-      </c>
+      <c r="E119" s="4" t="inlineStr"/>
+      <c r="F119" s="4" t="inlineStr"/>
       <c r="G119" s="4" t="n">
         <v>-1305</v>
       </c>
@@ -25197,16 +24309,8 @@
           <t>順達</t>
         </is>
       </c>
-      <c r="E120" s="4" t="inlineStr">
-        <is>
-          <t>384.00</t>
-        </is>
-      </c>
-      <c r="F120" s="4" t="inlineStr">
-        <is>
-          <t>+9.5</t>
-        </is>
-      </c>
+      <c r="E120" s="4" t="inlineStr"/>
+      <c r="F120" s="4" t="inlineStr"/>
       <c r="G120" s="4" t="n">
         <v>-1224</v>
       </c>
@@ -25230,16 +24334,8 @@
           <t>雙鴻</t>
         </is>
       </c>
-      <c r="E121" s="4" t="inlineStr">
-        <is>
-          <t>1070.00</t>
-        </is>
-      </c>
-      <c r="F121" s="4" t="inlineStr">
-        <is>
-          <t>-35.0</t>
-        </is>
-      </c>
+      <c r="E121" s="4" t="inlineStr"/>
+      <c r="F121" s="4" t="inlineStr"/>
       <c r="G121" s="4" t="n">
         <v>-1133</v>
       </c>
@@ -25263,16 +24359,8 @@
           <t>華星光</t>
         </is>
       </c>
-      <c r="E122" s="4" t="inlineStr">
-        <is>
-          <t>700.00</t>
-        </is>
-      </c>
-      <c r="F122" s="4" t="inlineStr">
-        <is>
-          <t>-3.0</t>
-        </is>
-      </c>
+      <c r="E122" s="4" t="inlineStr"/>
+      <c r="F122" s="4" t="inlineStr"/>
       <c r="G122" s="4" t="n">
         <v>-1063</v>
       </c>
@@ -25296,16 +24384,8 @@
           <t>光頡</t>
         </is>
       </c>
-      <c r="E123" s="4" t="inlineStr">
-        <is>
-          <t>59.40</t>
-        </is>
-      </c>
-      <c r="F123" s="4" t="inlineStr">
-        <is>
-          <t>+5.4</t>
-        </is>
-      </c>
+      <c r="E123" s="4" t="inlineStr"/>
+      <c r="F123" s="4" t="inlineStr"/>
       <c r="G123" s="4" t="n">
         <v>-966</v>
       </c>
@@ -25329,16 +24409,8 @@
           <t>新盛力</t>
         </is>
       </c>
-      <c r="E124" s="4" t="inlineStr">
-        <is>
-          <t>164.00</t>
-        </is>
-      </c>
-      <c r="F124" s="4" t="inlineStr">
-        <is>
-          <t>-2.5</t>
-        </is>
-      </c>
+      <c r="E124" s="4" t="inlineStr"/>
+      <c r="F124" s="4" t="inlineStr"/>
       <c r="G124" s="4" t="n">
         <v>-873</v>
       </c>
@@ -25362,16 +24434,8 @@
           <t>安國</t>
         </is>
       </c>
-      <c r="E125" s="4" t="inlineStr">
-        <is>
-          <t>107.00</t>
-        </is>
-      </c>
-      <c r="F125" s="4" t="inlineStr">
-        <is>
-          <t>-4.5</t>
-        </is>
-      </c>
+      <c r="E125" s="4" t="inlineStr"/>
+      <c r="F125" s="4" t="inlineStr"/>
       <c r="G125" s="4" t="n">
         <v>-866</v>
       </c>
@@ -25395,16 +24459,8 @@
           <t>方土昶</t>
         </is>
       </c>
-      <c r="E126" s="4" t="inlineStr">
-        <is>
-          <t>43.40</t>
-        </is>
-      </c>
-      <c r="F126" s="4" t="inlineStr">
-        <is>
-          <t>-0.7</t>
-        </is>
-      </c>
+      <c r="E126" s="4" t="inlineStr"/>
+      <c r="F126" s="4" t="inlineStr"/>
       <c r="G126" s="4" t="n">
         <v>-827</v>
       </c>
@@ -25428,16 +24484,8 @@
           <t>鉅橡</t>
         </is>
       </c>
-      <c r="E127" s="4" t="inlineStr">
-        <is>
-          <t>81.20</t>
-        </is>
-      </c>
-      <c r="F127" s="4" t="inlineStr">
-        <is>
-          <t>-3.3</t>
-        </is>
-      </c>
+      <c r="E127" s="4" t="inlineStr"/>
+      <c r="F127" s="4" t="inlineStr"/>
       <c r="G127" s="4" t="n">
         <v>-812</v>
       </c>
@@ -25461,16 +24509,8 @@
           <t>鈊象</t>
         </is>
       </c>
-      <c r="E128" s="4" t="inlineStr">
-        <is>
-          <t>720.00</t>
-        </is>
-      </c>
-      <c r="F128" s="4" t="inlineStr">
-        <is>
-          <t>-11.0</t>
-        </is>
-      </c>
+      <c r="E128" s="4" t="inlineStr"/>
+      <c r="F128" s="4" t="inlineStr"/>
       <c r="G128" s="4" t="n">
         <v>-810</v>
       </c>
@@ -25494,16 +24534,8 @@
           <t>佶優</t>
         </is>
       </c>
-      <c r="E129" s="4" t="inlineStr">
-        <is>
-          <t>32.95</t>
-        </is>
-      </c>
-      <c r="F129" s="4" t="inlineStr">
-        <is>
-          <t>-0.65</t>
-        </is>
-      </c>
+      <c r="E129" s="4" t="inlineStr"/>
+      <c r="F129" s="4" t="inlineStr"/>
       <c r="G129" s="4" t="n">
         <v>-705</v>
       </c>
@@ -25527,16 +24559,8 @@
           <t>環宇-KY</t>
         </is>
       </c>
-      <c r="E130" s="4" t="inlineStr">
-        <is>
-          <t>690.00</t>
-        </is>
-      </c>
-      <c r="F130" s="4" t="inlineStr">
-        <is>
-          <t>-35.0</t>
-        </is>
-      </c>
+      <c r="E130" s="4" t="inlineStr"/>
+      <c r="F130" s="4" t="inlineStr"/>
       <c r="G130" s="4" t="n">
         <v>-659</v>
       </c>
@@ -25560,16 +24584,8 @@
           <t>家登</t>
         </is>
       </c>
-      <c r="E131" s="4" t="inlineStr">
-        <is>
-          <t>585.00</t>
-        </is>
-      </c>
-      <c r="F131" s="4" t="inlineStr">
-        <is>
-          <t>+4.0</t>
-        </is>
-      </c>
+      <c r="E131" s="4" t="inlineStr"/>
+      <c r="F131" s="4" t="inlineStr"/>
       <c r="G131" s="4" t="n">
         <v>-600</v>
       </c>
@@ -25593,16 +24609,8 @@
           <t>胡連</t>
         </is>
       </c>
-      <c r="E132" s="4" t="inlineStr">
-        <is>
-          <t>124.00</t>
-        </is>
-      </c>
-      <c r="F132" s="4" t="inlineStr">
-        <is>
-          <t>+8.0</t>
-        </is>
-      </c>
+      <c r="E132" s="4" t="inlineStr"/>
+      <c r="F132" s="4" t="inlineStr"/>
       <c r="G132" s="4" t="n">
         <v>-596</v>
       </c>
@@ -25626,16 +24634,8 @@
           <t>華義*</t>
         </is>
       </c>
-      <c r="E133" s="4" t="inlineStr">
-        <is>
-          <t>40.55</t>
-        </is>
-      </c>
-      <c r="F133" s="4" t="inlineStr">
-        <is>
-          <t>-2.95</t>
-        </is>
-      </c>
+      <c r="E133" s="4" t="inlineStr"/>
+      <c r="F133" s="4" t="inlineStr"/>
       <c r="G133" s="4" t="n">
         <v>-564</v>
       </c>
@@ -25659,16 +24659,8 @@
           <t>世界</t>
         </is>
       </c>
-      <c r="E134" s="4" t="inlineStr">
-        <is>
-          <t>185.50</t>
-        </is>
-      </c>
-      <c r="F134" s="4" t="inlineStr">
-        <is>
-          <t>+16.5</t>
-        </is>
-      </c>
+      <c r="E134" s="4" t="inlineStr"/>
+      <c r="F134" s="4" t="inlineStr"/>
       <c r="G134" s="4" t="n">
         <v>-535</v>
       </c>
@@ -25692,16 +24684,8 @@
           <t>品安</t>
         </is>
       </c>
-      <c r="E135" s="4" t="inlineStr">
-        <is>
-          <t>55.10</t>
-        </is>
-      </c>
-      <c r="F135" s="4" t="inlineStr">
-        <is>
-          <t>+0.9</t>
-        </is>
-      </c>
+      <c r="E135" s="4" t="inlineStr"/>
+      <c r="F135" s="4" t="inlineStr"/>
       <c r="G135" s="4" t="n">
         <v>-524</v>
       </c>
@@ -25725,16 +24709,8 @@
           <t>信昌電</t>
         </is>
       </c>
-      <c r="E136" s="4" t="inlineStr">
-        <is>
-          <t>111.00</t>
-        </is>
-      </c>
-      <c r="F136" s="4" t="inlineStr">
-        <is>
-          <t>+10.0</t>
-        </is>
-      </c>
+      <c r="E136" s="4" t="inlineStr"/>
+      <c r="F136" s="4" t="inlineStr"/>
       <c r="G136" s="4" t="n">
         <v>-519</v>
       </c>
@@ -25758,16 +24734,8 @@
           <t>東捷</t>
         </is>
       </c>
-      <c r="E137" s="4" t="inlineStr">
-        <is>
-          <t>108.00</t>
-        </is>
-      </c>
-      <c r="F137" s="4" t="inlineStr">
-        <is>
-          <t>-4.5</t>
-        </is>
-      </c>
+      <c r="E137" s="4" t="inlineStr"/>
+      <c r="F137" s="4" t="inlineStr"/>
       <c r="G137" s="4" t="n">
         <v>-510</v>
       </c>
@@ -25791,16 +24759,8 @@
           <t>今展科</t>
         </is>
       </c>
-      <c r="E138" s="4" t="inlineStr">
-        <is>
-          <t>43.60</t>
-        </is>
-      </c>
-      <c r="F138" s="4" t="inlineStr">
-        <is>
-          <t>+1.35</t>
-        </is>
-      </c>
+      <c r="E138" s="4" t="inlineStr"/>
+      <c r="F138" s="4" t="inlineStr"/>
       <c r="G138" s="4" t="n">
         <v>-502</v>
       </c>
@@ -25824,16 +24784,8 @@
           <t>光洋科</t>
         </is>
       </c>
-      <c r="E139" s="4" t="inlineStr">
-        <is>
-          <t>185.00</t>
-        </is>
-      </c>
-      <c r="F139" s="4" t="inlineStr">
-        <is>
-          <t>+16.5</t>
-        </is>
-      </c>
+      <c r="E139" s="4" t="inlineStr"/>
+      <c r="F139" s="4" t="inlineStr"/>
       <c r="G139" s="4" t="n">
         <v>-495</v>
       </c>
@@ -25857,16 +24809,8 @@
           <t>德宏</t>
         </is>
       </c>
-      <c r="E140" s="4" t="inlineStr">
-        <is>
-          <t>348.00</t>
-        </is>
-      </c>
-      <c r="F140" s="4" t="inlineStr">
-        <is>
-          <t>-30.5</t>
-        </is>
-      </c>
+      <c r="E140" s="4" t="inlineStr"/>
+      <c r="F140" s="4" t="inlineStr"/>
       <c r="G140" s="4" t="n">
         <v>-432</v>
       </c>
@@ -25890,16 +24834,8 @@
           <t>松上</t>
         </is>
       </c>
-      <c r="E141" s="4" t="inlineStr">
-        <is>
-          <t>19.60</t>
-        </is>
-      </c>
-      <c r="F141" s="4" t="inlineStr">
-        <is>
-          <t>-1.4</t>
-        </is>
-      </c>
+      <c r="E141" s="4" t="inlineStr"/>
+      <c r="F141" s="4" t="inlineStr"/>
       <c r="G141" s="4" t="n">
         <v>-432</v>
       </c>
@@ -25923,16 +24859,8 @@
           <t>合一</t>
         </is>
       </c>
-      <c r="E142" s="4" t="inlineStr">
-        <is>
-          <t>52.90</t>
-        </is>
-      </c>
-      <c r="F142" s="4" t="inlineStr">
-        <is>
-          <t>-1.2</t>
-        </is>
-      </c>
+      <c r="E142" s="4" t="inlineStr"/>
+      <c r="F142" s="4" t="inlineStr"/>
       <c r="G142" s="4" t="n">
         <v>-426</v>
       </c>
@@ -25956,16 +24884,8 @@
           <t>美琪瑪</t>
         </is>
       </c>
-      <c r="E143" s="4" t="inlineStr">
-        <is>
-          <t>93.20</t>
-        </is>
-      </c>
-      <c r="F143" s="4" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
+      <c r="E143" s="4" t="inlineStr"/>
+      <c r="F143" s="4" t="inlineStr"/>
       <c r="G143" s="4" t="n">
         <v>-424</v>
       </c>
@@ -25989,16 +24909,8 @@
           <t>高鋒</t>
         </is>
       </c>
-      <c r="E144" s="4" t="inlineStr">
-        <is>
-          <t>46.95</t>
-        </is>
-      </c>
-      <c r="F144" s="4" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
+      <c r="E144" s="4" t="inlineStr"/>
+      <c r="F144" s="4" t="inlineStr"/>
       <c r="G144" s="4" t="n">
         <v>-421</v>
       </c>
@@ -26022,16 +24934,8 @@
           <t>聖暉*</t>
         </is>
       </c>
-      <c r="E145" s="4" t="inlineStr">
-        <is>
-          <t>861.00</t>
-        </is>
-      </c>
-      <c r="F145" s="4" t="inlineStr">
-        <is>
-          <t>-16.0</t>
-        </is>
-      </c>
+      <c r="E145" s="4" t="inlineStr"/>
+      <c r="F145" s="4" t="inlineStr"/>
       <c r="G145" s="4" t="n">
         <v>-386</v>
       </c>
@@ -26055,16 +24959,8 @@
           <t>精湛</t>
         </is>
       </c>
-      <c r="E146" s="4" t="inlineStr">
-        <is>
-          <t>72.60</t>
-        </is>
-      </c>
-      <c r="F146" s="4" t="inlineStr">
-        <is>
-          <t>+6.6</t>
-        </is>
-      </c>
+      <c r="E146" s="4" t="inlineStr"/>
+      <c r="F146" s="4" t="inlineStr"/>
       <c r="G146" s="4" t="n">
         <v>-376</v>
       </c>
@@ -26088,16 +24984,8 @@
           <t>漢科</t>
         </is>
       </c>
-      <c r="E147" s="4" t="inlineStr">
-        <is>
-          <t>144.00</t>
-        </is>
-      </c>
-      <c r="F147" s="4" t="inlineStr">
-        <is>
-          <t>-2.5</t>
-        </is>
-      </c>
+      <c r="E147" s="4" t="inlineStr"/>
+      <c r="F147" s="4" t="inlineStr"/>
       <c r="G147" s="4" t="n">
         <v>-370</v>
       </c>
@@ -26121,16 +25009,8 @@
           <t>智通*</t>
         </is>
       </c>
-      <c r="E148" s="4" t="inlineStr">
-        <is>
-          <t>91.50</t>
-        </is>
-      </c>
-      <c r="F148" s="4" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
+      <c r="E148" s="4" t="inlineStr"/>
+      <c r="F148" s="4" t="inlineStr"/>
       <c r="G148" s="4" t="n">
         <v>-367</v>
       </c>
@@ -26154,16 +25034,8 @@
           <t>台嘉碩</t>
         </is>
       </c>
-      <c r="E149" s="4" t="inlineStr">
-        <is>
-          <t>48.20</t>
-        </is>
-      </c>
-      <c r="F149" s="4" t="inlineStr">
-        <is>
-          <t>+4.3</t>
-        </is>
-      </c>
+      <c r="E149" s="4" t="inlineStr"/>
+      <c r="F149" s="4" t="inlineStr"/>
       <c r="G149" s="4" t="n">
         <v>-366</v>
       </c>
@@ -26187,16 +25059,8 @@
           <t>欣銓</t>
         </is>
       </c>
-      <c r="E150" s="4" t="inlineStr">
-        <is>
-          <t>248.50</t>
-        </is>
-      </c>
-      <c r="F150" s="4" t="inlineStr">
-        <is>
-          <t>+22.5</t>
-        </is>
-      </c>
+      <c r="E150" s="4" t="inlineStr"/>
+      <c r="F150" s="4" t="inlineStr"/>
       <c r="G150" s="4" t="n">
         <v>-330</v>
       </c>
@@ -26220,16 +25084,8 @@
           <t>高技</t>
         </is>
       </c>
-      <c r="E151" s="4" t="inlineStr">
-        <is>
-          <t>407.00</t>
-        </is>
-      </c>
-      <c r="F151" s="4" t="inlineStr">
-        <is>
-          <t>+1.0</t>
-        </is>
-      </c>
+      <c r="E151" s="4" t="inlineStr"/>
+      <c r="F151" s="4" t="inlineStr"/>
       <c r="G151" s="4" t="n">
         <v>-328</v>
       </c>
@@ -26253,16 +25109,8 @@
           <t>萬泰科</t>
         </is>
       </c>
-      <c r="E152" s="4" t="inlineStr">
-        <is>
-          <t>74.70</t>
-        </is>
-      </c>
-      <c r="F152" s="4" t="inlineStr">
-        <is>
-          <t>-0.3</t>
-        </is>
-      </c>
+      <c r="E152" s="4" t="inlineStr"/>
+      <c r="F152" s="4" t="inlineStr"/>
       <c r="G152" s="4" t="n">
         <v>-324</v>
       </c>
@@ -26286,16 +25134,8 @@
           <t>安碁</t>
         </is>
       </c>
-      <c r="E153" s="4" t="inlineStr">
-        <is>
-          <t>39.40</t>
-        </is>
-      </c>
-      <c r="F153" s="4" t="inlineStr">
-        <is>
-          <t>-1.9</t>
-        </is>
-      </c>
+      <c r="E153" s="4" t="inlineStr"/>
+      <c r="F153" s="4" t="inlineStr"/>
       <c r="G153" s="4" t="n">
         <v>-294</v>
       </c>
@@ -26319,16 +25159,8 @@
           <t>宜特</t>
         </is>
       </c>
-      <c r="E154" s="4" t="inlineStr">
-        <is>
-          <t>179.00</t>
-        </is>
-      </c>
-      <c r="F154" s="4" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
+      <c r="E154" s="4" t="inlineStr"/>
+      <c r="F154" s="4" t="inlineStr"/>
       <c r="G154" s="4" t="n">
         <v>-289</v>
       </c>
@@ -26352,16 +25184,8 @@
           <t>台星科</t>
         </is>
       </c>
-      <c r="E155" s="4" t="inlineStr">
-        <is>
-          <t>185.00</t>
-        </is>
-      </c>
-      <c r="F155" s="4" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
+      <c r="E155" s="4" t="inlineStr"/>
+      <c r="F155" s="4" t="inlineStr"/>
       <c r="G155" s="4" t="n">
         <v>-272</v>
       </c>
@@ -26385,16 +25209,8 @@
           <t>東浦</t>
         </is>
       </c>
-      <c r="E156" s="4" t="inlineStr">
-        <is>
-          <t>47.05</t>
-        </is>
-      </c>
-      <c r="F156" s="4" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
+      <c r="E156" s="4" t="inlineStr"/>
+      <c r="F156" s="4" t="inlineStr"/>
       <c r="G156" s="4" t="n">
         <v>-268</v>
       </c>
@@ -26418,16 +25234,8 @@
           <t>新漢</t>
         </is>
       </c>
-      <c r="E157" s="4" t="inlineStr">
-        <is>
-          <t>73.30</t>
-        </is>
-      </c>
-      <c r="F157" s="4" t="inlineStr">
-        <is>
-          <t>-0.7</t>
-        </is>
-      </c>
+      <c r="E157" s="4" t="inlineStr"/>
+      <c r="F157" s="4" t="inlineStr"/>
       <c r="G157" s="4" t="n">
         <v>-268</v>
       </c>
@@ -26451,16 +25259,8 @@
           <t>華宏</t>
         </is>
       </c>
-      <c r="E158" s="4" t="inlineStr">
-        <is>
-          <t>68.70</t>
-        </is>
-      </c>
-      <c r="F158" s="4" t="inlineStr">
-        <is>
-          <t>-1.2</t>
-        </is>
-      </c>
+      <c r="E158" s="4" t="inlineStr"/>
+      <c r="F158" s="4" t="inlineStr"/>
       <c r="G158" s="4" t="n">
         <v>-267</v>
       </c>

--- a/StockInfo/otc_analysis_result.xlsx
+++ b/StockInfo/otc_analysis_result.xlsx
@@ -5228,8 +5228,16 @@
           <t>方土昶</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>48.10</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>+4.35</t>
+        </is>
+      </c>
       <c r="G4" s="4" t="n">
         <v>6764</v>
       </c>
@@ -5268,8 +5276,16 @@
           <t>富喬</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr"/>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>107.00</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>+5.5</t>
+        </is>
+      </c>
       <c r="G5" s="4" t="n">
         <v>5944</v>
       </c>
@@ -5296,8 +5312,16 @@
           <t>穩懋</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr"/>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>531.00</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>+48.0</t>
+        </is>
+      </c>
       <c r="G6" s="4" t="n">
         <v>5434</v>
       </c>
@@ -5324,8 +5348,16 @@
           <t>合晶</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr"/>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>69.90</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>+6.3</t>
+        </is>
+      </c>
       <c r="G7" s="4" t="n">
         <v>4912</v>
       </c>
@@ -5356,8 +5388,16 @@
           <t>擎亞</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr"/>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>118.50</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>+10.5</t>
+        </is>
+      </c>
       <c r="G8" s="4" t="n">
         <v>4477</v>
       </c>
@@ -5384,8 +5424,16 @@
           <t>漢磊</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr"/>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>83.50</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>+3.5</t>
+        </is>
+      </c>
       <c r="G9" s="4" t="n">
         <v>3732</v>
       </c>
@@ -5412,8 +5460,16 @@
           <t>系統電</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr"/>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>69.30</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>+1.8</t>
+        </is>
+      </c>
       <c r="G10" s="4" t="n">
         <v>3515</v>
       </c>
@@ -5440,8 +5496,16 @@
           <t>宏捷科</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr"/>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>159.50</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>+10.5</t>
+        </is>
+      </c>
       <c r="G11" s="4" t="n">
         <v>2826</v>
       </c>
@@ -5472,8 +5536,16 @@
           <t>安可</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr"/>
-      <c r="F12" s="4" t="inlineStr"/>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>47.55</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>+4.3</t>
+        </is>
+      </c>
       <c r="G12" s="4" t="n">
         <v>2794</v>
       </c>
@@ -5508,8 +5580,16 @@
           <t>台嘉碩</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr"/>
-      <c r="F13" s="4" t="inlineStr"/>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>56.40</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>+5.1</t>
+        </is>
+      </c>
       <c r="G13" s="4" t="n">
         <v>2532</v>
       </c>
@@ -5544,8 +5624,16 @@
           <t>新盛力</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr"/>
-      <c r="F14" s="4" t="inlineStr"/>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>212.00</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>+19.0</t>
+        </is>
+      </c>
       <c r="G14" s="4" t="n">
         <v>2247</v>
       </c>
@@ -5584,8 +5672,16 @@
           <t>立敦</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr"/>
-      <c r="F15" s="4" t="inlineStr"/>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>88.30</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>+3.1</t>
+        </is>
+      </c>
       <c r="G15" s="4" t="n">
         <v>2088</v>
       </c>
@@ -5616,8 +5712,16 @@
           <t>佶優</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr"/>
-      <c r="F16" s="4" t="inlineStr"/>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>34.60</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>+1.8</t>
+        </is>
+      </c>
       <c r="G16" s="4" t="n">
         <v>1937</v>
       </c>
@@ -5648,8 +5752,16 @@
           <t>台星科</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="4" t="inlineStr"/>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>186.00</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>+8.5</t>
+        </is>
+      </c>
       <c r="G17" s="4" t="n">
         <v>1744</v>
       </c>
@@ -5684,8 +5796,16 @@
           <t>高鋒</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr"/>
-      <c r="F18" s="4" t="inlineStr"/>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>49.60</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>+2.0</t>
+        </is>
+      </c>
       <c r="G18" s="4" t="n">
         <v>1709</v>
       </c>
@@ -5724,8 +5844,16 @@
           <t>能率</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr"/>
-      <c r="F19" s="4" t="inlineStr"/>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>44.05</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>+2.5</t>
+        </is>
+      </c>
       <c r="G19" s="4" t="n">
         <v>1674</v>
       </c>
@@ -5764,8 +5892,16 @@
           <t>茂迪</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr"/>
-      <c r="F20" s="4" t="inlineStr"/>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>29.40</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>+1.05</t>
+        </is>
+      </c>
       <c r="G20" s="4" t="n">
         <v>1671</v>
       </c>
@@ -5796,8 +5932,16 @@
           <t>金居</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr"/>
-      <c r="F21" s="4" t="inlineStr"/>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>522.00</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>+24.0</t>
+        </is>
+      </c>
       <c r="G21" s="4" t="n">
         <v>1667</v>
       </c>
@@ -5828,8 +5972,16 @@
           <t>協易機</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr"/>
-      <c r="F22" s="4" t="inlineStr"/>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>33.40</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>+0.7</t>
+        </is>
+      </c>
       <c r="G22" s="4" t="n">
         <v>1555</v>
       </c>
@@ -5856,8 +6008,16 @@
           <t>佳邦</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr"/>
-      <c r="F23" s="4" t="inlineStr"/>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>102.50</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>+9.1</t>
+        </is>
+      </c>
       <c r="G23" s="4" t="n">
         <v>1348</v>
       </c>
@@ -5888,8 +6048,16 @@
           <t>中光電</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr"/>
-      <c r="F24" s="4" t="inlineStr"/>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>72.10</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>+0.2</t>
+        </is>
+      </c>
       <c r="G24" s="4" t="n">
         <v>1310</v>
       </c>
@@ -5920,8 +6088,16 @@
           <t>臺慶科</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr"/>
-      <c r="F25" s="4" t="inlineStr"/>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>279.00</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>+25.0</t>
+        </is>
+      </c>
       <c r="G25" s="4" t="n">
         <v>1299</v>
       </c>
@@ -5948,8 +6124,16 @@
           <t>加高</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr"/>
-      <c r="F26" s="4" t="inlineStr"/>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>41.35</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>+3.75</t>
+        </is>
+      </c>
       <c r="G26" s="4" t="n">
         <v>1244</v>
       </c>
@@ -5984,8 +6168,16 @@
           <t>廣明</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr"/>
-      <c r="F27" s="4" t="inlineStr"/>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>86.40</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>+2.9</t>
+        </is>
+      </c>
       <c r="G27" s="4" t="n">
         <v>1230</v>
       </c>
@@ -6012,8 +6204,16 @@
           <t>聯光通</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr"/>
-      <c r="F28" s="4" t="inlineStr"/>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>47.55</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>+2.25</t>
+        </is>
+      </c>
       <c r="G28" s="4" t="n">
         <v>1212</v>
       </c>
@@ -6040,8 +6240,16 @@
           <t>璟德</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr"/>
-      <c r="F29" s="4" t="inlineStr"/>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>181.50</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>+9.5</t>
+        </is>
+      </c>
       <c r="G29" s="4" t="n">
         <v>1185</v>
       </c>
@@ -6076,8 +6284,16 @@
           <t>華容</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr"/>
-      <c r="F30" s="4" t="inlineStr"/>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>35.50</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>+1.55</t>
+        </is>
+      </c>
       <c r="G30" s="4" t="n">
         <v>1105</v>
       </c>
@@ -6108,8 +6324,16 @@
           <t>順達</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr"/>
-      <c r="F31" s="4" t="inlineStr"/>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>388.00</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>+35.0</t>
+        </is>
+      </c>
       <c r="G31" s="4" t="n">
         <v>1066</v>
       </c>
@@ -6136,8 +6360,16 @@
           <t>環宇-KY</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr"/>
-      <c r="F32" s="4" t="inlineStr"/>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>814.00</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>+74.0</t>
+        </is>
+      </c>
       <c r="G32" s="4" t="n">
         <v>1055</v>
       </c>
@@ -6168,8 +6400,16 @@
           <t>創惟</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr"/>
-      <c r="F33" s="4" t="inlineStr"/>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>103.00</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>+1.5</t>
+        </is>
+      </c>
       <c r="G33" s="4" t="n">
         <v>898</v>
       </c>
@@ -6196,8 +6436,16 @@
           <t>千如</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr"/>
-      <c r="F34" s="4" t="inlineStr"/>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>53.00</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>+4.75</t>
+        </is>
+      </c>
       <c r="G34" s="4" t="n">
         <v>857</v>
       </c>
@@ -6228,8 +6476,16 @@
           <t>久元</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr"/>
-      <c r="F35" s="4" t="inlineStr"/>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>124.00</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>+11.0</t>
+        </is>
+      </c>
       <c r="G35" s="4" t="n">
         <v>857</v>
       </c>
@@ -6260,8 +6516,16 @@
           <t>茂綸</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr"/>
-      <c r="F36" s="4" t="inlineStr"/>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>128.00</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>+11.5</t>
+        </is>
+      </c>
       <c r="G36" s="4" t="n">
         <v>843</v>
       </c>
@@ -6296,8 +6560,16 @@
           <t>加百裕</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr"/>
-      <c r="F37" s="4" t="inlineStr"/>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>36.70</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>+1.3</t>
+        </is>
+      </c>
       <c r="G37" s="4" t="n">
         <v>834</v>
       </c>
@@ -6332,8 +6604,16 @@
           <t>越峰</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr"/>
-      <c r="F38" s="4" t="inlineStr"/>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>39.55</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>+2.2</t>
+        </is>
+      </c>
       <c r="G38" s="4" t="n">
         <v>830</v>
       </c>
@@ -6368,8 +6648,16 @@
           <t>聚和</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr"/>
-      <c r="F39" s="4" t="inlineStr"/>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>50.10</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>+0.95</t>
+        </is>
+      </c>
       <c r="G39" s="4" t="n">
         <v>815</v>
       </c>
@@ -6400,8 +6688,16 @@
           <t>原相</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr"/>
-      <c r="F40" s="4" t="inlineStr"/>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>233.00</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>+4.0</t>
+        </is>
+      </c>
       <c r="G40" s="4" t="n">
         <v>812</v>
       </c>
@@ -6432,8 +6728,16 @@
           <t>東捷</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr"/>
-      <c r="F41" s="4" t="inlineStr"/>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>132.50</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>+12.0</t>
+        </is>
+      </c>
       <c r="G41" s="4" t="n">
         <v>803</v>
       </c>
@@ -6460,8 +6764,16 @@
           <t>典範</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr"/>
-      <c r="F42" s="4" t="inlineStr"/>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>20.25</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>+0.4</t>
+        </is>
+      </c>
       <c r="G42" s="4" t="n">
         <v>781</v>
       </c>
@@ -6496,8 +6808,16 @@
           <t>品安</t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr"/>
-      <c r="F43" s="4" t="inlineStr"/>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>56.90</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>+2.8</t>
+        </is>
+      </c>
       <c r="G43" s="4" t="n">
         <v>720</v>
       </c>
@@ -6524,8 +6844,16 @@
           <t>廣運</t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr"/>
-      <c r="F44" s="4" t="inlineStr"/>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>59.50</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>+3.0</t>
+        </is>
+      </c>
       <c r="G44" s="4" t="n">
         <v>718</v>
       </c>
@@ -6552,8 +6880,16 @@
           <t>均豪</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr"/>
-      <c r="F45" s="4" t="inlineStr"/>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>121.50</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>+4.0</t>
+        </is>
+      </c>
       <c r="G45" s="4" t="n">
         <v>712</v>
       </c>
@@ -6580,8 +6916,16 @@
           <t>泰谷</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr"/>
-      <c r="F46" s="4" t="inlineStr"/>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>50.20</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>+3.6</t>
+        </is>
+      </c>
       <c r="G46" s="4" t="n">
         <v>702</v>
       </c>
@@ -6608,8 +6952,16 @@
           <t>長科*</t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr"/>
-      <c r="F47" s="4" t="inlineStr"/>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>51.90</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>+0.5</t>
+        </is>
+      </c>
       <c r="G47" s="4" t="n">
         <v>683</v>
       </c>
@@ -6636,8 +6988,16 @@
           <t>安國</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr"/>
-      <c r="F48" s="4" t="inlineStr"/>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>111.50</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>+2.0</t>
+        </is>
+      </c>
       <c r="G48" s="4" t="n">
         <v>672</v>
       </c>
@@ -6664,8 +7024,16 @@
           <t>鈊象</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr"/>
-      <c r="F49" s="4" t="inlineStr"/>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>748.00</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>+8.0</t>
+        </is>
+      </c>
       <c r="G49" s="4" t="n">
         <v>637</v>
       </c>
@@ -6696,8 +7064,16 @@
           <t>安碁</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr"/>
-      <c r="F50" s="4" t="inlineStr"/>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>46.75</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>+4.25</t>
+        </is>
+      </c>
       <c r="G50" s="4" t="n">
         <v>633</v>
       </c>
@@ -6732,8 +7108,16 @@
           <t>勤凱</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr"/>
-      <c r="F51" s="4" t="inlineStr"/>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>341.00</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>+31.0</t>
+        </is>
+      </c>
       <c r="G51" s="4" t="n">
         <v>610</v>
       </c>
@@ -6760,8 +7144,16 @@
           <t>旭軟</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr"/>
-      <c r="F52" s="4" t="inlineStr"/>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>28.65</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>+0.3</t>
+        </is>
+      </c>
       <c r="G52" s="4" t="n">
         <v>597</v>
       </c>
@@ -6792,8 +7184,16 @@
           <t>沛亨</t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr"/>
-      <c r="F53" s="4" t="inlineStr"/>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>541.00</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>+49.0</t>
+        </is>
+      </c>
       <c r="G53" s="4" t="n">
         <v>568</v>
       </c>
@@ -6820,8 +7220,16 @@
           <t>建舜電</t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr"/>
-      <c r="F54" s="4" t="inlineStr"/>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>13.45</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>+0.65</t>
+        </is>
+      </c>
       <c r="G54" s="4" t="n">
         <v>550</v>
       </c>
@@ -6856,8 +7264,16 @@
           <t>世禾</t>
         </is>
       </c>
-      <c r="E55" s="4" t="inlineStr"/>
-      <c r="F55" s="4" t="inlineStr"/>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>202.50</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>+5.5</t>
+        </is>
+      </c>
       <c r="G55" s="4" t="n">
         <v>549</v>
       </c>
@@ -6884,8 +7300,16 @@
           <t>立碁</t>
         </is>
       </c>
-      <c r="E56" s="4" t="inlineStr"/>
-      <c r="F56" s="4" t="inlineStr"/>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>66.80</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>+4.3</t>
+        </is>
+      </c>
       <c r="G56" s="4" t="n">
         <v>547</v>
       </c>
@@ -6912,8 +7336,16 @@
           <t>力致</t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr"/>
-      <c r="F57" s="4" t="inlineStr"/>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>94.60</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>+2.6</t>
+        </is>
+      </c>
       <c r="G57" s="4" t="n">
         <v>516</v>
       </c>
@@ -6948,8 +7380,16 @@
           <t>艾訊</t>
         </is>
       </c>
-      <c r="E58" s="4" t="inlineStr"/>
-      <c r="F58" s="4" t="inlineStr"/>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>142.00</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>+4.5</t>
+        </is>
+      </c>
       <c r="G58" s="4" t="n">
         <v>503</v>
       </c>
@@ -6976,8 +7416,16 @@
           <t>泰藝</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr"/>
-      <c r="F59" s="4" t="inlineStr"/>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>66.80</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>+6.0</t>
+        </is>
+      </c>
       <c r="G59" s="4" t="n">
         <v>503</v>
       </c>
@@ -7008,8 +7456,16 @@
           <t>茂達</t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr"/>
-      <c r="F60" s="4" t="inlineStr"/>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>318.50</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>+16.5</t>
+        </is>
+      </c>
       <c r="G60" s="4" t="n">
         <v>502</v>
       </c>
@@ -7036,8 +7492,16 @@
           <t>正基</t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr"/>
-      <c r="F61" s="4" t="inlineStr"/>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>78.90</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>+3.3</t>
+        </is>
+      </c>
       <c r="G61" s="4" t="n">
         <v>494</v>
       </c>
@@ -7072,8 +7536,16 @@
           <t>倚強科</t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr"/>
-      <c r="F62" s="4" t="inlineStr"/>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>92.90</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>+8.4</t>
+        </is>
+      </c>
       <c r="G62" s="4" t="n">
         <v>484</v>
       </c>
@@ -7108,8 +7580,16 @@
           <t>光環</t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr"/>
-      <c r="F63" s="4" t="inlineStr"/>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>104.00</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>+5.5</t>
+        </is>
+      </c>
       <c r="G63" s="4" t="n">
         <v>462</v>
       </c>
@@ -7140,8 +7620,16 @@
           <t>台燿</t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr"/>
-      <c r="F64" s="4" t="inlineStr"/>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>1455.00</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>+130.0</t>
+        </is>
+      </c>
       <c r="G64" s="4" t="n">
         <v>462</v>
       </c>
@@ -7172,8 +7660,16 @@
           <t>立端</t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr"/>
-      <c r="F65" s="4" t="inlineStr"/>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>88.00</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>+2.9</t>
+        </is>
+      </c>
       <c r="G65" s="4" t="n">
         <v>442</v>
       </c>
@@ -7204,8 +7700,16 @@
           <t>廣積</t>
         </is>
       </c>
-      <c r="E66" s="4" t="inlineStr"/>
-      <c r="F66" s="4" t="inlineStr"/>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>53.80</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>+2.5</t>
+        </is>
+      </c>
       <c r="G66" s="4" t="n">
         <v>436</v>
       </c>
@@ -7240,8 +7744,16 @@
           <t>昇達科</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr"/>
-      <c r="F67" s="4" t="inlineStr"/>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>1930.00</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>+80.0</t>
+        </is>
+      </c>
       <c r="G67" s="4" t="n">
         <v>426</v>
       </c>
@@ -7268,8 +7780,16 @@
           <t>磐亞</t>
         </is>
       </c>
-      <c r="E68" s="4" t="inlineStr"/>
-      <c r="F68" s="4" t="inlineStr"/>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>15.25</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>+0.45</t>
+        </is>
+      </c>
       <c r="G68" s="4" t="n">
         <v>413</v>
       </c>
@@ -7296,8 +7816,16 @@
           <t>律勝</t>
         </is>
       </c>
-      <c r="E69" s="4" t="inlineStr"/>
-      <c r="F69" s="4" t="inlineStr"/>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>34.75</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>+2.6</t>
+        </is>
+      </c>
       <c r="G69" s="4" t="n">
         <v>404</v>
       </c>
@@ -7324,8 +7852,16 @@
           <t>僑威</t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr"/>
-      <c r="F70" s="4" t="inlineStr"/>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>56.70</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>+1.5</t>
+        </is>
+      </c>
       <c r="G70" s="4" t="n">
         <v>403</v>
       </c>
@@ -7352,8 +7888,16 @@
           <t>尼克森</t>
         </is>
       </c>
-      <c r="E71" s="4" t="inlineStr"/>
-      <c r="F71" s="4" t="inlineStr"/>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>76.10</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>+0.4</t>
+        </is>
+      </c>
       <c r="G71" s="4" t="n">
         <v>402</v>
       </c>
@@ -7380,8 +7924,16 @@
           <t>鑫聯大投控</t>
         </is>
       </c>
-      <c r="E72" s="4" t="inlineStr"/>
-      <c r="F72" s="4" t="inlineStr"/>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>88.20</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>+1.2</t>
+        </is>
+      </c>
       <c r="G72" s="4" t="n">
         <v>401</v>
       </c>
@@ -7412,8 +7964,16 @@
           <t>泓格</t>
         </is>
       </c>
-      <c r="E73" s="4" t="inlineStr"/>
-      <c r="F73" s="4" t="inlineStr"/>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>145.50</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>+13.0</t>
+        </is>
+      </c>
       <c r="G73" s="4" t="n">
         <v>399</v>
       </c>
@@ -7448,8 +8008,16 @@
           <t>榮剛</t>
         </is>
       </c>
-      <c r="E74" s="4" t="inlineStr"/>
-      <c r="F74" s="4" t="inlineStr"/>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>35.60</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>+0.05</t>
+        </is>
+      </c>
       <c r="G74" s="4" t="n">
         <v>397</v>
       </c>
@@ -7476,8 +8044,16 @@
           <t>松上</t>
         </is>
       </c>
-      <c r="E75" s="4" t="inlineStr"/>
-      <c r="F75" s="4" t="inlineStr"/>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>19.25</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>+0.75</t>
+        </is>
+      </c>
       <c r="G75" s="4" t="n">
         <v>397</v>
       </c>
@@ -7512,8 +8088,16 @@
           <t>凱崴</t>
         </is>
       </c>
-      <c r="E76" s="4" t="inlineStr"/>
-      <c r="F76" s="4" t="inlineStr"/>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>66.80</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>+4.1</t>
+        </is>
+      </c>
       <c r="G76" s="4" t="n">
         <v>396</v>
       </c>
@@ -7540,8 +8124,16 @@
           <t>瀧澤科</t>
         </is>
       </c>
-      <c r="E77" s="4" t="inlineStr"/>
-      <c r="F77" s="4" t="inlineStr"/>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>46.35</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>+4.2</t>
+        </is>
+      </c>
       <c r="G77" s="4" t="n">
         <v>396</v>
       </c>
@@ -7576,8 +8168,16 @@
           <t>致和證</t>
         </is>
       </c>
-      <c r="E78" s="4" t="inlineStr"/>
-      <c r="F78" s="4" t="inlineStr"/>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>33.20</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>+0.9</t>
+        </is>
+      </c>
       <c r="G78" s="4" t="n">
         <v>387</v>
       </c>
@@ -7604,8 +8204,16 @@
           <t>聯亞</t>
         </is>
       </c>
-      <c r="E79" s="4" t="inlineStr"/>
-      <c r="F79" s="4" t="inlineStr"/>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>2710.00</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>+155.0</t>
+        </is>
+      </c>
       <c r="G79" s="4" t="n">
         <v>384</v>
       </c>
@@ -7632,8 +8240,16 @@
           <t>信昌電</t>
         </is>
       </c>
-      <c r="E80" s="4" t="inlineStr"/>
-      <c r="F80" s="4" t="inlineStr"/>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>192.50</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>+17.5</t>
+        </is>
+      </c>
       <c r="G80" s="4" t="n">
         <v>384</v>
       </c>
@@ -7664,8 +8280,16 @@
           <t>中美晶</t>
         </is>
       </c>
-      <c r="E81" s="4" t="inlineStr"/>
-      <c r="F81" s="4" t="inlineStr"/>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>147.50</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>+5.0</t>
+        </is>
+      </c>
       <c r="G81" s="4" t="n">
         <v>370</v>
       </c>
@@ -7692,8 +8316,16 @@
           <t>能率網通</t>
         </is>
       </c>
-      <c r="E82" s="4" t="inlineStr"/>
-      <c r="F82" s="4" t="inlineStr"/>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>20.05</t>
+        </is>
+      </c>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>+0.15</t>
+        </is>
+      </c>
       <c r="G82" s="4" t="n">
         <v>368</v>
       </c>
@@ -7728,8 +8360,16 @@
           <t>同亨</t>
         </is>
       </c>
-      <c r="E83" s="4" t="inlineStr"/>
-      <c r="F83" s="4" t="inlineStr"/>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>29.75</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>+1.05</t>
+        </is>
+      </c>
       <c r="G83" s="4" t="n">
         <v>357</v>
       </c>
@@ -7760,8 +8400,16 @@
           <t>協禧</t>
         </is>
       </c>
-      <c r="E84" s="4" t="inlineStr"/>
-      <c r="F84" s="4" t="inlineStr"/>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>30.60</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>+0.9</t>
+        </is>
+      </c>
       <c r="G84" s="4" t="n">
         <v>349</v>
       </c>
@@ -7792,8 +8440,16 @@
           <t>朋程</t>
         </is>
       </c>
-      <c r="E85" s="4" t="inlineStr"/>
-      <c r="F85" s="4" t="inlineStr"/>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>157.00</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>+2.5</t>
+        </is>
+      </c>
       <c r="G85" s="4" t="n">
         <v>346</v>
       </c>
@@ -7820,8 +8476,16 @@
           <t>亞矽</t>
         </is>
       </c>
-      <c r="E86" s="4" t="inlineStr"/>
-      <c r="F86" s="4" t="inlineStr"/>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>27.60</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>+2.25</t>
+        </is>
+      </c>
       <c r="G86" s="4" t="n">
         <v>345</v>
       </c>
@@ -7856,8 +8520,16 @@
           <t>亞電</t>
         </is>
       </c>
-      <c r="E87" s="4" t="inlineStr"/>
-      <c r="F87" s="4" t="inlineStr"/>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>39.55</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>+1.5</t>
+        </is>
+      </c>
       <c r="G87" s="4" t="n">
         <v>332</v>
       </c>
@@ -7884,8 +8556,16 @@
           <t>艾華</t>
         </is>
       </c>
-      <c r="E88" s="4" t="inlineStr"/>
-      <c r="F88" s="4" t="inlineStr"/>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>90.00</t>
+        </is>
+      </c>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t>+5.3</t>
+        </is>
+      </c>
       <c r="G88" s="4" t="n">
         <v>326</v>
       </c>
@@ -7920,8 +8600,16 @@
           <t>磐儀</t>
         </is>
       </c>
-      <c r="E89" s="4" t="inlineStr"/>
-      <c r="F89" s="4" t="inlineStr"/>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>52.00</t>
+        </is>
+      </c>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t>+1.2</t>
+        </is>
+      </c>
       <c r="G89" s="4" t="n">
         <v>323</v>
       </c>
@@ -7952,8 +8640,16 @@
           <t>中探針</t>
         </is>
       </c>
-      <c r="E90" s="4" t="inlineStr"/>
-      <c r="F90" s="4" t="inlineStr"/>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>272.00</t>
+        </is>
+      </c>
+      <c r="F90" s="4" t="inlineStr">
+        <is>
+          <t>+24.5</t>
+        </is>
+      </c>
       <c r="G90" s="4" t="n">
         <v>321</v>
       </c>
@@ -7980,8 +8676,16 @@
           <t>新復興</t>
         </is>
       </c>
-      <c r="E91" s="4" t="inlineStr"/>
-      <c r="F91" s="4" t="inlineStr"/>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>53.40</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>+1.9</t>
+        </is>
+      </c>
       <c r="G91" s="4" t="n">
         <v>310</v>
       </c>
@@ -8012,8 +8716,16 @@
           <t>萬泰科</t>
         </is>
       </c>
-      <c r="E92" s="4" t="inlineStr"/>
-      <c r="F92" s="4" t="inlineStr"/>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>80.00</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t>+1.0</t>
+        </is>
+      </c>
       <c r="G92" s="4" t="n">
         <v>305</v>
       </c>
@@ -8040,8 +8752,16 @@
           <t>捷波</t>
         </is>
       </c>
-      <c r="E93" s="4" t="inlineStr"/>
-      <c r="F93" s="4" t="inlineStr"/>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>53.80</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>+2.8</t>
+        </is>
+      </c>
       <c r="G93" s="4" t="n">
         <v>301</v>
       </c>
@@ -8076,8 +8796,16 @@
           <t>光譜</t>
         </is>
       </c>
-      <c r="E94" s="4" t="inlineStr"/>
-      <c r="F94" s="4" t="inlineStr"/>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>25.45</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t>+0.15</t>
+        </is>
+      </c>
       <c r="G94" s="4" t="n">
         <v>297</v>
       </c>
@@ -8104,8 +8832,16 @@
           <t>中裕</t>
         </is>
       </c>
-      <c r="E95" s="4" t="inlineStr"/>
-      <c r="F95" s="4" t="inlineStr"/>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>50.50</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>+1.5</t>
+        </is>
+      </c>
       <c r="G95" s="4" t="n">
         <v>285</v>
       </c>
@@ -8132,8 +8868,16 @@
           <t>類比科</t>
         </is>
       </c>
-      <c r="E96" s="4" t="inlineStr"/>
-      <c r="F96" s="4" t="inlineStr"/>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>71.40</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>+3.6</t>
+        </is>
+      </c>
       <c r="G96" s="4" t="n">
         <v>280</v>
       </c>
@@ -8168,8 +8912,16 @@
           <t>湧德</t>
         </is>
       </c>
-      <c r="E97" s="4" t="inlineStr"/>
-      <c r="F97" s="4" t="inlineStr"/>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>123.50</t>
+        </is>
+      </c>
+      <c r="F97" s="4" t="inlineStr">
+        <is>
+          <t>+2.5</t>
+        </is>
+      </c>
       <c r="G97" s="4" t="n">
         <v>275</v>
       </c>
@@ -8196,8 +8948,16 @@
           <t>國統</t>
         </is>
       </c>
-      <c r="E98" s="4" t="inlineStr"/>
-      <c r="F98" s="4" t="inlineStr"/>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>50.20</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>+0.2</t>
+        </is>
+      </c>
       <c r="G98" s="4" t="n">
         <v>264</v>
       </c>
@@ -8224,8 +8984,16 @@
           <t>精材</t>
         </is>
       </c>
-      <c r="E99" s="4" t="inlineStr"/>
-      <c r="F99" s="4" t="inlineStr"/>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>253.00</t>
+        </is>
+      </c>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t>+8.5</t>
+        </is>
+      </c>
       <c r="G99" s="4" t="n">
         <v>260</v>
       </c>
@@ -8252,8 +9020,16 @@
           <t>永捷</t>
         </is>
       </c>
-      <c r="E100" s="4" t="inlineStr"/>
-      <c r="F100" s="4" t="inlineStr"/>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t>13.30</t>
+        </is>
+      </c>
+      <c r="F100" s="4" t="inlineStr">
+        <is>
+          <t>-0.1</t>
+        </is>
+      </c>
       <c r="G100" s="4" t="n">
         <v>249</v>
       </c>
@@ -8280,8 +9056,16 @@
           <t>全宇昕</t>
         </is>
       </c>
-      <c r="E101" s="4" t="inlineStr"/>
-      <c r="F101" s="4" t="inlineStr"/>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t>137.50</t>
+        </is>
+      </c>
+      <c r="F101" s="4" t="inlineStr">
+        <is>
+          <t>+12.5</t>
+        </is>
+      </c>
       <c r="G101" s="4" t="n">
         <v>245</v>
       </c>
@@ -8316,8 +9100,16 @@
           <t>高技</t>
         </is>
       </c>
-      <c r="E102" s="4" t="inlineStr"/>
-      <c r="F102" s="4" t="inlineStr"/>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t>387.50</t>
+        </is>
+      </c>
+      <c r="F102" s="4" t="inlineStr">
+        <is>
+          <t>+11.0</t>
+        </is>
+      </c>
       <c r="G102" s="4" t="n">
         <v>244</v>
       </c>
@@ -8344,8 +9136,16 @@
           <t>禾瑞亞</t>
         </is>
       </c>
-      <c r="E103" s="4" t="inlineStr"/>
-      <c r="F103" s="4" t="inlineStr"/>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t>54.70</t>
+        </is>
+      </c>
+      <c r="F103" s="4" t="inlineStr">
+        <is>
+          <t>+0.7</t>
+        </is>
+      </c>
       <c r="G103" s="4" t="n">
         <v>241</v>
       </c>
@@ -8484,8 +9284,16 @@
           <t>頎邦</t>
         </is>
       </c>
-      <c r="E109" s="4" t="inlineStr"/>
-      <c r="F109" s="4" t="inlineStr"/>
+      <c r="E109" s="4" t="inlineStr">
+        <is>
+          <t>215.50</t>
+        </is>
+      </c>
+      <c r="F109" s="4" t="inlineStr">
+        <is>
+          <t>-7.0</t>
+        </is>
+      </c>
       <c r="G109" s="4" t="n">
         <v>-13993</v>
       </c>
@@ -8520,8 +9328,16 @@
           <t>世界</t>
         </is>
       </c>
-      <c r="E110" s="4" t="inlineStr"/>
-      <c r="F110" s="4" t="inlineStr"/>
+      <c r="E110" s="4" t="inlineStr">
+        <is>
+          <t>162.00</t>
+        </is>
+      </c>
+      <c r="F110" s="4" t="inlineStr">
+        <is>
+          <t>-1.5</t>
+        </is>
+      </c>
       <c r="G110" s="4" t="n">
         <v>-8199</v>
       </c>
@@ -8548,8 +9364,16 @@
           <t>台半</t>
         </is>
       </c>
-      <c r="E111" s="4" t="inlineStr"/>
-      <c r="F111" s="4" t="inlineStr"/>
+      <c r="E111" s="4" t="inlineStr">
+        <is>
+          <t>87.10</t>
+        </is>
+      </c>
+      <c r="F111" s="4" t="inlineStr">
+        <is>
+          <t>-3.3</t>
+        </is>
+      </c>
       <c r="G111" s="4" t="n">
         <v>-3927</v>
       </c>
@@ -8576,8 +9400,16 @@
           <t>雷科</t>
         </is>
       </c>
-      <c r="E112" s="4" t="inlineStr"/>
-      <c r="F112" s="4" t="inlineStr"/>
+      <c r="E112" s="4" t="inlineStr">
+        <is>
+          <t>89.90</t>
+        </is>
+      </c>
+      <c r="F112" s="4" t="inlineStr">
+        <is>
+          <t>+1.2</t>
+        </is>
+      </c>
       <c r="G112" s="4" t="n">
         <v>-2676</v>
       </c>
@@ -8612,8 +9444,16 @@
           <t>光洋科</t>
         </is>
       </c>
-      <c r="E113" s="4" t="inlineStr"/>
-      <c r="F113" s="4" t="inlineStr"/>
+      <c r="E113" s="4" t="inlineStr">
+        <is>
+          <t>144.00</t>
+        </is>
+      </c>
+      <c r="F113" s="4" t="inlineStr">
+        <is>
+          <t>+1.5</t>
+        </is>
+      </c>
       <c r="G113" s="4" t="n">
         <v>-2505</v>
       </c>
@@ -8644,8 +9484,16 @@
           <t>鑫科</t>
         </is>
       </c>
-      <c r="E114" s="4" t="inlineStr"/>
-      <c r="F114" s="4" t="inlineStr"/>
+      <c r="E114" s="4" t="inlineStr">
+        <is>
+          <t>86.90</t>
+        </is>
+      </c>
+      <c r="F114" s="4" t="inlineStr">
+        <is>
+          <t>+3.2</t>
+        </is>
+      </c>
       <c r="G114" s="4" t="n">
         <v>-2391</v>
       </c>
@@ -8680,8 +9528,16 @@
           <t>威剛</t>
         </is>
       </c>
-      <c r="E115" s="4" t="inlineStr"/>
-      <c r="F115" s="4" t="inlineStr"/>
+      <c r="E115" s="4" t="inlineStr">
+        <is>
+          <t>417.50</t>
+        </is>
+      </c>
+      <c r="F115" s="4" t="inlineStr">
+        <is>
+          <t>+4.5</t>
+        </is>
+      </c>
       <c r="G115" s="4" t="n">
         <v>-2117</v>
       </c>
@@ -8712,8 +9568,16 @@
           <t>環球晶</t>
         </is>
       </c>
-      <c r="E116" s="4" t="inlineStr"/>
-      <c r="F116" s="4" t="inlineStr"/>
+      <c r="E116" s="4" t="inlineStr">
+        <is>
+          <t>717.00</t>
+        </is>
+      </c>
+      <c r="F116" s="4" t="inlineStr">
+        <is>
+          <t>+16.0</t>
+        </is>
+      </c>
       <c r="G116" s="4" t="n">
         <v>-1786</v>
       </c>
@@ -8744,8 +9608,16 @@
           <t>中天</t>
         </is>
       </c>
-      <c r="E117" s="4" t="inlineStr"/>
-      <c r="F117" s="4" t="inlineStr"/>
+      <c r="E117" s="4" t="inlineStr">
+        <is>
+          <t>15.75</t>
+        </is>
+      </c>
+      <c r="F117" s="4" t="inlineStr">
+        <is>
+          <t>-0.3</t>
+        </is>
+      </c>
       <c r="G117" s="4" t="n">
         <v>-1010</v>
       </c>
@@ -8776,8 +9648,16 @@
           <t>由田</t>
         </is>
       </c>
-      <c r="E118" s="4" t="inlineStr"/>
-      <c r="F118" s="4" t="inlineStr"/>
+      <c r="E118" s="4" t="inlineStr">
+        <is>
+          <t>293.00</t>
+        </is>
+      </c>
+      <c r="F118" s="4" t="inlineStr">
+        <is>
+          <t>-17.0</t>
+        </is>
+      </c>
       <c r="G118" s="4" t="n">
         <v>-1000</v>
       </c>
@@ -8816,8 +9696,16 @@
           <t>福邦證</t>
         </is>
       </c>
-      <c r="E119" s="4" t="inlineStr"/>
-      <c r="F119" s="4" t="inlineStr"/>
+      <c r="E119" s="4" t="inlineStr">
+        <is>
+          <t>15.30</t>
+        </is>
+      </c>
+      <c r="F119" s="4" t="inlineStr">
+        <is>
+          <t>-0.05</t>
+        </is>
+      </c>
       <c r="G119" s="4" t="n">
         <v>-981</v>
       </c>
@@ -8848,8 +9736,16 @@
           <t>蜜望實</t>
         </is>
       </c>
-      <c r="E120" s="4" t="inlineStr"/>
-      <c r="F120" s="4" t="inlineStr"/>
+      <c r="E120" s="4" t="inlineStr">
+        <is>
+          <t>130.50</t>
+        </is>
+      </c>
+      <c r="F120" s="4" t="inlineStr">
+        <is>
+          <t>+5.0</t>
+        </is>
+      </c>
       <c r="G120" s="4" t="n">
         <v>-922</v>
       </c>
@@ -8880,8 +9776,16 @@
           <t>鈦昇</t>
         </is>
       </c>
-      <c r="E121" s="4" t="inlineStr"/>
-      <c r="F121" s="4" t="inlineStr"/>
+      <c r="E121" s="4" t="inlineStr">
+        <is>
+          <t>244.50</t>
+        </is>
+      </c>
+      <c r="F121" s="4" t="inlineStr">
+        <is>
+          <t>+3.0</t>
+        </is>
+      </c>
       <c r="G121" s="4" t="n">
         <v>-896</v>
       </c>
@@ -8912,8 +9816,16 @@
           <t>高端疫苗</t>
         </is>
       </c>
-      <c r="E122" s="4" t="inlineStr"/>
-      <c r="F122" s="4" t="inlineStr"/>
+      <c r="E122" s="4" t="inlineStr">
+        <is>
+          <t>47.95</t>
+        </is>
+      </c>
+      <c r="F122" s="4" t="inlineStr">
+        <is>
+          <t>-0.75</t>
+        </is>
+      </c>
       <c r="G122" s="4" t="n">
         <v>-824</v>
       </c>
@@ -8944,8 +9856,16 @@
           <t>雙鴻</t>
         </is>
       </c>
-      <c r="E123" s="4" t="inlineStr"/>
-      <c r="F123" s="4" t="inlineStr"/>
+      <c r="E123" s="4" t="inlineStr">
+        <is>
+          <t>1010.00</t>
+        </is>
+      </c>
+      <c r="F123" s="4" t="inlineStr">
+        <is>
+          <t>+10.0</t>
+        </is>
+      </c>
       <c r="G123" s="4" t="n">
         <v>-809</v>
       </c>
@@ -8980,8 +9900,16 @@
           <t>群聯</t>
         </is>
       </c>
-      <c r="E124" s="4" t="inlineStr"/>
-      <c r="F124" s="4" t="inlineStr"/>
+      <c r="E124" s="4" t="inlineStr">
+        <is>
+          <t>2430.00</t>
+        </is>
+      </c>
+      <c r="F124" s="4" t="inlineStr">
+        <is>
+          <t>+95.0</t>
+        </is>
+      </c>
       <c r="G124" s="4" t="n">
         <v>-801</v>
       </c>
@@ -9012,8 +9940,16 @@
           <t>晶焱</t>
         </is>
       </c>
-      <c r="E125" s="4" t="inlineStr"/>
-      <c r="F125" s="4" t="inlineStr"/>
+      <c r="E125" s="4" t="inlineStr">
+        <is>
+          <t>94.90</t>
+        </is>
+      </c>
+      <c r="F125" s="4" t="inlineStr">
+        <is>
+          <t>+0.3</t>
+        </is>
+      </c>
       <c r="G125" s="4" t="n">
         <v>-723</v>
       </c>
@@ -9052,8 +9988,16 @@
           <t>欣銓</t>
         </is>
       </c>
-      <c r="E126" s="4" t="inlineStr"/>
-      <c r="F126" s="4" t="inlineStr"/>
+      <c r="E126" s="4" t="inlineStr">
+        <is>
+          <t>221.50</t>
+        </is>
+      </c>
+      <c r="F126" s="4" t="inlineStr">
+        <is>
+          <t>+2.5</t>
+        </is>
+      </c>
       <c r="G126" s="4" t="n">
         <v>-704</v>
       </c>
@@ -9080,8 +10024,16 @@
           <t>精確</t>
         </is>
       </c>
-      <c r="E127" s="4" t="inlineStr"/>
-      <c r="F127" s="4" t="inlineStr"/>
+      <c r="E127" s="4" t="inlineStr">
+        <is>
+          <t>87.60</t>
+        </is>
+      </c>
+      <c r="F127" s="4" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
       <c r="G127" s="4" t="n">
         <v>-684</v>
       </c>
@@ -9112,8 +10064,16 @@
           <t>元太</t>
         </is>
       </c>
-      <c r="E128" s="4" t="inlineStr"/>
-      <c r="F128" s="4" t="inlineStr"/>
+      <c r="E128" s="4" t="inlineStr">
+        <is>
+          <t>224.00</t>
+        </is>
+      </c>
+      <c r="F128" s="4" t="inlineStr">
+        <is>
+          <t>-6.5</t>
+        </is>
+      </c>
       <c r="G128" s="4" t="n">
         <v>-637</v>
       </c>
@@ -9144,8 +10104,16 @@
           <t>單井</t>
         </is>
       </c>
-      <c r="E129" s="4" t="inlineStr"/>
-      <c r="F129" s="4" t="inlineStr"/>
+      <c r="E129" s="4" t="inlineStr">
+        <is>
+          <t>43.50</t>
+        </is>
+      </c>
+      <c r="F129" s="4" t="inlineStr">
+        <is>
+          <t>+2.8</t>
+        </is>
+      </c>
       <c r="G129" s="4" t="n">
         <v>-608</v>
       </c>
@@ -9172,8 +10140,16 @@
           <t>德宏</t>
         </is>
       </c>
-      <c r="E130" s="4" t="inlineStr"/>
-      <c r="F130" s="4" t="inlineStr"/>
+      <c r="E130" s="4" t="inlineStr">
+        <is>
+          <t>297.00</t>
+        </is>
+      </c>
+      <c r="F130" s="4" t="inlineStr">
+        <is>
+          <t>+10.0</t>
+        </is>
+      </c>
       <c r="G130" s="4" t="n">
         <v>-577</v>
       </c>
@@ -9200,8 +10176,16 @@
           <t>智通*</t>
         </is>
       </c>
-      <c r="E131" s="4" t="inlineStr"/>
-      <c r="F131" s="4" t="inlineStr"/>
+      <c r="E131" s="4" t="inlineStr">
+        <is>
+          <t>101.00</t>
+        </is>
+      </c>
+      <c r="F131" s="4" t="inlineStr">
+        <is>
+          <t>+1.0</t>
+        </is>
+      </c>
       <c r="G131" s="4" t="n">
         <v>-560</v>
       </c>
@@ -9228,8 +10212,16 @@
           <t>港建*</t>
         </is>
       </c>
-      <c r="E132" s="4" t="inlineStr"/>
-      <c r="F132" s="4" t="inlineStr"/>
+      <c r="E132" s="4" t="inlineStr">
+        <is>
+          <t>52.10</t>
+        </is>
+      </c>
+      <c r="F132" s="4" t="inlineStr">
+        <is>
+          <t>+3.65</t>
+        </is>
+      </c>
       <c r="G132" s="4" t="n">
         <v>-488</v>
       </c>
@@ -9256,8 +10248,16 @@
           <t>廣穎</t>
         </is>
       </c>
-      <c r="E133" s="4" t="inlineStr"/>
-      <c r="F133" s="4" t="inlineStr"/>
+      <c r="E133" s="4" t="inlineStr">
+        <is>
+          <t>115.00</t>
+        </is>
+      </c>
+      <c r="F133" s="4" t="inlineStr">
+        <is>
+          <t>+7.0</t>
+        </is>
+      </c>
       <c r="G133" s="4" t="n">
         <v>-469</v>
       </c>
@@ -9284,8 +10284,16 @@
           <t>基亞</t>
         </is>
       </c>
-      <c r="E134" s="4" t="inlineStr"/>
-      <c r="F134" s="4" t="inlineStr"/>
+      <c r="E134" s="4" t="inlineStr">
+        <is>
+          <t>37.25</t>
+        </is>
+      </c>
+      <c r="F134" s="4" t="inlineStr">
+        <is>
+          <t>-2.45</t>
+        </is>
+      </c>
       <c r="G134" s="4" t="n">
         <v>-460</v>
       </c>
@@ -9320,8 +10328,16 @@
           <t>熒茂</t>
         </is>
       </c>
-      <c r="E135" s="4" t="inlineStr"/>
-      <c r="F135" s="4" t="inlineStr"/>
+      <c r="E135" s="4" t="inlineStr">
+        <is>
+          <t>25.60</t>
+        </is>
+      </c>
+      <c r="F135" s="4" t="inlineStr">
+        <is>
+          <t>+1.55</t>
+        </is>
+      </c>
       <c r="G135" s="4" t="n">
         <v>-435</v>
       </c>
@@ -9356,8 +10372,16 @@
           <t>神盾</t>
         </is>
       </c>
-      <c r="E136" s="4" t="inlineStr"/>
-      <c r="F136" s="4" t="inlineStr"/>
+      <c r="E136" s="4" t="inlineStr">
+        <is>
+          <t>144.50</t>
+        </is>
+      </c>
+      <c r="F136" s="4" t="inlineStr">
+        <is>
+          <t>+4.0</t>
+        </is>
+      </c>
       <c r="G136" s="4" t="n">
         <v>-404</v>
       </c>
@@ -9384,8 +10408,16 @@
           <t>良維</t>
         </is>
       </c>
-      <c r="E137" s="4" t="inlineStr"/>
-      <c r="F137" s="4" t="inlineStr"/>
+      <c r="E137" s="4" t="inlineStr">
+        <is>
+          <t>278.00</t>
+        </is>
+      </c>
+      <c r="F137" s="4" t="inlineStr">
+        <is>
+          <t>+5.5</t>
+        </is>
+      </c>
       <c r="G137" s="4" t="n">
         <v>-402</v>
       </c>
@@ -9416,8 +10448,16 @@
           <t>晟德</t>
         </is>
       </c>
-      <c r="E138" s="4" t="inlineStr"/>
-      <c r="F138" s="4" t="inlineStr"/>
+      <c r="E138" s="4" t="inlineStr">
+        <is>
+          <t>38.70</t>
+        </is>
+      </c>
+      <c r="F138" s="4" t="inlineStr">
+        <is>
+          <t>-0.05</t>
+        </is>
+      </c>
       <c r="G138" s="4" t="n">
         <v>-395</v>
       </c>
@@ -9444,8 +10484,16 @@
           <t>太景*-KY</t>
         </is>
       </c>
-      <c r="E139" s="4" t="inlineStr"/>
-      <c r="F139" s="4" t="inlineStr"/>
+      <c r="E139" s="4" t="inlineStr">
+        <is>
+          <t>9.26</t>
+        </is>
+      </c>
+      <c r="F139" s="4" t="inlineStr">
+        <is>
+          <t>+0.05</t>
+        </is>
+      </c>
       <c r="G139" s="4" t="n">
         <v>-369</v>
       </c>
@@ -9472,8 +10520,16 @@
           <t>力麒</t>
         </is>
       </c>
-      <c r="E140" s="4" t="inlineStr"/>
-      <c r="F140" s="4" t="inlineStr"/>
+      <c r="E140" s="4" t="inlineStr">
+        <is>
+          <t>6.92</t>
+        </is>
+      </c>
+      <c r="F140" s="4" t="inlineStr">
+        <is>
+          <t>+0.01</t>
+        </is>
+      </c>
       <c r="G140" s="4" t="n">
         <v>-358</v>
       </c>
@@ -9500,8 +10556,16 @@
           <t>邑昇</t>
         </is>
       </c>
-      <c r="E141" s="4" t="inlineStr"/>
-      <c r="F141" s="4" t="inlineStr"/>
+      <c r="E141" s="4" t="inlineStr">
+        <is>
+          <t>76.90</t>
+        </is>
+      </c>
+      <c r="F141" s="4" t="inlineStr">
+        <is>
+          <t>-1.9</t>
+        </is>
+      </c>
       <c r="G141" s="4" t="n">
         <v>-355</v>
       </c>
@@ -9528,8 +10592,16 @@
           <t>閎康</t>
         </is>
       </c>
-      <c r="E142" s="4" t="inlineStr"/>
-      <c r="F142" s="4" t="inlineStr"/>
+      <c r="E142" s="4" t="inlineStr">
+        <is>
+          <t>342.00</t>
+        </is>
+      </c>
+      <c r="F142" s="4" t="inlineStr">
+        <is>
+          <t>+17.0</t>
+        </is>
+      </c>
       <c r="G142" s="4" t="n">
         <v>-350</v>
       </c>
@@ -9556,8 +10628,16 @@
           <t>先進光</t>
         </is>
       </c>
-      <c r="E143" s="4" t="inlineStr"/>
-      <c r="F143" s="4" t="inlineStr"/>
+      <c r="E143" s="4" t="inlineStr">
+        <is>
+          <t>120.00</t>
+        </is>
+      </c>
+      <c r="F143" s="4" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
       <c r="G143" s="4" t="n">
         <v>-343</v>
       </c>
@@ -9584,8 +10664,16 @@
           <t>奇鈦科</t>
         </is>
       </c>
-      <c r="E144" s="4" t="inlineStr"/>
-      <c r="F144" s="4" t="inlineStr"/>
+      <c r="E144" s="4" t="inlineStr">
+        <is>
+          <t>183.50</t>
+        </is>
+      </c>
+      <c r="F144" s="4" t="inlineStr">
+        <is>
+          <t>+9.5</t>
+        </is>
+      </c>
       <c r="G144" s="4" t="n">
         <v>-343</v>
       </c>
@@ -9616,8 +10704,16 @@
           <t>建榮</t>
         </is>
       </c>
-      <c r="E145" s="4" t="inlineStr"/>
-      <c r="F145" s="4" t="inlineStr"/>
+      <c r="E145" s="4" t="inlineStr">
+        <is>
+          <t>107.50</t>
+        </is>
+      </c>
+      <c r="F145" s="4" t="inlineStr">
+        <is>
+          <t>+7.0</t>
+        </is>
+      </c>
       <c r="G145" s="4" t="n">
         <v>-340</v>
       </c>
@@ -9644,8 +10740,16 @@
           <t>日揚</t>
         </is>
       </c>
-      <c r="E146" s="4" t="inlineStr"/>
-      <c r="F146" s="4" t="inlineStr"/>
+      <c r="E146" s="4" t="inlineStr">
+        <is>
+          <t>99.00</t>
+        </is>
+      </c>
+      <c r="F146" s="4" t="inlineStr">
+        <is>
+          <t>-3.0</t>
+        </is>
+      </c>
       <c r="G146" s="4" t="n">
         <v>-333</v>
       </c>
@@ -9680,8 +10784,16 @@
           <t>世紀*</t>
         </is>
       </c>
-      <c r="E147" s="4" t="inlineStr"/>
-      <c r="F147" s="4" t="inlineStr"/>
+      <c r="E147" s="4" t="inlineStr">
+        <is>
+          <t>67.00</t>
+        </is>
+      </c>
+      <c r="F147" s="4" t="inlineStr">
+        <is>
+          <t>-2.8</t>
+        </is>
+      </c>
       <c r="G147" s="4" t="n">
         <v>-324</v>
       </c>
@@ -9708,8 +10820,16 @@
           <t>易發</t>
         </is>
       </c>
-      <c r="E148" s="4" t="inlineStr"/>
-      <c r="F148" s="4" t="inlineStr"/>
+      <c r="E148" s="4" t="inlineStr">
+        <is>
+          <t>90.40</t>
+        </is>
+      </c>
+      <c r="F148" s="4" t="inlineStr">
+        <is>
+          <t>+0.2</t>
+        </is>
+      </c>
       <c r="G148" s="4" t="n">
         <v>-314</v>
       </c>
@@ -9736,8 +10856,16 @@
           <t>康和證</t>
         </is>
       </c>
-      <c r="E149" s="4" t="inlineStr"/>
-      <c r="F149" s="4" t="inlineStr"/>
+      <c r="E149" s="4" t="inlineStr">
+        <is>
+          <t>22.90</t>
+        </is>
+      </c>
+      <c r="F149" s="4" t="inlineStr">
+        <is>
+          <t>+0.45</t>
+        </is>
+      </c>
       <c r="G149" s="4" t="n">
         <v>-312</v>
       </c>
@@ -9768,8 +10896,16 @@
           <t>雍智科技</t>
         </is>
       </c>
-      <c r="E150" s="4" t="inlineStr"/>
-      <c r="F150" s="4" t="inlineStr"/>
+      <c r="E150" s="4" t="inlineStr">
+        <is>
+          <t>1650.00</t>
+        </is>
+      </c>
+      <c r="F150" s="4" t="inlineStr">
+        <is>
+          <t>-35.0</t>
+        </is>
+      </c>
       <c r="G150" s="4" t="n">
         <v>-302</v>
       </c>
@@ -9804,8 +10940,16 @@
           <t>華電網</t>
         </is>
       </c>
-      <c r="E151" s="4" t="inlineStr"/>
-      <c r="F151" s="4" t="inlineStr"/>
+      <c r="E151" s="4" t="inlineStr">
+        <is>
+          <t>53.20</t>
+        </is>
+      </c>
+      <c r="F151" s="4" t="inlineStr">
+        <is>
+          <t>-0.0</t>
+        </is>
+      </c>
       <c r="G151" s="4" t="n">
         <v>-298</v>
       </c>
@@ -9832,8 +10976,16 @@
           <t>富強鑫</t>
         </is>
       </c>
-      <c r="E152" s="4" t="inlineStr"/>
-      <c r="F152" s="4" t="inlineStr"/>
+      <c r="E152" s="4" t="inlineStr">
+        <is>
+          <t>22.40</t>
+        </is>
+      </c>
+      <c r="F152" s="4" t="inlineStr">
+        <is>
+          <t>+0.05</t>
+        </is>
+      </c>
       <c r="G152" s="4" t="n">
         <v>-298</v>
       </c>
@@ -9864,8 +11016,16 @@
           <t>聯寶</t>
         </is>
       </c>
-      <c r="E153" s="4" t="inlineStr"/>
-      <c r="F153" s="4" t="inlineStr"/>
+      <c r="E153" s="4" t="inlineStr">
+        <is>
+          <t>57.40</t>
+        </is>
+      </c>
+      <c r="F153" s="4" t="inlineStr">
+        <is>
+          <t>+0.2</t>
+        </is>
+      </c>
       <c r="G153" s="4" t="n">
         <v>-286</v>
       </c>
@@ -9900,8 +11060,16 @@
           <t>博智</t>
         </is>
       </c>
-      <c r="E154" s="4" t="inlineStr"/>
-      <c r="F154" s="4" t="inlineStr"/>
+      <c r="E154" s="4" t="inlineStr">
+        <is>
+          <t>413.50</t>
+        </is>
+      </c>
+      <c r="F154" s="4" t="inlineStr">
+        <is>
+          <t>+0.5</t>
+        </is>
+      </c>
       <c r="G154" s="4" t="n">
         <v>-284</v>
       </c>
@@ -9932,8 +11100,16 @@
           <t>九豪</t>
         </is>
       </c>
-      <c r="E155" s="4" t="inlineStr"/>
-      <c r="F155" s="4" t="inlineStr"/>
+      <c r="E155" s="4" t="inlineStr">
+        <is>
+          <t>52.50</t>
+        </is>
+      </c>
+      <c r="F155" s="4" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
       <c r="G155" s="4" t="n">
         <v>-275</v>
       </c>
@@ -9960,8 +11136,16 @@
           <t>家登</t>
         </is>
       </c>
-      <c r="E156" s="4" t="inlineStr"/>
-      <c r="F156" s="4" t="inlineStr"/>
+      <c r="E156" s="4" t="inlineStr">
+        <is>
+          <t>568.00</t>
+        </is>
+      </c>
+      <c r="F156" s="4" t="inlineStr">
+        <is>
+          <t>+24.0</t>
+        </is>
+      </c>
       <c r="G156" s="4" t="n">
         <v>-270</v>
       </c>
@@ -9988,8 +11172,16 @@
           <t>高僑</t>
         </is>
       </c>
-      <c r="E157" s="4" t="inlineStr"/>
-      <c r="F157" s="4" t="inlineStr"/>
+      <c r="E157" s="4" t="inlineStr">
+        <is>
+          <t>49.00</t>
+        </is>
+      </c>
+      <c r="F157" s="4" t="inlineStr">
+        <is>
+          <t>+2.2</t>
+        </is>
+      </c>
       <c r="G157" s="4" t="n">
         <v>-265</v>
       </c>
@@ -10020,8 +11212,16 @@
           <t>千附</t>
         </is>
       </c>
-      <c r="E158" s="4" t="inlineStr"/>
-      <c r="F158" s="4" t="inlineStr"/>
+      <c r="E158" s="4" t="inlineStr">
+        <is>
+          <t>59.30</t>
+        </is>
+      </c>
+      <c r="F158" s="4" t="inlineStr">
+        <is>
+          <t>+2.7</t>
+        </is>
+      </c>
       <c r="G158" s="4" t="n">
         <v>-264</v>
       </c>

--- a/StockInfo/otc_analysis_result.xlsx
+++ b/StockInfo/otc_analysis_result.xlsx
@@ -5411,8 +5411,16 @@
           <t>穩懋</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>528.00</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>+9.0</t>
+        </is>
+      </c>
       <c r="G4" s="4" t="n">
         <v>7641</v>
       </c>
@@ -5439,8 +5447,16 @@
           <t>世界</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr"/>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>174.50</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>+8.0</t>
+        </is>
+      </c>
       <c r="G5" s="4" t="n">
         <v>5052</v>
       </c>
@@ -5471,8 +5487,16 @@
           <t>欣銓</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr"/>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>232.50</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>+21.0</t>
+        </is>
+      </c>
       <c r="G6" s="4" t="n">
         <v>4975</v>
       </c>
@@ -5499,8 +5523,16 @@
           <t>華容</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr"/>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>56.50</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>+5.1</t>
+        </is>
+      </c>
       <c r="G7" s="4" t="n">
         <v>3945</v>
       </c>
@@ -5527,8 +5559,16 @@
           <t>臺慶科</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr"/>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>348.00</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>+31.5</t>
+        </is>
+      </c>
       <c r="G8" s="4" t="n">
         <v>3800</v>
       </c>
@@ -5563,8 +5603,16 @@
           <t>鈺創</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr"/>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>94.00</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>+2.0</t>
+        </is>
+      </c>
       <c r="G9" s="4" t="n">
         <v>3652</v>
       </c>
@@ -5591,8 +5639,16 @@
           <t>頎邦</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr"/>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>252.00</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>+22.5</t>
+        </is>
+      </c>
       <c r="G10" s="4" t="n">
         <v>3499</v>
       </c>
@@ -5619,8 +5675,16 @@
           <t>富喬</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr"/>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>98.10</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>+3.1</t>
+        </is>
+      </c>
       <c r="G11" s="4" t="n">
         <v>3193</v>
       </c>
@@ -5647,8 +5711,16 @@
           <t>尼克森</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr"/>
-      <c r="F12" s="4" t="inlineStr"/>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>88.30</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>+8.0</t>
+        </is>
+      </c>
       <c r="G12" s="4" t="n">
         <v>2952</v>
       </c>
@@ -5683,8 +5755,16 @@
           <t>合晶</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr"/>
-      <c r="F13" s="4" t="inlineStr"/>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>120.00</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>+6.0</t>
+        </is>
+      </c>
       <c r="G13" s="4" t="n">
         <v>1750</v>
       </c>
@@ -5715,8 +5795,16 @@
           <t>金居</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr"/>
-      <c r="F14" s="4" t="inlineStr"/>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>700.00</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>+60.0</t>
+        </is>
+      </c>
       <c r="G14" s="4" t="n">
         <v>1717</v>
       </c>
@@ -5747,8 +5835,16 @@
           <t>宏捷科</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr"/>
-      <c r="F15" s="4" t="inlineStr"/>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>166.00</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>+3.5</t>
+        </is>
+      </c>
       <c r="G15" s="4" t="n">
         <v>1707</v>
       </c>
@@ -5783,8 +5879,16 @@
           <t>光洋科</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr"/>
-      <c r="F16" s="4" t="inlineStr"/>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>149.00</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>+5.5</t>
+        </is>
+      </c>
       <c r="G16" s="4" t="n">
         <v>1556</v>
       </c>
@@ -5815,8 +5919,16 @@
           <t>創惟</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="4" t="inlineStr"/>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>103.50</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>+3.0</t>
+        </is>
+      </c>
       <c r="G17" s="4" t="n">
         <v>1509</v>
       </c>
@@ -5855,8 +5967,16 @@
           <t>鈊象</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr"/>
-      <c r="F18" s="4" t="inlineStr"/>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>793.00</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>+18.0</t>
+        </is>
+      </c>
       <c r="G18" s="4" t="n">
         <v>1389</v>
       </c>
@@ -5887,8 +6007,16 @@
           <t>精材</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr"/>
-      <c r="F19" s="4" t="inlineStr"/>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>251.00</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>+6.5</t>
+        </is>
+      </c>
       <c r="G19" s="4" t="n">
         <v>1336</v>
       </c>
@@ -5923,8 +6051,16 @@
           <t>台星科</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr"/>
-      <c r="F20" s="4" t="inlineStr"/>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>189.50</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>+17.0</t>
+        </is>
+      </c>
       <c r="G20" s="4" t="n">
         <v>1207</v>
       </c>
@@ -5955,8 +6091,16 @@
           <t>國統</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr"/>
-      <c r="F21" s="4" t="inlineStr"/>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>58.10</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>+3.0</t>
+        </is>
+      </c>
       <c r="G21" s="4" t="n">
         <v>1205</v>
       </c>
@@ -5983,8 +6127,16 @@
           <t>原相</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr"/>
-      <c r="F22" s="4" t="inlineStr"/>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>225.00</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>+7.5</t>
+        </is>
+      </c>
       <c r="G22" s="4" t="n">
         <v>1194</v>
       </c>
@@ -6015,8 +6167,16 @@
           <t>亞通</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr"/>
-      <c r="F23" s="4" t="inlineStr"/>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>26.80</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>+1.15</t>
+        </is>
+      </c>
       <c r="G23" s="4" t="n">
         <v>1186</v>
       </c>
@@ -6051,8 +6211,16 @@
           <t>艾訊</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr"/>
-      <c r="F24" s="4" t="inlineStr"/>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>145.00</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>+4.0</t>
+        </is>
+      </c>
       <c r="G24" s="4" t="n">
         <v>1130</v>
       </c>
@@ -6079,8 +6247,16 @@
           <t>台燿</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr"/>
-      <c r="F25" s="4" t="inlineStr"/>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>1835.00</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>+165.0</t>
+        </is>
+      </c>
       <c r="G25" s="4" t="n">
         <v>1116</v>
       </c>
@@ -6111,8 +6287,16 @@
           <t>網家</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr"/>
-      <c r="F26" s="4" t="inlineStr"/>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>31.15</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>+2.8</t>
+        </is>
+      </c>
       <c r="G26" s="4" t="n">
         <v>1098</v>
       </c>
@@ -6147,8 +6331,16 @@
           <t>光環</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr"/>
-      <c r="F27" s="4" t="inlineStr"/>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>145.00</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>+13.0</t>
+        </is>
+      </c>
       <c r="G27" s="4" t="n">
         <v>1078</v>
       </c>
@@ -6175,8 +6367,16 @@
           <t>群聯</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr"/>
-      <c r="F28" s="4" t="inlineStr"/>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>2530.00</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>+200.0</t>
+        </is>
+      </c>
       <c r="G28" s="4" t="n">
         <v>1033</v>
       </c>
@@ -6203,8 +6403,16 @@
           <t>晶焱</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr"/>
-      <c r="F29" s="4" t="inlineStr"/>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>106.50</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>+9.3</t>
+        </is>
+      </c>
       <c r="G29" s="4" t="n">
         <v>978</v>
       </c>
@@ -6239,8 +6447,16 @@
           <t>萬泰科</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr"/>
-      <c r="F30" s="4" t="inlineStr"/>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>82.90</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>+4.6</t>
+        </is>
+      </c>
       <c r="G30" s="4" t="n">
         <v>924</v>
       </c>
@@ -6267,8 +6483,16 @@
           <t>元太</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr"/>
-      <c r="F31" s="4" t="inlineStr"/>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>204.00</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>+5.5</t>
+        </is>
+      </c>
       <c r="G31" s="4" t="n">
         <v>878</v>
       </c>
@@ -6295,8 +6519,16 @@
           <t>信昌電</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr"/>
-      <c r="F32" s="4" t="inlineStr"/>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>316.00</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>+15.5</t>
+        </is>
+      </c>
       <c r="G32" s="4" t="n">
         <v>743</v>
       </c>
@@ -6323,8 +6555,16 @@
           <t>中光電</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr"/>
-      <c r="F33" s="4" t="inlineStr"/>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>70.00</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>+1.1</t>
+        </is>
+      </c>
       <c r="G33" s="4" t="n">
         <v>712</v>
       </c>
@@ -6355,8 +6595,16 @@
           <t>環球晶</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr"/>
-      <c r="F34" s="4" t="inlineStr"/>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>1110.00</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>+10.0</t>
+        </is>
+      </c>
       <c r="G34" s="4" t="n">
         <v>708</v>
       </c>
@@ -6387,8 +6635,16 @@
           <t>九豪</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr"/>
-      <c r="F35" s="4" t="inlineStr"/>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>84.40</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>+3.8</t>
+        </is>
+      </c>
       <c r="G35" s="4" t="n">
         <v>705</v>
       </c>
@@ -6419,8 +6675,16 @@
           <t>系統電</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr"/>
-      <c r="F36" s="4" t="inlineStr"/>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>69.00</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>+1.2</t>
+        </is>
+      </c>
       <c r="G36" s="4" t="n">
         <v>695</v>
       </c>
@@ -6447,8 +6711,16 @@
           <t>安國</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr"/>
-      <c r="F37" s="4" t="inlineStr"/>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>103.50</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>+3.9</t>
+        </is>
+      </c>
       <c r="G37" s="4" t="n">
         <v>672</v>
       </c>
@@ -6475,8 +6747,16 @@
           <t>晟田</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr"/>
-      <c r="F38" s="4" t="inlineStr"/>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>50.90</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>-0.1</t>
+        </is>
+      </c>
       <c r="G38" s="4" t="n">
         <v>658</v>
       </c>
@@ -6507,8 +6787,16 @@
           <t>岳豐</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr"/>
-      <c r="F39" s="4" t="inlineStr"/>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>38.35</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>+2.55</t>
+        </is>
+      </c>
       <c r="G39" s="4" t="n">
         <v>656</v>
       </c>
@@ -6543,8 +6831,16 @@
           <t>威剛</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr"/>
-      <c r="F40" s="4" t="inlineStr"/>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>423.00</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>+7.0</t>
+        </is>
+      </c>
       <c r="G40" s="4" t="n">
         <v>650</v>
       </c>
@@ -6571,8 +6867,16 @@
           <t>順達</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr"/>
-      <c r="F41" s="4" t="inlineStr"/>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>436.00</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>+8.0</t>
+        </is>
+      </c>
       <c r="G41" s="4" t="n">
         <v>638</v>
       </c>
@@ -6603,8 +6907,16 @@
           <t>聯亞</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr"/>
-      <c r="F42" s="4" t="inlineStr"/>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>2440.00</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>+195.0</t>
+        </is>
+      </c>
       <c r="G42" s="4" t="n">
         <v>542</v>
       </c>
@@ -6631,8 +6943,16 @@
           <t>久陽</t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr"/>
-      <c r="F43" s="4" t="inlineStr"/>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>21.60</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>+1.0</t>
+        </is>
+      </c>
       <c r="G43" s="4" t="n">
         <v>541</v>
       </c>
@@ -6667,8 +6987,16 @@
           <t>宜特</t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr"/>
-      <c r="F44" s="4" t="inlineStr"/>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>174.50</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>+5.0</t>
+        </is>
+      </c>
       <c r="G44" s="4" t="n">
         <v>531</v>
       </c>
@@ -6699,8 +7027,16 @@
           <t>家登</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr"/>
-      <c r="F45" s="4" t="inlineStr"/>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>542.00</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>+25.0</t>
+        </is>
+      </c>
       <c r="G45" s="4" t="n">
         <v>519</v>
       </c>
@@ -6727,8 +7063,16 @@
           <t>百徽</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr"/>
-      <c r="F46" s="4" t="inlineStr"/>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>35.85</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>+3.25</t>
+        </is>
+      </c>
       <c r="G46" s="4" t="n">
         <v>514</v>
       </c>
@@ -6763,8 +7107,16 @@
           <t>金益鼎</t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr"/>
-      <c r="F47" s="4" t="inlineStr"/>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>114.00</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>+1.0</t>
+        </is>
+      </c>
       <c r="G47" s="4" t="n">
         <v>491</v>
       </c>
@@ -6791,8 +7143,16 @@
           <t>耀勝</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr"/>
-      <c r="F48" s="4" t="inlineStr"/>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>68.40</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>+0.6</t>
+        </is>
+      </c>
       <c r="G48" s="4" t="n">
         <v>488</v>
       </c>
@@ -6827,8 +7187,16 @@
           <t>典範</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr"/>
-      <c r="F49" s="4" t="inlineStr"/>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>20.40</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>+0.5</t>
+        </is>
+      </c>
       <c r="G49" s="4" t="n">
         <v>475</v>
       </c>
@@ -6855,8 +7223,16 @@
           <t>佶優</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr"/>
-      <c r="F50" s="4" t="inlineStr"/>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>33.90</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>+0.6</t>
+        </is>
+      </c>
       <c r="G50" s="4" t="n">
         <v>423</v>
       </c>
@@ -6887,8 +7263,16 @@
           <t>士開</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr"/>
-      <c r="F51" s="4" t="inlineStr"/>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>12.10</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>-0.0</t>
+        </is>
+      </c>
       <c r="G51" s="4" t="n">
         <v>393</v>
       </c>
@@ -6923,8 +7307,16 @@
           <t>世禾</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr"/>
-      <c r="F52" s="4" t="inlineStr"/>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>208.00</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>+8.5</t>
+        </is>
+      </c>
       <c r="G52" s="4" t="n">
         <v>379</v>
       </c>
@@ -6955,8 +7347,16 @@
           <t>世紀*</t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr"/>
-      <c r="F53" s="4" t="inlineStr"/>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>59.00</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>+2.2</t>
+        </is>
+      </c>
       <c r="G53" s="4" t="n">
         <v>378</v>
       </c>
@@ -6987,8 +7387,16 @@
           <t>茂達</t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr"/>
-      <c r="F54" s="4" t="inlineStr"/>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>358.50</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>+32.5</t>
+        </is>
+      </c>
       <c r="G54" s="4" t="n">
         <v>363</v>
       </c>
@@ -7015,8 +7423,16 @@
           <t>信紘科</t>
         </is>
       </c>
-      <c r="E55" s="4" t="inlineStr"/>
-      <c r="F55" s="4" t="inlineStr"/>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>281.00</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>+4.0</t>
+        </is>
+      </c>
       <c r="G55" s="4" t="n">
         <v>358</v>
       </c>
@@ -7047,8 +7463,16 @@
           <t>信音</t>
         </is>
       </c>
-      <c r="E56" s="4" t="inlineStr"/>
-      <c r="F56" s="4" t="inlineStr"/>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>40.30</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>-0.1</t>
+        </is>
+      </c>
       <c r="G56" s="4" t="n">
         <v>349</v>
       </c>
@@ -7075,8 +7499,16 @@
           <t>越峰</t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr"/>
-      <c r="F57" s="4" t="inlineStr"/>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>53.40</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>+3.75</t>
+        </is>
+      </c>
       <c r="G57" s="4" t="n">
         <v>346</v>
       </c>
@@ -7103,8 +7535,16 @@
           <t>朋程</t>
         </is>
       </c>
-      <c r="E58" s="4" t="inlineStr"/>
-      <c r="F58" s="4" t="inlineStr"/>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>195.00</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>+17.5</t>
+        </is>
+      </c>
       <c r="G58" s="4" t="n">
         <v>345</v>
       </c>
@@ -7131,8 +7571,16 @@
           <t>美琪瑪</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr"/>
-      <c r="F59" s="4" t="inlineStr"/>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>100.50</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>+2.4</t>
+        </is>
+      </c>
       <c r="G59" s="4" t="n">
         <v>323</v>
       </c>
@@ -7159,8 +7607,16 @@
           <t>富強鑫</t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr"/>
-      <c r="F60" s="4" t="inlineStr"/>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>24.20</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>+2.2</t>
+        </is>
+      </c>
       <c r="G60" s="4" t="n">
         <v>321</v>
       </c>
@@ -7187,8 +7643,16 @@
           <t>協易機</t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr"/>
-      <c r="F61" s="4" t="inlineStr"/>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>30.20</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>+0.3</t>
+        </is>
+      </c>
       <c r="G61" s="4" t="n">
         <v>307</v>
       </c>
@@ -7215,8 +7679,16 @@
           <t>尚立</t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr"/>
-      <c r="F62" s="4" t="inlineStr"/>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>16.25</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>-0.35</t>
+        </is>
+      </c>
       <c r="G62" s="4" t="n">
         <v>299</v>
       </c>
@@ -7247,8 +7719,16 @@
           <t>聖暉*</t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr"/>
-      <c r="F63" s="4" t="inlineStr"/>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>1265.00</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>+75.0</t>
+        </is>
+      </c>
       <c r="G63" s="4" t="n">
         <v>295</v>
       </c>
@@ -7279,8 +7759,16 @@
           <t>中天</t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr"/>
-      <c r="F64" s="4" t="inlineStr"/>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>15.05</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>+0.3</t>
+        </is>
+      </c>
       <c r="G64" s="4" t="n">
         <v>282</v>
       </c>
@@ -7307,8 +7795,16 @@
           <t>晶宏</t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr"/>
-      <c r="F65" s="4" t="inlineStr"/>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>74.00</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>+2.4</t>
+        </is>
+      </c>
       <c r="G65" s="4" t="n">
         <v>280</v>
       </c>
@@ -7339,8 +7835,16 @@
           <t>太欣</t>
         </is>
       </c>
-      <c r="E66" s="4" t="inlineStr"/>
-      <c r="F66" s="4" t="inlineStr"/>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>12.55</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>+0.05</t>
+        </is>
+      </c>
       <c r="G66" s="4" t="n">
         <v>279</v>
       </c>
@@ -7371,8 +7875,16 @@
           <t>富致</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr"/>
-      <c r="F67" s="4" t="inlineStr"/>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>90.60</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>+4.7</t>
+        </is>
+      </c>
       <c r="G67" s="4" t="n">
         <v>273</v>
       </c>
@@ -7407,8 +7919,16 @@
           <t>松普</t>
         </is>
       </c>
-      <c r="E68" s="4" t="inlineStr"/>
-      <c r="F68" s="4" t="inlineStr"/>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>12.45</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>-0.15</t>
+        </is>
+      </c>
       <c r="G68" s="4" t="n">
         <v>257</v>
       </c>
@@ -7443,8 +7963,16 @@
           <t>凱崴</t>
         </is>
       </c>
-      <c r="E69" s="4" t="inlineStr"/>
-      <c r="F69" s="4" t="inlineStr"/>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>67.10</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>+0.7</t>
+        </is>
+      </c>
       <c r="G69" s="4" t="n">
         <v>253</v>
       </c>
@@ -7471,8 +7999,16 @@
           <t>IET-KY</t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr"/>
-      <c r="F70" s="4" t="inlineStr"/>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>578.00</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>+52.0</t>
+        </is>
+      </c>
       <c r="G70" s="4" t="n">
         <v>251</v>
       </c>
@@ -7499,8 +8035,16 @@
           <t>艾華</t>
         </is>
       </c>
-      <c r="E71" s="4" t="inlineStr"/>
-      <c r="F71" s="4" t="inlineStr"/>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>115.00</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>+8.5</t>
+        </is>
+      </c>
       <c r="G71" s="4" t="n">
         <v>250</v>
       </c>
@@ -7527,8 +8071,16 @@
           <t>聯寶</t>
         </is>
       </c>
-      <c r="E72" s="4" t="inlineStr"/>
-      <c r="F72" s="4" t="inlineStr"/>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>67.60</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>+6.1</t>
+        </is>
+      </c>
       <c r="G72" s="4" t="n">
         <v>248</v>
       </c>
@@ -7555,8 +8107,16 @@
           <t>港建*</t>
         </is>
       </c>
-      <c r="E73" s="4" t="inlineStr"/>
-      <c r="F73" s="4" t="inlineStr"/>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>65.00</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>+0.6</t>
+        </is>
+      </c>
       <c r="G73" s="4" t="n">
         <v>246</v>
       </c>
@@ -7583,8 +8143,16 @@
           <t>應廣</t>
         </is>
       </c>
-      <c r="E74" s="4" t="inlineStr"/>
-      <c r="F74" s="4" t="inlineStr"/>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>102.50</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>+2.0</t>
+        </is>
+      </c>
       <c r="G74" s="4" t="n">
         <v>245</v>
       </c>
@@ -7619,8 +8187,16 @@
           <t>慶騰</t>
         </is>
       </c>
-      <c r="E75" s="4" t="inlineStr"/>
-      <c r="F75" s="4" t="inlineStr"/>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>33.65</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>-0.0</t>
+        </is>
+      </c>
       <c r="G75" s="4" t="n">
         <v>235</v>
       </c>
@@ -7647,8 +8223,16 @@
           <t>建榮</t>
         </is>
       </c>
-      <c r="E76" s="4" t="inlineStr"/>
-      <c r="F76" s="4" t="inlineStr"/>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>90.00</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>+2.2</t>
+        </is>
+      </c>
       <c r="G76" s="4" t="n">
         <v>233</v>
       </c>
@@ -7675,8 +8259,16 @@
           <t>新鉅科</t>
         </is>
       </c>
-      <c r="E77" s="4" t="inlineStr"/>
-      <c r="F77" s="4" t="inlineStr"/>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>34.80</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
       <c r="G77" s="4" t="n">
         <v>230</v>
       </c>
@@ -7703,8 +8295,16 @@
           <t>致和證</t>
         </is>
       </c>
-      <c r="E78" s="4" t="inlineStr"/>
-      <c r="F78" s="4" t="inlineStr"/>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>49.05</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>+0.55</t>
+        </is>
+      </c>
       <c r="G78" s="4" t="n">
         <v>230</v>
       </c>
@@ -7735,8 +8335,16 @@
           <t>松瑞藥</t>
         </is>
       </c>
-      <c r="E79" s="4" t="inlineStr"/>
-      <c r="F79" s="4" t="inlineStr"/>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>19.95</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>+0.1</t>
+        </is>
+      </c>
       <c r="G79" s="4" t="n">
         <v>228</v>
       </c>
@@ -7763,8 +8371,16 @@
           <t>合一</t>
         </is>
       </c>
-      <c r="E80" s="4" t="inlineStr"/>
-      <c r="F80" s="4" t="inlineStr"/>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>48.00</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>+0.45</t>
+        </is>
+      </c>
       <c r="G80" s="4" t="n">
         <v>228</v>
       </c>
@@ -7791,8 +8407,16 @@
           <t>德宏</t>
         </is>
       </c>
-      <c r="E81" s="4" t="inlineStr"/>
-      <c r="F81" s="4" t="inlineStr"/>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>252.00</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>+22.5</t>
+        </is>
+      </c>
       <c r="G81" s="4" t="n">
         <v>228</v>
       </c>
@@ -7823,8 +8447,16 @@
           <t>力麒</t>
         </is>
       </c>
-      <c r="E82" s="4" t="inlineStr"/>
-      <c r="F82" s="4" t="inlineStr"/>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>7.95</t>
+        </is>
+      </c>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>-0.0</t>
+        </is>
+      </c>
       <c r="G82" s="4" t="n">
         <v>225</v>
       </c>
@@ -7855,8 +8487,16 @@
           <t>胡連</t>
         </is>
       </c>
-      <c r="E83" s="4" t="inlineStr"/>
-      <c r="F83" s="4" t="inlineStr"/>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>120.50</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>+2.5</t>
+        </is>
+      </c>
       <c r="G83" s="4" t="n">
         <v>217</v>
       </c>
@@ -7887,8 +8527,16 @@
           <t>宜鼎</t>
         </is>
       </c>
-      <c r="E84" s="4" t="inlineStr"/>
-      <c r="F84" s="4" t="inlineStr"/>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>1930.00</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>+75.0</t>
+        </is>
+      </c>
       <c r="G84" s="4" t="n">
         <v>214</v>
       </c>
@@ -7919,8 +8567,16 @@
           <t>千附</t>
         </is>
       </c>
-      <c r="E85" s="4" t="inlineStr"/>
-      <c r="F85" s="4" t="inlineStr"/>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>60.40</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>+0.3</t>
+        </is>
+      </c>
       <c r="G85" s="4" t="n">
         <v>213</v>
       </c>
@@ -7947,8 +8603,16 @@
           <t>建舜電</t>
         </is>
       </c>
-      <c r="E86" s="4" t="inlineStr"/>
-      <c r="F86" s="4" t="inlineStr"/>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>14.85</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>+0.15</t>
+        </is>
+      </c>
       <c r="G86" s="4" t="n">
         <v>210</v>
       </c>
@@ -7975,8 +8639,16 @@
           <t>廣積</t>
         </is>
       </c>
-      <c r="E87" s="4" t="inlineStr"/>
-      <c r="F87" s="4" t="inlineStr"/>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>55.70</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>+0.8</t>
+        </is>
+      </c>
       <c r="G87" s="4" t="n">
         <v>210</v>
       </c>
@@ -8003,8 +8675,16 @@
           <t>寬魚國際</t>
         </is>
       </c>
-      <c r="E88" s="4" t="inlineStr"/>
-      <c r="F88" s="4" t="inlineStr"/>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>41.65</t>
+        </is>
+      </c>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t>+1.15</t>
+        </is>
+      </c>
       <c r="G88" s="4" t="n">
         <v>209</v>
       </c>
@@ -8039,8 +8719,16 @@
           <t>弘塑</t>
         </is>
       </c>
-      <c r="E89" s="4" t="inlineStr"/>
-      <c r="F89" s="4" t="inlineStr"/>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>3520.00</t>
+        </is>
+      </c>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t>+275.0</t>
+        </is>
+      </c>
       <c r="G89" s="4" t="n">
         <v>207</v>
       </c>
@@ -8067,8 +8755,16 @@
           <t>廣閎科</t>
         </is>
       </c>
-      <c r="E90" s="4" t="inlineStr"/>
-      <c r="F90" s="4" t="inlineStr"/>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>215.00</t>
+        </is>
+      </c>
+      <c r="F90" s="4" t="inlineStr">
+        <is>
+          <t>+19.5</t>
+        </is>
+      </c>
       <c r="G90" s="4" t="n">
         <v>197</v>
       </c>
@@ -8099,8 +8795,16 @@
           <t>邦泰</t>
         </is>
       </c>
-      <c r="E91" s="4" t="inlineStr"/>
-      <c r="F91" s="4" t="inlineStr"/>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>22.75</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>+0.7</t>
+        </is>
+      </c>
       <c r="G91" s="4" t="n">
         <v>197</v>
       </c>
@@ -8127,8 +8831,16 @@
           <t>研通</t>
         </is>
       </c>
-      <c r="E92" s="4" t="inlineStr"/>
-      <c r="F92" s="4" t="inlineStr"/>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>27.75</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t>+1.3</t>
+        </is>
+      </c>
       <c r="G92" s="4" t="n">
         <v>196</v>
       </c>
@@ -8163,8 +8875,16 @@
           <t>台嘉碩</t>
         </is>
       </c>
-      <c r="E93" s="4" t="inlineStr"/>
-      <c r="F93" s="4" t="inlineStr"/>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>60.50</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>+1.2</t>
+        </is>
+      </c>
       <c r="G93" s="4" t="n">
         <v>190</v>
       </c>
@@ -8191,8 +8911,16 @@
           <t>好德</t>
         </is>
       </c>
-      <c r="E94" s="4" t="inlineStr"/>
-      <c r="F94" s="4" t="inlineStr"/>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>47.75</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t>+4.3</t>
+        </is>
+      </c>
       <c r="G94" s="4" t="n">
         <v>188</v>
       </c>
@@ -8223,8 +8951,16 @@
           <t>中裕</t>
         </is>
       </c>
-      <c r="E95" s="4" t="inlineStr"/>
-      <c r="F95" s="4" t="inlineStr"/>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>57.20</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>-0.0</t>
+        </is>
+      </c>
       <c r="G95" s="4" t="n">
         <v>187</v>
       </c>
@@ -8251,8 +8987,16 @@
           <t>伍豐</t>
         </is>
       </c>
-      <c r="E96" s="4" t="inlineStr"/>
-      <c r="F96" s="4" t="inlineStr"/>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>25.75</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>+0.2</t>
+        </is>
+      </c>
       <c r="G96" s="4" t="n">
         <v>181</v>
       </c>
@@ -8283,8 +9027,16 @@
           <t>大江</t>
         </is>
       </c>
-      <c r="E97" s="4" t="inlineStr"/>
-      <c r="F97" s="4" t="inlineStr"/>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>118.00</t>
+        </is>
+      </c>
+      <c r="F97" s="4" t="inlineStr">
+        <is>
+          <t>+1.0</t>
+        </is>
+      </c>
       <c r="G97" s="4" t="n">
         <v>181</v>
       </c>
@@ -8311,8 +9063,16 @@
           <t>寶碩</t>
         </is>
       </c>
-      <c r="E98" s="4" t="inlineStr"/>
-      <c r="F98" s="4" t="inlineStr"/>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>30.00</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>+0.35</t>
+        </is>
+      </c>
       <c r="G98" s="4" t="n">
         <v>174</v>
       </c>
@@ -8339,8 +9099,16 @@
           <t>智冠</t>
         </is>
       </c>
-      <c r="E99" s="4" t="inlineStr"/>
-      <c r="F99" s="4" t="inlineStr"/>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>106.50</t>
+        </is>
+      </c>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t>+1.5</t>
+        </is>
+      </c>
       <c r="G99" s="4" t="n">
         <v>174</v>
       </c>
@@ -8367,8 +9135,16 @@
           <t>湧德</t>
         </is>
       </c>
-      <c r="E100" s="4" t="inlineStr"/>
-      <c r="F100" s="4" t="inlineStr"/>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t>121.00</t>
+        </is>
+      </c>
+      <c r="F100" s="4" t="inlineStr">
+        <is>
+          <t>+2.5</t>
+        </is>
+      </c>
       <c r="G100" s="4" t="n">
         <v>173</v>
       </c>
@@ -8395,8 +9171,16 @@
           <t>久元</t>
         </is>
       </c>
-      <c r="E101" s="4" t="inlineStr"/>
-      <c r="F101" s="4" t="inlineStr"/>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t>98.80</t>
+        </is>
+      </c>
+      <c r="F101" s="4" t="inlineStr">
+        <is>
+          <t>+4.4</t>
+        </is>
+      </c>
       <c r="G101" s="4" t="n">
         <v>168</v>
       </c>
@@ -8423,8 +9207,16 @@
           <t>泓瀚</t>
         </is>
       </c>
-      <c r="E102" s="4" t="inlineStr"/>
-      <c r="F102" s="4" t="inlineStr"/>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t>64.60</t>
+        </is>
+      </c>
+      <c r="F102" s="4" t="inlineStr">
+        <is>
+          <t>-7.1</t>
+        </is>
+      </c>
       <c r="G102" s="4" t="n">
         <v>166</v>
       </c>
@@ -8451,8 +9243,16 @@
           <t>健喬</t>
         </is>
       </c>
-      <c r="E103" s="4" t="inlineStr"/>
-      <c r="F103" s="4" t="inlineStr"/>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t>30.95</t>
+        </is>
+      </c>
+      <c r="F103" s="4" t="inlineStr">
+        <is>
+          <t>+0.15</t>
+        </is>
+      </c>
       <c r="G103" s="4" t="n">
         <v>160</v>
       </c>
@@ -8587,8 +9387,16 @@
           <t>中美晶</t>
         </is>
       </c>
-      <c r="E109" s="4" t="inlineStr"/>
-      <c r="F109" s="4" t="inlineStr"/>
+      <c r="E109" s="4" t="inlineStr">
+        <is>
+          <t>181.00</t>
+        </is>
+      </c>
+      <c r="F109" s="4" t="inlineStr">
+        <is>
+          <t>-1.5</t>
+        </is>
+      </c>
       <c r="G109" s="4" t="n">
         <v>-3483</v>
       </c>
@@ -8619,8 +9427,16 @@
           <t>康和證</t>
         </is>
       </c>
-      <c r="E110" s="4" t="inlineStr"/>
-      <c r="F110" s="4" t="inlineStr"/>
+      <c r="E110" s="4" t="inlineStr">
+        <is>
+          <t>28.80</t>
+        </is>
+      </c>
+      <c r="F110" s="4" t="inlineStr">
+        <is>
+          <t>+0.05</t>
+        </is>
+      </c>
       <c r="G110" s="4" t="n">
         <v>-3305</v>
       </c>
@@ -8651,8 +9467,16 @@
           <t>雷科</t>
         </is>
       </c>
-      <c r="E111" s="4" t="inlineStr"/>
-      <c r="F111" s="4" t="inlineStr"/>
+      <c r="E111" s="4" t="inlineStr">
+        <is>
+          <t>165.50</t>
+        </is>
+      </c>
+      <c r="F111" s="4" t="inlineStr">
+        <is>
+          <t>+1.5</t>
+        </is>
+      </c>
       <c r="G111" s="4" t="n">
         <v>-2709</v>
       </c>
@@ -8679,8 +9503,16 @@
           <t>良維</t>
         </is>
       </c>
-      <c r="E112" s="4" t="inlineStr"/>
-      <c r="F112" s="4" t="inlineStr"/>
+      <c r="E112" s="4" t="inlineStr">
+        <is>
+          <t>319.50</t>
+        </is>
+      </c>
+      <c r="F112" s="4" t="inlineStr">
+        <is>
+          <t>+15.5</t>
+        </is>
+      </c>
       <c r="G112" s="4" t="n">
         <v>-2291</v>
       </c>
@@ -8711,8 +9543,16 @@
           <t>茂迪</t>
         </is>
       </c>
-      <c r="E113" s="4" t="inlineStr"/>
-      <c r="F113" s="4" t="inlineStr"/>
+      <c r="E113" s="4" t="inlineStr">
+        <is>
+          <t>28.45</t>
+        </is>
+      </c>
+      <c r="F113" s="4" t="inlineStr">
+        <is>
+          <t>-0.7</t>
+        </is>
+      </c>
       <c r="G113" s="4" t="n">
         <v>-2052</v>
       </c>
@@ -8739,8 +9579,16 @@
           <t>品安</t>
         </is>
       </c>
-      <c r="E114" s="4" t="inlineStr"/>
-      <c r="F114" s="4" t="inlineStr"/>
+      <c r="E114" s="4" t="inlineStr">
+        <is>
+          <t>69.20</t>
+        </is>
+      </c>
+      <c r="F114" s="4" t="inlineStr">
+        <is>
+          <t>+4.4</t>
+        </is>
+      </c>
       <c r="G114" s="4" t="n">
         <v>-1920</v>
       </c>
@@ -8779,8 +9627,16 @@
           <t>長科*</t>
         </is>
       </c>
-      <c r="E115" s="4" t="inlineStr"/>
-      <c r="F115" s="4" t="inlineStr"/>
+      <c r="E115" s="4" t="inlineStr">
+        <is>
+          <t>86.10</t>
+        </is>
+      </c>
+      <c r="F115" s="4" t="inlineStr">
+        <is>
+          <t>-3.0</t>
+        </is>
+      </c>
       <c r="G115" s="4" t="n">
         <v>-1882</v>
       </c>
@@ -8807,8 +9663,16 @@
           <t>立敦</t>
         </is>
       </c>
-      <c r="E116" s="4" t="inlineStr"/>
-      <c r="F116" s="4" t="inlineStr"/>
+      <c r="E116" s="4" t="inlineStr">
+        <is>
+          <t>114.00</t>
+        </is>
+      </c>
+      <c r="F116" s="4" t="inlineStr">
+        <is>
+          <t>+6.5</t>
+        </is>
+      </c>
       <c r="G116" s="4" t="n">
         <v>-1665</v>
       </c>
@@ -8835,8 +9699,16 @@
           <t>蜜望實</t>
         </is>
       </c>
-      <c r="E117" s="4" t="inlineStr"/>
-      <c r="F117" s="4" t="inlineStr"/>
+      <c r="E117" s="4" t="inlineStr">
+        <is>
+          <t>226.50</t>
+        </is>
+      </c>
+      <c r="F117" s="4" t="inlineStr">
+        <is>
+          <t>+6.5</t>
+        </is>
+      </c>
       <c r="G117" s="4" t="n">
         <v>-1310</v>
       </c>
@@ -8863,8 +9735,16 @@
           <t>波若威</t>
         </is>
       </c>
-      <c r="E118" s="4" t="inlineStr"/>
-      <c r="F118" s="4" t="inlineStr"/>
+      <c r="E118" s="4" t="inlineStr">
+        <is>
+          <t>893.00</t>
+        </is>
+      </c>
+      <c r="F118" s="4" t="inlineStr">
+        <is>
+          <t>-10.0</t>
+        </is>
+      </c>
       <c r="G118" s="4" t="n">
         <v>-1289</v>
       </c>
@@ -8899,8 +9779,16 @@
           <t>橘子</t>
         </is>
       </c>
-      <c r="E119" s="4" t="inlineStr"/>
-      <c r="F119" s="4" t="inlineStr"/>
+      <c r="E119" s="4" t="inlineStr">
+        <is>
+          <t>50.30</t>
+        </is>
+      </c>
+      <c r="F119" s="4" t="inlineStr">
+        <is>
+          <t>-0.1</t>
+        </is>
+      </c>
       <c r="G119" s="4" t="n">
         <v>-1089</v>
       </c>
@@ -8939,8 +9827,16 @@
           <t>先進光</t>
         </is>
       </c>
-      <c r="E120" s="4" t="inlineStr"/>
-      <c r="F120" s="4" t="inlineStr"/>
+      <c r="E120" s="4" t="inlineStr">
+        <is>
+          <t>211.00</t>
+        </is>
+      </c>
+      <c r="F120" s="4" t="inlineStr">
+        <is>
+          <t>+3.5</t>
+        </is>
+      </c>
       <c r="G120" s="4" t="n">
         <v>-932</v>
       </c>
@@ -8967,8 +9863,16 @@
           <t>東捷</t>
         </is>
       </c>
-      <c r="E121" s="4" t="inlineStr"/>
-      <c r="F121" s="4" t="inlineStr"/>
+      <c r="E121" s="4" t="inlineStr">
+        <is>
+          <t>156.00</t>
+        </is>
+      </c>
+      <c r="F121" s="4" t="inlineStr">
+        <is>
+          <t>+2.0</t>
+        </is>
+      </c>
       <c r="G121" s="4" t="n">
         <v>-925</v>
       </c>
@@ -8999,8 +9903,16 @@
           <t>中探針</t>
         </is>
       </c>
-      <c r="E122" s="4" t="inlineStr"/>
-      <c r="F122" s="4" t="inlineStr"/>
+      <c r="E122" s="4" t="inlineStr">
+        <is>
+          <t>247.00</t>
+        </is>
+      </c>
+      <c r="F122" s="4" t="inlineStr">
+        <is>
+          <t>+13.5</t>
+        </is>
+      </c>
       <c r="G122" s="4" t="n">
         <v>-902</v>
       </c>
@@ -9035,8 +9947,16 @@
           <t>能率</t>
         </is>
       </c>
-      <c r="E123" s="4" t="inlineStr"/>
-      <c r="F123" s="4" t="inlineStr"/>
+      <c r="E123" s="4" t="inlineStr">
+        <is>
+          <t>43.30</t>
+        </is>
+      </c>
+      <c r="F123" s="4" t="inlineStr">
+        <is>
+          <t>-1.55</t>
+        </is>
+      </c>
       <c r="G123" s="4" t="n">
         <v>-887</v>
       </c>
@@ -9067,8 +9987,16 @@
           <t>福邦證</t>
         </is>
       </c>
-      <c r="E124" s="4" t="inlineStr"/>
-      <c r="F124" s="4" t="inlineStr"/>
+      <c r="E124" s="4" t="inlineStr">
+        <is>
+          <t>17.05</t>
+        </is>
+      </c>
+      <c r="F124" s="4" t="inlineStr">
+        <is>
+          <t>+0.05</t>
+        </is>
+      </c>
       <c r="G124" s="4" t="n">
         <v>-791</v>
       </c>
@@ -9099,8 +10027,16 @@
           <t>風青</t>
         </is>
       </c>
-      <c r="E125" s="4" t="inlineStr"/>
-      <c r="F125" s="4" t="inlineStr"/>
+      <c r="E125" s="4" t="inlineStr">
+        <is>
+          <t>52.80</t>
+        </is>
+      </c>
+      <c r="F125" s="4" t="inlineStr">
+        <is>
+          <t>+4.75</t>
+        </is>
+      </c>
       <c r="G125" s="4" t="n">
         <v>-785</v>
       </c>
@@ -9139,8 +10075,16 @@
           <t>榮剛</t>
         </is>
       </c>
-      <c r="E126" s="4" t="inlineStr"/>
-      <c r="F126" s="4" t="inlineStr"/>
+      <c r="E126" s="4" t="inlineStr">
+        <is>
+          <t>34.75</t>
+        </is>
+      </c>
+      <c r="F126" s="4" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
       <c r="G126" s="4" t="n">
         <v>-770</v>
       </c>
@@ -9167,8 +10111,16 @@
           <t>聚和</t>
         </is>
       </c>
-      <c r="E127" s="4" t="inlineStr"/>
-      <c r="F127" s="4" t="inlineStr"/>
+      <c r="E127" s="4" t="inlineStr">
+        <is>
+          <t>47.95</t>
+        </is>
+      </c>
+      <c r="F127" s="4" t="inlineStr">
+        <is>
+          <t>+0.65</t>
+        </is>
+      </c>
       <c r="G127" s="4" t="n">
         <v>-752</v>
       </c>
@@ -9199,8 +10151,16 @@
           <t>磐亞</t>
         </is>
       </c>
-      <c r="E128" s="4" t="inlineStr"/>
-      <c r="F128" s="4" t="inlineStr"/>
+      <c r="E128" s="4" t="inlineStr">
+        <is>
+          <t>23.00</t>
+        </is>
+      </c>
+      <c r="F128" s="4" t="inlineStr">
+        <is>
+          <t>+0.4</t>
+        </is>
+      </c>
       <c r="G128" s="4" t="n">
         <v>-614</v>
       </c>
@@ -9231,8 +10191,16 @@
           <t>宣德</t>
         </is>
       </c>
-      <c r="E129" s="4" t="inlineStr"/>
-      <c r="F129" s="4" t="inlineStr"/>
+      <c r="E129" s="4" t="inlineStr">
+        <is>
+          <t>37.10</t>
+        </is>
+      </c>
+      <c r="F129" s="4" t="inlineStr">
+        <is>
+          <t>+0.35</t>
+        </is>
+      </c>
       <c r="G129" s="4" t="n">
         <v>-591</v>
       </c>
@@ -9263,8 +10231,16 @@
           <t>聯一光</t>
         </is>
       </c>
-      <c r="E130" s="4" t="inlineStr"/>
-      <c r="F130" s="4" t="inlineStr"/>
+      <c r="E130" s="4" t="inlineStr">
+        <is>
+          <t>92.30</t>
+        </is>
+      </c>
+      <c r="F130" s="4" t="inlineStr">
+        <is>
+          <t>+3.2</t>
+        </is>
+      </c>
       <c r="G130" s="4" t="n">
         <v>-553</v>
       </c>
@@ -9291,8 +10267,16 @@
           <t>南仁湖</t>
         </is>
       </c>
-      <c r="E131" s="4" t="inlineStr"/>
-      <c r="F131" s="4" t="inlineStr"/>
+      <c r="E131" s="4" t="inlineStr">
+        <is>
+          <t>8.70</t>
+        </is>
+      </c>
+      <c r="F131" s="4" t="inlineStr">
+        <is>
+          <t>-0.2</t>
+        </is>
+      </c>
       <c r="G131" s="4" t="n">
         <v>-545</v>
       </c>
@@ -9327,8 +10311,16 @@
           <t>千如</t>
         </is>
       </c>
-      <c r="E132" s="4" t="inlineStr"/>
-      <c r="F132" s="4" t="inlineStr"/>
+      <c r="E132" s="4" t="inlineStr">
+        <is>
+          <t>71.00</t>
+        </is>
+      </c>
+      <c r="F132" s="4" t="inlineStr">
+        <is>
+          <t>+3.9</t>
+        </is>
+      </c>
       <c r="G132" s="4" t="n">
         <v>-537</v>
       </c>
@@ -9359,8 +10351,16 @@
           <t>禾瑞亞</t>
         </is>
       </c>
-      <c r="E133" s="4" t="inlineStr"/>
-      <c r="F133" s="4" t="inlineStr"/>
+      <c r="E133" s="4" t="inlineStr">
+        <is>
+          <t>74.00</t>
+        </is>
+      </c>
+      <c r="F133" s="4" t="inlineStr">
+        <is>
+          <t>-2.4</t>
+        </is>
+      </c>
       <c r="G133" s="4" t="n">
         <v>-513</v>
       </c>
@@ -9395,8 +10395,16 @@
           <t>華電網</t>
         </is>
       </c>
-      <c r="E134" s="4" t="inlineStr"/>
-      <c r="F134" s="4" t="inlineStr"/>
+      <c r="E134" s="4" t="inlineStr">
+        <is>
+          <t>49.95</t>
+        </is>
+      </c>
+      <c r="F134" s="4" t="inlineStr">
+        <is>
+          <t>-0.75</t>
+        </is>
+      </c>
       <c r="G134" s="4" t="n">
         <v>-477</v>
       </c>
@@ -9423,8 +10431,16 @@
           <t>智通*</t>
         </is>
       </c>
-      <c r="E135" s="4" t="inlineStr"/>
-      <c r="F135" s="4" t="inlineStr"/>
+      <c r="E135" s="4" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="F135" s="4" t="inlineStr">
+        <is>
+          <t>-0.0</t>
+        </is>
+      </c>
       <c r="G135" s="4" t="n">
         <v>-471</v>
       </c>
@@ -9455,8 +10471,16 @@
           <t>永信建</t>
         </is>
       </c>
-      <c r="E136" s="4" t="inlineStr"/>
-      <c r="F136" s="4" t="inlineStr"/>
+      <c r="E136" s="4" t="inlineStr">
+        <is>
+          <t>61.70</t>
+        </is>
+      </c>
+      <c r="F136" s="4" t="inlineStr">
+        <is>
+          <t>+0.6</t>
+        </is>
+      </c>
       <c r="G136" s="4" t="n">
         <v>-463</v>
       </c>
@@ -9487,8 +10511,16 @@
           <t>高端疫苗</t>
         </is>
       </c>
-      <c r="E137" s="4" t="inlineStr"/>
-      <c r="F137" s="4" t="inlineStr"/>
+      <c r="E137" s="4" t="inlineStr">
+        <is>
+          <t>45.20</t>
+        </is>
+      </c>
+      <c r="F137" s="4" t="inlineStr">
+        <is>
+          <t>-0.3</t>
+        </is>
+      </c>
       <c r="G137" s="4" t="n">
         <v>-409</v>
       </c>
@@ -9519,8 +10551,16 @@
           <t>大國鋼</t>
         </is>
       </c>
-      <c r="E138" s="4" t="inlineStr"/>
-      <c r="F138" s="4" t="inlineStr"/>
+      <c r="E138" s="4" t="inlineStr">
+        <is>
+          <t>34.45</t>
+        </is>
+      </c>
+      <c r="F138" s="4" t="inlineStr">
+        <is>
+          <t>-0.9</t>
+        </is>
+      </c>
       <c r="G138" s="4" t="n">
         <v>-408</v>
       </c>
@@ -9551,8 +10591,16 @@
           <t>松上</t>
         </is>
       </c>
-      <c r="E139" s="4" t="inlineStr"/>
-      <c r="F139" s="4" t="inlineStr"/>
+      <c r="E139" s="4" t="inlineStr">
+        <is>
+          <t>24.35</t>
+        </is>
+      </c>
+      <c r="F139" s="4" t="inlineStr">
+        <is>
+          <t>+1.0</t>
+        </is>
+      </c>
       <c r="G139" s="4" t="n">
         <v>-394</v>
       </c>
@@ -9579,8 +10627,16 @@
           <t>華星光</t>
         </is>
       </c>
-      <c r="E140" s="4" t="inlineStr"/>
-      <c r="F140" s="4" t="inlineStr"/>
+      <c r="E140" s="4" t="inlineStr">
+        <is>
+          <t>567.00</t>
+        </is>
+      </c>
+      <c r="F140" s="4" t="inlineStr">
+        <is>
+          <t>+21.0</t>
+        </is>
+      </c>
       <c r="G140" s="4" t="n">
         <v>-390</v>
       </c>
@@ -9607,8 +10663,16 @@
           <t>台半</t>
         </is>
       </c>
-      <c r="E141" s="4" t="inlineStr"/>
-      <c r="F141" s="4" t="inlineStr"/>
+      <c r="E141" s="4" t="inlineStr">
+        <is>
+          <t>118.50</t>
+        </is>
+      </c>
+      <c r="F141" s="4" t="inlineStr">
+        <is>
+          <t>+10.5</t>
+        </is>
+      </c>
       <c r="G141" s="4" t="n">
         <v>-388</v>
       </c>
@@ -9635,8 +10699,16 @@
           <t>安碁</t>
         </is>
       </c>
-      <c r="E142" s="4" t="inlineStr"/>
-      <c r="F142" s="4" t="inlineStr"/>
+      <c r="E142" s="4" t="inlineStr">
+        <is>
+          <t>52.30</t>
+        </is>
+      </c>
+      <c r="F142" s="4" t="inlineStr">
+        <is>
+          <t>-0.6</t>
+        </is>
+      </c>
       <c r="G142" s="4" t="n">
         <v>-380</v>
       </c>
@@ -9663,8 +10735,16 @@
           <t>安勤</t>
         </is>
       </c>
-      <c r="E143" s="4" t="inlineStr"/>
-      <c r="F143" s="4" t="inlineStr"/>
+      <c r="E143" s="4" t="inlineStr">
+        <is>
+          <t>136.50</t>
+        </is>
+      </c>
+      <c r="F143" s="4" t="inlineStr">
+        <is>
+          <t>+3.0</t>
+        </is>
+      </c>
       <c r="G143" s="4" t="n">
         <v>-375</v>
       </c>
@@ -9691,8 +10771,16 @@
           <t>堡達</t>
         </is>
       </c>
-      <c r="E144" s="4" t="inlineStr"/>
-      <c r="F144" s="4" t="inlineStr"/>
+      <c r="E144" s="4" t="inlineStr">
+        <is>
+          <t>89.60</t>
+        </is>
+      </c>
+      <c r="F144" s="4" t="inlineStr">
+        <is>
+          <t>+8.1</t>
+        </is>
+      </c>
       <c r="G144" s="4" t="n">
         <v>-372</v>
       </c>
@@ -9719,8 +10807,16 @@
           <t>高技</t>
         </is>
       </c>
-      <c r="E145" s="4" t="inlineStr"/>
-      <c r="F145" s="4" t="inlineStr"/>
+      <c r="E145" s="4" t="inlineStr">
+        <is>
+          <t>332.50</t>
+        </is>
+      </c>
+      <c r="F145" s="4" t="inlineStr">
+        <is>
+          <t>+9.0</t>
+        </is>
+      </c>
       <c r="G145" s="4" t="n">
         <v>-363</v>
       </c>
@@ -9751,8 +10847,16 @@
           <t>威潤</t>
         </is>
       </c>
-      <c r="E146" s="4" t="inlineStr"/>
-      <c r="F146" s="4" t="inlineStr"/>
+      <c r="E146" s="4" t="inlineStr">
+        <is>
+          <t>71.20</t>
+        </is>
+      </c>
+      <c r="F146" s="4" t="inlineStr">
+        <is>
+          <t>+0.8</t>
+        </is>
+      </c>
       <c r="G146" s="4" t="n">
         <v>-331</v>
       </c>
@@ -9787,8 +10891,16 @@
           <t>佳邦</t>
         </is>
       </c>
-      <c r="E147" s="4" t="inlineStr"/>
-      <c r="F147" s="4" t="inlineStr"/>
+      <c r="E147" s="4" t="inlineStr">
+        <is>
+          <t>106.00</t>
+        </is>
+      </c>
+      <c r="F147" s="4" t="inlineStr">
+        <is>
+          <t>-1.5</t>
+        </is>
+      </c>
       <c r="G147" s="4" t="n">
         <v>-317</v>
       </c>
@@ -9815,8 +10927,16 @@
           <t>太普高</t>
         </is>
       </c>
-      <c r="E148" s="4" t="inlineStr"/>
-      <c r="F148" s="4" t="inlineStr"/>
+      <c r="E148" s="4" t="inlineStr">
+        <is>
+          <t>22.70</t>
+        </is>
+      </c>
+      <c r="F148" s="4" t="inlineStr">
+        <is>
+          <t>+0.5</t>
+        </is>
+      </c>
       <c r="G148" s="4" t="n">
         <v>-314</v>
       </c>
@@ -9851,8 +10971,16 @@
           <t>泰藝</t>
         </is>
       </c>
-      <c r="E149" s="4" t="inlineStr"/>
-      <c r="F149" s="4" t="inlineStr"/>
+      <c r="E149" s="4" t="inlineStr">
+        <is>
+          <t>67.10</t>
+        </is>
+      </c>
+      <c r="F149" s="4" t="inlineStr">
+        <is>
+          <t>-1.6</t>
+        </is>
+      </c>
       <c r="G149" s="4" t="n">
         <v>-312</v>
       </c>
@@ -9879,8 +11007,16 @@
           <t>大立</t>
         </is>
       </c>
-      <c r="E150" s="4" t="inlineStr"/>
-      <c r="F150" s="4" t="inlineStr"/>
+      <c r="E150" s="4" t="inlineStr">
+        <is>
+          <t>18.25</t>
+        </is>
+      </c>
+      <c r="F150" s="4" t="inlineStr">
+        <is>
+          <t>+1.05</t>
+        </is>
+      </c>
       <c r="G150" s="4" t="n">
         <v>-310</v>
       </c>
@@ -9907,8 +11043,16 @@
           <t>廣穎</t>
         </is>
       </c>
-      <c r="E151" s="4" t="inlineStr"/>
-      <c r="F151" s="4" t="inlineStr"/>
+      <c r="E151" s="4" t="inlineStr">
+        <is>
+          <t>193.50</t>
+        </is>
+      </c>
+      <c r="F151" s="4" t="inlineStr">
+        <is>
+          <t>+2.0</t>
+        </is>
+      </c>
       <c r="G151" s="4" t="n">
         <v>-288</v>
       </c>
@@ -9939,8 +11083,16 @@
           <t>優群</t>
         </is>
       </c>
-      <c r="E152" s="4" t="inlineStr"/>
-      <c r="F152" s="4" t="inlineStr"/>
+      <c r="E152" s="4" t="inlineStr">
+        <is>
+          <t>170.00</t>
+        </is>
+      </c>
+      <c r="F152" s="4" t="inlineStr">
+        <is>
+          <t>+0.5</t>
+        </is>
+      </c>
       <c r="G152" s="4" t="n">
         <v>-248</v>
       </c>
@@ -9971,8 +11123,16 @@
           <t>東浦</t>
         </is>
       </c>
-      <c r="E153" s="4" t="inlineStr"/>
-      <c r="F153" s="4" t="inlineStr"/>
+      <c r="E153" s="4" t="inlineStr">
+        <is>
+          <t>69.80</t>
+        </is>
+      </c>
+      <c r="F153" s="4" t="inlineStr">
+        <is>
+          <t>+4.0</t>
+        </is>
+      </c>
       <c r="G153" s="4" t="n">
         <v>-247</v>
       </c>
@@ -9999,8 +11159,16 @@
           <t>緯軟</t>
         </is>
       </c>
-      <c r="E154" s="4" t="inlineStr"/>
-      <c r="F154" s="4" t="inlineStr"/>
+      <c r="E154" s="4" t="inlineStr">
+        <is>
+          <t>132.50</t>
+        </is>
+      </c>
+      <c r="F154" s="4" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
       <c r="G154" s="4" t="n">
         <v>-243</v>
       </c>
@@ -10027,8 +11195,16 @@
           <t>翔名</t>
         </is>
       </c>
-      <c r="E155" s="4" t="inlineStr"/>
-      <c r="F155" s="4" t="inlineStr"/>
+      <c r="E155" s="4" t="inlineStr">
+        <is>
+          <t>281.00</t>
+        </is>
+      </c>
+      <c r="F155" s="4" t="inlineStr">
+        <is>
+          <t>+20.5</t>
+        </is>
+      </c>
       <c r="G155" s="4" t="n">
         <v>-240</v>
       </c>
@@ -10055,8 +11231,16 @@
           <t>亞昕</t>
         </is>
       </c>
-      <c r="E156" s="4" t="inlineStr"/>
-      <c r="F156" s="4" t="inlineStr"/>
+      <c r="E156" s="4" t="inlineStr">
+        <is>
+          <t>22.95</t>
+        </is>
+      </c>
+      <c r="F156" s="4" t="inlineStr">
+        <is>
+          <t>-0.4</t>
+        </is>
+      </c>
       <c r="G156" s="4" t="n">
         <v>-236</v>
       </c>
@@ -10087,8 +11271,16 @@
           <t>宏遠證</t>
         </is>
       </c>
-      <c r="E157" s="4" t="inlineStr"/>
-      <c r="F157" s="4" t="inlineStr"/>
+      <c r="E157" s="4" t="inlineStr">
+        <is>
+          <t>18.35</t>
+        </is>
+      </c>
+      <c r="F157" s="4" t="inlineStr">
+        <is>
+          <t>+0.15</t>
+        </is>
+      </c>
       <c r="G157" s="4" t="n">
         <v>-228</v>
       </c>
@@ -10119,8 +11311,16 @@
           <t>博智</t>
         </is>
       </c>
-      <c r="E158" s="4" t="inlineStr"/>
-      <c r="F158" s="4" t="inlineStr"/>
+      <c r="E158" s="4" t="inlineStr">
+        <is>
+          <t>404.50</t>
+        </is>
+      </c>
+      <c r="F158" s="4" t="inlineStr">
+        <is>
+          <t>-7.5</t>
+        </is>
+      </c>
       <c r="G158" s="4" t="n">
         <v>-223</v>
       </c>

--- a/StockInfo/otc_analysis_result.xlsx
+++ b/StockInfo/otc_analysis_result.xlsx
@@ -26788,16 +26788,8 @@
           <t>世界</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>169.50</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>+8.0</t>
-        </is>
-      </c>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr"/>
       <c r="G4" s="4" t="n">
         <v>10069</v>
       </c>
@@ -26821,16 +26813,8 @@
           <t>中美晶</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>159.00</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>+14.0</t>
-        </is>
-      </c>
+      <c r="E5" s="4" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr"/>
       <c r="G5" s="4" t="n">
         <v>8166</v>
       </c>
@@ -26854,16 +26838,8 @@
           <t>鈺創</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>88.70</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>+4.4</t>
-        </is>
-      </c>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr"/>
       <c r="G6" s="4" t="n">
         <v>7458</v>
       </c>
@@ -26887,16 +26863,8 @@
           <t>台半</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>101.00</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>+9.1</t>
-        </is>
-      </c>
+      <c r="E7" s="4" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr"/>
       <c r="G7" s="4" t="n">
         <v>5608</v>
       </c>
@@ -26920,16 +26888,8 @@
           <t>欣銓</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>227.50</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>+12.5</t>
-        </is>
-      </c>
+      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr"/>
       <c r="G8" s="4" t="n">
         <v>4151</v>
       </c>
@@ -26953,16 +26913,8 @@
           <t>穩懋</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>505.00</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>+23.5</t>
-        </is>
-      </c>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr"/>
       <c r="G9" s="4" t="n">
         <v>4044</v>
       </c>
@@ -26986,16 +26938,8 @@
           <t>富喬</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>96.20</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>+6.1</t>
-        </is>
-      </c>
+      <c r="E10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr"/>
       <c r="G10" s="4" t="n">
         <v>3698</v>
       </c>
@@ -27019,16 +26963,8 @@
           <t>光頡</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>118.00</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>+8.0</t>
-        </is>
-      </c>
+      <c r="E11" s="4" t="inlineStr"/>
+      <c r="F11" s="4" t="inlineStr"/>
       <c r="G11" s="4" t="n">
         <v>3294</v>
       </c>
@@ -27052,16 +26988,8 @@
           <t>擎亞</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>132.50</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>+11.5</t>
-        </is>
-      </c>
+      <c r="E12" s="4" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr"/>
       <c r="G12" s="4" t="n">
         <v>2904</v>
       </c>
@@ -27085,16 +27013,8 @@
           <t>智通*</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>106.50</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>+8.3</t>
-        </is>
-      </c>
+      <c r="E13" s="4" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr"/>
       <c r="G13" s="4" t="n">
         <v>2762</v>
       </c>
@@ -27118,16 +27038,8 @@
           <t>茂迪</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>31.10</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
+      <c r="E14" s="4" t="inlineStr"/>
+      <c r="F14" s="4" t="inlineStr"/>
       <c r="G14" s="4" t="n">
         <v>2209</v>
       </c>
@@ -27151,16 +27063,8 @@
           <t>亞電</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>66.20</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>+6.0</t>
-        </is>
-      </c>
+      <c r="E15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr"/>
       <c r="G15" s="4" t="n">
         <v>2139</v>
       </c>
@@ -27184,16 +27088,8 @@
           <t>致和證</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>47.20</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>+4.2</t>
-        </is>
-      </c>
+      <c r="E16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr"/>
       <c r="G16" s="4" t="n">
         <v>1699</v>
       </c>
@@ -27217,16 +27113,8 @@
           <t>信昌電</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>276.50</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>+25.0</t>
-        </is>
-      </c>
+      <c r="E17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr"/>
       <c r="G17" s="4" t="n">
         <v>1699</v>
       </c>
@@ -27250,16 +27138,8 @@
           <t>榮剛</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>36.30</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>+0.95</t>
-        </is>
-      </c>
+      <c r="E18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr"/>
       <c r="G18" s="4" t="n">
         <v>1643</v>
       </c>
@@ -27283,16 +27163,8 @@
           <t>方土昶</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>58.90</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>+1.2</t>
-        </is>
-      </c>
+      <c r="E19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr"/>
       <c r="G19" s="4" t="n">
         <v>1572</v>
       </c>
@@ -27316,16 +27188,8 @@
           <t>璟德</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>221.00</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>+20.0</t>
-        </is>
-      </c>
+      <c r="E20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr"/>
       <c r="G20" s="4" t="n">
         <v>1550</v>
       </c>
@@ -27349,16 +27213,8 @@
           <t>系統電</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>69.70</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>+3.1</t>
-        </is>
-      </c>
+      <c r="E21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr"/>
       <c r="G21" s="4" t="n">
         <v>1429</v>
       </c>
@@ -27382,16 +27238,8 @@
           <t>國統</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>56.00</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>+0.8</t>
-        </is>
-      </c>
+      <c r="E22" s="4" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr"/>
       <c r="G22" s="4" t="n">
         <v>1276</v>
       </c>
@@ -27415,16 +27263,8 @@
           <t>品安</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>61.40</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>+3.7</t>
-        </is>
-      </c>
+      <c r="E23" s="4" t="inlineStr"/>
+      <c r="F23" s="4" t="inlineStr"/>
       <c r="G23" s="4" t="n">
         <v>1244</v>
       </c>
@@ -27448,16 +27288,8 @@
           <t>福邦證</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>17.25</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>+0.7</t>
-        </is>
-      </c>
+      <c r="E24" s="4" t="inlineStr"/>
+      <c r="F24" s="4" t="inlineStr"/>
       <c r="G24" s="4" t="n">
         <v>1216</v>
       </c>
@@ -27481,16 +27313,8 @@
           <t>精材</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>233.00</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>+10.0</t>
-        </is>
-      </c>
+      <c r="E25" s="4" t="inlineStr"/>
+      <c r="F25" s="4" t="inlineStr"/>
       <c r="G25" s="4" t="n">
         <v>1017</v>
       </c>
@@ -27514,16 +27338,8 @@
           <t>合晶</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>88.90</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>+8.0</t>
-        </is>
-      </c>
+      <c r="E26" s="4" t="inlineStr"/>
+      <c r="F26" s="4" t="inlineStr"/>
       <c r="G26" s="4" t="n">
         <v>1008</v>
       </c>
@@ -27547,16 +27363,8 @@
           <t>順達</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>418.00</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>+19.5</t>
-        </is>
-      </c>
+      <c r="E27" s="4" t="inlineStr"/>
+      <c r="F27" s="4" t="inlineStr"/>
       <c r="G27" s="4" t="n">
         <v>751</v>
       </c>
@@ -27580,16 +27388,8 @@
           <t>漢科</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>145.00</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>+10.0</t>
-        </is>
-      </c>
+      <c r="E28" s="4" t="inlineStr"/>
+      <c r="F28" s="4" t="inlineStr"/>
       <c r="G28" s="4" t="n">
         <v>716</v>
       </c>
@@ -27613,16 +27413,8 @@
           <t>九豪</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>75.90</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>-3.1</t>
-        </is>
-      </c>
+      <c r="E29" s="4" t="inlineStr"/>
+      <c r="F29" s="4" t="inlineStr"/>
       <c r="G29" s="4" t="n">
         <v>678</v>
       </c>
@@ -27646,16 +27438,8 @@
           <t>旭軟</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>28.85</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>+1.5</t>
-        </is>
-      </c>
+      <c r="E30" s="4" t="inlineStr"/>
+      <c r="F30" s="4" t="inlineStr"/>
       <c r="G30" s="4" t="n">
         <v>647</v>
       </c>
@@ -27679,16 +27463,8 @@
           <t>茂訊</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>138.50</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>+4.5</t>
-        </is>
-      </c>
+      <c r="E31" s="4" t="inlineStr"/>
+      <c r="F31" s="4" t="inlineStr"/>
       <c r="G31" s="4" t="n">
         <v>616</v>
       </c>
@@ -27712,16 +27488,8 @@
           <t>廣明</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>81.20</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>+2.7</t>
-        </is>
-      </c>
+      <c r="E32" s="4" t="inlineStr"/>
+      <c r="F32" s="4" t="inlineStr"/>
       <c r="G32" s="4" t="n">
         <v>609</v>
       </c>
@@ -27745,16 +27513,8 @@
           <t>聖暉*</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>1180.00</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>+105.0</t>
-        </is>
-      </c>
+      <c r="E33" s="4" t="inlineStr"/>
+      <c r="F33" s="4" t="inlineStr"/>
       <c r="G33" s="4" t="n">
         <v>575</v>
       </c>
@@ -27778,16 +27538,8 @@
           <t>尼克森</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>78.60</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>+3.4</t>
-        </is>
-      </c>
+      <c r="E34" s="4" t="inlineStr"/>
+      <c r="F34" s="4" t="inlineStr"/>
       <c r="G34" s="4" t="n">
         <v>526</v>
       </c>
@@ -27811,16 +27563,8 @@
           <t>台星科</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>179.00</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>+9.5</t>
-        </is>
-      </c>
+      <c r="E35" s="4" t="inlineStr"/>
+      <c r="F35" s="4" t="inlineStr"/>
       <c r="G35" s="4" t="n">
         <v>521</v>
       </c>
@@ -27844,16 +27588,8 @@
           <t>臺慶科</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>293.00</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>+6.0</t>
-        </is>
-      </c>
+      <c r="E36" s="4" t="inlineStr"/>
+      <c r="F36" s="4" t="inlineStr"/>
       <c r="G36" s="4" t="n">
         <v>521</v>
       </c>
@@ -27877,16 +27613,8 @@
           <t>健喬</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>30.50</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>+0.25</t>
-        </is>
-      </c>
+      <c r="E37" s="4" t="inlineStr"/>
+      <c r="F37" s="4" t="inlineStr"/>
       <c r="G37" s="4" t="n">
         <v>484</v>
       </c>
@@ -27910,16 +27638,8 @@
           <t>慶騰</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>33.00</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>+3.0</t>
-        </is>
-      </c>
+      <c r="E38" s="4" t="inlineStr"/>
+      <c r="F38" s="4" t="inlineStr"/>
       <c r="G38" s="4" t="n">
         <v>480</v>
       </c>
@@ -27943,16 +27663,8 @@
           <t>太景*-KY</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>8.84</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>+0.24</t>
-        </is>
-      </c>
+      <c r="E39" s="4" t="inlineStr"/>
+      <c r="F39" s="4" t="inlineStr"/>
       <c r="G39" s="4" t="n">
         <v>465</v>
       </c>
@@ -27976,16 +27688,8 @@
           <t>佶優</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>32.20</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>+1.45</t>
-        </is>
-      </c>
+      <c r="E40" s="4" t="inlineStr"/>
+      <c r="F40" s="4" t="inlineStr"/>
       <c r="G40" s="4" t="n">
         <v>462</v>
       </c>
@@ -28009,16 +27713,8 @@
           <t>晶焱</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>97.70</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>+3.8</t>
-        </is>
-      </c>
+      <c r="E41" s="4" t="inlineStr"/>
+      <c r="F41" s="4" t="inlineStr"/>
       <c r="G41" s="4" t="n">
         <v>458</v>
       </c>
@@ -28042,16 +27738,8 @@
           <t>雙鴻</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>1055.00</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>+57.0</t>
-        </is>
-      </c>
+      <c r="E42" s="4" t="inlineStr"/>
+      <c r="F42" s="4" t="inlineStr"/>
       <c r="G42" s="4" t="n">
         <v>449</v>
       </c>
@@ -28075,16 +27763,8 @@
           <t>精剛</t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>19.65</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>+0.15</t>
-        </is>
-      </c>
+      <c r="E43" s="4" t="inlineStr"/>
+      <c r="F43" s="4" t="inlineStr"/>
       <c r="G43" s="4" t="n">
         <v>443</v>
       </c>
@@ -28108,16 +27788,8 @@
           <t>凱崴</t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>69.40</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>+2.7</t>
-        </is>
-      </c>
+      <c r="E44" s="4" t="inlineStr"/>
+      <c r="F44" s="4" t="inlineStr"/>
       <c r="G44" s="4" t="n">
         <v>413</v>
       </c>
@@ -28141,16 +27813,8 @@
           <t>漢磊</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>77.10</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>+3.1</t>
-        </is>
-      </c>
+      <c r="E45" s="4" t="inlineStr"/>
+      <c r="F45" s="4" t="inlineStr"/>
       <c r="G45" s="4" t="n">
         <v>396</v>
       </c>
@@ -28174,16 +27838,8 @@
           <t>朋億*</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>311.50</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>+25.0</t>
-        </is>
-      </c>
+      <c r="E46" s="4" t="inlineStr"/>
+      <c r="F46" s="4" t="inlineStr"/>
       <c r="G46" s="4" t="n">
         <v>384</v>
       </c>
@@ -28207,16 +27863,8 @@
           <t>華電網</t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>51.30</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t>+1.45</t>
-        </is>
-      </c>
+      <c r="E47" s="4" t="inlineStr"/>
+      <c r="F47" s="4" t="inlineStr"/>
       <c r="G47" s="4" t="n">
         <v>379</v>
       </c>
@@ -28240,16 +27888,8 @@
           <t>晟田</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>47.55</t>
-        </is>
-      </c>
-      <c r="F48" s="4" t="inlineStr">
-        <is>
-          <t>+0.6</t>
-        </is>
-      </c>
+      <c r="E48" s="4" t="inlineStr"/>
+      <c r="F48" s="4" t="inlineStr"/>
       <c r="G48" s="4" t="n">
         <v>370</v>
       </c>
@@ -28273,16 +27913,8 @@
           <t>亞通</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>24.00</t>
-        </is>
-      </c>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>+0.65</t>
-        </is>
-      </c>
+      <c r="E49" s="4" t="inlineStr"/>
+      <c r="F49" s="4" t="inlineStr"/>
       <c r="G49" s="4" t="n">
         <v>370</v>
       </c>
@@ -28306,16 +27938,8 @@
           <t>長科*</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>88.00</t>
-        </is>
-      </c>
-      <c r="F50" s="4" t="inlineStr">
-        <is>
-          <t>+4.0</t>
-        </is>
-      </c>
+      <c r="E50" s="4" t="inlineStr"/>
+      <c r="F50" s="4" t="inlineStr"/>
       <c r="G50" s="4" t="n">
         <v>370</v>
       </c>
@@ -28339,16 +27963,8 @@
           <t>金居</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>574.00</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="inlineStr">
-        <is>
-          <t>+34.0</t>
-        </is>
-      </c>
+      <c r="E51" s="4" t="inlineStr"/>
+      <c r="F51" s="4" t="inlineStr"/>
       <c r="G51" s="4" t="n">
         <v>364</v>
       </c>
@@ -28372,16 +27988,8 @@
           <t>晟德</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>37.65</t>
-        </is>
-      </c>
-      <c r="F52" s="4" t="inlineStr">
-        <is>
-          <t>+0.3</t>
-        </is>
-      </c>
+      <c r="E52" s="4" t="inlineStr"/>
+      <c r="F52" s="4" t="inlineStr"/>
       <c r="G52" s="4" t="n">
         <v>355</v>
       </c>
@@ -28405,16 +28013,8 @@
           <t>合一</t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>48.35</t>
-        </is>
-      </c>
-      <c r="F53" s="4" t="inlineStr">
-        <is>
-          <t>+0.6</t>
-        </is>
-      </c>
+      <c r="E53" s="4" t="inlineStr"/>
+      <c r="F53" s="4" t="inlineStr"/>
       <c r="G53" s="4" t="n">
         <v>355</v>
       </c>
@@ -28438,16 +28038,8 @@
           <t>德勝</t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>66.90</t>
-        </is>
-      </c>
-      <c r="F54" s="4" t="inlineStr">
-        <is>
-          <t>+4.1</t>
-        </is>
-      </c>
+      <c r="E54" s="4" t="inlineStr"/>
+      <c r="F54" s="4" t="inlineStr"/>
       <c r="G54" s="4" t="n">
         <v>319</v>
       </c>
@@ -28471,16 +28063,8 @@
           <t>聚和</t>
         </is>
       </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>46.25</t>
-        </is>
-      </c>
-      <c r="F55" s="4" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
+      <c r="E55" s="4" t="inlineStr"/>
+      <c r="F55" s="4" t="inlineStr"/>
       <c r="G55" s="4" t="n">
         <v>318</v>
       </c>
@@ -28504,16 +28088,8 @@
           <t>耀勝</t>
         </is>
       </c>
-      <c r="E56" s="4" t="inlineStr">
-        <is>
-          <t>67.90</t>
-        </is>
-      </c>
-      <c r="F56" s="4" t="inlineStr">
-        <is>
-          <t>+1.4</t>
-        </is>
-      </c>
+      <c r="E56" s="4" t="inlineStr"/>
+      <c r="F56" s="4" t="inlineStr"/>
       <c r="G56" s="4" t="n">
         <v>310</v>
       </c>
@@ -28537,16 +28113,8 @@
           <t>岱稜</t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr">
-        <is>
-          <t>58.90</t>
-        </is>
-      </c>
-      <c r="F57" s="4" t="inlineStr">
-        <is>
-          <t>+5.3</t>
-        </is>
-      </c>
+      <c r="E57" s="4" t="inlineStr"/>
+      <c r="F57" s="4" t="inlineStr"/>
       <c r="G57" s="4" t="n">
         <v>283</v>
       </c>
@@ -28570,16 +28138,8 @@
           <t>中光電</t>
         </is>
       </c>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t>68.00</t>
-        </is>
-      </c>
-      <c r="F58" s="4" t="inlineStr">
-        <is>
-          <t>+0.3</t>
-        </is>
-      </c>
+      <c r="E58" s="4" t="inlineStr"/>
+      <c r="F58" s="4" t="inlineStr"/>
       <c r="G58" s="4" t="n">
         <v>278</v>
       </c>
@@ -28603,16 +28163,8 @@
           <t>協易機</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>30.75</t>
-        </is>
-      </c>
-      <c r="F59" s="4" t="inlineStr">
-        <is>
-          <t>+0.6</t>
-        </is>
-      </c>
+      <c r="E59" s="4" t="inlineStr"/>
+      <c r="F59" s="4" t="inlineStr"/>
       <c r="G59" s="4" t="n">
         <v>275</v>
       </c>
@@ -28636,16 +28188,8 @@
           <t>永捷</t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>13.55</t>
-        </is>
-      </c>
-      <c r="F60" s="4" t="inlineStr">
-        <is>
-          <t>+0.2</t>
-        </is>
-      </c>
+      <c r="E60" s="4" t="inlineStr"/>
+      <c r="F60" s="4" t="inlineStr"/>
       <c r="G60" s="4" t="n">
         <v>270</v>
       </c>
@@ -28669,16 +28213,8 @@
           <t>太欣</t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>11.30</t>
-        </is>
-      </c>
-      <c r="F61" s="4" t="inlineStr">
-        <is>
-          <t>+0.3</t>
-        </is>
-      </c>
+      <c r="E61" s="4" t="inlineStr"/>
+      <c r="F61" s="4" t="inlineStr"/>
       <c r="G61" s="4" t="n">
         <v>260</v>
       </c>
@@ -28702,16 +28238,8 @@
           <t>南仁湖</t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr">
-        <is>
-          <t>8.44</t>
-        </is>
-      </c>
-      <c r="F62" s="4" t="inlineStr">
-        <is>
-          <t>+0.32</t>
-        </is>
-      </c>
+      <c r="E62" s="4" t="inlineStr"/>
+      <c r="F62" s="4" t="inlineStr"/>
       <c r="G62" s="4" t="n">
         <v>260</v>
       </c>
@@ -28735,16 +28263,8 @@
           <t>威潤</t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>60.90</t>
-        </is>
-      </c>
-      <c r="F63" s="4" t="inlineStr">
-        <is>
-          <t>+5.5</t>
-        </is>
-      </c>
+      <c r="E63" s="4" t="inlineStr"/>
+      <c r="F63" s="4" t="inlineStr"/>
       <c r="G63" s="4" t="n">
         <v>251</v>
       </c>
@@ -28768,16 +28288,8 @@
           <t>譜瑞-KY</t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t>675.00</t>
-        </is>
-      </c>
-      <c r="F64" s="4" t="inlineStr">
-        <is>
-          <t>+18.0</t>
-        </is>
-      </c>
+      <c r="E64" s="4" t="inlineStr"/>
+      <c r="F64" s="4" t="inlineStr"/>
       <c r="G64" s="4" t="n">
         <v>249</v>
       </c>
@@ -28801,16 +28313,8 @@
           <t>華星光</t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr">
-        <is>
-          <t>501.00</t>
-        </is>
-      </c>
-      <c r="F65" s="4" t="inlineStr">
-        <is>
-          <t>+28.0</t>
-        </is>
-      </c>
+      <c r="E65" s="4" t="inlineStr"/>
+      <c r="F65" s="4" t="inlineStr"/>
       <c r="G65" s="4" t="n">
         <v>249</v>
       </c>
@@ -28834,16 +28338,8 @@
           <t>千如</t>
         </is>
       </c>
-      <c r="E66" s="4" t="inlineStr">
-        <is>
-          <t>63.20</t>
-        </is>
-      </c>
-      <c r="F66" s="4" t="inlineStr">
-        <is>
-          <t>+5.7</t>
-        </is>
-      </c>
+      <c r="E66" s="4" t="inlineStr"/>
+      <c r="F66" s="4" t="inlineStr"/>
       <c r="G66" s="4" t="n">
         <v>241</v>
       </c>
@@ -28867,16 +28363,8 @@
           <t>松瑞藥</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>19.85</t>
-        </is>
-      </c>
-      <c r="F67" s="4" t="inlineStr">
-        <is>
-          <t>+0.2</t>
-        </is>
-      </c>
+      <c r="E67" s="4" t="inlineStr"/>
+      <c r="F67" s="4" t="inlineStr"/>
       <c r="G67" s="4" t="n">
         <v>235</v>
       </c>
@@ -28900,16 +28388,8 @@
           <t>寶雅</t>
         </is>
       </c>
-      <c r="E68" s="4" t="inlineStr">
-        <is>
-          <t>647.00</t>
-        </is>
-      </c>
-      <c r="F68" s="4" t="inlineStr">
-        <is>
-          <t>+22.0</t>
-        </is>
-      </c>
+      <c r="E68" s="4" t="inlineStr"/>
+      <c r="F68" s="4" t="inlineStr"/>
       <c r="G68" s="4" t="n">
         <v>230</v>
       </c>
@@ -28933,16 +28413,8 @@
           <t>原相</t>
         </is>
       </c>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>216.00</t>
-        </is>
-      </c>
-      <c r="F69" s="4" t="inlineStr">
-        <is>
-          <t>+3.0</t>
-        </is>
-      </c>
+      <c r="E69" s="4" t="inlineStr"/>
+      <c r="F69" s="4" t="inlineStr"/>
       <c r="G69" s="4" t="n">
         <v>225</v>
       </c>
@@ -28966,16 +28438,8 @@
           <t>大學光</t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr">
-        <is>
-          <t>135.00</t>
-        </is>
-      </c>
-      <c r="F70" s="4" t="inlineStr">
-        <is>
-          <t>+4.0</t>
-        </is>
-      </c>
+      <c r="E70" s="4" t="inlineStr"/>
+      <c r="F70" s="4" t="inlineStr"/>
       <c r="G70" s="4" t="n">
         <v>223</v>
       </c>
@@ -28999,16 +28463,8 @@
           <t>伍豐</t>
         </is>
       </c>
-      <c r="E71" s="4" t="inlineStr">
-        <is>
-          <t>26.85</t>
-        </is>
-      </c>
-      <c r="F71" s="4" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
+      <c r="E71" s="4" t="inlineStr"/>
+      <c r="F71" s="4" t="inlineStr"/>
       <c r="G71" s="4" t="n">
         <v>220</v>
       </c>
@@ -29032,16 +28488,8 @@
           <t>美好證</t>
         </is>
       </c>
-      <c r="E72" s="4" t="inlineStr">
-        <is>
-          <t>40.65</t>
-        </is>
-      </c>
-      <c r="F72" s="4" t="inlineStr">
-        <is>
-          <t>+1.9</t>
-        </is>
-      </c>
+      <c r="E72" s="4" t="inlineStr"/>
+      <c r="F72" s="4" t="inlineStr"/>
       <c r="G72" s="4" t="n">
         <v>216</v>
       </c>
@@ -29065,16 +28513,8 @@
           <t>力麒</t>
         </is>
       </c>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>7.92</t>
-        </is>
-      </c>
-      <c r="F73" s="4" t="inlineStr">
-        <is>
-          <t>+0.07</t>
-        </is>
-      </c>
+      <c r="E73" s="4" t="inlineStr"/>
+      <c r="F73" s="4" t="inlineStr"/>
       <c r="G73" s="4" t="n">
         <v>209</v>
       </c>
@@ -29098,16 +28538,8 @@
           <t>創惟</t>
         </is>
       </c>
-      <c r="E74" s="4" t="inlineStr">
-        <is>
-          <t>99.00</t>
-        </is>
-      </c>
-      <c r="F74" s="4" t="inlineStr">
-        <is>
-          <t>+0.4</t>
-        </is>
-      </c>
+      <c r="E74" s="4" t="inlineStr"/>
+      <c r="F74" s="4" t="inlineStr"/>
       <c r="G74" s="4" t="n">
         <v>208</v>
       </c>
@@ -29131,16 +28563,8 @@
           <t>普誠</t>
         </is>
       </c>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>15.35</t>
-        </is>
-      </c>
-      <c r="F75" s="4" t="inlineStr">
-        <is>
-          <t>+0.35</t>
-        </is>
-      </c>
+      <c r="E75" s="4" t="inlineStr"/>
+      <c r="F75" s="4" t="inlineStr"/>
       <c r="G75" s="4" t="n">
         <v>207</v>
       </c>
@@ -29164,16 +28588,8 @@
           <t>新復興</t>
         </is>
       </c>
-      <c r="E76" s="4" t="inlineStr">
-        <is>
-          <t>49.20</t>
-        </is>
-      </c>
-      <c r="F76" s="4" t="inlineStr">
-        <is>
-          <t>+1.1</t>
-        </is>
-      </c>
+      <c r="E76" s="4" t="inlineStr"/>
+      <c r="F76" s="4" t="inlineStr"/>
       <c r="G76" s="4" t="n">
         <v>198</v>
       </c>
@@ -29197,16 +28613,8 @@
           <t>大立</t>
         </is>
       </c>
-      <c r="E77" s="4" t="inlineStr">
-        <is>
-          <t>16.55</t>
-        </is>
-      </c>
-      <c r="F77" s="4" t="inlineStr">
-        <is>
-          <t>+0.05</t>
-        </is>
-      </c>
+      <c r="E77" s="4" t="inlineStr"/>
+      <c r="F77" s="4" t="inlineStr"/>
       <c r="G77" s="4" t="n">
         <v>197</v>
       </c>
@@ -29230,16 +28638,8 @@
           <t>晶宏</t>
         </is>
       </c>
-      <c r="E78" s="4" t="inlineStr">
-        <is>
-          <t>71.50</t>
-        </is>
-      </c>
-      <c r="F78" s="4" t="inlineStr">
-        <is>
-          <t>+0.2</t>
-        </is>
-      </c>
+      <c r="E78" s="4" t="inlineStr"/>
+      <c r="F78" s="4" t="inlineStr"/>
       <c r="G78" s="4" t="n">
         <v>189</v>
       </c>
@@ -29263,16 +28663,8 @@
           <t>大綜</t>
         </is>
       </c>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t>338.00</t>
-        </is>
-      </c>
-      <c r="F79" s="4" t="inlineStr">
-        <is>
-          <t>+20.0</t>
-        </is>
-      </c>
+      <c r="E79" s="4" t="inlineStr"/>
+      <c r="F79" s="4" t="inlineStr"/>
       <c r="G79" s="4" t="n">
         <v>189</v>
       </c>
@@ -29296,16 +28688,8 @@
           <t>僑威</t>
         </is>
       </c>
-      <c r="E80" s="4" t="inlineStr">
-        <is>
-          <t>54.50</t>
-        </is>
-      </c>
-      <c r="F80" s="4" t="inlineStr">
-        <is>
-          <t>+0.7</t>
-        </is>
-      </c>
+      <c r="E80" s="4" t="inlineStr"/>
+      <c r="F80" s="4" t="inlineStr"/>
       <c r="G80" s="4" t="n">
         <v>185</v>
       </c>
@@ -29329,16 +28713,8 @@
           <t>正基</t>
         </is>
       </c>
-      <c r="E81" s="4" t="inlineStr">
-        <is>
-          <t>74.00</t>
-        </is>
-      </c>
-      <c r="F81" s="4" t="inlineStr">
-        <is>
-          <t>+1.3</t>
-        </is>
-      </c>
+      <c r="E81" s="4" t="inlineStr"/>
+      <c r="F81" s="4" t="inlineStr"/>
       <c r="G81" s="4" t="n">
         <v>184</v>
       </c>
@@ -29362,16 +28738,8 @@
           <t>兆利</t>
         </is>
       </c>
-      <c r="E82" s="4" t="inlineStr">
-        <is>
-          <t>91.50</t>
-        </is>
-      </c>
-      <c r="F82" s="4" t="inlineStr">
-        <is>
-          <t>+2.2</t>
-        </is>
-      </c>
+      <c r="E82" s="4" t="inlineStr"/>
+      <c r="F82" s="4" t="inlineStr"/>
       <c r="G82" s="4" t="n">
         <v>183</v>
       </c>
@@ -29395,16 +28763,8 @@
           <t>信立</t>
         </is>
       </c>
-      <c r="E83" s="4" t="inlineStr">
-        <is>
-          <t>46.70</t>
-        </is>
-      </c>
-      <c r="F83" s="4" t="inlineStr">
-        <is>
-          <t>+0.9</t>
-        </is>
-      </c>
+      <c r="E83" s="4" t="inlineStr"/>
+      <c r="F83" s="4" t="inlineStr"/>
       <c r="G83" s="4" t="n">
         <v>182</v>
       </c>
@@ -29428,16 +28788,8 @@
           <t>中天</t>
         </is>
       </c>
-      <c r="E84" s="4" t="inlineStr">
-        <is>
-          <t>15.00</t>
-        </is>
-      </c>
-      <c r="F84" s="4" t="inlineStr">
-        <is>
-          <t>+0.35</t>
-        </is>
-      </c>
+      <c r="E84" s="4" t="inlineStr"/>
+      <c r="F84" s="4" t="inlineStr"/>
       <c r="G84" s="4" t="n">
         <v>181</v>
       </c>
@@ -29461,16 +28813,8 @@
           <t>家登</t>
         </is>
       </c>
-      <c r="E85" s="4" t="inlineStr">
-        <is>
-          <t>503.00</t>
-        </is>
-      </c>
-      <c r="F85" s="4" t="inlineStr">
-        <is>
-          <t>+23.0</t>
-        </is>
-      </c>
+      <c r="E85" s="4" t="inlineStr"/>
+      <c r="F85" s="4" t="inlineStr"/>
       <c r="G85" s="4" t="n">
         <v>178</v>
       </c>
@@ -29494,16 +28838,8 @@
           <t>力士</t>
         </is>
       </c>
-      <c r="E86" s="4" t="inlineStr">
-        <is>
-          <t>47.50</t>
-        </is>
-      </c>
-      <c r="F86" s="4" t="inlineStr">
-        <is>
-          <t>+4.3</t>
-        </is>
-      </c>
+      <c r="E86" s="4" t="inlineStr"/>
+      <c r="F86" s="4" t="inlineStr"/>
       <c r="G86" s="4" t="n">
         <v>178</v>
       </c>
@@ -29527,16 +28863,8 @@
           <t>森鉅</t>
         </is>
       </c>
-      <c r="E87" s="4" t="inlineStr">
-        <is>
-          <t>41.35</t>
-        </is>
-      </c>
-      <c r="F87" s="4" t="inlineStr">
-        <is>
-          <t>+0.85</t>
-        </is>
-      </c>
+      <c r="E87" s="4" t="inlineStr"/>
+      <c r="F87" s="4" t="inlineStr"/>
       <c r="G87" s="4" t="n">
         <v>173</v>
       </c>
@@ -29560,16 +28888,8 @@
           <t>新潤</t>
         </is>
       </c>
-      <c r="E88" s="4" t="inlineStr">
-        <is>
-          <t>41.05</t>
-        </is>
-      </c>
-      <c r="F88" s="4" t="inlineStr">
-        <is>
-          <t>+0.05</t>
-        </is>
-      </c>
+      <c r="E88" s="4" t="inlineStr"/>
+      <c r="F88" s="4" t="inlineStr"/>
       <c r="G88" s="4" t="n">
         <v>172</v>
       </c>
@@ -29593,16 +28913,8 @@
           <t>佳邦</t>
         </is>
       </c>
-      <c r="E89" s="4" t="inlineStr">
-        <is>
-          <t>98.60</t>
-        </is>
-      </c>
-      <c r="F89" s="4" t="inlineStr">
-        <is>
-          <t>+1.9</t>
-        </is>
-      </c>
+      <c r="E89" s="4" t="inlineStr"/>
+      <c r="F89" s="4" t="inlineStr"/>
       <c r="G89" s="4" t="n">
         <v>171</v>
       </c>
@@ -29626,16 +28938,8 @@
           <t>廣閎科</t>
         </is>
       </c>
-      <c r="E90" s="4" t="inlineStr">
-        <is>
-          <t>169.00</t>
-        </is>
-      </c>
-      <c r="F90" s="4" t="inlineStr">
-        <is>
-          <t>+14.0</t>
-        </is>
-      </c>
+      <c r="E90" s="4" t="inlineStr"/>
+      <c r="F90" s="4" t="inlineStr"/>
       <c r="G90" s="4" t="n">
         <v>171</v>
       </c>
@@ -29659,16 +28963,8 @@
           <t>尚立</t>
         </is>
       </c>
-      <c r="E91" s="4" t="inlineStr">
-        <is>
-          <t>15.00</t>
-        </is>
-      </c>
-      <c r="F91" s="4" t="inlineStr">
-        <is>
-          <t>+0.2</t>
-        </is>
-      </c>
+      <c r="E91" s="4" t="inlineStr"/>
+      <c r="F91" s="4" t="inlineStr"/>
       <c r="G91" s="4" t="n">
         <v>170</v>
       </c>
@@ -29692,16 +28988,8 @@
           <t>光聯</t>
         </is>
       </c>
-      <c r="E92" s="4" t="inlineStr">
-        <is>
-          <t>22.20</t>
-        </is>
-      </c>
-      <c r="F92" s="4" t="inlineStr">
-        <is>
-          <t>+0.15</t>
-        </is>
-      </c>
+      <c r="E92" s="4" t="inlineStr"/>
+      <c r="F92" s="4" t="inlineStr"/>
       <c r="G92" s="4" t="n">
         <v>165</v>
       </c>
@@ -29725,16 +29013,8 @@
           <t>環球晶</t>
         </is>
       </c>
-      <c r="E93" s="4" t="inlineStr">
-        <is>
-          <t>864.00</t>
-        </is>
-      </c>
-      <c r="F93" s="4" t="inlineStr">
-        <is>
-          <t>+78.0</t>
-        </is>
-      </c>
+      <c r="E93" s="4" t="inlineStr"/>
+      <c r="F93" s="4" t="inlineStr"/>
       <c r="G93" s="4" t="n">
         <v>161</v>
       </c>
@@ -29758,16 +29038,8 @@
           <t>緯軟</t>
         </is>
       </c>
-      <c r="E94" s="4" t="inlineStr">
-        <is>
-          <t>135.50</t>
-        </is>
-      </c>
-      <c r="F94" s="4" t="inlineStr">
-        <is>
-          <t>+1.0</t>
-        </is>
-      </c>
+      <c r="E94" s="4" t="inlineStr"/>
+      <c r="F94" s="4" t="inlineStr"/>
       <c r="G94" s="4" t="n">
         <v>154</v>
       </c>
@@ -29791,16 +29063,8 @@
           <t>浩鼎</t>
         </is>
       </c>
-      <c r="E95" s="4" t="inlineStr">
-        <is>
-          <t>28.10</t>
-        </is>
-      </c>
-      <c r="F95" s="4" t="inlineStr">
-        <is>
-          <t>+0.4</t>
-        </is>
-      </c>
+      <c r="E95" s="4" t="inlineStr"/>
+      <c r="F95" s="4" t="inlineStr"/>
       <c r="G95" s="4" t="n">
         <v>146</v>
       </c>
@@ -29824,16 +29088,8 @@
           <t>大國鋼</t>
         </is>
       </c>
-      <c r="E96" s="4" t="inlineStr">
-        <is>
-          <t>35.40</t>
-        </is>
-      </c>
-      <c r="F96" s="4" t="inlineStr">
-        <is>
-          <t>+0.3</t>
-        </is>
-      </c>
+      <c r="E96" s="4" t="inlineStr"/>
+      <c r="F96" s="4" t="inlineStr"/>
       <c r="G96" s="4" t="n">
         <v>146</v>
       </c>
@@ -29857,16 +29113,8 @@
           <t>91APP*-KY</t>
         </is>
       </c>
-      <c r="E97" s="4" t="inlineStr">
-        <is>
-          <t>62.60</t>
-        </is>
-      </c>
-      <c r="F97" s="4" t="inlineStr">
-        <is>
-          <t>+1.5</t>
-        </is>
-      </c>
+      <c r="E97" s="4" t="inlineStr"/>
+      <c r="F97" s="4" t="inlineStr"/>
       <c r="G97" s="4" t="n">
         <v>141</v>
       </c>
@@ -29890,16 +29138,8 @@
           <t>華宏</t>
         </is>
       </c>
-      <c r="E98" s="4" t="inlineStr">
-        <is>
-          <t>56.30</t>
-        </is>
-      </c>
-      <c r="F98" s="4" t="inlineStr">
-        <is>
-          <t>+1.4</t>
-        </is>
-      </c>
+      <c r="E98" s="4" t="inlineStr"/>
+      <c r="F98" s="4" t="inlineStr"/>
       <c r="G98" s="4" t="n">
         <v>141</v>
       </c>
@@ -29923,16 +29163,8 @@
           <t>熒茂</t>
         </is>
       </c>
-      <c r="E99" s="4" t="inlineStr">
-        <is>
-          <t>22.10</t>
-        </is>
-      </c>
-      <c r="F99" s="4" t="inlineStr">
-        <is>
-          <t>+1.0</t>
-        </is>
-      </c>
+      <c r="E99" s="4" t="inlineStr"/>
+      <c r="F99" s="4" t="inlineStr"/>
       <c r="G99" s="4" t="n">
         <v>136</v>
       </c>
@@ -29956,16 +29188,8 @@
           <t>旺矽</t>
         </is>
       </c>
-      <c r="E100" s="4" t="inlineStr">
-        <is>
-          <t>6485.00</t>
-        </is>
-      </c>
-      <c r="F100" s="4" t="inlineStr">
-        <is>
-          <t>+395.0</t>
-        </is>
-      </c>
+      <c r="E100" s="4" t="inlineStr"/>
+      <c r="F100" s="4" t="inlineStr"/>
       <c r="G100" s="4" t="n">
         <v>136</v>
       </c>
@@ -29989,16 +29213,8 @@
           <t>正德</t>
         </is>
       </c>
-      <c r="E101" s="4" t="inlineStr">
-        <is>
-          <t>18.80</t>
-        </is>
-      </c>
-      <c r="F101" s="4" t="inlineStr">
-        <is>
-          <t>+0.25</t>
-        </is>
-      </c>
+      <c r="E101" s="4" t="inlineStr"/>
+      <c r="F101" s="4" t="inlineStr"/>
       <c r="G101" s="4" t="n">
         <v>133</v>
       </c>
@@ -30022,16 +29238,8 @@
           <t>德昌</t>
         </is>
       </c>
-      <c r="E102" s="4" t="inlineStr">
-        <is>
-          <t>76.20</t>
-        </is>
-      </c>
-      <c r="F102" s="4" t="inlineStr">
-        <is>
-          <t>+0.2</t>
-        </is>
-      </c>
+      <c r="E102" s="4" t="inlineStr"/>
+      <c r="F102" s="4" t="inlineStr"/>
       <c r="G102" s="4" t="n">
         <v>131</v>
       </c>
@@ -30055,16 +29263,8 @@
           <t>歐買尬</t>
         </is>
       </c>
-      <c r="E103" s="4" t="inlineStr">
-        <is>
-          <t>79.30</t>
-        </is>
-      </c>
-      <c r="F103" s="4" t="inlineStr">
-        <is>
-          <t>+1.5</t>
-        </is>
-      </c>
+      <c r="E103" s="4" t="inlineStr"/>
+      <c r="F103" s="4" t="inlineStr"/>
       <c r="G103" s="4" t="n">
         <v>130</v>
       </c>
@@ -30165,16 +29365,8 @@
           <t>光洋科</t>
         </is>
       </c>
-      <c r="E109" s="4" t="inlineStr">
-        <is>
-          <t>141.50</t>
-        </is>
-      </c>
-      <c r="F109" s="4" t="inlineStr">
-        <is>
-          <t>-4.0</t>
-        </is>
-      </c>
+      <c r="E109" s="4" t="inlineStr"/>
+      <c r="F109" s="4" t="inlineStr"/>
       <c r="G109" s="4" t="n">
         <v>-5967</v>
       </c>
@@ -30198,16 +29390,8 @@
           <t>華容</t>
         </is>
       </c>
-      <c r="E110" s="4" t="inlineStr">
-        <is>
-          <t>42.35</t>
-        </is>
-      </c>
-      <c r="F110" s="4" t="inlineStr">
-        <is>
-          <t>-0.85</t>
-        </is>
-      </c>
+      <c r="E110" s="4" t="inlineStr"/>
+      <c r="F110" s="4" t="inlineStr"/>
       <c r="G110" s="4" t="n">
         <v>-3986</v>
       </c>
@@ -30231,16 +29415,8 @@
           <t>頎邦</t>
         </is>
       </c>
-      <c r="E111" s="4" t="inlineStr">
-        <is>
-          <t>224.00</t>
-        </is>
-      </c>
-      <c r="F111" s="4" t="inlineStr">
-        <is>
-          <t>+1.5</t>
-        </is>
-      </c>
+      <c r="E111" s="4" t="inlineStr"/>
+      <c r="F111" s="4" t="inlineStr"/>
       <c r="G111" s="4" t="n">
         <v>-3656</v>
       </c>
@@ -30264,16 +29440,8 @@
           <t>信音</t>
         </is>
       </c>
-      <c r="E112" s="4" t="inlineStr">
-        <is>
-          <t>40.25</t>
-        </is>
-      </c>
-      <c r="F112" s="4" t="inlineStr">
-        <is>
-          <t>-1.3</t>
-        </is>
-      </c>
+      <c r="E112" s="4" t="inlineStr"/>
+      <c r="F112" s="4" t="inlineStr"/>
       <c r="G112" s="4" t="n">
         <v>-3445</v>
       </c>
@@ -30297,16 +29465,8 @@
           <t>立敦</t>
         </is>
       </c>
-      <c r="E113" s="4" t="inlineStr">
-        <is>
-          <t>98.60</t>
-        </is>
-      </c>
-      <c r="F113" s="4" t="inlineStr">
-        <is>
-          <t>-4.4</t>
-        </is>
-      </c>
+      <c r="E113" s="4" t="inlineStr"/>
+      <c r="F113" s="4" t="inlineStr"/>
       <c r="G113" s="4" t="n">
         <v>-2920</v>
       </c>
@@ -30330,16 +29490,8 @@
           <t>高技</t>
         </is>
       </c>
-      <c r="E114" s="4" t="inlineStr">
-        <is>
-          <t>327.00</t>
-        </is>
-      </c>
-      <c r="F114" s="4" t="inlineStr">
-        <is>
-          <t>-19.0</t>
-        </is>
-      </c>
+      <c r="E114" s="4" t="inlineStr"/>
+      <c r="F114" s="4" t="inlineStr"/>
       <c r="G114" s="4" t="n">
         <v>-2638</v>
       </c>
@@ -30363,16 +29515,8 @@
           <t>泰藝</t>
         </is>
       </c>
-      <c r="E115" s="4" t="inlineStr">
-        <is>
-          <t>68.00</t>
-        </is>
-      </c>
-      <c r="F115" s="4" t="inlineStr">
-        <is>
-          <t>-4.6</t>
-        </is>
-      </c>
+      <c r="E115" s="4" t="inlineStr"/>
+      <c r="F115" s="4" t="inlineStr"/>
       <c r="G115" s="4" t="n">
         <v>-2027</v>
       </c>
@@ -30396,16 +29540,8 @@
           <t>台燿</t>
         </is>
       </c>
-      <c r="E116" s="4" t="inlineStr">
-        <is>
-          <t>1430.00</t>
-        </is>
-      </c>
-      <c r="F116" s="4" t="inlineStr">
-        <is>
-          <t>-45.0</t>
-        </is>
-      </c>
+      <c r="E116" s="4" t="inlineStr"/>
+      <c r="F116" s="4" t="inlineStr"/>
       <c r="G116" s="4" t="n">
         <v>-1837</v>
       </c>
@@ -30429,16 +29565,8 @@
           <t>艾訊</t>
         </is>
       </c>
-      <c r="E117" s="4" t="inlineStr">
-        <is>
-          <t>141.00</t>
-        </is>
-      </c>
-      <c r="F117" s="4" t="inlineStr">
-        <is>
-          <t>-4.0</t>
-        </is>
-      </c>
+      <c r="E117" s="4" t="inlineStr"/>
+      <c r="F117" s="4" t="inlineStr"/>
       <c r="G117" s="4" t="n">
         <v>-1755</v>
       </c>
@@ -30462,16 +29590,8 @@
           <t>加高</t>
         </is>
       </c>
-      <c r="E118" s="4" t="inlineStr">
-        <is>
-          <t>53.60</t>
-        </is>
-      </c>
-      <c r="F118" s="4" t="inlineStr">
-        <is>
-          <t>-0.9</t>
-        </is>
-      </c>
+      <c r="E118" s="4" t="inlineStr"/>
+      <c r="F118" s="4" t="inlineStr"/>
       <c r="G118" s="4" t="n">
         <v>-1733</v>
       </c>
@@ -30495,16 +29615,8 @@
           <t>康和證</t>
         </is>
       </c>
-      <c r="E119" s="4" t="inlineStr">
-        <is>
-          <t>28.45</t>
-        </is>
-      </c>
-      <c r="F119" s="4" t="inlineStr">
-        <is>
-          <t>+1.35</t>
-        </is>
-      </c>
+      <c r="E119" s="4" t="inlineStr"/>
+      <c r="F119" s="4" t="inlineStr"/>
       <c r="G119" s="4" t="n">
         <v>-1580</v>
       </c>
@@ -30528,16 +29640,8 @@
           <t>先進光</t>
         </is>
       </c>
-      <c r="E120" s="4" t="inlineStr">
-        <is>
-          <t>160.50</t>
-        </is>
-      </c>
-      <c r="F120" s="4" t="inlineStr">
-        <is>
-          <t>-3.5</t>
-        </is>
-      </c>
+      <c r="E120" s="4" t="inlineStr"/>
+      <c r="F120" s="4" t="inlineStr"/>
       <c r="G120" s="4" t="n">
         <v>-1361</v>
       </c>
@@ -30561,16 +29665,8 @@
           <t>安碁</t>
         </is>
       </c>
-      <c r="E121" s="4" t="inlineStr">
-        <is>
-          <t>50.30</t>
-        </is>
-      </c>
-      <c r="F121" s="4" t="inlineStr">
-        <is>
-          <t>-1.4</t>
-        </is>
-      </c>
+      <c r="E121" s="4" t="inlineStr"/>
+      <c r="F121" s="4" t="inlineStr"/>
       <c r="G121" s="4" t="n">
         <v>-1289</v>
       </c>
@@ -30594,16 +29690,8 @@
           <t>堡達</t>
         </is>
       </c>
-      <c r="E122" s="4" t="inlineStr">
-        <is>
-          <t>75.60</t>
-        </is>
-      </c>
-      <c r="F122" s="4" t="inlineStr">
-        <is>
-          <t>-2.7</t>
-        </is>
-      </c>
+      <c r="E122" s="4" t="inlineStr"/>
+      <c r="F122" s="4" t="inlineStr"/>
       <c r="G122" s="4" t="n">
         <v>-1041</v>
       </c>
@@ -30627,16 +29715,8 @@
           <t>碩禾</t>
         </is>
       </c>
-      <c r="E123" s="4" t="inlineStr">
-        <is>
-          <t>158.50</t>
-        </is>
-      </c>
-      <c r="F123" s="4" t="inlineStr">
-        <is>
-          <t>-8.5</t>
-        </is>
-      </c>
+      <c r="E123" s="4" t="inlineStr"/>
+      <c r="F123" s="4" t="inlineStr"/>
       <c r="G123" s="4" t="n">
         <v>-984</v>
       </c>
@@ -30660,16 +29740,8 @@
           <t>倍微</t>
         </is>
       </c>
-      <c r="E124" s="4" t="inlineStr">
-        <is>
-          <t>34.40</t>
-        </is>
-      </c>
-      <c r="F124" s="4" t="inlineStr">
-        <is>
-          <t>-0.8</t>
-        </is>
-      </c>
+      <c r="E124" s="4" t="inlineStr"/>
+      <c r="F124" s="4" t="inlineStr"/>
       <c r="G124" s="4" t="n">
         <v>-961</v>
       </c>
@@ -30693,16 +29765,8 @@
           <t>良維</t>
         </is>
       </c>
-      <c r="E125" s="4" t="inlineStr">
-        <is>
-          <t>301.50</t>
-        </is>
-      </c>
-      <c r="F125" s="4" t="inlineStr">
-        <is>
-          <t>+5.0</t>
-        </is>
-      </c>
+      <c r="E125" s="4" t="inlineStr"/>
+      <c r="F125" s="4" t="inlineStr"/>
       <c r="G125" s="4" t="n">
         <v>-957</v>
       </c>
@@ -30726,16 +29790,8 @@
           <t>鈊象</t>
         </is>
       </c>
-      <c r="E126" s="4" t="inlineStr">
-        <is>
-          <t>755.00</t>
-        </is>
-      </c>
-      <c r="F126" s="4" t="inlineStr">
-        <is>
-          <t>-7.0</t>
-        </is>
-      </c>
+      <c r="E126" s="4" t="inlineStr"/>
+      <c r="F126" s="4" t="inlineStr"/>
       <c r="G126" s="4" t="n">
         <v>-898</v>
       </c>
@@ -30759,16 +29815,8 @@
           <t>蜜望實</t>
         </is>
       </c>
-      <c r="E127" s="4" t="inlineStr">
-        <is>
-          <t>184.50</t>
-        </is>
-      </c>
-      <c r="F127" s="4" t="inlineStr">
-        <is>
-          <t>-7.0</t>
-        </is>
-      </c>
+      <c r="E127" s="4" t="inlineStr"/>
+      <c r="F127" s="4" t="inlineStr"/>
       <c r="G127" s="4" t="n">
         <v>-887</v>
       </c>
@@ -30792,16 +29840,8 @@
           <t>聯一光</t>
         </is>
       </c>
-      <c r="E128" s="4" t="inlineStr">
-        <is>
-          <t>70.00</t>
-        </is>
-      </c>
-      <c r="F128" s="4" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
+      <c r="E128" s="4" t="inlineStr"/>
+      <c r="F128" s="4" t="inlineStr"/>
       <c r="G128" s="4" t="n">
         <v>-883</v>
       </c>
@@ -30825,16 +29865,8 @@
           <t>中裕</t>
         </is>
       </c>
-      <c r="E129" s="4" t="inlineStr">
-        <is>
-          <t>57.30</t>
-        </is>
-      </c>
-      <c r="F129" s="4" t="inlineStr">
-        <is>
-          <t>-1.3</t>
-        </is>
-      </c>
+      <c r="E129" s="4" t="inlineStr"/>
+      <c r="F129" s="4" t="inlineStr"/>
       <c r="G129" s="4" t="n">
         <v>-841</v>
       </c>
@@ -30858,16 +29890,8 @@
           <t>宏遠證</t>
         </is>
       </c>
-      <c r="E130" s="4" t="inlineStr">
-        <is>
-          <t>18.50</t>
-        </is>
-      </c>
-      <c r="F130" s="4" t="inlineStr">
-        <is>
-          <t>+0.65</t>
-        </is>
-      </c>
+      <c r="E130" s="4" t="inlineStr"/>
+      <c r="F130" s="4" t="inlineStr"/>
       <c r="G130" s="4" t="n">
         <v>-757</v>
       </c>
@@ -30891,16 +29915,8 @@
           <t>新盛力</t>
         </is>
       </c>
-      <c r="E131" s="4" t="inlineStr">
-        <is>
-          <t>236.00</t>
-        </is>
-      </c>
-      <c r="F131" s="4" t="inlineStr">
-        <is>
-          <t>+2.0</t>
-        </is>
-      </c>
+      <c r="E131" s="4" t="inlineStr"/>
+      <c r="F131" s="4" t="inlineStr"/>
       <c r="G131" s="4" t="n">
         <v>-727</v>
       </c>
@@ -30924,16 +29940,8 @@
           <t>今展科</t>
         </is>
       </c>
-      <c r="E132" s="4" t="inlineStr">
-        <is>
-          <t>70.10</t>
-        </is>
-      </c>
-      <c r="F132" s="4" t="inlineStr">
-        <is>
-          <t>-2.8</t>
-        </is>
-      </c>
+      <c r="E132" s="4" t="inlineStr"/>
+      <c r="F132" s="4" t="inlineStr"/>
       <c r="G132" s="4" t="n">
         <v>-727</v>
       </c>
@@ -30957,16 +29965,8 @@
           <t>台嘉碩</t>
         </is>
       </c>
-      <c r="E133" s="4" t="inlineStr">
-        <is>
-          <t>60.40</t>
-        </is>
-      </c>
-      <c r="F133" s="4" t="inlineStr">
-        <is>
-          <t>+0.4</t>
-        </is>
-      </c>
+      <c r="E133" s="4" t="inlineStr"/>
+      <c r="F133" s="4" t="inlineStr"/>
       <c r="G133" s="4" t="n">
         <v>-627</v>
       </c>
@@ -30990,16 +29990,8 @@
           <t>九暘</t>
         </is>
       </c>
-      <c r="E134" s="4" t="inlineStr">
-        <is>
-          <t>95.20</t>
-        </is>
-      </c>
-      <c r="F134" s="4" t="inlineStr">
-        <is>
-          <t>-1.3</t>
-        </is>
-      </c>
+      <c r="E134" s="4" t="inlineStr"/>
+      <c r="F134" s="4" t="inlineStr"/>
       <c r="G134" s="4" t="n">
         <v>-610</v>
       </c>
@@ -31023,16 +30015,8 @@
           <t>立端</t>
         </is>
       </c>
-      <c r="E135" s="4" t="inlineStr">
-        <is>
-          <t>81.00</t>
-        </is>
-      </c>
-      <c r="F135" s="4" t="inlineStr">
-        <is>
-          <t>-1.4</t>
-        </is>
-      </c>
+      <c r="E135" s="4" t="inlineStr"/>
+      <c r="F135" s="4" t="inlineStr"/>
       <c r="G135" s="4" t="n">
         <v>-590</v>
       </c>
@@ -31056,16 +30040,8 @@
           <t>皇將</t>
         </is>
       </c>
-      <c r="E136" s="4" t="inlineStr">
-        <is>
-          <t>30.40</t>
-        </is>
-      </c>
-      <c r="F136" s="4" t="inlineStr">
-        <is>
-          <t>-3.35</t>
-        </is>
-      </c>
+      <c r="E136" s="4" t="inlineStr"/>
+      <c r="F136" s="4" t="inlineStr"/>
       <c r="G136" s="4" t="n">
         <v>-574</v>
       </c>
@@ -31089,16 +30065,8 @@
           <t>威剛</t>
         </is>
       </c>
-      <c r="E137" s="4" t="inlineStr">
-        <is>
-          <t>405.50</t>
-        </is>
-      </c>
-      <c r="F137" s="4" t="inlineStr">
-        <is>
-          <t>+11.0</t>
-        </is>
-      </c>
+      <c r="E137" s="4" t="inlineStr"/>
+      <c r="F137" s="4" t="inlineStr"/>
       <c r="G137" s="4" t="n">
         <v>-565</v>
       </c>
@@ -31122,16 +30090,8 @@
           <t>中探針</t>
         </is>
       </c>
-      <c r="E138" s="4" t="inlineStr">
-        <is>
-          <t>239.00</t>
-        </is>
-      </c>
-      <c r="F138" s="4" t="inlineStr">
-        <is>
-          <t>+11.0</t>
-        </is>
-      </c>
+      <c r="E138" s="4" t="inlineStr"/>
+      <c r="F138" s="4" t="inlineStr"/>
       <c r="G138" s="4" t="n">
         <v>-565</v>
       </c>
@@ -31155,16 +30115,8 @@
           <t>光環</t>
         </is>
       </c>
-      <c r="E139" s="4" t="inlineStr">
-        <is>
-          <t>111.50</t>
-        </is>
-      </c>
-      <c r="F139" s="4" t="inlineStr">
-        <is>
-          <t>+2.5</t>
-        </is>
-      </c>
+      <c r="E139" s="4" t="inlineStr"/>
+      <c r="F139" s="4" t="inlineStr"/>
       <c r="G139" s="4" t="n">
         <v>-515</v>
       </c>
@@ -31188,16 +30140,8 @@
           <t>橘子</t>
         </is>
       </c>
-      <c r="E140" s="4" t="inlineStr">
-        <is>
-          <t>44.60</t>
-        </is>
-      </c>
-      <c r="F140" s="4" t="inlineStr">
-        <is>
-          <t>-0.65</t>
-        </is>
-      </c>
+      <c r="E140" s="4" t="inlineStr"/>
+      <c r="F140" s="4" t="inlineStr"/>
       <c r="G140" s="4" t="n">
         <v>-506</v>
       </c>
@@ -31221,16 +30165,8 @@
           <t>新鉅科</t>
         </is>
       </c>
-      <c r="E141" s="4" t="inlineStr">
-        <is>
-          <t>29.10</t>
-        </is>
-      </c>
-      <c r="F141" s="4" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
+      <c r="E141" s="4" t="inlineStr"/>
+      <c r="F141" s="4" t="inlineStr"/>
       <c r="G141" s="4" t="n">
         <v>-505</v>
       </c>
@@ -31254,16 +30190,8 @@
           <t>霖宏</t>
         </is>
       </c>
-      <c r="E142" s="4" t="inlineStr">
-        <is>
-          <t>71.80</t>
-        </is>
-      </c>
-      <c r="F142" s="4" t="inlineStr">
-        <is>
-          <t>+1.9</t>
-        </is>
-      </c>
+      <c r="E142" s="4" t="inlineStr"/>
+      <c r="F142" s="4" t="inlineStr"/>
       <c r="G142" s="4" t="n">
         <v>-498</v>
       </c>
@@ -31287,16 +30215,8 @@
           <t>群聯</t>
         </is>
       </c>
-      <c r="E143" s="4" t="inlineStr">
-        <is>
-          <t>2310.00</t>
-        </is>
-      </c>
-      <c r="F143" s="4" t="inlineStr">
-        <is>
-          <t>+110.0</t>
-        </is>
-      </c>
+      <c r="E143" s="4" t="inlineStr"/>
+      <c r="F143" s="4" t="inlineStr"/>
       <c r="G143" s="4" t="n">
         <v>-464</v>
       </c>
@@ -31320,16 +30240,8 @@
           <t>廣積</t>
         </is>
       </c>
-      <c r="E144" s="4" t="inlineStr">
-        <is>
-          <t>57.70</t>
-        </is>
-      </c>
-      <c r="F144" s="4" t="inlineStr">
-        <is>
-          <t>-0.8</t>
-        </is>
-      </c>
+      <c r="E144" s="4" t="inlineStr"/>
+      <c r="F144" s="4" t="inlineStr"/>
       <c r="G144" s="4" t="n">
         <v>-453</v>
       </c>
@@ -31353,16 +30265,8 @@
           <t>昇達科</t>
         </is>
       </c>
-      <c r="E145" s="4" t="inlineStr">
-        <is>
-          <t>1690.00</t>
-        </is>
-      </c>
-      <c r="F145" s="4" t="inlineStr">
-        <is>
-          <t>+10.0</t>
-        </is>
-      </c>
+      <c r="E145" s="4" t="inlineStr"/>
+      <c r="F145" s="4" t="inlineStr"/>
       <c r="G145" s="4" t="n">
         <v>-407</v>
       </c>
@@ -31386,16 +30290,8 @@
           <t>元太</t>
         </is>
       </c>
-      <c r="E146" s="4" t="inlineStr">
-        <is>
-          <t>196.00</t>
-        </is>
-      </c>
-      <c r="F146" s="4" t="inlineStr">
-        <is>
-          <t>+5.5</t>
-        </is>
-      </c>
+      <c r="E146" s="4" t="inlineStr"/>
+      <c r="F146" s="4" t="inlineStr"/>
       <c r="G146" s="4" t="n">
         <v>-402</v>
       </c>
@@ -31419,16 +30315,8 @@
           <t>廣運</t>
         </is>
       </c>
-      <c r="E147" s="4" t="inlineStr">
-        <is>
-          <t>60.50</t>
-        </is>
-      </c>
-      <c r="F147" s="4" t="inlineStr">
-        <is>
-          <t>+0.6</t>
-        </is>
-      </c>
+      <c r="E147" s="4" t="inlineStr"/>
+      <c r="F147" s="4" t="inlineStr"/>
       <c r="G147" s="4" t="n">
         <v>-398</v>
       </c>
@@ -31452,16 +30340,8 @@
           <t>松上</t>
         </is>
       </c>
-      <c r="E148" s="4" t="inlineStr">
-        <is>
-          <t>20.55</t>
-        </is>
-      </c>
-      <c r="F148" s="4" t="inlineStr">
-        <is>
-          <t>+0.1</t>
-        </is>
-      </c>
+      <c r="E148" s="4" t="inlineStr"/>
+      <c r="F148" s="4" t="inlineStr"/>
       <c r="G148" s="4" t="n">
         <v>-395</v>
       </c>
@@ -31485,16 +30365,8 @@
           <t>綠界科技*</t>
         </is>
       </c>
-      <c r="E149" s="4" t="inlineStr">
-        <is>
-          <t>48.20</t>
-        </is>
-      </c>
-      <c r="F149" s="4" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
+      <c r="E149" s="4" t="inlineStr"/>
+      <c r="F149" s="4" t="inlineStr"/>
       <c r="G149" s="4" t="n">
         <v>-388</v>
       </c>
@@ -31518,16 +30390,8 @@
           <t>萬旭</t>
         </is>
       </c>
-      <c r="E150" s="4" t="inlineStr">
-        <is>
-          <t>35.50</t>
-        </is>
-      </c>
-      <c r="F150" s="4" t="inlineStr">
-        <is>
-          <t>+0.05</t>
-        </is>
-      </c>
+      <c r="E150" s="4" t="inlineStr"/>
+      <c r="F150" s="4" t="inlineStr"/>
       <c r="G150" s="4" t="n">
         <v>-377</v>
       </c>
@@ -31551,16 +30415,8 @@
           <t>德微</t>
         </is>
       </c>
-      <c r="E151" s="4" t="inlineStr">
-        <is>
-          <t>311.00</t>
-        </is>
-      </c>
-      <c r="F151" s="4" t="inlineStr">
-        <is>
-          <t>+11.0</t>
-        </is>
-      </c>
+      <c r="E151" s="4" t="inlineStr"/>
+      <c r="F151" s="4" t="inlineStr"/>
       <c r="G151" s="4" t="n">
         <v>-357</v>
       </c>
@@ -31584,16 +30440,8 @@
           <t>雷科</t>
         </is>
       </c>
-      <c r="E152" s="4" t="inlineStr">
-        <is>
-          <t>124.00</t>
-        </is>
-      </c>
-      <c r="F152" s="4" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
+      <c r="E152" s="4" t="inlineStr"/>
+      <c r="F152" s="4" t="inlineStr"/>
       <c r="G152" s="4" t="n">
         <v>-346</v>
       </c>
@@ -31617,16 +30465,8 @@
           <t>百徽</t>
         </is>
       </c>
-      <c r="E153" s="4" t="inlineStr">
-        <is>
-          <t>27.60</t>
-        </is>
-      </c>
-      <c r="F153" s="4" t="inlineStr">
-        <is>
-          <t>-2.15</t>
-        </is>
-      </c>
+      <c r="E153" s="4" t="inlineStr"/>
+      <c r="F153" s="4" t="inlineStr"/>
       <c r="G153" s="4" t="n">
         <v>-339</v>
       </c>
@@ -31650,16 +30490,8 @@
           <t>安勤</t>
         </is>
       </c>
-      <c r="E154" s="4" t="inlineStr">
-        <is>
-          <t>133.00</t>
-        </is>
-      </c>
-      <c r="F154" s="4" t="inlineStr">
-        <is>
-          <t>+1.0</t>
-        </is>
-      </c>
+      <c r="E154" s="4" t="inlineStr"/>
+      <c r="F154" s="4" t="inlineStr"/>
       <c r="G154" s="4" t="n">
         <v>-329</v>
       </c>
@@ -31683,16 +30515,8 @@
           <t>安可</t>
         </is>
       </c>
-      <c r="E155" s="4" t="inlineStr">
-        <is>
-          <t>49.65</t>
-        </is>
-      </c>
-      <c r="F155" s="4" t="inlineStr">
-        <is>
-          <t>-0.85</t>
-        </is>
-      </c>
+      <c r="E155" s="4" t="inlineStr"/>
+      <c r="F155" s="4" t="inlineStr"/>
       <c r="G155" s="4" t="n">
         <v>-322</v>
       </c>
@@ -31716,16 +30540,8 @@
           <t>萬泰科</t>
         </is>
       </c>
-      <c r="E156" s="4" t="inlineStr">
-        <is>
-          <t>80.40</t>
-        </is>
-      </c>
-      <c r="F156" s="4" t="inlineStr">
-        <is>
-          <t>+1.4</t>
-        </is>
-      </c>
+      <c r="E156" s="4" t="inlineStr"/>
+      <c r="F156" s="4" t="inlineStr"/>
       <c r="G156" s="4" t="n">
         <v>-316</v>
       </c>
@@ -31749,16 +30565,8 @@
           <t>萬潤</t>
         </is>
       </c>
-      <c r="E157" s="4" t="inlineStr">
-        <is>
-          <t>1085.00</t>
-        </is>
-      </c>
-      <c r="F157" s="4" t="inlineStr">
-        <is>
-          <t>+55.0</t>
-        </is>
-      </c>
+      <c r="E157" s="4" t="inlineStr"/>
+      <c r="F157" s="4" t="inlineStr"/>
       <c r="G157" s="4" t="n">
         <v>-309</v>
       </c>
@@ -31782,16 +30590,8 @@
           <t>聯寶</t>
         </is>
       </c>
-      <c r="E158" s="4" t="inlineStr">
-        <is>
-          <t>67.50</t>
-        </is>
-      </c>
-      <c r="F158" s="4" t="inlineStr">
-        <is>
-          <t>+0.2</t>
-        </is>
-      </c>
+      <c r="E158" s="4" t="inlineStr"/>
+      <c r="F158" s="4" t="inlineStr"/>
       <c r="G158" s="4" t="n">
         <v>-283</v>
       </c>

--- a/StockInfo/otc_analysis_result.xlsx
+++ b/StockInfo/otc_analysis_result.xlsx
@@ -4324,94 +4324,94 @@
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>8071</t>
+          <t>1785</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>能率網通</t>
+          <t>光洋科</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>其他電子業</t>
         </is>
       </c>
       <c r="D125" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22, 23, 25</t>
         </is>
       </c>
       <c r="F125" s="4" t="n">
-        <v>828</v>
+        <v>4861</v>
       </c>
       <c r="G125" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H125" s="4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>-1148</v>
+        <v>-5181</v>
       </c>
       <c r="J125" s="4" t="n">
         <v>-320</v>
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>[('sell', '26'), ('neutral', '25'), ('neutral', '24'), ('buy', '23'), ('neutral', '22')]</t>
+          <t>[('neutral', '26'), ('buy', '25'), ('sell', '24'), ('buy', '23'), ('buy', '22')]</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t>1785</t>
+          <t>8071</t>
         </is>
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>光洋科</t>
+          <t>能率網通</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>其他電子業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D126" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>22, 23, 25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="F126" s="4" t="n">
-        <v>4861</v>
+        <v>828</v>
       </c>
       <c r="G126" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H126" s="4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>-5181</v>
+        <v>-1148</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>-320</v>
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>[('neutral', '26'), ('buy', '25'), ('sell', '24'), ('buy', '23'), ('buy', '22')]</t>
+          <t>[('sell', '26'), ('neutral', '25'), ('neutral', '24'), ('buy', '23'), ('neutral', '22')]</t>
         </is>
       </c>
     </row>
@@ -26759,16 +26759,8 @@
           <t>富喬</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>106.50</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>+8.4</t>
-        </is>
-      </c>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr"/>
       <c r="G4" s="4" t="n">
         <v>11593</v>
       </c>
@@ -26792,16 +26784,8 @@
           <t>漢磊</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>91.50</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>+8.3</t>
-        </is>
-      </c>
+      <c r="E5" s="4" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr"/>
       <c r="G5" s="4" t="n">
         <v>9977</v>
       </c>
@@ -26825,16 +26809,8 @@
           <t>鈺創</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>99.80</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>+5.8</t>
-        </is>
-      </c>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr"/>
       <c r="G6" s="4" t="n">
         <v>4421</v>
       </c>
@@ -26858,16 +26834,8 @@
           <t>榮剛</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>37.00</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>+2.25</t>
-        </is>
-      </c>
+      <c r="E7" s="4" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr"/>
       <c r="G7" s="4" t="n">
         <v>3865</v>
       </c>
@@ -26891,16 +26859,8 @@
           <t>欣銓</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>242.00</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>+9.5</t>
-        </is>
-      </c>
+      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr"/>
       <c r="G8" s="4" t="n">
         <v>3712</v>
       </c>
@@ -26924,16 +26884,8 @@
           <t>穩懋</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>541.00</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>+13.0</t>
-        </is>
-      </c>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr"/>
       <c r="G9" s="4" t="n">
         <v>3332</v>
       </c>
@@ -26957,16 +26909,8 @@
           <t>光頡</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>176.50</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>+16.0</t>
-        </is>
-      </c>
+      <c r="E10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr"/>
       <c r="G10" s="4" t="n">
         <v>3142</v>
       </c>
@@ -26990,16 +26934,8 @@
           <t>頎邦</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>277.00</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>+25.0</t>
-        </is>
-      </c>
+      <c r="E11" s="4" t="inlineStr"/>
+      <c r="F11" s="4" t="inlineStr"/>
       <c r="G11" s="4" t="n">
         <v>2976</v>
       </c>
@@ -27023,16 +26959,8 @@
           <t>光洋科</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>+1.0</t>
-        </is>
-      </c>
+      <c r="E12" s="4" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr"/>
       <c r="G12" s="4" t="n">
         <v>2844</v>
       </c>
@@ -27056,16 +26984,8 @@
           <t>精材</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>276.00</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>+25.0</t>
-        </is>
-      </c>
+      <c r="E13" s="4" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr"/>
       <c r="G13" s="4" t="n">
         <v>2726</v>
       </c>
@@ -27089,16 +27009,8 @@
           <t>安國</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>113.50</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>+10.0</t>
-        </is>
-      </c>
+      <c r="E14" s="4" t="inlineStr"/>
+      <c r="F14" s="4" t="inlineStr"/>
       <c r="G14" s="4" t="n">
         <v>2434</v>
       </c>
@@ -27122,16 +27034,8 @@
           <t>佶優</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>35.55</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>+1.65</t>
-        </is>
-      </c>
+      <c r="E15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr"/>
       <c r="G15" s="4" t="n">
         <v>2039</v>
       </c>
@@ -27155,16 +27059,8 @@
           <t>安可</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>60.90</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>+5.5</t>
-        </is>
-      </c>
+      <c r="E16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr"/>
       <c r="G16" s="4" t="n">
         <v>1476</v>
       </c>
@@ -27188,16 +27084,8 @@
           <t>凱崴</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>68.90</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>+1.8</t>
-        </is>
-      </c>
+      <c r="E17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr"/>
       <c r="G17" s="4" t="n">
         <v>1432</v>
       </c>
@@ -27221,16 +27109,8 @@
           <t>長科*</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>94.70</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>+8.6</t>
-        </is>
-      </c>
+      <c r="E18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr"/>
       <c r="G18" s="4" t="n">
         <v>1310</v>
       </c>
@@ -27254,16 +27134,8 @@
           <t>致和證</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>50.50</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>+1.45</t>
-        </is>
-      </c>
+      <c r="E19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr"/>
       <c r="G19" s="4" t="n">
         <v>1275</v>
       </c>
@@ -27287,16 +27159,8 @@
           <t>順達</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>452.50</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>+16.5</t>
-        </is>
-      </c>
+      <c r="E20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr"/>
       <c r="G20" s="4" t="n">
         <v>1233</v>
       </c>
@@ -27320,16 +27184,8 @@
           <t>創惟</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>108.50</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>+5.0</t>
-        </is>
-      </c>
+      <c r="E21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr"/>
       <c r="G21" s="4" t="n">
         <v>1123</v>
       </c>
@@ -27353,16 +27209,8 @@
           <t>中光電</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>74.60</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>+4.6</t>
-        </is>
-      </c>
+      <c r="E22" s="4" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr"/>
       <c r="G22" s="4" t="n">
         <v>1101</v>
       </c>
@@ -27386,16 +27234,8 @@
           <t>東捷</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>165.50</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>+9.5</t>
-        </is>
-      </c>
+      <c r="E23" s="4" t="inlineStr"/>
+      <c r="F23" s="4" t="inlineStr"/>
       <c r="G23" s="4" t="n">
         <v>1080</v>
       </c>
@@ -27419,16 +27259,8 @@
           <t>原相</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>230.00</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>+5.0</t>
-        </is>
-      </c>
+      <c r="E24" s="4" t="inlineStr"/>
+      <c r="F24" s="4" t="inlineStr"/>
       <c r="G24" s="4" t="n">
         <v>1028</v>
       </c>
@@ -27452,16 +27284,8 @@
           <t>建榮</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>99.00</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>+9.0</t>
-        </is>
-      </c>
+      <c r="E25" s="4" t="inlineStr"/>
+      <c r="F25" s="4" t="inlineStr"/>
       <c r="G25" s="4" t="n">
         <v>1004</v>
       </c>
@@ -27485,16 +27309,8 @@
           <t>金居</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>691.00</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>-9.0</t>
-        </is>
-      </c>
+      <c r="E26" s="4" t="inlineStr"/>
+      <c r="F26" s="4" t="inlineStr"/>
       <c r="G26" s="4" t="n">
         <v>946</v>
       </c>
@@ -27518,16 +27334,8 @@
           <t>普誠</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>17.00</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>+1.1</t>
-        </is>
-      </c>
+      <c r="E27" s="4" t="inlineStr"/>
+      <c r="F27" s="4" t="inlineStr"/>
       <c r="G27" s="4" t="n">
         <v>941</v>
       </c>
@@ -27551,16 +27359,8 @@
           <t>松上</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>26.75</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>+2.4</t>
-        </is>
-      </c>
+      <c r="E28" s="4" t="inlineStr"/>
+      <c r="F28" s="4" t="inlineStr"/>
       <c r="G28" s="4" t="n">
         <v>940</v>
       </c>
@@ -27584,16 +27384,8 @@
           <t>朋程</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>214.50</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>+19.5</t>
-        </is>
-      </c>
+      <c r="E29" s="4" t="inlineStr"/>
+      <c r="F29" s="4" t="inlineStr"/>
       <c r="G29" s="4" t="n">
         <v>885</v>
       </c>
@@ -27617,16 +27409,8 @@
           <t>環球晶</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>1115.00</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>+5.0</t>
-        </is>
-      </c>
+      <c r="E30" s="4" t="inlineStr"/>
+      <c r="F30" s="4" t="inlineStr"/>
       <c r="G30" s="4" t="n">
         <v>835</v>
       </c>
@@ -27650,16 +27434,8 @@
           <t>鉅橡</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>77.70</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>+3.8</t>
-        </is>
-      </c>
+      <c r="E31" s="4" t="inlineStr"/>
+      <c r="F31" s="4" t="inlineStr"/>
       <c r="G31" s="4" t="n">
         <v>789</v>
       </c>
@@ -27683,16 +27459,8 @@
           <t>九豪</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>85.30</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>+0.9</t>
-        </is>
-      </c>
+      <c r="E32" s="4" t="inlineStr"/>
+      <c r="F32" s="4" t="inlineStr"/>
       <c r="G32" s="4" t="n">
         <v>748</v>
       </c>
@@ -27716,16 +27484,8 @@
           <t>康和證</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>29.75</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>+0.95</t>
-        </is>
-      </c>
+      <c r="E33" s="4" t="inlineStr"/>
+      <c r="F33" s="4" t="inlineStr"/>
       <c r="G33" s="4" t="n">
         <v>743</v>
       </c>
@@ -27749,16 +27509,8 @@
           <t>碩禾</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>162.00</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>+7.5</t>
-        </is>
-      </c>
+      <c r="E34" s="4" t="inlineStr"/>
+      <c r="F34" s="4" t="inlineStr"/>
       <c r="G34" s="4" t="n">
         <v>697</v>
       </c>
@@ -27782,16 +27534,8 @@
           <t>華電網</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>51.00</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>+1.05</t>
-        </is>
-      </c>
+      <c r="E35" s="4" t="inlineStr"/>
+      <c r="F35" s="4" t="inlineStr"/>
       <c r="G35" s="4" t="n">
         <v>694</v>
       </c>
@@ -27815,16 +27559,8 @@
           <t>高鋒</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>46.70</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>+1.4</t>
-        </is>
-      </c>
+      <c r="E36" s="4" t="inlineStr"/>
+      <c r="F36" s="4" t="inlineStr"/>
       <c r="G36" s="4" t="n">
         <v>644</v>
       </c>
@@ -27848,16 +27584,8 @@
           <t>穩得</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>222.00</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>+18.0</t>
-        </is>
-      </c>
+      <c r="E37" s="4" t="inlineStr"/>
+      <c r="F37" s="4" t="inlineStr"/>
       <c r="G37" s="4" t="n">
         <v>638</v>
       </c>
@@ -27881,16 +27609,8 @@
           <t>力麒</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>8.00</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>+0.05</t>
-        </is>
-      </c>
+      <c r="E38" s="4" t="inlineStr"/>
+      <c r="F38" s="4" t="inlineStr"/>
       <c r="G38" s="4" t="n">
         <v>601</v>
       </c>
@@ -27914,16 +27634,8 @@
           <t>台燿</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>1900.00</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>+65.0</t>
-        </is>
-      </c>
+      <c r="E39" s="4" t="inlineStr"/>
+      <c r="F39" s="4" t="inlineStr"/>
       <c r="G39" s="4" t="n">
         <v>556</v>
       </c>
@@ -27947,16 +27659,8 @@
           <t>元山</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>51.40</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>+4.1</t>
-        </is>
-      </c>
+      <c r="E40" s="4" t="inlineStr"/>
+      <c r="F40" s="4" t="inlineStr"/>
       <c r="G40" s="4" t="n">
         <v>554</v>
       </c>
@@ -27980,16 +27684,8 @@
           <t>大甲</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>52.80</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>+4.75</t>
-        </is>
-      </c>
+      <c r="E41" s="4" t="inlineStr"/>
+      <c r="F41" s="4" t="inlineStr"/>
       <c r="G41" s="4" t="n">
         <v>526</v>
       </c>
@@ -28013,16 +27709,8 @@
           <t>士開</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>12.25</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>+0.15</t>
-        </is>
-      </c>
+      <c r="E42" s="4" t="inlineStr"/>
+      <c r="F42" s="4" t="inlineStr"/>
       <c r="G42" s="4" t="n">
         <v>525</v>
       </c>
@@ -28046,16 +27734,8 @@
           <t>茂達</t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>394.00</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>+35.5</t>
-        </is>
-      </c>
+      <c r="E43" s="4" t="inlineStr"/>
+      <c r="F43" s="4" t="inlineStr"/>
       <c r="G43" s="4" t="n">
         <v>524</v>
       </c>
@@ -28079,16 +27759,8 @@
           <t>尚立</t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>17.25</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>+1.0</t>
-        </is>
-      </c>
+      <c r="E44" s="4" t="inlineStr"/>
+      <c r="F44" s="4" t="inlineStr"/>
       <c r="G44" s="4" t="n">
         <v>510</v>
       </c>
@@ -28112,16 +27784,8 @@
           <t>艾訊</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>144.00</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
+      <c r="E45" s="4" t="inlineStr"/>
+      <c r="F45" s="4" t="inlineStr"/>
       <c r="G45" s="4" t="n">
         <v>470</v>
       </c>
@@ -28145,16 +27809,8 @@
           <t>尼克森</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>97.10</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>+8.8</t>
-        </is>
-      </c>
+      <c r="E46" s="4" t="inlineStr"/>
+      <c r="F46" s="4" t="inlineStr"/>
       <c r="G46" s="4" t="n">
         <v>461</v>
       </c>
@@ -28178,16 +27834,8 @@
           <t>宜鼎</t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>1970.00</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t>+40.0</t>
-        </is>
-      </c>
+      <c r="E47" s="4" t="inlineStr"/>
+      <c r="F47" s="4" t="inlineStr"/>
       <c r="G47" s="4" t="n">
         <v>454</v>
       </c>
@@ -28211,16 +27859,8 @@
           <t>系微</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>304.50</t>
-        </is>
-      </c>
-      <c r="F48" s="4" t="inlineStr">
-        <is>
-          <t>+27.5</t>
-        </is>
-      </c>
+      <c r="E48" s="4" t="inlineStr"/>
+      <c r="F48" s="4" t="inlineStr"/>
       <c r="G48" s="4" t="n">
         <v>451</v>
       </c>
@@ -28244,16 +27884,8 @@
           <t>中探針</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>271.50</t>
-        </is>
-      </c>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>+24.5</t>
-        </is>
-      </c>
+      <c r="E49" s="4" t="inlineStr"/>
+      <c r="F49" s="4" t="inlineStr"/>
       <c r="G49" s="4" t="n">
         <v>445</v>
       </c>
@@ -28277,16 +27909,8 @@
           <t>協易機</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>30.30</t>
-        </is>
-      </c>
-      <c r="F50" s="4" t="inlineStr">
-        <is>
-          <t>+0.1</t>
-        </is>
-      </c>
+      <c r="E50" s="4" t="inlineStr"/>
+      <c r="F50" s="4" t="inlineStr"/>
       <c r="G50" s="4" t="n">
         <v>400</v>
       </c>
@@ -28310,16 +27934,8 @@
           <t>協禧</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>33.60</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="inlineStr">
-        <is>
-          <t>+0.4</t>
-        </is>
-      </c>
+      <c r="E51" s="4" t="inlineStr"/>
+      <c r="F51" s="4" t="inlineStr"/>
       <c r="G51" s="4" t="n">
         <v>396</v>
       </c>
@@ -28343,16 +27959,8 @@
           <t>類比科</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>78.50</t>
-        </is>
-      </c>
-      <c r="F52" s="4" t="inlineStr">
-        <is>
-          <t>+5.9</t>
-        </is>
-      </c>
+      <c r="E52" s="4" t="inlineStr"/>
+      <c r="F52" s="4" t="inlineStr"/>
       <c r="G52" s="4" t="n">
         <v>394</v>
       </c>
@@ -28376,16 +27984,8 @@
           <t>川寶</t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>84.70</t>
-        </is>
-      </c>
-      <c r="F53" s="4" t="inlineStr">
-        <is>
-          <t>+7.7</t>
-        </is>
-      </c>
+      <c r="E53" s="4" t="inlineStr"/>
+      <c r="F53" s="4" t="inlineStr"/>
       <c r="G53" s="4" t="n">
         <v>393</v>
       </c>
@@ -28409,16 +28009,8 @@
           <t>由田</t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>266.00</t>
-        </is>
-      </c>
-      <c r="F54" s="4" t="inlineStr">
-        <is>
-          <t>+24.0</t>
-        </is>
-      </c>
+      <c r="E54" s="4" t="inlineStr"/>
+      <c r="F54" s="4" t="inlineStr"/>
       <c r="G54" s="4" t="n">
         <v>373</v>
       </c>
@@ -28442,16 +28034,8 @@
           <t>加高</t>
         </is>
       </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>49.10</t>
-        </is>
-      </c>
-      <c r="F55" s="4" t="inlineStr">
-        <is>
-          <t>-1.9</t>
-        </is>
-      </c>
+      <c r="E55" s="4" t="inlineStr"/>
+      <c r="F55" s="4" t="inlineStr"/>
       <c r="G55" s="4" t="n">
         <v>365</v>
       </c>
@@ -28475,16 +28059,8 @@
           <t>御嵿</t>
         </is>
       </c>
-      <c r="E56" s="4" t="inlineStr">
-        <is>
-          <t>12.95</t>
-        </is>
-      </c>
-      <c r="F56" s="4" t="inlineStr">
-        <is>
-          <t>+1.15</t>
-        </is>
-      </c>
+      <c r="E56" s="4" t="inlineStr"/>
+      <c r="F56" s="4" t="inlineStr"/>
       <c r="G56" s="4" t="n">
         <v>360</v>
       </c>
@@ -28508,16 +28084,8 @@
           <t>建舜電</t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr">
-        <is>
-          <t>15.35</t>
-        </is>
-      </c>
-      <c r="F57" s="4" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
+      <c r="E57" s="4" t="inlineStr"/>
+      <c r="F57" s="4" t="inlineStr"/>
       <c r="G57" s="4" t="n">
         <v>349</v>
       </c>
@@ -28541,16 +28109,8 @@
           <t>方土昶</t>
         </is>
       </c>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t>59.80</t>
-        </is>
-      </c>
-      <c r="F58" s="4" t="inlineStr">
-        <is>
-          <t>+2.2</t>
-        </is>
-      </c>
+      <c r="E58" s="4" t="inlineStr"/>
+      <c r="F58" s="4" t="inlineStr"/>
       <c r="G58" s="4" t="n">
         <v>345</v>
       </c>
@@ -28574,16 +28134,8 @@
           <t>風青</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>58.00</t>
-        </is>
-      </c>
-      <c r="F59" s="4" t="inlineStr">
-        <is>
-          <t>+5.2</t>
-        </is>
-      </c>
+      <c r="E59" s="4" t="inlineStr"/>
+      <c r="F59" s="4" t="inlineStr"/>
       <c r="G59" s="4" t="n">
         <v>337</v>
       </c>
@@ -28607,16 +28159,8 @@
           <t>熒茂</t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>24.20</t>
-        </is>
-      </c>
-      <c r="F60" s="4" t="inlineStr">
-        <is>
-          <t>+2.2</t>
-        </is>
-      </c>
+      <c r="E60" s="4" t="inlineStr"/>
+      <c r="F60" s="4" t="inlineStr"/>
       <c r="G60" s="4" t="n">
         <v>327</v>
       </c>
@@ -28640,16 +28184,8 @@
           <t>慶騰</t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>33.80</t>
-        </is>
-      </c>
-      <c r="F61" s="4" t="inlineStr">
-        <is>
-          <t>+0.15</t>
-        </is>
-      </c>
+      <c r="E61" s="4" t="inlineStr"/>
+      <c r="F61" s="4" t="inlineStr"/>
       <c r="G61" s="4" t="n">
         <v>326</v>
       </c>
@@ -28673,16 +28209,8 @@
           <t>萬旭</t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr">
-        <is>
-          <t>36.45</t>
-        </is>
-      </c>
-      <c r="F62" s="4" t="inlineStr">
-        <is>
-          <t>+0.9</t>
-        </is>
-      </c>
+      <c r="E62" s="4" t="inlineStr"/>
+      <c r="F62" s="4" t="inlineStr"/>
       <c r="G62" s="4" t="n">
         <v>319</v>
       </c>
@@ -28706,16 +28234,8 @@
           <t>加百裕</t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>36.00</t>
-        </is>
-      </c>
-      <c r="F63" s="4" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
+      <c r="E63" s="4" t="inlineStr"/>
+      <c r="F63" s="4" t="inlineStr"/>
       <c r="G63" s="4" t="n">
         <v>318</v>
       </c>
@@ -28739,16 +28259,8 @@
           <t>新鉅科</t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t>33.65</t>
-        </is>
-      </c>
-      <c r="F64" s="4" t="inlineStr">
-        <is>
-          <t>-1.15</t>
-        </is>
-      </c>
+      <c r="E64" s="4" t="inlineStr"/>
+      <c r="F64" s="4" t="inlineStr"/>
       <c r="G64" s="4" t="n">
         <v>302</v>
       </c>
@@ -28772,16 +28284,8 @@
           <t>亞通</t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr">
-        <is>
-          <t>26.70</t>
-        </is>
-      </c>
-      <c r="F65" s="4" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
+      <c r="E65" s="4" t="inlineStr"/>
+      <c r="F65" s="4" t="inlineStr"/>
       <c r="G65" s="4" t="n">
         <v>302</v>
       </c>
@@ -28805,16 +28309,8 @@
           <t>精星</t>
         </is>
       </c>
-      <c r="E66" s="4" t="inlineStr">
-        <is>
-          <t>33.10</t>
-        </is>
-      </c>
-      <c r="F66" s="4" t="inlineStr">
-        <is>
-          <t>+0.55</t>
-        </is>
-      </c>
+      <c r="E66" s="4" t="inlineStr"/>
+      <c r="F66" s="4" t="inlineStr"/>
       <c r="G66" s="4" t="n">
         <v>302</v>
       </c>
@@ -28838,16 +28334,8 @@
           <t>台星科</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>193.50</t>
-        </is>
-      </c>
-      <c r="F67" s="4" t="inlineStr">
-        <is>
-          <t>+4.0</t>
-        </is>
-      </c>
+      <c r="E67" s="4" t="inlineStr"/>
+      <c r="F67" s="4" t="inlineStr"/>
       <c r="G67" s="4" t="n">
         <v>296</v>
       </c>
@@ -28871,16 +28359,8 @@
           <t>精剛</t>
         </is>
       </c>
-      <c r="E68" s="4" t="inlineStr">
-        <is>
-          <t>19.55</t>
-        </is>
-      </c>
-      <c r="F68" s="4" t="inlineStr">
-        <is>
-          <t>nannan</t>
-        </is>
-      </c>
+      <c r="E68" s="4" t="inlineStr"/>
+      <c r="F68" s="4" t="inlineStr"/>
       <c r="G68" s="4" t="n">
         <v>294</v>
       </c>
@@ -28904,16 +28384,8 @@
           <t>聯光通</t>
         </is>
       </c>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>40.25</t>
-        </is>
-      </c>
-      <c r="F69" s="4" t="inlineStr">
-        <is>
-          <t>+1.45</t>
-        </is>
-      </c>
+      <c r="E69" s="4" t="inlineStr"/>
+      <c r="F69" s="4" t="inlineStr"/>
       <c r="G69" s="4" t="n">
         <v>289</v>
       </c>
@@ -28937,16 +28409,8 @@
           <t>新復興</t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr">
-        <is>
-          <t>49.85</t>
-        </is>
-      </c>
-      <c r="F70" s="4" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
+      <c r="E70" s="4" t="inlineStr"/>
+      <c r="F70" s="4" t="inlineStr"/>
       <c r="G70" s="4" t="n">
         <v>287</v>
       </c>
@@ -28970,16 +28434,8 @@
           <t>晶宏</t>
         </is>
       </c>
-      <c r="E71" s="4" t="inlineStr">
-        <is>
-          <t>78.40</t>
-        </is>
-      </c>
-      <c r="F71" s="4" t="inlineStr">
-        <is>
-          <t>+4.4</t>
-        </is>
-      </c>
+      <c r="E71" s="4" t="inlineStr"/>
+      <c r="F71" s="4" t="inlineStr"/>
       <c r="G71" s="4" t="n">
         <v>277</v>
       </c>
@@ -29003,16 +28459,8 @@
           <t>光譜</t>
         </is>
       </c>
-      <c r="E72" s="4" t="inlineStr">
-        <is>
-          <t>29.20</t>
-        </is>
-      </c>
-      <c r="F72" s="4" t="inlineStr">
-        <is>
-          <t>+1.4</t>
-        </is>
-      </c>
+      <c r="E72" s="4" t="inlineStr"/>
+      <c r="F72" s="4" t="inlineStr"/>
       <c r="G72" s="4" t="n">
         <v>270</v>
       </c>
@@ -29036,16 +28484,8 @@
           <t>安格</t>
         </is>
       </c>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>55.50</t>
-        </is>
-      </c>
-      <c r="F73" s="4" t="inlineStr">
-        <is>
-          <t>+5.0</t>
-        </is>
-      </c>
+      <c r="E73" s="4" t="inlineStr"/>
+      <c r="F73" s="4" t="inlineStr"/>
       <c r="G73" s="4" t="n">
         <v>263</v>
       </c>
@@ -29069,16 +28509,8 @@
           <t>信音</t>
         </is>
       </c>
-      <c r="E74" s="4" t="inlineStr">
-        <is>
-          <t>40.15</t>
-        </is>
-      </c>
-      <c r="F74" s="4" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
+      <c r="E74" s="4" t="inlineStr"/>
+      <c r="F74" s="4" t="inlineStr"/>
       <c r="G74" s="4" t="n">
         <v>257</v>
       </c>
@@ -29102,16 +28534,8 @@
           <t>英濟</t>
         </is>
       </c>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
-      </c>
-      <c r="F75" s="4" t="inlineStr">
-        <is>
-          <t>+0.3</t>
-        </is>
-      </c>
+      <c r="E75" s="4" t="inlineStr"/>
+      <c r="F75" s="4" t="inlineStr"/>
       <c r="G75" s="4" t="n">
         <v>254</v>
       </c>
@@ -29135,16 +28559,8 @@
           <t>聖暉*</t>
         </is>
       </c>
-      <c r="E76" s="4" t="inlineStr">
-        <is>
-          <t>1280.00</t>
-        </is>
-      </c>
-      <c r="F76" s="4" t="inlineStr">
-        <is>
-          <t>+15.0</t>
-        </is>
-      </c>
+      <c r="E76" s="4" t="inlineStr"/>
+      <c r="F76" s="4" t="inlineStr"/>
       <c r="G76" s="4" t="n">
         <v>253</v>
       </c>
@@ -29168,16 +28584,8 @@
           <t>合騏*</t>
         </is>
       </c>
-      <c r="E77" s="4" t="inlineStr">
-        <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="F77" s="4" t="inlineStr">
-        <is>
-          <t>+2.7</t>
-        </is>
-      </c>
+      <c r="E77" s="4" t="inlineStr"/>
+      <c r="F77" s="4" t="inlineStr"/>
       <c r="G77" s="4" t="n">
         <v>247</v>
       </c>
@@ -29201,16 +28609,8 @@
           <t>金山電</t>
         </is>
       </c>
-      <c r="E78" s="4" t="inlineStr">
-        <is>
-          <t>190.50</t>
-        </is>
-      </c>
-      <c r="F78" s="4" t="inlineStr">
-        <is>
-          <t>-4.5</t>
-        </is>
-      </c>
+      <c r="E78" s="4" t="inlineStr"/>
+      <c r="F78" s="4" t="inlineStr"/>
       <c r="G78" s="4" t="n">
         <v>226</v>
       </c>
@@ -29234,16 +28634,8 @@
           <t>力士</t>
         </is>
       </c>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t>63.40</t>
-        </is>
-      </c>
-      <c r="F79" s="4" t="inlineStr">
-        <is>
-          <t>+5.7</t>
-        </is>
-      </c>
+      <c r="E79" s="4" t="inlineStr"/>
+      <c r="F79" s="4" t="inlineStr"/>
       <c r="G79" s="4" t="n">
         <v>225</v>
       </c>
@@ -29267,16 +28659,8 @@
           <t>保勝光學</t>
         </is>
       </c>
-      <c r="E80" s="4" t="inlineStr">
-        <is>
-          <t>77.10</t>
-        </is>
-      </c>
-      <c r="F80" s="4" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
+      <c r="E80" s="4" t="inlineStr"/>
+      <c r="F80" s="4" t="inlineStr"/>
       <c r="G80" s="4" t="n">
         <v>216</v>
       </c>
@@ -29300,16 +28684,8 @@
           <t>凌陽創新</t>
         </is>
       </c>
-      <c r="E81" s="4" t="inlineStr">
-        <is>
-          <t>176.00</t>
-        </is>
-      </c>
-      <c r="F81" s="4" t="inlineStr">
-        <is>
-          <t>+10.0</t>
-        </is>
-      </c>
+      <c r="E81" s="4" t="inlineStr"/>
+      <c r="F81" s="4" t="inlineStr"/>
       <c r="G81" s="4" t="n">
         <v>215</v>
       </c>
@@ -29333,16 +28709,8 @@
           <t>旺玖</t>
         </is>
       </c>
-      <c r="E82" s="4" t="inlineStr">
-        <is>
-          <t>26.10</t>
-        </is>
-      </c>
-      <c r="F82" s="4" t="inlineStr">
-        <is>
-          <t>+1.05</t>
-        </is>
-      </c>
+      <c r="E82" s="4" t="inlineStr"/>
+      <c r="F82" s="4" t="inlineStr"/>
       <c r="G82" s="4" t="n">
         <v>215</v>
       </c>
@@ -29366,16 +28734,8 @@
           <t>旭軟</t>
         </is>
       </c>
-      <c r="E83" s="4" t="inlineStr">
-        <is>
-          <t>29.40</t>
-        </is>
-      </c>
-      <c r="F83" s="4" t="inlineStr">
-        <is>
-          <t>+0.9</t>
-        </is>
-      </c>
+      <c r="E83" s="4" t="inlineStr"/>
+      <c r="F83" s="4" t="inlineStr"/>
       <c r="G83" s="4" t="n">
         <v>213</v>
       </c>
@@ -29399,16 +28759,8 @@
           <t>杰力</t>
         </is>
       </c>
-      <c r="E84" s="4" t="inlineStr">
-        <is>
-          <t>129.00</t>
-        </is>
-      </c>
-      <c r="F84" s="4" t="inlineStr">
-        <is>
-          <t>+11.5</t>
-        </is>
-      </c>
+      <c r="E84" s="4" t="inlineStr"/>
+      <c r="F84" s="4" t="inlineStr"/>
       <c r="G84" s="4" t="n">
         <v>212</v>
       </c>
@@ -29432,16 +28784,8 @@
           <t>亞元</t>
         </is>
       </c>
-      <c r="E85" s="4" t="inlineStr">
-        <is>
-          <t>12.75</t>
-        </is>
-      </c>
-      <c r="F85" s="4" t="inlineStr">
-        <is>
-          <t>+1.15</t>
-        </is>
-      </c>
+      <c r="E85" s="4" t="inlineStr"/>
+      <c r="F85" s="4" t="inlineStr"/>
       <c r="G85" s="4" t="n">
         <v>211</v>
       </c>
@@ -29465,16 +28809,8 @@
           <t>宇環</t>
         </is>
       </c>
-      <c r="E86" s="4" t="inlineStr">
-        <is>
-          <t>15.70</t>
-        </is>
-      </c>
-      <c r="F86" s="4" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
+      <c r="E86" s="4" t="inlineStr"/>
+      <c r="F86" s="4" t="inlineStr"/>
       <c r="G86" s="4" t="n">
         <v>206</v>
       </c>
@@ -29498,16 +28834,8 @@
           <t>驊訊</t>
         </is>
       </c>
-      <c r="E87" s="4" t="inlineStr">
-        <is>
-          <t>47.65</t>
-        </is>
-      </c>
-      <c r="F87" s="4" t="inlineStr">
-        <is>
-          <t>+1.65</t>
-        </is>
-      </c>
+      <c r="E87" s="4" t="inlineStr"/>
+      <c r="F87" s="4" t="inlineStr"/>
       <c r="G87" s="4" t="n">
         <v>203</v>
       </c>
@@ -29531,16 +28859,8 @@
           <t>優群</t>
         </is>
       </c>
-      <c r="E88" s="4" t="inlineStr">
-        <is>
-          <t>176.50</t>
-        </is>
-      </c>
-      <c r="F88" s="4" t="inlineStr">
-        <is>
-          <t>+6.5</t>
-        </is>
-      </c>
+      <c r="E88" s="4" t="inlineStr"/>
+      <c r="F88" s="4" t="inlineStr"/>
       <c r="G88" s="4" t="n">
         <v>202</v>
       </c>
@@ -29564,16 +28884,8 @@
           <t>漢科</t>
         </is>
       </c>
-      <c r="E89" s="4" t="inlineStr">
-        <is>
-          <t>142.00</t>
-        </is>
-      </c>
-      <c r="F89" s="4" t="inlineStr">
-        <is>
-          <t>+1.5</t>
-        </is>
-      </c>
+      <c r="E89" s="4" t="inlineStr"/>
+      <c r="F89" s="4" t="inlineStr"/>
       <c r="G89" s="4" t="n">
         <v>201</v>
       </c>
@@ -29597,16 +28909,8 @@
           <t>新漢</t>
         </is>
       </c>
-      <c r="E90" s="4" t="inlineStr">
-        <is>
-          <t>65.50</t>
-        </is>
-      </c>
-      <c r="F90" s="4" t="inlineStr">
-        <is>
-          <t>+1.9</t>
-        </is>
-      </c>
+      <c r="E90" s="4" t="inlineStr"/>
+      <c r="F90" s="4" t="inlineStr"/>
       <c r="G90" s="4" t="n">
         <v>201</v>
       </c>
@@ -29630,16 +28934,8 @@
           <t>萬潤</t>
         </is>
       </c>
-      <c r="E91" s="4" t="inlineStr">
-        <is>
-          <t>1260.00</t>
-        </is>
-      </c>
-      <c r="F91" s="4" t="inlineStr">
-        <is>
-          <t>+25.0</t>
-        </is>
-      </c>
+      <c r="E91" s="4" t="inlineStr"/>
+      <c r="F91" s="4" t="inlineStr"/>
       <c r="G91" s="4" t="n">
         <v>200</v>
       </c>
@@ -29663,16 +28959,8 @@
           <t>單井</t>
         </is>
       </c>
-      <c r="E92" s="4" t="inlineStr">
-        <is>
-          <t>33.40</t>
-        </is>
-      </c>
-      <c r="F92" s="4" t="inlineStr">
-        <is>
-          <t>+0.95</t>
-        </is>
-      </c>
+      <c r="E92" s="4" t="inlineStr"/>
+      <c r="F92" s="4" t="inlineStr"/>
       <c r="G92" s="4" t="n">
         <v>198</v>
       </c>
@@ -29696,16 +28984,8 @@
           <t>伍豐</t>
         </is>
       </c>
-      <c r="E93" s="4" t="inlineStr">
-        <is>
-          <t>25.90</t>
-        </is>
-      </c>
-      <c r="F93" s="4" t="inlineStr">
-        <is>
-          <t>+0.15</t>
-        </is>
-      </c>
+      <c r="E93" s="4" t="inlineStr"/>
+      <c r="F93" s="4" t="inlineStr"/>
       <c r="G93" s="4" t="n">
         <v>194</v>
       </c>
@@ -29729,16 +29009,8 @@
           <t>金益鼎</t>
         </is>
       </c>
-      <c r="E94" s="4" t="inlineStr">
-        <is>
-          <t>116.00</t>
-        </is>
-      </c>
-      <c r="F94" s="4" t="inlineStr">
-        <is>
-          <t>+2.0</t>
-        </is>
-      </c>
+      <c r="E94" s="4" t="inlineStr"/>
+      <c r="F94" s="4" t="inlineStr"/>
       <c r="G94" s="4" t="n">
         <v>188</v>
       </c>
@@ -29762,16 +29034,8 @@
           <t>晶采</t>
         </is>
       </c>
-      <c r="E95" s="4" t="inlineStr">
-        <is>
-          <t>27.90</t>
-        </is>
-      </c>
-      <c r="F95" s="4" t="inlineStr">
-        <is>
-          <t>+0.2</t>
-        </is>
-      </c>
+      <c r="E95" s="4" t="inlineStr"/>
+      <c r="F95" s="4" t="inlineStr"/>
       <c r="G95" s="4" t="n">
         <v>187</v>
       </c>
@@ -29795,16 +29059,8 @@
           <t>環宇-KY</t>
         </is>
       </c>
-      <c r="E96" s="4" t="inlineStr">
-        <is>
-          <t>564.00</t>
-        </is>
-      </c>
-      <c r="F96" s="4" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
+      <c r="E96" s="4" t="inlineStr"/>
+      <c r="F96" s="4" t="inlineStr"/>
       <c r="G96" s="4" t="n">
         <v>185</v>
       </c>
@@ -29828,16 +29084,8 @@
           <t>倉和</t>
         </is>
       </c>
-      <c r="E97" s="4" t="inlineStr">
-        <is>
-          <t>125.50</t>
-        </is>
-      </c>
-      <c r="F97" s="4" t="inlineStr">
-        <is>
-          <t>+11.0</t>
-        </is>
-      </c>
+      <c r="E97" s="4" t="inlineStr"/>
+      <c r="F97" s="4" t="inlineStr"/>
       <c r="G97" s="4" t="n">
         <v>184</v>
       </c>
@@ -29861,16 +29109,8 @@
           <t>長園科</t>
         </is>
       </c>
-      <c r="E98" s="4" t="inlineStr">
-        <is>
-          <t>41.10</t>
-        </is>
-      </c>
-      <c r="F98" s="4" t="inlineStr">
-        <is>
-          <t>+0.3</t>
-        </is>
-      </c>
+      <c r="E98" s="4" t="inlineStr"/>
+      <c r="F98" s="4" t="inlineStr"/>
       <c r="G98" s="4" t="n">
         <v>184</v>
       </c>
@@ -29894,16 +29134,8 @@
           <t>李洲</t>
         </is>
       </c>
-      <c r="E99" s="4" t="inlineStr">
-        <is>
-          <t>22.05</t>
-        </is>
-      </c>
-      <c r="F99" s="4" t="inlineStr">
-        <is>
-          <t>+0.75</t>
-        </is>
-      </c>
+      <c r="E99" s="4" t="inlineStr"/>
+      <c r="F99" s="4" t="inlineStr"/>
       <c r="G99" s="4" t="n">
         <v>182</v>
       </c>
@@ -29927,16 +29159,8 @@
           <t>茂綸</t>
         </is>
       </c>
-      <c r="E100" s="4" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
-      </c>
-      <c r="F100" s="4" t="inlineStr">
-        <is>
-          <t>+3.0</t>
-        </is>
-      </c>
+      <c r="E100" s="4" t="inlineStr"/>
+      <c r="F100" s="4" t="inlineStr"/>
       <c r="G100" s="4" t="n">
         <v>178</v>
       </c>
@@ -29960,16 +29184,8 @@
           <t>森鉅</t>
         </is>
       </c>
-      <c r="E101" s="4" t="inlineStr">
-        <is>
-          <t>42.20</t>
-        </is>
-      </c>
-      <c r="F101" s="4" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
+      <c r="E101" s="4" t="inlineStr"/>
+      <c r="F101" s="4" t="inlineStr"/>
       <c r="G101" s="4" t="n">
         <v>176</v>
       </c>
@@ -29993,16 +29209,8 @@
           <t>高僑</t>
         </is>
       </c>
-      <c r="E102" s="4" t="inlineStr">
-        <is>
-          <t>46.80</t>
-        </is>
-      </c>
-      <c r="F102" s="4" t="inlineStr">
-        <is>
-          <t>+1.7</t>
-        </is>
-      </c>
+      <c r="E102" s="4" t="inlineStr"/>
+      <c r="F102" s="4" t="inlineStr"/>
       <c r="G102" s="4" t="n">
         <v>172</v>
       </c>
@@ -30026,16 +29234,8 @@
           <t>德勝</t>
         </is>
       </c>
-      <c r="E103" s="4" t="inlineStr">
-        <is>
-          <t>66.80</t>
-        </is>
-      </c>
-      <c r="F103" s="4" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
+      <c r="E103" s="4" t="inlineStr"/>
+      <c r="F103" s="4" t="inlineStr"/>
       <c r="G103" s="4" t="n">
         <v>172</v>
       </c>
@@ -30136,16 +29336,8 @@
           <t>合晶</t>
         </is>
       </c>
-      <c r="E109" s="4" t="inlineStr">
-        <is>
-          <t>116.50</t>
-        </is>
-      </c>
-      <c r="F109" s="4" t="inlineStr">
-        <is>
-          <t>-3.5</t>
-        </is>
-      </c>
+      <c r="E109" s="4" t="inlineStr"/>
+      <c r="F109" s="4" t="inlineStr"/>
       <c r="G109" s="4" t="n">
         <v>-13670</v>
       </c>
@@ -30169,16 +29361,8 @@
           <t>綠河-KY</t>
         </is>
       </c>
-      <c r="E110" s="4" t="inlineStr">
-        <is>
-          <t>5.06</t>
-        </is>
-      </c>
-      <c r="F110" s="4" t="inlineStr">
-        <is>
-          <t>+0.46</t>
-        </is>
-      </c>
+      <c r="E110" s="4" t="inlineStr"/>
+      <c r="F110" s="4" t="inlineStr"/>
       <c r="G110" s="4" t="n">
         <v>-9996</v>
       </c>
@@ -30202,16 +29386,8 @@
           <t>華容</t>
         </is>
       </c>
-      <c r="E111" s="4" t="inlineStr">
-        <is>
-          <t>58.00</t>
-        </is>
-      </c>
-      <c r="F111" s="4" t="inlineStr">
-        <is>
-          <t>+1.5</t>
-        </is>
-      </c>
+      <c r="E111" s="4" t="inlineStr"/>
+      <c r="F111" s="4" t="inlineStr"/>
       <c r="G111" s="4" t="n">
         <v>-6472</v>
       </c>
@@ -30235,16 +29411,8 @@
           <t>中美晶</t>
         </is>
       </c>
-      <c r="E112" s="4" t="inlineStr">
-        <is>
-          <t>180.50</t>
-        </is>
-      </c>
-      <c r="F112" s="4" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
+      <c r="E112" s="4" t="inlineStr"/>
+      <c r="F112" s="4" t="inlineStr"/>
       <c r="G112" s="4" t="n">
         <v>-4813</v>
       </c>
@@ -30268,16 +29436,8 @@
           <t>世界</t>
         </is>
       </c>
-      <c r="E113" s="4" t="inlineStr">
-        <is>
-          <t>191.50</t>
-        </is>
-      </c>
-      <c r="F113" s="4" t="inlineStr">
-        <is>
-          <t>+17.0</t>
-        </is>
-      </c>
+      <c r="E113" s="4" t="inlineStr"/>
+      <c r="F113" s="4" t="inlineStr"/>
       <c r="G113" s="4" t="n">
         <v>-2519</v>
       </c>
@@ -30301,16 +29461,8 @@
           <t>擎亞</t>
         </is>
       </c>
-      <c r="E114" s="4" t="inlineStr">
-        <is>
-          <t>157.50</t>
-        </is>
-      </c>
-      <c r="F114" s="4" t="inlineStr">
-        <is>
-          <t>+2.0</t>
-        </is>
-      </c>
+      <c r="E114" s="4" t="inlineStr"/>
+      <c r="F114" s="4" t="inlineStr"/>
       <c r="G114" s="4" t="n">
         <v>-2397</v>
       </c>
@@ -30334,16 +29486,8 @@
           <t>千如</t>
         </is>
       </c>
-      <c r="E115" s="4" t="inlineStr">
-        <is>
-          <t>66.40</t>
-        </is>
-      </c>
-      <c r="F115" s="4" t="inlineStr">
-        <is>
-          <t>-4.6</t>
-        </is>
-      </c>
+      <c r="E115" s="4" t="inlineStr"/>
+      <c r="F115" s="4" t="inlineStr"/>
       <c r="G115" s="4" t="n">
         <v>-2277</v>
       </c>
@@ -30367,16 +29511,8 @@
           <t>良維</t>
         </is>
       </c>
-      <c r="E116" s="4" t="inlineStr">
-        <is>
-          <t>318.00</t>
-        </is>
-      </c>
-      <c r="F116" s="4" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
+      <c r="E116" s="4" t="inlineStr"/>
+      <c r="F116" s="4" t="inlineStr"/>
       <c r="G116" s="4" t="n">
         <v>-1857</v>
       </c>
@@ -30400,16 +29536,8 @@
           <t>雷科</t>
         </is>
       </c>
-      <c r="E117" s="4" t="inlineStr">
-        <is>
-          <t>165.50</t>
-        </is>
-      </c>
-      <c r="F117" s="4" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
+      <c r="E117" s="4" t="inlineStr"/>
+      <c r="F117" s="4" t="inlineStr"/>
       <c r="G117" s="4" t="n">
         <v>-1822</v>
       </c>
@@ -30433,16 +29561,8 @@
           <t>元太</t>
         </is>
       </c>
-      <c r="E118" s="4" t="inlineStr">
-        <is>
-          <t>203.00</t>
-        </is>
-      </c>
-      <c r="F118" s="4" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
+      <c r="E118" s="4" t="inlineStr"/>
+      <c r="F118" s="4" t="inlineStr"/>
       <c r="G118" s="4" t="n">
         <v>-1631</v>
       </c>
@@ -30466,16 +29586,8 @@
           <t>蜜望實</t>
         </is>
       </c>
-      <c r="E119" s="4" t="inlineStr">
-        <is>
-          <t>213.00</t>
-        </is>
-      </c>
-      <c r="F119" s="4" t="inlineStr">
-        <is>
-          <t>-13.5</t>
-        </is>
-      </c>
+      <c r="E119" s="4" t="inlineStr"/>
+      <c r="F119" s="4" t="inlineStr"/>
       <c r="G119" s="4" t="n">
         <v>-1597</v>
       </c>
@@ -30499,16 +29611,8 @@
           <t>萬泰科</t>
         </is>
       </c>
-      <c r="E120" s="4" t="inlineStr">
-        <is>
-          <t>83.70</t>
-        </is>
-      </c>
-      <c r="F120" s="4" t="inlineStr">
-        <is>
-          <t>+0.8</t>
-        </is>
-      </c>
+      <c r="E120" s="4" t="inlineStr"/>
+      <c r="F120" s="4" t="inlineStr"/>
       <c r="G120" s="4" t="n">
         <v>-1438</v>
       </c>
@@ -30532,16 +29636,8 @@
           <t>越峰</t>
         </is>
       </c>
-      <c r="E121" s="4" t="inlineStr">
-        <is>
-          <t>54.40</t>
-        </is>
-      </c>
-      <c r="F121" s="4" t="inlineStr">
-        <is>
-          <t>+1.0</t>
-        </is>
-      </c>
+      <c r="E121" s="4" t="inlineStr"/>
+      <c r="F121" s="4" t="inlineStr"/>
       <c r="G121" s="4" t="n">
         <v>-1424</v>
       </c>
@@ -30565,16 +29661,8 @@
           <t>光環</t>
         </is>
       </c>
-      <c r="E122" s="4" t="inlineStr">
-        <is>
-          <t>139.00</t>
-        </is>
-      </c>
-      <c r="F122" s="4" t="inlineStr">
-        <is>
-          <t>-6.0</t>
-        </is>
-      </c>
+      <c r="E122" s="4" t="inlineStr"/>
+      <c r="F122" s="4" t="inlineStr"/>
       <c r="G122" s="4" t="n">
         <v>-1409</v>
       </c>
@@ -30598,16 +29686,8 @@
           <t>崧騰</t>
         </is>
       </c>
-      <c r="E123" s="4" t="inlineStr">
-        <is>
-          <t>52.90</t>
-        </is>
-      </c>
-      <c r="F123" s="4" t="inlineStr">
-        <is>
-          <t>-2.2</t>
-        </is>
-      </c>
+      <c r="E123" s="4" t="inlineStr"/>
+      <c r="F123" s="4" t="inlineStr"/>
       <c r="G123" s="4" t="n">
         <v>-1263</v>
       </c>
@@ -30631,16 +29711,8 @@
           <t>德宏</t>
         </is>
       </c>
-      <c r="E124" s="4" t="inlineStr">
-        <is>
-          <t>277.00</t>
-        </is>
-      </c>
-      <c r="F124" s="4" t="inlineStr">
-        <is>
-          <t>+25.0</t>
-        </is>
-      </c>
+      <c r="E124" s="4" t="inlineStr"/>
+      <c r="F124" s="4" t="inlineStr"/>
       <c r="G124" s="4" t="n">
         <v>-1218</v>
       </c>
@@ -30664,16 +29736,8 @@
           <t>今展科</t>
         </is>
       </c>
-      <c r="E125" s="4" t="inlineStr">
-        <is>
-          <t>81.30</t>
-        </is>
-      </c>
-      <c r="F125" s="4" t="inlineStr">
-        <is>
-          <t>-5.6</t>
-        </is>
-      </c>
+      <c r="E125" s="4" t="inlineStr"/>
+      <c r="F125" s="4" t="inlineStr"/>
       <c r="G125" s="4" t="n">
         <v>-1154</v>
       </c>
@@ -30697,16 +29761,8 @@
           <t>立敦</t>
         </is>
       </c>
-      <c r="E126" s="4" t="inlineStr">
-        <is>
-          <t>109.00</t>
-        </is>
-      </c>
-      <c r="F126" s="4" t="inlineStr">
-        <is>
-          <t>-5.0</t>
-        </is>
-      </c>
+      <c r="E126" s="4" t="inlineStr"/>
+      <c r="F126" s="4" t="inlineStr"/>
       <c r="G126" s="4" t="n">
         <v>-1100</v>
       </c>
@@ -30730,16 +29786,8 @@
           <t>前鼎</t>
         </is>
       </c>
-      <c r="E127" s="4" t="inlineStr">
-        <is>
-          <t>201.00</t>
-        </is>
-      </c>
-      <c r="F127" s="4" t="inlineStr">
-        <is>
-          <t>-11.0</t>
-        </is>
-      </c>
+      <c r="E127" s="4" t="inlineStr"/>
+      <c r="F127" s="4" t="inlineStr"/>
       <c r="G127" s="4" t="n">
         <v>-1014</v>
       </c>
@@ -30763,16 +29811,8 @@
           <t>岳豐</t>
         </is>
       </c>
-      <c r="E128" s="4" t="inlineStr">
-        <is>
-          <t>39.85</t>
-        </is>
-      </c>
-      <c r="F128" s="4" t="inlineStr">
-        <is>
-          <t>+1.5</t>
-        </is>
-      </c>
+      <c r="E128" s="4" t="inlineStr"/>
+      <c r="F128" s="4" t="inlineStr"/>
       <c r="G128" s="4" t="n">
         <v>-950</v>
       </c>
@@ -30796,16 +29836,8 @@
           <t>新潤</t>
         </is>
       </c>
-      <c r="E129" s="4" t="inlineStr">
-        <is>
-          <t>40.80</t>
-        </is>
-      </c>
-      <c r="F129" s="4" t="inlineStr">
-        <is>
-          <t>-1.55</t>
-        </is>
-      </c>
+      <c r="E129" s="4" t="inlineStr"/>
+      <c r="F129" s="4" t="inlineStr"/>
       <c r="G129" s="4" t="n">
         <v>-841</v>
       </c>
@@ -30829,16 +29861,8 @@
           <t>永信建</t>
         </is>
       </c>
-      <c r="E130" s="4" t="inlineStr">
-        <is>
-          <t>56.30</t>
-        </is>
-      </c>
-      <c r="F130" s="4" t="inlineStr">
-        <is>
-          <t>-5.4</t>
-        </is>
-      </c>
+      <c r="E130" s="4" t="inlineStr"/>
+      <c r="F130" s="4" t="inlineStr"/>
       <c r="G130" s="4" t="n">
         <v>-834</v>
       </c>
@@ -30862,16 +29886,8 @@
           <t>國統</t>
         </is>
       </c>
-      <c r="E131" s="4" t="inlineStr">
-        <is>
-          <t>60.50</t>
-        </is>
-      </c>
-      <c r="F131" s="4" t="inlineStr">
-        <is>
-          <t>+2.4</t>
-        </is>
-      </c>
+      <c r="E131" s="4" t="inlineStr"/>
+      <c r="F131" s="4" t="inlineStr"/>
       <c r="G131" s="4" t="n">
         <v>-818</v>
       </c>
@@ -30895,16 +29911,8 @@
           <t>群聯</t>
         </is>
       </c>
-      <c r="E132" s="4" t="inlineStr">
-        <is>
-          <t>2580.00</t>
-        </is>
-      </c>
-      <c r="F132" s="4" t="inlineStr">
-        <is>
-          <t>+50.0</t>
-        </is>
-      </c>
+      <c r="E132" s="4" t="inlineStr"/>
+      <c r="F132" s="4" t="inlineStr"/>
       <c r="G132" s="4" t="n">
         <v>-796</v>
       </c>
@@ -30928,16 +29936,8 @@
           <t>富強鑫</t>
         </is>
       </c>
-      <c r="E133" s="4" t="inlineStr">
-        <is>
-          <t>25.35</t>
-        </is>
-      </c>
-      <c r="F133" s="4" t="inlineStr">
-        <is>
-          <t>+1.15</t>
-        </is>
-      </c>
+      <c r="E133" s="4" t="inlineStr"/>
+      <c r="F133" s="4" t="inlineStr"/>
       <c r="G133" s="4" t="n">
         <v>-785</v>
       </c>
@@ -30961,16 +29961,8 @@
           <t>堡達</t>
         </is>
       </c>
-      <c r="E134" s="4" t="inlineStr">
-        <is>
-          <t>86.00</t>
-        </is>
-      </c>
-      <c r="F134" s="4" t="inlineStr">
-        <is>
-          <t>-3.6</t>
-        </is>
-      </c>
+      <c r="E134" s="4" t="inlineStr"/>
+      <c r="F134" s="4" t="inlineStr"/>
       <c r="G134" s="4" t="n">
         <v>-768</v>
       </c>
@@ -30994,16 +29986,8 @@
           <t>茂迪</t>
         </is>
       </c>
-      <c r="E135" s="4" t="inlineStr">
-        <is>
-          <t>28.60</t>
-        </is>
-      </c>
-      <c r="F135" s="4" t="inlineStr">
-        <is>
-          <t>+0.15</t>
-        </is>
-      </c>
+      <c r="E135" s="4" t="inlineStr"/>
+      <c r="F135" s="4" t="inlineStr"/>
       <c r="G135" s="4" t="n">
         <v>-739</v>
       </c>
@@ -31027,16 +30011,8 @@
           <t>臺慶科</t>
         </is>
       </c>
-      <c r="E136" s="4" t="inlineStr">
-        <is>
-          <t>346.50</t>
-        </is>
-      </c>
-      <c r="F136" s="4" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
+      <c r="E136" s="4" t="inlineStr"/>
+      <c r="F136" s="4" t="inlineStr"/>
       <c r="G136" s="4" t="n">
         <v>-711</v>
       </c>
@@ -31060,16 +30036,8 @@
           <t>廣運</t>
         </is>
       </c>
-      <c r="E137" s="4" t="inlineStr">
-        <is>
-          <t>62.60</t>
-        </is>
-      </c>
-      <c r="F137" s="4" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
+      <c r="E137" s="4" t="inlineStr"/>
+      <c r="F137" s="4" t="inlineStr"/>
       <c r="G137" s="4" t="n">
         <v>-703</v>
       </c>
@@ -31093,16 +30061,8 @@
           <t>永捷</t>
         </is>
       </c>
-      <c r="E138" s="4" t="inlineStr">
-        <is>
-          <t>12.95</t>
-        </is>
-      </c>
-      <c r="F138" s="4" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
+      <c r="E138" s="4" t="inlineStr"/>
+      <c r="F138" s="4" t="inlineStr"/>
       <c r="G138" s="4" t="n">
         <v>-636</v>
       </c>
@@ -31126,16 +30086,8 @@
           <t>廣穎</t>
         </is>
       </c>
-      <c r="E139" s="4" t="inlineStr">
-        <is>
-          <t>191.50</t>
-        </is>
-      </c>
-      <c r="F139" s="4" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
+      <c r="E139" s="4" t="inlineStr"/>
+      <c r="F139" s="4" t="inlineStr"/>
       <c r="G139" s="4" t="n">
         <v>-621</v>
       </c>
@@ -31159,16 +30111,8 @@
           <t>IET-KY</t>
         </is>
       </c>
-      <c r="E140" s="4" t="inlineStr">
-        <is>
-          <t>571.00</t>
-        </is>
-      </c>
-      <c r="F140" s="4" t="inlineStr">
-        <is>
-          <t>-7.0</t>
-        </is>
-      </c>
+      <c r="E140" s="4" t="inlineStr"/>
+      <c r="F140" s="4" t="inlineStr"/>
       <c r="G140" s="4" t="n">
         <v>-564</v>
       </c>
@@ -31192,16 +30136,8 @@
           <t>宏遠證</t>
         </is>
       </c>
-      <c r="E141" s="4" t="inlineStr">
-        <is>
-          <t>19.00</t>
-        </is>
-      </c>
-      <c r="F141" s="4" t="inlineStr">
-        <is>
-          <t>+0.65</t>
-        </is>
-      </c>
+      <c r="E141" s="4" t="inlineStr"/>
+      <c r="F141" s="4" t="inlineStr"/>
       <c r="G141" s="4" t="n">
         <v>-553</v>
       </c>
@@ -31225,16 +30161,8 @@
           <t>鈊象</t>
         </is>
       </c>
-      <c r="E142" s="4" t="inlineStr">
-        <is>
-          <t>778.00</t>
-        </is>
-      </c>
-      <c r="F142" s="4" t="inlineStr">
-        <is>
-          <t>-15.0</t>
-        </is>
-      </c>
+      <c r="E142" s="4" t="inlineStr"/>
+      <c r="F142" s="4" t="inlineStr"/>
       <c r="G142" s="4" t="n">
         <v>-551</v>
       </c>
@@ -31258,16 +30186,8 @@
           <t>橘子</t>
         </is>
       </c>
-      <c r="E143" s="4" t="inlineStr">
-        <is>
-          <t>51.40</t>
-        </is>
-      </c>
-      <c r="F143" s="4" t="inlineStr">
-        <is>
-          <t>+1.1</t>
-        </is>
-      </c>
+      <c r="E143" s="4" t="inlineStr"/>
+      <c r="F143" s="4" t="inlineStr"/>
       <c r="G143" s="4" t="n">
         <v>-541</v>
       </c>
@@ -31291,16 +30211,8 @@
           <t>翔名</t>
         </is>
       </c>
-      <c r="E144" s="4" t="inlineStr">
-        <is>
-          <t>272.50</t>
-        </is>
-      </c>
-      <c r="F144" s="4" t="inlineStr">
-        <is>
-          <t>-8.5</t>
-        </is>
-      </c>
+      <c r="E144" s="4" t="inlineStr"/>
+      <c r="F144" s="4" t="inlineStr"/>
       <c r="G144" s="4" t="n">
         <v>-539</v>
       </c>
@@ -31324,16 +30236,8 @@
           <t>福邦證</t>
         </is>
       </c>
-      <c r="E145" s="4" t="inlineStr">
-        <is>
-          <t>17.15</t>
-        </is>
-      </c>
-      <c r="F145" s="4" t="inlineStr">
-        <is>
-          <t>+0.1</t>
-        </is>
-      </c>
+      <c r="E145" s="4" t="inlineStr"/>
+      <c r="F145" s="4" t="inlineStr"/>
       <c r="G145" s="4" t="n">
         <v>-520</v>
       </c>
@@ -31357,16 +30261,8 @@
           <t>昇達科</t>
         </is>
       </c>
-      <c r="E146" s="4" t="inlineStr">
-        <is>
-          <t>1470.00</t>
-        </is>
-      </c>
-      <c r="F146" s="4" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
+      <c r="E146" s="4" t="inlineStr"/>
+      <c r="F146" s="4" t="inlineStr"/>
       <c r="G146" s="4" t="n">
         <v>-510</v>
       </c>
@@ -31390,16 +30286,8 @@
           <t>閎康</t>
         </is>
       </c>
-      <c r="E147" s="4" t="inlineStr">
-        <is>
-          <t>323.00</t>
-        </is>
-      </c>
-      <c r="F147" s="4" t="inlineStr">
-        <is>
-          <t>+19.0</t>
-        </is>
-      </c>
+      <c r="E147" s="4" t="inlineStr"/>
+      <c r="F147" s="4" t="inlineStr"/>
       <c r="G147" s="4" t="n">
         <v>-482</v>
       </c>
@@ -31423,16 +30311,8 @@
           <t>亞泰金屬</t>
         </is>
       </c>
-      <c r="E148" s="4" t="inlineStr">
-        <is>
-          <t>485.50</t>
-        </is>
-      </c>
-      <c r="F148" s="4" t="inlineStr">
-        <is>
-          <t>+36.5</t>
-        </is>
-      </c>
+      <c r="E148" s="4" t="inlineStr"/>
+      <c r="F148" s="4" t="inlineStr"/>
       <c r="G148" s="4" t="n">
         <v>-480</v>
       </c>
@@ -31456,16 +30336,8 @@
           <t>鈺鎧</t>
         </is>
       </c>
-      <c r="E149" s="4" t="inlineStr">
-        <is>
-          <t>70.20</t>
-        </is>
-      </c>
-      <c r="F149" s="4" t="inlineStr">
-        <is>
-          <t>-5.3</t>
-        </is>
-      </c>
+      <c r="E149" s="4" t="inlineStr"/>
+      <c r="F149" s="4" t="inlineStr"/>
       <c r="G149" s="4" t="n">
         <v>-471</v>
       </c>
@@ -31489,16 +30361,8 @@
           <t>精確</t>
         </is>
       </c>
-      <c r="E150" s="4" t="inlineStr">
-        <is>
-          <t>84.60</t>
-        </is>
-      </c>
-      <c r="F150" s="4" t="inlineStr">
-        <is>
-          <t>-0.9</t>
-        </is>
-      </c>
+      <c r="E150" s="4" t="inlineStr"/>
+      <c r="F150" s="4" t="inlineStr"/>
       <c r="G150" s="4" t="n">
         <v>-447</v>
       </c>
@@ -31522,16 +30386,8 @@
           <t>東洋</t>
         </is>
       </c>
-      <c r="E151" s="4" t="inlineStr">
-        <is>
-          <t>73.70</t>
-        </is>
-      </c>
-      <c r="F151" s="4" t="inlineStr">
-        <is>
-          <t>+0.2</t>
-        </is>
-      </c>
+      <c r="E151" s="4" t="inlineStr"/>
+      <c r="F151" s="4" t="inlineStr"/>
       <c r="G151" s="4" t="n">
         <v>-447</v>
       </c>
@@ -31555,16 +30411,8 @@
           <t>宣德</t>
         </is>
       </c>
-      <c r="E152" s="4" t="inlineStr">
-        <is>
-          <t>36.80</t>
-        </is>
-      </c>
-      <c r="F152" s="4" t="inlineStr">
-        <is>
-          <t>-0.3</t>
-        </is>
-      </c>
+      <c r="E152" s="4" t="inlineStr"/>
+      <c r="F152" s="4" t="inlineStr"/>
       <c r="G152" s="4" t="n">
         <v>-446</v>
       </c>
@@ -31588,16 +30436,8 @@
           <t>波若威</t>
         </is>
       </c>
-      <c r="E153" s="4" t="inlineStr">
-        <is>
-          <t>870.00</t>
-        </is>
-      </c>
-      <c r="F153" s="4" t="inlineStr">
-        <is>
-          <t>-23.0</t>
-        </is>
-      </c>
+      <c r="E153" s="4" t="inlineStr"/>
+      <c r="F153" s="4" t="inlineStr"/>
       <c r="G153" s="4" t="n">
         <v>-445</v>
       </c>
@@ -31621,16 +30461,8 @@
           <t>網家</t>
         </is>
       </c>
-      <c r="E154" s="4" t="inlineStr">
-        <is>
-          <t>31.30</t>
-        </is>
-      </c>
-      <c r="F154" s="4" t="inlineStr">
-        <is>
-          <t>+0.15</t>
-        </is>
-      </c>
+      <c r="E154" s="4" t="inlineStr"/>
+      <c r="F154" s="4" t="inlineStr"/>
       <c r="G154" s="4" t="n">
         <v>-443</v>
       </c>
@@ -31654,16 +30486,8 @@
           <t>東浦</t>
         </is>
       </c>
-      <c r="E155" s="4" t="inlineStr">
-        <is>
-          <t>68.80</t>
-        </is>
-      </c>
-      <c r="F155" s="4" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
+      <c r="E155" s="4" t="inlineStr"/>
+      <c r="F155" s="4" t="inlineStr"/>
       <c r="G155" s="4" t="n">
         <v>-432</v>
       </c>
@@ -31687,16 +30511,8 @@
           <t>系統電</t>
         </is>
       </c>
-      <c r="E156" s="4" t="inlineStr">
-        <is>
-          <t>70.20</t>
-        </is>
-      </c>
-      <c r="F156" s="4" t="inlineStr">
-        <is>
-          <t>+1.2</t>
-        </is>
-      </c>
+      <c r="E156" s="4" t="inlineStr"/>
+      <c r="F156" s="4" t="inlineStr"/>
       <c r="G156" s="4" t="n">
         <v>-428</v>
       </c>
@@ -31720,16 +30536,8 @@
           <t>宏捷科</t>
         </is>
       </c>
-      <c r="E157" s="4" t="inlineStr">
-        <is>
-          <t>165.50</t>
-        </is>
-      </c>
-      <c r="F157" s="4" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
+      <c r="E157" s="4" t="inlineStr"/>
+      <c r="F157" s="4" t="inlineStr"/>
       <c r="G157" s="4" t="n">
         <v>-420</v>
       </c>
@@ -31753,16 +30561,8 @@
           <t>威剛</t>
         </is>
       </c>
-      <c r="E158" s="4" t="inlineStr">
-        <is>
-          <t>434.00</t>
-        </is>
-      </c>
-      <c r="F158" s="4" t="inlineStr">
-        <is>
-          <t>+11.0</t>
-        </is>
-      </c>
+      <c r="E158" s="4" t="inlineStr"/>
+      <c r="F158" s="4" t="inlineStr"/>
       <c r="G158" s="4" t="n">
         <v>-406</v>
       </c>

--- a/StockInfo/otc_analysis_result.xlsx
+++ b/StockInfo/otc_analysis_result.xlsx
@@ -26949,16 +26949,8 @@
           <t>合晶</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>+9.0</t>
-        </is>
-      </c>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr"/>
       <c r="G4" s="4" t="n">
         <v>5740</v>
       </c>
@@ -26982,16 +26974,8 @@
           <t>富喬</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>107.00</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
+      <c r="E5" s="4" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr"/>
       <c r="G5" s="4" t="n">
         <v>3232</v>
       </c>
@@ -27015,16 +26999,8 @@
           <t>華容</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>63.90</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>+5.8</t>
-        </is>
-      </c>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr"/>
       <c r="G6" s="4" t="n">
         <v>2889</v>
       </c>
@@ -27048,16 +27024,8 @@
           <t>原相</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>227.50</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
+      <c r="E7" s="4" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr"/>
       <c r="G7" s="4" t="n">
         <v>1579</v>
       </c>
@@ -27081,16 +27049,8 @@
           <t>漢科</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>149.50</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>+8.0</t>
-        </is>
-      </c>
+      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr"/>
       <c r="G8" s="4" t="n">
         <v>1141</v>
       </c>
@@ -27114,16 +27074,8 @@
           <t>優群</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>187.50</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>+10.5</t>
-        </is>
-      </c>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr"/>
       <c r="G9" s="4" t="n">
         <v>1133</v>
       </c>
@@ -27147,16 +27099,8 @@
           <t>千如</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>70.10</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>+6.3</t>
-        </is>
-      </c>
+      <c r="E10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr"/>
       <c r="G10" s="4" t="n">
         <v>1122</v>
       </c>
@@ -27180,16 +27124,8 @@
           <t>南俊國際</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>728.00</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>+66.0</t>
-        </is>
-      </c>
+      <c r="E11" s="4" t="inlineStr"/>
+      <c r="F11" s="4" t="inlineStr"/>
       <c r="G11" s="4" t="n">
         <v>1112</v>
       </c>
@@ -27213,16 +27149,8 @@
           <t>先進光</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>211.00</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>+19.0</t>
-        </is>
-      </c>
+      <c r="E12" s="4" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr"/>
       <c r="G12" s="4" t="n">
         <v>956</v>
       </c>
@@ -27246,16 +27174,8 @@
           <t>能率</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>45.75</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>+3.35</t>
-        </is>
-      </c>
+      <c r="E13" s="4" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr"/>
       <c r="G13" s="4" t="n">
         <v>903</v>
       </c>
@@ -27279,16 +27199,8 @@
           <t>國統</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>59.30</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>+1.5</t>
-        </is>
-      </c>
+      <c r="E14" s="4" t="inlineStr"/>
+      <c r="F14" s="4" t="inlineStr"/>
       <c r="G14" s="4" t="n">
         <v>843</v>
       </c>
@@ -27312,16 +27224,8 @@
           <t>倍微</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>42.50</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>+3.85</t>
-        </is>
-      </c>
+      <c r="E15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr"/>
       <c r="G15" s="4" t="n">
         <v>708</v>
       </c>
@@ -27345,16 +27249,8 @@
           <t>寶碩</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>33.25</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>+3.0</t>
-        </is>
-      </c>
+      <c r="E16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr"/>
       <c r="G16" s="4" t="n">
         <v>630</v>
       </c>
@@ -27378,16 +27274,8 @@
           <t>智通*</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>114.50</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>+10.0</t>
-        </is>
-      </c>
+      <c r="E17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr"/>
       <c r="G17" s="4" t="n">
         <v>580</v>
       </c>
@@ -27411,16 +27299,8 @@
           <t>精材</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>301.50</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>-10.5</t>
-        </is>
-      </c>
+      <c r="E18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr"/>
       <c r="G18" s="4" t="n">
         <v>570</v>
       </c>
@@ -27444,16 +27324,8 @@
           <t>新潤</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>41.95</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>+0.95</t>
-        </is>
-      </c>
+      <c r="E19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr"/>
       <c r="G19" s="4" t="n">
         <v>562</v>
       </c>
@@ -27477,16 +27349,8 @@
           <t>光洋科</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>142.50</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
+      <c r="E20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr"/>
       <c r="G20" s="4" t="n">
         <v>536</v>
       </c>
@@ -27510,16 +27374,8 @@
           <t>聯光通</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>42.45</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>+1.45</t>
-        </is>
-      </c>
+      <c r="E21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr"/>
       <c r="G21" s="4" t="n">
         <v>536</v>
       </c>
@@ -27543,16 +27399,8 @@
           <t>松上</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>24.90</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>-1.25</t>
-        </is>
-      </c>
+      <c r="E22" s="4" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr"/>
       <c r="G22" s="4" t="n">
         <v>512</v>
       </c>
@@ -27576,16 +27424,8 @@
           <t>雷笛克光學</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>21.85</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>+1.95</t>
-        </is>
-      </c>
+      <c r="E23" s="4" t="inlineStr"/>
+      <c r="F23" s="4" t="inlineStr"/>
       <c r="G23" s="4" t="n">
         <v>509</v>
       </c>
@@ -27609,16 +27449,8 @@
           <t>太普高</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>29.15</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>+2.65</t>
-        </is>
-      </c>
+      <c r="E24" s="4" t="inlineStr"/>
+      <c r="F24" s="4" t="inlineStr"/>
       <c r="G24" s="4" t="n">
         <v>488</v>
       </c>
@@ -27642,16 +27474,8 @@
           <t>上詮</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>629.00</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>-41.0</t>
-        </is>
-      </c>
+      <c r="E25" s="4" t="inlineStr"/>
+      <c r="F25" s="4" t="inlineStr"/>
       <c r="G25" s="4" t="n">
         <v>483</v>
       </c>
@@ -27675,16 +27499,8 @@
           <t>佳邦</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>102.00</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
+      <c r="E26" s="4" t="inlineStr"/>
+      <c r="F26" s="4" t="inlineStr"/>
       <c r="G26" s="4" t="n">
         <v>474</v>
       </c>
@@ -27708,16 +27524,8 @@
           <t>中美晶</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>174.50</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>+5.5</t>
-        </is>
-      </c>
+      <c r="E27" s="4" t="inlineStr"/>
+      <c r="F27" s="4" t="inlineStr"/>
       <c r="G27" s="4" t="n">
         <v>452</v>
       </c>
@@ -27741,16 +27549,8 @@
           <t>大立</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>24.20</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>+2.2</t>
-        </is>
-      </c>
+      <c r="E28" s="4" t="inlineStr"/>
+      <c r="F28" s="4" t="inlineStr"/>
       <c r="G28" s="4" t="n">
         <v>389</v>
       </c>
@@ -27774,16 +27574,8 @@
           <t>華星光</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>475.50</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>-24.5</t>
-        </is>
-      </c>
+      <c r="E29" s="4" t="inlineStr"/>
+      <c r="F29" s="4" t="inlineStr"/>
       <c r="G29" s="4" t="n">
         <v>377</v>
       </c>
@@ -27807,16 +27599,8 @@
           <t>統振</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>52.70</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>+0.9</t>
-        </is>
-      </c>
+      <c r="E30" s="4" t="inlineStr"/>
+      <c r="F30" s="4" t="inlineStr"/>
       <c r="G30" s="4" t="n">
         <v>337</v>
       </c>
@@ -27840,16 +27624,8 @@
           <t>青雲</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>538.00</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>+36.0</t>
-        </is>
-      </c>
+      <c r="E31" s="4" t="inlineStr"/>
+      <c r="F31" s="4" t="inlineStr"/>
       <c r="G31" s="4" t="n">
         <v>331</v>
       </c>
@@ -27873,16 +27649,8 @@
           <t>力麒</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>7.94</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
+      <c r="E32" s="4" t="inlineStr"/>
+      <c r="F32" s="4" t="inlineStr"/>
       <c r="G32" s="4" t="n">
         <v>331</v>
       </c>
@@ -27906,16 +27674,8 @@
           <t>威剛</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>409.50</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>+1.0</t>
-        </is>
-      </c>
+      <c r="E33" s="4" t="inlineStr"/>
+      <c r="F33" s="4" t="inlineStr"/>
       <c r="G33" s="4" t="n">
         <v>330</v>
       </c>
@@ -27939,16 +27699,8 @@
           <t>金山電</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>200.50</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>+8.5</t>
-        </is>
-      </c>
+      <c r="E34" s="4" t="inlineStr"/>
+      <c r="F34" s="4" t="inlineStr"/>
       <c r="G34" s="4" t="n">
         <v>329</v>
       </c>
@@ -27972,16 +27724,8 @@
           <t>泰藝</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>58.00</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>-2.7</t>
-        </is>
-      </c>
+      <c r="E35" s="4" t="inlineStr"/>
+      <c r="F35" s="4" t="inlineStr"/>
       <c r="G35" s="4" t="n">
         <v>328</v>
       </c>
@@ -28005,16 +27749,8 @@
           <t>光頡</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>154.00</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>+6.5</t>
-        </is>
-      </c>
+      <c r="E36" s="4" t="inlineStr"/>
+      <c r="F36" s="4" t="inlineStr"/>
       <c r="G36" s="4" t="n">
         <v>320</v>
       </c>
@@ -28038,16 +27774,8 @@
           <t>信音</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>39.60</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>-0.2</t>
-        </is>
-      </c>
+      <c r="E37" s="4" t="inlineStr"/>
+      <c r="F37" s="4" t="inlineStr"/>
       <c r="G37" s="4" t="n">
         <v>317</v>
       </c>
@@ -28071,16 +27799,8 @@
           <t>合一</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>50.20</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>+0.8</t>
-        </is>
-      </c>
+      <c r="E38" s="4" t="inlineStr"/>
+      <c r="F38" s="4" t="inlineStr"/>
       <c r="G38" s="4" t="n">
         <v>297</v>
       </c>
@@ -28104,16 +27824,8 @@
           <t>同亨</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>29.30</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>+0.85</t>
-        </is>
-      </c>
+      <c r="E39" s="4" t="inlineStr"/>
+      <c r="F39" s="4" t="inlineStr"/>
       <c r="G39" s="4" t="n">
         <v>297</v>
       </c>
@@ -28137,16 +27849,8 @@
           <t>三聯</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>95.50</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>+5.5</t>
-        </is>
-      </c>
+      <c r="E40" s="4" t="inlineStr"/>
+      <c r="F40" s="4" t="inlineStr"/>
       <c r="G40" s="4" t="n">
         <v>295</v>
       </c>
@@ -28170,16 +27874,8 @@
           <t>艾訊</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>142.50</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>+1.0</t>
-        </is>
-      </c>
+      <c r="E41" s="4" t="inlineStr"/>
+      <c r="F41" s="4" t="inlineStr"/>
       <c r="G41" s="4" t="n">
         <v>290</v>
       </c>
@@ -28203,16 +27899,8 @@
           <t>聯亞</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>2120.00</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>-35.0</t>
-        </is>
-      </c>
+      <c r="E42" s="4" t="inlineStr"/>
+      <c r="F42" s="4" t="inlineStr"/>
       <c r="G42" s="4" t="n">
         <v>254</v>
       </c>
@@ -28236,16 +27924,8 @@
           <t>霖宏</t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>107.50</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>+9.5</t>
-        </is>
-      </c>
+      <c r="E43" s="4" t="inlineStr"/>
+      <c r="F43" s="4" t="inlineStr"/>
       <c r="G43" s="4" t="n">
         <v>253</v>
       </c>
@@ -28269,16 +27949,8 @@
           <t>勤凱</t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>340.50</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>-6.0</t>
-        </is>
-      </c>
+      <c r="E44" s="4" t="inlineStr"/>
+      <c r="F44" s="4" t="inlineStr"/>
       <c r="G44" s="4" t="n">
         <v>241</v>
       </c>
@@ -28302,16 +27974,8 @@
           <t>力旺</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>3245.00</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>nannan</t>
-        </is>
-      </c>
+      <c r="E45" s="4" t="inlineStr"/>
+      <c r="F45" s="4" t="inlineStr"/>
       <c r="G45" s="4" t="n">
         <v>219</v>
       </c>
@@ -28335,16 +27999,8 @@
           <t>元大期</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>99.80</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>+0.1</t>
-        </is>
-      </c>
+      <c r="E46" s="4" t="inlineStr"/>
+      <c r="F46" s="4" t="inlineStr"/>
       <c r="G46" s="4" t="n">
         <v>215</v>
       </c>
@@ -28368,16 +28024,8 @@
           <t>環球晶</t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>1040.00</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t>+75.0</t>
-        </is>
-      </c>
+      <c r="E47" s="4" t="inlineStr"/>
+      <c r="F47" s="4" t="inlineStr"/>
       <c r="G47" s="4" t="n">
         <v>215</v>
       </c>
@@ -28401,16 +28049,8 @@
           <t>聯一光</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>92.80</t>
-        </is>
-      </c>
-      <c r="F48" s="4" t="inlineStr">
-        <is>
-          <t>+2.5</t>
-        </is>
-      </c>
+      <c r="E48" s="4" t="inlineStr"/>
+      <c r="F48" s="4" t="inlineStr"/>
       <c r="G48" s="4" t="n">
         <v>213</v>
       </c>
@@ -28434,16 +28074,8 @@
           <t>萬旭</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>35.20</t>
-        </is>
-      </c>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>+1.25</t>
-        </is>
-      </c>
+      <c r="E49" s="4" t="inlineStr"/>
+      <c r="F49" s="4" t="inlineStr"/>
       <c r="G49" s="4" t="n">
         <v>204</v>
       </c>
@@ -28467,16 +28099,8 @@
           <t>五福</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>108.50</t>
-        </is>
-      </c>
-      <c r="F50" s="4" t="inlineStr">
-        <is>
-          <t>+2.0</t>
-        </is>
-      </c>
+      <c r="E50" s="4" t="inlineStr"/>
+      <c r="F50" s="4" t="inlineStr"/>
       <c r="G50" s="4" t="n">
         <v>180</v>
       </c>
@@ -28500,16 +28124,8 @@
           <t>中天</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>15.50</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="inlineStr">
-        <is>
-          <t>+0.35</t>
-        </is>
-      </c>
+      <c r="E51" s="4" t="inlineStr"/>
+      <c r="F51" s="4" t="inlineStr"/>
       <c r="G51" s="4" t="n">
         <v>170</v>
       </c>
@@ -28533,16 +28149,8 @@
           <t>東洋</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>74.70</t>
-        </is>
-      </c>
-      <c r="F52" s="4" t="inlineStr">
-        <is>
-          <t>+0.1</t>
-        </is>
-      </c>
+      <c r="E52" s="4" t="inlineStr"/>
+      <c r="F52" s="4" t="inlineStr"/>
       <c r="G52" s="4" t="n">
         <v>164</v>
       </c>
@@ -28566,16 +28174,8 @@
           <t>能率網通</t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>30.80</t>
-        </is>
-      </c>
-      <c r="F53" s="4" t="inlineStr">
-        <is>
-          <t>+2.8</t>
-        </is>
-      </c>
+      <c r="E53" s="4" t="inlineStr"/>
+      <c r="F53" s="4" t="inlineStr"/>
       <c r="G53" s="4" t="n">
         <v>152</v>
       </c>
@@ -28599,16 +28199,8 @@
           <t>磐亞</t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>25.50</t>
-        </is>
-      </c>
-      <c r="F54" s="4" t="inlineStr">
-        <is>
-          <t>+2.3</t>
-        </is>
-      </c>
+      <c r="E54" s="4" t="inlineStr"/>
+      <c r="F54" s="4" t="inlineStr"/>
       <c r="G54" s="4" t="n">
         <v>148</v>
       </c>
@@ -28632,16 +28224,8 @@
           <t>保勝光學</t>
         </is>
       </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>73.00</t>
-        </is>
-      </c>
-      <c r="F55" s="4" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
+      <c r="E55" s="4" t="inlineStr"/>
+      <c r="F55" s="4" t="inlineStr"/>
       <c r="G55" s="4" t="n">
         <v>142</v>
       </c>
@@ -28665,16 +28249,8 @@
           <t>富旺</t>
         </is>
       </c>
-      <c r="E56" s="4" t="inlineStr">
-        <is>
-          <t>13.25</t>
-        </is>
-      </c>
-      <c r="F56" s="4" t="inlineStr">
-        <is>
-          <t>+0.25</t>
-        </is>
-      </c>
+      <c r="E56" s="4" t="inlineStr"/>
+      <c r="F56" s="4" t="inlineStr"/>
       <c r="G56" s="4" t="n">
         <v>139</v>
       </c>
@@ -28698,16 +28274,8 @@
           <t>鈦昇</t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr">
-        <is>
-          <t>233.00</t>
-        </is>
-      </c>
-      <c r="F57" s="4" t="inlineStr">
-        <is>
-          <t>+1.5</t>
-        </is>
-      </c>
+      <c r="E57" s="4" t="inlineStr"/>
+      <c r="F57" s="4" t="inlineStr"/>
       <c r="G57" s="4" t="n">
         <v>127</v>
       </c>
@@ -28731,16 +28299,8 @@
           <t>創威</t>
         </is>
       </c>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t>89.40</t>
-        </is>
-      </c>
-      <c r="F58" s="4" t="inlineStr">
-        <is>
-          <t>-2.2</t>
-        </is>
-      </c>
+      <c r="E58" s="4" t="inlineStr"/>
+      <c r="F58" s="4" t="inlineStr"/>
       <c r="G58" s="4" t="n">
         <v>126</v>
       </c>
@@ -28764,16 +28324,8 @@
           <t>湧德</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>118.00</t>
-        </is>
-      </c>
-      <c r="F59" s="4" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
+      <c r="E59" s="4" t="inlineStr"/>
+      <c r="F59" s="4" t="inlineStr"/>
       <c r="G59" s="4" t="n">
         <v>124</v>
       </c>
@@ -28797,16 +28349,8 @@
           <t>環宇-KY</t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>562.00</t>
-        </is>
-      </c>
-      <c r="F60" s="4" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
+      <c r="E60" s="4" t="inlineStr"/>
+      <c r="F60" s="4" t="inlineStr"/>
       <c r="G60" s="4" t="n">
         <v>118</v>
       </c>
@@ -28830,16 +28374,8 @@
           <t>沛亨</t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>594.00</t>
-        </is>
-      </c>
-      <c r="F61" s="4" t="inlineStr">
-        <is>
-          <t>+31.0</t>
-        </is>
-      </c>
+      <c r="E61" s="4" t="inlineStr"/>
+      <c r="F61" s="4" t="inlineStr"/>
       <c r="G61" s="4" t="n">
         <v>111</v>
       </c>
@@ -28863,16 +28399,8 @@
           <t>聖暉*</t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr">
-        <is>
-          <t>1350.00</t>
-        </is>
-      </c>
-      <c r="F62" s="4" t="inlineStr">
-        <is>
-          <t>+50.0</t>
-        </is>
-      </c>
+      <c r="E62" s="4" t="inlineStr"/>
+      <c r="F62" s="4" t="inlineStr"/>
       <c r="G62" s="4" t="n">
         <v>105</v>
       </c>
@@ -28896,16 +28424,8 @@
           <t>長園科</t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>40.70</t>
-        </is>
-      </c>
-      <c r="F63" s="4" t="inlineStr">
-        <is>
-          <t>+0.25</t>
-        </is>
-      </c>
+      <c r="E63" s="4" t="inlineStr"/>
+      <c r="F63" s="4" t="inlineStr"/>
       <c r="G63" s="4" t="n">
         <v>105</v>
       </c>
@@ -28929,16 +28449,8 @@
           <t>大國鋼</t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t>35.20</t>
-        </is>
-      </c>
-      <c r="F64" s="4" t="inlineStr">
-        <is>
-          <t>+0.1</t>
-        </is>
-      </c>
+      <c r="E64" s="4" t="inlineStr"/>
+      <c r="F64" s="4" t="inlineStr"/>
       <c r="G64" s="4" t="n">
         <v>103</v>
       </c>
@@ -28962,16 +28474,8 @@
           <t>天良</t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr">
-        <is>
-          <t>64.50</t>
-        </is>
-      </c>
-      <c r="F65" s="4" t="inlineStr">
-        <is>
-          <t>+0.4</t>
-        </is>
-      </c>
+      <c r="E65" s="4" t="inlineStr"/>
+      <c r="F65" s="4" t="inlineStr"/>
       <c r="G65" s="4" t="n">
         <v>101</v>
       </c>
@@ -28995,16 +28499,8 @@
           <t>松瑞藥</t>
         </is>
       </c>
-      <c r="E66" s="4" t="inlineStr">
-        <is>
-          <t>19.25</t>
-        </is>
-      </c>
-      <c r="F66" s="4" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
+      <c r="E66" s="4" t="inlineStr"/>
+      <c r="F66" s="4" t="inlineStr"/>
       <c r="G66" s="4" t="n">
         <v>100</v>
       </c>
@@ -29028,16 +28524,8 @@
           <t>明安</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>54.10</t>
-        </is>
-      </c>
-      <c r="F67" s="4" t="inlineStr">
-        <is>
-          <t>+0.8</t>
-        </is>
-      </c>
+      <c r="E67" s="4" t="inlineStr"/>
+      <c r="F67" s="4" t="inlineStr"/>
       <c r="G67" s="4" t="n">
         <v>96</v>
       </c>
@@ -29061,16 +28549,8 @@
           <t>東浦</t>
         </is>
       </c>
-      <c r="E68" s="4" t="inlineStr">
-        <is>
-          <t>71.30</t>
-        </is>
-      </c>
-      <c r="F68" s="4" t="inlineStr">
-        <is>
-          <t>+2.8</t>
-        </is>
-      </c>
+      <c r="E68" s="4" t="inlineStr"/>
+      <c r="F68" s="4" t="inlineStr"/>
       <c r="G68" s="4" t="n">
         <v>90</v>
       </c>
@@ -29094,16 +28574,8 @@
           <t>臺龍</t>
         </is>
       </c>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>16.10</t>
-        </is>
-      </c>
-      <c r="F69" s="4" t="inlineStr">
-        <is>
-          <t>+0.15</t>
-        </is>
-      </c>
+      <c r="E69" s="4" t="inlineStr"/>
+      <c r="F69" s="4" t="inlineStr"/>
       <c r="G69" s="4" t="n">
         <v>90</v>
       </c>
@@ -29127,16 +28599,8 @@
           <t>豪勉</t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr">
-        <is>
-          <t>40.15</t>
-        </is>
-      </c>
-      <c r="F70" s="4" t="inlineStr">
-        <is>
-          <t>+0.15</t>
-        </is>
-      </c>
+      <c r="E70" s="4" t="inlineStr"/>
+      <c r="F70" s="4" t="inlineStr"/>
       <c r="G70" s="4" t="n">
         <v>86</v>
       </c>
@@ -29160,16 +28624,8 @@
           <t>耕興</t>
         </is>
       </c>
-      <c r="E71" s="4" t="inlineStr">
-        <is>
-          <t>195.50</t>
-        </is>
-      </c>
-      <c r="F71" s="4" t="inlineStr">
-        <is>
-          <t>+5.0</t>
-        </is>
-      </c>
+      <c r="E71" s="4" t="inlineStr"/>
+      <c r="F71" s="4" t="inlineStr"/>
       <c r="G71" s="4" t="n">
         <v>82</v>
       </c>
@@ -29193,16 +28649,8 @@
           <t>晶采</t>
         </is>
       </c>
-      <c r="E72" s="4" t="inlineStr">
-        <is>
-          <t>27.25</t>
-        </is>
-      </c>
-      <c r="F72" s="4" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
+      <c r="E72" s="4" t="inlineStr"/>
+      <c r="F72" s="4" t="inlineStr"/>
       <c r="G72" s="4" t="n">
         <v>78</v>
       </c>
@@ -29226,16 +28674,8 @@
           <t>聚積</t>
         </is>
       </c>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>66.60</t>
-        </is>
-      </c>
-      <c r="F73" s="4" t="inlineStr">
-        <is>
-          <t>-0.9</t>
-        </is>
-      </c>
+      <c r="E73" s="4" t="inlineStr"/>
+      <c r="F73" s="4" t="inlineStr"/>
       <c r="G73" s="4" t="n">
         <v>76</v>
       </c>
@@ -29259,16 +28699,8 @@
           <t>茂綸</t>
         </is>
       </c>
-      <c r="E74" s="4" t="inlineStr">
-        <is>
-          <t>121.50</t>
-        </is>
-      </c>
-      <c r="F74" s="4" t="inlineStr">
-        <is>
-          <t>+2.0</t>
-        </is>
-      </c>
+      <c r="E74" s="4" t="inlineStr"/>
+      <c r="F74" s="4" t="inlineStr"/>
       <c r="G74" s="4" t="n">
         <v>75</v>
       </c>
@@ -29292,16 +28724,8 @@
           <t>寶雅</t>
         </is>
       </c>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>660.00</t>
-        </is>
-      </c>
-      <c r="F75" s="4" t="inlineStr">
-        <is>
-          <t>+2.0</t>
-        </is>
-      </c>
+      <c r="E75" s="4" t="inlineStr"/>
+      <c r="F75" s="4" t="inlineStr"/>
       <c r="G75" s="4" t="n">
         <v>70</v>
       </c>
@@ -29325,16 +28749,8 @@
           <t>逸昌</t>
         </is>
       </c>
-      <c r="E76" s="4" t="inlineStr">
-        <is>
-          <t>29.75</t>
-        </is>
-      </c>
-      <c r="F76" s="4" t="inlineStr">
-        <is>
-          <t>+0.95</t>
-        </is>
-      </c>
+      <c r="E76" s="4" t="inlineStr"/>
+      <c r="F76" s="4" t="inlineStr"/>
       <c r="G76" s="4" t="n">
         <v>64</v>
       </c>
@@ -29358,16 +28774,8 @@
           <t>博智</t>
         </is>
       </c>
-      <c r="E77" s="4" t="inlineStr">
-        <is>
-          <t>391.50</t>
-        </is>
-      </c>
-      <c r="F77" s="4" t="inlineStr">
-        <is>
-          <t>+5.0</t>
-        </is>
-      </c>
+      <c r="E77" s="4" t="inlineStr"/>
+      <c r="F77" s="4" t="inlineStr"/>
       <c r="G77" s="4" t="n">
         <v>64</v>
       </c>
@@ -29391,16 +28799,8 @@
           <t>大江</t>
         </is>
       </c>
-      <c r="E78" s="4" t="inlineStr">
-        <is>
-          <t>117.50</t>
-        </is>
-      </c>
-      <c r="F78" s="4" t="inlineStr">
-        <is>
-          <t>+1.0</t>
-        </is>
-      </c>
+      <c r="E78" s="4" t="inlineStr"/>
+      <c r="F78" s="4" t="inlineStr"/>
       <c r="G78" s="4" t="n">
         <v>64</v>
       </c>
@@ -29424,16 +28824,8 @@
           <t>永信建</t>
         </is>
       </c>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t>54.50</t>
-        </is>
-      </c>
-      <c r="F79" s="4" t="inlineStr">
-        <is>
-          <t>-0.7</t>
-        </is>
-      </c>
+      <c r="E79" s="4" t="inlineStr"/>
+      <c r="F79" s="4" t="inlineStr"/>
       <c r="G79" s="4" t="n">
         <v>63</v>
       </c>
@@ -29457,16 +28849,8 @@
           <t>崇友</t>
         </is>
       </c>
-      <c r="E80" s="4" t="inlineStr">
-        <is>
-          <t>119.50</t>
-        </is>
-      </c>
-      <c r="F80" s="4" t="inlineStr">
-        <is>
-          <t>+1.0</t>
-        </is>
-      </c>
+      <c r="E80" s="4" t="inlineStr"/>
+      <c r="F80" s="4" t="inlineStr"/>
       <c r="G80" s="4" t="n">
         <v>60</v>
       </c>
@@ -29490,16 +28874,8 @@
           <t>恒耀</t>
         </is>
       </c>
-      <c r="E81" s="4" t="inlineStr">
-        <is>
-          <t>40.60</t>
-        </is>
-      </c>
-      <c r="F81" s="4" t="inlineStr">
-        <is>
-          <t>-0.55</t>
-        </is>
-      </c>
+      <c r="E81" s="4" t="inlineStr"/>
+      <c r="F81" s="4" t="inlineStr"/>
       <c r="G81" s="4" t="n">
         <v>60</v>
       </c>
@@ -29523,16 +28899,8 @@
           <t>擎邦</t>
         </is>
       </c>
-      <c r="E82" s="4" t="inlineStr">
-        <is>
-          <t>48.10</t>
-        </is>
-      </c>
-      <c r="F82" s="4" t="inlineStr">
-        <is>
-          <t>+0.55</t>
-        </is>
-      </c>
+      <c r="E82" s="4" t="inlineStr"/>
+      <c r="F82" s="4" t="inlineStr"/>
       <c r="G82" s="4" t="n">
         <v>59</v>
       </c>
@@ -29556,16 +28924,8 @@
           <t>九豪</t>
         </is>
       </c>
-      <c r="E83" s="4" t="inlineStr">
-        <is>
-          <t>93.60</t>
-        </is>
-      </c>
-      <c r="F83" s="4" t="inlineStr">
-        <is>
-          <t>+8.5</t>
-        </is>
-      </c>
+      <c r="E83" s="4" t="inlineStr"/>
+      <c r="F83" s="4" t="inlineStr"/>
       <c r="G83" s="4" t="n">
         <v>59</v>
       </c>
@@ -29589,16 +28949,8 @@
           <t>品安</t>
         </is>
       </c>
-      <c r="E84" s="4" t="inlineStr">
-        <is>
-          <t>66.50</t>
-        </is>
-      </c>
-      <c r="F84" s="4" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
+      <c r="E84" s="4" t="inlineStr"/>
+      <c r="F84" s="4" t="inlineStr"/>
       <c r="G84" s="4" t="n">
         <v>58</v>
       </c>
@@ -29622,16 +28974,8 @@
           <t>正德</t>
         </is>
       </c>
-      <c r="E85" s="4" t="inlineStr">
-        <is>
-          <t>18.00</t>
-        </is>
-      </c>
-      <c r="F85" s="4" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
+      <c r="E85" s="4" t="inlineStr"/>
+      <c r="F85" s="4" t="inlineStr"/>
       <c r="G85" s="4" t="n">
         <v>57</v>
       </c>
@@ -29655,16 +28999,8 @@
           <t>凱鈺</t>
         </is>
       </c>
-      <c r="E86" s="4" t="inlineStr">
-        <is>
-          <t>30.00</t>
-        </is>
-      </c>
-      <c r="F86" s="4" t="inlineStr">
-        <is>
-          <t>-2.7</t>
-        </is>
-      </c>
+      <c r="E86" s="4" t="inlineStr"/>
+      <c r="F86" s="4" t="inlineStr"/>
       <c r="G86" s="4" t="n">
         <v>57</v>
       </c>
@@ -29688,16 +29024,8 @@
           <t>易飛網</t>
         </is>
       </c>
-      <c r="E87" s="4" t="inlineStr">
-        <is>
-          <t>15.55</t>
-        </is>
-      </c>
-      <c r="F87" s="4" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
+      <c r="E87" s="4" t="inlineStr"/>
+      <c r="F87" s="4" t="inlineStr"/>
       <c r="G87" s="4" t="n">
         <v>56</v>
       </c>
@@ -29721,16 +29049,8 @@
           <t>營邦</t>
         </is>
       </c>
-      <c r="E88" s="4" t="inlineStr">
-        <is>
-          <t>504.00</t>
-        </is>
-      </c>
-      <c r="F88" s="4" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
+      <c r="E88" s="4" t="inlineStr"/>
+      <c r="F88" s="4" t="inlineStr"/>
       <c r="G88" s="4" t="n">
         <v>55</v>
       </c>
@@ -29754,16 +29074,8 @@
           <t>昇佳電子</t>
         </is>
       </c>
-      <c r="E89" s="4" t="inlineStr">
-        <is>
-          <t>170.50</t>
-        </is>
-      </c>
-      <c r="F89" s="4" t="inlineStr">
-        <is>
-          <t>+1.0</t>
-        </is>
-      </c>
+      <c r="E89" s="4" t="inlineStr"/>
+      <c r="F89" s="4" t="inlineStr"/>
       <c r="G89" s="4" t="n">
         <v>55</v>
       </c>
@@ -29787,16 +29099,8 @@
           <t>愛地雅</t>
         </is>
       </c>
-      <c r="E90" s="4" t="inlineStr">
-        <is>
-          <t>4.55</t>
-        </is>
-      </c>
-      <c r="F90" s="4" t="inlineStr">
-        <is>
-          <t>-0.13</t>
-        </is>
-      </c>
+      <c r="E90" s="4" t="inlineStr"/>
+      <c r="F90" s="4" t="inlineStr"/>
       <c r="G90" s="4" t="n">
         <v>55</v>
       </c>
@@ -29820,16 +29124,8 @@
           <t>宇峻</t>
         </is>
       </c>
-      <c r="E91" s="4" t="inlineStr">
-        <is>
-          <t>83.60</t>
-        </is>
-      </c>
-      <c r="F91" s="4" t="inlineStr">
-        <is>
-          <t>-0.7</t>
-        </is>
-      </c>
+      <c r="E91" s="4" t="inlineStr"/>
+      <c r="F91" s="4" t="inlineStr"/>
       <c r="G91" s="4" t="n">
         <v>54</v>
       </c>
@@ -29853,16 +29149,8 @@
           <t>台林</t>
         </is>
       </c>
-      <c r="E92" s="4" t="inlineStr">
-        <is>
-          <t>32.70</t>
-        </is>
-      </c>
-      <c r="F92" s="4" t="inlineStr">
-        <is>
-          <t>+1.1</t>
-        </is>
-      </c>
+      <c r="E92" s="4" t="inlineStr"/>
+      <c r="F92" s="4" t="inlineStr"/>
       <c r="G92" s="4" t="n">
         <v>54</v>
       </c>
@@ -29886,16 +29174,8 @@
           <t>精確</t>
         </is>
       </c>
-      <c r="E93" s="4" t="inlineStr">
-        <is>
-          <t>82.30</t>
-        </is>
-      </c>
-      <c r="F93" s="4" t="inlineStr">
-        <is>
-          <t>-0.6</t>
-        </is>
-      </c>
+      <c r="E93" s="4" t="inlineStr"/>
+      <c r="F93" s="4" t="inlineStr"/>
       <c r="G93" s="4" t="n">
         <v>52</v>
       </c>
@@ -29919,16 +29199,8 @@
           <t>系微</t>
         </is>
       </c>
-      <c r="E94" s="4" t="inlineStr">
-        <is>
-          <t>311.00</t>
-        </is>
-      </c>
-      <c r="F94" s="4" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
+      <c r="E94" s="4" t="inlineStr"/>
+      <c r="F94" s="4" t="inlineStr"/>
       <c r="G94" s="4" t="n">
         <v>51</v>
       </c>
@@ -29952,16 +29224,8 @@
           <t>精華</t>
         </is>
       </c>
-      <c r="E95" s="4" t="inlineStr">
-        <is>
-          <t>95.20</t>
-        </is>
-      </c>
-      <c r="F95" s="4" t="inlineStr">
-        <is>
-          <t>+2.2</t>
-        </is>
-      </c>
+      <c r="E95" s="4" t="inlineStr"/>
+      <c r="F95" s="4" t="inlineStr"/>
       <c r="G95" s="4" t="n">
         <v>49</v>
       </c>
@@ -29985,16 +29249,8 @@
           <t>森寶</t>
         </is>
       </c>
-      <c r="E96" s="4" t="inlineStr">
-        <is>
-          <t>22.75</t>
-        </is>
-      </c>
-      <c r="F96" s="4" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
+      <c r="E96" s="4" t="inlineStr"/>
+      <c r="F96" s="4" t="inlineStr"/>
       <c r="G96" s="4" t="n">
         <v>48</v>
       </c>
@@ -30018,16 +29274,8 @@
           <t>維田</t>
         </is>
       </c>
-      <c r="E97" s="4" t="inlineStr">
-        <is>
-          <t>51.50</t>
-        </is>
-      </c>
-      <c r="F97" s="4" t="inlineStr">
-        <is>
-          <t>-1.1</t>
-        </is>
-      </c>
+      <c r="E97" s="4" t="inlineStr"/>
+      <c r="F97" s="4" t="inlineStr"/>
       <c r="G97" s="4" t="n">
         <v>47</v>
       </c>
@@ -30051,16 +29299,8 @@
           <t>岳豐</t>
         </is>
       </c>
-      <c r="E98" s="4" t="inlineStr">
-        <is>
-          <t>39.30</t>
-        </is>
-      </c>
-      <c r="F98" s="4" t="inlineStr">
-        <is>
-          <t>+0.6</t>
-        </is>
-      </c>
+      <c r="E98" s="4" t="inlineStr"/>
+      <c r="F98" s="4" t="inlineStr"/>
       <c r="G98" s="4" t="n">
         <v>46</v>
       </c>
@@ -30084,16 +29324,8 @@
           <t>亞昕</t>
         </is>
       </c>
-      <c r="E99" s="4" t="inlineStr">
-        <is>
-          <t>22.45</t>
-        </is>
-      </c>
-      <c r="F99" s="4" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
+      <c r="E99" s="4" t="inlineStr"/>
+      <c r="F99" s="4" t="inlineStr"/>
       <c r="G99" s="4" t="n">
         <v>45</v>
       </c>
@@ -30117,16 +29349,8 @@
           <t>生華科</t>
         </is>
       </c>
-      <c r="E100" s="4" t="inlineStr">
-        <is>
-          <t>43.00</t>
-        </is>
-      </c>
-      <c r="F100" s="4" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
+      <c r="E100" s="4" t="inlineStr"/>
+      <c r="F100" s="4" t="inlineStr"/>
       <c r="G100" s="4" t="n">
         <v>45</v>
       </c>
@@ -30150,16 +29374,8 @@
           <t>和勤</t>
         </is>
       </c>
-      <c r="E101" s="4" t="inlineStr">
-        <is>
-          <t>20.00</t>
-        </is>
-      </c>
-      <c r="F101" s="4" t="inlineStr">
-        <is>
-          <t>+0.05</t>
-        </is>
-      </c>
+      <c r="E101" s="4" t="inlineStr"/>
+      <c r="F101" s="4" t="inlineStr"/>
       <c r="G101" s="4" t="n">
         <v>44</v>
       </c>
@@ -30183,16 +29399,8 @@
           <t>東友</t>
         </is>
       </c>
-      <c r="E102" s="4" t="inlineStr">
-        <is>
-          <t>19.35</t>
-        </is>
-      </c>
-      <c r="F102" s="4" t="inlineStr">
-        <is>
-          <t>+0.15</t>
-        </is>
-      </c>
+      <c r="E102" s="4" t="inlineStr"/>
+      <c r="F102" s="4" t="inlineStr"/>
       <c r="G102" s="4" t="n">
         <v>44</v>
       </c>
@@ -30216,16 +29424,8 @@
           <t>金益鼎</t>
         </is>
       </c>
-      <c r="E103" s="4" t="inlineStr">
-        <is>
-          <t>108.00</t>
-        </is>
-      </c>
-      <c r="F103" s="4" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
+      <c r="E103" s="4" t="inlineStr"/>
+      <c r="F103" s="4" t="inlineStr"/>
       <c r="G103" s="4" t="n">
         <v>44</v>
       </c>
@@ -30326,16 +29526,8 @@
           <t>漢磊</t>
         </is>
       </c>
-      <c r="E109" s="4" t="inlineStr">
-        <is>
-          <t>85.80</t>
-        </is>
-      </c>
-      <c r="F109" s="4" t="inlineStr">
-        <is>
-          <t>-4.7</t>
-        </is>
-      </c>
+      <c r="E109" s="4" t="inlineStr"/>
+      <c r="F109" s="4" t="inlineStr"/>
       <c r="G109" s="4" t="n">
         <v>-4889</v>
       </c>
@@ -30359,16 +29551,8 @@
           <t>穩懋</t>
         </is>
       </c>
-      <c r="E110" s="4" t="inlineStr">
-        <is>
-          <t>463.00</t>
-        </is>
-      </c>
-      <c r="F110" s="4" t="inlineStr">
-        <is>
-          <t>-15.0</t>
-        </is>
-      </c>
+      <c r="E110" s="4" t="inlineStr"/>
+      <c r="F110" s="4" t="inlineStr"/>
       <c r="G110" s="4" t="n">
         <v>-4717</v>
       </c>
@@ -30392,16 +29576,8 @@
           <t>長科*</t>
         </is>
       </c>
-      <c r="E111" s="4" t="inlineStr">
-        <is>
-          <t>86.60</t>
-        </is>
-      </c>
-      <c r="F111" s="4" t="inlineStr">
-        <is>
-          <t>-5.0</t>
-        </is>
-      </c>
+      <c r="E111" s="4" t="inlineStr"/>
+      <c r="F111" s="4" t="inlineStr"/>
       <c r="G111" s="4" t="n">
         <v>-4037</v>
       </c>
@@ -30425,16 +29601,8 @@
           <t>頎邦</t>
         </is>
       </c>
-      <c r="E112" s="4" t="inlineStr">
-        <is>
-          <t>240.50</t>
-        </is>
-      </c>
-      <c r="F112" s="4" t="inlineStr">
-        <is>
-          <t>-8.5</t>
-        </is>
-      </c>
+      <c r="E112" s="4" t="inlineStr"/>
+      <c r="F112" s="4" t="inlineStr"/>
       <c r="G112" s="4" t="n">
         <v>-3760</v>
       </c>
@@ -30458,16 +29626,8 @@
           <t>中光電</t>
         </is>
       </c>
-      <c r="E113" s="4" t="inlineStr">
-        <is>
-          <t>74.70</t>
-        </is>
-      </c>
-      <c r="F113" s="4" t="inlineStr">
-        <is>
-          <t>-3.9</t>
-        </is>
-      </c>
+      <c r="E113" s="4" t="inlineStr"/>
+      <c r="F113" s="4" t="inlineStr"/>
       <c r="G113" s="4" t="n">
         <v>-3066</v>
       </c>
@@ -30491,16 +29651,8 @@
           <t>台半</t>
         </is>
       </c>
-      <c r="E114" s="4" t="inlineStr">
-        <is>
-          <t>127.00</t>
-        </is>
-      </c>
-      <c r="F114" s="4" t="inlineStr">
-        <is>
-          <t>-5.5</t>
-        </is>
-      </c>
+      <c r="E114" s="4" t="inlineStr"/>
+      <c r="F114" s="4" t="inlineStr"/>
       <c r="G114" s="4" t="n">
         <v>-2818</v>
       </c>
@@ -30524,16 +29676,8 @@
           <t>光環</t>
         </is>
       </c>
-      <c r="E115" s="4" t="inlineStr">
-        <is>
-          <t>135.50</t>
-        </is>
-      </c>
-      <c r="F115" s="4" t="inlineStr">
-        <is>
-          <t>-10.0</t>
-        </is>
-      </c>
+      <c r="E115" s="4" t="inlineStr"/>
+      <c r="F115" s="4" t="inlineStr"/>
       <c r="G115" s="4" t="n">
         <v>-2083</v>
       </c>
@@ -30557,16 +29701,8 @@
           <t>世界</t>
         </is>
       </c>
-      <c r="E116" s="4" t="inlineStr">
-        <is>
-          <t>220.00</t>
-        </is>
-      </c>
-      <c r="F116" s="4" t="inlineStr">
-        <is>
-          <t>+20.0</t>
-        </is>
-      </c>
+      <c r="E116" s="4" t="inlineStr"/>
+      <c r="F116" s="4" t="inlineStr"/>
       <c r="G116" s="4" t="n">
         <v>-1881</v>
       </c>
@@ -30590,16 +29726,8 @@
           <t>榮剛</t>
         </is>
       </c>
-      <c r="E117" s="4" t="inlineStr">
-        <is>
-          <t>34.95</t>
-        </is>
-      </c>
-      <c r="F117" s="4" t="inlineStr">
-        <is>
-          <t>-0.75</t>
-        </is>
-      </c>
+      <c r="E117" s="4" t="inlineStr"/>
+      <c r="F117" s="4" t="inlineStr"/>
       <c r="G117" s="4" t="n">
         <v>-1868</v>
       </c>
@@ -30623,16 +29751,8 @@
           <t>福邦證</t>
         </is>
       </c>
-      <c r="E118" s="4" t="inlineStr">
-        <is>
-          <t>16.75</t>
-        </is>
-      </c>
-      <c r="F118" s="4" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
+      <c r="E118" s="4" t="inlineStr"/>
+      <c r="F118" s="4" t="inlineStr"/>
       <c r="G118" s="4" t="n">
         <v>-1840</v>
       </c>
@@ -30656,16 +29776,8 @@
           <t>安國</t>
         </is>
       </c>
-      <c r="E119" s="4" t="inlineStr">
-        <is>
-          <t>130.00</t>
-        </is>
-      </c>
-      <c r="F119" s="4" t="inlineStr">
-        <is>
-          <t>-6.5</t>
-        </is>
-      </c>
+      <c r="E119" s="4" t="inlineStr"/>
+      <c r="F119" s="4" t="inlineStr"/>
       <c r="G119" s="4" t="n">
         <v>-1777</v>
       </c>
@@ -30689,16 +29801,8 @@
           <t>順達</t>
         </is>
       </c>
-      <c r="E120" s="4" t="inlineStr">
-        <is>
-          <t>408.00</t>
-        </is>
-      </c>
-      <c r="F120" s="4" t="inlineStr">
-        <is>
-          <t>-11.0</t>
-        </is>
-      </c>
+      <c r="E120" s="4" t="inlineStr"/>
+      <c r="F120" s="4" t="inlineStr"/>
       <c r="G120" s="4" t="n">
         <v>-1324</v>
       </c>
@@ -30722,16 +29826,8 @@
           <t>宏捷科</t>
         </is>
       </c>
-      <c r="E121" s="4" t="inlineStr">
-        <is>
-          <t>150.50</t>
-        </is>
-      </c>
-      <c r="F121" s="4" t="inlineStr">
-        <is>
-          <t>-4.0</t>
-        </is>
-      </c>
+      <c r="E121" s="4" t="inlineStr"/>
+      <c r="F121" s="4" t="inlineStr"/>
       <c r="G121" s="4" t="n">
         <v>-1264</v>
       </c>
@@ -30755,16 +29851,8 @@
           <t>東捷</t>
         </is>
       </c>
-      <c r="E122" s="4" t="inlineStr">
-        <is>
-          <t>144.50</t>
-        </is>
-      </c>
-      <c r="F122" s="4" t="inlineStr">
-        <is>
-          <t>-7.5</t>
-        </is>
-      </c>
+      <c r="E122" s="4" t="inlineStr"/>
+      <c r="F122" s="4" t="inlineStr"/>
       <c r="G122" s="4" t="n">
         <v>-1257</v>
       </c>
@@ -30788,16 +29876,8 @@
           <t>蜜望實</t>
         </is>
       </c>
-      <c r="E123" s="4" t="inlineStr">
-        <is>
-          <t>199.00</t>
-        </is>
-      </c>
-      <c r="F123" s="4" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
+      <c r="E123" s="4" t="inlineStr"/>
+      <c r="F123" s="4" t="inlineStr"/>
       <c r="G123" s="4" t="n">
         <v>-1228</v>
       </c>
@@ -30821,16 +29901,8 @@
           <t>金居</t>
         </is>
       </c>
-      <c r="E124" s="4" t="inlineStr">
-        <is>
-          <t>630.00</t>
-        </is>
-      </c>
-      <c r="F124" s="4" t="inlineStr">
-        <is>
-          <t>-8.0</t>
-        </is>
-      </c>
+      <c r="E124" s="4" t="inlineStr"/>
+      <c r="F124" s="4" t="inlineStr"/>
       <c r="G124" s="4" t="n">
         <v>-1193</v>
       </c>
@@ -30854,16 +29926,8 @@
           <t>尚立</t>
         </is>
       </c>
-      <c r="E125" s="4" t="inlineStr">
-        <is>
-          <t>20.90</t>
-        </is>
-      </c>
-      <c r="F125" s="4" t="inlineStr">
-        <is>
-          <t>+1.2</t>
-        </is>
-      </c>
+      <c r="E125" s="4" t="inlineStr"/>
+      <c r="F125" s="4" t="inlineStr"/>
       <c r="G125" s="4" t="n">
         <v>-1119</v>
       </c>
@@ -30887,16 +29951,8 @@
           <t>安可</t>
         </is>
       </c>
-      <c r="E126" s="4" t="inlineStr">
-        <is>
-          <t>52.90</t>
-        </is>
-      </c>
-      <c r="F126" s="4" t="inlineStr">
-        <is>
-          <t>-4.1</t>
-        </is>
-      </c>
+      <c r="E126" s="4" t="inlineStr"/>
+      <c r="F126" s="4" t="inlineStr"/>
       <c r="G126" s="4" t="n">
         <v>-1087</v>
       </c>
@@ -30920,16 +29976,8 @@
           <t>系統電</t>
         </is>
       </c>
-      <c r="E127" s="4" t="inlineStr">
-        <is>
-          <t>66.00</t>
-        </is>
-      </c>
-      <c r="F127" s="4" t="inlineStr">
-        <is>
-          <t>-1.1</t>
-        </is>
-      </c>
+      <c r="E127" s="4" t="inlineStr"/>
+      <c r="F127" s="4" t="inlineStr"/>
       <c r="G127" s="4" t="n">
         <v>-1053</v>
       </c>
@@ -30953,16 +30001,8 @@
           <t>方土昶</t>
         </is>
       </c>
-      <c r="E128" s="4" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
-      </c>
-      <c r="F128" s="4" t="inlineStr">
-        <is>
-          <t>-0.9</t>
-        </is>
-      </c>
+      <c r="E128" s="4" t="inlineStr"/>
+      <c r="F128" s="4" t="inlineStr"/>
       <c r="G128" s="4" t="n">
         <v>-972</v>
       </c>
@@ -30986,16 +30026,8 @@
           <t>康和證</t>
         </is>
       </c>
-      <c r="E129" s="4" t="inlineStr">
-        <is>
-          <t>28.35</t>
-        </is>
-      </c>
-      <c r="F129" s="4" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
+      <c r="E129" s="4" t="inlineStr"/>
+      <c r="F129" s="4" t="inlineStr"/>
       <c r="G129" s="4" t="n">
         <v>-924</v>
       </c>
@@ -31019,16 +30051,8 @@
           <t>雙鴻</t>
         </is>
       </c>
-      <c r="E130" s="4" t="inlineStr">
-        <is>
-          <t>1010.00</t>
-        </is>
-      </c>
-      <c r="F130" s="4" t="inlineStr">
-        <is>
-          <t>-45.0</t>
-        </is>
-      </c>
+      <c r="E130" s="4" t="inlineStr"/>
+      <c r="F130" s="4" t="inlineStr"/>
       <c r="G130" s="4" t="n">
         <v>-874</v>
       </c>
@@ -31052,16 +30076,8 @@
           <t>立敦</t>
         </is>
       </c>
-      <c r="E131" s="4" t="inlineStr">
-        <is>
-          <t>116.50</t>
-        </is>
-      </c>
-      <c r="F131" s="4" t="inlineStr">
-        <is>
-          <t>+1.0</t>
-        </is>
-      </c>
+      <c r="E131" s="4" t="inlineStr"/>
+      <c r="F131" s="4" t="inlineStr"/>
       <c r="G131" s="4" t="n">
         <v>-838</v>
       </c>
@@ -31085,16 +30101,8 @@
           <t>致和證</t>
         </is>
       </c>
-      <c r="E132" s="4" t="inlineStr">
-        <is>
-          <t>47.45</t>
-        </is>
-      </c>
-      <c r="F132" s="4" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
+      <c r="E132" s="4" t="inlineStr"/>
+      <c r="F132" s="4" t="inlineStr"/>
       <c r="G132" s="4" t="n">
         <v>-832</v>
       </c>
@@ -31118,16 +30126,8 @@
           <t>創惟</t>
         </is>
       </c>
-      <c r="E133" s="4" t="inlineStr">
-        <is>
-          <t>102.50</t>
-        </is>
-      </c>
-      <c r="F133" s="4" t="inlineStr">
-        <is>
-          <t>-2.5</t>
-        </is>
-      </c>
+      <c r="E133" s="4" t="inlineStr"/>
+      <c r="F133" s="4" t="inlineStr"/>
       <c r="G133" s="4" t="n">
         <v>-796</v>
       </c>
@@ -31151,16 +30151,8 @@
           <t>尼克森</t>
         </is>
       </c>
-      <c r="E134" s="4" t="inlineStr">
-        <is>
-          <t>92.80</t>
-        </is>
-      </c>
-      <c r="F134" s="4" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
+      <c r="E134" s="4" t="inlineStr"/>
+      <c r="F134" s="4" t="inlineStr"/>
       <c r="G134" s="4" t="n">
         <v>-789</v>
       </c>
@@ -31184,16 +30176,8 @@
           <t>翔名</t>
         </is>
       </c>
-      <c r="E135" s="4" t="inlineStr">
-        <is>
-          <t>264.00</t>
-        </is>
-      </c>
-      <c r="F135" s="4" t="inlineStr">
-        <is>
-          <t>-22.0</t>
-        </is>
-      </c>
+      <c r="E135" s="4" t="inlineStr"/>
+      <c r="F135" s="4" t="inlineStr"/>
       <c r="G135" s="4" t="n">
         <v>-776</v>
       </c>
@@ -31217,16 +30201,8 @@
           <t>宜鼎</t>
         </is>
       </c>
-      <c r="E136" s="4" t="inlineStr">
-        <is>
-          <t>1740.00</t>
-        </is>
-      </c>
-      <c r="F136" s="4" t="inlineStr">
-        <is>
-          <t>-55.0</t>
-        </is>
-      </c>
+      <c r="E136" s="4" t="inlineStr"/>
+      <c r="F136" s="4" t="inlineStr"/>
       <c r="G136" s="4" t="n">
         <v>-763</v>
       </c>
@@ -31250,16 +30226,8 @@
           <t>太欣</t>
         </is>
       </c>
-      <c r="E137" s="4" t="inlineStr">
-        <is>
-          <t>13.05</t>
-        </is>
-      </c>
-      <c r="F137" s="4" t="inlineStr">
-        <is>
-          <t>-1.4</t>
-        </is>
-      </c>
+      <c r="E137" s="4" t="inlineStr"/>
+      <c r="F137" s="4" t="inlineStr"/>
       <c r="G137" s="4" t="n">
         <v>-738</v>
       </c>
@@ -31283,16 +30251,8 @@
           <t>九暘</t>
         </is>
       </c>
-      <c r="E138" s="4" t="inlineStr">
-        <is>
-          <t>116.50</t>
-        </is>
-      </c>
-      <c r="F138" s="4" t="inlineStr">
-        <is>
-          <t>-8.5</t>
-        </is>
-      </c>
+      <c r="E138" s="4" t="inlineStr"/>
+      <c r="F138" s="4" t="inlineStr"/>
       <c r="G138" s="4" t="n">
         <v>-734</v>
       </c>
@@ -31316,16 +30276,8 @@
           <t>精剛</t>
         </is>
       </c>
-      <c r="E139" s="4" t="inlineStr">
-        <is>
-          <t>18.95</t>
-        </is>
-      </c>
-      <c r="F139" s="4" t="inlineStr">
-        <is>
-          <t>-0.2</t>
-        </is>
-      </c>
+      <c r="E139" s="4" t="inlineStr"/>
+      <c r="F139" s="4" t="inlineStr"/>
       <c r="G139" s="4" t="n">
         <v>-728</v>
       </c>
@@ -31349,16 +30301,8 @@
           <t>神盾</t>
         </is>
       </c>
-      <c r="E140" s="4" t="inlineStr">
-        <is>
-          <t>124.50</t>
-        </is>
-      </c>
-      <c r="F140" s="4" t="inlineStr">
-        <is>
-          <t>-9.5</t>
-        </is>
-      </c>
+      <c r="E140" s="4" t="inlineStr"/>
+      <c r="F140" s="4" t="inlineStr"/>
       <c r="G140" s="4" t="n">
         <v>-712</v>
       </c>
@@ -31382,16 +30326,8 @@
           <t>橘子</t>
         </is>
       </c>
-      <c r="E141" s="4" t="inlineStr">
-        <is>
-          <t>47.60</t>
-        </is>
-      </c>
-      <c r="F141" s="4" t="inlineStr">
-        <is>
-          <t>-1.25</t>
-        </is>
-      </c>
+      <c r="E141" s="4" t="inlineStr"/>
+      <c r="F141" s="4" t="inlineStr"/>
       <c r="G141" s="4" t="n">
         <v>-700</v>
       </c>
@@ -31415,16 +30351,8 @@
           <t>千附</t>
         </is>
       </c>
-      <c r="E142" s="4" t="inlineStr">
-        <is>
-          <t>61.60</t>
-        </is>
-      </c>
-      <c r="F142" s="4" t="inlineStr">
-        <is>
-          <t>-1.2</t>
-        </is>
-      </c>
+      <c r="E142" s="4" t="inlineStr"/>
+      <c r="F142" s="4" t="inlineStr"/>
       <c r="G142" s="4" t="n">
         <v>-695</v>
       </c>
@@ -31448,16 +30376,8 @@
           <t>普誠</t>
         </is>
       </c>
-      <c r="E143" s="4" t="inlineStr">
-        <is>
-          <t>19.65</t>
-        </is>
-      </c>
-      <c r="F143" s="4" t="inlineStr">
-        <is>
-          <t>+0.75</t>
-        </is>
-      </c>
+      <c r="E143" s="4" t="inlineStr"/>
+      <c r="F143" s="4" t="inlineStr"/>
       <c r="G143" s="4" t="n">
         <v>-635</v>
       </c>
@@ -31481,16 +30401,8 @@
           <t>新鉅科</t>
         </is>
       </c>
-      <c r="E144" s="4" t="inlineStr">
-        <is>
-          <t>32.15</t>
-        </is>
-      </c>
-      <c r="F144" s="4" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
+      <c r="E144" s="4" t="inlineStr"/>
+      <c r="F144" s="4" t="inlineStr"/>
       <c r="G144" s="4" t="n">
         <v>-634</v>
       </c>
@@ -31514,16 +30426,8 @@
           <t>佶優</t>
         </is>
       </c>
-      <c r="E145" s="4" t="inlineStr">
-        <is>
-          <t>33.40</t>
-        </is>
-      </c>
-      <c r="F145" s="4" t="inlineStr">
-        <is>
-          <t>-0.55</t>
-        </is>
-      </c>
+      <c r="E145" s="4" t="inlineStr"/>
+      <c r="F145" s="4" t="inlineStr"/>
       <c r="G145" s="4" t="n">
         <v>-583</v>
       </c>
@@ -31547,16 +30451,8 @@
           <t>昇達科</t>
         </is>
       </c>
-      <c r="E146" s="4" t="inlineStr">
-        <is>
-          <t>1340.00</t>
-        </is>
-      </c>
-      <c r="F146" s="4" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
+      <c r="E146" s="4" t="inlineStr"/>
+      <c r="F146" s="4" t="inlineStr"/>
       <c r="G146" s="4" t="n">
         <v>-572</v>
       </c>
@@ -31580,16 +30476,8 @@
           <t>高僑</t>
         </is>
       </c>
-      <c r="E147" s="4" t="inlineStr">
-        <is>
-          <t>48.75</t>
-        </is>
-      </c>
-      <c r="F147" s="4" t="inlineStr">
-        <is>
-          <t>-1.65</t>
-        </is>
-      </c>
+      <c r="E147" s="4" t="inlineStr"/>
+      <c r="F147" s="4" t="inlineStr"/>
       <c r="G147" s="4" t="n">
         <v>-559</v>
       </c>
@@ -31613,16 +30501,8 @@
           <t>典範</t>
         </is>
       </c>
-      <c r="E148" s="4" t="inlineStr">
-        <is>
-          <t>21.90</t>
-        </is>
-      </c>
-      <c r="F148" s="4" t="inlineStr">
-        <is>
-          <t>-1.1</t>
-        </is>
-      </c>
+      <c r="E148" s="4" t="inlineStr"/>
+      <c r="F148" s="4" t="inlineStr"/>
       <c r="G148" s="4" t="n">
         <v>-537</v>
       </c>
@@ -31646,16 +30526,8 @@
           <t>台燿</t>
         </is>
       </c>
-      <c r="E149" s="4" t="inlineStr">
-        <is>
-          <t>1700.00</t>
-        </is>
-      </c>
-      <c r="F149" s="4" t="inlineStr">
-        <is>
-          <t>-65.0</t>
-        </is>
-      </c>
+      <c r="E149" s="4" t="inlineStr"/>
+      <c r="F149" s="4" t="inlineStr"/>
       <c r="G149" s="4" t="n">
         <v>-534</v>
       </c>
@@ -31679,16 +30551,8 @@
           <t>千附精密</t>
         </is>
       </c>
-      <c r="E150" s="4" t="inlineStr">
-        <is>
-          <t>224.00</t>
-        </is>
-      </c>
-      <c r="F150" s="4" t="inlineStr">
-        <is>
-          <t>-2.5</t>
-        </is>
-      </c>
+      <c r="E150" s="4" t="inlineStr"/>
+      <c r="F150" s="4" t="inlineStr"/>
       <c r="G150" s="4" t="n">
         <v>-518</v>
       </c>
@@ -31712,16 +30576,8 @@
           <t>耀勝</t>
         </is>
       </c>
-      <c r="E151" s="4" t="inlineStr">
-        <is>
-          <t>67.30</t>
-        </is>
-      </c>
-      <c r="F151" s="4" t="inlineStr">
-        <is>
-          <t>-2.8</t>
-        </is>
-      </c>
+      <c r="E151" s="4" t="inlineStr"/>
+      <c r="F151" s="4" t="inlineStr"/>
       <c r="G151" s="4" t="n">
         <v>-505</v>
       </c>
@@ -31745,16 +30601,8 @@
           <t>臺慶科</t>
         </is>
       </c>
-      <c r="E152" s="4" t="inlineStr">
-        <is>
-          <t>316.00</t>
-        </is>
-      </c>
-      <c r="F152" s="4" t="inlineStr">
-        <is>
-          <t>-3.5</t>
-        </is>
-      </c>
+      <c r="E152" s="4" t="inlineStr"/>
+      <c r="F152" s="4" t="inlineStr"/>
       <c r="G152" s="4" t="n">
         <v>-481</v>
       </c>
@@ -31778,16 +30626,8 @@
           <t>前鼎</t>
         </is>
       </c>
-      <c r="E153" s="4" t="inlineStr">
-        <is>
-          <t>195.50</t>
-        </is>
-      </c>
-      <c r="F153" s="4" t="inlineStr">
-        <is>
-          <t>-7.5</t>
-        </is>
-      </c>
+      <c r="E153" s="4" t="inlineStr"/>
+      <c r="F153" s="4" t="inlineStr"/>
       <c r="G153" s="4" t="n">
         <v>-471</v>
       </c>
@@ -31811,16 +30651,8 @@
           <t>鉅橡</t>
         </is>
       </c>
-      <c r="E154" s="4" t="inlineStr">
-        <is>
-          <t>68.90</t>
-        </is>
-      </c>
-      <c r="F154" s="4" t="inlineStr">
-        <is>
-          <t>-2.1</t>
-        </is>
-      </c>
+      <c r="E154" s="4" t="inlineStr"/>
+      <c r="F154" s="4" t="inlineStr"/>
       <c r="G154" s="4" t="n">
         <v>-469</v>
       </c>
@@ -31844,16 +30676,8 @@
           <t>岱稜</t>
         </is>
       </c>
-      <c r="E155" s="4" t="inlineStr">
-        <is>
-          <t>58.80</t>
-        </is>
-      </c>
-      <c r="F155" s="4" t="inlineStr">
-        <is>
-          <t>-1.8</t>
-        </is>
-      </c>
+      <c r="E155" s="4" t="inlineStr"/>
+      <c r="F155" s="4" t="inlineStr"/>
       <c r="G155" s="4" t="n">
         <v>-457</v>
       </c>
@@ -31877,16 +30701,8 @@
           <t>久元</t>
         </is>
       </c>
-      <c r="E156" s="4" t="inlineStr">
-        <is>
-          <t>96.00</t>
-        </is>
-      </c>
-      <c r="F156" s="4" t="inlineStr">
-        <is>
-          <t>-3.5</t>
-        </is>
-      </c>
+      <c r="E156" s="4" t="inlineStr"/>
+      <c r="F156" s="4" t="inlineStr"/>
       <c r="G156" s="4" t="n">
         <v>-451</v>
       </c>
@@ -31910,16 +30726,8 @@
           <t>鈺創</t>
         </is>
       </c>
-      <c r="E157" s="4" t="inlineStr">
-        <is>
-          <t>93.50</t>
-        </is>
-      </c>
-      <c r="F157" s="4" t="inlineStr">
-        <is>
-          <t>+1.6</t>
-        </is>
-      </c>
+      <c r="E157" s="4" t="inlineStr"/>
+      <c r="F157" s="4" t="inlineStr"/>
       <c r="G157" s="4" t="n">
         <v>-446</v>
       </c>
@@ -31943,16 +30751,8 @@
           <t>僑威</t>
         </is>
       </c>
-      <c r="E158" s="4" t="inlineStr">
-        <is>
-          <t>53.50</t>
-        </is>
-      </c>
-      <c r="F158" s="4" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
+      <c r="E158" s="4" t="inlineStr"/>
+      <c r="F158" s="4" t="inlineStr"/>
       <c r="G158" s="4" t="n">
         <v>-444</v>
       </c>

--- a/StockInfo/otc_analysis_result.xlsx
+++ b/StockInfo/otc_analysis_result.xlsx
@@ -5177,8 +5177,16 @@
           <t>中美晶</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>235.50</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>-23.5</t>
+        </is>
+      </c>
       <c r="G4" s="4" t="n">
         <v>5977</v>
       </c>
@@ -5209,8 +5217,16 @@
           <t>光洋科</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr"/>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>107.50</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>-6.5</t>
+        </is>
+      </c>
       <c r="G5" s="4" t="n">
         <v>5741</v>
       </c>
@@ -5237,8 +5253,16 @@
           <t>頎邦</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr"/>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>178.50</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>-19.5</t>
+        </is>
+      </c>
       <c r="G6" s="4" t="n">
         <v>4419</v>
       </c>
@@ -5265,8 +5289,16 @@
           <t>富喬</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr"/>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>81.50</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>-7.6</t>
+        </is>
+      </c>
       <c r="G7" s="4" t="n">
         <v>3116</v>
       </c>
@@ -5297,8 +5329,16 @@
           <t>環球晶</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr"/>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>1240.00</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>-130.0</t>
+        </is>
+      </c>
       <c r="G8" s="4" t="n">
         <v>2984</v>
       </c>
@@ -5325,8 +5365,16 @@
           <t>金居</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr"/>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>398.50</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>nannan</t>
+        </is>
+      </c>
       <c r="G9" s="4" t="n">
         <v>2699</v>
       </c>
@@ -5353,8 +5401,16 @@
           <t>台半</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr"/>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>92.50</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>-9.5</t>
+        </is>
+      </c>
       <c r="G10" s="4" t="n">
         <v>2597</v>
       </c>
@@ -5381,8 +5437,16 @@
           <t>亞電</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr"/>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>60.20</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>-6.6</t>
+        </is>
+      </c>
       <c r="G11" s="4" t="n">
         <v>2271</v>
       </c>
@@ -5417,8 +5481,16 @@
           <t>華星光</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr"/>
-      <c r="F12" s="4" t="inlineStr"/>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>356.00</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>-36.0</t>
+        </is>
+      </c>
       <c r="G12" s="4" t="n">
         <v>2079</v>
       </c>
@@ -5453,8 +5525,16 @@
           <t>環宇-KY</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr"/>
-      <c r="F13" s="4" t="inlineStr"/>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>360.00</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
       <c r="G13" s="4" t="n">
         <v>1947</v>
       </c>
@@ -5489,8 +5569,16 @@
           <t>蜜望實</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr"/>
-      <c r="F14" s="4" t="inlineStr"/>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>141.00</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>-12.0</t>
+        </is>
+      </c>
       <c r="G14" s="4" t="n">
         <v>1779</v>
       </c>
@@ -5517,8 +5605,16 @@
           <t>光頡</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr"/>
-      <c r="F15" s="4" t="inlineStr"/>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>97.70</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>-10.8</t>
+        </is>
+      </c>
       <c r="G15" s="4" t="n">
         <v>1750</v>
       </c>
@@ -5549,8 +5645,16 @@
           <t>台燿</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr"/>
-      <c r="F16" s="4" t="inlineStr"/>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>1170.00</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>-125.0</t>
+        </is>
+      </c>
       <c r="G16" s="4" t="n">
         <v>1527</v>
       </c>
@@ -5581,8 +5685,16 @@
           <t>元太</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="4" t="inlineStr"/>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>181.50</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>-2.5</t>
+        </is>
+      </c>
       <c r="G17" s="4" t="n">
         <v>1526</v>
       </c>
@@ -5613,8 +5725,16 @@
           <t>金山電</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr"/>
-      <c r="F18" s="4" t="inlineStr"/>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>129.50</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>-14.0</t>
+        </is>
+      </c>
       <c r="G18" s="4" t="n">
         <v>1497</v>
       </c>
@@ -5641,8 +5761,16 @@
           <t>精材</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr"/>
-      <c r="F19" s="4" t="inlineStr"/>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>358.50</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>-36.5</t>
+        </is>
+      </c>
       <c r="G19" s="4" t="n">
         <v>1352</v>
       </c>
@@ -5673,8 +5801,16 @@
           <t>凱崴</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr"/>
-      <c r="F20" s="4" t="inlineStr"/>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>49.05</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>-4.95</t>
+        </is>
+      </c>
       <c r="G20" s="4" t="n">
         <v>1352</v>
       </c>
@@ -5705,8 +5841,16 @@
           <t>長科*</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr"/>
-      <c r="F21" s="4" t="inlineStr"/>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>73.50</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>-4.0</t>
+        </is>
+      </c>
       <c r="G21" s="4" t="n">
         <v>1196</v>
       </c>
@@ -5737,8 +5881,16 @@
           <t>臺慶科</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr"/>
-      <c r="F22" s="4" t="inlineStr"/>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>218.00</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>-18.5</t>
+        </is>
+      </c>
       <c r="G22" s="4" t="n">
         <v>1112</v>
       </c>
@@ -5769,8 +5921,16 @@
           <t>九豪</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr"/>
-      <c r="F23" s="4" t="inlineStr"/>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>60.10</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>-6.6</t>
+        </is>
+      </c>
       <c r="G23" s="4" t="n">
         <v>1005</v>
       </c>
@@ -5797,8 +5957,16 @@
           <t>漢磊</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr"/>
-      <c r="F24" s="4" t="inlineStr"/>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>68.70</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>-6.8</t>
+        </is>
+      </c>
       <c r="G24" s="4" t="n">
         <v>995</v>
       </c>
@@ -5825,8 +5993,16 @@
           <t>晟田</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr"/>
-      <c r="F25" s="4" t="inlineStr"/>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>72.60</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>+1.3</t>
+        </is>
+      </c>
       <c r="G25" s="4" t="n">
         <v>994</v>
       </c>
@@ -5853,8 +6029,16 @@
           <t>華電網</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr"/>
-      <c r="F26" s="4" t="inlineStr"/>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>40.30</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>-4.25</t>
+        </is>
+      </c>
       <c r="G26" s="4" t="n">
         <v>927</v>
       </c>
@@ -5885,8 +6069,16 @@
           <t>德宏</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr"/>
-      <c r="F27" s="4" t="inlineStr"/>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>158.00</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>-17.5</t>
+        </is>
+      </c>
       <c r="G27" s="4" t="n">
         <v>878</v>
       </c>
@@ -5917,8 +6109,16 @@
           <t>由田</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr"/>
-      <c r="F28" s="4" t="inlineStr"/>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>-18.0</t>
+        </is>
+      </c>
       <c r="G28" s="4" t="n">
         <v>868</v>
       </c>
@@ -5953,8 +6153,16 @@
           <t>良維</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr"/>
-      <c r="F29" s="4" t="inlineStr"/>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>232.50</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>-25.0</t>
+        </is>
+      </c>
       <c r="G29" s="4" t="n">
         <v>821</v>
       </c>
@@ -5981,8 +6189,16 @@
           <t>千如</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr"/>
-      <c r="F30" s="4" t="inlineStr"/>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>48.35</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>-5.35</t>
+        </is>
+      </c>
       <c r="G30" s="4" t="n">
         <v>774</v>
       </c>
@@ -6009,8 +6225,16 @@
           <t>前鼎</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr"/>
-      <c r="F31" s="4" t="inlineStr"/>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>138.00</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>-13.5</t>
+        </is>
+      </c>
       <c r="G31" s="4" t="n">
         <v>773</v>
       </c>
@@ -6041,8 +6265,16 @@
           <t>先進光</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr"/>
-      <c r="F32" s="4" t="inlineStr"/>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>156.00</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>-13.5</t>
+        </is>
+      </c>
       <c r="G32" s="4" t="n">
         <v>687</v>
       </c>
@@ -6069,8 +6301,16 @@
           <t>松上</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr"/>
-      <c r="F33" s="4" t="inlineStr"/>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>24.35</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>-1.95</t>
+        </is>
+      </c>
       <c r="G33" s="4" t="n">
         <v>677</v>
       </c>
@@ -6097,8 +6337,16 @@
           <t>宜鼎</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr"/>
-      <c r="F34" s="4" t="inlineStr"/>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>1275.00</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>-120.0</t>
+        </is>
+      </c>
       <c r="G34" s="4" t="n">
         <v>639</v>
       </c>
@@ -6125,8 +6373,16 @@
           <t>風青</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr"/>
-      <c r="F35" s="4" t="inlineStr"/>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>56.70</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>-6.3</t>
+        </is>
+      </c>
       <c r="G35" s="4" t="n">
         <v>614</v>
       </c>
@@ -6153,8 +6409,16 @@
           <t>雍智科技</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr"/>
-      <c r="F36" s="4" t="inlineStr"/>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>1215.00</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>-135.0</t>
+        </is>
+      </c>
       <c r="G36" s="4" t="n">
         <v>599</v>
       </c>
@@ -6189,8 +6453,16 @@
           <t>聯亞</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr"/>
-      <c r="F37" s="4" t="inlineStr"/>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>1480.00</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>-140.0</t>
+        </is>
+      </c>
       <c r="G37" s="4" t="n">
         <v>587</v>
       </c>
@@ -6217,8 +6489,16 @@
           <t>光環</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr"/>
-      <c r="F38" s="4" t="inlineStr"/>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>100.50</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>-7.5</t>
+        </is>
+      </c>
       <c r="G38" s="4" t="n">
         <v>558</v>
       </c>
@@ -6249,8 +6529,16 @@
           <t>雙鴻</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr"/>
-      <c r="F39" s="4" t="inlineStr"/>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>913.00</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>+11.0</t>
+        </is>
+      </c>
       <c r="G39" s="4" t="n">
         <v>543</v>
       </c>
@@ -6277,8 +6565,16 @@
           <t>佳邦</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr"/>
-      <c r="F40" s="4" t="inlineStr"/>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>81.10</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>-7.7</t>
+        </is>
+      </c>
       <c r="G40" s="4" t="n">
         <v>527</v>
       </c>
@@ -6305,8 +6601,16 @@
           <t>士開</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr"/>
-      <c r="F41" s="4" t="inlineStr"/>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>12.00</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>-0.2</t>
+        </is>
+      </c>
       <c r="G41" s="4" t="n">
         <v>522</v>
       </c>
@@ -6341,8 +6645,16 @@
           <t>高技</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr"/>
-      <c r="F42" s="4" t="inlineStr"/>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>262.00</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>-27.0</t>
+        </is>
+      </c>
       <c r="G42" s="4" t="n">
         <v>522</v>
       </c>
@@ -6369,8 +6681,16 @@
           <t>勤凱</t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr"/>
-      <c r="F43" s="4" t="inlineStr"/>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>250.00</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>-25.5</t>
+        </is>
+      </c>
       <c r="G43" s="4" t="n">
         <v>513</v>
       </c>
@@ -6401,8 +6721,16 @@
           <t>廣穎</t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr"/>
-      <c r="F44" s="4" t="inlineStr"/>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>141.00</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>-10.0</t>
+        </is>
+      </c>
       <c r="G44" s="4" t="n">
         <v>507</v>
       </c>
@@ -6429,8 +6757,16 @@
           <t>寶雅</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr"/>
-      <c r="F45" s="4" t="inlineStr"/>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>615.00</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>-8.0</t>
+        </is>
+      </c>
       <c r="G45" s="4" t="n">
         <v>504</v>
       </c>
@@ -6465,8 +6801,16 @@
           <t>建榮</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr"/>
-      <c r="F46" s="4" t="inlineStr"/>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>71.00</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>-6.7</t>
+        </is>
+      </c>
       <c r="G46" s="4" t="n">
         <v>483</v>
       </c>
@@ -6493,8 +6837,16 @@
           <t>合晶</t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr"/>
-      <c r="F47" s="4" t="inlineStr"/>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>149.50</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>-16.5</t>
+        </is>
+      </c>
       <c r="G47" s="4" t="n">
         <v>482</v>
       </c>
@@ -6521,8 +6873,16 @@
           <t>大中</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr"/>
-      <c r="F48" s="4" t="inlineStr"/>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>290.00</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>-18.5</t>
+        </is>
+      </c>
       <c r="G48" s="4" t="n">
         <v>445</v>
       </c>
@@ -6553,8 +6913,16 @@
           <t>東洋</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr"/>
-      <c r="F49" s="4" t="inlineStr"/>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>77.80</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>-0.9</t>
+        </is>
+      </c>
       <c r="G49" s="4" t="n">
         <v>442</v>
       </c>
@@ -6585,8 +6953,16 @@
           <t>宏碁資訊</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr"/>
-      <c r="F50" s="4" t="inlineStr"/>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>239.50</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>+11.0</t>
+        </is>
+      </c>
       <c r="G50" s="4" t="n">
         <v>434</v>
       </c>
@@ -6621,8 +6997,16 @@
           <t>邑錡</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr"/>
-      <c r="F51" s="4" t="inlineStr"/>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>117.00</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>-10.5</t>
+        </is>
+      </c>
       <c r="G51" s="4" t="n">
         <v>418</v>
       </c>
@@ -6653,8 +7037,16 @@
           <t>高僑</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr"/>
-      <c r="F52" s="4" t="inlineStr"/>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>36.75</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>-3.25</t>
+        </is>
+      </c>
       <c r="G52" s="4" t="n">
         <v>394</v>
       </c>
@@ -6681,8 +7073,16 @@
           <t>擎亞</t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr"/>
-      <c r="F53" s="4" t="inlineStr"/>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>128.00</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>-14.0</t>
+        </is>
+      </c>
       <c r="G53" s="4" t="n">
         <v>385</v>
       </c>
@@ -6709,8 +7109,16 @@
           <t>德微</t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr"/>
-      <c r="F54" s="4" t="inlineStr"/>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>285.50</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>-31.5</t>
+        </is>
+      </c>
       <c r="G54" s="4" t="n">
         <v>382</v>
       </c>
@@ -6737,8 +7145,16 @@
           <t>泰藝</t>
         </is>
       </c>
-      <c r="E55" s="4" t="inlineStr"/>
-      <c r="F55" s="4" t="inlineStr"/>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>47.30</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>-5.1</t>
+        </is>
+      </c>
       <c r="G55" s="4" t="n">
         <v>367</v>
       </c>
@@ -6765,8 +7181,16 @@
           <t>群聯</t>
         </is>
       </c>
-      <c r="E56" s="4" t="inlineStr"/>
-      <c r="F56" s="4" t="inlineStr"/>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>1785.00</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>-195.0</t>
+        </is>
+      </c>
       <c r="G56" s="4" t="n">
         <v>361</v>
       </c>
@@ -6793,8 +7217,16 @@
           <t>九暘</t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr"/>
-      <c r="F57" s="4" t="inlineStr"/>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>75.40</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>-7.1</t>
+        </is>
+      </c>
       <c r="G57" s="4" t="n">
         <v>331</v>
       </c>
@@ -6821,8 +7253,16 @@
           <t>能率網通</t>
         </is>
       </c>
-      <c r="E58" s="4" t="inlineStr"/>
-      <c r="F58" s="4" t="inlineStr"/>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
       <c r="G58" s="4" t="n">
         <v>315</v>
       </c>
@@ -6853,8 +7293,16 @@
           <t>波若威</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr"/>
-      <c r="F59" s="4" t="inlineStr"/>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>652.00</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>-72.0</t>
+        </is>
+      </c>
       <c r="G59" s="4" t="n">
         <v>306</v>
       </c>
@@ -6885,8 +7333,16 @@
           <t>今展科</t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr"/>
-      <c r="F60" s="4" t="inlineStr"/>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>66.10</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>-6.9</t>
+        </is>
+      </c>
       <c r="G60" s="4" t="n">
         <v>301</v>
       </c>
@@ -6913,8 +7369,16 @@
           <t>廣閎科</t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr"/>
-      <c r="F61" s="4" t="inlineStr"/>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>191.00</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>-21.0</t>
+        </is>
+      </c>
       <c r="G61" s="4" t="n">
         <v>301</v>
       </c>
@@ -6945,8 +7409,16 @@
           <t>上詮</t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr"/>
-      <c r="F62" s="4" t="inlineStr"/>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>504.00</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>-51.0</t>
+        </is>
+      </c>
       <c r="G62" s="4" t="n">
         <v>274</v>
       </c>
@@ -6977,8 +7449,16 @@
           <t>港建*</t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr"/>
-      <c r="F63" s="4" t="inlineStr"/>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>47.30</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>-3.6</t>
+        </is>
+      </c>
       <c r="G63" s="4" t="n">
         <v>260</v>
       </c>
@@ -7005,8 +7485,16 @@
           <t>昇達科</t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr"/>
-      <c r="F64" s="4" t="inlineStr"/>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>1355.00</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>+45.0</t>
+        </is>
+      </c>
       <c r="G64" s="4" t="n">
         <v>242</v>
       </c>
@@ -7033,8 +7521,16 @@
           <t>大國鋼</t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr"/>
-      <c r="F65" s="4" t="inlineStr"/>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>35.80</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>-0.3</t>
+        </is>
+      </c>
       <c r="G65" s="4" t="n">
         <v>235</v>
       </c>
@@ -7065,8 +7561,16 @@
           <t>力士</t>
         </is>
       </c>
-      <c r="E66" s="4" t="inlineStr"/>
-      <c r="F66" s="4" t="inlineStr"/>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>48.90</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>-4.7</t>
+        </is>
+      </c>
       <c r="G66" s="4" t="n">
         <v>230</v>
       </c>
@@ -7093,8 +7597,16 @@
           <t>世紀*</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr"/>
-      <c r="F67" s="4" t="inlineStr"/>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>59.20</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>-5.0</t>
+        </is>
+      </c>
       <c r="G67" s="4" t="n">
         <v>219</v>
       </c>
@@ -7121,8 +7633,16 @@
           <t>龍巖</t>
         </is>
       </c>
-      <c r="E68" s="4" t="inlineStr"/>
-      <c r="F68" s="4" t="inlineStr"/>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>48.35</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>-0.15</t>
+        </is>
+      </c>
       <c r="G68" s="4" t="n">
         <v>215</v>
       </c>
@@ -7153,8 +7673,16 @@
           <t>博智</t>
         </is>
       </c>
-      <c r="E69" s="4" t="inlineStr"/>
-      <c r="F69" s="4" t="inlineStr"/>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>302.00</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>-25.5</t>
+        </is>
+      </c>
       <c r="G69" s="4" t="n">
         <v>214</v>
       </c>
@@ -7181,8 +7709,16 @@
           <t>沛亨</t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr"/>
-      <c r="F70" s="4" t="inlineStr"/>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>373.50</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>-39.0</t>
+        </is>
+      </c>
       <c r="G70" s="4" t="n">
         <v>213</v>
       </c>
@@ -7209,8 +7745,16 @@
           <t>東捷</t>
         </is>
       </c>
-      <c r="E71" s="4" t="inlineStr"/>
-      <c r="F71" s="4" t="inlineStr"/>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>116.00</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>-11.5</t>
+        </is>
+      </c>
       <c r="G71" s="4" t="n">
         <v>201</v>
       </c>
@@ -7237,8 +7781,16 @@
           <t>保勝光學</t>
         </is>
       </c>
-      <c r="E72" s="4" t="inlineStr"/>
-      <c r="F72" s="4" t="inlineStr"/>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>73.90</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>+2.9</t>
+        </is>
+      </c>
       <c r="G72" s="4" t="n">
         <v>197</v>
       </c>
@@ -7269,8 +7821,16 @@
           <t>堡達</t>
         </is>
       </c>
-      <c r="E73" s="4" t="inlineStr"/>
-      <c r="F73" s="4" t="inlineStr"/>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>57.00</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>-5.1</t>
+        </is>
+      </c>
       <c r="G73" s="4" t="n">
         <v>193</v>
       </c>
@@ -7297,8 +7857,16 @@
           <t>鑫永洋</t>
         </is>
       </c>
-      <c r="E74" s="4" t="inlineStr"/>
-      <c r="F74" s="4" t="inlineStr"/>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>16.80</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>-0.9</t>
+        </is>
+      </c>
       <c r="G74" s="4" t="n">
         <v>190</v>
       </c>
@@ -7333,8 +7901,16 @@
           <t>系微</t>
         </is>
       </c>
-      <c r="E75" s="4" t="inlineStr"/>
-      <c r="F75" s="4" t="inlineStr"/>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>230.50</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>-18.0</t>
+        </is>
+      </c>
       <c r="G75" s="4" t="n">
         <v>175</v>
       </c>
@@ -7365,8 +7941,16 @@
           <t>晟德</t>
         </is>
       </c>
-      <c r="E76" s="4" t="inlineStr"/>
-      <c r="F76" s="4" t="inlineStr"/>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>37.00</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
       <c r="G76" s="4" t="n">
         <v>174</v>
       </c>
@@ -7393,8 +7977,16 @@
           <t>倍微</t>
         </is>
       </c>
-      <c r="E77" s="4" t="inlineStr"/>
-      <c r="F77" s="4" t="inlineStr"/>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>30.90</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>-2.3</t>
+        </is>
+      </c>
       <c r="G77" s="4" t="n">
         <v>174</v>
       </c>
@@ -7421,8 +8013,16 @@
           <t>立凱-KY</t>
         </is>
       </c>
-      <c r="E78" s="4" t="inlineStr"/>
-      <c r="F78" s="4" t="inlineStr"/>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>31.20</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>-0.05</t>
+        </is>
+      </c>
       <c r="G78" s="4" t="n">
         <v>171</v>
       </c>
@@ -7453,8 +8053,16 @@
           <t>博磊</t>
         </is>
       </c>
-      <c r="E79" s="4" t="inlineStr"/>
-      <c r="F79" s="4" t="inlineStr"/>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>115.50</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>-8.0</t>
+        </is>
+      </c>
       <c r="G79" s="4" t="n">
         <v>169</v>
       </c>
@@ -7485,8 +8093,16 @@
           <t>創威</t>
         </is>
       </c>
-      <c r="E80" s="4" t="inlineStr"/>
-      <c r="F80" s="4" t="inlineStr"/>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>69.00</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>-5.5</t>
+        </is>
+      </c>
       <c r="G80" s="4" t="n">
         <v>143</v>
       </c>
@@ -7517,8 +8133,16 @@
           <t>大立</t>
         </is>
       </c>
-      <c r="E81" s="4" t="inlineStr"/>
-      <c r="F81" s="4" t="inlineStr"/>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>18.80</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>-1.4</t>
+        </is>
+      </c>
       <c r="G81" s="4" t="n">
         <v>139</v>
       </c>
@@ -7545,8 +8169,16 @@
           <t>IET-KY</t>
         </is>
       </c>
-      <c r="E82" s="4" t="inlineStr"/>
-      <c r="F82" s="4" t="inlineStr"/>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>375.00</t>
+        </is>
+      </c>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>-41.5</t>
+        </is>
+      </c>
       <c r="G82" s="4" t="n">
         <v>137</v>
       </c>
@@ -7577,8 +8209,16 @@
           <t>德昌</t>
         </is>
       </c>
-      <c r="E83" s="4" t="inlineStr"/>
-      <c r="F83" s="4" t="inlineStr"/>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>67.90</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>+1.5</t>
+        </is>
+      </c>
       <c r="G83" s="4" t="n">
         <v>136</v>
       </c>
@@ -7605,8 +8245,16 @@
           <t>旺矽</t>
         </is>
       </c>
-      <c r="E84" s="4" t="inlineStr"/>
-      <c r="F84" s="4" t="inlineStr"/>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>5600.00</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>-620.0</t>
+        </is>
+      </c>
       <c r="G84" s="4" t="n">
         <v>131</v>
       </c>
@@ -7633,8 +8281,16 @@
           <t>川寶</t>
         </is>
       </c>
-      <c r="E85" s="4" t="inlineStr"/>
-      <c r="F85" s="4" t="inlineStr"/>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>59.50</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>-3.7</t>
+        </is>
+      </c>
       <c r="G85" s="4" t="n">
         <v>129</v>
       </c>
@@ -7665,8 +8321,16 @@
           <t>鈺鎧</t>
         </is>
       </c>
-      <c r="E86" s="4" t="inlineStr"/>
-      <c r="F86" s="4" t="inlineStr"/>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>43.55</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>-4.8</t>
+        </is>
+      </c>
       <c r="G86" s="4" t="n">
         <v>128</v>
       </c>
@@ -7697,8 +8361,16 @@
           <t>大樹</t>
         </is>
       </c>
-      <c r="E87" s="4" t="inlineStr"/>
-      <c r="F87" s="4" t="inlineStr"/>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>77.80</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>-0.7</t>
+        </is>
+      </c>
       <c r="G87" s="4" t="n">
         <v>123</v>
       </c>
@@ -7729,8 +8401,16 @@
           <t>華宏</t>
         </is>
       </c>
-      <c r="E88" s="4" t="inlineStr"/>
-      <c r="F88" s="4" t="inlineStr"/>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>42.75</t>
+        </is>
+      </c>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t>-3.55</t>
+        </is>
+      </c>
       <c r="G88" s="4" t="n">
         <v>122</v>
       </c>
@@ -7761,8 +8441,16 @@
           <t>泓格</t>
         </is>
       </c>
-      <c r="E89" s="4" t="inlineStr"/>
-      <c r="F89" s="4" t="inlineStr"/>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>130.00</t>
+        </is>
+      </c>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t>-8.5</t>
+        </is>
+      </c>
       <c r="G89" s="4" t="n">
         <v>121</v>
       </c>
@@ -7789,8 +8477,16 @@
           <t>達航科技</t>
         </is>
       </c>
-      <c r="E90" s="4" t="inlineStr"/>
-      <c r="F90" s="4" t="inlineStr"/>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>70.00</t>
+        </is>
+      </c>
+      <c r="F90" s="4" t="inlineStr">
+        <is>
+          <t>-6.9</t>
+        </is>
+      </c>
       <c r="G90" s="4" t="n">
         <v>117</v>
       </c>
@@ -7821,8 +8517,16 @@
           <t>千附精密</t>
         </is>
       </c>
-      <c r="E91" s="4" t="inlineStr"/>
-      <c r="F91" s="4" t="inlineStr"/>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>208.50</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>-23.0</t>
+        </is>
+      </c>
       <c r="G91" s="4" t="n">
         <v>117</v>
       </c>
@@ -7849,8 +8553,16 @@
           <t>青雲</t>
         </is>
       </c>
-      <c r="E92" s="4" t="inlineStr"/>
-      <c r="F92" s="4" t="inlineStr"/>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>378.00</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t>-5.0</t>
+        </is>
+      </c>
       <c r="G92" s="4" t="n">
         <v>115</v>
       </c>
@@ -7881,8 +8593,16 @@
           <t>好德</t>
         </is>
       </c>
-      <c r="E93" s="4" t="inlineStr"/>
-      <c r="F93" s="4" t="inlineStr"/>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>33.35</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>-2.35</t>
+        </is>
+      </c>
       <c r="G93" s="4" t="n">
         <v>114</v>
       </c>
@@ -7913,8 +8633,16 @@
           <t>點序</t>
         </is>
       </c>
-      <c r="E94" s="4" t="inlineStr"/>
-      <c r="F94" s="4" t="inlineStr"/>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>65.50</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t>-3.6</t>
+        </is>
+      </c>
       <c r="G94" s="4" t="n">
         <v>114</v>
       </c>
@@ -7941,8 +8669,16 @@
           <t>倉和</t>
         </is>
       </c>
-      <c r="E95" s="4" t="inlineStr"/>
-      <c r="F95" s="4" t="inlineStr"/>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>137.00</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>-11.0</t>
+        </is>
+      </c>
       <c r="G95" s="4" t="n">
         <v>111</v>
       </c>
@@ -7969,8 +8705,16 @@
           <t>朋程</t>
         </is>
       </c>
-      <c r="E96" s="4" t="inlineStr"/>
-      <c r="F96" s="4" t="inlineStr"/>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>150.50</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>-14.0</t>
+        </is>
+      </c>
       <c r="G96" s="4" t="n">
         <v>111</v>
       </c>
@@ -7997,8 +8741,16 @@
           <t>錦明</t>
         </is>
       </c>
-      <c r="E97" s="4" t="inlineStr"/>
-      <c r="F97" s="4" t="inlineStr"/>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>45.45</t>
+        </is>
+      </c>
+      <c r="F97" s="4" t="inlineStr">
+        <is>
+          <t>-5.05</t>
+        </is>
+      </c>
       <c r="G97" s="4" t="n">
         <v>110</v>
       </c>
@@ -8029,8 +8781,16 @@
           <t>崇越電</t>
         </is>
       </c>
-      <c r="E98" s="4" t="inlineStr"/>
-      <c r="F98" s="4" t="inlineStr"/>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>75.00</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>-4.5</t>
+        </is>
+      </c>
       <c r="G98" s="4" t="n">
         <v>100</v>
       </c>
@@ -8061,8 +8821,16 @@
           <t>博大</t>
         </is>
       </c>
-      <c r="E99" s="4" t="inlineStr"/>
-      <c r="F99" s="4" t="inlineStr"/>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>130.50</t>
+        </is>
+      </c>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t>-6.0</t>
+        </is>
+      </c>
       <c r="G99" s="4" t="n">
         <v>100</v>
       </c>
@@ -8089,8 +8857,16 @@
           <t>橘子</t>
         </is>
       </c>
-      <c r="E100" s="4" t="inlineStr"/>
-      <c r="F100" s="4" t="inlineStr"/>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t>43.50</t>
+        </is>
+      </c>
+      <c r="F100" s="4" t="inlineStr">
+        <is>
+          <t>-2.1</t>
+        </is>
+      </c>
       <c r="G100" s="4" t="n">
         <v>98</v>
       </c>
@@ -8117,8 +8893,16 @@
           <t>鈦昇</t>
         </is>
       </c>
-      <c r="E101" s="4" t="inlineStr"/>
-      <c r="F101" s="4" t="inlineStr"/>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t>215.50</t>
+        </is>
+      </c>
+      <c r="F101" s="4" t="inlineStr">
+        <is>
+          <t>-23.5</t>
+        </is>
+      </c>
       <c r="G101" s="4" t="n">
         <v>98</v>
       </c>
@@ -8149,8 +8933,16 @@
           <t>東典光電</t>
         </is>
       </c>
-      <c r="E102" s="4" t="inlineStr"/>
-      <c r="F102" s="4" t="inlineStr"/>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t>71.60</t>
+        </is>
+      </c>
+      <c r="F102" s="4" t="inlineStr">
+        <is>
+          <t>-6.8</t>
+        </is>
+      </c>
       <c r="G102" s="4" t="n">
         <v>93</v>
       </c>
@@ -8177,8 +8969,16 @@
           <t>艾華</t>
         </is>
       </c>
-      <c r="E103" s="4" t="inlineStr"/>
-      <c r="F103" s="4" t="inlineStr"/>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t>76.00</t>
+        </is>
+      </c>
+      <c r="F103" s="4" t="inlineStr">
+        <is>
+          <t>-8.1</t>
+        </is>
+      </c>
       <c r="G103" s="4" t="n">
         <v>90</v>
       </c>
@@ -8309,8 +9109,16 @@
           <t>鈺創</t>
         </is>
       </c>
-      <c r="E109" s="4" t="inlineStr"/>
-      <c r="F109" s="4" t="inlineStr"/>
+      <c r="E109" s="4" t="inlineStr">
+        <is>
+          <t>88.00</t>
+        </is>
+      </c>
+      <c r="F109" s="4" t="inlineStr">
+        <is>
+          <t>-9.7</t>
+        </is>
+      </c>
       <c r="G109" s="4" t="n">
         <v>-6455</v>
       </c>
@@ -8337,8 +9145,16 @@
           <t>世界</t>
         </is>
       </c>
-      <c r="E110" s="4" t="inlineStr"/>
-      <c r="F110" s="4" t="inlineStr"/>
+      <c r="E110" s="4" t="inlineStr">
+        <is>
+          <t>169.00</t>
+        </is>
+      </c>
+      <c r="F110" s="4" t="inlineStr">
+        <is>
+          <t>-18.5</t>
+        </is>
+      </c>
       <c r="G110" s="4" t="n">
         <v>-5989</v>
       </c>
@@ -8365,8 +9181,16 @@
           <t>欣銓</t>
         </is>
       </c>
-      <c r="E111" s="4" t="inlineStr"/>
-      <c r="F111" s="4" t="inlineStr"/>
+      <c r="E111" s="4" t="inlineStr">
+        <is>
+          <t>214.00</t>
+        </is>
+      </c>
+      <c r="F111" s="4" t="inlineStr">
+        <is>
+          <t>-23.5</t>
+        </is>
+      </c>
       <c r="G111" s="4" t="n">
         <v>-3336</v>
       </c>
@@ -8401,8 +9225,16 @@
           <t>正德</t>
         </is>
       </c>
-      <c r="E112" s="4" t="inlineStr"/>
-      <c r="F112" s="4" t="inlineStr"/>
+      <c r="E112" s="4" t="inlineStr">
+        <is>
+          <t>16.80</t>
+        </is>
+      </c>
+      <c r="F112" s="4" t="inlineStr">
+        <is>
+          <t>-0.7</t>
+        </is>
+      </c>
       <c r="G112" s="4" t="n">
         <v>-2685</v>
       </c>
@@ -8441,8 +9273,16 @@
           <t>健喬</t>
         </is>
       </c>
-      <c r="E113" s="4" t="inlineStr"/>
-      <c r="F113" s="4" t="inlineStr"/>
+      <c r="E113" s="4" t="inlineStr">
+        <is>
+          <t>29.60</t>
+        </is>
+      </c>
+      <c r="F113" s="4" t="inlineStr">
+        <is>
+          <t>nannan</t>
+        </is>
+      </c>
       <c r="G113" s="4" t="n">
         <v>-2078</v>
       </c>
@@ -8481,8 +9321,16 @@
           <t>均豪</t>
         </is>
       </c>
-      <c r="E114" s="4" t="inlineStr"/>
-      <c r="F114" s="4" t="inlineStr"/>
+      <c r="E114" s="4" t="inlineStr">
+        <is>
+          <t>97.70</t>
+        </is>
+      </c>
+      <c r="F114" s="4" t="inlineStr">
+        <is>
+          <t>-10.8</t>
+        </is>
+      </c>
       <c r="G114" s="4" t="n">
         <v>-2022</v>
       </c>
@@ -8517,8 +9365,16 @@
           <t>家登</t>
         </is>
       </c>
-      <c r="E115" s="4" t="inlineStr"/>
-      <c r="F115" s="4" t="inlineStr"/>
+      <c r="E115" s="4" t="inlineStr">
+        <is>
+          <t>464.50</t>
+        </is>
+      </c>
+      <c r="F115" s="4" t="inlineStr">
+        <is>
+          <t>-51.5</t>
+        </is>
+      </c>
       <c r="G115" s="4" t="n">
         <v>-1768</v>
       </c>
@@ -8553,8 +9409,16 @@
           <t>原相</t>
         </is>
       </c>
-      <c r="E116" s="4" t="inlineStr"/>
-      <c r="F116" s="4" t="inlineStr"/>
+      <c r="E116" s="4" t="inlineStr">
+        <is>
+          <t>178.00</t>
+        </is>
+      </c>
+      <c r="F116" s="4" t="inlineStr">
+        <is>
+          <t>-12.0</t>
+        </is>
+      </c>
       <c r="G116" s="4" t="n">
         <v>-1379</v>
       </c>
@@ -8585,8 +9449,16 @@
           <t>順達</t>
         </is>
       </c>
-      <c r="E117" s="4" t="inlineStr"/>
-      <c r="F117" s="4" t="inlineStr"/>
+      <c r="E117" s="4" t="inlineStr">
+        <is>
+          <t>385.50</t>
+        </is>
+      </c>
+      <c r="F117" s="4" t="inlineStr">
+        <is>
+          <t>-41.0</t>
+        </is>
+      </c>
       <c r="G117" s="4" t="n">
         <v>-1200</v>
       </c>
@@ -8617,8 +9489,16 @@
           <t>合一</t>
         </is>
       </c>
-      <c r="E118" s="4" t="inlineStr"/>
-      <c r="F118" s="4" t="inlineStr"/>
+      <c r="E118" s="4" t="inlineStr">
+        <is>
+          <t>48.60</t>
+        </is>
+      </c>
+      <c r="F118" s="4" t="inlineStr">
+        <is>
+          <t>-1.7</t>
+        </is>
+      </c>
       <c r="G118" s="4" t="n">
         <v>-1078</v>
       </c>
@@ -8649,8 +9529,16 @@
           <t>湧德</t>
         </is>
       </c>
-      <c r="E119" s="4" t="inlineStr"/>
-      <c r="F119" s="4" t="inlineStr"/>
+      <c r="E119" s="4" t="inlineStr">
+        <is>
+          <t>106.00</t>
+        </is>
+      </c>
+      <c r="F119" s="4" t="inlineStr">
+        <is>
+          <t>-8.5</t>
+        </is>
+      </c>
       <c r="G119" s="4" t="n">
         <v>-1055</v>
       </c>
@@ -8681,8 +9569,16 @@
           <t>福邦證</t>
         </is>
       </c>
-      <c r="E120" s="4" t="inlineStr"/>
-      <c r="F120" s="4" t="inlineStr"/>
+      <c r="E120" s="4" t="inlineStr">
+        <is>
+          <t>14.10</t>
+        </is>
+      </c>
+      <c r="F120" s="4" t="inlineStr">
+        <is>
+          <t>-0.6</t>
+        </is>
+      </c>
       <c r="G120" s="4" t="n">
         <v>-1019</v>
       </c>
@@ -8713,8 +9609,16 @@
           <t>創惟</t>
         </is>
       </c>
-      <c r="E121" s="4" t="inlineStr"/>
-      <c r="F121" s="4" t="inlineStr"/>
+      <c r="E121" s="4" t="inlineStr">
+        <is>
+          <t>90.00</t>
+        </is>
+      </c>
+      <c r="F121" s="4" t="inlineStr">
+        <is>
+          <t>-7.2</t>
+        </is>
+      </c>
       <c r="G121" s="4" t="n">
         <v>-991</v>
       </c>
@@ -8745,8 +9649,16 @@
           <t>聚和</t>
         </is>
       </c>
-      <c r="E122" s="4" t="inlineStr"/>
-      <c r="F122" s="4" t="inlineStr"/>
+      <c r="E122" s="4" t="inlineStr">
+        <is>
+          <t>48.15</t>
+        </is>
+      </c>
+      <c r="F122" s="4" t="inlineStr">
+        <is>
+          <t>-2.15</t>
+        </is>
+      </c>
       <c r="G122" s="4" t="n">
         <v>-918</v>
       </c>
@@ -8781,8 +9693,16 @@
           <t>伍豐</t>
         </is>
       </c>
-      <c r="E123" s="4" t="inlineStr"/>
-      <c r="F123" s="4" t="inlineStr"/>
+      <c r="E123" s="4" t="inlineStr">
+        <is>
+          <t>22.80</t>
+        </is>
+      </c>
+      <c r="F123" s="4" t="inlineStr">
+        <is>
+          <t>-1.25</t>
+        </is>
+      </c>
       <c r="G123" s="4" t="n">
         <v>-915</v>
       </c>
@@ -8813,8 +9733,16 @@
           <t>立敦</t>
         </is>
       </c>
-      <c r="E124" s="4" t="inlineStr"/>
-      <c r="F124" s="4" t="inlineStr"/>
+      <c r="E124" s="4" t="inlineStr">
+        <is>
+          <t>99.00</t>
+        </is>
+      </c>
+      <c r="F124" s="4" t="inlineStr">
+        <is>
+          <t>-11.0</t>
+        </is>
+      </c>
       <c r="G124" s="4" t="n">
         <v>-865</v>
       </c>
@@ -8841,8 +9769,16 @@
           <t>宏遠證</t>
         </is>
       </c>
-      <c r="E125" s="4" t="inlineStr"/>
-      <c r="F125" s="4" t="inlineStr"/>
+      <c r="E125" s="4" t="inlineStr">
+        <is>
+          <t>16.50</t>
+        </is>
+      </c>
+      <c r="F125" s="4" t="inlineStr">
+        <is>
+          <t>-0.8</t>
+        </is>
+      </c>
       <c r="G125" s="4" t="n">
         <v>-769</v>
       </c>
@@ -8873,8 +9809,16 @@
           <t>華容</t>
         </is>
       </c>
-      <c r="E126" s="4" t="inlineStr"/>
-      <c r="F126" s="4" t="inlineStr"/>
+      <c r="E126" s="4" t="inlineStr">
+        <is>
+          <t>60.30</t>
+        </is>
+      </c>
+      <c r="F126" s="4" t="inlineStr">
+        <is>
+          <t>-6.7</t>
+        </is>
+      </c>
       <c r="G126" s="4" t="n">
         <v>-753</v>
       </c>
@@ -8901,8 +9845,16 @@
           <t>元大期</t>
         </is>
       </c>
-      <c r="E127" s="4" t="inlineStr"/>
-      <c r="F127" s="4" t="inlineStr"/>
+      <c r="E127" s="4" t="inlineStr">
+        <is>
+          <t>87.80</t>
+        </is>
+      </c>
+      <c r="F127" s="4" t="inlineStr">
+        <is>
+          <t>nannan</t>
+        </is>
+      </c>
       <c r="G127" s="4" t="n">
         <v>-744</v>
       </c>
@@ -8941,8 +9893,16 @@
           <t>榮剛</t>
         </is>
       </c>
-      <c r="E128" s="4" t="inlineStr"/>
-      <c r="F128" s="4" t="inlineStr"/>
+      <c r="E128" s="4" t="inlineStr">
+        <is>
+          <t>33.50</t>
+        </is>
+      </c>
+      <c r="F128" s="4" t="inlineStr">
+        <is>
+          <t>-1.45</t>
+        </is>
+      </c>
       <c r="G128" s="4" t="n">
         <v>-743</v>
       </c>
@@ -8973,8 +9933,16 @@
           <t>陽程</t>
         </is>
       </c>
-      <c r="E129" s="4" t="inlineStr"/>
-      <c r="F129" s="4" t="inlineStr"/>
+      <c r="E129" s="4" t="inlineStr">
+        <is>
+          <t>117.00</t>
+        </is>
+      </c>
+      <c r="F129" s="4" t="inlineStr">
+        <is>
+          <t>-12.5</t>
+        </is>
+      </c>
       <c r="G129" s="4" t="n">
         <v>-732</v>
       </c>
@@ -9001,8 +9969,16 @@
           <t>致和證</t>
         </is>
       </c>
-      <c r="E130" s="4" t="inlineStr"/>
-      <c r="F130" s="4" t="inlineStr"/>
+      <c r="E130" s="4" t="inlineStr">
+        <is>
+          <t>33.20</t>
+        </is>
+      </c>
+      <c r="F130" s="4" t="inlineStr">
+        <is>
+          <t>-2.85</t>
+        </is>
+      </c>
       <c r="G130" s="4" t="n">
         <v>-716</v>
       </c>
@@ -9029,8 +10005,16 @@
           <t>東浦</t>
         </is>
       </c>
-      <c r="E131" s="4" t="inlineStr"/>
-      <c r="F131" s="4" t="inlineStr"/>
+      <c r="E131" s="4" t="inlineStr">
+        <is>
+          <t>62.60</t>
+        </is>
+      </c>
+      <c r="F131" s="4" t="inlineStr">
+        <is>
+          <t>-5.4</t>
+        </is>
+      </c>
       <c r="G131" s="4" t="n">
         <v>-712</v>
       </c>
@@ -9057,8 +10041,16 @@
           <t>能率</t>
         </is>
       </c>
-      <c r="E132" s="4" t="inlineStr"/>
-      <c r="F132" s="4" t="inlineStr"/>
+      <c r="E132" s="4" t="inlineStr">
+        <is>
+          <t>42.60</t>
+        </is>
+      </c>
+      <c r="F132" s="4" t="inlineStr">
+        <is>
+          <t>-1.95</t>
+        </is>
+      </c>
       <c r="G132" s="4" t="n">
         <v>-691</v>
       </c>
@@ -9089,8 +10081,16 @@
           <t>威剛</t>
         </is>
       </c>
-      <c r="E133" s="4" t="inlineStr"/>
-      <c r="F133" s="4" t="inlineStr"/>
+      <c r="E133" s="4" t="inlineStr">
+        <is>
+          <t>366.50</t>
+        </is>
+      </c>
+      <c r="F133" s="4" t="inlineStr">
+        <is>
+          <t>-34.0</t>
+        </is>
+      </c>
       <c r="G133" s="4" t="n">
         <v>-590</v>
       </c>
@@ -9117,8 +10117,16 @@
           <t>典範</t>
         </is>
       </c>
-      <c r="E134" s="4" t="inlineStr"/>
-      <c r="F134" s="4" t="inlineStr"/>
+      <c r="E134" s="4" t="inlineStr">
+        <is>
+          <t>16.95</t>
+        </is>
+      </c>
+      <c r="F134" s="4" t="inlineStr">
+        <is>
+          <t>-0.9</t>
+        </is>
+      </c>
       <c r="G134" s="4" t="n">
         <v>-570</v>
       </c>
@@ -9149,8 +10157,16 @@
           <t>萬潤</t>
         </is>
       </c>
-      <c r="E135" s="4" t="inlineStr"/>
-      <c r="F135" s="4" t="inlineStr"/>
+      <c r="E135" s="4" t="inlineStr">
+        <is>
+          <t>975.00</t>
+        </is>
+      </c>
+      <c r="F135" s="4" t="inlineStr">
+        <is>
+          <t>-100.0</t>
+        </is>
+      </c>
       <c r="G135" s="4" t="n">
         <v>-565</v>
       </c>
@@ -9177,8 +10193,16 @@
           <t>松普</t>
         </is>
       </c>
-      <c r="E136" s="4" t="inlineStr"/>
-      <c r="F136" s="4" t="inlineStr"/>
+      <c r="E136" s="4" t="inlineStr">
+        <is>
+          <t>16.05</t>
+        </is>
+      </c>
+      <c r="F136" s="4" t="inlineStr">
+        <is>
+          <t>-0.35</t>
+        </is>
+      </c>
       <c r="G136" s="4" t="n">
         <v>-540</v>
       </c>
@@ -9205,8 +10229,16 @@
           <t>系統電</t>
         </is>
       </c>
-      <c r="E137" s="4" t="inlineStr"/>
-      <c r="F137" s="4" t="inlineStr"/>
+      <c r="E137" s="4" t="inlineStr">
+        <is>
+          <t>53.30</t>
+        </is>
+      </c>
+      <c r="F137" s="4" t="inlineStr">
+        <is>
+          <t>-4.7</t>
+        </is>
+      </c>
       <c r="G137" s="4" t="n">
         <v>-538</v>
       </c>
@@ -9237,8 +10269,16 @@
           <t>岱稜</t>
         </is>
       </c>
-      <c r="E138" s="4" t="inlineStr"/>
-      <c r="F138" s="4" t="inlineStr"/>
+      <c r="E138" s="4" t="inlineStr">
+        <is>
+          <t>53.80</t>
+        </is>
+      </c>
+      <c r="F138" s="4" t="inlineStr">
+        <is>
+          <t>-3.6</t>
+        </is>
+      </c>
       <c r="G138" s="4" t="n">
         <v>-537</v>
       </c>
@@ -9265,8 +10305,16 @@
           <t>茂迪</t>
         </is>
       </c>
-      <c r="E139" s="4" t="inlineStr"/>
-      <c r="F139" s="4" t="inlineStr"/>
+      <c r="E139" s="4" t="inlineStr">
+        <is>
+          <t>25.95</t>
+        </is>
+      </c>
+      <c r="F139" s="4" t="inlineStr">
+        <is>
+          <t>-0.55</t>
+        </is>
+      </c>
       <c r="G139" s="4" t="n">
         <v>-534</v>
       </c>
@@ -9297,8 +10345,16 @@
           <t>同亨</t>
         </is>
       </c>
-      <c r="E140" s="4" t="inlineStr"/>
-      <c r="F140" s="4" t="inlineStr"/>
+      <c r="E140" s="4" t="inlineStr">
+        <is>
+          <t>28.40</t>
+        </is>
+      </c>
+      <c r="F140" s="4" t="inlineStr">
+        <is>
+          <t>-2.05</t>
+        </is>
+      </c>
       <c r="G140" s="4" t="n">
         <v>-514</v>
       </c>
@@ -9333,8 +10389,16 @@
           <t>僑威</t>
         </is>
       </c>
-      <c r="E141" s="4" t="inlineStr"/>
-      <c r="F141" s="4" t="inlineStr"/>
+      <c r="E141" s="4" t="inlineStr">
+        <is>
+          <t>51.90</t>
+        </is>
+      </c>
+      <c r="F141" s="4" t="inlineStr">
+        <is>
+          <t>-1.6</t>
+        </is>
+      </c>
       <c r="G141" s="4" t="n">
         <v>-485</v>
       </c>
@@ -9365,8 +10429,16 @@
           <t>艾訊</t>
         </is>
       </c>
-      <c r="E142" s="4" t="inlineStr"/>
-      <c r="F142" s="4" t="inlineStr"/>
+      <c r="E142" s="4" t="inlineStr">
+        <is>
+          <t>129.00</t>
+        </is>
+      </c>
+      <c r="F142" s="4" t="inlineStr">
+        <is>
+          <t>-9.0</t>
+        </is>
+      </c>
       <c r="G142" s="4" t="n">
         <v>-468</v>
       </c>
@@ -9393,8 +10465,16 @@
           <t>信音</t>
         </is>
       </c>
-      <c r="E143" s="4" t="inlineStr"/>
-      <c r="F143" s="4" t="inlineStr"/>
+      <c r="E143" s="4" t="inlineStr">
+        <is>
+          <t>30.65</t>
+        </is>
+      </c>
+      <c r="F143" s="4" t="inlineStr">
+        <is>
+          <t>-1.8</t>
+        </is>
+      </c>
       <c r="G143" s="4" t="n">
         <v>-463</v>
       </c>
@@ -9425,8 +10505,16 @@
           <t>金益鼎</t>
         </is>
       </c>
-      <c r="E144" s="4" t="inlineStr"/>
-      <c r="F144" s="4" t="inlineStr"/>
+      <c r="E144" s="4" t="inlineStr">
+        <is>
+          <t>94.20</t>
+        </is>
+      </c>
+      <c r="F144" s="4" t="inlineStr">
+        <is>
+          <t>nannan</t>
+        </is>
+      </c>
       <c r="G144" s="4" t="n">
         <v>-449</v>
       </c>
@@ -9457,8 +10545,16 @@
           <t>廣積</t>
         </is>
       </c>
-      <c r="E145" s="4" t="inlineStr"/>
-      <c r="F145" s="4" t="inlineStr"/>
+      <c r="E145" s="4" t="inlineStr">
+        <is>
+          <t>57.20</t>
+        </is>
+      </c>
+      <c r="F145" s="4" t="inlineStr">
+        <is>
+          <t>-3.9</t>
+        </is>
+      </c>
       <c r="G145" s="4" t="n">
         <v>-445</v>
       </c>
@@ -9485,8 +10581,16 @@
           <t>普誠</t>
         </is>
       </c>
-      <c r="E146" s="4" t="inlineStr"/>
-      <c r="F146" s="4" t="inlineStr"/>
+      <c r="E146" s="4" t="inlineStr">
+        <is>
+          <t>15.35</t>
+        </is>
+      </c>
+      <c r="F146" s="4" t="inlineStr">
+        <is>
+          <t>-1.3</t>
+        </is>
+      </c>
       <c r="G146" s="4" t="n">
         <v>-439</v>
       </c>
@@ -9517,8 +10621,16 @@
           <t>廣明</t>
         </is>
       </c>
-      <c r="E147" s="4" t="inlineStr"/>
-      <c r="F147" s="4" t="inlineStr"/>
+      <c r="E147" s="4" t="inlineStr">
+        <is>
+          <t>69.80</t>
+        </is>
+      </c>
+      <c r="F147" s="4" t="inlineStr">
+        <is>
+          <t>-3.9</t>
+        </is>
+      </c>
       <c r="G147" s="4" t="n">
         <v>-428</v>
       </c>
@@ -9545,8 +10657,16 @@
           <t>協易機</t>
         </is>
       </c>
-      <c r="E148" s="4" t="inlineStr"/>
-      <c r="F148" s="4" t="inlineStr"/>
+      <c r="E148" s="4" t="inlineStr">
+        <is>
+          <t>26.00</t>
+        </is>
+      </c>
+      <c r="F148" s="4" t="inlineStr">
+        <is>
+          <t>-1.8</t>
+        </is>
+      </c>
       <c r="G148" s="4" t="n">
         <v>-427</v>
       </c>
@@ -9577,8 +10697,16 @@
           <t>鑫聯大投控</t>
         </is>
       </c>
-      <c r="E149" s="4" t="inlineStr"/>
-      <c r="F149" s="4" t="inlineStr"/>
+      <c r="E149" s="4" t="inlineStr">
+        <is>
+          <t>74.00</t>
+        </is>
+      </c>
+      <c r="F149" s="4" t="inlineStr">
+        <is>
+          <t>-4.0</t>
+        </is>
+      </c>
       <c r="G149" s="4" t="n">
         <v>-418</v>
       </c>
@@ -9609,8 +10737,16 @@
           <t>立端</t>
         </is>
       </c>
-      <c r="E150" s="4" t="inlineStr"/>
-      <c r="F150" s="4" t="inlineStr"/>
+      <c r="E150" s="4" t="inlineStr">
+        <is>
+          <t>75.90</t>
+        </is>
+      </c>
+      <c r="F150" s="4" t="inlineStr">
+        <is>
+          <t>-4.7</t>
+        </is>
+      </c>
       <c r="G150" s="4" t="n">
         <v>-408</v>
       </c>
@@ -9637,8 +10773,16 @@
           <t>松瑞藥</t>
         </is>
       </c>
-      <c r="E151" s="4" t="inlineStr"/>
-      <c r="F151" s="4" t="inlineStr"/>
+      <c r="E151" s="4" t="inlineStr">
+        <is>
+          <t>20.65</t>
+        </is>
+      </c>
+      <c r="F151" s="4" t="inlineStr">
+        <is>
+          <t>-0.9</t>
+        </is>
+      </c>
       <c r="G151" s="4" t="n">
         <v>-403</v>
       </c>
@@ -9665,8 +10809,16 @@
           <t>百徽</t>
         </is>
       </c>
-      <c r="E152" s="4" t="inlineStr"/>
-      <c r="F152" s="4" t="inlineStr"/>
+      <c r="E152" s="4" t="inlineStr">
+        <is>
+          <t>33.20</t>
+        </is>
+      </c>
+      <c r="F152" s="4" t="inlineStr">
+        <is>
+          <t>-3.65</t>
+        </is>
+      </c>
       <c r="G152" s="4" t="n">
         <v>-396</v>
       </c>
@@ -9693,8 +10845,16 @@
           <t>宣德</t>
         </is>
       </c>
-      <c r="E153" s="4" t="inlineStr"/>
-      <c r="F153" s="4" t="inlineStr"/>
+      <c r="E153" s="4" t="inlineStr">
+        <is>
+          <t>29.65</t>
+        </is>
+      </c>
+      <c r="F153" s="4" t="inlineStr">
+        <is>
+          <t>-1.75</t>
+        </is>
+      </c>
       <c r="G153" s="4" t="n">
         <v>-392</v>
       </c>
@@ -9725,8 +10885,16 @@
           <t>建舜電</t>
         </is>
       </c>
-      <c r="E154" s="4" t="inlineStr"/>
-      <c r="F154" s="4" t="inlineStr"/>
+      <c r="E154" s="4" t="inlineStr">
+        <is>
+          <t>12.15</t>
+        </is>
+      </c>
+      <c r="F154" s="4" t="inlineStr">
+        <is>
+          <t>-0.75</t>
+        </is>
+      </c>
       <c r="G154" s="4" t="n">
         <v>-389</v>
       </c>
@@ -9757,8 +10925,16 @@
           <t>中天</t>
         </is>
       </c>
-      <c r="E155" s="4" t="inlineStr"/>
-      <c r="F155" s="4" t="inlineStr"/>
+      <c r="E155" s="4" t="inlineStr">
+        <is>
+          <t>15.45</t>
+        </is>
+      </c>
+      <c r="F155" s="4" t="inlineStr">
+        <is>
+          <t>-0.4</t>
+        </is>
+      </c>
       <c r="G155" s="4" t="n">
         <v>-371</v>
       </c>
@@ -9789,8 +10965,16 @@
           <t>亞通</t>
         </is>
       </c>
-      <c r="E156" s="4" t="inlineStr"/>
-      <c r="F156" s="4" t="inlineStr"/>
+      <c r="E156" s="4" t="inlineStr">
+        <is>
+          <t>24.80</t>
+        </is>
+      </c>
+      <c r="F156" s="4" t="inlineStr">
+        <is>
+          <t>-2.2</t>
+        </is>
+      </c>
       <c r="G156" s="4" t="n">
         <v>-358</v>
       </c>
@@ -9821,8 +11005,16 @@
           <t>世禾</t>
         </is>
       </c>
-      <c r="E157" s="4" t="inlineStr"/>
-      <c r="F157" s="4" t="inlineStr"/>
+      <c r="E157" s="4" t="inlineStr">
+        <is>
+          <t>192.50</t>
+        </is>
+      </c>
+      <c r="F157" s="4" t="inlineStr">
+        <is>
+          <t>-20.5</t>
+        </is>
+      </c>
       <c r="G157" s="4" t="n">
         <v>-356</v>
       </c>
@@ -9849,8 +11041,16 @@
           <t>久正</t>
         </is>
       </c>
-      <c r="E158" s="4" t="inlineStr"/>
-      <c r="F158" s="4" t="inlineStr"/>
+      <c r="E158" s="4" t="inlineStr">
+        <is>
+          <t>10.75</t>
+        </is>
+      </c>
+      <c r="F158" s="4" t="inlineStr">
+        <is>
+          <t>-0.7</t>
+        </is>
+      </c>
       <c r="G158" s="4" t="n">
         <v>-338</v>
       </c>

--- a/StockInfo/otc_analysis_result.xlsx
+++ b/StockInfo/otc_analysis_result.xlsx
@@ -26320,16 +26320,8 @@
           <t>穩懋</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>339.50</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>+26.0</t>
-        </is>
-      </c>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr"/>
       <c r="G4" s="4" t="n">
         <v>1499</v>
       </c>
@@ -26353,16 +26345,8 @@
           <t>元太</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>193.00</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>+17.5</t>
-        </is>
-      </c>
+      <c r="E5" s="4" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr"/>
       <c r="G5" s="4" t="n">
         <v>1188</v>
       </c>
@@ -26386,16 +26370,8 @@
           <t>晟田</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>75.70</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>+6.8</t>
-        </is>
-      </c>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr"/>
       <c r="G6" s="4" t="n">
         <v>1148</v>
       </c>
@@ -26419,16 +26395,8 @@
           <t>中光電</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>89.50</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>+5.7</t>
-        </is>
-      </c>
+      <c r="E7" s="4" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr"/>
       <c r="G7" s="4" t="n">
         <v>940</v>
       </c>
@@ -26452,16 +26420,8 @@
           <t>安勤</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>148.50</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>+13.5</t>
-        </is>
-      </c>
+      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr"/>
       <c r="G8" s="4" t="n">
         <v>831</v>
       </c>
@@ -26485,16 +26445,8 @@
           <t>世紀*</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>60.80</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>+3.1</t>
-        </is>
-      </c>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr"/>
       <c r="G9" s="4" t="n">
         <v>739</v>
       </c>
@@ -26518,16 +26470,8 @@
           <t>家登</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>481.00</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>+43.5</t>
-        </is>
-      </c>
+      <c r="E10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr"/>
       <c r="G10" s="4" t="n">
         <v>683</v>
       </c>
@@ -26551,16 +26495,8 @@
           <t>廣積</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>60.50</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>+4.9</t>
-        </is>
-      </c>
+      <c r="E11" s="4" t="inlineStr"/>
+      <c r="F11" s="4" t="inlineStr"/>
       <c r="G11" s="4" t="n">
         <v>599</v>
       </c>
@@ -26584,16 +26520,8 @@
           <t>茂迪</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>25.85</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>+0.85</t>
-        </is>
-      </c>
+      <c r="E12" s="4" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr"/>
       <c r="G12" s="4" t="n">
         <v>593</v>
       </c>
@@ -26617,16 +26545,8 @@
           <t>91APP*-KY</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>55.70</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>-0.6</t>
-        </is>
-      </c>
+      <c r="E13" s="4" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr"/>
       <c r="G13" s="4" t="n">
         <v>549</v>
       </c>
@@ -26650,16 +26570,8 @@
           <t>雙鴻</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>926.00</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>+68.0</t>
-        </is>
-      </c>
+      <c r="E14" s="4" t="inlineStr"/>
+      <c r="F14" s="4" t="inlineStr"/>
       <c r="G14" s="4" t="n">
         <v>461</v>
       </c>
@@ -26683,16 +26595,8 @@
           <t>光頡</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>90.90</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>+1.4</t>
-        </is>
-      </c>
+      <c r="E15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr"/>
       <c r="G15" s="4" t="n">
         <v>433</v>
       </c>
@@ -26716,16 +26620,8 @@
           <t>原相</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>193.00</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>+10.5</t>
-        </is>
-      </c>
+      <c r="E16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr"/>
       <c r="G16" s="4" t="n">
         <v>432</v>
       </c>
@@ -26749,16 +26645,8 @@
           <t>正德</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>17.20</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>+0.35</t>
-        </is>
-      </c>
+      <c r="E17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr"/>
       <c r="G17" s="4" t="n">
         <v>426</v>
       </c>
@@ -26782,16 +26670,8 @@
           <t>鈊象</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>718.00</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>+12.0</t>
-        </is>
-      </c>
+      <c r="E18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr"/>
       <c r="G18" s="4" t="n">
         <v>410</v>
       </c>
@@ -26815,16 +26695,8 @@
           <t>擎亞</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>+12.0</t>
-        </is>
-      </c>
+      <c r="E19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr"/>
       <c r="G19" s="4" t="n">
         <v>368</v>
       </c>
@@ -26848,16 +26720,8 @@
           <t>同亨</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>31.65</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>+2.65</t>
-        </is>
-      </c>
+      <c r="E20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr"/>
       <c r="G20" s="4" t="n">
         <v>330</v>
       </c>
@@ -26881,16 +26745,8 @@
           <t>威剛</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>368.50</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>+20.0</t>
-        </is>
-      </c>
+      <c r="E21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr"/>
       <c r="G21" s="4" t="n">
         <v>329</v>
       </c>
@@ -26914,16 +26770,8 @@
           <t>台翰</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>16.65</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>+1.5</t>
-        </is>
-      </c>
+      <c r="E22" s="4" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr"/>
       <c r="G22" s="4" t="n">
         <v>292</v>
       </c>
@@ -26947,16 +26795,8 @@
           <t>立端</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>79.50</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>+3.0</t>
-        </is>
-      </c>
+      <c r="E23" s="4" t="inlineStr"/>
+      <c r="F23" s="4" t="inlineStr"/>
       <c r="G23" s="4" t="n">
         <v>286</v>
       </c>
@@ -26980,16 +26820,8 @@
           <t>欣銓</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>210.00</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>+12.5</t>
-        </is>
-      </c>
+      <c r="E24" s="4" t="inlineStr"/>
+      <c r="F24" s="4" t="inlineStr"/>
       <c r="G24" s="4" t="n">
         <v>266</v>
       </c>
@@ -27013,16 +26845,8 @@
           <t>宇環</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>18.30</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>+1.35</t>
-        </is>
-      </c>
+      <c r="E25" s="4" t="inlineStr"/>
+      <c r="F25" s="4" t="inlineStr"/>
       <c r="G25" s="4" t="n">
         <v>265</v>
       </c>
@@ -27046,16 +26870,8 @@
           <t>鈦昇</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>197.50</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>+3.5</t>
-        </is>
-      </c>
+      <c r="E26" s="4" t="inlineStr"/>
+      <c r="F26" s="4" t="inlineStr"/>
       <c r="G26" s="4" t="n">
         <v>263</v>
       </c>
@@ -27079,16 +26895,8 @@
           <t>廣明</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>71.50</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>+0.9</t>
-        </is>
-      </c>
+      <c r="E27" s="4" t="inlineStr"/>
+      <c r="F27" s="4" t="inlineStr"/>
       <c r="G27" s="4" t="n">
         <v>246</v>
       </c>
@@ -27112,16 +26920,8 @@
           <t>德宏</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>146.50</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
+      <c r="E28" s="4" t="inlineStr"/>
+      <c r="F28" s="4" t="inlineStr"/>
       <c r="G28" s="4" t="n">
         <v>244</v>
       </c>
@@ -27145,16 +26945,8 @@
           <t>僑威</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>53.20</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>+1.7</t>
-        </is>
-      </c>
+      <c r="E29" s="4" t="inlineStr"/>
+      <c r="F29" s="4" t="inlineStr"/>
       <c r="G29" s="4" t="n">
         <v>237</v>
       </c>
@@ -27178,16 +26970,8 @@
           <t>新潤</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>42.75</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>+0.4</t>
-        </is>
-      </c>
+      <c r="E30" s="4" t="inlineStr"/>
+      <c r="F30" s="4" t="inlineStr"/>
       <c r="G30" s="4" t="n">
         <v>236</v>
       </c>
@@ -27211,16 +26995,8 @@
           <t>大國鋼</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>36.65</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
+      <c r="E31" s="4" t="inlineStr"/>
+      <c r="F31" s="4" t="inlineStr"/>
       <c r="G31" s="4" t="n">
         <v>233</v>
       </c>
@@ -27244,16 +27020,8 @@
           <t>大綜</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>228.50</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>+20.5</t>
-        </is>
-      </c>
+      <c r="E32" s="4" t="inlineStr"/>
+      <c r="F32" s="4" t="inlineStr"/>
       <c r="G32" s="4" t="n">
         <v>232</v>
       </c>
@@ -27277,16 +27045,8 @@
           <t>茂訊</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>125.50</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>+5.0</t>
-        </is>
-      </c>
+      <c r="E33" s="4" t="inlineStr"/>
+      <c r="F33" s="4" t="inlineStr"/>
       <c r="G33" s="4" t="n">
         <v>232</v>
       </c>
@@ -27310,16 +27070,8 @@
           <t>創惟</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>92.70</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>+3.2</t>
-        </is>
-      </c>
+      <c r="E34" s="4" t="inlineStr"/>
+      <c r="F34" s="4" t="inlineStr"/>
       <c r="G34" s="4" t="n">
         <v>225</v>
       </c>
@@ -27343,16 +27095,8 @@
           <t>中菲行</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>78.90</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>+1.3</t>
-        </is>
-      </c>
+      <c r="E35" s="4" t="inlineStr"/>
+      <c r="F35" s="4" t="inlineStr"/>
       <c r="G35" s="4" t="n">
         <v>220</v>
       </c>
@@ -27376,16 +27120,8 @@
           <t>富旺</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>13.35</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
+      <c r="E36" s="4" t="inlineStr"/>
+      <c r="F36" s="4" t="inlineStr"/>
       <c r="G36" s="4" t="n">
         <v>220</v>
       </c>
@@ -27409,16 +27145,8 @@
           <t>鑫聯大投控</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>73.10</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>+0.4</t>
-        </is>
-      </c>
+      <c r="E37" s="4" t="inlineStr"/>
+      <c r="F37" s="4" t="inlineStr"/>
       <c r="G37" s="4" t="n">
         <v>213</v>
       </c>
@@ -27442,16 +27170,8 @@
           <t>榮剛</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>33.70</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>+0.9</t>
-        </is>
-      </c>
+      <c r="E38" s="4" t="inlineStr"/>
+      <c r="F38" s="4" t="inlineStr"/>
       <c r="G38" s="4" t="n">
         <v>211</v>
       </c>
@@ -27475,16 +27195,8 @@
           <t>群聯</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>1855.00</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>+120.0</t>
-        </is>
-      </c>
+      <c r="E39" s="4" t="inlineStr"/>
+      <c r="F39" s="4" t="inlineStr"/>
       <c r="G39" s="4" t="n">
         <v>207</v>
       </c>
@@ -27508,16 +27220,8 @@
           <t>信立</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>43.85</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>+1.85</t>
-        </is>
-      </c>
+      <c r="E40" s="4" t="inlineStr"/>
+      <c r="F40" s="4" t="inlineStr"/>
       <c r="G40" s="4" t="n">
         <v>205</v>
       </c>
@@ -27541,16 +27245,8 @@
           <t>福裕</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>21.45</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>+1.95</t>
-        </is>
-      </c>
+      <c r="E41" s="4" t="inlineStr"/>
+      <c r="F41" s="4" t="inlineStr"/>
       <c r="G41" s="4" t="n">
         <v>200</v>
       </c>
@@ -27574,16 +27270,8 @@
           <t>福邦證</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>14.45</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>+0.45</t>
-        </is>
-      </c>
+      <c r="E42" s="4" t="inlineStr"/>
+      <c r="F42" s="4" t="inlineStr"/>
       <c r="G42" s="4" t="n">
         <v>200</v>
       </c>
@@ -27607,16 +27295,8 @@
           <t>艾訊</t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>138.50</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>+12.5</t>
-        </is>
-      </c>
+      <c r="E43" s="4" t="inlineStr"/>
+      <c r="F43" s="4" t="inlineStr"/>
       <c r="G43" s="4" t="n">
         <v>192</v>
       </c>
@@ -27640,16 +27320,8 @@
           <t>波若威</t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>664.00</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>+42.0</t>
-        </is>
-      </c>
+      <c r="E44" s="4" t="inlineStr"/>
+      <c r="F44" s="4" t="inlineStr"/>
       <c r="G44" s="4" t="n">
         <v>171</v>
       </c>
@@ -27673,16 +27345,8 @@
           <t>新普</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>370.50</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>+8.0</t>
-        </is>
-      </c>
+      <c r="E45" s="4" t="inlineStr"/>
+      <c r="F45" s="4" t="inlineStr"/>
       <c r="G45" s="4" t="n">
         <v>170</v>
       </c>
@@ -27706,16 +27370,8 @@
           <t>力麒</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>7.92</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>+0.11</t>
-        </is>
-      </c>
+      <c r="E46" s="4" t="inlineStr"/>
+      <c r="F46" s="4" t="inlineStr"/>
       <c r="G46" s="4" t="n">
         <v>168</v>
       </c>
@@ -27739,16 +27395,8 @@
           <t>磐亞</t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>32.85</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t>-3.6</t>
-        </is>
-      </c>
+      <c r="E47" s="4" t="inlineStr"/>
+      <c r="F47" s="4" t="inlineStr"/>
       <c r="G47" s="4" t="n">
         <v>164</v>
       </c>
@@ -27772,16 +27420,8 @@
           <t>立碁</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>47.00</t>
-        </is>
-      </c>
-      <c r="F48" s="4" t="inlineStr">
-        <is>
-          <t>+2.75</t>
-        </is>
-      </c>
+      <c r="E48" s="4" t="inlineStr"/>
+      <c r="F48" s="4" t="inlineStr"/>
       <c r="G48" s="4" t="n">
         <v>163</v>
       </c>
@@ -27805,16 +27445,8 @@
           <t>網家</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>27.10</t>
-        </is>
-      </c>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>+0.2</t>
-        </is>
-      </c>
+      <c r="E49" s="4" t="inlineStr"/>
+      <c r="F49" s="4" t="inlineStr"/>
       <c r="G49" s="4" t="n">
         <v>150</v>
       </c>
@@ -27838,16 +27470,8 @@
           <t>台星科</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>162.00</t>
-        </is>
-      </c>
-      <c r="F50" s="4" t="inlineStr">
-        <is>
-          <t>+11.5</t>
-        </is>
-      </c>
+      <c r="E50" s="4" t="inlineStr"/>
+      <c r="F50" s="4" t="inlineStr"/>
       <c r="G50" s="4" t="n">
         <v>148</v>
       </c>
@@ -27871,16 +27495,8 @@
           <t>頎邦</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>173.00</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="inlineStr">
-        <is>
-          <t>+9.0</t>
-        </is>
-      </c>
+      <c r="E51" s="4" t="inlineStr"/>
+      <c r="F51" s="4" t="inlineStr"/>
       <c r="G51" s="4" t="n">
         <v>144</v>
       </c>
@@ -27904,16 +27520,8 @@
           <t>禾瑞亞</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>64.10</t>
-        </is>
-      </c>
-      <c r="F52" s="4" t="inlineStr">
-        <is>
-          <t>+3.1</t>
-        </is>
-      </c>
+      <c r="E52" s="4" t="inlineStr"/>
+      <c r="F52" s="4" t="inlineStr"/>
       <c r="G52" s="4" t="n">
         <v>143</v>
       </c>
@@ -27937,16 +27545,8 @@
           <t>立凱-KY</t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>35.40</t>
-        </is>
-      </c>
-      <c r="F53" s="4" t="inlineStr">
-        <is>
-          <t>+3.2</t>
-        </is>
-      </c>
+      <c r="E53" s="4" t="inlineStr"/>
+      <c r="F53" s="4" t="inlineStr"/>
       <c r="G53" s="4" t="n">
         <v>136</v>
       </c>
@@ -27970,16 +27570,8 @@
           <t>松瑞藥</t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>20.90</t>
-        </is>
-      </c>
-      <c r="F54" s="4" t="inlineStr">
-        <is>
-          <t>+0.4</t>
-        </is>
-      </c>
+      <c r="E54" s="4" t="inlineStr"/>
+      <c r="F54" s="4" t="inlineStr"/>
       <c r="G54" s="4" t="n">
         <v>127</v>
       </c>
@@ -28003,16 +27595,8 @@
           <t>新漢</t>
         </is>
       </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>61.30</t>
-        </is>
-      </c>
-      <c r="F55" s="4" t="inlineStr">
-        <is>
-          <t>+2.6</t>
-        </is>
-      </c>
+      <c r="E55" s="4" t="inlineStr"/>
+      <c r="F55" s="4" t="inlineStr"/>
       <c r="G55" s="4" t="n">
         <v>127</v>
       </c>
@@ -28036,16 +27620,8 @@
           <t>寶雅</t>
         </is>
       </c>
-      <c r="E56" s="4" t="inlineStr">
-        <is>
-          <t>633.00</t>
-        </is>
-      </c>
-      <c r="F56" s="4" t="inlineStr">
-        <is>
-          <t>+22.0</t>
-        </is>
-      </c>
+      <c r="E56" s="4" t="inlineStr"/>
+      <c r="F56" s="4" t="inlineStr"/>
       <c r="G56" s="4" t="n">
         <v>124</v>
       </c>
@@ -28069,16 +27645,8 @@
           <t>胡連</t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr">
-        <is>
-          <t>118.00</t>
-        </is>
-      </c>
-      <c r="F57" s="4" t="inlineStr">
-        <is>
-          <t>+4.0</t>
-        </is>
-      </c>
+      <c r="E57" s="4" t="inlineStr"/>
+      <c r="F57" s="4" t="inlineStr"/>
       <c r="G57" s="4" t="n">
         <v>124</v>
       </c>
@@ -28102,16 +27670,8 @@
           <t>磐儀</t>
         </is>
       </c>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t>48.90</t>
-        </is>
-      </c>
-      <c r="F58" s="4" t="inlineStr">
-        <is>
-          <t>+2.9</t>
-        </is>
-      </c>
+      <c r="E58" s="4" t="inlineStr"/>
+      <c r="F58" s="4" t="inlineStr"/>
       <c r="G58" s="4" t="n">
         <v>117</v>
       </c>
@@ -28135,16 +27695,8 @@
           <t>德昌</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>71.60</t>
-        </is>
-      </c>
-      <c r="F59" s="4" t="inlineStr">
-        <is>
-          <t>+2.5</t>
-        </is>
-      </c>
+      <c r="E59" s="4" t="inlineStr"/>
+      <c r="F59" s="4" t="inlineStr"/>
       <c r="G59" s="4" t="n">
         <v>117</v>
       </c>
@@ -28168,16 +27720,8 @@
           <t>大學光</t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>139.00</t>
-        </is>
-      </c>
-      <c r="F60" s="4" t="inlineStr">
-        <is>
-          <t>+3.5</t>
-        </is>
-      </c>
+      <c r="E60" s="4" t="inlineStr"/>
+      <c r="F60" s="4" t="inlineStr"/>
       <c r="G60" s="4" t="n">
         <v>116</v>
       </c>
@@ -28201,16 +27745,8 @@
           <t>緯軟</t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>123.50</t>
-        </is>
-      </c>
-      <c r="F61" s="4" t="inlineStr">
-        <is>
-          <t>+2.0</t>
-        </is>
-      </c>
+      <c r="E61" s="4" t="inlineStr"/>
+      <c r="F61" s="4" t="inlineStr"/>
       <c r="G61" s="4" t="n">
         <v>113</v>
       </c>
@@ -28234,16 +27770,8 @@
           <t>富強鑫</t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr">
-        <is>
-          <t>24.65</t>
-        </is>
-      </c>
-      <c r="F62" s="4" t="inlineStr">
-        <is>
-          <t>+0.55</t>
-        </is>
-      </c>
+      <c r="E62" s="4" t="inlineStr"/>
+      <c r="F62" s="4" t="inlineStr"/>
       <c r="G62" s="4" t="n">
         <v>112</v>
       </c>
@@ -28267,16 +27795,8 @@
           <t>歐買尬</t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>76.10</t>
-        </is>
-      </c>
-      <c r="F63" s="4" t="inlineStr">
-        <is>
-          <t>+4.8</t>
-        </is>
-      </c>
+      <c r="E63" s="4" t="inlineStr"/>
+      <c r="F63" s="4" t="inlineStr"/>
       <c r="G63" s="4" t="n">
         <v>111</v>
       </c>
@@ -28300,16 +27820,8 @@
           <t>優群</t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
-      </c>
-      <c r="F64" s="4" t="inlineStr">
-        <is>
-          <t>+6.0</t>
-        </is>
-      </c>
+      <c r="E64" s="4" t="inlineStr"/>
+      <c r="F64" s="4" t="inlineStr"/>
       <c r="G64" s="4" t="n">
         <v>109</v>
       </c>
@@ -28333,16 +27845,8 @@
           <t>伍豐</t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr">
-        <is>
-          <t>23.55</t>
-        </is>
-      </c>
-      <c r="F65" s="4" t="inlineStr">
-        <is>
-          <t>+0.55</t>
-        </is>
-      </c>
+      <c r="E65" s="4" t="inlineStr"/>
+      <c r="F65" s="4" t="inlineStr"/>
       <c r="G65" s="4" t="n">
         <v>109</v>
       </c>
@@ -28366,16 +27870,8 @@
           <t>崇友</t>
         </is>
       </c>
-      <c r="E66" s="4" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
-      </c>
-      <c r="F66" s="4" t="inlineStr">
-        <is>
-          <t>+2.0</t>
-        </is>
-      </c>
+      <c r="E66" s="4" t="inlineStr"/>
+      <c r="F66" s="4" t="inlineStr"/>
       <c r="G66" s="4" t="n">
         <v>106</v>
       </c>
@@ -28399,16 +27895,8 @@
           <t>萬潤</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>998.00</t>
-        </is>
-      </c>
-      <c r="F67" s="4" t="inlineStr">
-        <is>
-          <t>+63.0</t>
-        </is>
-      </c>
+      <c r="E67" s="4" t="inlineStr"/>
+      <c r="F67" s="4" t="inlineStr"/>
       <c r="G67" s="4" t="n">
         <v>106</v>
       </c>
@@ -28432,16 +27920,8 @@
           <t>華盈</t>
         </is>
       </c>
-      <c r="E68" s="4" t="inlineStr">
-        <is>
-          <t>16.55</t>
-        </is>
-      </c>
-      <c r="F68" s="4" t="inlineStr">
-        <is>
-          <t>+0.15</t>
-        </is>
-      </c>
+      <c r="E68" s="4" t="inlineStr"/>
+      <c r="F68" s="4" t="inlineStr"/>
       <c r="G68" s="4" t="n">
         <v>105</v>
       </c>
@@ -28465,16 +27945,8 @@
           <t>大樹</t>
         </is>
       </c>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>78.50</t>
-        </is>
-      </c>
-      <c r="F69" s="4" t="inlineStr">
-        <is>
-          <t>+1.2</t>
-        </is>
-      </c>
+      <c r="E69" s="4" t="inlineStr"/>
+      <c r="F69" s="4" t="inlineStr"/>
       <c r="G69" s="4" t="n">
         <v>102</v>
       </c>
@@ -28498,16 +27970,8 @@
           <t>匯鑽科</t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr">
-        <is>
-          <t>48.80</t>
-        </is>
-      </c>
-      <c r="F70" s="4" t="inlineStr">
-        <is>
-          <t>+2.5</t>
-        </is>
-      </c>
+      <c r="E70" s="4" t="inlineStr"/>
+      <c r="F70" s="4" t="inlineStr"/>
       <c r="G70" s="4" t="n">
         <v>102</v>
       </c>
@@ -28531,16 +27995,8 @@
           <t>元大期</t>
         </is>
       </c>
-      <c r="E71" s="4" t="inlineStr">
-        <is>
-          <t>86.80</t>
-        </is>
-      </c>
-      <c r="F71" s="4" t="inlineStr">
-        <is>
-          <t>+1.3</t>
-        </is>
-      </c>
+      <c r="E71" s="4" t="inlineStr"/>
+      <c r="F71" s="4" t="inlineStr"/>
       <c r="G71" s="4" t="n">
         <v>98</v>
       </c>
@@ -28564,16 +28020,8 @@
           <t>亞信</t>
         </is>
       </c>
-      <c r="E72" s="4" t="inlineStr">
-        <is>
-          <t>104.50</t>
-        </is>
-      </c>
-      <c r="F72" s="4" t="inlineStr">
-        <is>
-          <t>+5.0</t>
-        </is>
-      </c>
+      <c r="E72" s="4" t="inlineStr"/>
+      <c r="F72" s="4" t="inlineStr"/>
       <c r="G72" s="4" t="n">
         <v>97</v>
       </c>
@@ -28597,16 +28045,8 @@
           <t>中探針</t>
         </is>
       </c>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>169.00</t>
-        </is>
-      </c>
-      <c r="F73" s="4" t="inlineStr">
-        <is>
-          <t>-8.0</t>
-        </is>
-      </c>
+      <c r="E73" s="4" t="inlineStr"/>
+      <c r="F73" s="4" t="inlineStr"/>
       <c r="G73" s="4" t="n">
         <v>91</v>
       </c>
@@ -28630,16 +28070,8 @@
           <t>明安</t>
         </is>
       </c>
-      <c r="E74" s="4" t="inlineStr">
-        <is>
-          <t>56.20</t>
-        </is>
-      </c>
-      <c r="F74" s="4" t="inlineStr">
-        <is>
-          <t>+0.6</t>
-        </is>
-      </c>
+      <c r="E74" s="4" t="inlineStr"/>
+      <c r="F74" s="4" t="inlineStr"/>
       <c r="G74" s="4" t="n">
         <v>91</v>
       </c>
@@ -28663,16 +28095,8 @@
           <t>旭然</t>
         </is>
       </c>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>125.50</t>
-        </is>
-      </c>
-      <c r="F75" s="4" t="inlineStr">
-        <is>
-          <t>+11.0</t>
-        </is>
-      </c>
+      <c r="E75" s="4" t="inlineStr"/>
+      <c r="F75" s="4" t="inlineStr"/>
       <c r="G75" s="4" t="n">
         <v>90</v>
       </c>
@@ -28696,16 +28120,8 @@
           <t>亞昕</t>
         </is>
       </c>
-      <c r="E76" s="4" t="inlineStr">
-        <is>
-          <t>22.00</t>
-        </is>
-      </c>
-      <c r="F76" s="4" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
+      <c r="E76" s="4" t="inlineStr"/>
+      <c r="F76" s="4" t="inlineStr"/>
       <c r="G76" s="4" t="n">
         <v>88</v>
       </c>
@@ -28729,16 +28145,8 @@
           <t>國眾</t>
         </is>
       </c>
-      <c r="E77" s="4" t="inlineStr">
-        <is>
-          <t>36.80</t>
-        </is>
-      </c>
-      <c r="F77" s="4" t="inlineStr">
-        <is>
-          <t>+0.75</t>
-        </is>
-      </c>
+      <c r="E77" s="4" t="inlineStr"/>
+      <c r="F77" s="4" t="inlineStr"/>
       <c r="G77" s="4" t="n">
         <v>88</v>
       </c>
@@ -28762,16 +28170,8 @@
           <t>宸曜</t>
         </is>
       </c>
-      <c r="E78" s="4" t="inlineStr">
-        <is>
-          <t>182.50</t>
-        </is>
-      </c>
-      <c r="F78" s="4" t="inlineStr">
-        <is>
-          <t>+16.5</t>
-        </is>
-      </c>
+      <c r="E78" s="4" t="inlineStr"/>
+      <c r="F78" s="4" t="inlineStr"/>
       <c r="G78" s="4" t="n">
         <v>83</v>
       </c>
@@ -28795,16 +28195,8 @@
           <t>天品</t>
         </is>
       </c>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t>100.50</t>
-        </is>
-      </c>
-      <c r="F79" s="4" t="inlineStr">
-        <is>
-          <t>+4.6</t>
-        </is>
-      </c>
+      <c r="E79" s="4" t="inlineStr"/>
+      <c r="F79" s="4" t="inlineStr"/>
       <c r="G79" s="4" t="n">
         <v>82</v>
       </c>
@@ -28828,16 +28220,8 @@
           <t>順藥</t>
         </is>
       </c>
-      <c r="E80" s="4" t="inlineStr">
-        <is>
-          <t>86.90</t>
-        </is>
-      </c>
-      <c r="F80" s="4" t="inlineStr">
-        <is>
-          <t>-0.3</t>
-        </is>
-      </c>
+      <c r="E80" s="4" t="inlineStr"/>
+      <c r="F80" s="4" t="inlineStr"/>
       <c r="G80" s="4" t="n">
         <v>80</v>
       </c>
@@ -28861,16 +28245,8 @@
           <t>南良</t>
         </is>
       </c>
-      <c r="E81" s="4" t="inlineStr">
-        <is>
-          <t>17.95</t>
-        </is>
-      </c>
-      <c r="F81" s="4" t="inlineStr">
-        <is>
-          <t>-0.8</t>
-        </is>
-      </c>
+      <c r="E81" s="4" t="inlineStr"/>
+      <c r="F81" s="4" t="inlineStr"/>
       <c r="G81" s="4" t="n">
         <v>79</v>
       </c>
@@ -28894,16 +28270,8 @@
           <t>鑫永洋</t>
         </is>
       </c>
-      <c r="E82" s="4" t="inlineStr">
-        <is>
-          <t>16.50</t>
-        </is>
-      </c>
-      <c r="F82" s="4" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
+      <c r="E82" s="4" t="inlineStr"/>
+      <c r="F82" s="4" t="inlineStr"/>
       <c r="G82" s="4" t="n">
         <v>79</v>
       </c>
@@ -28927,16 +28295,8 @@
           <t>龍巖</t>
         </is>
       </c>
-      <c r="E83" s="4" t="inlineStr">
-        <is>
-          <t>48.85</t>
-        </is>
-      </c>
-      <c r="F83" s="4" t="inlineStr">
-        <is>
-          <t>+0.45</t>
-        </is>
-      </c>
+      <c r="E83" s="4" t="inlineStr"/>
+      <c r="F83" s="4" t="inlineStr"/>
       <c r="G83" s="4" t="n">
         <v>78</v>
       </c>
@@ -28960,16 +28320,8 @@
           <t>耕興</t>
         </is>
       </c>
-      <c r="E84" s="4" t="inlineStr">
-        <is>
-          <t>193.00</t>
-        </is>
-      </c>
-      <c r="F84" s="4" t="inlineStr">
-        <is>
-          <t>+4.0</t>
-        </is>
-      </c>
+      <c r="E84" s="4" t="inlineStr"/>
+      <c r="F84" s="4" t="inlineStr"/>
       <c r="G84" s="4" t="n">
         <v>76</v>
       </c>
@@ -28993,16 +28345,8 @@
           <t>點序</t>
         </is>
       </c>
-      <c r="E85" s="4" t="inlineStr">
-        <is>
-          <t>63.00</t>
-        </is>
-      </c>
-      <c r="F85" s="4" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
+      <c r="E85" s="4" t="inlineStr"/>
+      <c r="F85" s="4" t="inlineStr"/>
       <c r="G85" s="4" t="n">
         <v>76</v>
       </c>
@@ -29026,16 +28370,8 @@
           <t>逸達</t>
         </is>
       </c>
-      <c r="E86" s="4" t="inlineStr">
-        <is>
-          <t>82.20</t>
-        </is>
-      </c>
-      <c r="F86" s="4" t="inlineStr">
-        <is>
-          <t>+2.5</t>
-        </is>
-      </c>
+      <c r="E86" s="4" t="inlineStr"/>
+      <c r="F86" s="4" t="inlineStr"/>
       <c r="G86" s="4" t="n">
         <v>76</v>
       </c>
@@ -29059,16 +28395,8 @@
           <t>安國</t>
         </is>
       </c>
-      <c r="E87" s="4" t="inlineStr">
-        <is>
-          <t>95.10</t>
-        </is>
-      </c>
-      <c r="F87" s="4" t="inlineStr">
-        <is>
-          <t>+6.4</t>
-        </is>
-      </c>
+      <c r="E87" s="4" t="inlineStr"/>
+      <c r="F87" s="4" t="inlineStr"/>
       <c r="G87" s="4" t="n">
         <v>74</v>
       </c>
@@ -29092,16 +28420,8 @@
           <t>明係</t>
         </is>
       </c>
-      <c r="E88" s="4" t="inlineStr">
-        <is>
-          <t>16.75</t>
-        </is>
-      </c>
-      <c r="F88" s="4" t="inlineStr">
-        <is>
-          <t>+0.65</t>
-        </is>
-      </c>
+      <c r="E88" s="4" t="inlineStr"/>
+      <c r="F88" s="4" t="inlineStr"/>
       <c r="G88" s="4" t="n">
         <v>71</v>
       </c>
@@ -29125,16 +28445,8 @@
           <t>宏捷科</t>
         </is>
       </c>
-      <c r="E89" s="4" t="inlineStr">
-        <is>
-          <t>119.50</t>
-        </is>
-      </c>
-      <c r="F89" s="4" t="inlineStr">
-        <is>
-          <t>+4.5</t>
-        </is>
-      </c>
+      <c r="E89" s="4" t="inlineStr"/>
+      <c r="F89" s="4" t="inlineStr"/>
       <c r="G89" s="4" t="n">
         <v>71</v>
       </c>
@@ -29158,16 +28470,8 @@
           <t>旭源</t>
         </is>
       </c>
-      <c r="E90" s="4" t="inlineStr">
-        <is>
-          <t>15.65</t>
-        </is>
-      </c>
-      <c r="F90" s="4" t="inlineStr">
-        <is>
-          <t>+1.4</t>
-        </is>
-      </c>
+      <c r="E90" s="4" t="inlineStr"/>
+      <c r="F90" s="4" t="inlineStr"/>
       <c r="G90" s="4" t="n">
         <v>71</v>
       </c>
@@ -29191,16 +28495,8 @@
           <t>北基</t>
         </is>
       </c>
-      <c r="E91" s="4" t="inlineStr">
-        <is>
-          <t>20.10</t>
-        </is>
-      </c>
-      <c r="F91" s="4" t="inlineStr">
-        <is>
-          <t>-0.2</t>
-        </is>
-      </c>
+      <c r="E91" s="4" t="inlineStr"/>
+      <c r="F91" s="4" t="inlineStr"/>
       <c r="G91" s="4" t="n">
         <v>69</v>
       </c>
@@ -29224,16 +28520,8 @@
           <t>宇峻</t>
         </is>
       </c>
-      <c r="E92" s="4" t="inlineStr">
-        <is>
-          <t>73.30</t>
-        </is>
-      </c>
-      <c r="F92" s="4" t="inlineStr">
-        <is>
-          <t>+1.9</t>
-        </is>
-      </c>
+      <c r="E92" s="4" t="inlineStr"/>
+      <c r="F92" s="4" t="inlineStr"/>
       <c r="G92" s="4" t="n">
         <v>66</v>
       </c>
@@ -29257,16 +28545,8 @@
           <t>環泰</t>
         </is>
       </c>
-      <c r="E93" s="4" t="inlineStr">
-        <is>
-          <t>20.00</t>
-        </is>
-      </c>
-      <c r="F93" s="4" t="inlineStr">
-        <is>
-          <t>+0.25</t>
-        </is>
-      </c>
+      <c r="E93" s="4" t="inlineStr"/>
+      <c r="F93" s="4" t="inlineStr"/>
       <c r="G93" s="4" t="n">
         <v>66</v>
       </c>
@@ -29290,16 +28570,8 @@
           <t>建舜電</t>
         </is>
       </c>
-      <c r="E94" s="4" t="inlineStr">
-        <is>
-          <t>12.45</t>
-        </is>
-      </c>
-      <c r="F94" s="4" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
+      <c r="E94" s="4" t="inlineStr"/>
+      <c r="F94" s="4" t="inlineStr"/>
       <c r="G94" s="4" t="n">
         <v>65</v>
       </c>
@@ -29323,16 +28595,8 @@
           <t>建錩</t>
         </is>
       </c>
-      <c r="E95" s="4" t="inlineStr">
-        <is>
-          <t>11.05</t>
-        </is>
-      </c>
-      <c r="F95" s="4" t="inlineStr">
-        <is>
-          <t>+0.05</t>
-        </is>
-      </c>
+      <c r="E95" s="4" t="inlineStr"/>
+      <c r="F95" s="4" t="inlineStr"/>
       <c r="G95" s="4" t="n">
         <v>65</v>
       </c>
@@ -29356,16 +28620,8 @@
           <t>精星</t>
         </is>
       </c>
-      <c r="E96" s="4" t="inlineStr">
-        <is>
-          <t>30.60</t>
-        </is>
-      </c>
-      <c r="F96" s="4" t="inlineStr">
-        <is>
-          <t>+0.6</t>
-        </is>
-      </c>
+      <c r="E96" s="4" t="inlineStr"/>
+      <c r="F96" s="4" t="inlineStr"/>
       <c r="G96" s="4" t="n">
         <v>61</v>
       </c>
@@ -29389,16 +28645,8 @@
           <t>昇佳電子</t>
         </is>
       </c>
-      <c r="E97" s="4" t="inlineStr">
-        <is>
-          <t>204.00</t>
-        </is>
-      </c>
-      <c r="F97" s="4" t="inlineStr">
-        <is>
-          <t>+8.5</t>
-        </is>
-      </c>
+      <c r="E97" s="4" t="inlineStr"/>
+      <c r="F97" s="4" t="inlineStr"/>
       <c r="G97" s="4" t="n">
         <v>60</v>
       </c>
@@ -29422,16 +28670,8 @@
           <t>智擎</t>
         </is>
       </c>
-      <c r="E98" s="4" t="inlineStr">
-        <is>
-          <t>68.00</t>
-        </is>
-      </c>
-      <c r="F98" s="4" t="inlineStr">
-        <is>
-          <t>+3.7</t>
-        </is>
-      </c>
+      <c r="E98" s="4" t="inlineStr"/>
+      <c r="F98" s="4" t="inlineStr"/>
       <c r="G98" s="4" t="n">
         <v>59</v>
       </c>
@@ -29455,16 +28695,8 @@
           <t>高鋒</t>
         </is>
       </c>
-      <c r="E99" s="4" t="inlineStr">
-        <is>
-          <t>38.95</t>
-        </is>
-      </c>
-      <c r="F99" s="4" t="inlineStr">
-        <is>
-          <t>+0.85</t>
-        </is>
-      </c>
+      <c r="E99" s="4" t="inlineStr"/>
+      <c r="F99" s="4" t="inlineStr"/>
       <c r="G99" s="4" t="n">
         <v>58</v>
       </c>
@@ -29488,16 +28720,8 @@
           <t>科嶠</t>
         </is>
       </c>
-      <c r="E100" s="4" t="inlineStr">
-        <is>
-          <t>324.50</t>
-        </is>
-      </c>
-      <c r="F100" s="4" t="inlineStr">
-        <is>
-          <t>+29.5</t>
-        </is>
-      </c>
+      <c r="E100" s="4" t="inlineStr"/>
+      <c r="F100" s="4" t="inlineStr"/>
       <c r="G100" s="4" t="n">
         <v>58</v>
       </c>
@@ -29521,16 +28745,8 @@
           <t>亞泰</t>
         </is>
       </c>
-      <c r="E101" s="4" t="inlineStr">
-        <is>
-          <t>68.50</t>
-        </is>
-      </c>
-      <c r="F101" s="4" t="inlineStr">
-        <is>
-          <t>+1.9</t>
-        </is>
-      </c>
+      <c r="E101" s="4" t="inlineStr"/>
+      <c r="F101" s="4" t="inlineStr"/>
       <c r="G101" s="4" t="n">
         <v>56</v>
       </c>
@@ -29554,16 +28770,8 @@
           <t>天方能源</t>
         </is>
       </c>
-      <c r="E102" s="4" t="inlineStr">
-        <is>
-          <t>21.45</t>
-        </is>
-      </c>
-      <c r="F102" s="4" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
+      <c r="E102" s="4" t="inlineStr"/>
+      <c r="F102" s="4" t="inlineStr"/>
       <c r="G102" s="4" t="n">
         <v>54</v>
       </c>
@@ -29587,16 +28795,8 @@
           <t>華電網</t>
         </is>
       </c>
-      <c r="E103" s="4" t="inlineStr">
-        <is>
-          <t>41.00</t>
-        </is>
-      </c>
-      <c r="F103" s="4" t="inlineStr">
-        <is>
-          <t>+1.65</t>
-        </is>
-      </c>
+      <c r="E103" s="4" t="inlineStr"/>
+      <c r="F103" s="4" t="inlineStr"/>
       <c r="G103" s="4" t="n">
         <v>54</v>
       </c>
@@ -29697,16 +28897,8 @@
           <t>合晶</t>
         </is>
       </c>
-      <c r="E109" s="4" t="inlineStr">
-        <is>
-          <t>130.00</t>
-        </is>
-      </c>
-      <c r="F109" s="4" t="inlineStr">
-        <is>
-          <t>-5.0</t>
-        </is>
-      </c>
+      <c r="E109" s="4" t="inlineStr"/>
+      <c r="F109" s="4" t="inlineStr"/>
       <c r="G109" s="4" t="n">
         <v>-4178</v>
       </c>
@@ -29730,16 +28922,8 @@
           <t>鈺創</t>
         </is>
       </c>
-      <c r="E110" s="4" t="inlineStr">
-        <is>
-          <t>88.90</t>
-        </is>
-      </c>
-      <c r="F110" s="4" t="inlineStr">
-        <is>
-          <t>+6.1</t>
-        </is>
-      </c>
+      <c r="E110" s="4" t="inlineStr"/>
+      <c r="F110" s="4" t="inlineStr"/>
       <c r="G110" s="4" t="n">
         <v>-3681</v>
       </c>
@@ -29763,16 +28947,8 @@
           <t>世界</t>
         </is>
       </c>
-      <c r="E111" s="4" t="inlineStr">
-        <is>
-          <t>155.50</t>
-        </is>
-      </c>
-      <c r="F111" s="4" t="inlineStr">
-        <is>
-          <t>+3.0</t>
-        </is>
-      </c>
+      <c r="E111" s="4" t="inlineStr"/>
+      <c r="F111" s="4" t="inlineStr"/>
       <c r="G111" s="4" t="n">
         <v>-3284</v>
       </c>
@@ -29796,16 +28972,8 @@
           <t>金居</t>
         </is>
       </c>
-      <c r="E112" s="4" t="inlineStr">
-        <is>
-          <t>394.50</t>
-        </is>
-      </c>
-      <c r="F112" s="4" t="inlineStr">
-        <is>
-          <t>+23.5</t>
-        </is>
-      </c>
+      <c r="E112" s="4" t="inlineStr"/>
+      <c r="F112" s="4" t="inlineStr"/>
       <c r="G112" s="4" t="n">
         <v>-2358</v>
       </c>
@@ -29829,16 +28997,8 @@
           <t>台半</t>
         </is>
       </c>
-      <c r="E113" s="4" t="inlineStr">
-        <is>
-          <t>89.50</t>
-        </is>
-      </c>
-      <c r="F113" s="4" t="inlineStr">
-        <is>
-          <t>+3.5</t>
-        </is>
-      </c>
+      <c r="E113" s="4" t="inlineStr"/>
+      <c r="F113" s="4" t="inlineStr"/>
       <c r="G113" s="4" t="n">
         <v>-2299</v>
       </c>
@@ -29862,16 +29022,8 @@
           <t>東洋</t>
         </is>
       </c>
-      <c r="E114" s="4" t="inlineStr">
-        <is>
-          <t>79.10</t>
-        </is>
-      </c>
-      <c r="F114" s="4" t="inlineStr">
-        <is>
-          <t>+1.0</t>
-        </is>
-      </c>
+      <c r="E114" s="4" t="inlineStr"/>
+      <c r="F114" s="4" t="inlineStr"/>
       <c r="G114" s="4" t="n">
         <v>-2203</v>
       </c>
@@ -29895,16 +29047,8 @@
           <t>精材</t>
         </is>
       </c>
-      <c r="E115" s="4" t="inlineStr">
-        <is>
-          <t>380.00</t>
-        </is>
-      </c>
-      <c r="F115" s="4" t="inlineStr">
-        <is>
-          <t>+34.5</t>
-        </is>
-      </c>
+      <c r="E115" s="4" t="inlineStr"/>
+      <c r="F115" s="4" t="inlineStr"/>
       <c r="G115" s="4" t="n">
         <v>-2061</v>
       </c>
@@ -29928,16 +29072,8 @@
           <t>漢磊</t>
         </is>
       </c>
-      <c r="E116" s="4" t="inlineStr">
-        <is>
-          <t>65.40</t>
-        </is>
-      </c>
-      <c r="F116" s="4" t="inlineStr">
-        <is>
-          <t>+0.6</t>
-        </is>
-      </c>
+      <c r="E116" s="4" t="inlineStr"/>
+      <c r="F116" s="4" t="inlineStr"/>
       <c r="G116" s="4" t="n">
         <v>-1633</v>
       </c>
@@ -29961,16 +29097,8 @@
           <t>蜜望實</t>
         </is>
       </c>
-      <c r="E117" s="4" t="inlineStr">
-        <is>
-          <t>141.50</t>
-        </is>
-      </c>
-      <c r="F117" s="4" t="inlineStr">
-        <is>
-          <t>+6.0</t>
-        </is>
-      </c>
+      <c r="E117" s="4" t="inlineStr"/>
+      <c r="F117" s="4" t="inlineStr"/>
       <c r="G117" s="4" t="n">
         <v>-1411</v>
       </c>
@@ -29994,16 +29122,8 @@
           <t>中美晶</t>
         </is>
       </c>
-      <c r="E118" s="4" t="inlineStr">
-        <is>
-          <t>220.50</t>
-        </is>
-      </c>
-      <c r="F118" s="4" t="inlineStr">
-        <is>
-          <t>-7.0</t>
-        </is>
-      </c>
+      <c r="E118" s="4" t="inlineStr"/>
+      <c r="F118" s="4" t="inlineStr"/>
       <c r="G118" s="4" t="n">
         <v>-1328</v>
       </c>
@@ -30027,16 +29147,8 @@
           <t>金山電</t>
         </is>
       </c>
-      <c r="E119" s="4" t="inlineStr">
-        <is>
-          <t>120.50</t>
-        </is>
-      </c>
-      <c r="F119" s="4" t="inlineStr">
-        <is>
-          <t>+3.0</t>
-        </is>
-      </c>
+      <c r="E119" s="4" t="inlineStr"/>
+      <c r="F119" s="4" t="inlineStr"/>
       <c r="G119" s="4" t="n">
         <v>-1309</v>
       </c>
@@ -30060,16 +29172,8 @@
           <t>立敦</t>
         </is>
       </c>
-      <c r="E120" s="4" t="inlineStr">
-        <is>
-          <t>87.90</t>
-        </is>
-      </c>
-      <c r="F120" s="4" t="inlineStr">
-        <is>
-          <t>-1.2</t>
-        </is>
-      </c>
+      <c r="E120" s="4" t="inlineStr"/>
+      <c r="F120" s="4" t="inlineStr"/>
       <c r="G120" s="4" t="n">
         <v>-1178</v>
       </c>
@@ -30093,16 +29197,8 @@
           <t>環球晶</t>
         </is>
       </c>
-      <c r="E121" s="4" t="inlineStr">
-        <is>
-          <t>1205.00</t>
-        </is>
-      </c>
-      <c r="F121" s="4" t="inlineStr">
-        <is>
-          <t>-60.0</t>
-        </is>
-      </c>
+      <c r="E121" s="4" t="inlineStr"/>
+      <c r="F121" s="4" t="inlineStr"/>
       <c r="G121" s="4" t="n">
         <v>-1038</v>
       </c>
@@ -30126,16 +29222,8 @@
           <t>富喬</t>
         </is>
       </c>
-      <c r="E122" s="4" t="inlineStr">
-        <is>
-          <t>79.20</t>
-        </is>
-      </c>
-      <c r="F122" s="4" t="inlineStr">
-        <is>
-          <t>+1.9</t>
-        </is>
-      </c>
+      <c r="E122" s="4" t="inlineStr"/>
+      <c r="F122" s="4" t="inlineStr"/>
       <c r="G122" s="4" t="n">
         <v>-1031</v>
       </c>
@@ -30159,16 +29247,8 @@
           <t>順達</t>
         </is>
       </c>
-      <c r="E123" s="4" t="inlineStr">
-        <is>
-          <t>380.00</t>
-        </is>
-      </c>
-      <c r="F123" s="4" t="inlineStr">
-        <is>
-          <t>+26.0</t>
-        </is>
-      </c>
+      <c r="E123" s="4" t="inlineStr"/>
+      <c r="F123" s="4" t="inlineStr"/>
       <c r="G123" s="4" t="n">
         <v>-1010</v>
       </c>
@@ -30192,16 +29272,8 @@
           <t>信昌電</t>
         </is>
       </c>
-      <c r="E124" s="4" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
-      </c>
-      <c r="F124" s="4" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
+      <c r="E124" s="4" t="inlineStr"/>
+      <c r="F124" s="4" t="inlineStr"/>
       <c r="G124" s="4" t="n">
         <v>-896</v>
       </c>
@@ -30225,16 +29297,8 @@
           <t>合一</t>
         </is>
       </c>
-      <c r="E125" s="4" t="inlineStr">
-        <is>
-          <t>47.80</t>
-        </is>
-      </c>
-      <c r="F125" s="4" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
+      <c r="E125" s="4" t="inlineStr"/>
+      <c r="F125" s="4" t="inlineStr"/>
       <c r="G125" s="4" t="n">
         <v>-829</v>
       </c>
@@ -30258,16 +29322,8 @@
           <t>致和證</t>
         </is>
       </c>
-      <c r="E126" s="4" t="inlineStr">
-        <is>
-          <t>32.75</t>
-        </is>
-      </c>
-      <c r="F126" s="4" t="inlineStr">
-        <is>
-          <t>+0.85</t>
-        </is>
-      </c>
+      <c r="E126" s="4" t="inlineStr"/>
+      <c r="F126" s="4" t="inlineStr"/>
       <c r="G126" s="4" t="n">
         <v>-747</v>
       </c>
@@ -30291,16 +29347,8 @@
           <t>九豪</t>
         </is>
       </c>
-      <c r="E127" s="4" t="inlineStr">
-        <is>
-          <t>56.30</t>
-        </is>
-      </c>
-      <c r="F127" s="4" t="inlineStr">
-        <is>
-          <t>+1.2</t>
-        </is>
-      </c>
+      <c r="E127" s="4" t="inlineStr"/>
+      <c r="F127" s="4" t="inlineStr"/>
       <c r="G127" s="4" t="n">
         <v>-736</v>
       </c>
@@ -30324,16 +29372,8 @@
           <t>光洋科</t>
         </is>
       </c>
-      <c r="E128" s="4" t="inlineStr">
-        <is>
-          <t>107.50</t>
-        </is>
-      </c>
-      <c r="F128" s="4" t="inlineStr">
-        <is>
-          <t>+3.0</t>
-        </is>
-      </c>
+      <c r="E128" s="4" t="inlineStr"/>
+      <c r="F128" s="4" t="inlineStr"/>
       <c r="G128" s="4" t="n">
         <v>-720</v>
       </c>
@@ -30357,16 +29397,8 @@
           <t>佳邦</t>
         </is>
       </c>
-      <c r="E129" s="4" t="inlineStr">
-        <is>
-          <t>82.50</t>
-        </is>
-      </c>
-      <c r="F129" s="4" t="inlineStr">
-        <is>
-          <t>+4.5</t>
-        </is>
-      </c>
+      <c r="E129" s="4" t="inlineStr"/>
+      <c r="F129" s="4" t="inlineStr"/>
       <c r="G129" s="4" t="n">
         <v>-700</v>
       </c>
@@ -30390,16 +29422,8 @@
           <t>亞電</t>
         </is>
       </c>
-      <c r="E130" s="4" t="inlineStr">
-        <is>
-          <t>72.80</t>
-        </is>
-      </c>
-      <c r="F130" s="4" t="inlineStr">
-        <is>
-          <t>+6.6</t>
-        </is>
-      </c>
+      <c r="E130" s="4" t="inlineStr"/>
+      <c r="F130" s="4" t="inlineStr"/>
       <c r="G130" s="4" t="n">
         <v>-689</v>
       </c>
@@ -30423,16 +29447,8 @@
           <t>聯一光</t>
         </is>
       </c>
-      <c r="E131" s="4" t="inlineStr">
-        <is>
-          <t>63.70</t>
-        </is>
-      </c>
-      <c r="F131" s="4" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
+      <c r="E131" s="4" t="inlineStr"/>
+      <c r="F131" s="4" t="inlineStr"/>
       <c r="G131" s="4" t="n">
         <v>-654</v>
       </c>
@@ -30456,16 +29472,8 @@
           <t>臺慶科</t>
         </is>
       </c>
-      <c r="E132" s="4" t="inlineStr">
-        <is>
-          <t>219.00</t>
-        </is>
-      </c>
-      <c r="F132" s="4" t="inlineStr">
-        <is>
-          <t>+11.5</t>
-        </is>
-      </c>
+      <c r="E132" s="4" t="inlineStr"/>
+      <c r="F132" s="4" t="inlineStr"/>
       <c r="G132" s="4" t="n">
         <v>-627</v>
       </c>
@@ -30489,16 +29497,8 @@
           <t>雷科</t>
         </is>
       </c>
-      <c r="E133" s="4" t="inlineStr">
-        <is>
-          <t>124.50</t>
-        </is>
-      </c>
-      <c r="F133" s="4" t="inlineStr">
-        <is>
-          <t>+7.0</t>
-        </is>
-      </c>
+      <c r="E133" s="4" t="inlineStr"/>
+      <c r="F133" s="4" t="inlineStr"/>
       <c r="G133" s="4" t="n">
         <v>-622</v>
       </c>
@@ -30522,16 +29522,8 @@
           <t>健喬</t>
         </is>
       </c>
-      <c r="E134" s="4" t="inlineStr">
-        <is>
-          <t>29.70</t>
-        </is>
-      </c>
-      <c r="F134" s="4" t="inlineStr">
-        <is>
-          <t>+0.4</t>
-        </is>
-      </c>
+      <c r="E134" s="4" t="inlineStr"/>
+      <c r="F134" s="4" t="inlineStr"/>
       <c r="G134" s="4" t="n">
         <v>-597</v>
       </c>
@@ -30555,16 +29547,8 @@
           <t>千如</t>
         </is>
       </c>
-      <c r="E135" s="4" t="inlineStr">
-        <is>
-          <t>46.10</t>
-        </is>
-      </c>
-      <c r="F135" s="4" t="inlineStr">
-        <is>
-          <t>+1.65</t>
-        </is>
-      </c>
+      <c r="E135" s="4" t="inlineStr"/>
+      <c r="F135" s="4" t="inlineStr"/>
       <c r="G135" s="4" t="n">
         <v>-573</v>
       </c>
@@ -30588,16 +29572,8 @@
           <t>萬泰科</t>
         </is>
       </c>
-      <c r="E136" s="4" t="inlineStr">
-        <is>
-          <t>69.80</t>
-        </is>
-      </c>
-      <c r="F136" s="4" t="inlineStr">
-        <is>
-          <t>+0.6</t>
-        </is>
-      </c>
+      <c r="E136" s="4" t="inlineStr"/>
+      <c r="F136" s="4" t="inlineStr"/>
       <c r="G136" s="4" t="n">
         <v>-562</v>
       </c>
@@ -30621,16 +29597,8 @@
           <t>華容</t>
         </is>
       </c>
-      <c r="E137" s="4" t="inlineStr">
-        <is>
-          <t>60.30</t>
-        </is>
-      </c>
-      <c r="F137" s="4" t="inlineStr">
-        <is>
-          <t>+5.4</t>
-        </is>
-      </c>
+      <c r="E137" s="4" t="inlineStr"/>
+      <c r="F137" s="4" t="inlineStr"/>
       <c r="G137" s="4" t="n">
         <v>-531</v>
       </c>
@@ -30654,16 +29622,8 @@
           <t>尼克森</t>
         </is>
       </c>
-      <c r="E138" s="4" t="inlineStr">
-        <is>
-          <t>78.00</t>
-        </is>
-      </c>
-      <c r="F138" s="4" t="inlineStr">
-        <is>
-          <t>+0.2</t>
-        </is>
-      </c>
+      <c r="E138" s="4" t="inlineStr"/>
+      <c r="F138" s="4" t="inlineStr"/>
       <c r="G138" s="4" t="n">
         <v>-530</v>
       </c>
@@ -30687,16 +29647,8 @@
           <t>茂達</t>
         </is>
       </c>
-      <c r="E139" s="4" t="inlineStr">
-        <is>
-          <t>318.00</t>
-        </is>
-      </c>
-      <c r="F139" s="4" t="inlineStr">
-        <is>
-          <t>+28.5</t>
-        </is>
-      </c>
+      <c r="E139" s="4" t="inlineStr"/>
+      <c r="F139" s="4" t="inlineStr"/>
       <c r="G139" s="4" t="n">
         <v>-521</v>
       </c>
@@ -30720,16 +29672,8 @@
           <t>錦明</t>
         </is>
       </c>
-      <c r="E140" s="4" t="inlineStr">
-        <is>
-          <t>47.25</t>
-        </is>
-      </c>
-      <c r="F140" s="4" t="inlineStr">
-        <is>
-          <t>+4.25</t>
-        </is>
-      </c>
+      <c r="E140" s="4" t="inlineStr"/>
+      <c r="F140" s="4" t="inlineStr"/>
       <c r="G140" s="4" t="n">
         <v>-463</v>
       </c>
@@ -30753,16 +29697,8 @@
           <t>智通*</t>
         </is>
       </c>
-      <c r="E141" s="4" t="inlineStr">
-        <is>
-          <t>118.50</t>
-        </is>
-      </c>
-      <c r="F141" s="4" t="inlineStr">
-        <is>
-          <t>+2.0</t>
-        </is>
-      </c>
+      <c r="E141" s="4" t="inlineStr"/>
+      <c r="F141" s="4" t="inlineStr"/>
       <c r="G141" s="4" t="n">
         <v>-463</v>
       </c>
@@ -30786,16 +29722,8 @@
           <t>台燿</t>
         </is>
       </c>
-      <c r="E142" s="4" t="inlineStr">
-        <is>
-          <t>1235.00</t>
-        </is>
-      </c>
-      <c r="F142" s="4" t="inlineStr">
-        <is>
-          <t>+110.0</t>
-        </is>
-      </c>
+      <c r="E142" s="4" t="inlineStr"/>
+      <c r="F142" s="4" t="inlineStr"/>
       <c r="G142" s="4" t="n">
         <v>-436</v>
       </c>
@@ -30819,16 +29747,8 @@
           <t>高端疫苗</t>
         </is>
       </c>
-      <c r="E143" s="4" t="inlineStr">
-        <is>
-          <t>46.65</t>
-        </is>
-      </c>
-      <c r="F143" s="4" t="inlineStr">
-        <is>
-          <t>-0.35</t>
-        </is>
-      </c>
+      <c r="E143" s="4" t="inlineStr"/>
+      <c r="F143" s="4" t="inlineStr"/>
       <c r="G143" s="4" t="n">
         <v>-413</v>
       </c>
@@ -30852,16 +29772,8 @@
           <t>泓格</t>
         </is>
       </c>
-      <c r="E144" s="4" t="inlineStr">
-        <is>
-          <t>157.00</t>
-        </is>
-      </c>
-      <c r="F144" s="4" t="inlineStr">
-        <is>
-          <t>+14.0</t>
-        </is>
-      </c>
+      <c r="E144" s="4" t="inlineStr"/>
+      <c r="F144" s="4" t="inlineStr"/>
       <c r="G144" s="4" t="n">
         <v>-408</v>
       </c>
@@ -30885,16 +29797,8 @@
           <t>慶騰</t>
         </is>
       </c>
-      <c r="E145" s="4" t="inlineStr">
-        <is>
-          <t>36.50</t>
-        </is>
-      </c>
-      <c r="F145" s="4" t="inlineStr">
-        <is>
-          <t>-1.05</t>
-        </is>
-      </c>
+      <c r="E145" s="4" t="inlineStr"/>
+      <c r="F145" s="4" t="inlineStr"/>
       <c r="G145" s="4" t="n">
         <v>-406</v>
       </c>
@@ -30918,16 +29822,8 @@
           <t>良維</t>
         </is>
       </c>
-      <c r="E146" s="4" t="inlineStr">
-        <is>
-          <t>247.00</t>
-        </is>
-      </c>
-      <c r="F146" s="4" t="inlineStr">
-        <is>
-          <t>+7.5</t>
-        </is>
-      </c>
+      <c r="E146" s="4" t="inlineStr"/>
+      <c r="F146" s="4" t="inlineStr"/>
       <c r="G146" s="4" t="n">
         <v>-358</v>
       </c>
@@ -30951,16 +29847,8 @@
           <t>新盛力</t>
         </is>
       </c>
-      <c r="E147" s="4" t="inlineStr">
-        <is>
-          <t>209.00</t>
-        </is>
-      </c>
-      <c r="F147" s="4" t="inlineStr">
-        <is>
-          <t>+6.5</t>
-        </is>
-      </c>
+      <c r="E147" s="4" t="inlineStr"/>
+      <c r="F147" s="4" t="inlineStr"/>
       <c r="G147" s="4" t="n">
         <v>-335</v>
       </c>
@@ -30984,16 +29872,8 @@
           <t>康和證</t>
         </is>
       </c>
-      <c r="E148" s="4" t="inlineStr">
-        <is>
-          <t>24.45</t>
-        </is>
-      </c>
-      <c r="F148" s="4" t="inlineStr">
-        <is>
-          <t>+0.55</t>
-        </is>
-      </c>
+      <c r="E148" s="4" t="inlineStr"/>
+      <c r="F148" s="4" t="inlineStr"/>
       <c r="G148" s="4" t="n">
         <v>-333</v>
       </c>
@@ -31017,16 +29897,8 @@
           <t>東捷</t>
         </is>
       </c>
-      <c r="E149" s="4" t="inlineStr">
-        <is>
-          <t>112.00</t>
-        </is>
-      </c>
-      <c r="F149" s="4" t="inlineStr">
-        <is>
-          <t>+4.0</t>
-        </is>
-      </c>
+      <c r="E149" s="4" t="inlineStr"/>
+      <c r="F149" s="4" t="inlineStr"/>
       <c r="G149" s="4" t="n">
         <v>-326</v>
       </c>
@@ -31050,16 +29922,8 @@
           <t>旺矽</t>
         </is>
       </c>
-      <c r="E150" s="4" t="inlineStr">
-        <is>
-          <t>5875.00</t>
-        </is>
-      </c>
-      <c r="F150" s="4" t="inlineStr">
-        <is>
-          <t>+420.0</t>
-        </is>
-      </c>
+      <c r="E150" s="4" t="inlineStr"/>
+      <c r="F150" s="4" t="inlineStr"/>
       <c r="G150" s="4" t="n">
         <v>-309</v>
       </c>
@@ -31083,16 +29947,8 @@
           <t>元創精密</t>
         </is>
       </c>
-      <c r="E151" s="4" t="inlineStr">
-        <is>
-          <t>36.45</t>
-        </is>
-      </c>
-      <c r="F151" s="4" t="inlineStr">
-        <is>
-          <t>-1.2</t>
-        </is>
-      </c>
+      <c r="E151" s="4" t="inlineStr"/>
+      <c r="F151" s="4" t="inlineStr"/>
       <c r="G151" s="4" t="n">
         <v>-307</v>
       </c>
@@ -31116,16 +29972,8 @@
           <t>先進光</t>
         </is>
       </c>
-      <c r="E152" s="4" t="inlineStr">
-        <is>
-          <t>151.50</t>
-        </is>
-      </c>
-      <c r="F152" s="4" t="inlineStr">
-        <is>
-          <t>+3.0</t>
-        </is>
-      </c>
+      <c r="E152" s="4" t="inlineStr"/>
+      <c r="F152" s="4" t="inlineStr"/>
       <c r="G152" s="4" t="n">
         <v>-274</v>
       </c>
@@ -31149,16 +29997,8 @@
           <t>華星光</t>
         </is>
       </c>
-      <c r="E153" s="4" t="inlineStr">
-        <is>
-          <t>357.00</t>
-        </is>
-      </c>
-      <c r="F153" s="4" t="inlineStr">
-        <is>
-          <t>+17.0</t>
-        </is>
-      </c>
+      <c r="E153" s="4" t="inlineStr"/>
+      <c r="F153" s="4" t="inlineStr"/>
       <c r="G153" s="4" t="n">
         <v>-266</v>
       </c>
@@ -31182,16 +30022,8 @@
           <t>聚和</t>
         </is>
       </c>
-      <c r="E154" s="4" t="inlineStr">
-        <is>
-          <t>48.00</t>
-        </is>
-      </c>
-      <c r="F154" s="4" t="inlineStr">
-        <is>
-          <t>+1.0</t>
-        </is>
-      </c>
+      <c r="E154" s="4" t="inlineStr"/>
+      <c r="F154" s="4" t="inlineStr"/>
       <c r="G154" s="4" t="n">
         <v>-265</v>
       </c>
@@ -31215,16 +30047,8 @@
           <t>倉和</t>
         </is>
       </c>
-      <c r="E155" s="4" t="inlineStr">
-        <is>
-          <t>137.50</t>
-        </is>
-      </c>
-      <c r="F155" s="4" t="inlineStr">
-        <is>
-          <t>-4.0</t>
-        </is>
-      </c>
+      <c r="E155" s="4" t="inlineStr"/>
+      <c r="F155" s="4" t="inlineStr"/>
       <c r="G155" s="4" t="n">
         <v>-257</v>
       </c>
@@ -31248,16 +30072,8 @@
           <t>光環</t>
         </is>
       </c>
-      <c r="E156" s="4" t="inlineStr">
-        <is>
-          <t>98.70</t>
-        </is>
-      </c>
-      <c r="F156" s="4" t="inlineStr">
-        <is>
-          <t>+2.4</t>
-        </is>
-      </c>
+      <c r="E156" s="4" t="inlineStr"/>
+      <c r="F156" s="4" t="inlineStr"/>
       <c r="G156" s="4" t="n">
         <v>-251</v>
       </c>
@@ -31281,16 +30097,8 @@
           <t>普誠</t>
         </is>
       </c>
-      <c r="E157" s="4" t="inlineStr">
-        <is>
-          <t>15.25</t>
-        </is>
-      </c>
-      <c r="F157" s="4" t="inlineStr">
-        <is>
-          <t>+0.1</t>
-        </is>
-      </c>
+      <c r="E157" s="4" t="inlineStr"/>
+      <c r="F157" s="4" t="inlineStr"/>
       <c r="G157" s="4" t="n">
         <v>-248</v>
       </c>
@@ -31314,16 +30122,8 @@
           <t>晟德</t>
         </is>
       </c>
-      <c r="E158" s="4" t="inlineStr">
-        <is>
-          <t>38.05</t>
-        </is>
-      </c>
-      <c r="F158" s="4" t="inlineStr">
-        <is>
-          <t>+0.55</t>
-        </is>
-      </c>
+      <c r="E158" s="4" t="inlineStr"/>
+      <c r="F158" s="4" t="inlineStr"/>
       <c r="G158" s="4" t="n">
         <v>-244</v>
       </c>

--- a/StockInfo/otc_analysis_result.xlsx
+++ b/StockInfo/otc_analysis_result.xlsx
@@ -5024,8 +5024,16 @@
           <t>富喬</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>112.00</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>+5.0</t>
+        </is>
+      </c>
       <c r="G4" s="4" t="n">
         <v>15197</v>
       </c>
@@ -5060,8 +5068,16 @@
           <t>威剛</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr"/>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>422.50</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>+21.5</t>
+        </is>
+      </c>
       <c r="G5" s="4" t="n">
         <v>11989</v>
       </c>
@@ -5096,8 +5112,16 @@
           <t>金居</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr"/>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>436.00</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>+22.5</t>
+        </is>
+      </c>
       <c r="G6" s="4" t="n">
         <v>5154</v>
       </c>
@@ -5136,8 +5160,16 @@
           <t>榮剛</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr"/>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>35.20</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>+0.95</t>
+        </is>
+      </c>
       <c r="G7" s="4" t="n">
         <v>2741</v>
       </c>
@@ -5168,8 +5200,16 @@
           <t>正德</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr"/>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>18.95</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>+0.6</t>
+        </is>
+      </c>
       <c r="G8" s="4" t="n">
         <v>2595</v>
       </c>
@@ -5208,8 +5248,16 @@
           <t>鈺創</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr"/>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>123.00</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>+5.0</t>
+        </is>
+      </c>
       <c r="G9" s="4" t="n">
         <v>2563</v>
       </c>
@@ -5236,8 +5284,16 @@
           <t>亞電</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr"/>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>66.50</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>+3.8</t>
+        </is>
+      </c>
       <c r="G10" s="4" t="n">
         <v>1570</v>
       </c>
@@ -5264,8 +5320,16 @@
           <t>華星光</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr"/>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>577.00</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>+7.0</t>
+        </is>
+      </c>
       <c r="G11" s="4" t="n">
         <v>1401</v>
       </c>
@@ -5300,8 +5364,16 @@
           <t>宜鼎</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr"/>
-      <c r="F12" s="4" t="inlineStr"/>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>1560.00</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>+70.0</t>
+        </is>
+      </c>
       <c r="G12" s="4" t="n">
         <v>844</v>
       </c>
@@ -5328,8 +5400,16 @@
           <t>方土昶</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr"/>
-      <c r="F13" s="4" t="inlineStr"/>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>59.50</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>+3.0</t>
+        </is>
+      </c>
       <c r="G13" s="4" t="n">
         <v>820</v>
       </c>
@@ -5356,8 +5436,16 @@
           <t>松瑞藥</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr"/>
-      <c r="F14" s="4" t="inlineStr"/>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>20.95</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>+0.25</t>
+        </is>
+      </c>
       <c r="G14" s="4" t="n">
         <v>795</v>
       </c>
@@ -5388,8 +5476,16 @@
           <t>廣穎</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr"/>
-      <c r="F15" s="4" t="inlineStr"/>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>159.00</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>+7.0</t>
+        </is>
+      </c>
       <c r="G15" s="4" t="n">
         <v>702</v>
       </c>
@@ -5420,8 +5516,16 @@
           <t>亞通</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr"/>
-      <c r="F16" s="4" t="inlineStr"/>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>27.20</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>+0.75</t>
+        </is>
+      </c>
       <c r="G16" s="4" t="n">
         <v>695</v>
       </c>
@@ -5448,8 +5552,16 @@
           <t>合一</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="4" t="inlineStr"/>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>+1.7</t>
+        </is>
+      </c>
       <c r="G17" s="4" t="n">
         <v>692</v>
       </c>
@@ -5480,8 +5592,16 @@
           <t>群聯</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr"/>
-      <c r="F18" s="4" t="inlineStr"/>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>2075.00</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>+80.0</t>
+        </is>
+      </c>
       <c r="G18" s="4" t="n">
         <v>688</v>
       </c>
@@ -5512,8 +5632,16 @@
           <t>光頡</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr"/>
-      <c r="F19" s="4" t="inlineStr"/>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>87.80</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>+1.5</t>
+        </is>
+      </c>
       <c r="G19" s="4" t="n">
         <v>652</v>
       </c>
@@ -5540,8 +5668,16 @@
           <t>立碁</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr"/>
-      <c r="F20" s="4" t="inlineStr"/>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>65.00</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>+5.0</t>
+        </is>
+      </c>
       <c r="G20" s="4" t="n">
         <v>584</v>
       </c>
@@ -5572,8 +5708,16 @@
           <t>光環</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr"/>
-      <c r="F21" s="4" t="inlineStr"/>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>151.00</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>-0.0</t>
+        </is>
+      </c>
       <c r="G21" s="4" t="n">
         <v>578</v>
       </c>
@@ -5604,8 +5748,16 @@
           <t>三圓</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr"/>
-      <c r="F22" s="4" t="inlineStr"/>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>13.75</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>+1.25</t>
+        </is>
+      </c>
       <c r="G22" s="4" t="n">
         <v>511</v>
       </c>
@@ -5644,8 +5796,16 @@
           <t>生華科</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr"/>
-      <c r="F23" s="4" t="inlineStr"/>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>34.80</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>-2.9</t>
+        </is>
+      </c>
       <c r="G23" s="4" t="n">
         <v>473</v>
       </c>
@@ -5684,8 +5844,16 @@
           <t>基亞</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr"/>
-      <c r="F24" s="4" t="inlineStr"/>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>37.20</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>+1.65</t>
+        </is>
+      </c>
       <c r="G24" s="4" t="n">
         <v>451</v>
       </c>
@@ -5720,8 +5888,16 @@
           <t>中裕</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr"/>
-      <c r="F25" s="4" t="inlineStr"/>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>63.10</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>-0.6</t>
+        </is>
+      </c>
       <c r="G25" s="4" t="n">
         <v>428</v>
       </c>
@@ -5752,8 +5928,16 @@
           <t>致和證</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr"/>
-      <c r="F26" s="4" t="inlineStr"/>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>34.30</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>+0.3</t>
+        </is>
+      </c>
       <c r="G26" s="4" t="n">
         <v>403</v>
       </c>
@@ -5780,8 +5964,16 @@
           <t>聯一光</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr"/>
-      <c r="F27" s="4" t="inlineStr"/>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>107.00</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>+9.7</t>
+        </is>
+      </c>
       <c r="G27" s="4" t="n">
         <v>382</v>
       </c>
@@ -5812,8 +6004,16 @@
           <t>力麒</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr"/>
-      <c r="F28" s="4" t="inlineStr"/>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>7.85</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>+0.01</t>
+        </is>
+      </c>
       <c r="G28" s="4" t="n">
         <v>374</v>
       </c>
@@ -5844,8 +6044,16 @@
           <t>創惟</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr"/>
-      <c r="F29" s="4" t="inlineStr"/>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>95.30</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>+1.9</t>
+        </is>
+      </c>
       <c r="G29" s="4" t="n">
         <v>360</v>
       </c>
@@ -5876,8 +6084,16 @@
           <t>陽程</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr"/>
-      <c r="F30" s="4" t="inlineStr"/>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>192.00</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>+8.5</t>
+        </is>
+      </c>
       <c r="G30" s="4" t="n">
         <v>355</v>
       </c>
@@ -5908,8 +6124,16 @@
           <t>波若威</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr"/>
-      <c r="F31" s="4" t="inlineStr"/>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>783.00</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>+47.0</t>
+        </is>
+      </c>
       <c r="G31" s="4" t="n">
         <v>349</v>
       </c>
@@ -5936,8 +6160,16 @@
           <t>新盛力</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr"/>
-      <c r="F32" s="4" t="inlineStr"/>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>280.00</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>+7.0</t>
+        </is>
+      </c>
       <c r="G32" s="4" t="n">
         <v>283</v>
       </c>
@@ -5968,8 +6200,16 @@
           <t>智崴</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr"/>
-      <c r="F33" s="4" t="inlineStr"/>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>90.60</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>+2.5</t>
+        </is>
+      </c>
       <c r="G33" s="4" t="n">
         <v>242</v>
       </c>
@@ -6004,8 +6244,16 @@
           <t>宏遠證</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr"/>
-      <c r="F34" s="4" t="inlineStr"/>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>15.90</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>+0.15</t>
+        </is>
+      </c>
       <c r="G34" s="4" t="n">
         <v>239</v>
       </c>
@@ -6032,8 +6280,16 @@
           <t>僑威</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr"/>
-      <c r="F35" s="4" t="inlineStr"/>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>54.50</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>+1.0</t>
+        </is>
+      </c>
       <c r="G35" s="4" t="n">
         <v>232</v>
       </c>
@@ -6064,8 +6320,16 @@
           <t>永捷</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr"/>
-      <c r="F36" s="4" t="inlineStr"/>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>10.75</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>+0.2</t>
+        </is>
+      </c>
       <c r="G36" s="4" t="n">
         <v>225</v>
       </c>
@@ -6096,8 +6360,16 @@
           <t>能率</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr"/>
-      <c r="F37" s="4" t="inlineStr"/>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>46.05</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>+0.95</t>
+        </is>
+      </c>
       <c r="G37" s="4" t="n">
         <v>221</v>
       </c>
@@ -6128,8 +6400,16 @@
           <t>錦明</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr"/>
-      <c r="F38" s="4" t="inlineStr"/>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>43.25</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>+1.7</t>
+        </is>
+      </c>
       <c r="G38" s="4" t="n">
         <v>216</v>
       </c>
@@ -6156,8 +6436,16 @@
           <t>中天</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr"/>
-      <c r="F39" s="4" t="inlineStr"/>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>15.60</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>+0.35</t>
+        </is>
+      </c>
       <c r="G39" s="4" t="n">
         <v>215</v>
       </c>
@@ -6184,8 +6472,16 @@
           <t>美而快</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr"/>
-      <c r="F40" s="4" t="inlineStr"/>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>72.90</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>+1.0</t>
+        </is>
+      </c>
       <c r="G40" s="4" t="n">
         <v>215</v>
       </c>
@@ -6220,8 +6516,16 @@
           <t>亞昕</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr"/>
-      <c r="F41" s="4" t="inlineStr"/>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>21.45</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>+0.25</t>
+        </is>
+      </c>
       <c r="G41" s="4" t="n">
         <v>203</v>
       </c>
@@ -6252,8 +6556,16 @@
           <t>風青</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr"/>
-      <c r="F42" s="4" t="inlineStr"/>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>50.10</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>+0.35</t>
+        </is>
+      </c>
       <c r="G42" s="4" t="n">
         <v>176</v>
       </c>
@@ -6280,8 +6592,16 @@
           <t>晟田</t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr"/>
-      <c r="F43" s="4" t="inlineStr"/>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>68.80</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>+1.2</t>
+        </is>
+      </c>
       <c r="G43" s="4" t="n">
         <v>166</v>
       </c>
@@ -6308,8 +6628,16 @@
           <t>大甲</t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr"/>
-      <c r="F44" s="4" t="inlineStr"/>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>57.60</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>+3.3</t>
+        </is>
+      </c>
       <c r="G44" s="4" t="n">
         <v>158</v>
       </c>
@@ -6340,8 +6668,16 @@
           <t>華盈</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr"/>
-      <c r="F45" s="4" t="inlineStr"/>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>18.60</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>+0.6</t>
+        </is>
+      </c>
       <c r="G45" s="4" t="n">
         <v>151</v>
       </c>
@@ -6368,8 +6704,16 @@
           <t>泰谷</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr"/>
-      <c r="F46" s="4" t="inlineStr"/>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>38.15</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>+0.2</t>
+        </is>
+      </c>
       <c r="G46" s="4" t="n">
         <v>143</v>
       </c>
@@ -6396,8 +6740,16 @@
           <t>巨有科技</t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr"/>
-      <c r="F47" s="4" t="inlineStr"/>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>156.00</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>+9.0</t>
+        </is>
+      </c>
       <c r="G47" s="4" t="n">
         <v>143</v>
       </c>
@@ -6424,8 +6776,16 @@
           <t>胡連</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr"/>
-      <c r="F48" s="4" t="inlineStr"/>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>128.00</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>+0.5</t>
+        </is>
+      </c>
       <c r="G48" s="4" t="n">
         <v>141</v>
       </c>
@@ -6456,8 +6816,16 @@
           <t>北基</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr"/>
-      <c r="F49" s="4" t="inlineStr"/>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>20.40</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>+0.4</t>
+        </is>
+      </c>
       <c r="G49" s="4" t="n">
         <v>140</v>
       </c>
@@ -6488,8 +6856,16 @@
           <t>大樹</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr"/>
-      <c r="F50" s="4" t="inlineStr"/>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>70.60</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>+1.5</t>
+        </is>
+      </c>
       <c r="G50" s="4" t="n">
         <v>132</v>
       </c>
@@ -6516,8 +6892,16 @@
           <t>康和證</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr"/>
-      <c r="F51" s="4" t="inlineStr"/>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>19.60</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>+0.25</t>
+        </is>
+      </c>
       <c r="G51" s="4" t="n">
         <v>128</v>
       </c>
@@ -6544,8 +6928,16 @@
           <t>群翊</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr"/>
-      <c r="F52" s="4" t="inlineStr"/>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>364.50</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>+33.0</t>
+        </is>
+      </c>
       <c r="G52" s="4" t="n">
         <v>124</v>
       </c>
@@ -6572,8 +6964,16 @@
           <t>福邦證</t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr"/>
-      <c r="F53" s="4" t="inlineStr"/>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>14.80</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>+0.15</t>
+        </is>
+      </c>
       <c r="G53" s="4" t="n">
         <v>120</v>
       </c>
@@ -6604,8 +7004,16 @@
           <t>擎亞</t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr"/>
-      <c r="F54" s="4" t="inlineStr"/>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>105.50</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>-2.5</t>
+        </is>
+      </c>
       <c r="G54" s="4" t="n">
         <v>117</v>
       </c>
@@ -6636,8 +7044,16 @@
           <t>濱川</t>
         </is>
       </c>
-      <c r="E55" s="4" t="inlineStr"/>
-      <c r="F55" s="4" t="inlineStr"/>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>44.85</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>+1.3</t>
+        </is>
+      </c>
       <c r="G55" s="4" t="n">
         <v>113</v>
       </c>
@@ -6668,8 +7084,16 @@
           <t>寬宏藝術</t>
         </is>
       </c>
-      <c r="E56" s="4" t="inlineStr"/>
-      <c r="F56" s="4" t="inlineStr"/>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>95.40</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>+1.5</t>
+        </is>
+      </c>
       <c r="G56" s="4" t="n">
         <v>112</v>
       </c>
@@ -6704,8 +7128,16 @@
           <t>振發</t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr"/>
-      <c r="F57" s="4" t="inlineStr"/>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>27.35</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>+0.15</t>
+        </is>
+      </c>
       <c r="G57" s="4" t="n">
         <v>109</v>
       </c>
@@ -6736,8 +7168,16 @@
           <t>磐亞</t>
         </is>
       </c>
-      <c r="E58" s="4" t="inlineStr"/>
-      <c r="F58" s="4" t="inlineStr"/>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>32.90</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>+0.35</t>
+        </is>
+      </c>
       <c r="G58" s="4" t="n">
         <v>108</v>
       </c>
@@ -6768,8 +7208,16 @@
           <t>能率網通</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr"/>
-      <c r="F59" s="4" t="inlineStr"/>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>24.05</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>+0.35</t>
+        </is>
+      </c>
       <c r="G59" s="4" t="n">
         <v>106</v>
       </c>
@@ -6796,8 +7244,16 @@
           <t>泰藝</t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr"/>
-      <c r="F60" s="4" t="inlineStr"/>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>46.45</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>+0.45</t>
+        </is>
+      </c>
       <c r="G60" s="4" t="n">
         <v>92</v>
       </c>
@@ -6824,8 +7280,16 @@
           <t>廣閎科</t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr"/>
-      <c r="F61" s="4" t="inlineStr"/>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>163.50</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>-5.5</t>
+        </is>
+      </c>
       <c r="G61" s="4" t="n">
         <v>89</v>
       </c>
@@ -6856,8 +7320,16 @@
           <t>匯鑽科</t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr"/>
-      <c r="F62" s="4" t="inlineStr"/>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>46.60</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>+1.3</t>
+        </is>
+      </c>
       <c r="G62" s="4" t="n">
         <v>89</v>
       </c>
@@ -6884,8 +7356,16 @@
           <t>森鉅</t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr"/>
-      <c r="F63" s="4" t="inlineStr"/>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>42.25</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>+0.25</t>
+        </is>
+      </c>
       <c r="G63" s="4" t="n">
         <v>88</v>
       </c>
@@ -6916,8 +7396,16 @@
           <t>國眾</t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr"/>
-      <c r="F64" s="4" t="inlineStr"/>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>36.25</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>+0.35</t>
+        </is>
+      </c>
       <c r="G64" s="4" t="n">
         <v>86</v>
       </c>
@@ -6944,8 +7432,16 @@
           <t>美好證</t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr"/>
-      <c r="F65" s="4" t="inlineStr"/>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>38.45</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>+2.1</t>
+        </is>
+      </c>
       <c r="G65" s="4" t="n">
         <v>86</v>
       </c>
@@ -6972,8 +7468,16 @@
           <t>佶優</t>
         </is>
       </c>
-      <c r="E66" s="4" t="inlineStr"/>
-      <c r="F66" s="4" t="inlineStr"/>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>27.05</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>+0.35</t>
+        </is>
+      </c>
       <c r="G66" s="4" t="n">
         <v>84</v>
       </c>
@@ -7004,8 +7508,16 @@
           <t>永信建</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr"/>
-      <c r="F67" s="4" t="inlineStr"/>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>53.80</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>+0.3</t>
+        </is>
+      </c>
       <c r="G67" s="4" t="n">
         <v>79</v>
       </c>
@@ -7036,8 +7548,16 @@
           <t>應廣</t>
         </is>
       </c>
-      <c r="E68" s="4" t="inlineStr"/>
-      <c r="F68" s="4" t="inlineStr"/>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>133.00</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>-0.0</t>
+        </is>
+      </c>
       <c r="G68" s="4" t="n">
         <v>76</v>
       </c>
@@ -7068,8 +7588,16 @@
           <t>中菲行</t>
         </is>
       </c>
-      <c r="E69" s="4" t="inlineStr"/>
-      <c r="F69" s="4" t="inlineStr"/>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>79.40</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>+1.3</t>
+        </is>
+      </c>
       <c r="G69" s="4" t="n">
         <v>75</v>
       </c>
@@ -7100,8 +7628,16 @@
           <t>創威</t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr"/>
-      <c r="F70" s="4" t="inlineStr"/>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>82.10</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
       <c r="G70" s="4" t="n">
         <v>73</v>
       </c>
@@ -7128,8 +7664,16 @@
           <t>豪勉</t>
         </is>
       </c>
-      <c r="E71" s="4" t="inlineStr"/>
-      <c r="F71" s="4" t="inlineStr"/>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>37.85</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>-0.15</t>
+        </is>
+      </c>
       <c r="G71" s="4" t="n">
         <v>71</v>
       </c>
@@ -7156,8 +7700,16 @@
           <t>光譜</t>
         </is>
       </c>
-      <c r="E72" s="4" t="inlineStr"/>
-      <c r="F72" s="4" t="inlineStr"/>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>24.45</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>+0.5</t>
+        </is>
+      </c>
       <c r="G72" s="4" t="n">
         <v>66</v>
       </c>
@@ -7188,8 +7740,16 @@
           <t>富強鑫</t>
         </is>
       </c>
-      <c r="E73" s="4" t="inlineStr"/>
-      <c r="F73" s="4" t="inlineStr"/>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>27.00</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>-0.1</t>
+        </is>
+      </c>
       <c r="G73" s="4" t="n">
         <v>63</v>
       </c>
@@ -7216,8 +7776,16 @@
           <t>國統</t>
         </is>
       </c>
-      <c r="E74" s="4" t="inlineStr"/>
-      <c r="F74" s="4" t="inlineStr"/>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>51.10</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>+0.1</t>
+        </is>
+      </c>
       <c r="G74" s="4" t="n">
         <v>63</v>
       </c>
@@ -7244,8 +7812,16 @@
           <t>協易機</t>
         </is>
       </c>
-      <c r="E75" s="4" t="inlineStr"/>
-      <c r="F75" s="4" t="inlineStr"/>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>25.55</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>-0.3</t>
+        </is>
+      </c>
       <c r="G75" s="4" t="n">
         <v>62</v>
       </c>
@@ -7272,8 +7848,16 @@
           <t>元大期</t>
         </is>
       </c>
-      <c r="E76" s="4" t="inlineStr"/>
-      <c r="F76" s="4" t="inlineStr"/>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>82.80</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>+0.3</t>
+        </is>
+      </c>
       <c r="G76" s="4" t="n">
         <v>62</v>
       </c>
@@ -7300,8 +7884,16 @@
           <t>青雲</t>
         </is>
       </c>
-      <c r="E77" s="4" t="inlineStr"/>
-      <c r="F77" s="4" t="inlineStr"/>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>236.00</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>+5.5</t>
+        </is>
+      </c>
       <c r="G77" s="4" t="n">
         <v>61</v>
       </c>
@@ -7328,8 +7920,16 @@
           <t>連展投控</t>
         </is>
       </c>
-      <c r="E78" s="4" t="inlineStr"/>
-      <c r="F78" s="4" t="inlineStr"/>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>-0.0</t>
+        </is>
+      </c>
       <c r="G78" s="4" t="n">
         <v>59</v>
       </c>
@@ -7356,8 +7956,16 @@
           <t>智擎</t>
         </is>
       </c>
-      <c r="E79" s="4" t="inlineStr"/>
-      <c r="F79" s="4" t="inlineStr"/>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>+0.7</t>
+        </is>
+      </c>
       <c r="G79" s="4" t="n">
         <v>59</v>
       </c>
@@ -7384,8 +7992,16 @@
           <t>廣寰科</t>
         </is>
       </c>
-      <c r="E80" s="4" t="inlineStr"/>
-      <c r="F80" s="4" t="inlineStr"/>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>37.75</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>+0.25</t>
+        </is>
+      </c>
       <c r="G80" s="4" t="n">
         <v>58</v>
       </c>
@@ -7412,8 +8028,16 @@
           <t>宸曜</t>
         </is>
       </c>
-      <c r="E81" s="4" t="inlineStr"/>
-      <c r="F81" s="4" t="inlineStr"/>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>202.50</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>+7.5</t>
+        </is>
+      </c>
       <c r="G81" s="4" t="n">
         <v>55</v>
       </c>
@@ -7440,8 +8064,16 @@
           <t>亞泰</t>
         </is>
       </c>
-      <c r="E82" s="4" t="inlineStr"/>
-      <c r="F82" s="4" t="inlineStr"/>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>69.60</t>
+        </is>
+      </c>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>+0.7</t>
+        </is>
+      </c>
       <c r="G82" s="4" t="n">
         <v>54</v>
       </c>
@@ -7472,8 +8104,16 @@
           <t>精剛</t>
         </is>
       </c>
-      <c r="E83" s="4" t="inlineStr"/>
-      <c r="F83" s="4" t="inlineStr"/>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>18.20</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>+0.2</t>
+        </is>
+      </c>
       <c r="G83" s="4" t="n">
         <v>52</v>
       </c>
@@ -7500,8 +8140,16 @@
           <t>晶呈科技</t>
         </is>
       </c>
-      <c r="E84" s="4" t="inlineStr"/>
-      <c r="F84" s="4" t="inlineStr"/>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>337.00</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>+23.0</t>
+        </is>
+      </c>
       <c r="G84" s="4" t="n">
         <v>52</v>
       </c>
@@ -7528,8 +8176,16 @@
           <t>均華</t>
         </is>
       </c>
-      <c r="E85" s="4" t="inlineStr"/>
-      <c r="F85" s="4" t="inlineStr"/>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>1045.00</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>+91.0</t>
+        </is>
+      </c>
       <c r="G85" s="4" t="n">
         <v>52</v>
       </c>
@@ -7556,8 +8212,16 @@
           <t>福華</t>
         </is>
       </c>
-      <c r="E86" s="4" t="inlineStr"/>
-      <c r="F86" s="4" t="inlineStr"/>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>12.35</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>-0.0</t>
+        </is>
+      </c>
       <c r="G86" s="4" t="n">
         <v>52</v>
       </c>
@@ -7588,8 +8252,16 @@
           <t>龍巖</t>
         </is>
       </c>
-      <c r="E87" s="4" t="inlineStr"/>
-      <c r="F87" s="4" t="inlineStr"/>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>50.50</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>+0.4</t>
+        </is>
+      </c>
       <c r="G87" s="4" t="n">
         <v>51</v>
       </c>
@@ -7616,8 +8288,16 @@
           <t>橘子</t>
         </is>
       </c>
-      <c r="E88" s="4" t="inlineStr"/>
-      <c r="F88" s="4" t="inlineStr"/>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>41.50</t>
+        </is>
+      </c>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t>+0.3</t>
+        </is>
+      </c>
       <c r="G88" s="4" t="n">
         <v>45</v>
       </c>
@@ -7644,8 +8324,16 @@
           <t>神盾</t>
         </is>
       </c>
-      <c r="E89" s="4" t="inlineStr"/>
-      <c r="F89" s="4" t="inlineStr"/>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t>+1.5</t>
+        </is>
+      </c>
       <c r="G89" s="4" t="n">
         <v>44</v>
       </c>
@@ -7676,8 +8364,16 @@
           <t>駿吉-KY</t>
         </is>
       </c>
-      <c r="E90" s="4" t="inlineStr"/>
-      <c r="F90" s="4" t="inlineStr"/>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>36.30</t>
+        </is>
+      </c>
+      <c r="F90" s="4" t="inlineStr">
+        <is>
+          <t>+0.6</t>
+        </is>
+      </c>
       <c r="G90" s="4" t="n">
         <v>43</v>
       </c>
@@ -7704,8 +8400,16 @@
           <t>博磊</t>
         </is>
       </c>
-      <c r="E91" s="4" t="inlineStr"/>
-      <c r="F91" s="4" t="inlineStr"/>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>103.50</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>-2.5</t>
+        </is>
+      </c>
       <c r="G91" s="4" t="n">
         <v>43</v>
       </c>
@@ -7736,8 +8440,16 @@
           <t>德昌</t>
         </is>
       </c>
-      <c r="E92" s="4" t="inlineStr"/>
-      <c r="F92" s="4" t="inlineStr"/>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>72.90</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t>+0.1</t>
+        </is>
+      </c>
       <c r="G92" s="4" t="n">
         <v>43</v>
       </c>
@@ -7768,8 +8480,16 @@
           <t>易發</t>
         </is>
       </c>
-      <c r="E93" s="4" t="inlineStr"/>
-      <c r="F93" s="4" t="inlineStr"/>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>57.60</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>-1.4</t>
+        </is>
+      </c>
       <c r="G93" s="4" t="n">
         <v>43</v>
       </c>
@@ -7796,8 +8516,16 @@
           <t>艾華</t>
         </is>
       </c>
-      <c r="E94" s="4" t="inlineStr"/>
-      <c r="F94" s="4" t="inlineStr"/>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>87.60</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t>+4.3</t>
+        </is>
+      </c>
       <c r="G94" s="4" t="n">
         <v>42</v>
       </c>
@@ -7824,8 +8552,16 @@
           <t>沛亨</t>
         </is>
       </c>
-      <c r="E95" s="4" t="inlineStr"/>
-      <c r="F95" s="4" t="inlineStr"/>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>388.50</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>+10.0</t>
+        </is>
+      </c>
       <c r="G95" s="4" t="n">
         <v>42</v>
       </c>
@@ -7852,8 +8588,16 @@
           <t>逸達</t>
         </is>
       </c>
-      <c r="E96" s="4" t="inlineStr"/>
-      <c r="F96" s="4" t="inlineStr"/>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>80.00</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>+0.2</t>
+        </is>
+      </c>
       <c r="G96" s="4" t="n">
         <v>42</v>
       </c>
@@ -7880,8 +8624,16 @@
           <t>亞信</t>
         </is>
       </c>
-      <c r="E97" s="4" t="inlineStr"/>
-      <c r="F97" s="4" t="inlineStr"/>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>101.50</t>
+        </is>
+      </c>
+      <c r="F97" s="4" t="inlineStr">
+        <is>
+          <t>+1.5</t>
+        </is>
+      </c>
       <c r="G97" s="4" t="n">
         <v>41</v>
       </c>
@@ -7908,8 +8660,16 @@
           <t>九暘</t>
         </is>
       </c>
-      <c r="E98" s="4" t="inlineStr"/>
-      <c r="F98" s="4" t="inlineStr"/>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>69.60</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>-0.1</t>
+        </is>
+      </c>
       <c r="G98" s="4" t="n">
         <v>39</v>
       </c>
@@ -7940,8 +8700,16 @@
           <t>森寶</t>
         </is>
       </c>
-      <c r="E99" s="4" t="inlineStr"/>
-      <c r="F99" s="4" t="inlineStr"/>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>22.20</t>
+        </is>
+      </c>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t>+0.5</t>
+        </is>
+      </c>
       <c r="G99" s="4" t="n">
         <v>38</v>
       </c>
@@ -7968,8 +8736,16 @@
           <t>振曜</t>
         </is>
       </c>
-      <c r="E100" s="4" t="inlineStr"/>
-      <c r="F100" s="4" t="inlineStr"/>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t>90.00</t>
+        </is>
+      </c>
+      <c r="F100" s="4" t="inlineStr">
+        <is>
+          <t>+0.4</t>
+        </is>
+      </c>
       <c r="G100" s="4" t="n">
         <v>38</v>
       </c>
@@ -7996,8 +8772,16 @@
           <t>川寶</t>
         </is>
       </c>
-      <c r="E101" s="4" t="inlineStr"/>
-      <c r="F101" s="4" t="inlineStr"/>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t>62.80</t>
+        </is>
+      </c>
+      <c r="F101" s="4" t="inlineStr">
+        <is>
+          <t>+0.6</t>
+        </is>
+      </c>
       <c r="G101" s="4" t="n">
         <v>37</v>
       </c>
@@ -8028,8 +8812,16 @@
           <t>友輝</t>
         </is>
       </c>
-      <c r="E102" s="4" t="inlineStr"/>
-      <c r="F102" s="4" t="inlineStr"/>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t>54.20</t>
+        </is>
+      </c>
+      <c r="F102" s="4" t="inlineStr">
+        <is>
+          <t>+0.3</t>
+        </is>
+      </c>
       <c r="G102" s="4" t="n">
         <v>37</v>
       </c>
@@ -8056,8 +8848,16 @@
           <t>金益鼎</t>
         </is>
       </c>
-      <c r="E103" s="4" t="inlineStr"/>
-      <c r="F103" s="4" t="inlineStr"/>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t>99.00</t>
+        </is>
+      </c>
+      <c r="F103" s="4" t="inlineStr">
+        <is>
+          <t>+1.5</t>
+        </is>
+      </c>
       <c r="G103" s="4" t="n">
         <v>37</v>
       </c>
@@ -8188,8 +8988,16 @@
           <t>中美晶</t>
         </is>
       </c>
-      <c r="E109" s="4" t="inlineStr"/>
-      <c r="F109" s="4" t="inlineStr"/>
+      <c r="E109" s="4" t="inlineStr">
+        <is>
+          <t>176.00</t>
+        </is>
+      </c>
+      <c r="F109" s="4" t="inlineStr">
+        <is>
+          <t>-10.5</t>
+        </is>
+      </c>
       <c r="G109" s="4" t="n">
         <v>-12042</v>
       </c>
@@ -8224,8 +9032,16 @@
           <t>頎邦</t>
         </is>
       </c>
-      <c r="E110" s="4" t="inlineStr"/>
-      <c r="F110" s="4" t="inlineStr"/>
+      <c r="E110" s="4" t="inlineStr">
+        <is>
+          <t>156.50</t>
+        </is>
+      </c>
+      <c r="F110" s="4" t="inlineStr">
+        <is>
+          <t>-7.0</t>
+        </is>
+      </c>
       <c r="G110" s="4" t="n">
         <v>-2935</v>
       </c>
@@ -8252,8 +9068,16 @@
           <t>環宇-KY</t>
         </is>
       </c>
-      <c r="E111" s="4" t="inlineStr"/>
-      <c r="F111" s="4" t="inlineStr"/>
+      <c r="E111" s="4" t="inlineStr">
+        <is>
+          <t>481.00</t>
+        </is>
+      </c>
+      <c r="F111" s="4" t="inlineStr">
+        <is>
+          <t>-39.0</t>
+        </is>
+      </c>
       <c r="G111" s="4" t="n">
         <v>-2279</v>
       </c>
@@ -8292,8 +9116,16 @@
           <t>寶雅*</t>
         </is>
       </c>
-      <c r="E112" s="4" t="inlineStr"/>
-      <c r="F112" s="4" t="inlineStr"/>
+      <c r="E112" s="4" t="inlineStr">
+        <is>
+          <t>74.50</t>
+        </is>
+      </c>
+      <c r="F112" s="4" t="inlineStr">
+        <is>
+          <t>-1.4</t>
+        </is>
+      </c>
       <c r="G112" s="4" t="n">
         <v>-2125</v>
       </c>
@@ -8324,8 +9156,16 @@
           <t>環球晶</t>
         </is>
       </c>
-      <c r="E113" s="4" t="inlineStr"/>
-      <c r="F113" s="4" t="inlineStr"/>
+      <c r="E113" s="4" t="inlineStr">
+        <is>
+          <t>941.00</t>
+        </is>
+      </c>
+      <c r="F113" s="4" t="inlineStr">
+        <is>
+          <t>-52.0</t>
+        </is>
+      </c>
       <c r="G113" s="4" t="n">
         <v>-2036</v>
       </c>
@@ -8356,8 +9196,16 @@
           <t>信昌電</t>
         </is>
       </c>
-      <c r="E114" s="4" t="inlineStr"/>
-      <c r="F114" s="4" t="inlineStr"/>
+      <c r="E114" s="4" t="inlineStr">
+        <is>
+          <t>212.00</t>
+        </is>
+      </c>
+      <c r="F114" s="4" t="inlineStr">
+        <is>
+          <t>-9.0</t>
+        </is>
+      </c>
       <c r="G114" s="4" t="n">
         <v>-1755</v>
       </c>
@@ -8384,8 +9232,16 @@
           <t>凱崴</t>
         </is>
       </c>
-      <c r="E115" s="4" t="inlineStr"/>
-      <c r="F115" s="4" t="inlineStr"/>
+      <c r="E115" s="4" t="inlineStr">
+        <is>
+          <t>50.40</t>
+        </is>
+      </c>
+      <c r="F115" s="4" t="inlineStr">
+        <is>
+          <t>-0.3</t>
+        </is>
+      </c>
       <c r="G115" s="4" t="n">
         <v>-1676</v>
       </c>
@@ -8424,8 +9280,16 @@
           <t>台半</t>
         </is>
       </c>
-      <c r="E116" s="4" t="inlineStr"/>
-      <c r="F116" s="4" t="inlineStr"/>
+      <c r="E116" s="4" t="inlineStr">
+        <is>
+          <t>88.20</t>
+        </is>
+      </c>
+      <c r="F116" s="4" t="inlineStr">
+        <is>
+          <t>-2.1</t>
+        </is>
+      </c>
       <c r="G116" s="4" t="n">
         <v>-1647</v>
       </c>
@@ -8452,8 +9316,16 @@
           <t>穩懋</t>
         </is>
       </c>
-      <c r="E117" s="4" t="inlineStr"/>
-      <c r="F117" s="4" t="inlineStr"/>
+      <c r="E117" s="4" t="inlineStr">
+        <is>
+          <t>373.00</t>
+        </is>
+      </c>
+      <c r="F117" s="4" t="inlineStr">
+        <is>
+          <t>-6.0</t>
+        </is>
+      </c>
       <c r="G117" s="4" t="n">
         <v>-1636</v>
       </c>
@@ -8480,8 +9352,16 @@
           <t>宏捷科</t>
         </is>
       </c>
-      <c r="E118" s="4" t="inlineStr"/>
-      <c r="F118" s="4" t="inlineStr"/>
+      <c r="E118" s="4" t="inlineStr">
+        <is>
+          <t>110.50</t>
+        </is>
+      </c>
+      <c r="F118" s="4" t="inlineStr">
+        <is>
+          <t>-4.0</t>
+        </is>
+      </c>
       <c r="G118" s="4" t="n">
         <v>-1259</v>
       </c>
@@ -8512,8 +9392,16 @@
           <t>元太</t>
         </is>
       </c>
-      <c r="E119" s="4" t="inlineStr"/>
-      <c r="F119" s="4" t="inlineStr"/>
+      <c r="E119" s="4" t="inlineStr">
+        <is>
+          <t>160.50</t>
+        </is>
+      </c>
+      <c r="F119" s="4" t="inlineStr">
+        <is>
+          <t>-2.5</t>
+        </is>
+      </c>
       <c r="G119" s="4" t="n">
         <v>-1237</v>
       </c>
@@ -8544,8 +9432,16 @@
           <t>合晶</t>
         </is>
       </c>
-      <c r="E120" s="4" t="inlineStr"/>
-      <c r="F120" s="4" t="inlineStr"/>
+      <c r="E120" s="4" t="inlineStr">
+        <is>
+          <t>106.00</t>
+        </is>
+      </c>
+      <c r="F120" s="4" t="inlineStr">
+        <is>
+          <t>-3.5</t>
+        </is>
+      </c>
       <c r="G120" s="4" t="n">
         <v>-1083</v>
       </c>
@@ -8576,8 +9472,16 @@
           <t>鈊象</t>
         </is>
       </c>
-      <c r="E121" s="4" t="inlineStr"/>
-      <c r="F121" s="4" t="inlineStr"/>
+      <c r="E121" s="4" t="inlineStr">
+        <is>
+          <t>732.00</t>
+        </is>
+      </c>
+      <c r="F121" s="4" t="inlineStr">
+        <is>
+          <t>-26.0</t>
+        </is>
+      </c>
       <c r="G121" s="4" t="n">
         <v>-971</v>
       </c>
@@ -8604,8 +9508,16 @@
           <t>順達</t>
         </is>
       </c>
-      <c r="E122" s="4" t="inlineStr"/>
-      <c r="F122" s="4" t="inlineStr"/>
+      <c r="E122" s="4" t="inlineStr">
+        <is>
+          <t>350.50</t>
+        </is>
+      </c>
+      <c r="F122" s="4" t="inlineStr">
+        <is>
+          <t>-4.5</t>
+        </is>
+      </c>
       <c r="G122" s="4" t="n">
         <v>-911</v>
       </c>
@@ -8636,8 +9548,16 @@
           <t>台燿</t>
         </is>
       </c>
-      <c r="E123" s="4" t="inlineStr"/>
-      <c r="F123" s="4" t="inlineStr"/>
+      <c r="E123" s="4" t="inlineStr">
+        <is>
+          <t>1495.00</t>
+        </is>
+      </c>
+      <c r="F123" s="4" t="inlineStr">
+        <is>
+          <t>-80.0</t>
+        </is>
+      </c>
       <c r="G123" s="4" t="n">
         <v>-908</v>
       </c>
@@ -8668,8 +9588,16 @@
           <t>台星科</t>
         </is>
       </c>
-      <c r="E124" s="4" t="inlineStr"/>
-      <c r="F124" s="4" t="inlineStr"/>
+      <c r="E124" s="4" t="inlineStr">
+        <is>
+          <t>167.50</t>
+        </is>
+      </c>
+      <c r="F124" s="4" t="inlineStr">
+        <is>
+          <t>-7.0</t>
+        </is>
+      </c>
       <c r="G124" s="4" t="n">
         <v>-834</v>
       </c>
@@ -8700,8 +9628,16 @@
           <t>高技</t>
         </is>
       </c>
-      <c r="E125" s="4" t="inlineStr"/>
-      <c r="F125" s="4" t="inlineStr"/>
+      <c r="E125" s="4" t="inlineStr">
+        <is>
+          <t>239.50</t>
+        </is>
+      </c>
+      <c r="F125" s="4" t="inlineStr">
+        <is>
+          <t>-4.0</t>
+        </is>
+      </c>
       <c r="G125" s="4" t="n">
         <v>-829</v>
       </c>
@@ -8736,8 +9672,16 @@
           <t>光洋科</t>
         </is>
       </c>
-      <c r="E126" s="4" t="inlineStr"/>
-      <c r="F126" s="4" t="inlineStr"/>
+      <c r="E126" s="4" t="inlineStr">
+        <is>
+          <t>101.00</t>
+        </is>
+      </c>
+      <c r="F126" s="4" t="inlineStr">
+        <is>
+          <t>-2.5</t>
+        </is>
+      </c>
       <c r="G126" s="4" t="n">
         <v>-724</v>
       </c>
@@ -8768,8 +9712,16 @@
           <t>欣銓</t>
         </is>
       </c>
-      <c r="E127" s="4" t="inlineStr"/>
-      <c r="F127" s="4" t="inlineStr"/>
+      <c r="E127" s="4" t="inlineStr">
+        <is>
+          <t>203.00</t>
+        </is>
+      </c>
+      <c r="F127" s="4" t="inlineStr">
+        <is>
+          <t>-5.5</t>
+        </is>
+      </c>
       <c r="G127" s="4" t="n">
         <v>-721</v>
       </c>
@@ -8800,8 +9752,16 @@
           <t>IET-KY</t>
         </is>
       </c>
-      <c r="E128" s="4" t="inlineStr"/>
-      <c r="F128" s="4" t="inlineStr"/>
+      <c r="E128" s="4" t="inlineStr">
+        <is>
+          <t>588.00</t>
+        </is>
+      </c>
+      <c r="F128" s="4" t="inlineStr">
+        <is>
+          <t>+8.0</t>
+        </is>
+      </c>
       <c r="G128" s="4" t="n">
         <v>-668</v>
       </c>
@@ -8840,8 +9800,16 @@
           <t>萬潤</t>
         </is>
       </c>
-      <c r="E129" s="4" t="inlineStr"/>
-      <c r="F129" s="4" t="inlineStr"/>
+      <c r="E129" s="4" t="inlineStr">
+        <is>
+          <t>1195.00</t>
+        </is>
+      </c>
+      <c r="F129" s="4" t="inlineStr">
+        <is>
+          <t>-70.0</t>
+        </is>
+      </c>
       <c r="G129" s="4" t="n">
         <v>-658</v>
       </c>
@@ -8868,8 +9836,16 @@
           <t>雷科</t>
         </is>
       </c>
-      <c r="E130" s="4" t="inlineStr"/>
-      <c r="F130" s="4" t="inlineStr"/>
+      <c r="E130" s="4" t="inlineStr">
+        <is>
+          <t>103.50</t>
+        </is>
+      </c>
+      <c r="F130" s="4" t="inlineStr">
+        <is>
+          <t>+0.5</t>
+        </is>
+      </c>
       <c r="G130" s="4" t="n">
         <v>-595</v>
       </c>
@@ -8896,8 +9872,16 @@
           <t>健喬</t>
         </is>
       </c>
-      <c r="E131" s="4" t="inlineStr"/>
-      <c r="F131" s="4" t="inlineStr"/>
+      <c r="E131" s="4" t="inlineStr">
+        <is>
+          <t>30.55</t>
+        </is>
+      </c>
+      <c r="F131" s="4" t="inlineStr">
+        <is>
+          <t>-0.7</t>
+        </is>
+      </c>
       <c r="G131" s="4" t="n">
         <v>-554</v>
       </c>
@@ -8924,8 +9908,16 @@
           <t>原相</t>
         </is>
       </c>
-      <c r="E132" s="4" t="inlineStr"/>
-      <c r="F132" s="4" t="inlineStr"/>
+      <c r="E132" s="4" t="inlineStr">
+        <is>
+          <t>195.00</t>
+        </is>
+      </c>
+      <c r="F132" s="4" t="inlineStr">
+        <is>
+          <t>-5.0</t>
+        </is>
+      </c>
       <c r="G132" s="4" t="n">
         <v>-471</v>
       </c>
@@ -8952,8 +9944,16 @@
           <t>漢磊</t>
         </is>
       </c>
-      <c r="E133" s="4" t="inlineStr"/>
-      <c r="F133" s="4" t="inlineStr"/>
+      <c r="E133" s="4" t="inlineStr">
+        <is>
+          <t>61.30</t>
+        </is>
+      </c>
+      <c r="F133" s="4" t="inlineStr">
+        <is>
+          <t>-1.6</t>
+        </is>
+      </c>
       <c r="G133" s="4" t="n">
         <v>-463</v>
       </c>
@@ -8984,8 +9984,16 @@
           <t>廣運</t>
         </is>
       </c>
-      <c r="E134" s="4" t="inlineStr"/>
-      <c r="F134" s="4" t="inlineStr"/>
+      <c r="E134" s="4" t="inlineStr">
+        <is>
+          <t>54.70</t>
+        </is>
+      </c>
+      <c r="F134" s="4" t="inlineStr">
+        <is>
+          <t>-1.5</t>
+        </is>
+      </c>
       <c r="G134" s="4" t="n">
         <v>-450</v>
       </c>
@@ -9016,8 +10024,16 @@
           <t>千如</t>
         </is>
       </c>
-      <c r="E135" s="4" t="inlineStr"/>
-      <c r="F135" s="4" t="inlineStr"/>
+      <c r="E135" s="4" t="inlineStr">
+        <is>
+          <t>44.00</t>
+        </is>
+      </c>
+      <c r="F135" s="4" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
       <c r="G135" s="4" t="n">
         <v>-443</v>
       </c>
@@ -9044,8 +10060,16 @@
           <t>倉和</t>
         </is>
       </c>
-      <c r="E136" s="4" t="inlineStr"/>
-      <c r="F136" s="4" t="inlineStr"/>
+      <c r="E136" s="4" t="inlineStr">
+        <is>
+          <t>196.50</t>
+        </is>
+      </c>
+      <c r="F136" s="4" t="inlineStr">
+        <is>
+          <t>+2.5</t>
+        </is>
+      </c>
       <c r="G136" s="4" t="n">
         <v>-375</v>
       </c>
@@ -9076,8 +10100,16 @@
           <t>聚和</t>
         </is>
       </c>
-      <c r="E137" s="4" t="inlineStr"/>
-      <c r="F137" s="4" t="inlineStr"/>
+      <c r="E137" s="4" t="inlineStr">
+        <is>
+          <t>46.10</t>
+        </is>
+      </c>
+      <c r="F137" s="4" t="inlineStr">
+        <is>
+          <t>-0.9</t>
+        </is>
+      </c>
       <c r="G137" s="4" t="n">
         <v>-362</v>
       </c>
@@ -9104,8 +10136,16 @@
           <t>同亨</t>
         </is>
       </c>
-      <c r="E138" s="4" t="inlineStr"/>
-      <c r="F138" s="4" t="inlineStr"/>
+      <c r="E138" s="4" t="inlineStr">
+        <is>
+          <t>29.35</t>
+        </is>
+      </c>
+      <c r="F138" s="4" t="inlineStr">
+        <is>
+          <t>-0.65</t>
+        </is>
+      </c>
       <c r="G138" s="4" t="n">
         <v>-349</v>
       </c>
@@ -9136,8 +10176,16 @@
           <t>精材</t>
         </is>
       </c>
-      <c r="E139" s="4" t="inlineStr"/>
-      <c r="F139" s="4" t="inlineStr"/>
+      <c r="E139" s="4" t="inlineStr">
+        <is>
+          <t>306.50</t>
+        </is>
+      </c>
+      <c r="F139" s="4" t="inlineStr">
+        <is>
+          <t>+3.0</t>
+        </is>
+      </c>
       <c r="G139" s="4" t="n">
         <v>-341</v>
       </c>
@@ -9168,8 +10216,16 @@
           <t>大江</t>
         </is>
       </c>
-      <c r="E140" s="4" t="inlineStr"/>
-      <c r="F140" s="4" t="inlineStr"/>
+      <c r="E140" s="4" t="inlineStr">
+        <is>
+          <t>125.50</t>
+        </is>
+      </c>
+      <c r="F140" s="4" t="inlineStr">
+        <is>
+          <t>+0.5</t>
+        </is>
+      </c>
       <c r="G140" s="4" t="n">
         <v>-336</v>
       </c>
@@ -9200,8 +10256,16 @@
           <t>先進光</t>
         </is>
       </c>
-      <c r="E141" s="4" t="inlineStr"/>
-      <c r="F141" s="4" t="inlineStr"/>
+      <c r="E141" s="4" t="inlineStr">
+        <is>
+          <t>194.50</t>
+        </is>
+      </c>
+      <c r="F141" s="4" t="inlineStr">
+        <is>
+          <t>+8.5</t>
+        </is>
+      </c>
       <c r="G141" s="4" t="n">
         <v>-329</v>
       </c>
@@ -9232,8 +10296,16 @@
           <t>智通*</t>
         </is>
       </c>
-      <c r="E142" s="4" t="inlineStr"/>
-      <c r="F142" s="4" t="inlineStr"/>
+      <c r="E142" s="4" t="inlineStr">
+        <is>
+          <t>106.00</t>
+        </is>
+      </c>
+      <c r="F142" s="4" t="inlineStr">
+        <is>
+          <t>-6.0</t>
+        </is>
+      </c>
       <c r="G142" s="4" t="n">
         <v>-326</v>
       </c>
@@ -9260,8 +10332,16 @@
           <t>東典光電</t>
         </is>
       </c>
-      <c r="E143" s="4" t="inlineStr"/>
-      <c r="F143" s="4" t="inlineStr"/>
+      <c r="E143" s="4" t="inlineStr">
+        <is>
+          <t>107.50</t>
+        </is>
+      </c>
+      <c r="F143" s="4" t="inlineStr">
+        <is>
+          <t>+6.5</t>
+        </is>
+      </c>
       <c r="G143" s="4" t="n">
         <v>-318</v>
       </c>
@@ -9288,8 +10368,16 @@
           <t>亞泰金屬</t>
         </is>
       </c>
-      <c r="E144" s="4" t="inlineStr"/>
-      <c r="F144" s="4" t="inlineStr"/>
+      <c r="E144" s="4" t="inlineStr">
+        <is>
+          <t>443.00</t>
+        </is>
+      </c>
+      <c r="F144" s="4" t="inlineStr">
+        <is>
+          <t>-17.0</t>
+        </is>
+      </c>
       <c r="G144" s="4" t="n">
         <v>-315</v>
       </c>
@@ -9320,8 +10408,16 @@
           <t>建榮</t>
         </is>
       </c>
-      <c r="E145" s="4" t="inlineStr"/>
-      <c r="F145" s="4" t="inlineStr"/>
+      <c r="E145" s="4" t="inlineStr">
+        <is>
+          <t>78.60</t>
+        </is>
+      </c>
+      <c r="F145" s="4" t="inlineStr">
+        <is>
+          <t>+0.4</t>
+        </is>
+      </c>
       <c r="G145" s="4" t="n">
         <v>-302</v>
       </c>
@@ -9348,8 +10444,16 @@
           <t>博智</t>
         </is>
       </c>
-      <c r="E146" s="4" t="inlineStr"/>
-      <c r="F146" s="4" t="inlineStr"/>
+      <c r="E146" s="4" t="inlineStr">
+        <is>
+          <t>316.50</t>
+        </is>
+      </c>
+      <c r="F146" s="4" t="inlineStr">
+        <is>
+          <t>-8.0</t>
+        </is>
+      </c>
       <c r="G146" s="4" t="n">
         <v>-301</v>
       </c>
@@ -9376,8 +10480,16 @@
           <t>晟德</t>
         </is>
       </c>
-      <c r="E147" s="4" t="inlineStr"/>
-      <c r="F147" s="4" t="inlineStr"/>
+      <c r="E147" s="4" t="inlineStr">
+        <is>
+          <t>32.95</t>
+        </is>
+      </c>
+      <c r="F147" s="4" t="inlineStr">
+        <is>
+          <t>+0.55</t>
+        </is>
+      </c>
       <c r="G147" s="4" t="n">
         <v>-267</v>
       </c>
@@ -9408,8 +10520,16 @@
           <t>力旺</t>
         </is>
       </c>
-      <c r="E148" s="4" t="inlineStr"/>
-      <c r="F148" s="4" t="inlineStr"/>
+      <c r="E148" s="4" t="inlineStr">
+        <is>
+          <t>2155.00</t>
+        </is>
+      </c>
+      <c r="F148" s="4" t="inlineStr">
+        <is>
+          <t>-55.0</t>
+        </is>
+      </c>
       <c r="G148" s="4" t="n">
         <v>-265</v>
       </c>
@@ -9440,8 +10560,16 @@
           <t>雙鴻</t>
         </is>
       </c>
-      <c r="E149" s="4" t="inlineStr"/>
-      <c r="F149" s="4" t="inlineStr"/>
+      <c r="E149" s="4" t="inlineStr">
+        <is>
+          <t>969.00</t>
+        </is>
+      </c>
+      <c r="F149" s="4" t="inlineStr">
+        <is>
+          <t>-24.0</t>
+        </is>
+      </c>
       <c r="G149" s="4" t="n">
         <v>-256</v>
       </c>
@@ -9472,8 +10600,16 @@
           <t>茂迪</t>
         </is>
       </c>
-      <c r="E150" s="4" t="inlineStr"/>
-      <c r="F150" s="4" t="inlineStr"/>
+      <c r="E150" s="4" t="inlineStr">
+        <is>
+          <t>24.55</t>
+        </is>
+      </c>
+      <c r="F150" s="4" t="inlineStr">
+        <is>
+          <t>-0.4</t>
+        </is>
+      </c>
       <c r="G150" s="4" t="n">
         <v>-238</v>
       </c>
@@ -9500,8 +10636,16 @@
           <t>良維</t>
         </is>
       </c>
-      <c r="E151" s="4" t="inlineStr"/>
-      <c r="F151" s="4" t="inlineStr"/>
+      <c r="E151" s="4" t="inlineStr">
+        <is>
+          <t>211.50</t>
+        </is>
+      </c>
+      <c r="F151" s="4" t="inlineStr">
+        <is>
+          <t>-3.0</t>
+        </is>
+      </c>
       <c r="G151" s="4" t="n">
         <v>-237</v>
       </c>
@@ -9528,8 +10672,16 @@
           <t>璟德</t>
         </is>
       </c>
-      <c r="E152" s="4" t="inlineStr"/>
-      <c r="F152" s="4" t="inlineStr"/>
+      <c r="E152" s="4" t="inlineStr">
+        <is>
+          <t>256.50</t>
+        </is>
+      </c>
+      <c r="F152" s="4" t="inlineStr">
+        <is>
+          <t>+23.0</t>
+        </is>
+      </c>
       <c r="G152" s="4" t="n">
         <v>-236</v>
       </c>
@@ -9556,8 +10708,16 @@
           <t>曜越</t>
         </is>
       </c>
-      <c r="E153" s="4" t="inlineStr"/>
-      <c r="F153" s="4" t="inlineStr"/>
+      <c r="E153" s="4" t="inlineStr">
+        <is>
+          <t>23.80</t>
+        </is>
+      </c>
+      <c r="F153" s="4" t="inlineStr">
+        <is>
+          <t>+2.15</t>
+        </is>
+      </c>
       <c r="G153" s="4" t="n">
         <v>-236</v>
       </c>
@@ -9584,8 +10744,16 @@
           <t>立端</t>
         </is>
       </c>
-      <c r="E154" s="4" t="inlineStr"/>
-      <c r="F154" s="4" t="inlineStr"/>
+      <c r="E154" s="4" t="inlineStr">
+        <is>
+          <t>81.40</t>
+        </is>
+      </c>
+      <c r="F154" s="4" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
       <c r="G154" s="4" t="n">
         <v>-213</v>
       </c>
@@ -9616,8 +10784,16 @@
           <t>茂達</t>
         </is>
       </c>
-      <c r="E155" s="4" t="inlineStr"/>
-      <c r="F155" s="4" t="inlineStr"/>
+      <c r="E155" s="4" t="inlineStr">
+        <is>
+          <t>282.50</t>
+        </is>
+      </c>
+      <c r="F155" s="4" t="inlineStr">
+        <is>
+          <t>-7.5</t>
+        </is>
+      </c>
       <c r="G155" s="4" t="n">
         <v>-200</v>
       </c>
@@ -9648,8 +10824,16 @@
           <t>德宏</t>
         </is>
       </c>
-      <c r="E156" s="4" t="inlineStr"/>
-      <c r="F156" s="4" t="inlineStr"/>
+      <c r="E156" s="4" t="inlineStr">
+        <is>
+          <t>174.50</t>
+        </is>
+      </c>
+      <c r="F156" s="4" t="inlineStr">
+        <is>
+          <t>-1.5</t>
+        </is>
+      </c>
       <c r="G156" s="4" t="n">
         <v>-190</v>
       </c>
@@ -9676,8 +10860,16 @@
           <t>太景*-KY</t>
         </is>
       </c>
-      <c r="E157" s="4" t="inlineStr"/>
-      <c r="F157" s="4" t="inlineStr"/>
+      <c r="E157" s="4" t="inlineStr">
+        <is>
+          <t>9.05</t>
+        </is>
+      </c>
+      <c r="F157" s="4" t="inlineStr">
+        <is>
+          <t>+0.05</t>
+        </is>
+      </c>
       <c r="G157" s="4" t="n">
         <v>-185</v>
       </c>
@@ -9704,8 +10896,16 @@
           <t>鑫聯大投控</t>
         </is>
       </c>
-      <c r="E158" s="4" t="inlineStr"/>
-      <c r="F158" s="4" t="inlineStr"/>
+      <c r="E158" s="4" t="inlineStr">
+        <is>
+          <t>67.80</t>
+        </is>
+      </c>
+      <c r="F158" s="4" t="inlineStr">
+        <is>
+          <t>+0.3</t>
+        </is>
+      </c>
       <c r="G158" s="4" t="n">
         <v>-180</v>
       </c>

--- a/StockInfo/otc_analysis_result.xlsx
+++ b/StockInfo/otc_analysis_result.xlsx
@@ -3917,12 +3917,12 @@
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>6217</t>
+          <t>6127</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>中探針</t>
+          <t>九豪</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
@@ -3931,45 +3931,45 @@
         </is>
       </c>
       <c r="D116" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>01, 04</t>
         </is>
       </c>
       <c r="F116" s="4" t="n">
-        <v>1315</v>
+        <v>1696</v>
       </c>
       <c r="G116" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H116" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>-891</v>
+        <v>-1272</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>424</v>
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>[('neutral', '04'), ('sell', '03'), ('neutral', '02'), ('buy', '01'), ('neutral', '31')]</t>
+          <t>[('buy', '04'), ('neutral', '03'), ('sell', '02'), ('buy', '01'), ('neutral', '31')]</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>6127</t>
+          <t>6217</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>九豪</t>
+          <t>中探針</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
@@ -3978,33 +3978,33 @@
         </is>
       </c>
       <c r="D117" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>01, 04</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F117" s="4" t="n">
-        <v>1696</v>
+        <v>1315</v>
       </c>
       <c r="G117" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H117" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>-1272</v>
+        <v>-891</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>424</v>
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>[('buy', '04'), ('neutral', '03'), ('sell', '02'), ('buy', '01'), ('neutral', '31')]</t>
+          <t>[('neutral', '04'), ('sell', '03'), ('neutral', '02'), ('buy', '01'), ('neutral', '31')]</t>
         </is>
       </c>
     </row>

--- a/StockInfo/otc_analysis_result.xlsx
+++ b/StockInfo/otc_analysis_result.xlsx
@@ -3917,12 +3917,12 @@
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>6127</t>
+          <t>6217</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>九豪</t>
+          <t>中探針</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
@@ -3931,45 +3931,45 @@
         </is>
       </c>
       <c r="D116" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>01, 04</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F116" s="4" t="n">
-        <v>1696</v>
+        <v>1315</v>
       </c>
       <c r="G116" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H116" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>-1272</v>
+        <v>-891</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>424</v>
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>[('buy', '04'), ('neutral', '03'), ('sell', '02'), ('buy', '01'), ('neutral', '31')]</t>
+          <t>[('neutral', '04'), ('sell', '03'), ('neutral', '02'), ('buy', '01'), ('neutral', '31')]</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>6217</t>
+          <t>6127</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>中探針</t>
+          <t>九豪</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
@@ -3978,33 +3978,33 @@
         </is>
       </c>
       <c r="D117" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>01, 04</t>
         </is>
       </c>
       <c r="F117" s="4" t="n">
-        <v>1315</v>
+        <v>1696</v>
       </c>
       <c r="G117" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H117" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>-891</v>
+        <v>-1272</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>424</v>
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>[('neutral', '04'), ('sell', '03'), ('neutral', '02'), ('buy', '01'), ('neutral', '31')]</t>
+          <t>[('buy', '04'), ('neutral', '03'), ('sell', '02'), ('buy', '01'), ('neutral', '31')]</t>
         </is>
       </c>
     </row>
